--- a/data/IF.MI.xlsx
+++ b/data/IF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2009" uniqueCount="2009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2010" uniqueCount="2010">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.737078666687</t>
+    <t xml:space="preserve">15.7370796203613</t>
   </si>
   <si>
     <t xml:space="preserve">IF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3903465270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3232383728027</t>
+    <t xml:space="preserve">15.3903503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3232374191284</t>
   </si>
   <si>
     <t xml:space="preserve">14.5458917617798</t>
@@ -59,163 +59,163 @@
     <t xml:space="preserve">14.3781175613403</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4284524917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.176794052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8646602630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8524293899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4955606460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.640962600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.434042930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3735704421997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3959398269653</t>
+    <t xml:space="preserve">14.4284496307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1767911911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8646612167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8524312973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4955596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6409664154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4340438842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3735723495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3959379196167</t>
   </si>
   <si>
     <t xml:space="preserve">15.9384050369263</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9439964294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5637149810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1061763763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0502548217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7706336975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1722393035889</t>
+    <t xml:space="preserve">15.943998336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5637130737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1061782836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.050256729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7706317901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1722412109375</t>
   </si>
   <si>
     <t xml:space="preserve">14.9597320556641</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5403003692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0583047866821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0974540710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7405815124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7685461044312</t>
+    <t xml:space="preserve">14.5402984619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0583057403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0974531173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7405834197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7685470581055</t>
   </si>
   <si>
     <t xml:space="preserve">13.8244676589966</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5347108840942</t>
+    <t xml:space="preserve">14.5347061157227</t>
   </si>
   <si>
     <t xml:space="preserve">14.4396362304688</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3501586914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2718648910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3333778381348</t>
+    <t xml:space="preserve">14.3501596450806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2718639373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3333797454834</t>
   </si>
   <si>
     <t xml:space="preserve">15.4350862503052</t>
   </si>
   <si>
-    <t xml:space="preserve">14.976508140564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7416257858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2057991027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0995435714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0436162948608</t>
+    <t xml:space="preserve">14.9765110015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7416276931763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2057971954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0995426177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0436182022095</t>
   </si>
   <si>
     <t xml:space="preserve">15.4966039657593</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2840929031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9876899719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4452276229858</t>
+    <t xml:space="preserve">15.2840900421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9876937866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4452295303345</t>
   </si>
   <si>
     <t xml:space="preserve">14.5570755004883</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1656074523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4843730926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7192573547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1834268569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3791627883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.999924659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.234806060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0949954986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9663696289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1173629760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1403408050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4849720001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7204723358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4160442352295</t>
+    <t xml:space="preserve">14.1656055450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4843740463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.719256401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1834297180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3791637420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9999198913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2348041534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0949935913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9663677215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1173610687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1403369903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4849739074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7204704284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4160461425781</t>
   </si>
   <si>
     <t xml:space="preserve">15.8473997116089</t>
@@ -224,37 +224,37 @@
     <t xml:space="preserve">16.3815841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6004133224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6808252334595</t>
+    <t xml:space="preserve">15.6004123687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6808271408081</t>
   </si>
   <si>
     <t xml:space="preserve">15.7842178344727</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8876075744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.634877204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2787551879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4280967712402</t>
+    <t xml:space="preserve">15.8876085281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6348743438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.278754234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4280948638916</t>
   </si>
   <si>
     <t xml:space="preserve">15.2385473251343</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1409015655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3821439743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9570960998535</t>
+    <t xml:space="preserve">15.1408996582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3821487426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9570999145508</t>
   </si>
   <si>
     <t xml:space="preserve">14.8479604721069</t>
@@ -263,64 +263,64 @@
     <t xml:space="preserve">14.5894870758057</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6239471435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.70436668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.555025100708</t>
+    <t xml:space="preserve">14.6239500045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7043657302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5550231933594</t>
   </si>
   <si>
     <t xml:space="preserve">14.3482427597046</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1184892654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8427820205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1644411087036</t>
+    <t xml:space="preserve">14.1184902191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8427829742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1644382476807</t>
   </si>
   <si>
     <t xml:space="preserve">13.6704626083374</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6417446136475</t>
+    <t xml:space="preserve">13.6417455673218</t>
   </si>
   <si>
     <t xml:space="preserve">13.325831413269</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1075639724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8375997543335</t>
+    <t xml:space="preserve">13.1075630187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8376016616821</t>
   </si>
   <si>
     <t xml:space="preserve">12.9811983108521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7629289627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4814786911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6365633010864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6882600784302</t>
+    <t xml:space="preserve">12.7629299163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4814796447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6365642547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6882581710815</t>
   </si>
   <si>
     <t xml:space="preserve">12.3493690490723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5791244506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9352474212646</t>
+    <t xml:space="preserve">12.5791234970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9352464675903</t>
   </si>
   <si>
     <t xml:space="preserve">14.514817237854</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">13.785343170166</t>
   </si>
   <si>
-    <t xml:space="preserve">13.561333656311</t>
+    <t xml:space="preserve">13.5613327026367</t>
   </si>
   <si>
     <t xml:space="preserve">13.664722442627</t>
@@ -344,58 +344,58 @@
     <t xml:space="preserve">13.2683925628662</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3602933883667</t>
+    <t xml:space="preserve">13.3602962493896</t>
   </si>
   <si>
     <t xml:space="preserve">13.1535148620605</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639644622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7801609039307</t>
+    <t xml:space="preserve">12.9639663696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7801637649536</t>
   </si>
   <si>
     <t xml:space="preserve">12.5504064559937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2057733535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0564308166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9185771942139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6084060668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2287473678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6537971496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5963554382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9869403839111</t>
+    <t xml:space="preserve">12.2057704925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0564298629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9185762405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6084070205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2287492752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6537961959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5963573455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9869432449341</t>
   </si>
   <si>
     <t xml:space="preserve">12.1196136474609</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1781778335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2643375396729</t>
+    <t xml:space="preserve">10.1781768798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2643356323242</t>
   </si>
   <si>
     <t xml:space="preserve">10.3217754364014</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4251651763916</t>
+    <t xml:space="preserve">10.425163269043</t>
   </si>
   <si>
     <t xml:space="preserve">10.4366521835327</t>
@@ -404,16 +404,16 @@
     <t xml:space="preserve">10.4538841247559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93693447113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58081245422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5693244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7301549911499</t>
+    <t xml:space="preserve">9.93693351745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58081340789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56932640075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73015403747559</t>
   </si>
   <si>
     <t xml:space="preserve">9.76461791992188</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">10.8272380828857</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2810039520264</t>
+    <t xml:space="preserve">11.281005859375</t>
   </si>
   <si>
     <t xml:space="preserve">11.4877853393555</t>
@@ -431,22 +431,22 @@
     <t xml:space="preserve">11.3269557952881</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5165042877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2580289840698</t>
+    <t xml:space="preserve">11.516505241394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2580299377441</t>
   </si>
   <si>
     <t xml:space="preserve">11.4992742538452</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2293109893799</t>
+    <t xml:space="preserve">11.2293090820312</t>
   </si>
   <si>
     <t xml:space="preserve">11.0455055236816</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8617010116577</t>
+    <t xml:space="preserve">10.861701965332</t>
   </si>
   <si>
     <t xml:space="preserve">10.6032257080078</t>
@@ -455,22 +455,22 @@
     <t xml:space="preserve">10.9995546340942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7175397872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4188585281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.579686164856</t>
+    <t xml:space="preserve">11.7175416946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4188575744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5796871185303</t>
   </si>
   <si>
     <t xml:space="preserve">11.1144323348999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1431512832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6026639938354</t>
+    <t xml:space="preserve">11.1431522369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6026630401611</t>
   </si>
   <si>
     <t xml:space="preserve">11.7405157089233</t>
@@ -479,49 +479,49 @@
     <t xml:space="preserve">11.4016265869141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6543607711792</t>
+    <t xml:space="preserve">11.6543588638306</t>
   </si>
   <si>
     <t xml:space="preserve">11.5567140579224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4533224105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3843946456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2867498397827</t>
+    <t xml:space="preserve">11.4533214569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3843975067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2867488861084</t>
   </si>
   <si>
     <t xml:space="preserve">10.9880666732788</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9765768051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0397596359253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0282754898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0972013473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9708366394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9650897979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1201753616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2063341140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1891012191772</t>
+    <t xml:space="preserve">10.9765787124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0397615432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0282745361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0972003936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9708337783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9650907516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1201763153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.206335067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1891021728516</t>
   </si>
   <si>
     <t xml:space="preserve">11.4303464889526</t>
@@ -530,28 +530,28 @@
     <t xml:space="preserve">11.8324193954468</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3149061203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.395320892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9587841033936</t>
+    <t xml:space="preserve">12.3149080276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3953199386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9587831497192</t>
   </si>
   <si>
     <t xml:space="preserve">11.6945657730103</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7749795913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6715898513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6888208389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5739440917969</t>
+    <t xml:space="preserve">11.774977684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6715888977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6888217926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5739421844482</t>
   </si>
   <si>
     <t xml:space="preserve">11.7692365646362</t>
@@ -560,22 +560,22 @@
     <t xml:space="preserve">12.0621747970581</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0219697952271</t>
+    <t xml:space="preserve">12.0219678878784</t>
   </si>
   <si>
     <t xml:space="preserve">11.660101890564</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5107612609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4935293197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5279932022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7060518264771</t>
+    <t xml:space="preserve">11.5107622146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4935302734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5279903411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7060527801514</t>
   </si>
   <si>
     <t xml:space="preserve">11.7577476501465</t>
@@ -584,34 +584,34 @@
     <t xml:space="preserve">12.0277118682861</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4068078994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.434965133667</t>
+    <t xml:space="preserve">12.4068088531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4349660873413</t>
   </si>
   <si>
     <t xml:space="preserve">13.6991834640503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7279014587402</t>
+    <t xml:space="preserve">13.7279043197632</t>
   </si>
   <si>
     <t xml:space="preserve">13.8657569885254</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9519138336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1759271621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3712215423584</t>
+    <t xml:space="preserve">13.9519176483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.175929069519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3712205886841</t>
   </si>
   <si>
     <t xml:space="preserve">14.4631223678589</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8824253082275</t>
+    <t xml:space="preserve">14.8824262619019</t>
   </si>
   <si>
     <t xml:space="preserve">14.9628400802612</t>
@@ -620,181 +620,181 @@
     <t xml:space="preserve">15.1064386367798</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2270565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.135157585144</t>
+    <t xml:space="preserve">15.2270584106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1351585388184</t>
   </si>
   <si>
     <t xml:space="preserve">14.9456062316895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7158527374268</t>
+    <t xml:space="preserve">14.7158555984497</t>
   </si>
   <si>
     <t xml:space="preserve">14.7330837249756</t>
   </si>
   <si>
-    <t xml:space="preserve">14.509072303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5952301025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5435361862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3827075958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0725383758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0610475540161</t>
+    <t xml:space="preserve">14.5090732574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5952291488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5435352325439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3827085494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0725364685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0610485076904</t>
   </si>
   <si>
     <t xml:space="preserve">13.6474895477295</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6876974105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5900506973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5383529663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0501251220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1190500259399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1822347640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7514410018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2109537124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4407091140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4234790802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2856245040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1414651870728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2735729217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1931591033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3597316741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9398632049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6871337890625</t>
+    <t xml:space="preserve">13.6876964569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5900497436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5383567810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0501222610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1190490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1822338104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7514419555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2109527587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4407081604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4234752655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.285623550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1414642333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2735738754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1931581497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3597326278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9398641586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6871328353882</t>
   </si>
   <si>
     <t xml:space="preserve">14.3884506225586</t>
   </si>
   <si>
-    <t xml:space="preserve">14.474609375</t>
+    <t xml:space="preserve">14.4746103286743</t>
   </si>
   <si>
     <t xml:space="preserve">14.784779548645</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9341230392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2213163375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5831785202026</t>
+    <t xml:space="preserve">14.9341201782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2213153839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5831813812256</t>
   </si>
   <si>
     <t xml:space="preserve">15.4970235824585</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4510726928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3361930847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8364753723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9915590286255</t>
+    <t xml:space="preserve">15.4510698318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3361921310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8364725112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9915618896484</t>
   </si>
   <si>
     <t xml:space="preserve">15.2959852218628</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1638765335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0375099182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.089204788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0719747543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8307294845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6469259262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5320501327515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2333650588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5263032913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4171724319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.394193649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0489988327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7618045806885</t>
+    <t xml:space="preserve">15.1638793945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0375089645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.089207649231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0719766616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8307304382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6469249725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5320491790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2333660125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5263071060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4171705245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3941946029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.048996925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7618055343628</t>
   </si>
   <si>
     <t xml:space="preserve">14.6584148406982</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8766813278198</t>
+    <t xml:space="preserve">14.8766822814941</t>
   </si>
   <si>
     <t xml:space="preserve">15.3936309814453</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8531446456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8416538238525</t>
+    <t xml:space="preserve">15.8531427383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8416566848755</t>
   </si>
   <si>
     <t xml:space="preserve">16.0369472503662</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">16.9559707641602</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0880813598633</t>
+    <t xml:space="preserve">17.0880794525146</t>
   </si>
   <si>
     <t xml:space="preserve">16.6343097686768</t>
@@ -815,25 +815,25 @@
     <t xml:space="preserve">16.6113395690918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0829010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8870449066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9444847106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3465538024902</t>
+    <t xml:space="preserve">16.0828990936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8870468139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9444808959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3465557098389</t>
   </si>
   <si>
     <t xml:space="preserve">17.4844093322754</t>
   </si>
   <si>
-    <t xml:space="preserve">17.593542098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.059362411499</t>
+    <t xml:space="preserve">17.5935440063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0593605041504</t>
   </si>
   <si>
     <t xml:space="preserve">17.1684970855713</t>
@@ -842,19 +842,19 @@
     <t xml:space="preserve">17.6911907196045</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9152011871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7365760803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5522136688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8164291381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9944953918457</t>
+    <t xml:space="preserve">17.9152030944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7365779876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5522117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.816427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9944915771484</t>
   </si>
   <si>
     <t xml:space="preserve">20.942232131958</t>
@@ -863,70 +863,70 @@
     <t xml:space="preserve">20.522928237915</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8503303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7354507446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6780128479004</t>
+    <t xml:space="preserve">20.8503265380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7354564666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.678014755249</t>
   </si>
   <si>
     <t xml:space="preserve">20.6492958068848</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3218955993652</t>
+    <t xml:space="preserve">20.3218898773193</t>
   </si>
   <si>
     <t xml:space="preserve">20.5631351470947</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6378078460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8388423919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8216114044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6090908050537</t>
+    <t xml:space="preserve">20.6378059387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8388385772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8216094970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6090869903564</t>
   </si>
   <si>
     <t xml:space="preserve">21.1088066101074</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4132308959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2409133911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.177734375</t>
+    <t xml:space="preserve">21.4132328033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2409152984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1777305603027</t>
   </si>
   <si>
     <t xml:space="preserve">21.0226459503174</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9594631195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3098430633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5855503082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3155822753906</t>
+    <t xml:space="preserve">20.9594669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3098392486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5855522155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3155860900879</t>
   </si>
   <si>
     <t xml:space="preserve">22.2690715789795</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1369609832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9818801879883</t>
+    <t xml:space="preserve">22.136962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9818782806396</t>
   </si>
   <si>
     <t xml:space="preserve">22.2288646697998</t>
@@ -935,28 +935,28 @@
     <t xml:space="preserve">22.745813369751</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9335079193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5815868377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3938941955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4671669006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4583301544189</t>
+    <t xml:space="preserve">22.9335041046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5815830230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3938961029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4671726226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4583282470703</t>
   </si>
   <si>
     <t xml:space="preserve">21.1035194396973</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8161163330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6342906951904</t>
+    <t xml:space="preserve">20.8161201477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6342926025391</t>
   </si>
   <si>
     <t xml:space="preserve">20.692943572998</t>
@@ -965,55 +965,55 @@
     <t xml:space="preserve">20.587366104126</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2969913482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5872821807861</t>
+    <t xml:space="preserve">19.296989440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5872840881348</t>
   </si>
   <si>
     <t xml:space="preserve">19.5433387756348</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9656429290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4817867279053</t>
+    <t xml:space="preserve">19.9656410217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4817905426025</t>
   </si>
   <si>
     <t xml:space="preserve">20.4700603485107</t>
   </si>
   <si>
-    <t xml:space="preserve">20.528715133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4114055633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2706413269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3058338165283</t>
+    <t xml:space="preserve">20.5287132263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4114074707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2706432342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3058319091797</t>
   </si>
   <si>
     <t xml:space="preserve">19.7955455780029</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6078548431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8835258483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2471790313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0594844818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1767959594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7515983581543</t>
+    <t xml:space="preserve">19.607852935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8835277557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2471771240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0594863891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1767921447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7515964508057</t>
   </si>
   <si>
     <t xml:space="preserve">20.6988086700439</t>
@@ -1025,13 +1025,13 @@
     <t xml:space="preserve">20.5521755218506</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5052509307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7046756744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.440731048584</t>
+    <t xml:space="preserve">20.5052528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7046737670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4407348632812</t>
   </si>
   <si>
     <t xml:space="preserve">20.1474647521973</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">20.0477542877197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0008296966553</t>
+    <t xml:space="preserve">20.0008335113525</t>
   </si>
   <si>
     <t xml:space="preserve">20.4876556396484</t>
@@ -1049,67 +1049,67 @@
     <t xml:space="preserve">20.6694850921631</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6460208892822</t>
+    <t xml:space="preserve">20.6460227966309</t>
   </si>
   <si>
     <t xml:space="preserve">20.863037109375</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9334239959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.009672164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9275588989258</t>
+    <t xml:space="preserve">20.933422088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0096702575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9275569915771</t>
   </si>
   <si>
     <t xml:space="preserve">21.1152496337891</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2560195922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2912101745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5551490783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.748706817627</t>
+    <t xml:space="preserve">21.2560176849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2912063598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5551509857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7487087249756</t>
   </si>
   <si>
     <t xml:space="preserve">21.6313991546631</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6079349517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6431274414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8366851806641</t>
+    <t xml:space="preserve">21.6079406738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6431293487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8366889953613</t>
   </si>
   <si>
     <t xml:space="preserve">22.0830326080322</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7604331970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4642772674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9041805267334</t>
+    <t xml:space="preserve">21.7604351043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4642791748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9041786193848</t>
   </si>
   <si>
     <t xml:space="preserve">22.6402397155762</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9686965942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7575435638428</t>
+    <t xml:space="preserve">22.9686985015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7575454711914</t>
   </si>
   <si>
     <t xml:space="preserve">23.2854251861572</t>
@@ -1121,34 +1121,34 @@
     <t xml:space="preserve">23.7722492218018</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0068626403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2708072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8719615936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1007099151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.047924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5435028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5669651031494</t>
+    <t xml:space="preserve">24.0068645477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.270809173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8719635009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1007118225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0479183197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5434989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5669631958008</t>
   </si>
   <si>
     <t xml:space="preserve">24.1593627929688</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3529224395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3059978485107</t>
+    <t xml:space="preserve">24.3529186248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3059959411621</t>
   </si>
   <si>
     <t xml:space="preserve">23.8543643951416</t>
@@ -1157,88 +1157,88 @@
     <t xml:space="preserve">24.036190032959</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8367671966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8191719055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9716701507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7898464202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6373462677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1153335571289</t>
+    <t xml:space="preserve">23.8367729187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8191738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9716739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7898483276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6373443603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1153316497803</t>
   </si>
   <si>
     <t xml:space="preserve">23.7077312469482</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9012870788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1652297973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5347461700439</t>
+    <t xml:space="preserve">23.9012908935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1652317047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5347480773926</t>
   </si>
   <si>
     <t xml:space="preserve">24.3411903381348</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0831127166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7400341033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7107086181641</t>
+    <t xml:space="preserve">24.0831146240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7400321960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7107028961182</t>
   </si>
   <si>
     <t xml:space="preserve">24.4936866760254</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6989784240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0684909820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7078151702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7136821746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1594467163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4937725067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3823299407959</t>
+    <t xml:space="preserve">24.698974609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0684967041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7078170776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.713680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.15944480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4937705993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3823261260986</t>
   </si>
   <si>
     <t xml:space="preserve">26.5876159667969</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1301193237305</t>
+    <t xml:space="preserve">26.1301212310791</t>
   </si>
   <si>
     <t xml:space="preserve">26.5993461608887</t>
   </si>
   <si>
-    <t xml:space="preserve">26.822229385376</t>
+    <t xml:space="preserve">26.8222312927246</t>
   </si>
   <si>
     <t xml:space="preserve">27.1330947875977</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7548179626465</t>
+    <t xml:space="preserve">27.7548198699951</t>
   </si>
   <si>
     <t xml:space="preserve">28.0656852722168</t>
@@ -1247,49 +1247,49 @@
     <t xml:space="preserve">28.2064514160156</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8984794616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7489604949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4997158050537</t>
+    <t xml:space="preserve">26.8984832763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7489547729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4997177124023</t>
   </si>
   <si>
     <t xml:space="preserve">28.8281803131104</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8926963806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6580867767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0539608001709</t>
+    <t xml:space="preserve">28.8927021026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6580848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0539531707764</t>
   </si>
   <si>
     <t xml:space="preserve">26.927806854248</t>
   </si>
   <si>
-    <t xml:space="preserve">26.528959274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2152080535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6404075622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5378074645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.631649017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6668395996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8428020477295</t>
+    <t xml:space="preserve">26.5289611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2152099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.64040184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5378017425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6316509246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6668376922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8428058624268</t>
   </si>
   <si>
     <t xml:space="preserve">28.3237609863281</t>
@@ -1298,67 +1298,67 @@
     <t xml:space="preserve">27.5671310424805</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6023216247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4556903839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5026111602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0803050994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8163681030273</t>
+    <t xml:space="preserve">27.6023235321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4556922912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5026168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0803070068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8163661956787</t>
   </si>
   <si>
     <t xml:space="preserve">26.3060817718506</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9365653991699</t>
+    <t xml:space="preserve">25.9365634918213</t>
   </si>
   <si>
     <t xml:space="preserve">24.5992660522461</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8954200744629</t>
+    <t xml:space="preserve">23.8954219818115</t>
   </si>
   <si>
     <t xml:space="preserve">22.9511032104492</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8279285430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6021595001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7164897918701</t>
+    <t xml:space="preserve">22.8279266357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6021575927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7164878845215</t>
   </si>
   <si>
     <t xml:space="preserve">22.7282180786133</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3176460266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9833183288574</t>
+    <t xml:space="preserve">22.3176422119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9833202362061</t>
   </si>
   <si>
     <t xml:space="preserve">22.6754283905029</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4056262969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.610912322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7927417755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2355270385742</t>
+    <t xml:space="preserve">22.4056243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6109142303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7927379608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2355289459229</t>
   </si>
   <si>
     <t xml:space="preserve">21.5492839813232</t>
@@ -1367,22 +1367,22 @@
     <t xml:space="preserve">21.5199565887451</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7311096191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8249530792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4495754241943</t>
+    <t xml:space="preserve">21.731107711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8249588012695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4495697021484</t>
   </si>
   <si>
     <t xml:space="preserve">20.9040966033936</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4026508331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.877742767334</t>
+    <t xml:space="preserve">21.4026527404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8777446746826</t>
   </si>
   <si>
     <t xml:space="preserve">22.4701442718506</t>
@@ -1391,10 +1391,10 @@
     <t xml:space="preserve">21.1914978027344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1093864440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0565986633301</t>
+    <t xml:space="preserve">21.1093826293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0565948486328</t>
   </si>
   <si>
     <t xml:space="preserve">21.7135143280029</t>
@@ -1403,97 +1403,97 @@
     <t xml:space="preserve">22.7047576904297</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9130210876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0449466705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3440818786621</t>
+    <t xml:space="preserve">23.9130153656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0449485778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3440780639648</t>
   </si>
   <si>
     <t xml:space="preserve">23.7546539306641</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7663860321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4496574401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5200424194336</t>
+    <t xml:space="preserve">23.7663879394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4496555328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5200462341309</t>
   </si>
   <si>
     <t xml:space="preserve">22.3469715118408</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0273513793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1563873291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8631229400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0508117675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9569683074951</t>
+    <t xml:space="preserve">23.0273494720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1563892364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8631210327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0508136749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9569664001465</t>
   </si>
   <si>
     <t xml:space="preserve">22.781005859375</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5229339599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4994735717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2765884399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9452342987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4525489807129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0771675109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2208251953125</t>
+    <t xml:space="preserve">22.5229301452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4994697570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2765827178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9452362060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4525470733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0771656036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2208232879639</t>
   </si>
   <si>
     <t xml:space="preserve">20.7398681640625</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2677459716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6489105224609</t>
+    <t xml:space="preserve">21.2677478790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6489124298096</t>
   </si>
   <si>
     <t xml:space="preserve">19.4260272979736</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7750587463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1621704101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9158248901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3733215332031</t>
+    <t xml:space="preserve">20.7750568389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1621723175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9158267974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3733234405518</t>
   </si>
   <si>
     <t xml:space="preserve">21.3615913391113</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3263988494873</t>
+    <t xml:space="preserve">21.3264007568359</t>
   </si>
   <si>
     <t xml:space="preserve">21.2794761657715</t>
@@ -1514,31 +1514,31 @@
     <t xml:space="preserve">20.0125637054443</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3321838378906</t>
+    <t xml:space="preserve">19.332181930542</t>
   </si>
   <si>
     <t xml:space="preserve">19.015453338623</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3556423187256</t>
+    <t xml:space="preserve">19.3556442260742</t>
   </si>
   <si>
     <t xml:space="preserve">19.0975685119629</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0858364105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0712146759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9891033172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8394908905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3468036651611</t>
+    <t xml:space="preserve">19.0858383178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0712184906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9891014099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8394927978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3468055725098</t>
   </si>
   <si>
     <t xml:space="preserve">18.5227661132812</t>
@@ -1547,49 +1547,49 @@
     <t xml:space="preserve">19.4377613067627</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2618007659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9919929504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3233432769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3614273071289</t>
+    <t xml:space="preserve">19.2617988586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9919910430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3233451843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3614292144775</t>
   </si>
   <si>
     <t xml:space="preserve">18.6987247467041</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9596939086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7221851348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1210327148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2735290527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4142971038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1533317565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7310256958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5785293579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8131427764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6958389282227</t>
+    <t xml:space="preserve">17.9596900939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.722188949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1210308074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2735328674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4142990112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1533336639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7310237884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5785274505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8131408691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6958351135254</t>
   </si>
   <si>
     <t xml:space="preserve">19.3461227416992</t>
@@ -1601,10 +1601,10 @@
     <t xml:space="preserve">19.1404418945312</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0920448303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1646404266357</t>
+    <t xml:space="preserve">19.0920467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1646385192871</t>
   </si>
   <si>
     <t xml:space="preserve">19.7816829681396</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">19.9752655029297</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2656345367432</t>
+    <t xml:space="preserve">20.2656383514404</t>
   </si>
   <si>
     <t xml:space="preserve">20.435022354126</t>
@@ -1622,37 +1622,37 @@
     <t xml:space="preserve">20.6648998260498</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3745269775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.02366065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5397033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4429111480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6485939025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7211875915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9589576721191</t>
+    <t xml:space="preserve">20.3745288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0236587524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5397052764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4429130554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6485958099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7211856842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9589595794678</t>
   </si>
   <si>
     <t xml:space="preserve">18.3298149108887</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4103012084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0836277008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.228816986084</t>
+    <t xml:space="preserve">17.4102993011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0836296081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2288188934326</t>
   </si>
   <si>
     <t xml:space="preserve">16.8779487609863</t>
@@ -1661,100 +1661,100 @@
     <t xml:space="preserve">16.5149841308594</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6075668334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.167797088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8853149414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1194009780884</t>
+    <t xml:space="preserve">15.6075649261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1677989959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8853158950806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1194038391113</t>
   </si>
   <si>
     <t xml:space="preserve">14.2282943725586</t>
   </si>
   <si>
-    <t xml:space="preserve">15.426082611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4865760803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.014720916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1478080749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8332366943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7001476287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2929935455322</t>
+    <t xml:space="preserve">15.4260816574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4865770339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0147190093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1478099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8332376480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7001495361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2929944992065</t>
   </si>
   <si>
     <t xml:space="preserve">16.1520156860352</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5996742248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5754776000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0794239044189</t>
+    <t xml:space="preserve">16.5996761322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.575475692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0794219970703</t>
   </si>
   <si>
     <t xml:space="preserve">16.7932567596436</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2409152984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7327613830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9021472930908</t>
+    <t xml:space="preserve">17.2409133911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7327651977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9021492004395</t>
   </si>
   <si>
     <t xml:space="preserve">16.623872756958</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9705333709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4623775482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5712699890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5954666137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6438646316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6196613311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7890501022339</t>
+    <t xml:space="preserve">15.970531463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4623794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.571270942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5954647064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6438608169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6196622848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7890472412109</t>
   </si>
   <si>
     <t xml:space="preserve">16.0431251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4060955047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.587574005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.273006439209</t>
+    <t xml:space="preserve">16.4060935974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5875759124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2730045318604</t>
   </si>
   <si>
     <t xml:space="preserve">15.9100379943848</t>
@@ -1763,16 +1763,16 @@
     <t xml:space="preserve">15.9947319030762</t>
   </si>
   <si>
-    <t xml:space="preserve">15.825345993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6722660064697</t>
+    <t xml:space="preserve">15.8253469467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6722679138184</t>
   </si>
   <si>
     <t xml:space="preserve">16.9384422302246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2851028442383</t>
+    <t xml:space="preserve">16.2851047515869</t>
   </si>
   <si>
     <t xml:space="preserve">16.0552253723145</t>
@@ -1781,112 +1781,112 @@
     <t xml:space="preserve">16.2972030639648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3577003479004</t>
+    <t xml:space="preserve">16.3576965332031</t>
   </si>
   <si>
     <t xml:space="preserve">16.2125091552734</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3655862808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5470714569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6396551132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3692722320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6838407516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6475439071655</t>
+    <t xml:space="preserve">15.3655881881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5470724105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6396570205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3692712783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6838426589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6475458145142</t>
   </si>
   <si>
     <t xml:space="preserve">13.6354475021362</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2845783233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0426015853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5102510452271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3771600723267</t>
+    <t xml:space="preserve">13.2845792770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0426006317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5102519989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3771619796753</t>
   </si>
   <si>
     <t xml:space="preserve">12.4860515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4497537612915</t>
+    <t xml:space="preserve">12.4497556686401</t>
   </si>
   <si>
     <t xml:space="preserve">13.2603816986084</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7885246276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9700078964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9216136932373</t>
+    <t xml:space="preserve">12.7885255813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9700088500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9216146469116</t>
   </si>
   <si>
     <t xml:space="preserve">13.0909967422485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3408651351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2924690246582</t>
+    <t xml:space="preserve">12.3408660888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2924709320068</t>
   </si>
   <si>
     <t xml:space="preserve">12.2561740875244</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7643280029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1998872756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6596460342407</t>
+    <t xml:space="preserve">12.7643260955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1998844146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6596450805664</t>
   </si>
   <si>
     <t xml:space="preserve">13.526556968689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3571739196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8895244598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5749521255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6717433929443</t>
+    <t xml:space="preserve">13.3571720123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8895235061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5749530792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6717462539673</t>
   </si>
   <si>
     <t xml:space="preserve">13.3208780288696</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3450746536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5023584365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0589056015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4218721389771</t>
+    <t xml:space="preserve">13.3450727462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5023603439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0589094161987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4218759536743</t>
   </si>
   <si>
     <t xml:space="preserve">14.3976755142212</t>
@@ -1895,37 +1895,37 @@
     <t xml:space="preserve">14.2645893096924</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4339742660522</t>
+    <t xml:space="preserve">14.4339733123779</t>
   </si>
   <si>
     <t xml:space="preserve">13.3934688568115</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7359218597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8648014068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3003606796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6088838577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9779005050659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8024644851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3143005371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5865287780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2356605529785</t>
+    <t xml:space="preserve">11.7359209060669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.864800453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3003625869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6088829040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9778985977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8024654388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3143014907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5865278244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2356595993042</t>
   </si>
   <si>
     <t xml:space="preserve">9.86664295196533</t>
@@ -1934,28 +1934,28 @@
     <t xml:space="preserve">10.3264007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3022041320801</t>
+    <t xml:space="preserve">10.3022031784058</t>
   </si>
   <si>
     <t xml:space="preserve">10.4957857131958</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92108726501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89689064025879</t>
+    <t xml:space="preserve">9.92108821868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89689159393311</t>
   </si>
   <si>
     <t xml:space="preserve">9.5339241027832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73539733886719</t>
+    <t xml:space="preserve">8.73539638519287</t>
   </si>
   <si>
     <t xml:space="preserve">8.37847995758057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22119522094727</t>
+    <t xml:space="preserve">8.22119331359863</t>
   </si>
   <si>
     <t xml:space="preserve">8.4692211151123</t>
@@ -1967,10 +1967,10 @@
     <t xml:space="preserve">8.9713249206543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06206703186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40083503723145</t>
+    <t xml:space="preserve">9.06206607818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40083694458008</t>
   </si>
   <si>
     <t xml:space="preserve">9.67910957336426</t>
@@ -1979,22 +1979,22 @@
     <t xml:space="preserve">10.217511177063</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88479232788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12256145477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21935272216797</t>
+    <t xml:space="preserve">9.88479137420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12256240844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21935367584229</t>
   </si>
   <si>
     <t xml:space="preserve">8.82008934020996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12861156463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24959945678711</t>
+    <t xml:space="preserve">9.12861061096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24960136413574</t>
   </si>
   <si>
     <t xml:space="preserve">9.36453914642334</t>
@@ -2003,127 +2003,127 @@
     <t xml:space="preserve">9.58836841583252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48552894592285</t>
+    <t xml:space="preserve">9.48552799224854</t>
   </si>
   <si>
     <t xml:space="preserve">9.45528125762939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70935821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6125659942627</t>
+    <t xml:space="preserve">9.70935726165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61256694793701</t>
   </si>
   <si>
     <t xml:space="preserve">9.57022094726562</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8406047821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1370258331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9071474075317</t>
+    <t xml:space="preserve">10.8406038284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1370277404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9071483612061</t>
   </si>
   <si>
     <t xml:space="preserve">11.5967845916748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3064107894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0099878311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9676418304443</t>
+    <t xml:space="preserve">11.3064126968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.00998878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.96764087677</t>
   </si>
   <si>
     <t xml:space="preserve">10.5139331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8285055160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3385000228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7377624511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2840547561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6409721374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1007308959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0039377212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8587532043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3747959136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8121976852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69121074676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37058925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17095756530762</t>
+    <t xml:space="preserve">10.8285045623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3385009765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7377634048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2840557098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6409711837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1007289886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0039396286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8587522506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3747968673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81219673156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69120979309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3705883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1709566116333</t>
   </si>
   <si>
     <t xml:space="preserve">9.03786849975586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34034252166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34639072418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94528675079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4050445556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8043079376221</t>
+    <t xml:space="preserve">9.34034156799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34639263153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94528579711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4050436019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8043050765991</t>
   </si>
   <si>
     <t xml:space="preserve">10.5562801361084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6228227615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5804777145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5502319335938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0239286422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62466430664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1025724411011</t>
+    <t xml:space="preserve">10.6228246688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5804767608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5502300262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0239295959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62466526031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1025714874268</t>
   </si>
   <si>
     <t xml:space="preserve">10.2296104431152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4655380249023</t>
+    <t xml:space="preserve">10.465537071228</t>
   </si>
   <si>
     <t xml:space="preserve">10.3687467575073</t>
@@ -2132,13 +2132,13 @@
     <t xml:space="preserve">9.98763275146484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96948432922363</t>
+    <t xml:space="preserve">9.96948337554932</t>
   </si>
   <si>
     <t xml:space="preserve">10.2780055999756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4352922439575</t>
+    <t xml:space="preserve">10.4352912902832</t>
   </si>
   <si>
     <t xml:space="preserve">10.5320825576782</t>
@@ -2153,31 +2153,31 @@
     <t xml:space="preserve">10.1267690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3445482254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0662755966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64886379241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0946807861328</t>
+    <t xml:space="preserve">10.3445501327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0662746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64886283874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0946798324585</t>
   </si>
   <si>
     <t xml:space="preserve">12.6433372497559</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0323448181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.372953414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8768997192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7014675140381</t>
+    <t xml:space="preserve">12.0323429107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3729553222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8769006729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7014665603638</t>
   </si>
   <si>
     <t xml:space="preserve">10.6107244491577</t>
@@ -2186,37 +2186,37 @@
     <t xml:space="preserve">10.5683784484863</t>
   </si>
   <si>
-    <t xml:space="preserve">10.10862159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3505983352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9373941421509</t>
+    <t xml:space="preserve">10.1086196899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3505992889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9373950958252</t>
   </si>
   <si>
     <t xml:space="preserve">11.0341854095459</t>
   </si>
   <si>
-    <t xml:space="preserve">11.112829208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4818449020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.973690032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54602241516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35849094390869</t>
+    <t xml:space="preserve">11.1128301620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4818439483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9736919403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54602336883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35848999023438</t>
   </si>
   <si>
     <t xml:space="preserve">9.22540283203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1104621887207</t>
+    <t xml:space="preserve">9.11046314239502</t>
   </si>
   <si>
     <t xml:space="preserve">9.08626556396484</t>
@@ -2231,37 +2231,37 @@
     <t xml:space="preserve">8.97737503051758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95317649841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84428787231445</t>
+    <t xml:space="preserve">8.9531774520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84428691864014</t>
   </si>
   <si>
     <t xml:space="preserve">8.89873218536377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07416534423828</t>
+    <t xml:space="preserve">9.0741662979126</t>
   </si>
   <si>
     <t xml:space="preserve">9.00157260894775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24355030059814</t>
+    <t xml:space="preserve">9.24355125427246</t>
   </si>
   <si>
     <t xml:space="preserve">9.4976282119751</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47947883605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46132946014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38873767852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63676452636719</t>
+    <t xml:space="preserve">9.47947978973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46133041381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38873672485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6367654800415</t>
   </si>
   <si>
     <t xml:space="preserve">9.68515968322754</t>
@@ -2270,13 +2270,13 @@
     <t xml:space="preserve">9.71540641784668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83034706115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2636585235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94029235839844</t>
+    <t xml:space="preserve">9.83034801483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2636575698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94029140472412</t>
   </si>
   <si>
     <t xml:space="preserve">9.65572929382324</t>
@@ -2297,16 +2297,16 @@
     <t xml:space="preserve">8.52394485473633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27818584442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86427640914917</t>
+    <t xml:space="preserve">8.2781867980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86427736282349</t>
   </si>
   <si>
     <t xml:space="preserve">8.32345867156982</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37519550323486</t>
+    <t xml:space="preserve">8.3751974105835</t>
   </si>
   <si>
     <t xml:space="preserve">8.31698989868164</t>
@@ -2315,16 +2315,16 @@
     <t xml:space="preserve">8.07123184204102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87721252441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90954923629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82547330856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56678056716919</t>
+    <t xml:space="preserve">7.87721157073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90954637527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82547426223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56677961349487</t>
   </si>
   <si>
     <t xml:space="preserve">7.72199583053589</t>
@@ -2333,37 +2333,37 @@
     <t xml:space="preserve">7.59264945983887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54091119766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50210666656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37275981903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31455326080322</t>
+    <t xml:space="preserve">7.5409107208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50210762023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37275886535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31455373764038</t>
   </si>
   <si>
     <t xml:space="preserve">7.66379022598267</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3274884223938</t>
+    <t xml:space="preserve">7.32748937606812</t>
   </si>
   <si>
     <t xml:space="preserve">7.24341297149658</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28868532180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52150869369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26281547546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2951512336731</t>
+    <t xml:space="preserve">7.2886848449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52150917053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26281499862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29515171051025</t>
   </si>
   <si>
     <t xml:space="preserve">7.25634813308716</t>
@@ -2372,22 +2372,22 @@
     <t xml:space="preserve">7.41803073883057</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70906114578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03242778778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84487533569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70259475708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55384540557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76726770401001</t>
+    <t xml:space="preserve">7.70906162261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03242874145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84487438201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70259237289429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55384492874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76726722717285</t>
   </si>
   <si>
     <t xml:space="preserve">7.79960441589355</t>
@@ -2396,10 +2396,10 @@
     <t xml:space="preserve">7.67672491073608</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99362421035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18117523193359</t>
+    <t xml:space="preserve">7.99362277984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18117713928223</t>
   </si>
   <si>
     <t xml:space="preserve">8.7050313949585</t>
@@ -2408,13 +2408,13 @@
     <t xml:space="preserve">8.65329265594482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69856357574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79557228088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58215236663818</t>
+    <t xml:space="preserve">8.69856262207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79557418823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58215141296387</t>
   </si>
   <si>
     <t xml:space="preserve">8.57568359375</t>
@@ -2423,22 +2423,22 @@
     <t xml:space="preserve">8.49160861968994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55628204345703</t>
+    <t xml:space="preserve">8.5562801361084</t>
   </si>
   <si>
     <t xml:space="preserve">8.95725631713867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94432163238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9378547668457</t>
+    <t xml:space="preserve">8.94432353973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93785381317139</t>
   </si>
   <si>
     <t xml:space="preserve">8.75030136108398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62742328643799</t>
+    <t xml:space="preserve">8.62742233276367</t>
   </si>
   <si>
     <t xml:space="preserve">8.82791042327881</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">8.83437633514404</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71149730682373</t>
+    <t xml:space="preserve">8.71149826049805</t>
   </si>
   <si>
     <t xml:space="preserve">8.6080207824707</t>
@@ -2462,10 +2462,10 @@
     <t xml:space="preserve">8.29758930206299</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54334831237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02839660644531</t>
+    <t xml:space="preserve">8.5433464050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02839756011963</t>
   </si>
   <si>
     <t xml:space="preserve">8.91845226287842</t>
@@ -2477,13 +2477,13 @@
     <t xml:space="preserve">9.12540721893311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48513984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11003684997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87074422836304</t>
+    <t xml:space="preserve">8.48514080047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11003589630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87074518203735</t>
   </si>
   <si>
     <t xml:space="preserve">8.26525211334229</t>
@@ -2492,28 +2492,28 @@
     <t xml:space="preserve">8.33639144897461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4334020614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36872863769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28465366363525</t>
+    <t xml:space="preserve">8.43340110778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36872959136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28465461730957</t>
   </si>
   <si>
     <t xml:space="preserve">8.23938274383545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56274795532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76970386505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02193069458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13187313079834</t>
+    <t xml:space="preserve">8.5627498626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76970481872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02192974090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13187408447266</t>
   </si>
   <si>
     <t xml:space="preserve">9.2224178314209</t>
@@ -2528,22 +2528,22 @@
     <t xml:space="preserve">9.50697994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55871963500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58458805084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69453239440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91442108154297</t>
+    <t xml:space="preserve">9.55871868133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58458709716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69453144073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91442203521729</t>
   </si>
   <si>
     <t xml:space="preserve">9.92088985443115</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73333549499512</t>
+    <t xml:space="preserve">9.73333644866943</t>
   </si>
   <si>
     <t xml:space="preserve">9.89501953125</t>
@@ -2555,37 +2555,37 @@
     <t xml:space="preserve">9.67513084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57812023162842</t>
+    <t xml:space="preserve">9.57812213897705</t>
   </si>
   <si>
     <t xml:space="preserve">9.66866397857666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90148830413818</t>
+    <t xml:space="preserve">9.90148735046387</t>
   </si>
   <si>
     <t xml:space="preserve">9.70746803283691</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51991558074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30649375915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33236122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43583869934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09953784942627</t>
+    <t xml:space="preserve">9.5199146270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30649185180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33236217498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43583965301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09953689575195</t>
   </si>
   <si>
     <t xml:space="preserve">9.37116622924805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52638149261475</t>
+    <t xml:space="preserve">9.52638244628906</t>
   </si>
   <si>
     <t xml:space="preserve">9.79154300689697</t>
@@ -2594,31 +2594,31 @@
     <t xml:space="preserve">9.7398042678833</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76567268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87561893463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95322704315186</t>
+    <t xml:space="preserve">9.76567363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87561798095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95322608947754</t>
   </si>
   <si>
     <t xml:space="preserve">9.99849700927734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94675827026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77213954925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88208484649658</t>
+    <t xml:space="preserve">9.94675922393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.772141456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8820858001709</t>
   </si>
   <si>
     <t xml:space="preserve">9.98556232452393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2248554229736</t>
+    <t xml:space="preserve">10.224853515625</t>
   </si>
   <si>
     <t xml:space="preserve">9.44877338409424</t>
@@ -2630,52 +2630,52 @@
     <t xml:space="preserve">9.86915111541748</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1925163269043</t>
+    <t xml:space="preserve">10.1925172805786</t>
   </si>
   <si>
     <t xml:space="preserve">10.2377891540527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62339115142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41643714904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34529685974121</t>
+    <t xml:space="preserve">9.62339210510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41643810272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34529590606689</t>
   </si>
   <si>
     <t xml:space="preserve">9.24181938171387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19007873535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06073474884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08013439178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97665977478027</t>
+    <t xml:space="preserve">9.19007968902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06073379516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0801362991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97665882110596</t>
   </si>
   <si>
     <t xml:space="preserve">9.04133129119873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9249210357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76323509216309</t>
+    <t xml:space="preserve">8.92492008209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7632360458374</t>
   </si>
   <si>
     <t xml:space="preserve">8.84731197357178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78263759613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61448764801025</t>
+    <t xml:space="preserve">8.78263854980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61448669433594</t>
   </si>
   <si>
     <t xml:space="preserve">8.56921577453613</t>
@@ -2684,16 +2684,16 @@
     <t xml:space="preserve">8.67916202545166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86671447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87318134307861</t>
+    <t xml:space="preserve">8.86671352386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87318229675293</t>
   </si>
   <si>
     <t xml:space="preserve">8.81497478485107</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8602466583252</t>
+    <t xml:space="preserve">8.86024570465088</t>
   </si>
   <si>
     <t xml:space="preserve">9.24828720092773</t>
@@ -2714,19 +2714,19 @@
     <t xml:space="preserve">9.13834190368652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26768779754639</t>
+    <t xml:space="preserve">9.2676887512207</t>
   </si>
   <si>
     <t xml:space="preserve">9.09307098388672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93138694763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20301532745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59105587005615</t>
+    <t xml:space="preserve">8.93138790130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2030143737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59105491638184</t>
   </si>
   <si>
     <t xml:space="preserve">9.57165336608887</t>
@@ -2744,13 +2744,13 @@
     <t xml:space="preserve">9.30002593994141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74627017974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47464179992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27415657043457</t>
+    <t xml:space="preserve">9.74627113342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47464370727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27415561676025</t>
   </si>
   <si>
     <t xml:space="preserve">9.62985897064209</t>
@@ -2759,10 +2759,10 @@
     <t xml:space="preserve">9.70100021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80447769165039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1343107223511</t>
+    <t xml:space="preserve">9.80447673797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1343116760254</t>
   </si>
   <si>
     <t xml:space="preserve">10.1278438568115</t>
@@ -2777,106 +2777,106 @@
     <t xml:space="preserve">10.0049648284912</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1472444534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35176372528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5522518157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8925838470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40753364562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90308237075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88124227523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61608076095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5966796875</t>
+    <t xml:space="preserve">10.1472454071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35176467895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55225086212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89258289337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40753269195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90308094024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88124322891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61608171463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59668016433716</t>
   </si>
   <si>
     <t xml:space="preserve">5.67185115814209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93701219558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61364555358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44549465179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45842933654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43902778625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75592708587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57160711288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84000158309937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86910533905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98228311538696</t>
+    <t xml:space="preserve">5.93701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61364507675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44549512863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45842885971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43902730941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75592613220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57160758972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84000205993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86910486221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98228406906128</t>
   </si>
   <si>
     <t xml:space="preserve">5.90790939331055</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66215133666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78826332092285</t>
+    <t xml:space="preserve">5.66214990615845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78826284408569</t>
   </si>
   <si>
     <t xml:space="preserve">5.75916004180908</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70095348358154</t>
+    <t xml:space="preserve">5.7009539604187</t>
   </si>
   <si>
     <t xml:space="preserve">5.78179550170898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83676815032959</t>
+    <t xml:space="preserve">5.83676862716675</t>
   </si>
   <si>
     <t xml:space="preserve">5.96934843063354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9467134475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9758152961731</t>
+    <t xml:space="preserve">5.94671297073364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97581624984741</t>
   </si>
   <si>
     <t xml:space="preserve">5.83353519439697</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71388912200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76886081695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77532863616943</t>
+    <t xml:space="preserve">5.71388864517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76886129379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77532768249512</t>
   </si>
   <si>
     <t xml:space="preserve">5.49723339080811</t>
@@ -2888,25 +2888,25 @@
     <t xml:space="preserve">5.51663541793823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81413221359253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93054485321045</t>
+    <t xml:space="preserve">5.81413269042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93054437637329</t>
   </si>
   <si>
     <t xml:space="preserve">5.77209520339966</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56190729141235</t>
+    <t xml:space="preserve">5.56190633773804</t>
   </si>
   <si>
     <t xml:space="preserve">5.62011241912842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58454275131226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47136449813843</t>
+    <t xml:space="preserve">5.5845422744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47136402130127</t>
   </si>
   <si>
     <t xml:space="preserve">5.55867338180542</t>
@@ -2918,34 +2918,34 @@
     <t xml:space="preserve">5.40669012069702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32584857940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22560501098633</t>
+    <t xml:space="preserve">5.3258490562439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22560548782349</t>
   </si>
   <si>
     <t xml:space="preserve">5.19326829910278</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17386674880981</t>
+    <t xml:space="preserve">5.17386627197266</t>
   </si>
   <si>
     <t xml:space="preserve">4.947509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81169557571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70821857452393</t>
+    <t xml:space="preserve">4.81169605255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70821905136108</t>
   </si>
   <si>
     <t xml:space="preserve">4.7211537361145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9798469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18033456802368</t>
+    <t xml:space="preserve">4.97984647750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18033409118652</t>
   </si>
   <si>
     <t xml:space="preserve">5.33554983139038</t>
@@ -2963,52 +2963,52 @@
     <t xml:space="preserve">5.72682332992554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94347953796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25391101837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70015811920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2862491607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09222745895386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67508459091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63304710388184</t>
+    <t xml:space="preserve">5.94347906112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25391149520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70015621185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28624820709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09222793579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67508506774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63304805755615</t>
   </si>
   <si>
     <t xml:space="preserve">5.78502941131592</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87880563735962</t>
+    <t xml:space="preserve">5.87880611419678</t>
   </si>
   <si>
     <t xml:space="preserve">5.8206000328064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7332911491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58777713775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53603744506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3969898223877</t>
+    <t xml:space="preserve">5.73329067230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58777666091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53603792190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39699029922485</t>
   </si>
   <si>
     <t xml:space="preserve">5.31614780426025</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37435340881348</t>
+    <t xml:space="preserve">5.37435388565063</t>
   </si>
   <si>
     <t xml:space="preserve">5.49399948120117</t>
@@ -3017,46 +3017,46 @@
     <t xml:space="preserve">5.52957010269165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5134015083313</t>
+    <t xml:space="preserve">5.51340103149414</t>
   </si>
   <si>
     <t xml:space="preserve">5.6459813117981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75269317626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8658709526062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80119848251343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89497375488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87557220458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22804260253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3476881980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3994255065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19570446014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05989074707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91760921478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77856302261353</t>
+    <t xml:space="preserve">5.75269365310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86587142944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80119800567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89497470855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87557172775269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22804164886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34768676757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39942693710327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19570541381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05989170074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91761016845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77856254577637</t>
   </si>
   <si>
     <t xml:space="preserve">5.60717821121216</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">5.60394430160522</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80766534805298</t>
+    <t xml:space="preserve">5.80766487121582</t>
   </si>
   <si>
     <t xml:space="preserve">5.81736612319946</t>
@@ -3074,16 +3074,16 @@
     <t xml:space="preserve">5.68478584289551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93377876281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91114282608032</t>
+    <t xml:space="preserve">5.93377780914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91114330291748</t>
   </si>
   <si>
     <t xml:space="preserve">5.94024610519409</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82383346557617</t>
+    <t xml:space="preserve">5.82383394241333</t>
   </si>
   <si>
     <t xml:space="preserve">5.79473066329956</t>
@@ -3092,70 +3092,70 @@
     <t xml:space="preserve">5.89820766448975</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73652505874634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7494592666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79796504974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6395149230957</t>
+    <t xml:space="preserve">5.73652458190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74945974349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79796457290649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63951444625854</t>
   </si>
   <si>
     <t xml:space="preserve">5.59101009368896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58130931854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70418787002563</t>
+    <t xml:space="preserve">5.58130836486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70418834686279</t>
   </si>
   <si>
     <t xml:space="preserve">5.70742130279541</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66538429260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69448661804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88203907012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80443239212036</t>
+    <t xml:space="preserve">5.66538381576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69448804855347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88204002380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80443143844604</t>
   </si>
   <si>
     <t xml:space="preserve">5.71065521240234</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50693464279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39052248001099</t>
+    <t xml:space="preserve">5.50693416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39052200317383</t>
   </si>
   <si>
     <t xml:space="preserve">5.33878374099731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43255949020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30321359634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31938219070435</t>
+    <t xml:space="preserve">5.43255996704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30321311950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31938171386719</t>
   </si>
   <si>
     <t xml:space="preserve">5.21267080307007</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21590328216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22883939743042</t>
+    <t xml:space="preserve">5.21590375900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2288384437561</t>
   </si>
   <si>
     <t xml:space="preserve">5.34201765060425</t>
@@ -3164,37 +3164,37 @@
     <t xml:space="preserve">5.26764345169067</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32261562347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29997873306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21913766860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07362222671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12212753295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07685661315918</t>
+    <t xml:space="preserve">5.32261514663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2999792098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21913814544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07362270355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12212800979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07685708999634</t>
   </si>
   <si>
     <t xml:space="preserve">5.07038927078247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10919380187988</t>
+    <t xml:space="preserve">5.10919332504272</t>
   </si>
   <si>
     <t xml:space="preserve">5.20296955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0412859916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9960150718689</t>
+    <t xml:space="preserve">5.04128646850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99601554870605</t>
   </si>
   <si>
     <t xml:space="preserve">4.92164087295532</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">4.50773143768311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36221647262573</t>
+    <t xml:space="preserve">4.36221694946289</t>
   </si>
   <si>
     <t xml:space="preserve">4.4527587890625</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">4.58857297897339</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7825927734375</t>
+    <t xml:space="preserve">4.78259372711182</t>
   </si>
   <si>
     <t xml:space="preserve">4.89900493621826</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">4.82786464691162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79229402542114</t>
+    <t xml:space="preserve">4.79229354858398</t>
   </si>
   <si>
     <t xml:space="preserve">5.13829660415649</t>
@@ -3242,94 +3242,94 @@
     <t xml:space="preserve">5.23530626296997</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65891742706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8432354927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85940456390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07605981826782</t>
+    <t xml:space="preserve">5.65891695022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84323596954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85940408706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07606029510498</t>
   </si>
   <si>
     <t xml:space="preserve">6.00815296173096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97904872894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98875141143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90467500686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17630338668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2991828918457</t>
+    <t xml:space="preserve">5.97904968261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98874998092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90467596054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17630290985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29918146133423</t>
   </si>
   <si>
     <t xml:space="preserve">6.31858444213867</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34445428848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2183403968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19247102737427</t>
+    <t xml:space="preserve">6.34445381164551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21834135055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19247198104858</t>
   </si>
   <si>
     <t xml:space="preserve">6.13103199005127</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05665731430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10516262054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10192918777466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04048871994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03725528717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06635904312134</t>
+    <t xml:space="preserve">6.0566577911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10516309738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10192966461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0404896736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03725481033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06635808944702</t>
   </si>
   <si>
     <t xml:space="preserve">5.8885064125061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95317983627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99198484420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9855170249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02432012557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01138687133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97258186340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73005771636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7397575378418</t>
+    <t xml:space="preserve">5.95318078994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99198389053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98551654815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02432060241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01138591766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97258234024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73005723953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73975849151611</t>
   </si>
   <si>
     <t xml:space="preserve">5.64921522140503</t>
@@ -3344,10 +3344,10 @@
     <t xml:space="preserve">5.46813058853149</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41639137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72359037399292</t>
+    <t xml:space="preserve">5.41639184951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7235894203186</t>
   </si>
   <si>
     <t xml:space="preserve">6.07282590866089</t>
@@ -3365,37 +3365,37 @@
     <t xml:space="preserve">6.67428731918335</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75189590454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66782140731812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66135406494141</t>
+    <t xml:space="preserve">6.75189542770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66782093048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66135358810425</t>
   </si>
   <si>
     <t xml:space="preserve">6.58374547958374</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64195251464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69369029998779</t>
+    <t xml:space="preserve">6.64195108413696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69369125366211</t>
   </si>
   <si>
     <t xml:space="preserve">6.90064525604248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80363464355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97178554534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83597040176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85537338256836</t>
+    <t xml:space="preserve">6.803635597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9717845916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83597183227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85537385940552</t>
   </si>
   <si>
     <t xml:space="preserve">6.78423261642456</t>
@@ -3407,22 +3407,22 @@
     <t xml:space="preserve">7.19167423248291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23694515228271</t>
+    <t xml:space="preserve">7.23694658279419</t>
   </si>
   <si>
     <t xml:space="preserve">7.42449855804443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48270559310913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39216279983521</t>
+    <t xml:space="preserve">7.4827036857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39216232299805</t>
   </si>
   <si>
     <t xml:space="preserve">7.41156339645386</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16580390930176</t>
+    <t xml:space="preserve">7.16580533981323</t>
   </si>
   <si>
     <t xml:space="preserve">7.19814157485962</t>
@@ -3431,106 +3431,106 @@
     <t xml:space="preserve">7.24988079071045</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35335826873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36629295349121</t>
+    <t xml:space="preserve">7.35335731506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36629199981689</t>
   </si>
   <si>
     <t xml:space="preserve">7.27574968338013</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32102060317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34689044952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15287017822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49563980102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43743181228638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39862966537476</t>
+    <t xml:space="preserve">7.32102108001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34688997268677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15287113189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49563884735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43743276596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3986291885376</t>
   </si>
   <si>
     <t xml:space="preserve">7.3598256111145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08172988891602</t>
+    <t xml:space="preserve">7.08172941207886</t>
   </si>
   <si>
     <t xml:space="preserve">7.26928234100342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46330165863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51503992080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46976947784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44390058517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47623682022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52797555923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95482015609741</t>
+    <t xml:space="preserve">7.46330213546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51504182815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46977043151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44390201568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47623729705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52797603607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95482110977173</t>
   </si>
   <si>
     <t xml:space="preserve">7.69612598419189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11650276184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43987083435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46573925018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40106678009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25878620147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18764400482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05182933807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22644805908203</t>
+    <t xml:space="preserve">8.1165018081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43986892700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46573829650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40106582641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2587833404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18764305114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05182838439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22644710540771</t>
   </si>
   <si>
     <t xml:space="preserve">8.31052398681641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34932708740234</t>
+    <t xml:space="preserve">8.34932613372803</t>
   </si>
   <si>
     <t xml:space="preserve">8.4204683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38166427612305</t>
+    <t xml:space="preserve">8.38166332244873</t>
   </si>
   <si>
     <t xml:space="preserve">8.50454330444336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14883995056152</t>
+    <t xml:space="preserve">8.14884090423584</t>
   </si>
   <si>
     <t xml:space="preserve">9.01546287536621</t>
@@ -3548,19 +3548,19 @@
     <t xml:space="preserve">8.51101016998291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29112148284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78910541534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23291397094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35579490661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96372509002686</t>
+    <t xml:space="preserve">8.29111957550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78910446166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23291492462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35579586029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96372318267822</t>
   </si>
   <si>
     <t xml:space="preserve">8.98312568664551</t>
@@ -3572,31 +3572,31 @@
     <t xml:space="preserve">9.07366847991943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00252914428711</t>
+    <t xml:space="preserve">9.00252819061279</t>
   </si>
   <si>
     <t xml:space="preserve">8.99605941772461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06720066070557</t>
+    <t xml:space="preserve">9.06720161437988</t>
   </si>
   <si>
     <t xml:space="preserve">9.19654750823975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46817493438721</t>
+    <t xml:space="preserve">9.46817588806152</t>
   </si>
   <si>
     <t xml:space="preserve">9.4229040145874</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3776330947876</t>
+    <t xml:space="preserve">9.37763214111328</t>
   </si>
   <si>
     <t xml:space="preserve">9.39056777954102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46170806884766</t>
+    <t xml:space="preserve">9.46170902252197</t>
   </si>
   <si>
     <t xml:space="preserve">9.20948314666748</t>
@@ -3611,16 +3611,16 @@
     <t xml:space="preserve">9.48110961914062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.565185546875</t>
+    <t xml:space="preserve">9.56518745422363</t>
   </si>
   <si>
     <t xml:space="preserve">9.81094455718994</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0437679290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0890398025513</t>
+    <t xml:space="preserve">10.0437669754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0890407562256</t>
   </si>
   <si>
     <t xml:space="preserve">10.3283309936523</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">10.4447431564331</t>
   </si>
   <si>
-    <t xml:space="preserve">10.244255065918</t>
+    <t xml:space="preserve">10.2442560195923</t>
   </si>
   <si>
     <t xml:space="preserve">10.7616424560547</t>
@@ -3647,10 +3647,10 @@
     <t xml:space="preserve">10.5611553192139</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9685974121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5934915542603</t>
+    <t xml:space="preserve">10.9685964584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5934906005859</t>
   </si>
   <si>
     <t xml:space="preserve">10.813380241394</t>
@@ -3659,43 +3659,43 @@
     <t xml:space="preserve">10.6775674819946</t>
   </si>
   <si>
-    <t xml:space="preserve">10.658166885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8198480606079</t>
+    <t xml:space="preserve">10.6581649780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8198490142822</t>
   </si>
   <si>
     <t xml:space="preserve">10.6840353012085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0074014663696</t>
+    <t xml:space="preserve">11.0074024200439</t>
   </si>
   <si>
     <t xml:space="preserve">11.0009346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2567691802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2291107177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0908231735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9110450744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.007848739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1046504974365</t>
+    <t xml:space="preserve">11.2567710876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2291116714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0908222198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9110460281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0078477859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1046514511108</t>
   </si>
   <si>
     <t xml:space="preserve">11.0424203872681</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0562496185303</t>
+    <t xml:space="preserve">11.056248664856</t>
   </si>
   <si>
     <t xml:space="preserve">11.1945390701294</t>
@@ -3710,22 +3710,22 @@
     <t xml:space="preserve">11.5748348236084</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5955781936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6854667663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6508941650391</t>
+    <t xml:space="preserve">11.5955791473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6854658126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6508951187134</t>
   </si>
   <si>
     <t xml:space="preserve">11.4780321121216</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7131252288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6923818588257</t>
+    <t xml:space="preserve">11.7131261825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6923828125</t>
   </si>
   <si>
     <t xml:space="preserve">11.6301517486572</t>
@@ -3734,43 +3734,43 @@
     <t xml:space="preserve">11.5402631759644</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2636852264404</t>
+    <t xml:space="preserve">11.2636842727661</t>
   </si>
   <si>
     <t xml:space="preserve">11.1392240524292</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8280715942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9456186294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.55149269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5100049972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4961776733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97067737579346</t>
+    <t xml:space="preserve">10.828070640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9456176757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5514917373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5100059509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4961767196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97067642211914</t>
   </si>
   <si>
     <t xml:space="preserve">10.10205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2057685852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6828680038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5445785522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4616041183472</t>
+    <t xml:space="preserve">10.2057676315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6828670501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5445775985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4616050720215</t>
   </si>
   <si>
     <t xml:space="preserve">10.8419008255005</t>
@@ -3782,13 +3782,13 @@
     <t xml:space="preserve">10.8764734268188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9663619995117</t>
+    <t xml:space="preserve">10.9663610458374</t>
   </si>
   <si>
     <t xml:space="preserve">10.9179601669312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.82115650177</t>
+    <t xml:space="preserve">10.8211574554443</t>
   </si>
   <si>
     <t xml:space="preserve">10.5653209686279</t>
@@ -3806,13 +3806,13 @@
     <t xml:space="preserve">11.7546119689941</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8030138015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0934219360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2317113876343</t>
+    <t xml:space="preserve">11.8030118942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0934209823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.23171043396</t>
   </si>
   <si>
     <t xml:space="preserve">12.1487369537354</t>
@@ -3821,58 +3821,58 @@
     <t xml:space="preserve">11.9413032531738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1210794448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0795917510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2593688964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4184017181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4737186431885</t>
+    <t xml:space="preserve">12.1210803985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0795907974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2593679428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4184007644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4737176895142</t>
   </si>
   <si>
     <t xml:space="preserve">12.6050910949707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7572116851807</t>
+    <t xml:space="preserve">12.757212638855</t>
   </si>
   <si>
     <t xml:space="preserve">12.3285121917725</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2870254516602</t>
+    <t xml:space="preserve">12.2870283126831</t>
   </si>
   <si>
     <t xml:space="preserve">12.6880674362183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5705194473267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8514137268066</t>
+    <t xml:space="preserve">12.570520401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8514127731323</t>
   </si>
   <si>
     <t xml:space="preserve">12.2455387115479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3561725616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3769149780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2662839889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2040519714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6396656036377</t>
+    <t xml:space="preserve">12.3561716079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.376914024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.266282081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2040510177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6396646499634</t>
   </si>
   <si>
     <t xml:space="preserve">12.4806318283081</t>
@@ -3881,52 +3881,52 @@
     <t xml:space="preserve">12.3907442092896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7364664077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2757968902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1885080337524</t>
+    <t xml:space="preserve">12.7364683151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2757959365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1885070800781</t>
   </si>
   <si>
     <t xml:space="preserve">14.3129692077637</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9352741241455</t>
+    <t xml:space="preserve">14.9352722167969</t>
   </si>
   <si>
     <t xml:space="preserve">14.9905872344971</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7554960250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7969818115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9672431945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6215200424194</t>
+    <t xml:space="preserve">14.7554941177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7969808578491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9672451019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6215190887451</t>
   </si>
   <si>
     <t xml:space="preserve">12.68115234375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3380270004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0960216522217</t>
+    <t xml:space="preserve">13.3380279541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0960206985474</t>
   </si>
   <si>
     <t xml:space="preserve">12.3354272842407</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5774335861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3492565155029</t>
+    <t xml:space="preserve">12.5774345397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3492574691772</t>
   </si>
   <si>
     <t xml:space="preserve">11.2498550415039</t>
@@ -3935,52 +3935,52 @@
     <t xml:space="preserve">10.7589273452759</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7615270614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0285911560059</t>
+    <t xml:space="preserve">11.7615261077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0285921096802</t>
   </si>
   <si>
     <t xml:space="preserve">11.3674011230469</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8652420043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1694793701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8056135177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7157249450684</t>
+    <t xml:space="preserve">11.8652429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1694812774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8056116104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7157220840454</t>
   </si>
   <si>
     <t xml:space="preserve">12.7433815002441</t>
   </si>
   <si>
-    <t xml:space="preserve">13.061448097229</t>
+    <t xml:space="preserve">13.0614471435547</t>
   </si>
   <si>
     <t xml:space="preserve">12.9992160797119</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8885850906372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0337896347046</t>
+    <t xml:space="preserve">12.8885869979858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0337915420532</t>
   </si>
   <si>
     <t xml:space="preserve">13.0683622360229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9093284606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.019962310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2731962203979</t>
+    <t xml:space="preserve">12.909330368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0199604034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2731971740723</t>
   </si>
   <si>
     <t xml:space="preserve">12.6465797424316</t>
@@ -3989,10 +3989,10 @@
     <t xml:space="preserve">12.494460105896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5428609848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2524547576904</t>
+    <t xml:space="preserve">12.5428619384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2524538040161</t>
   </si>
   <si>
     <t xml:space="preserve">12.5566921234131</t>
@@ -4001,10 +4001,10 @@
     <t xml:space="preserve">11.955132484436</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0865058898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9205589294434</t>
+    <t xml:space="preserve">12.0865077972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9205598831177</t>
   </si>
   <si>
     <t xml:space="preserve">11.3466567993164</t>
@@ -4013,61 +4013,61 @@
     <t xml:space="preserve">11.5817489624023</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0242748260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3008556365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0381059646606</t>
+    <t xml:space="preserve">12.0242767333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.300856590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0381050109863</t>
   </si>
   <si>
     <t xml:space="preserve">12.5793085098267</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939340591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5208005905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7694597244263</t>
+    <t xml:space="preserve">12.5939331054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5207996368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.769458770752</t>
   </si>
   <si>
     <t xml:space="preserve">12.6743831634521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.747519493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4184093475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3964700698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.374529838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3452730178833</t>
+    <t xml:space="preserve">12.7475204467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4184083938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3964691162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3745288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3452739715576</t>
   </si>
   <si>
     <t xml:space="preserve">12.3525876998901</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1404943466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9795970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7455625534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0434617996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.480318069458</t>
+    <t xml:space="preserve">12.140495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9795951843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7455615997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0434627532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4803190231323</t>
   </si>
   <si>
     <t xml:space="preserve">10.5900220870972</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">10.4437503814697</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6777858734131</t>
+    <t xml:space="preserve">10.6777849197388</t>
   </si>
   <si>
     <t xml:space="preserve">10.5095729827881</t>
@@ -4091,22 +4091,22 @@
     <t xml:space="preserve">10.5022592544556</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2389717102051</t>
+    <t xml:space="preserve">10.2389726638794</t>
   </si>
   <si>
     <t xml:space="preserve">10.494945526123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4291248321533</t>
+    <t xml:space="preserve">10.429123878479</t>
   </si>
   <si>
     <t xml:space="preserve">10.3998689651489</t>
   </si>
   <si>
-    <t xml:space="preserve">10.209716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88060855865479</t>
+    <t xml:space="preserve">10.2097187042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88060760498047</t>
   </si>
   <si>
     <t xml:space="preserve">9.75627708435059</t>
@@ -4115,16 +4115,16 @@
     <t xml:space="preserve">9.70508193969727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31014919281006</t>
+    <t xml:space="preserve">9.31015014648438</t>
   </si>
   <si>
     <t xml:space="preserve">9.23701477050781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43448066711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69776916503906</t>
+    <t xml:space="preserve">9.43448162078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69776821136475</t>
   </si>
   <si>
     <t xml:space="preserve">9.41254043579102</t>
@@ -4133,19 +4133,19 @@
     <t xml:space="preserve">9.46373462677002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06149005889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62267780303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8274564743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97372722625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20776081085205</t>
+    <t xml:space="preserve">9.06148910522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62267684936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82745742797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97372817993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20776176452637</t>
   </si>
   <si>
     <t xml:space="preserve">9.24432849884033</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">9.21507453918457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3686580657959</t>
+    <t xml:space="preserve">9.36865997314453</t>
   </si>
   <si>
     <t xml:space="preserve">9.39791393280029</t>
@@ -4178,25 +4178,25 @@
     <t xml:space="preserve">9.55881118774414</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95374202728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0195636749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98299789428711</t>
+    <t xml:space="preserve">9.95374298095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0195655822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98299598693848</t>
   </si>
   <si>
     <t xml:space="preserve">9.72702312469482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47104740142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57343864440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80747222900391</t>
+    <t xml:space="preserve">9.47104930877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57343769073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80747127532959</t>
   </si>
   <si>
     <t xml:space="preserve">9.97568416595459</t>
@@ -4208,34 +4208,34 @@
     <t xml:space="preserve">9.10537147521973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22238731384277</t>
+    <t xml:space="preserve">9.22238826751709</t>
   </si>
   <si>
     <t xml:space="preserve">9.20044708251953</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06880378723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82014179229736</t>
+    <t xml:space="preserve">9.06880283355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.820143699646</t>
   </si>
   <si>
     <t xml:space="preserve">8.75432109832764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81282901763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73969268798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51297378540039</t>
+    <t xml:space="preserve">8.81282997131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7396936416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51297473907471</t>
   </si>
   <si>
     <t xml:space="preserve">8.68849849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44715118408203</t>
+    <t xml:space="preserve">8.44715213775635</t>
   </si>
   <si>
     <t xml:space="preserve">8.40326976776123</t>
@@ -4256,22 +4256,22 @@
     <t xml:space="preserve">9.02492237091064</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14925289154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94447231292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89327812194824</t>
+    <t xml:space="preserve">9.14925193786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94447326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89327716827393</t>
   </si>
   <si>
     <t xml:space="preserve">8.59342193603516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63730335235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34476089477539</t>
+    <t xml:space="preserve">8.63730525970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34476184844971</t>
   </si>
   <si>
     <t xml:space="preserve">8.35938930511475</t>
@@ -4280,31 +4280,31 @@
     <t xml:space="preserve">8.22043132781982</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13266944885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86938142776489</t>
+    <t xml:space="preserve">8.13266849517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86938095092773</t>
   </si>
   <si>
     <t xml:space="preserve">8.32282066345215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41789722442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33013439178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24237155914307</t>
+    <t xml:space="preserve">8.41789817810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33013534545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24237251281738</t>
   </si>
   <si>
     <t xml:space="preserve">8.14729690551758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07415962219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1619234085083</t>
+    <t xml:space="preserve">8.0741605758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16192245483398</t>
   </si>
   <si>
     <t xml:space="preserve">8.04490566253662</t>
@@ -4313,58 +4313,58 @@
     <t xml:space="preserve">8.05221939086914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28625297546387</t>
+    <t xml:space="preserve">8.28625392913818</t>
   </si>
   <si>
     <t xml:space="preserve">8.26431274414062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30088043212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38864326477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48371982574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56416893005371</t>
+    <t xml:space="preserve">8.30088138580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38864231109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48371887207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56416797637939</t>
   </si>
   <si>
     <t xml:space="preserve">8.71775245666504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88596343994141</t>
+    <t xml:space="preserve">8.88596534729004</t>
   </si>
   <si>
     <t xml:space="preserve">8.922532081604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56612586975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52955627441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84403896331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0488195419312</t>
+    <t xml:space="preserve">9.56612491607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52955722808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84403991699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0488185882568</t>
   </si>
   <si>
     <t xml:space="preserve">10.1804628372192</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1512079238892</t>
+    <t xml:space="preserve">10.1512088775635</t>
   </si>
   <si>
     <t xml:space="preserve">10.1146411895752</t>
   </si>
   <si>
-    <t xml:space="preserve">10.004937171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3340473175049</t>
+    <t xml:space="preserve">10.0049381256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3340482711792</t>
   </si>
   <si>
     <t xml:space="preserve">10.2789545059204</t>
@@ -4373,22 +4373,22 @@
     <t xml:space="preserve">10.3104362487793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3261766433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3576593399048</t>
+    <t xml:space="preserve">10.3261775970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3576583862305</t>
   </si>
   <si>
     <t xml:space="preserve">10.3497886657715</t>
   </si>
   <si>
-    <t xml:space="preserve">10.389142036438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2553415298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2710828781128</t>
+    <t xml:space="preserve">10.3891410827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2553424835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2710838317871</t>
   </si>
   <si>
     <t xml:space="preserve">10.2002477645874</t>
@@ -4397,7 +4397,7 @@
     <t xml:space="preserve">10.0428371429443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86968517303467</t>
+    <t xml:space="preserve">9.86968421936035</t>
   </si>
   <si>
     <t xml:space="preserve">9.88542652130127</t>
@@ -4409,7 +4409,7 @@
     <t xml:space="preserve">9.96413135528564</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1608953475952</t>
+    <t xml:space="preserve">10.1608943939209</t>
   </si>
   <si>
     <t xml:space="preserve">10.1845064163208</t>
@@ -4418,10 +4418,10 @@
     <t xml:space="preserve">10.0034837722778</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0900592803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5229406356812</t>
+    <t xml:space="preserve">10.0900602340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5229415893555</t>
   </si>
   <si>
     <t xml:space="preserve">10.3419179916382</t>
@@ -4430,22 +4430,22 @@
     <t xml:space="preserve">10.4521064758301</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3812694549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4678478240967</t>
+    <t xml:space="preserve">10.3812713623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4678468704224</t>
   </si>
   <si>
     <t xml:space="preserve">10.47571849823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5780344009399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7433166503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0030450820923</t>
+    <t xml:space="preserve">10.5780353546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7433156967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.003044128418</t>
   </si>
   <si>
     <t xml:space="preserve">11.0345277786255</t>
@@ -4454,10 +4454,10 @@
     <t xml:space="preserve">11.0423984527588</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1998100280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2234210968018</t>
+    <t xml:space="preserve">11.1998090744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2234201431274</t>
   </si>
   <si>
     <t xml:space="preserve">11.2863855361938</t>
@@ -4466,25 +4466,25 @@
     <t xml:space="preserve">11.3650903701782</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3493509292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3414783477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3099975585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1919393539429</t>
+    <t xml:space="preserve">11.3493499755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3414793014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3099966049194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1919384002686</t>
   </si>
   <si>
     <t xml:space="preserve">11.4123153686523</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3965740203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2155504226685</t>
+    <t xml:space="preserve">11.3965730667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2155513763428</t>
   </si>
   <si>
     <t xml:space="preserve">11.4280567169189</t>
@@ -4493,16 +4493,16 @@
     <t xml:space="preserve">11.4752788543701</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8294534683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0813131332397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1678876876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3725233078003</t>
+    <t xml:space="preserve">11.8294544219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0813121795654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1678886413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.372522354126</t>
   </si>
   <si>
     <t xml:space="preserve">12.3095598220825</t>
@@ -4514,10 +4514,10 @@
     <t xml:space="preserve">12.5220632553101</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5141925811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7266979217529</t>
+    <t xml:space="preserve">12.5141916275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7266988754272</t>
   </si>
   <si>
     <t xml:space="preserve">12.8368854522705</t>
@@ -4526,16 +4526,16 @@
     <t xml:space="preserve">12.8132753372192</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5378046035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3882656097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9077215194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7345685958862</t>
+    <t xml:space="preserve">12.537805557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3882637023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9077205657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7345695495605</t>
   </si>
   <si>
     <t xml:space="preserve">12.5063238143921</t>
@@ -4547,28 +4547,28 @@
     <t xml:space="preserve">12.1049242019653</t>
   </si>
   <si>
-    <t xml:space="preserve">12.270206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2308530807495</t>
+    <t xml:space="preserve">12.2702054977417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2308521270752</t>
   </si>
   <si>
     <t xml:space="preserve">12.3016872406006</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3252992630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9160308837891</t>
+    <t xml:space="preserve">12.3253002166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9160299301147</t>
   </si>
   <si>
     <t xml:space="preserve">11.4516668319702</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6563024520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1132326126099</t>
+    <t xml:space="preserve">11.6563014984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1132335662842</t>
   </si>
   <si>
     <t xml:space="preserve">11.1289739608765</t>
@@ -4580,49 +4580,49 @@
     <t xml:space="preserve">11.0266571044922</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8062810897827</t>
+    <t xml:space="preserve">10.8062801361084</t>
   </si>
   <si>
     <t xml:space="preserve">10.8456344604492</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7118349075317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8613758087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.995174407959</t>
+    <t xml:space="preserve">10.7118339538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8613748550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9951753616333</t>
   </si>
   <si>
     <t xml:space="preserve">10.9873046875</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9085988998413</t>
+    <t xml:space="preserve">10.908597946167</t>
   </si>
   <si>
     <t xml:space="preserve">11.0581398010254</t>
   </si>
   <si>
-    <t xml:space="preserve">11.176197052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.585467338562</t>
+    <t xml:space="preserve">11.1761980056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5854663848877</t>
   </si>
   <si>
     <t xml:space="preserve">11.5225019454956</t>
   </si>
   <si>
-    <t xml:space="preserve">11.774359703064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8766765594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8137130737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9947366714478</t>
+    <t xml:space="preserve">11.7743606567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8766784667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8137140274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9947357177734</t>
   </si>
   <si>
     <t xml:space="preserve">12.1285352706909</t>
@@ -4637,10 +4637,10 @@
     <t xml:space="preserve">11.9789953231812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5697250366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.60120677948</t>
+    <t xml:space="preserve">11.5697269439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6012077331543</t>
   </si>
   <si>
     <t xml:space="preserve">11.8058423995972</t>
@@ -4664,7 +4664,7 @@
     <t xml:space="preserve">11.8475370407104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6614074707031</t>
+    <t xml:space="preserve">11.6614084243774</t>
   </si>
   <si>
     <t xml:space="preserve">11.6290378570557</t>
@@ -4676,16 +4676,16 @@
     <t xml:space="preserve">11.7666120529175</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4995574951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3296127319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5076494216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6371307373047</t>
+    <t xml:space="preserve">11.4995565414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3296136856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5076484680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.637131690979</t>
   </si>
   <si>
     <t xml:space="preserve">11.5319271087646</t>
@@ -4694,46 +4694,46 @@
     <t xml:space="preserve">11.5966672897339</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5885753631592</t>
+    <t xml:space="preserve">11.5885744094849</t>
   </si>
   <si>
     <t xml:space="preserve">11.5400190353394</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4429082870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3862600326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5157423019409</t>
+    <t xml:space="preserve">11.4429092407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3862609863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5157413482666</t>
   </si>
   <si>
     <t xml:space="preserve">11.4671869277954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4186305999756</t>
+    <t xml:space="preserve">11.4186296463013</t>
   </si>
   <si>
     <t xml:space="preserve">11.3781681060791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3700761795044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5723905563354</t>
+    <t xml:space="preserve">11.3700752258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5723896026611</t>
   </si>
   <si>
     <t xml:space="preserve">11.3943529129028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4510011672974</t>
+    <t xml:space="preserve">11.451000213623</t>
   </si>
   <si>
     <t xml:space="preserve">11.6047601699829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6533155441284</t>
+    <t xml:space="preserve">11.6533145904541</t>
   </si>
   <si>
     <t xml:space="preserve">11.6209449768066</t>
@@ -4751,10 +4751,10 @@
     <t xml:space="preserve">11.8232593536377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9446477890015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.815167427063</t>
+    <t xml:space="preserve">11.9446487426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8151664733887</t>
   </si>
   <si>
     <t xml:space="preserve">11.9365568161011</t>
@@ -4763,7 +4763,7 @@
     <t xml:space="preserve">12.090313911438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1712408065796</t>
+    <t xml:space="preserve">12.1712417602539</t>
   </si>
   <si>
     <t xml:space="preserve">12.2521667480469</t>
@@ -4784,13 +4784,13 @@
     <t xml:space="preserve">12.3007221221924</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4140176773071</t>
+    <t xml:space="preserve">12.4140186309814</t>
   </si>
   <si>
     <t xml:space="preserve">12.6082401275635</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8914804458618</t>
+    <t xml:space="preserve">12.8914813995361</t>
   </si>
   <si>
     <t xml:space="preserve">12.9966831207275</t>
@@ -4820,22 +4820,22 @@
     <t xml:space="preserve">12.9804992675781</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0290546417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0937948226929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1989974975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9076652526855</t>
+    <t xml:space="preserve">13.0290555953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0937957763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1989984512329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9076642990112</t>
   </si>
   <si>
     <t xml:space="preserve">12.851016998291</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9885911941528</t>
+    <t xml:space="preserve">12.9885902404785</t>
   </si>
   <si>
     <t xml:space="preserve">12.9238510131836</t>
@@ -4850,7 +4850,7 @@
     <t xml:space="preserve">13.1747217178345</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1666278839111</t>
+    <t xml:space="preserve">13.1666288375854</t>
   </si>
   <si>
     <t xml:space="preserve">12.9724073410034</t>
@@ -4865,16 +4865,16 @@
     <t xml:space="preserve">12.5677766799927</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4787588119507</t>
+    <t xml:space="preserve">12.478759765625</t>
   </si>
   <si>
     <t xml:space="preserve">12.7539072036743</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7296276092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5839624404907</t>
+    <t xml:space="preserve">12.7296285629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.583963394165</t>
   </si>
   <si>
     <t xml:space="preserve">12.5758695602417</t>
@@ -4892,25 +4892,25 @@
     <t xml:space="preserve">13.0209617614746</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0371465682983</t>
+    <t xml:space="preserve">13.0371475219727</t>
   </si>
   <si>
     <t xml:space="preserve">13.2475538253784</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9400358200073</t>
+    <t xml:space="preserve">12.940034866333</t>
   </si>
   <si>
     <t xml:space="preserve">13.1504430770874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3365716934204</t>
+    <t xml:space="preserve">13.3365726470947</t>
   </si>
   <si>
     <t xml:space="preserve">13.5874433517456</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4903316497803</t>
+    <t xml:space="preserve">13.490330696106</t>
   </si>
   <si>
     <t xml:space="preserve">13.2880172729492</t>
@@ -4919,19 +4919,19 @@
     <t xml:space="preserve">13.3203868865967</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3042020797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0128679275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7862768173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2036113739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4544820785522</t>
+    <t xml:space="preserve">13.3042011260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0128688812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7862777709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2036104202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4544801712036</t>
   </si>
   <si>
     <t xml:space="preserve">12.8995733261108</t>
@@ -4940,7 +4940,7 @@
     <t xml:space="preserve">13.0533313751221</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2151823043823</t>
+    <t xml:space="preserve">13.2151832580566</t>
   </si>
   <si>
     <t xml:space="preserve">13.5388870239258</t>
@@ -4952,13 +4952,13 @@
     <t xml:space="preserve">13.4579601287842</t>
   </si>
   <si>
-    <t xml:space="preserve">13.595534324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0163478851318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8221263885498</t>
+    <t xml:space="preserve">13.5955352783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0163488388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8221273422241</t>
   </si>
   <si>
     <t xml:space="preserve">13.9435157775879</t>
@@ -4973,34 +4973,34 @@
     <t xml:space="preserve">13.9597005844116</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8814220428467</t>
+    <t xml:space="preserve">13.881422996521</t>
   </si>
   <si>
     <t xml:space="preserve">13.5770053863525</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7248659133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6900749206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7509593963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.490029335022</t>
+    <t xml:space="preserve">13.7248640060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.69007396698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7509574890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4900283813477</t>
   </si>
   <si>
     <t xml:space="preserve">13.5248193740845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6987724304199</t>
+    <t xml:space="preserve">13.6987714767456</t>
   </si>
   <si>
     <t xml:space="preserve">13.6552839279175</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8553295135498</t>
+    <t xml:space="preserve">13.8553304672241</t>
   </si>
   <si>
     <t xml:space="preserve">13.672679901123</t>
@@ -5009,19 +5009,19 @@
     <t xml:space="preserve">13.7857484817505</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7770509719849</t>
+    <t xml:space="preserve">13.7770500183105</t>
   </si>
   <si>
     <t xml:space="preserve">13.8205394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1336536407471</t>
+    <t xml:space="preserve">14.1336545944214</t>
   </si>
   <si>
     <t xml:space="preserve">13.9683980941772</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8466320037842</t>
+    <t xml:space="preserve">13.8466329574585</t>
   </si>
   <si>
     <t xml:space="preserve">13.7074699401855</t>
@@ -5045,13 +5045,13 @@
     <t xml:space="preserve">14.342396736145</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0379791259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.011887550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5161228179932</t>
+    <t xml:space="preserve">14.0379781723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0118865966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5161218643188</t>
   </si>
   <si>
     <t xml:space="preserve">13.620493888855</t>
@@ -5069,7 +5069,7 @@
     <t xml:space="preserve">13.9857940673828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9249114990234</t>
+    <t xml:space="preserve">13.9249105453491</t>
   </si>
   <si>
     <t xml:space="preserve">13.8031435012817</t>
@@ -5096,19 +5096,19 @@
     <t xml:space="preserve">14.4032802581787</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2815141677856</t>
+    <t xml:space="preserve">14.2815132141113</t>
   </si>
   <si>
     <t xml:space="preserve">14.3076066970825</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3858852386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.603325843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5598363876343</t>
+    <t xml:space="preserve">14.3858861923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6033267974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5598373413086</t>
   </si>
   <si>
     <t xml:space="preserve">14.7598829269409</t>
@@ -5117,55 +5117,55 @@
     <t xml:space="preserve">14.9686260223389</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8294639587402</t>
+    <t xml:space="preserve">14.8294630050659</t>
   </si>
   <si>
     <t xml:space="preserve">14.6990003585815</t>
   </si>
   <si>
-    <t xml:space="preserve">14.620719909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7337913513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7076969146729</t>
+    <t xml:space="preserve">14.6207208633423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7337923049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7076978683472</t>
   </si>
   <si>
     <t xml:space="preserve">14.6903018951416</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8990459442139</t>
+    <t xml:space="preserve">14.8990440368652</t>
   </si>
   <si>
     <t xml:space="preserve">14.8381624221802</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7511854171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7250928878784</t>
+    <t xml:space="preserve">14.7511863708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7250938415527</t>
   </si>
   <si>
     <t xml:space="preserve">14.6729078292847</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0121145248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0816965103149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1164855957031</t>
+    <t xml:space="preserve">15.0121154785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0816955566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1164846420288</t>
   </si>
   <si>
     <t xml:space="preserve">15.4469966888428</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6122512817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7079267501831</t>
+    <t xml:space="preserve">15.6122531890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7079248428345</t>
   </si>
   <si>
     <t xml:space="preserve">15.7862033843994</t>
@@ -5174,10 +5174,10 @@
     <t xml:space="preserve">15.7340183258057</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9862489700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1341075897217</t>
+    <t xml:space="preserve">15.9862499237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1341094970703</t>
   </si>
   <si>
     <t xml:space="preserve">15.9253644943237</t>
@@ -5198,7 +5198,7 @@
     <t xml:space="preserve">16.9951763153076</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9777793884277</t>
+    <t xml:space="preserve">16.9777812957764</t>
   </si>
   <si>
     <t xml:space="preserve">17.1952209472656</t>
@@ -5219,13 +5219,13 @@
     <t xml:space="preserve">18.038890838623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8127517700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3172149658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2128429412842</t>
+    <t xml:space="preserve">17.8127536773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3172168731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2128448486328</t>
   </si>
   <si>
     <t xml:space="preserve">18.4041919708252</t>
@@ -5234,19 +5234,19 @@
     <t xml:space="preserve">18.3346118927002</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5433559417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6651210784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7173080444336</t>
+    <t xml:space="preserve">18.5433540344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6651191711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.717306137085</t>
   </si>
   <si>
     <t xml:space="preserve">17.9519138336182</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0736827850342</t>
+    <t xml:space="preserve">18.0736808776855</t>
   </si>
   <si>
     <t xml:space="preserve">17.7605667114258</t>
@@ -6039,6 +6039,9 @@
   </si>
   <si>
     <t xml:space="preserve">22.7600002288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7199993133545</t>
   </si>
 </sst>
 </file>
@@ -71039,7 +71042,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6495833333</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>162877</v>
@@ -71060,6 +71063,32 @@
         <v>1991</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6493402778</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>170384</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>22.7800006866455</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>22.4200000762939</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>22.7800006866455</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>22.7199993133545</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>2009</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IF.MI.xlsx
+++ b/data/IF.MI.xlsx
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7370796203613</t>
+    <t xml:space="preserve">15.7370777130127</t>
   </si>
   <si>
     <t xml:space="preserve">IF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3903503417969</t>
+    <t xml:space="preserve">15.3903474807739</t>
   </si>
   <si>
     <t xml:space="preserve">15.3232374191284</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5458917617798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3613414764404</t>
+    <t xml:space="preserve">14.5458898544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3613424301147</t>
   </si>
   <si>
     <t xml:space="preserve">14.3781175613403</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4284496307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1767911911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8646612167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8524312973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4955596923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6409664154053</t>
+    <t xml:space="preserve">14.4284505844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1767921447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8646593093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8524293899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4955606460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.640962600708</t>
   </si>
   <si>
     <t xml:space="preserve">14.4340438842773</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">15.3735723495483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3959379196167</t>
+    <t xml:space="preserve">15.3959426879883</t>
   </si>
   <si>
     <t xml:space="preserve">15.9384050369263</t>
@@ -92,22 +92,22 @@
     <t xml:space="preserve">15.943998336792</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5637130737305</t>
+    <t xml:space="preserve">15.5637140274048</t>
   </si>
   <si>
     <t xml:space="preserve">16.1061782836914</t>
   </si>
   <si>
-    <t xml:space="preserve">16.050256729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7706317901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1722412109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9597320556641</t>
+    <t xml:space="preserve">16.0502529144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7706346511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1722421646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9597311019897</t>
   </si>
   <si>
     <t xml:space="preserve">14.5402984619141</t>
@@ -116,46 +116,46 @@
     <t xml:space="preserve">13.0583057403564</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0974531173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7405834197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7685470581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8244676589966</t>
+    <t xml:space="preserve">13.0974550247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7405815124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7685432434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8244695663452</t>
   </si>
   <si>
     <t xml:space="preserve">14.5347061157227</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4396362304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3501596450806</t>
+    <t xml:space="preserve">14.4396371841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.350154876709</t>
   </si>
   <si>
     <t xml:space="preserve">14.2718639373779</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3333797454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4350862503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9765110015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7416276931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2057971954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0995426177979</t>
+    <t xml:space="preserve">14.3333806991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4350872039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9765100479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7416286468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2057962417603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0995416641235</t>
   </si>
   <si>
     <t xml:space="preserve">15.0436182022095</t>
@@ -164,28 +164,28 @@
     <t xml:space="preserve">15.4966039657593</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2840900421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9876937866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4452295303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5570755004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1656055450439</t>
+    <t xml:space="preserve">15.2840909957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9876928329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4452285766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5570774078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1656074523926</t>
   </si>
   <si>
     <t xml:space="preserve">14.4843740463257</t>
   </si>
   <si>
-    <t xml:space="preserve">14.719256401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1834297180176</t>
+    <t xml:space="preserve">14.7192554473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1834287643433</t>
   </si>
   <si>
     <t xml:space="preserve">15.3791637420654</t>
@@ -194,70 +194,70 @@
     <t xml:space="preserve">15.9999198913574</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2348041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0949935913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9663677215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1173610687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1403369903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4849739074707</t>
+    <t xml:space="preserve">16.234806060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0949954986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.966365814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1173629760742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1403388977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4849720001221</t>
   </si>
   <si>
     <t xml:space="preserve">16.7204704284668</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4160461425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8473997116089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3815841674805</t>
+    <t xml:space="preserve">16.4160442352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8473978042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3815822601318</t>
   </si>
   <si>
     <t xml:space="preserve">15.6004123687744</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6808271408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7842178344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8876085281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6348743438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.278754234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4280948638916</t>
+    <t xml:space="preserve">15.6808261871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7842149734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8876094818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6348762512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2787551879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4280967712402</t>
   </si>
   <si>
     <t xml:space="preserve">15.2385473251343</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1408996582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3821487426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9570999145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8479604721069</t>
+    <t xml:space="preserve">15.1409025192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3821449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9570989608765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8479642868042</t>
   </si>
   <si>
     <t xml:space="preserve">14.5894870758057</t>
@@ -266,46 +266,46 @@
     <t xml:space="preserve">14.6239500045776</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7043657302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5550231933594</t>
+    <t xml:space="preserve">14.7043647766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5550241470337</t>
   </si>
   <si>
     <t xml:space="preserve">14.3482427597046</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1184902191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8427829742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1644382476807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6704626083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6417455673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.325831413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1075630187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8376016616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9811983108521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7629299163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4814796447754</t>
+    <t xml:space="preserve">14.1184883117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8427801132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1644411087036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.670464515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6417446136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3258323669434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1075639724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8375997543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9811973571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7629280090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4814805984497</t>
   </si>
   <si>
     <t xml:space="preserve">12.6365642547607</t>
@@ -314,10 +314,10 @@
     <t xml:space="preserve">12.6882581710815</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3493690490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5791234970093</t>
+    <t xml:space="preserve">12.3493680953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5791244506836</t>
   </si>
   <si>
     <t xml:space="preserve">12.9352464675903</t>
@@ -332,46 +332,46 @@
     <t xml:space="preserve">13.785343170166</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5613327026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.664722442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3488054275513</t>
+    <t xml:space="preserve">13.5613298416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6647233963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3488063812256</t>
   </si>
   <si>
     <t xml:space="preserve">13.2683925628662</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3602962493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1535148620605</t>
+    <t xml:space="preserve">13.3602933883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1535129547119</t>
   </si>
   <si>
     <t xml:space="preserve">12.9639663696289</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7801637649536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5504064559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2057704925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0564298629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9185762405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6084070205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2287492752075</t>
+    <t xml:space="preserve">12.780161857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.550407409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2057695388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0564308166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9185771942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6084060668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2287473678589</t>
   </si>
   <si>
     <t xml:space="preserve">12.6537961959839</t>
@@ -380,31 +380,31 @@
     <t xml:space="preserve">12.5963573455811</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9869432449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1196136474609</t>
+    <t xml:space="preserve">12.9869403839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1196146011353</t>
   </si>
   <si>
     <t xml:space="preserve">10.1781768798828</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2643356323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3217754364014</t>
+    <t xml:space="preserve">10.2643375396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3217744827271</t>
   </si>
   <si>
     <t xml:space="preserve">10.425163269043</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4366521835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4538841247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93693351745605</t>
+    <t xml:space="preserve">10.436653137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4538860321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93693256378174</t>
   </si>
   <si>
     <t xml:space="preserve">9.58081340789795</t>
@@ -413,10 +413,10 @@
     <t xml:space="preserve">9.56932640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73015403747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76461791992188</t>
+    <t xml:space="preserve">9.7301549911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76461887359619</t>
   </si>
   <si>
     <t xml:space="preserve">10.8272380828857</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">11.4877853393555</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3269557952881</t>
+    <t xml:space="preserve">11.3269577026367</t>
   </si>
   <si>
     <t xml:space="preserve">11.516505241394</t>
@@ -437,16 +437,16 @@
     <t xml:space="preserve">11.2580299377441</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4992742538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2293090820312</t>
+    <t xml:space="preserve">11.4992723464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2293109893799</t>
   </si>
   <si>
     <t xml:space="preserve">11.0455055236816</t>
   </si>
   <si>
-    <t xml:space="preserve">10.861701965332</t>
+    <t xml:space="preserve">10.8617010116577</t>
   </si>
   <si>
     <t xml:space="preserve">10.6032257080078</t>
@@ -455,46 +455,46 @@
     <t xml:space="preserve">10.9995546340942</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7175416946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4188575744629</t>
+    <t xml:space="preserve">11.7175407409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4188585281372</t>
   </si>
   <si>
     <t xml:space="preserve">11.5796871185303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1144323348999</t>
+    <t xml:space="preserve">11.1144332885742</t>
   </si>
   <si>
     <t xml:space="preserve">11.1431522369385</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6026630401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7405157089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4016265869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6543588638306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5567140579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4533214569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3843975067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2867488861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9880666732788</t>
+    <t xml:space="preserve">11.6026639938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7405166625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4016284942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6543598175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5567121505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4533233642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3843946456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2867498397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9880657196045</t>
   </si>
   <si>
     <t xml:space="preserve">10.9765787124634</t>
@@ -506,22 +506,22 @@
     <t xml:space="preserve">11.0282745361328</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0972003936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9708337783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9650907516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1201763153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.206335067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1891021728516</t>
+    <t xml:space="preserve">11.0971994400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9708347320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9650897979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1201782226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2063360214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1891031265259</t>
   </si>
   <si>
     <t xml:space="preserve">11.4303464889526</t>
@@ -530,40 +530,40 @@
     <t xml:space="preserve">11.8324193954468</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3149080276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3953199386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9587831497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6945657730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.774977684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6715888977051</t>
+    <t xml:space="preserve">12.3149061203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3953218460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9587850570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6945629119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7749805450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6715908050537</t>
   </si>
   <si>
     <t xml:space="preserve">11.6888217926025</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5739421844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7692365646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0621747970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0219678878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.660101890564</t>
+    <t xml:space="preserve">11.5739431381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7692375183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0621738433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0219669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6601028442383</t>
   </si>
   <si>
     <t xml:space="preserve">11.5107622146606</t>
@@ -572,61 +572,61 @@
     <t xml:space="preserve">11.4935302734375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5279903411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7060527801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7577476501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0277118682861</t>
+    <t xml:space="preserve">11.5279932022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7060508728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7577466964722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0277137756348</t>
   </si>
   <si>
     <t xml:space="preserve">12.4068088531494</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4349660873413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6991834640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7279043197632</t>
+    <t xml:space="preserve">13.4349641799927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6991853713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7279033660889</t>
   </si>
   <si>
     <t xml:space="preserve">13.8657569885254</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9519176483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.175929069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3712205886841</t>
+    <t xml:space="preserve">13.9519147872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1759300231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3712196350098</t>
   </si>
   <si>
     <t xml:space="preserve">14.4631223678589</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8824262619019</t>
+    <t xml:space="preserve">14.8824234008789</t>
   </si>
   <si>
     <t xml:space="preserve">14.9628400802612</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1064386367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2270584106445</t>
+    <t xml:space="preserve">15.1064376831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2270603179932</t>
   </si>
   <si>
     <t xml:space="preserve">15.1351585388184</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9456062316895</t>
+    <t xml:space="preserve">14.9456100463867</t>
   </si>
   <si>
     <t xml:space="preserve">14.7158555984497</t>
@@ -635,46 +635,46 @@
     <t xml:space="preserve">14.7330837249756</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5090732574463</t>
+    <t xml:space="preserve">14.5090713500977</t>
   </si>
   <si>
     <t xml:space="preserve">14.5952291488647</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5435352325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3827085494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0725364685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0610485076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6474895477295</t>
+    <t xml:space="preserve">14.5435371398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3827056884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0725374221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0610475540161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6474905014038</t>
   </si>
   <si>
     <t xml:space="preserve">13.6876964569092</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5900497436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5383567810059</t>
+    <t xml:space="preserve">13.5900506973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5383558273315</t>
   </si>
   <si>
     <t xml:space="preserve">13.0501222610474</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1190490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1822338104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7514419555664</t>
+    <t xml:space="preserve">13.1190500259399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1822328567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7514429092407</t>
   </si>
   <si>
     <t xml:space="preserve">13.2109527587891</t>
@@ -683,70 +683,70 @@
     <t xml:space="preserve">13.4407081604004</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4234752655029</t>
+    <t xml:space="preserve">13.4234762191772</t>
   </si>
   <si>
     <t xml:space="preserve">13.285623550415</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1414642333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2735738754272</t>
+    <t xml:space="preserve">14.1414623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2735748291016</t>
   </si>
   <si>
     <t xml:space="preserve">14.1931581497192</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3597326278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9398641586304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6871328353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3884506225586</t>
+    <t xml:space="preserve">14.35973072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.939866065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6871347427368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3884534835815</t>
   </si>
   <si>
     <t xml:space="preserve">14.4746103286743</t>
   </si>
   <si>
-    <t xml:space="preserve">14.784779548645</t>
+    <t xml:space="preserve">14.7847785949707</t>
   </si>
   <si>
     <t xml:space="preserve">14.9341201782227</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2213153839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5831813812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4970235824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4510698318481</t>
+    <t xml:space="preserve">15.2213163375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5831823348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4970216751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4510688781738</t>
   </si>
   <si>
     <t xml:space="preserve">15.3361921310425</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8364725112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9915618896484</t>
+    <t xml:space="preserve">14.8364744186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9915599822998</t>
   </si>
   <si>
     <t xml:space="preserve">15.2959852218628</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1638793945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0375089645386</t>
+    <t xml:space="preserve">15.1638784408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0375099182129</t>
   </si>
   <si>
     <t xml:space="preserve">15.089207649231</t>
@@ -755,10 +755,10 @@
     <t xml:space="preserve">15.0719766616821</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8307304382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6469249725342</t>
+    <t xml:space="preserve">14.8307313919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6469278335571</t>
   </si>
   <si>
     <t xml:space="preserve">14.5320491790771</t>
@@ -767,49 +767,49 @@
     <t xml:space="preserve">14.2333660125732</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5263071060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4171705245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3941946029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.048996925354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7618055343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6584148406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8766822814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3936309814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8531427383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8416566848755</t>
+    <t xml:space="preserve">14.5263051986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4171724319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3941955566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0489978790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7618045806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6584157943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8766832351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3936328887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8531436920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8416557312012</t>
   </si>
   <si>
     <t xml:space="preserve">16.0369472503662</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5079460144043</t>
+    <t xml:space="preserve">16.5079479217529</t>
   </si>
   <si>
     <t xml:space="preserve">16.9559707641602</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0880794525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6343097686768</t>
+    <t xml:space="preserve">17.0880813598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.634313583374</t>
   </si>
   <si>
     <t xml:space="preserve">16.6113395690918</t>
@@ -818,13 +818,13 @@
     <t xml:space="preserve">16.0828990936279</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8870468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9444808959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3465557098389</t>
+    <t xml:space="preserve">16.8870429992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9444828033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3465538024902</t>
   </si>
   <si>
     <t xml:space="preserve">17.4844093322754</t>
@@ -833,10 +833,10 @@
     <t xml:space="preserve">17.5935440063477</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0593605041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1684970855713</t>
+    <t xml:space="preserve">17.0593585968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.168493270874</t>
   </si>
   <si>
     <t xml:space="preserve">17.6911907196045</t>
@@ -848,124 +848,124 @@
     <t xml:space="preserve">18.7365779876709</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5522117614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.816427230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9944915771484</t>
+    <t xml:space="preserve">19.552209854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8164310455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9944896697998</t>
   </si>
   <si>
     <t xml:space="preserve">20.942232131958</t>
   </si>
   <si>
-    <t xml:space="preserve">20.522928237915</t>
+    <t xml:space="preserve">20.5229301452637</t>
   </si>
   <si>
     <t xml:space="preserve">20.8503265380859</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7354564666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.678014755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6492958068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3218898773193</t>
+    <t xml:space="preserve">20.7354526519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6780128479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6492919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.321891784668</t>
   </si>
   <si>
     <t xml:space="preserve">20.5631351470947</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6378059387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8388385772705</t>
+    <t xml:space="preserve">20.6378078460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8388404846191</t>
   </si>
   <si>
     <t xml:space="preserve">20.8216094970703</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6090869903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1088066101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4132328033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2409152984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1777305603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0226459503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9594669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3098392486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5855522155762</t>
+    <t xml:space="preserve">20.6090888977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1088047027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4132308959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2409133911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1777286529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0226497650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9594650268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3098411560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5855484008789</t>
   </si>
   <si>
     <t xml:space="preserve">21.3155860900879</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2690715789795</t>
+    <t xml:space="preserve">22.2690734863281</t>
   </si>
   <si>
     <t xml:space="preserve">22.136962890625</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9818782806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2288646697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.745813369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9335041046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5815830230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3938961029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4671726226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4583282470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1035194396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8161201477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6342926025391</t>
+    <t xml:space="preserve">21.9818801879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2288665771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7458152770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9335060119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5815868377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.393892288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4671688079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4583301544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1035175323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8161182403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6342906951904</t>
   </si>
   <si>
     <t xml:space="preserve">20.692943572998</t>
   </si>
   <si>
-    <t xml:space="preserve">20.587366104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.296989440918</t>
+    <t xml:space="preserve">20.5873641967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2969913482666</t>
   </si>
   <si>
     <t xml:space="preserve">18.5872840881348</t>
@@ -986,19 +986,19 @@
     <t xml:space="preserve">20.5287132263184</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4114074707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2706432342529</t>
+    <t xml:space="preserve">20.4114055633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2706356048584</t>
   </si>
   <si>
     <t xml:space="preserve">20.3058319091797</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7955455780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.607852935791</t>
+    <t xml:space="preserve">19.7955474853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6078548431396</t>
   </si>
   <si>
     <t xml:space="preserve">19.8835277557373</t>
@@ -1010,19 +1010,19 @@
     <t xml:space="preserve">20.0594863891602</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1767921447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7515964508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6988086700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3527526855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5521755218506</t>
+    <t xml:space="preserve">20.176794052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7515983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6988105773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3527507781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5521774291992</t>
   </si>
   <si>
     <t xml:space="preserve">20.5052528381348</t>
@@ -1034,37 +1034,37 @@
     <t xml:space="preserve">20.4407348632812</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1474647521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0477542877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0008335113525</t>
+    <t xml:space="preserve">20.1474666595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0477561950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0008316040039</t>
   </si>
   <si>
     <t xml:space="preserve">20.4876556396484</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6694850921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6460227966309</t>
+    <t xml:space="preserve">20.6694869995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6460189819336</t>
   </si>
   <si>
     <t xml:space="preserve">20.863037109375</t>
   </si>
   <si>
-    <t xml:space="preserve">20.933422088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0096702575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9275569915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1152496337891</t>
+    <t xml:space="preserve">20.9334239959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.009672164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9275550842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1152458190918</t>
   </si>
   <si>
     <t xml:space="preserve">21.2560176849365</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">21.6313991546631</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6079406738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6431293487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8366889953613</t>
+    <t xml:space="preserve">21.6079349517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6431312561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8366870880127</t>
   </si>
   <si>
     <t xml:space="preserve">22.0830326080322</t>
@@ -1103,46 +1103,46 @@
     <t xml:space="preserve">22.9041786193848</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6402397155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9686985015869</t>
+    <t xml:space="preserve">22.6402378082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9686965942383</t>
   </si>
   <si>
     <t xml:space="preserve">22.7575454711914</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2854251861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4907131195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7722492218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0068645477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.270809173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8719635009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1007118225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0479183197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5434989929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5669631958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1593627929688</t>
+    <t xml:space="preserve">23.2854270935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4907093048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7722511291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0068626403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2708034515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8719615936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1007099151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0479221343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5435009002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5669651031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1593608856201</t>
   </si>
   <si>
     <t xml:space="preserve">24.3529186248779</t>
@@ -1151,61 +1151,61 @@
     <t xml:space="preserve">24.3059959411621</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8543643951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.036190032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8367729187012</t>
+    <t xml:space="preserve">23.854362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0361919403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8367710113525</t>
   </si>
   <si>
     <t xml:space="preserve">23.8191738128662</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9716739654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7898483276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6373443603516</t>
+    <t xml:space="preserve">23.9716720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7898464202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6373462677002</t>
   </si>
   <si>
     <t xml:space="preserve">23.1153316497803</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7077312469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9012908935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1652317047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5347480773926</t>
+    <t xml:space="preserve">23.7077293395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9012928009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1652278900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5347423553467</t>
   </si>
   <si>
     <t xml:space="preserve">24.3411903381348</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0831146240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7400321960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7107028961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4936866760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.698974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0684967041016</t>
+    <t xml:space="preserve">24.0831165313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7400302886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7107086181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.493688583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6989765167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0684947967529</t>
   </si>
   <si>
     <t xml:space="preserve">25.7078170776367</t>
@@ -1220,79 +1220,79 @@
     <t xml:space="preserve">26.4937705993652</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3823261260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5876159667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1301212310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5993461608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8222312927246</t>
+    <t xml:space="preserve">26.3823299407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5876197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1301174163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.59934425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.822229385376</t>
   </si>
   <si>
     <t xml:space="preserve">27.1330947875977</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7548198699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0656852722168</t>
+    <t xml:space="preserve">27.7548236846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0656833648682</t>
   </si>
   <si>
     <t xml:space="preserve">28.2064514160156</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8984832763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7489547729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4997177124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8281803131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8927021026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6580848693848</t>
+    <t xml:space="preserve">26.8984813690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7489566802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4997215270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.828182220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8927001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6580867767334</t>
   </si>
   <si>
     <t xml:space="preserve">28.0539531707764</t>
   </si>
   <si>
-    <t xml:space="preserve">26.927806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5289611816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2152099609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.64040184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5378017425537</t>
+    <t xml:space="preserve">26.9278087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5289630889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2152118682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6404037475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5378036499023</t>
   </si>
   <si>
     <t xml:space="preserve">27.6316509246826</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6668376922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8428058624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3237609863281</t>
+    <t xml:space="preserve">27.6668395996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8428001403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3237648010254</t>
   </si>
   <si>
     <t xml:space="preserve">27.5671310424805</t>
@@ -1301,28 +1301,28 @@
     <t xml:space="preserve">27.6023235321045</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4556922912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5026168823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0803070068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8163661956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3060817718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9365634918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5992660522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8954219818115</t>
+    <t xml:space="preserve">27.4556903839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5026111602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0803050994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8163642883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3060779571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9365653991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5992603302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8954257965088</t>
   </si>
   <si>
     <t xml:space="preserve">22.9511032104492</t>
@@ -1337,25 +1337,25 @@
     <t xml:space="preserve">22.7164878845215</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7282180786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3176422119141</t>
+    <t xml:space="preserve">22.7282161712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3176460266113</t>
   </si>
   <si>
     <t xml:space="preserve">21.9833202362061</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6754283905029</t>
+    <t xml:space="preserve">22.6754302978516</t>
   </si>
   <si>
     <t xml:space="preserve">22.4056243896484</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6109142303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7927379608154</t>
+    <t xml:space="preserve">22.610912322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7927398681641</t>
   </si>
   <si>
     <t xml:space="preserve">22.2355289459229</t>
@@ -1370,16 +1370,16 @@
     <t xml:space="preserve">21.731107711792</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8249588012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4495697021484</t>
+    <t xml:space="preserve">21.8249530792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4495716094971</t>
   </si>
   <si>
     <t xml:space="preserve">20.9040966033936</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4026527404785</t>
+    <t xml:space="preserve">21.4026508331299</t>
   </si>
   <si>
     <t xml:space="preserve">21.8777446746826</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">22.4701442718506</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1914978027344</t>
+    <t xml:space="preserve">21.1915016174316</t>
   </si>
   <si>
     <t xml:space="preserve">21.1093826293945</t>
@@ -1400,31 +1400,31 @@
     <t xml:space="preserve">21.7135143280029</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7047576904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9130153656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0449485778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3440780639648</t>
+    <t xml:space="preserve">22.7047557830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9130172729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0449504852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3440799713135</t>
   </si>
   <si>
     <t xml:space="preserve">23.7546539306641</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7663879394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4496555328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5200462341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3469715118408</t>
+    <t xml:space="preserve">23.7663860321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4496574401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5200386047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3469696044922</t>
   </si>
   <si>
     <t xml:space="preserve">23.0273494720459</t>
@@ -1439,31 +1439,31 @@
     <t xml:space="preserve">23.0508136749268</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9569664001465</t>
+    <t xml:space="preserve">22.9569683074951</t>
   </si>
   <si>
     <t xml:space="preserve">22.781005859375</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5229301452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4994697570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2765827178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9452362060547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4525470733643</t>
+    <t xml:space="preserve">22.5229320526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4994716644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2765884399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9452381134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4525451660156</t>
   </si>
   <si>
     <t xml:space="preserve">22.0771656036377</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2208232879639</t>
+    <t xml:space="preserve">21.2208271026611</t>
   </si>
   <si>
     <t xml:space="preserve">20.7398681640625</t>
@@ -1475,10 +1475,10 @@
     <t xml:space="preserve">19.6489124298096</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4260272979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7750568389893</t>
+    <t xml:space="preserve">19.4260292053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7750606536865</t>
   </si>
   <si>
     <t xml:space="preserve">21.1621723175049</t>
@@ -1487,16 +1487,16 @@
     <t xml:space="preserve">20.9158267974854</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3733234405518</t>
+    <t xml:space="preserve">21.3733196258545</t>
   </si>
   <si>
     <t xml:space="preserve">21.3615913391113</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3264007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2794761657715</t>
+    <t xml:space="preserve">21.3264045715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2794780731201</t>
   </si>
   <si>
     <t xml:space="preserve">21.3967838287354</t>
@@ -1505,13 +1505,13 @@
     <t xml:space="preserve">21.0448665618896</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7985191345215</t>
+    <t xml:space="preserve">20.7985210418701</t>
   </si>
   <si>
     <t xml:space="preserve">20.6812114715576</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0125637054443</t>
+    <t xml:space="preserve">20.012565612793</t>
   </si>
   <si>
     <t xml:space="preserve">19.332181930542</t>
@@ -1526,13 +1526,13 @@
     <t xml:space="preserve">19.0975685119629</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0858383178711</t>
+    <t xml:space="preserve">19.0858402252197</t>
   </si>
   <si>
     <t xml:space="preserve">20.0712184906006</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9891014099121</t>
+    <t xml:space="preserve">19.9891033172607</t>
   </si>
   <si>
     <t xml:space="preserve">18.8394927978516</t>
@@ -1544,100 +1544,100 @@
     <t xml:space="preserve">18.5227661132812</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4377613067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2617988586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9919910430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3233451843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3614292144775</t>
+    <t xml:space="preserve">19.4377593994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2617969512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9919929504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3233432769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3614253997803</t>
   </si>
   <si>
     <t xml:space="preserve">18.6987247467041</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9596900939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.722188949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1210308074951</t>
+    <t xml:space="preserve">17.9596920013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7221870422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1210289001465</t>
   </si>
   <si>
     <t xml:space="preserve">19.2735328674316</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4142990112305</t>
+    <t xml:space="preserve">19.4142971038818</t>
   </si>
   <si>
     <t xml:space="preserve">20.1533336639404</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7310237884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5785274505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8131408691406</t>
+    <t xml:space="preserve">19.7310276031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5785293579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.813138961792</t>
   </si>
   <si>
     <t xml:space="preserve">19.6958351135254</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3461227416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3582191467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1404418945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0920467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1646385192871</t>
+    <t xml:space="preserve">19.3461246490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3582210540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1404399871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0920448303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1646366119385</t>
   </si>
   <si>
     <t xml:space="preserve">19.7816829681396</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9752655029297</t>
+    <t xml:space="preserve">19.9752635955811</t>
   </si>
   <si>
     <t xml:space="preserve">20.2656383514404</t>
   </si>
   <si>
-    <t xml:space="preserve">20.435022354126</t>
+    <t xml:space="preserve">20.4350204467773</t>
   </si>
   <si>
     <t xml:space="preserve">20.6648998260498</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3745288848877</t>
+    <t xml:space="preserve">20.3745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">20.0236587524414</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5397052764893</t>
+    <t xml:space="preserve">19.5397033691406</t>
   </si>
   <si>
     <t xml:space="preserve">19.4429130554199</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6485958099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7211856842041</t>
+    <t xml:space="preserve">19.6485919952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7211875915527</t>
   </si>
   <si>
     <t xml:space="preserve">18.9589595794678</t>
@@ -1646,70 +1646,70 @@
     <t xml:space="preserve">18.3298149108887</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4102993011475</t>
+    <t xml:space="preserve">17.4103012084961</t>
   </si>
   <si>
     <t xml:space="preserve">17.0836296081543</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2288188934326</t>
+    <t xml:space="preserve">17.228816986084</t>
   </si>
   <si>
     <t xml:space="preserve">16.8779487609863</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5149841308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6075649261475</t>
+    <t xml:space="preserve">16.5149822235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6075658798218</t>
   </si>
   <si>
     <t xml:space="preserve">14.1677989959717</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8853158950806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1194038391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2282943725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4260816574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4865770339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0147190093994</t>
+    <t xml:space="preserve">12.8853149414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.119402885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2282915115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.426082611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4865779876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0147228240967</t>
   </si>
   <si>
     <t xml:space="preserve">15.1478099822998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8332376480103</t>
+    <t xml:space="preserve">14.8332366943359</t>
   </si>
   <si>
     <t xml:space="preserve">14.7001495361328</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2929944992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1520156860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5996761322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.575475692749</t>
+    <t xml:space="preserve">15.2929964065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1520175933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5996723175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5754776000977</t>
   </si>
   <si>
     <t xml:space="preserve">16.0794219970703</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7932567596436</t>
+    <t xml:space="preserve">16.7932586669922</t>
   </si>
   <si>
     <t xml:space="preserve">17.2409133911133</t>
@@ -1724,31 +1724,31 @@
     <t xml:space="preserve">16.623872756958</t>
   </si>
   <si>
-    <t xml:space="preserve">15.970531463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4623794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.571270942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5954647064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6438608169556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6196622848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7890472412109</t>
+    <t xml:space="preserve">15.9705333709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.462381362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5712690353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5954666137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6438627243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.619665145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7890491485596</t>
   </si>
   <si>
     <t xml:space="preserve">16.0431251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4060935974121</t>
+    <t xml:space="preserve">16.4060916900635</t>
   </si>
   <si>
     <t xml:space="preserve">16.5875759124756</t>
@@ -1760,49 +1760,49 @@
     <t xml:space="preserve">15.9100379943848</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9947319030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8253469467163</t>
+    <t xml:space="preserve">15.9947290420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8253450393677</t>
   </si>
   <si>
     <t xml:space="preserve">16.6722679138184</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9384422302246</t>
+    <t xml:space="preserve">16.9384441375732</t>
   </si>
   <si>
     <t xml:space="preserve">16.2851047515869</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0552253723145</t>
+    <t xml:space="preserve">16.0552234649658</t>
   </si>
   <si>
     <t xml:space="preserve">16.2972030639648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3576965332031</t>
+    <t xml:space="preserve">16.3576984405518</t>
   </si>
   <si>
     <t xml:space="preserve">16.2125091552734</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3655881881714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5470724105835</t>
+    <t xml:space="preserve">15.3655872344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5470743179321</t>
   </si>
   <si>
     <t xml:space="preserve">14.6396570205688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3692712783813</t>
+    <t xml:space="preserve">13.369270324707</t>
   </si>
   <si>
     <t xml:space="preserve">13.6838426589966</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6475458145142</t>
+    <t xml:space="preserve">13.6475448608398</t>
   </si>
   <si>
     <t xml:space="preserve">13.6354475021362</t>
@@ -1811,19 +1811,19 @@
     <t xml:space="preserve">13.2845792770386</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0426006317139</t>
+    <t xml:space="preserve">13.0426015853882</t>
   </si>
   <si>
     <t xml:space="preserve">12.5102519989014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3771619796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4860515594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4497556686401</t>
+    <t xml:space="preserve">12.377161026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4860525131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4497566223145</t>
   </si>
   <si>
     <t xml:space="preserve">13.2603816986084</t>
@@ -1832,67 +1832,67 @@
     <t xml:space="preserve">12.7885255813599</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9700088500977</t>
+    <t xml:space="preserve">12.9700059890747</t>
   </si>
   <si>
     <t xml:space="preserve">12.9216146469116</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0909967422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3408660888672</t>
+    <t xml:space="preserve">13.0909976959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3408651351929</t>
   </si>
   <si>
     <t xml:space="preserve">12.2924709320068</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2561740875244</t>
+    <t xml:space="preserve">12.2561750411987</t>
   </si>
   <si>
     <t xml:space="preserve">12.7643260955811</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1998844146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6596450805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.526556968689</t>
+    <t xml:space="preserve">13.1998882293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.659646987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5265588760376</t>
   </si>
   <si>
     <t xml:space="preserve">13.3571720123291</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8895235061646</t>
+    <t xml:space="preserve">13.8895225524902</t>
   </si>
   <si>
     <t xml:space="preserve">13.5749530792236</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6717462539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3208780288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3450727462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5023603439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0589094161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4218759536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3976755142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2645893096924</t>
+    <t xml:space="preserve">13.67174243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3208770751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3450736999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5023593902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.058910369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3976764678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.264591217041</t>
   </si>
   <si>
     <t xml:space="preserve">14.4339733123779</t>
@@ -1901,10 +1901,10 @@
     <t xml:space="preserve">13.3934688568115</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7359209060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.864800453186</t>
+    <t xml:space="preserve">11.7359218597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8648023605347</t>
   </si>
   <si>
     <t xml:space="preserve">11.3003625869751</t>
@@ -1925,16 +1925,16 @@
     <t xml:space="preserve">10.5865278244019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2356595993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86664295196533</t>
+    <t xml:space="preserve">10.2356605529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86664199829102</t>
   </si>
   <si>
     <t xml:space="preserve">10.3264007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3022031784058</t>
+    <t xml:space="preserve">10.3022050857544</t>
   </si>
   <si>
     <t xml:space="preserve">10.4957857131958</t>
@@ -1943,106 +1943,106 @@
     <t xml:space="preserve">9.92108821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89689159393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5339241027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73539638519287</t>
+    <t xml:space="preserve">9.89689064025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53392314910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73539733886719</t>
   </si>
   <si>
     <t xml:space="preserve">8.37847995758057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22119331359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4692211151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49946975708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9713249206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06206607818604</t>
+    <t xml:space="preserve">8.22119522094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46922206878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49946880340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97132587432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06206703186035</t>
   </si>
   <si>
     <t xml:space="preserve">9.40083694458008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67910957336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.217511177063</t>
+    <t xml:space="preserve">9.67911052703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2175102233887</t>
   </si>
   <si>
     <t xml:space="preserve">9.88479137420654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12256240844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21935367584229</t>
+    <t xml:space="preserve">9.12256145477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21935272216797</t>
   </si>
   <si>
     <t xml:space="preserve">8.82008934020996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12861061096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24960136413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36453914642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58836841583252</t>
+    <t xml:space="preserve">9.12861251831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24959945678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36454010009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58836936950684</t>
   </si>
   <si>
     <t xml:space="preserve">9.48552799224854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45528125762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70935726165771</t>
+    <t xml:space="preserve">9.45528030395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7093563079834</t>
   </si>
   <si>
     <t xml:space="preserve">9.61256694793701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57022094726562</t>
+    <t xml:space="preserve">9.57021999359131</t>
   </si>
   <si>
     <t xml:space="preserve">10.8406038284302</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1370277404785</t>
+    <t xml:space="preserve">11.1370258331299</t>
   </si>
   <si>
     <t xml:space="preserve">10.9071483612061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5967845916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3064126968384</t>
+    <t xml:space="preserve">11.5967855453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3064117431641</t>
   </si>
   <si>
     <t xml:space="preserve">11.00998878479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.96764087677</t>
+    <t xml:space="preserve">10.9676418304443</t>
   </si>
   <si>
     <t xml:space="preserve">10.5139331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8285045623779</t>
+    <t xml:space="preserve">10.8285036087036</t>
   </si>
   <si>
     <t xml:space="preserve">10.3385009765625</t>
@@ -2051,73 +2051,73 @@
     <t xml:space="preserve">10.7377634048462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2840557098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6409711837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1007289886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0039396286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8587522506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3747968673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81219673156738</t>
+    <t xml:space="preserve">10.2840547561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6409730911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1007308959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0039386749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.85875415802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3747959136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8121976852417</t>
   </si>
   <si>
     <t xml:space="preserve">9.69120979309082</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3705883026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1709566116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03786849975586</t>
+    <t xml:space="preserve">9.37059020996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17095851898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03786945343018</t>
   </si>
   <si>
     <t xml:space="preserve">9.34034156799316</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34639263153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94528579711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4050436019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8043050765991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5562801361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6228246688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5804767608643</t>
+    <t xml:space="preserve">9.34639167785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94528675079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4050445556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8043069839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5562810897827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.62282371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5804786682129</t>
   </si>
   <si>
     <t xml:space="preserve">10.5502300262451</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0239295959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62466526031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1025714874268</t>
+    <t xml:space="preserve">10.0239286422729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62466621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1025724411011</t>
   </si>
   <si>
     <t xml:space="preserve">10.2296104431152</t>
@@ -2129,10 +2129,10 @@
     <t xml:space="preserve">10.3687467575073</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98763275146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96948337554932</t>
+    <t xml:space="preserve">9.98763179779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96948432922363</t>
   </si>
   <si>
     <t xml:space="preserve">10.2780055999756</t>
@@ -2141,16 +2141,16 @@
     <t xml:space="preserve">10.4352912902832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5320825576782</t>
+    <t xml:space="preserve">10.5320816040039</t>
   </si>
   <si>
     <t xml:space="preserve">10.1509675979614</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0299787521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1267690658569</t>
+    <t xml:space="preserve">10.0299777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1267681121826</t>
   </si>
   <si>
     <t xml:space="preserve">10.3445501327515</t>
@@ -2162,34 +2162,34 @@
     <t xml:space="preserve">9.64886283874512</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0946798324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6433372497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0323429107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3729553222656</t>
+    <t xml:space="preserve">11.0946807861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6433391571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0323438644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3729562759399</t>
   </si>
   <si>
     <t xml:space="preserve">10.8769006729126</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7014665603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6107244491577</t>
+    <t xml:space="preserve">10.7014675140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.610725402832</t>
   </si>
   <si>
     <t xml:space="preserve">10.5683784484863</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1086196899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3505992889404</t>
+    <t xml:space="preserve">10.1086206436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3506002426147</t>
   </si>
   <si>
     <t xml:space="preserve">10.9373950958252</t>
@@ -2198,31 +2198,31 @@
     <t xml:space="preserve">11.0341854095459</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1128301620483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4818439483643</t>
+    <t xml:space="preserve">11.112829208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4818449020386</t>
   </si>
   <si>
     <t xml:space="preserve">10.9736919403076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54602336883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35848999023438</t>
+    <t xml:space="preserve">9.54602241516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35849094390869</t>
   </si>
   <si>
     <t xml:space="preserve">9.22540283203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11046314239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08626556396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1346607208252</t>
+    <t xml:space="preserve">9.11046409606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08626461029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13465976715088</t>
   </si>
   <si>
     <t xml:space="preserve">8.92897891998291</t>
@@ -2237,16 +2237,16 @@
     <t xml:space="preserve">8.84428691864014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89873218536377</t>
+    <t xml:space="preserve">8.89873313903809</t>
   </si>
   <si>
     <t xml:space="preserve">9.0741662979126</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00157260894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24355125427246</t>
+    <t xml:space="preserve">9.00157356262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24355030059814</t>
   </si>
   <si>
     <t xml:space="preserve">9.4976282119751</t>
@@ -2255,19 +2255,19 @@
     <t xml:space="preserve">9.47947978973389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46133041381836</t>
+    <t xml:space="preserve">9.46133136749268</t>
   </si>
   <si>
     <t xml:space="preserve">9.38873672485352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6367654800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68515968322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71540641784668</t>
+    <t xml:space="preserve">9.63676643371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68516063690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.715407371521</t>
   </si>
   <si>
     <t xml:space="preserve">9.83034801483154</t>
@@ -2276,16 +2276,16 @@
     <t xml:space="preserve">10.2636575698853</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94029140472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65572929382324</t>
+    <t xml:space="preserve">9.9402904510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65572834014893</t>
   </si>
   <si>
     <t xml:space="preserve">9.72686958312988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21594905853271</t>
+    <t xml:space="preserve">9.21595001220703</t>
   </si>
   <si>
     <t xml:space="preserve">9.0477991104126</t>
@@ -2294,16 +2294,16 @@
     <t xml:space="preserve">8.73736763000488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52394485473633</t>
+    <t xml:space="preserve">8.52394580841064</t>
   </si>
   <si>
     <t xml:space="preserve">8.2781867980957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86427736282349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32345867156982</t>
+    <t xml:space="preserve">7.86427640914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32345771789551</t>
   </si>
   <si>
     <t xml:space="preserve">8.3751974105835</t>
@@ -2312,43 +2312,43 @@
     <t xml:space="preserve">8.31698989868164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07123184204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87721157073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90954637527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82547426223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56677961349487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72199583053589</t>
+    <t xml:space="preserve">8.0712308883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87721252441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90954732894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82547330856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56678056716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72199487686157</t>
   </si>
   <si>
     <t xml:space="preserve">7.59264945983887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5409107208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50210762023926</t>
+    <t xml:space="preserve">7.54091024398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50210618972778</t>
   </si>
   <si>
     <t xml:space="preserve">7.37275886535645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31455373764038</t>
+    <t xml:space="preserve">7.31455421447754</t>
   </si>
   <si>
     <t xml:space="preserve">7.66379022598267</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32748937606812</t>
+    <t xml:space="preserve">7.32748746871948</t>
   </si>
   <si>
     <t xml:space="preserve">7.24341297149658</t>
@@ -2357,16 +2357,16 @@
     <t xml:space="preserve">7.2886848449707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52150917053223</t>
+    <t xml:space="preserve">7.52150821685791</t>
   </si>
   <si>
     <t xml:space="preserve">7.26281499862671</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29515171051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25634813308716</t>
+    <t xml:space="preserve">7.2951512336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25634717941284</t>
   </si>
   <si>
     <t xml:space="preserve">7.41803073883057</t>
@@ -2378,40 +2378,40 @@
     <t xml:space="preserve">8.03242874145508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84487438201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70259237289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55384492874146</t>
+    <t xml:space="preserve">7.84487628936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70259428024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55384635925293</t>
   </si>
   <si>
     <t xml:space="preserve">7.76726722717285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79960441589355</t>
+    <t xml:space="preserve">7.79960346221924</t>
   </si>
   <si>
     <t xml:space="preserve">7.67672491073608</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99362277984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18117713928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7050313949585</t>
+    <t xml:space="preserve">7.99362373352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18117618560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70503044128418</t>
   </si>
   <si>
     <t xml:space="preserve">8.65329265594482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69856262207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79557418823242</t>
+    <t xml:space="preserve">8.69856357574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79557323455811</t>
   </si>
   <si>
     <t xml:space="preserve">8.58215141296387</t>
@@ -2420,19 +2420,19 @@
     <t xml:space="preserve">8.57568359375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49160861968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5562801361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95725631713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94432353973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93785381317139</t>
+    <t xml:space="preserve">8.49160957336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55628108978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95725536346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94432258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9378547668457</t>
   </si>
   <si>
     <t xml:space="preserve">8.75030136108398</t>
@@ -2444,13 +2444,13 @@
     <t xml:space="preserve">8.82791042327881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83437633514404</t>
+    <t xml:space="preserve">8.83437728881836</t>
   </si>
   <si>
     <t xml:space="preserve">8.71149826049805</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6080207824707</t>
+    <t xml:space="preserve">8.60802173614502</t>
   </si>
   <si>
     <t xml:space="preserve">8.66622638702393</t>
@@ -2459,22 +2459,22 @@
     <t xml:space="preserve">8.38813209533691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29758930206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5433464050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02839756011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91845226287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88611602783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12540721893311</t>
+    <t xml:space="preserve">8.29758739471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54334735870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02839660644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9184513092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88611698150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12540626525879</t>
   </si>
   <si>
     <t xml:space="preserve">8.48514080047607</t>
@@ -2483,25 +2483,25 @@
     <t xml:space="preserve">8.11003589630127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87074518203735</t>
+    <t xml:space="preserve">7.8707447052002</t>
   </si>
   <si>
     <t xml:space="preserve">8.26525211334229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33639144897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43340110778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36872959136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28465461730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23938274383545</t>
+    <t xml:space="preserve">8.33639240264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4334020614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36872863769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28465557098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23938369750977</t>
   </si>
   <si>
     <t xml:space="preserve">8.5627498626709</t>
@@ -2513,25 +2513,25 @@
     <t xml:space="preserve">9.02192974090576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13187408447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2224178314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45524120330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.442307472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50697994232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55871868133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58458709716797</t>
+    <t xml:space="preserve">9.13187313079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22241687774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45524024963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44230651855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50698089599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55871772766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58458805084229</t>
   </si>
   <si>
     <t xml:space="preserve">9.69453144073486</t>
@@ -2540,10 +2540,10 @@
     <t xml:space="preserve">9.91442203521729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92088985443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73333644866943</t>
+    <t xml:space="preserve">9.92089080810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73333549499512</t>
   </si>
   <si>
     <t xml:space="preserve">9.89501953125</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">9.67513084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57812213897705</t>
+    <t xml:space="preserve">9.57812118530273</t>
   </si>
   <si>
     <t xml:space="preserve">9.66866397857666</t>
@@ -2564,22 +2564,22 @@
     <t xml:space="preserve">9.90148735046387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70746803283691</t>
+    <t xml:space="preserve">9.7074670791626</t>
   </si>
   <si>
     <t xml:space="preserve">9.5199146270752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30649185180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33236217498779</t>
+    <t xml:space="preserve">9.30649280548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33236122131348</t>
   </si>
   <si>
     <t xml:space="preserve">9.43583965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09953689575195</t>
+    <t xml:space="preserve">9.09953784942627</t>
   </si>
   <si>
     <t xml:space="preserve">9.37116622924805</t>
@@ -2588,19 +2588,19 @@
     <t xml:space="preserve">9.52638244628906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79154300689697</t>
+    <t xml:space="preserve">9.79154396057129</t>
   </si>
   <si>
     <t xml:space="preserve">9.7398042678833</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76567363739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87561798095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95322608947754</t>
+    <t xml:space="preserve">9.76567268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87561893463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95322704315186</t>
   </si>
   <si>
     <t xml:space="preserve">9.99849700927734</t>
@@ -2609,10 +2609,10 @@
     <t xml:space="preserve">9.94675922393799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.772141456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8820858001709</t>
+    <t xml:space="preserve">9.77214050292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88208484649658</t>
   </si>
   <si>
     <t xml:space="preserve">9.98556232452393</t>
@@ -2624,13 +2624,13 @@
     <t xml:space="preserve">9.44877338409424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83034610748291</t>
+    <t xml:space="preserve">9.83034706115723</t>
   </si>
   <si>
     <t xml:space="preserve">9.86915111541748</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1925172805786</t>
+    <t xml:space="preserve">10.1925182342529</t>
   </si>
   <si>
     <t xml:space="preserve">10.2377891540527</t>
@@ -2639,31 +2639,31 @@
     <t xml:space="preserve">9.62339210510254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41643810272217</t>
+    <t xml:space="preserve">9.41643714904785</t>
   </si>
   <si>
     <t xml:space="preserve">9.34529590606689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24181938171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19007968902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06073379516602</t>
+    <t xml:space="preserve">9.24181842803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1900806427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0607328414917</t>
   </si>
   <si>
     <t xml:space="preserve">9.0801362991333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97665882110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04133129119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92492008209229</t>
+    <t xml:space="preserve">8.97665977478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04133224487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92491912841797</t>
   </si>
   <si>
     <t xml:space="preserve">8.7632360458374</t>
@@ -2675,34 +2675,34 @@
     <t xml:space="preserve">8.78263854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61448669433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56921577453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67916202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86671352386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87318229675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81497478485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86024570465088</t>
+    <t xml:space="preserve">8.61448764801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56921672821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67916107177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86671447753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87318134307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81497669219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8602466583252</t>
   </si>
   <si>
     <t xml:space="preserve">9.24828720092773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05426597595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14480876922607</t>
+    <t xml:space="preserve">9.05426692962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14481067657471</t>
   </si>
   <si>
     <t xml:space="preserve">9.2353515625</t>
@@ -2711,7 +2711,7 @@
     <t xml:space="preserve">9.15774440765381</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13834190368652</t>
+    <t xml:space="preserve">9.13834285736084</t>
   </si>
   <si>
     <t xml:space="preserve">9.2676887512207</t>
@@ -2732,22 +2732,22 @@
     <t xml:space="preserve">9.57165336608887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51344680786133</t>
+    <t xml:space="preserve">9.51344776153564</t>
   </si>
   <si>
     <t xml:space="preserve">9.53284931182861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32589530944824</t>
+    <t xml:space="preserve">9.32589435577393</t>
   </si>
   <si>
     <t xml:space="preserve">9.30002593994141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74627113342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47464370727539</t>
+    <t xml:space="preserve">9.74627208709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47464275360107</t>
   </si>
   <si>
     <t xml:space="preserve">9.27415561676025</t>
@@ -2759,16 +2759,16 @@
     <t xml:space="preserve">9.70100021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80447673797607</t>
+    <t xml:space="preserve">9.80447769165039</t>
   </si>
   <si>
     <t xml:space="preserve">10.1343116760254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1278438568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.069637298584</t>
+    <t xml:space="preserve">10.1278448104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0696382522583</t>
   </si>
   <si>
     <t xml:space="preserve">10.1407785415649</t>
@@ -2777,37 +2777,37 @@
     <t xml:space="preserve">10.0049648284912</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1472454071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35176467895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55225086212158</t>
+    <t xml:space="preserve">10.1472444534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35176372528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5522518157959</t>
   </si>
   <si>
     <t xml:space="preserve">8.89258289337158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40753269195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90308094024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88124322891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61608171463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59668016433716</t>
+    <t xml:space="preserve">8.40753364562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9030818939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88124227523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61608123779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59667921066284</t>
   </si>
   <si>
     <t xml:space="preserve">5.67185115814209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93701171875</t>
+    <t xml:space="preserve">5.93701219558716</t>
   </si>
   <si>
     <t xml:space="preserve">5.61364507675171</t>
@@ -2816,31 +2816,31 @@
     <t xml:space="preserve">5.44549512863159</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45842885971069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43902730941772</t>
+    <t xml:space="preserve">5.45842838287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43902683258057</t>
   </si>
   <si>
     <t xml:space="preserve">5.75592613220215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57160758972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84000205993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86910486221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98228406906128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90790939331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66214990615845</t>
+    <t xml:space="preserve">5.57160806655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84000158309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86910533905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9822826385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90790891647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66215038299561</t>
   </si>
   <si>
     <t xml:space="preserve">5.78826284408569</t>
@@ -2852,16 +2852,16 @@
     <t xml:space="preserve">5.7009539604187</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78179550170898</t>
+    <t xml:space="preserve">5.78179597854614</t>
   </si>
   <si>
     <t xml:space="preserve">5.83676862716675</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96934843063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94671297073364</t>
+    <t xml:space="preserve">5.9693489074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9467134475708</t>
   </si>
   <si>
     <t xml:space="preserve">5.97581624984741</t>
@@ -2870,13 +2870,13 @@
     <t xml:space="preserve">5.83353519439697</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71388864517212</t>
+    <t xml:space="preserve">5.71388912200928</t>
   </si>
   <si>
     <t xml:space="preserve">5.76886129379272</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77532768249512</t>
+    <t xml:space="preserve">5.77532863616943</t>
   </si>
   <si>
     <t xml:space="preserve">5.49723339080811</t>
@@ -2885,19 +2885,19 @@
     <t xml:space="preserve">5.38405466079712</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51663541793823</t>
+    <t xml:space="preserve">5.51663494110107</t>
   </si>
   <si>
     <t xml:space="preserve">5.81413269042969</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93054437637329</t>
+    <t xml:space="preserve">5.93054485321045</t>
   </si>
   <si>
     <t xml:space="preserve">5.77209520339966</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56190633773804</t>
+    <t xml:space="preserve">5.5619068145752</t>
   </si>
   <si>
     <t xml:space="preserve">5.62011241912842</t>
@@ -2906,28 +2906,28 @@
     <t xml:space="preserve">5.5845422744751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47136402130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55867338180542</t>
+    <t xml:space="preserve">5.47136449813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55867290496826</t>
   </si>
   <si>
     <t xml:space="preserve">5.48106527328491</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40669012069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3258490562439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22560548782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19326829910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17386627197266</t>
+    <t xml:space="preserve">5.40668964385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32584857940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22560596466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19326782226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17386674880981</t>
   </si>
   <si>
     <t xml:space="preserve">4.947509765625</t>
@@ -2936,40 +2936,40 @@
     <t xml:space="preserve">4.81169605255127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70821905136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7211537361145</t>
+    <t xml:space="preserve">4.70821857452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72115325927734</t>
   </si>
   <si>
     <t xml:space="preserve">4.97984647750854</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18033409118652</t>
+    <t xml:space="preserve">5.18033456802368</t>
   </si>
   <si>
     <t xml:space="preserve">5.33554983139038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4293270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36465311050415</t>
+    <t xml:space="preserve">5.42932653427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36465406417847</t>
   </si>
   <si>
     <t xml:space="preserve">5.40022325515747</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72682332992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94347906112671</t>
+    <t xml:space="preserve">5.72682428359985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94347953796387</t>
   </si>
   <si>
     <t xml:space="preserve">6.25391149520874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70015621185303</t>
+    <t xml:space="preserve">6.70015716552734</t>
   </si>
   <si>
     <t xml:space="preserve">6.28624820709229</t>
@@ -2981,28 +2981,28 @@
     <t xml:space="preserve">5.67508506774902</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63304805755615</t>
+    <t xml:space="preserve">5.63304758071899</t>
   </si>
   <si>
     <t xml:space="preserve">5.78502941131592</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87880611419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8206000328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73329067230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58777666091919</t>
+    <t xml:space="preserve">5.87880516052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82059955596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7332911491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58777713775635</t>
   </si>
   <si>
     <t xml:space="preserve">5.53603792190552</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39699029922485</t>
+    <t xml:space="preserve">5.3969898223877</t>
   </si>
   <si>
     <t xml:space="preserve">5.31614780426025</t>
@@ -3020,25 +3020,25 @@
     <t xml:space="preserve">5.51340103149414</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6459813117981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75269365310669</t>
+    <t xml:space="preserve">5.64598226547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75269317626953</t>
   </si>
   <si>
     <t xml:space="preserve">5.86587142944336</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80119800567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89497470855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87557172775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22804164886475</t>
+    <t xml:space="preserve">5.80119848251343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89497375488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.875572681427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22804260253906</t>
   </si>
   <si>
     <t xml:space="preserve">6.34768676757812</t>
@@ -3047,16 +3047,16 @@
     <t xml:space="preserve">6.39942693710327</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19570541381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05989170074463</t>
+    <t xml:space="preserve">6.1957049369812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05989122390747</t>
   </si>
   <si>
     <t xml:space="preserve">5.91761016845703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77856254577637</t>
+    <t xml:space="preserve">5.77856302261353</t>
   </si>
   <si>
     <t xml:space="preserve">5.60717821121216</t>
@@ -3065,16 +3065,16 @@
     <t xml:space="preserve">5.60394430160522</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80766487121582</t>
+    <t xml:space="preserve">5.80766534805298</t>
   </si>
   <si>
     <t xml:space="preserve">5.81736612319946</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68478584289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93377780914307</t>
+    <t xml:space="preserve">5.68478536605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93377876281738</t>
   </si>
   <si>
     <t xml:space="preserve">5.91114330291748</t>
@@ -3083,10 +3083,10 @@
     <t xml:space="preserve">5.94024610519409</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82383394241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79473066329956</t>
+    <t xml:space="preserve">5.82383298873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79473114013672</t>
   </si>
   <si>
     <t xml:space="preserve">5.89820766448975</t>
@@ -3101,67 +3101,67 @@
     <t xml:space="preserve">5.79796457290649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63951444625854</t>
+    <t xml:space="preserve">5.6395149230957</t>
   </si>
   <si>
     <t xml:space="preserve">5.59101009368896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58130836486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70418834686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70742130279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66538381576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69448804855347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88204002380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80443143844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71065521240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50693416595459</t>
+    <t xml:space="preserve">5.58130884170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70418739318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70742177963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66538429260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69448709487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88203954696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80443239212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7106556892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50693511962891</t>
   </si>
   <si>
     <t xml:space="preserve">5.39052200317383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33878374099731</t>
+    <t xml:space="preserve">5.33878326416016</t>
   </si>
   <si>
     <t xml:space="preserve">5.43255996704102</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30321311950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31938171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21267080307007</t>
+    <t xml:space="preserve">5.30321264266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31938123703003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21267032623291</t>
   </si>
   <si>
     <t xml:space="preserve">5.21590375900269</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2288384437561</t>
+    <t xml:space="preserve">5.22883892059326</t>
   </si>
   <si>
     <t xml:space="preserve">5.34201765060425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26764345169067</t>
+    <t xml:space="preserve">5.26764249801636</t>
   </si>
   <si>
     <t xml:space="preserve">5.32261514663696</t>
@@ -3173,7 +3173,7 @@
     <t xml:space="preserve">5.21913814544678</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07362270355225</t>
+    <t xml:space="preserve">5.07362222671509</t>
   </si>
   <si>
     <t xml:space="preserve">5.12212800979614</t>
@@ -3185,16 +3185,16 @@
     <t xml:space="preserve">5.07038927078247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10919332504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20296955108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04128646850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99601554870605</t>
+    <t xml:space="preserve">5.10919284820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20297050476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04128694534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9960150718689</t>
   </si>
   <si>
     <t xml:space="preserve">4.92164087295532</t>
@@ -3206,28 +3206,28 @@
     <t xml:space="preserve">4.82463073730469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50773143768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36221694946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4527587890625</t>
+    <t xml:space="preserve">4.50773096084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36221647262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45275926589966</t>
   </si>
   <si>
     <t xml:space="preserve">4.58857297897339</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78259372711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89900493621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82786464691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79229354858398</t>
+    <t xml:space="preserve">4.7825927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8990044593811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82786417007446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79229402542114</t>
   </si>
   <si>
     <t xml:space="preserve">5.13829660415649</t>
@@ -3245,13 +3245,13 @@
     <t xml:space="preserve">5.65891695022583</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84323596954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85940408706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07606029510498</t>
+    <t xml:space="preserve">5.84323501586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85940456390381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07606077194214</t>
   </si>
   <si>
     <t xml:space="preserve">6.00815296173096</t>
@@ -3260,25 +3260,25 @@
     <t xml:space="preserve">5.97904968261719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98874998092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90467596054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17630290985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29918146133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31858444213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34445381164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21834135055542</t>
+    <t xml:space="preserve">5.98875093460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90467548370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17630243301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29918336868286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31858491897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34445428848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21834182739258</t>
   </si>
   <si>
     <t xml:space="preserve">6.19247198104858</t>
@@ -3290,55 +3290,55 @@
     <t xml:space="preserve">6.0566577911377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10516309738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10192966461182</t>
+    <t xml:space="preserve">6.10516166687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1019287109375</t>
   </si>
   <si>
     <t xml:space="preserve">6.0404896736145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03725481033325</t>
+    <t xml:space="preserve">6.03725576400757</t>
   </si>
   <si>
     <t xml:space="preserve">6.06635808944702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8885064125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95318078994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99198389053345</t>
+    <t xml:space="preserve">5.88850688934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95317983627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99198484420776</t>
   </si>
   <si>
     <t xml:space="preserve">5.98551654815674</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02432060241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01138591766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97258234024048</t>
+    <t xml:space="preserve">6.02432012557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01138639450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97258186340332</t>
   </si>
   <si>
     <t xml:space="preserve">5.73005723953247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73975849151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64921522140503</t>
+    <t xml:space="preserve">5.73975801467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64921474456787</t>
   </si>
   <si>
     <t xml:space="preserve">5.55543947219849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36788654327393</t>
+    <t xml:space="preserve">5.36788702011108</t>
   </si>
   <si>
     <t xml:space="preserve">5.46813058853149</t>
@@ -3347,19 +3347,19 @@
     <t xml:space="preserve">5.41639184951782</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7235894203186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07282590866089</t>
+    <t xml:space="preserve">5.72358989715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07282638549805</t>
   </si>
   <si>
     <t xml:space="preserve">6.26037883758545</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39619302749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75836277008057</t>
+    <t xml:space="preserve">6.39619255065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75836372375488</t>
   </si>
   <si>
     <t xml:space="preserve">6.67428731918335</t>
@@ -3368,31 +3368,31 @@
     <t xml:space="preserve">6.75189542770386</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66782093048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66135358810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58374547958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64195108413696</t>
+    <t xml:space="preserve">6.6678204536438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66135311126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5837459564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64195251464844</t>
   </si>
   <si>
     <t xml:space="preserve">6.69369125366211</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90064525604248</t>
+    <t xml:space="preserve">6.90064430236816</t>
   </si>
   <si>
     <t xml:space="preserve">6.803635597229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9717845916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83597183227539</t>
+    <t xml:space="preserve">6.97178554534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83597087860107</t>
   </si>
   <si>
     <t xml:space="preserve">6.85537385940552</t>
@@ -3404,16 +3404,16 @@
     <t xml:space="preserve">7.2110767364502</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19167423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23694658279419</t>
+    <t xml:space="preserve">7.19167470932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23694610595703</t>
   </si>
   <si>
     <t xml:space="preserve">7.42449855804443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4827036857605</t>
+    <t xml:space="preserve">7.48270463943481</t>
   </si>
   <si>
     <t xml:space="preserve">7.39216232299805</t>
@@ -3422,49 +3422,49 @@
     <t xml:space="preserve">7.41156339645386</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16580533981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19814157485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24988079071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35335731506348</t>
+    <t xml:space="preserve">7.16580486297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19814205169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24987983703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35335826873779</t>
   </si>
   <si>
     <t xml:space="preserve">7.36629199981689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27574968338013</t>
+    <t xml:space="preserve">7.27575063705444</t>
   </si>
   <si>
     <t xml:space="preserve">7.32102108001709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34688997268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15287113189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49563884735107</t>
+    <t xml:space="preserve">7.34689140319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15287065505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49564075469971</t>
   </si>
   <si>
     <t xml:space="preserve">7.43743276596069</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3986291885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3598256111145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08172941207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26928234100342</t>
+    <t xml:space="preserve">7.39862871170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35982465744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08173036575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26928329467773</t>
   </si>
   <si>
     <t xml:space="preserve">7.46330213546753</t>
@@ -3473,10 +3473,10 @@
     <t xml:space="preserve">7.51504182815552</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46977043151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44390201568604</t>
+    <t xml:space="preserve">7.46976947784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44390106201172</t>
   </si>
   <si>
     <t xml:space="preserve">7.47623729705811</t>
@@ -3491,73 +3491,73 @@
     <t xml:space="preserve">7.69612598419189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1165018081665</t>
+    <t xml:space="preserve">8.11650276184082</t>
   </si>
   <si>
     <t xml:space="preserve">8.43986892700195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46573829650879</t>
+    <t xml:space="preserve">8.46573925018311</t>
   </si>
   <si>
     <t xml:space="preserve">8.40106582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2587833404541</t>
+    <t xml:space="preserve">8.25878524780273</t>
   </si>
   <si>
     <t xml:space="preserve">8.18764305114746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05182838439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22644710540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31052398681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34932613372803</t>
+    <t xml:space="preserve">8.05183029174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22644805908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31052494049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34932708740234</t>
   </si>
   <si>
     <t xml:space="preserve">8.4204683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38166332244873</t>
+    <t xml:space="preserve">8.38166427612305</t>
   </si>
   <si>
     <t xml:space="preserve">8.50454330444336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14884090423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01546287536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.905517578125</t>
+    <t xml:space="preserve">8.14883995056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01546192169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90551853179932</t>
   </si>
   <si>
     <t xml:space="preserve">8.64682388305664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59508609771729</t>
+    <t xml:space="preserve">8.59508514404297</t>
   </si>
   <si>
     <t xml:space="preserve">8.51101016998291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29111957550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78910446166992</t>
+    <t xml:space="preserve">8.2911205291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78910541534424</t>
   </si>
   <si>
     <t xml:space="preserve">8.23291492462158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35579586029053</t>
+    <t xml:space="preserve">8.35579395294189</t>
   </si>
   <si>
     <t xml:space="preserve">8.96372318267822</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">9.00252819061279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99605941772461</t>
+    <t xml:space="preserve">8.99606132507324</t>
   </si>
   <si>
     <t xml:space="preserve">9.06720161437988</t>
@@ -3584,19 +3584,19 @@
     <t xml:space="preserve">9.19654750823975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46817588806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4229040145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37763214111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39056777954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46170902252197</t>
+    <t xml:space="preserve">9.46817684173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42290496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3776330947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39056873321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46170997619629</t>
   </si>
   <si>
     <t xml:space="preserve">9.20948314666748</t>
@@ -3605,19 +3605,19 @@
     <t xml:space="preserve">9.36469841003418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49404525756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48110961914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56518745422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81094455718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0437669754028</t>
+    <t xml:space="preserve">9.49404430389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48111057281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.565185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81094551086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0437679290771</t>
   </si>
   <si>
     <t xml:space="preserve">10.0890407562256</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">10.3283309936523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4059391021729</t>
+    <t xml:space="preserve">10.4059410095215</t>
   </si>
   <si>
     <t xml:space="preserve">10.4447431564331</t>
@@ -3638,28 +3638,28 @@
     <t xml:space="preserve">10.7616424560547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8263158798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1173467636108</t>
+    <t xml:space="preserve">10.8263149261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1173458099365</t>
   </si>
   <si>
     <t xml:space="preserve">10.5611553192139</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9685964584351</t>
+    <t xml:space="preserve">10.9685974121094</t>
   </si>
   <si>
     <t xml:space="preserve">10.5934906005859</t>
   </si>
   <si>
-    <t xml:space="preserve">10.813380241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6775674819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6581649780273</t>
+    <t xml:space="preserve">10.8133792877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6775665283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6581659317017</t>
   </si>
   <si>
     <t xml:space="preserve">10.8198490142822</t>
@@ -3671,10 +3671,10 @@
     <t xml:space="preserve">11.0074024200439</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0009346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2567710876465</t>
+    <t xml:space="preserve">11.0009336471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2567691802979</t>
   </si>
   <si>
     <t xml:space="preserve">11.2291116714478</t>
@@ -3683,28 +3683,28 @@
     <t xml:space="preserve">11.0908222198486</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9110460281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0078477859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1046514511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0424203872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.056248664856</t>
+    <t xml:space="preserve">10.9110450744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.007848739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1046504974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0424213409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0562496185303</t>
   </si>
   <si>
     <t xml:space="preserve">11.1945390701294</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3051710128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.505690574646</t>
+    <t xml:space="preserve">11.3051719665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5056896209717</t>
   </si>
   <si>
     <t xml:space="preserve">11.5748348236084</t>
@@ -3719,40 +3719,40 @@
     <t xml:space="preserve">11.6508951187134</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4780321121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7131261825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6923828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6301517486572</t>
+    <t xml:space="preserve">11.4780330657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7131252288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6923818588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6301507949829</t>
   </si>
   <si>
     <t xml:space="preserve">11.5402631759644</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2636842727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1392240524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.828070640564</t>
+    <t xml:space="preserve">11.2636833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1392230987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8280715942383</t>
   </si>
   <si>
     <t xml:space="preserve">10.9456176757812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5514917373657</t>
+    <t xml:space="preserve">10.55149269104</t>
   </si>
   <si>
     <t xml:space="preserve">10.5100059509277</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4961767196655</t>
+    <t xml:space="preserve">10.4961757659912</t>
   </si>
   <si>
     <t xml:space="preserve">9.97067642211914</t>
@@ -3767,10 +3767,10 @@
     <t xml:space="preserve">10.6828670501709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5445775985718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4616050720215</t>
+    <t xml:space="preserve">10.5445785522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4616041183472</t>
   </si>
   <si>
     <t xml:space="preserve">10.8419008255005</t>
@@ -3785,10 +3785,10 @@
     <t xml:space="preserve">10.9663610458374</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9179601669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8211574554443</t>
+    <t xml:space="preserve">10.9179592132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.82115650177</t>
   </si>
   <si>
     <t xml:space="preserve">10.5653209686279</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">11.0493354797363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0355062484741</t>
+    <t xml:space="preserve">11.0355052947998</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546119689941</t>
@@ -3809,19 +3809,19 @@
     <t xml:space="preserve">11.8030118942261</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0934209823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.23171043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1487369537354</t>
+    <t xml:space="preserve">12.0934219360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2317113876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.148736000061</t>
   </si>
   <si>
     <t xml:space="preserve">11.9413032531738</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1210803985596</t>
+    <t xml:space="preserve">12.1210794448853</t>
   </si>
   <si>
     <t xml:space="preserve">12.0795907974243</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">12.2593679428101</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4184007644653</t>
+    <t xml:space="preserve">12.418402671814</t>
   </si>
   <si>
     <t xml:space="preserve">12.4737176895142</t>
@@ -3839,64 +3839,64 @@
     <t xml:space="preserve">12.6050910949707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.757212638855</t>
+    <t xml:space="preserve">12.7572116851807</t>
   </si>
   <si>
     <t xml:space="preserve">12.3285121917725</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2870283126831</t>
+    <t xml:space="preserve">12.2870273590088</t>
   </si>
   <si>
     <t xml:space="preserve">12.6880674362183</t>
   </si>
   <si>
-    <t xml:space="preserve">12.570520401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8514127731323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2455387115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3561716079712</t>
+    <t xml:space="preserve">12.5705194473267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8514137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2455396652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3561725616455</t>
   </si>
   <si>
     <t xml:space="preserve">12.376914024353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.266282081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2040510177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6396646499634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4806318283081</t>
+    <t xml:space="preserve">12.2662830352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2040519714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6396656036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4806327819824</t>
   </si>
   <si>
     <t xml:space="preserve">12.3907442092896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7364683151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2757959365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1885070800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3129692077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9352722167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9905872344971</t>
+    <t xml:space="preserve">12.7364673614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2757978439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1885080337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.312970161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9352703094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9905891418457</t>
   </si>
   <si>
     <t xml:space="preserve">14.7554941177368</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">13.9672451019287</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6215190887451</t>
+    <t xml:space="preserve">13.6215209960938</t>
   </si>
   <si>
     <t xml:space="preserve">12.68115234375</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">12.3354272842407</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5774345397949</t>
+    <t xml:space="preserve">12.5774335861206</t>
   </si>
   <si>
     <t xml:space="preserve">12.3492574691772</t>
@@ -3938,7 +3938,7 @@
     <t xml:space="preserve">11.7615261077881</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0285921096802</t>
+    <t xml:space="preserve">11.0285911560059</t>
   </si>
   <si>
     <t xml:space="preserve">11.3674011230469</t>
@@ -3947,13 +3947,13 @@
     <t xml:space="preserve">11.8652429580688</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1694812774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8056116104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7157220840454</t>
+    <t xml:space="preserve">12.1694803237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8056125640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7157249450684</t>
   </si>
   <si>
     <t xml:space="preserve">12.7433815002441</t>
@@ -3962,28 +3962,28 @@
     <t xml:space="preserve">13.0614471435547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9992160797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8885869979858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0337915420532</t>
+    <t xml:space="preserve">12.9992170333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8885850906372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0337896347046</t>
   </si>
   <si>
     <t xml:space="preserve">13.0683622360229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.909330368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0199604034424</t>
+    <t xml:space="preserve">12.9093294143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0199613571167</t>
   </si>
   <si>
     <t xml:space="preserve">12.2731971740723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6465797424316</t>
+    <t xml:space="preserve">12.646580696106</t>
   </si>
   <si>
     <t xml:space="preserve">12.494460105896</t>
@@ -4004,16 +4004,16 @@
     <t xml:space="preserve">12.0865077972412</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9205598831177</t>
+    <t xml:space="preserve">11.9205589294434</t>
   </si>
   <si>
     <t xml:space="preserve">11.3466567993164</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5817489624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0242767333984</t>
+    <t xml:space="preserve">11.5817499160767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0242757797241</t>
   </si>
   <si>
     <t xml:space="preserve">12.300856590271</t>
@@ -4022,13 +4022,13 @@
     <t xml:space="preserve">12.0381050109863</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5793085098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5939331054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5207996368408</t>
+    <t xml:space="preserve">12.579309463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5939340591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5208005905151</t>
   </si>
   <si>
     <t xml:space="preserve">12.769458770752</t>
@@ -4040,16 +4040,16 @@
     <t xml:space="preserve">12.7475204467773</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4184083938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3964691162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3745288848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3452739715576</t>
+    <t xml:space="preserve">12.4184093475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3964700698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.374529838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3452749252319</t>
   </si>
   <si>
     <t xml:space="preserve">12.3525876998901</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">12.140495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9795951843262</t>
+    <t xml:space="preserve">11.9795961380005</t>
   </si>
   <si>
     <t xml:space="preserve">11.7455615997314</t>
@@ -4067,10 +4067,10 @@
     <t xml:space="preserve">11.0434627532959</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4803190231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5900220870972</t>
+    <t xml:space="preserve">10.480318069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5900230407715</t>
   </si>
   <si>
     <t xml:space="preserve">10.9630126953125</t>
@@ -4079,19 +4079,19 @@
     <t xml:space="preserve">10.4583787918091</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4437503814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6777849197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5095729827881</t>
+    <t xml:space="preserve">10.443751335144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6777858734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5095720291138</t>
   </si>
   <si>
     <t xml:space="preserve">10.5022592544556</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2389726638794</t>
+    <t xml:space="preserve">10.2389717102051</t>
   </si>
   <si>
     <t xml:space="preserve">10.494945526123</t>
@@ -4103,7 +4103,7 @@
     <t xml:space="preserve">10.3998689651489</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2097187042236</t>
+    <t xml:space="preserve">10.2097177505493</t>
   </si>
   <si>
     <t xml:space="preserve">9.88060760498047</t>
@@ -4112,16 +4112,16 @@
     <t xml:space="preserve">9.75627708435059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70508193969727</t>
+    <t xml:space="preserve">9.70508289337158</t>
   </si>
   <si>
     <t xml:space="preserve">9.31015014648438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23701477050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43448162078857</t>
+    <t xml:space="preserve">9.23701572418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43448066711426</t>
   </si>
   <si>
     <t xml:space="preserve">9.69776821136475</t>
@@ -4130,7 +4130,7 @@
     <t xml:space="preserve">9.41254043579102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46373462677002</t>
+    <t xml:space="preserve">9.4637336730957</t>
   </si>
   <si>
     <t xml:space="preserve">9.06148910522461</t>
@@ -4139,7 +4139,7 @@
     <t xml:space="preserve">8.62267684936523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82745742797852</t>
+    <t xml:space="preserve">8.8274564743042</t>
   </si>
   <si>
     <t xml:space="preserve">8.97372817993164</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">9.18582057952881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25895500183105</t>
+    <t xml:space="preserve">9.25895595550537</t>
   </si>
   <si>
     <t xml:space="preserve">9.5368709564209</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">9.21507453918457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36865997314453</t>
+    <t xml:space="preserve">9.36865901947021</t>
   </si>
   <si>
     <t xml:space="preserve">9.39791393280029</t>
@@ -4175,28 +4175,28 @@
     <t xml:space="preserve">9.68314170837402</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55881118774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95374298095703</t>
+    <t xml:space="preserve">9.55881214141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95374202728271</t>
   </si>
   <si>
     <t xml:space="preserve">10.0195655822754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98299598693848</t>
+    <t xml:space="preserve">9.98299694061279</t>
   </si>
   <si>
     <t xml:space="preserve">9.72702312469482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47104930877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57343769073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80747127532959</t>
+    <t xml:space="preserve">9.47104835510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57343864440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80747222900391</t>
   </si>
   <si>
     <t xml:space="preserve">9.97568416595459</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">9.10537147521973</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22238826751709</t>
+    <t xml:space="preserve">9.22238731384277</t>
   </si>
   <si>
     <t xml:space="preserve">9.20044708251953</t>
@@ -4217,25 +4217,25 @@
     <t xml:space="preserve">9.06880283355713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.820143699646</t>
+    <t xml:space="preserve">8.82014274597168</t>
   </si>
   <si>
     <t xml:space="preserve">8.75432109832764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81282997131348</t>
+    <t xml:space="preserve">8.81282806396484</t>
   </si>
   <si>
     <t xml:space="preserve">8.7396936416626</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51297473907471</t>
+    <t xml:space="preserve">8.51297378540039</t>
   </si>
   <si>
     <t xml:space="preserve">8.68849849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44715213775635</t>
+    <t xml:space="preserve">8.44715118408203</t>
   </si>
   <si>
     <t xml:space="preserve">8.40326976776123</t>
@@ -4265,10 +4265,10 @@
     <t xml:space="preserve">8.89327716827393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59342193603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63730525970459</t>
+    <t xml:space="preserve">8.59342288970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63730430603027</t>
   </si>
   <si>
     <t xml:space="preserve">8.34476184844971</t>
@@ -4283,7 +4283,7 @@
     <t xml:space="preserve">8.13266849517822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86938095092773</t>
+    <t xml:space="preserve">7.86937999725342</t>
   </si>
   <si>
     <t xml:space="preserve">8.32282066345215</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">8.41789817810059</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33013534545898</t>
+    <t xml:space="preserve">8.33013439178467</t>
   </si>
   <si>
     <t xml:space="preserve">8.24237251281738</t>
@@ -4304,25 +4304,25 @@
     <t xml:space="preserve">8.0741605758667</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16192245483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04490566253662</t>
+    <t xml:space="preserve">8.16192150115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0449047088623</t>
   </si>
   <si>
     <t xml:space="preserve">8.05221939086914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28625392913818</t>
+    <t xml:space="preserve">8.28625297546387</t>
   </si>
   <si>
     <t xml:space="preserve">8.26431274414062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30088138580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38864231109619</t>
+    <t xml:space="preserve">8.30088233947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38864326477051</t>
   </si>
   <si>
     <t xml:space="preserve">8.48371887207031</t>
@@ -4334,7 +4334,7 @@
     <t xml:space="preserve">8.71775245666504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88596534729004</t>
+    <t xml:space="preserve">8.88596439361572</t>
   </si>
   <si>
     <t xml:space="preserve">8.922532081604</t>
@@ -4349,10 +4349,10 @@
     <t xml:space="preserve">9.84403991699219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488185882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1804628372192</t>
+    <t xml:space="preserve">10.0488195419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1804637908936</t>
   </si>
   <si>
     <t xml:space="preserve">10.1512088775635</t>
@@ -4367,13 +4367,13 @@
     <t xml:space="preserve">10.3340482711792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2789545059204</t>
+    <t xml:space="preserve">10.2789535522461</t>
   </si>
   <si>
     <t xml:space="preserve">10.3104362487793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3261775970459</t>
+    <t xml:space="preserve">10.3261766433716</t>
   </si>
   <si>
     <t xml:space="preserve">10.3576583862305</t>
@@ -4382,10 +4382,10 @@
     <t xml:space="preserve">10.3497886657715</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3891410827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2553424835205</t>
+    <t xml:space="preserve">10.3891401290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2553415298462</t>
   </si>
   <si>
     <t xml:space="preserve">10.2710838317871</t>
@@ -4400,7 +4400,7 @@
     <t xml:space="preserve">9.86968421936035</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88542652130127</t>
+    <t xml:space="preserve">9.88542556762695</t>
   </si>
   <si>
     <t xml:space="preserve">10.0507068634033</t>
@@ -4415,7 +4415,7 @@
     <t xml:space="preserve">10.1845064163208</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0034837722778</t>
+    <t xml:space="preserve">10.0034847259521</t>
   </si>
   <si>
     <t xml:space="preserve">10.0900602340698</t>
@@ -4454,19 +4454,19 @@
     <t xml:space="preserve">11.0423984527588</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1998090744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2234201431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2863855361938</t>
+    <t xml:space="preserve">11.1998100280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2234210968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2863864898682</t>
   </si>
   <si>
     <t xml:space="preserve">11.3650903701782</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3493499755859</t>
+    <t xml:space="preserve">11.3493490219116</t>
   </si>
   <si>
     <t xml:space="preserve">11.3414793014526</t>
@@ -4484,7 +4484,7 @@
     <t xml:space="preserve">11.3965730667114</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2155513763428</t>
+    <t xml:space="preserve">11.2155504226685</t>
   </si>
   <si>
     <t xml:space="preserve">11.4280567169189</t>
@@ -4496,7 +4496,7 @@
     <t xml:space="preserve">11.8294544219971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0813121795654</t>
+    <t xml:space="preserve">12.0813131332397</t>
   </si>
   <si>
     <t xml:space="preserve">12.1678886413574</t>
@@ -4505,10 +4505,10 @@
     <t xml:space="preserve">12.372522354126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3095598220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4040060043335</t>
+    <t xml:space="preserve">12.3095588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4040050506592</t>
   </si>
   <si>
     <t xml:space="preserve">12.5220632553101</t>
@@ -4526,13 +4526,13 @@
     <t xml:space="preserve">12.8132753372192</t>
   </si>
   <si>
-    <t xml:space="preserve">12.537805557251</t>
+    <t xml:space="preserve">12.5378046035767</t>
   </si>
   <si>
     <t xml:space="preserve">12.3882637023926</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9077205657959</t>
+    <t xml:space="preserve">12.9077215194702</t>
   </si>
   <si>
     <t xml:space="preserve">12.7345695495605</t>
@@ -4541,10 +4541,10 @@
     <t xml:space="preserve">12.5063238143921</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2465944290161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1049242019653</t>
+    <t xml:space="preserve">12.2465953826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1049251556396</t>
   </si>
   <si>
     <t xml:space="preserve">12.2702054977417</t>
@@ -4568,10 +4568,10 @@
     <t xml:space="preserve">11.6563014984131</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1132335662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1289739608765</t>
+    <t xml:space="preserve">11.1132326126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1289749145508</t>
   </si>
   <si>
     <t xml:space="preserve">11.0974912643433</t>
@@ -4580,7 +4580,7 @@
     <t xml:space="preserve">11.0266571044922</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8062801361084</t>
+    <t xml:space="preserve">10.8062810897827</t>
   </si>
   <si>
     <t xml:space="preserve">10.8456344604492</t>
@@ -4595,10 +4595,10 @@
     <t xml:space="preserve">10.9951753616333</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9873046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.908597946167</t>
+    <t xml:space="preserve">10.9873037338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9085969924927</t>
   </si>
   <si>
     <t xml:space="preserve">11.0581398010254</t>
@@ -4607,19 +4607,19 @@
     <t xml:space="preserve">11.1761980056763</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5854663848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5225019454956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7743606567383</t>
+    <t xml:space="preserve">11.585467338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5225028991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.774359703064</t>
   </si>
   <si>
     <t xml:space="preserve">11.8766784667969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8137140274048</t>
+    <t xml:space="preserve">11.8137130737305</t>
   </si>
   <si>
     <t xml:space="preserve">11.9947357177734</t>
@@ -4652,10 +4652,10 @@
     <t xml:space="preserve">11.325737953186</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3572206497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3336086273193</t>
+    <t xml:space="preserve">11.3572216033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3336095809937</t>
   </si>
   <si>
     <t xml:space="preserve">11.912278175354</t>
@@ -71068,7 +71068,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6493402778</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>170384</v>
@@ -71089,6 +71089,32 @@
         <v>2009</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6494907407</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>165673</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>22.8199996948242</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>22.2399997711182</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>22.8199996948242</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>22.2199993133545</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1942</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IF.MI.xlsx
+++ b/data/IF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2012" uniqueCount="2012">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2013" uniqueCount="2013">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.737078666687</t>
+    <t xml:space="preserve">15.7370748519897</t>
   </si>
   <si>
     <t xml:space="preserve">IF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3903474807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3232383728027</t>
+    <t xml:space="preserve">15.3903465270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3232393264771</t>
   </si>
   <si>
     <t xml:space="preserve">14.5458917617798</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3613443374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3781185150146</t>
+    <t xml:space="preserve">14.3613414764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3781175613403</t>
   </si>
   <si>
     <t xml:space="preserve">14.4284524917603</t>
@@ -65,91 +65,91 @@
     <t xml:space="preserve">14.1767911911011</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8646593093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8524312973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4955577850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6409635543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4340438842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3735704421997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3959407806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9384059906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9439992904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5637140274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1061782836914</t>
+    <t xml:space="preserve">14.8646621704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8524322509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4955596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6409645080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4340448379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3735723495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.395941734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9384050369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.943998336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5637130737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1061763763428</t>
   </si>
   <si>
     <t xml:space="preserve">16.0502548217773</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7706327438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1722450256348</t>
+    <t xml:space="preserve">15.7706336975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1722431182861</t>
   </si>
   <si>
     <t xml:space="preserve">14.9597311019897</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5402984619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0583076477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0974540710449</t>
+    <t xml:space="preserve">14.540301322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0583086013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0974559783936</t>
   </si>
   <si>
     <t xml:space="preserve">13.7405843734741</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7685441970825</t>
+    <t xml:space="preserve">13.7685480117798</t>
   </si>
   <si>
     <t xml:space="preserve">13.8244686126709</t>
   </si>
   <si>
-    <t xml:space="preserve">14.534707069397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4396333694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3501558303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2718639373779</t>
+    <t xml:space="preserve">14.5347061157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4396362304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3501567840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2718629837036</t>
   </si>
   <si>
     <t xml:space="preserve">14.3333778381348</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4350852966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9765119552612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7416257858276</t>
+    <t xml:space="preserve">15.4350862503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9765090942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.741626739502</t>
   </si>
   <si>
     <t xml:space="preserve">15.2057981491089</t>
@@ -158,70 +158,70 @@
     <t xml:space="preserve">15.0995426177979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0436172485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4966049194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2840909957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9876918792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4452304840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5570774078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1656093597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7192583084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1834268569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3791599273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9999217987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2348041534424</t>
+    <t xml:space="preserve">15.0436162948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.496600151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2840919494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9876956939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4452285766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5570764541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1656064987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4843759536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7192554473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1834297180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3791637420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9999227523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2348022460938</t>
   </si>
   <si>
     <t xml:space="preserve">16.0949935913086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9663667678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1173629760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1403369903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4849739074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7204723358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4160461425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8474006652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3815822601318</t>
+    <t xml:space="preserve">15.9663677215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1173610687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1403388977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4849720001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7204704284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4160442352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8473997116089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3815803527832</t>
   </si>
   <si>
     <t xml:space="preserve">15.6004123687744</t>
@@ -230,43 +230,43 @@
     <t xml:space="preserve">15.6808271408081</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7842149734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8876085281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6348743438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.278754234314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4280958175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.23854637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1408987045288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3821458816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9570970535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8479614257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.58948802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.623950958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7043676376343</t>
+    <t xml:space="preserve">15.7842178344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8876066207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.634877204895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2787561416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4280948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2385473251343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1408996582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3821468353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9570951461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8479623794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5894861221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6239528656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7043647766113</t>
   </si>
   <si>
     <t xml:space="preserve">14.5550231933594</t>
@@ -278,22 +278,22 @@
     <t xml:space="preserve">14.1184873580933</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8427829742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.164439201355</t>
+    <t xml:space="preserve">13.8427839279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1644411087036</t>
   </si>
   <si>
     <t xml:space="preserve">13.670464515686</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6417455673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.325831413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1075630187988</t>
+    <t xml:space="preserve">13.6417465209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3258295059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1075620651245</t>
   </si>
   <si>
     <t xml:space="preserve">12.8376007080078</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">12.9811964035034</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7629280090332</t>
+    <t xml:space="preserve">12.7629289627075</t>
   </si>
   <si>
     <t xml:space="preserve">12.4814796447754</t>
@@ -314,16 +314,16 @@
     <t xml:space="preserve">12.6882600784302</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3493680953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5791263580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.935245513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.514817237854</t>
+    <t xml:space="preserve">12.3493690490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5791254043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9352464675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5148153305054</t>
   </si>
   <si>
     <t xml:space="preserve">13.9576578140259</t>
@@ -335,37 +335,37 @@
     <t xml:space="preserve">13.5613307952881</t>
   </si>
   <si>
-    <t xml:space="preserve">13.664722442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3488054275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2683916091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3602924346924</t>
+    <t xml:space="preserve">13.6647205352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3488082885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2683925628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3602952957153</t>
   </si>
   <si>
     <t xml:space="preserve">13.1535158157349</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9639673233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7801609039307</t>
+    <t xml:space="preserve">12.9639663696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.780161857605</t>
   </si>
   <si>
     <t xml:space="preserve">12.5504064559937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2057704925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0564308166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9185781478882</t>
+    <t xml:space="preserve">12.205771446228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0564317703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9185771942139</t>
   </si>
   <si>
     <t xml:space="preserve">11.6084070205688</t>
@@ -377,31 +377,31 @@
     <t xml:space="preserve">12.6537952423096</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5963573455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9869422912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1196146011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1781778335571</t>
+    <t xml:space="preserve">12.5963582992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9869432449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1196136474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1781768798828</t>
   </si>
   <si>
     <t xml:space="preserve">10.2643365859985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3217754364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4251651763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4366540908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4538841247559</t>
+    <t xml:space="preserve">10.3217725753784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4251642227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4366521835327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4538850784302</t>
   </si>
   <si>
     <t xml:space="preserve">9.93693351745605</t>
@@ -410,31 +410,31 @@
     <t xml:space="preserve">9.58081340789795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5693244934082</t>
+    <t xml:space="preserve">9.56932544708252</t>
   </si>
   <si>
     <t xml:space="preserve">9.7301549911499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76461887359619</t>
+    <t xml:space="preserve">9.76461791992188</t>
   </si>
   <si>
     <t xml:space="preserve">10.8272371292114</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2810039520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4877862930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3269557952881</t>
+    <t xml:space="preserve">11.281005859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4877853393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3269567489624</t>
   </si>
   <si>
     <t xml:space="preserve">11.5165042877197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2580308914185</t>
+    <t xml:space="preserve">11.2580289840698</t>
   </si>
   <si>
     <t xml:space="preserve">11.4992742538452</t>
@@ -449,34 +449,34 @@
     <t xml:space="preserve">10.8617000579834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6032238006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9995555877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7175388336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4188585281372</t>
+    <t xml:space="preserve">10.6032247543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9995536804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7175397872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4188604354858</t>
   </si>
   <si>
     <t xml:space="preserve">11.5796871185303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1144313812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1431522369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6026639938354</t>
+    <t xml:space="preserve">11.1144332885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1431512832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6026649475098</t>
   </si>
   <si>
     <t xml:space="preserve">11.7405157089233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4016265869141</t>
+    <t xml:space="preserve">11.4016275405884</t>
   </si>
   <si>
     <t xml:space="preserve">11.6543588638306</t>
@@ -485,55 +485,55 @@
     <t xml:space="preserve">11.5567121505737</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4533214569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3843965530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2867488861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9880666732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.976580619812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0397615432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0282754898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0972003936768</t>
+    <t xml:space="preserve">11.4533233642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3843936920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2867498397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9880676269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9765787124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0397605895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0282726287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0972013473511</t>
   </si>
   <si>
     <t xml:space="preserve">10.97083568573</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9650907516479</t>
+    <t xml:space="preserve">10.9650917053223</t>
   </si>
   <si>
     <t xml:space="preserve">11.1201763153076</t>
   </si>
   <si>
-    <t xml:space="preserve">11.206335067749</t>
+    <t xml:space="preserve">11.2063331604004</t>
   </si>
   <si>
     <t xml:space="preserve">11.1891031265259</t>
   </si>
   <si>
-    <t xml:space="preserve">11.430344581604</t>
+    <t xml:space="preserve">11.4303464889526</t>
   </si>
   <si>
     <t xml:space="preserve">11.8324193954468</t>
   </si>
   <si>
-    <t xml:space="preserve">12.314905166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3953189849854</t>
+    <t xml:space="preserve">12.3149070739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3953199386597</t>
   </si>
   <si>
     <t xml:space="preserve">11.9587841033936</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">11.7749814987183</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6715888977051</t>
+    <t xml:space="preserve">11.6715898513794</t>
   </si>
   <si>
     <t xml:space="preserve">11.6888217926025</t>
@@ -560,31 +560,31 @@
     <t xml:space="preserve">12.0621728897095</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0219669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.660101890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5107612609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4935283660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5279922485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7060546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7577476501465</t>
+    <t xml:space="preserve">12.0219697952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6600999832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5107622146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4935293197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5279912948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7060537338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7577466964722</t>
   </si>
   <si>
     <t xml:space="preserve">12.0277109146118</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4068088531494</t>
+    <t xml:space="preserve">12.4068069458008</t>
   </si>
   <si>
     <t xml:space="preserve">13.434965133667</t>
@@ -593,175 +593,175 @@
     <t xml:space="preserve">13.6991834640503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7279024124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8657579421997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9519147872925</t>
+    <t xml:space="preserve">13.7279014587402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8657569885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9519157409668</t>
   </si>
   <si>
     <t xml:space="preserve">14.1759281158447</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3712186813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4631195068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8824291229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9628410339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1064376831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2270574569702</t>
+    <t xml:space="preserve">14.3712205886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4631214141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8824253082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9628391265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1064367294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2270612716675</t>
   </si>
   <si>
     <t xml:space="preserve">15.1351566314697</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9456100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7158536911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7330846786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5090732574463</t>
+    <t xml:space="preserve">14.945611000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7158517837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7330856323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5090742111206</t>
   </si>
   <si>
     <t xml:space="preserve">14.5952301025391</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5435371398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3827075958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0725374221802</t>
+    <t xml:space="preserve">14.5435390472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3827066421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0725383758545</t>
   </si>
   <si>
     <t xml:space="preserve">14.0610485076904</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6474885940552</t>
+    <t xml:space="preserve">13.6474905014038</t>
   </si>
   <si>
     <t xml:space="preserve">13.6876964569092</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5900497436523</t>
+    <t xml:space="preserve">13.590048789978</t>
   </si>
   <si>
     <t xml:space="preserve">13.5383548736572</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0501251220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1190538406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1822357177734</t>
+    <t xml:space="preserve">13.0501232147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1190519332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1822328567505</t>
   </si>
   <si>
     <t xml:space="preserve">12.7514429092407</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2109508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4407062530518</t>
+    <t xml:space="preserve">13.2109518051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4407081604004</t>
   </si>
   <si>
     <t xml:space="preserve">13.4234771728516</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2856254577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1414632797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.27357006073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1931581497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3597326278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9398679733276</t>
+    <t xml:space="preserve">13.2856245040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1414661407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2735738754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1931562423706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.35973072052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9398651123047</t>
   </si>
   <si>
     <t xml:space="preserve">14.6871318817139</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3884534835815</t>
+    <t xml:space="preserve">14.3884506225586</t>
   </si>
   <si>
     <t xml:space="preserve">14.4746112823486</t>
   </si>
   <si>
-    <t xml:space="preserve">14.784779548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9341220855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2213172912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5831804275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4970235824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4510736465454</t>
+    <t xml:space="preserve">14.7847785949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9341192245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2213153839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5831813812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4970254898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4510698318481</t>
   </si>
   <si>
     <t xml:space="preserve">15.3361930847168</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8364744186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9915609359741</t>
+    <t xml:space="preserve">14.8364725112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9915580749512</t>
   </si>
   <si>
     <t xml:space="preserve">15.2959852218628</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1638784408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0375099182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.089207649231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0719766616821</t>
+    <t xml:space="preserve">15.1638774871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0375108718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0892057418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0719728469849</t>
   </si>
   <si>
     <t xml:space="preserve">14.8307304382324</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6469249725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5320491790771</t>
+    <t xml:space="preserve">14.6469259262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5320472717285</t>
   </si>
   <si>
     <t xml:space="preserve">14.2333641052246</t>
@@ -770,31 +770,31 @@
     <t xml:space="preserve">14.5263051986694</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4171695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3941955566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0489978790283</t>
+    <t xml:space="preserve">14.4171705245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3941946029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0489988327026</t>
   </si>
   <si>
     <t xml:space="preserve">14.7618026733398</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6584148406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8766813278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3936319351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8531455993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8416557312012</t>
+    <t xml:space="preserve">14.6584157943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8766832351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3936309814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8531446456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8416585922241</t>
   </si>
   <si>
     <t xml:space="preserve">16.0369491577148</t>
@@ -812,16 +812,16 @@
     <t xml:space="preserve">16.6343116760254</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6113357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0828971862793</t>
+    <t xml:space="preserve">16.6113395690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0829010009766</t>
   </si>
   <si>
     <t xml:space="preserve">16.8870449066162</t>
   </si>
   <si>
-    <t xml:space="preserve">16.944486618042</t>
+    <t xml:space="preserve">16.9444847106934</t>
   </si>
   <si>
     <t xml:space="preserve">17.3465557098389</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">17.4844093322754</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5935401916504</t>
+    <t xml:space="preserve">17.593542098999</t>
   </si>
   <si>
     <t xml:space="preserve">17.059362411499</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">17.9152011871338</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7365779876709</t>
+    <t xml:space="preserve">18.7365798950195</t>
   </si>
   <si>
     <t xml:space="preserve">19.5522117614746</t>
@@ -854,193 +854,193 @@
     <t xml:space="preserve">19.8164291381836</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9944915771484</t>
+    <t xml:space="preserve">19.9944896697998</t>
   </si>
   <si>
     <t xml:space="preserve">20.942232131958</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5229244232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8503303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7354507446289</t>
+    <t xml:space="preserve">20.5229301452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8503284454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7354526519775</t>
   </si>
   <si>
     <t xml:space="preserve">20.6780128479004</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6492938995361</t>
+    <t xml:space="preserve">20.6492977142334</t>
   </si>
   <si>
     <t xml:space="preserve">20.3218936920166</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5631351470947</t>
+    <t xml:space="preserve">20.5631370544434</t>
   </si>
   <si>
     <t xml:space="preserve">20.6378059387207</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8388442993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8216075897217</t>
+    <t xml:space="preserve">20.8388404846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8216094970703</t>
   </si>
   <si>
     <t xml:space="preserve">20.6090869903564</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1088047027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4132289886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2409172058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1777305603027</t>
+    <t xml:space="preserve">21.1088066101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4132308959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2409133911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1777324676514</t>
   </si>
   <si>
     <t xml:space="preserve">21.022647857666</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9594669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3098430633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5855503082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3155860900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2690715789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1369647979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9818782806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2288627624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.745813369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9335079193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5815887451172</t>
+    <t xml:space="preserve">20.9594688415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3098411560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5855522155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3155899047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2690677642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1369609832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9818820953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2288665771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7458152770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9335060119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5815849304199</t>
   </si>
   <si>
     <t xml:space="preserve">22.3938961029053</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4671688079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4583282470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1035213470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8161201477051</t>
+    <t xml:space="preserve">21.467170715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4583301544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1035194396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8161182403564</t>
   </si>
   <si>
     <t xml:space="preserve">20.6342887878418</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6929454803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5873622894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2969932556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5872840881348</t>
+    <t xml:space="preserve">20.6929416656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.587366104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2969913482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5872859954834</t>
   </si>
   <si>
     <t xml:space="preserve">19.5433349609375</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9656410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4817905426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4700584411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5287170410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4114055633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2706413269043</t>
+    <t xml:space="preserve">19.9656391143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4817886352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.470064163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.528715133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4114074707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2706394195557</t>
   </si>
   <si>
     <t xml:space="preserve">20.3058300018311</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7955474853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6078548431396</t>
+    <t xml:space="preserve">19.7955436706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.607852935791</t>
   </si>
   <si>
     <t xml:space="preserve">19.8835277557373</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2471752166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0594844818115</t>
+    <t xml:space="preserve">20.2471771240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0594863891602</t>
   </si>
   <si>
     <t xml:space="preserve">20.176794052124</t>
   </si>
   <si>
-    <t xml:space="preserve">20.751594543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6988105773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3527526855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5521774291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5052547454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7046718597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4407329559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1474647521973</t>
+    <t xml:space="preserve">20.7515983581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6988124847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3527545928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5521755218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5052509307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7046737670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.440731048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1474628448486</t>
   </si>
   <si>
     <t xml:space="preserve">20.0477542877197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0008335113525</t>
+    <t xml:space="preserve">20.0008296966553</t>
   </si>
   <si>
     <t xml:space="preserve">20.4876556396484</t>
@@ -1049,34 +1049,34 @@
     <t xml:space="preserve">20.6694831848145</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6460208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8630409240723</t>
+    <t xml:space="preserve">20.6460227966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8630390167236</t>
   </si>
   <si>
     <t xml:space="preserve">20.933422088623</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0096740722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9275608062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1152458190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2560195922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2912082672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5551490783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7487087249756</t>
+    <t xml:space="preserve">21.009672164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9275550842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1152496337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2560214996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2912063598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5551509857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7487049102783</t>
   </si>
   <si>
     <t xml:space="preserve">21.6314010620117</t>
@@ -1085,16 +1085,16 @@
     <t xml:space="preserve">21.6079387664795</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6431331634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8366851806641</t>
+    <t xml:space="preserve">21.6431274414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8366870880127</t>
   </si>
   <si>
     <t xml:space="preserve">22.0830345153809</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7604370117188</t>
+    <t xml:space="preserve">21.7604351043701</t>
   </si>
   <si>
     <t xml:space="preserve">22.4642791748047</t>
@@ -1103,19 +1103,19 @@
     <t xml:space="preserve">22.9041805267334</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6402359008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9686965942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7575454711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2854270935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4907169342041</t>
+    <t xml:space="preserve">22.6402397155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9687004089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7575435638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2854290008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4907150268555</t>
   </si>
   <si>
     <t xml:space="preserve">23.7722473144531</t>
@@ -1127,40 +1127,40 @@
     <t xml:space="preserve">24.2708034515381</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8719635009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1007118225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.047924041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5435028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5669631958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1593608856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3529186248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3059959411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8543643951416</t>
+    <t xml:space="preserve">23.8719615936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1007080078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0479259490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5434989929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5669612884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1593627929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3529224395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3059978485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8543663024902</t>
   </si>
   <si>
     <t xml:space="preserve">24.036190032959</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8367671966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8191699981689</t>
+    <t xml:space="preserve">23.8367691040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8191738128662</t>
   </si>
   <si>
     <t xml:space="preserve">23.9716720581055</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">23.7898464202881</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6373481750488</t>
+    <t xml:space="preserve">23.6373519897461</t>
   </si>
   <si>
     <t xml:space="preserve">23.1153316497803</t>
@@ -1178,70 +1178,70 @@
     <t xml:space="preserve">23.7077312469482</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9012870788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1652297973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5347480773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3411903381348</t>
+    <t xml:space="preserve">23.9012889862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1652317047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5347461700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3411884307861</t>
   </si>
   <si>
     <t xml:space="preserve">24.0831127166748</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7400321960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7107067108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.493688583374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6989784240723</t>
+    <t xml:space="preserve">24.7400360107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7107048034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4936847686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.698974609375</t>
   </si>
   <si>
     <t xml:space="preserve">25.0684986114502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7078151702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.713680267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.15944480896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4937705993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3823318481445</t>
+    <t xml:space="preserve">25.7078170776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7136783599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1594467163086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4937725067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3823280334473</t>
   </si>
   <si>
     <t xml:space="preserve">26.5876197814941</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1301212310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5993461608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8222312927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1330947875977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7548179626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0656814575195</t>
+    <t xml:space="preserve">26.1301193237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5993518829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8222274780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1330966949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7548198699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0656833648682</t>
   </si>
   <si>
     <t xml:space="preserve">28.2064514160156</t>
@@ -1253,88 +1253,88 @@
     <t xml:space="preserve">27.7489547729492</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4997177124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8281764984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8926982879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6580867767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0539588928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.927806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5289649963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2152137756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6404037475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5378074645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.631649017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.666841506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8428058624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3237609863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5671291351318</t>
+    <t xml:space="preserve">28.499719619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8281841278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8927001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6580848693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.053955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9278049468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5289611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2152080535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6404075622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5378017425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6316509246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6668395996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8428020477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3237571716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5671310424805</t>
   </si>
   <si>
     <t xml:space="preserve">27.6023235321045</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4556884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5026073455811</t>
+    <t xml:space="preserve">27.4556903839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5026054382324</t>
   </si>
   <si>
     <t xml:space="preserve">27.0803050994873</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8163642883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3060817718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9365634918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5992603302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8954219818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9511051177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8279266357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6021556854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7164897918701</t>
+    <t xml:space="preserve">26.8163661956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3060779571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9365653991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5992660522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8954238891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9511032104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8279285430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6021575927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7164878845215</t>
   </si>
   <si>
     <t xml:space="preserve">22.7282180786133</t>
@@ -1346,109 +1346,109 @@
     <t xml:space="preserve">21.9833202362061</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6754322052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4056243896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.610912322998</t>
+    <t xml:space="preserve">22.6754302978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4056262969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6109142303467</t>
   </si>
   <si>
     <t xml:space="preserve">22.7927398681641</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2355289459229</t>
+    <t xml:space="preserve">22.2355327606201</t>
   </si>
   <si>
     <t xml:space="preserve">21.5492820739746</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5199584960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7311115264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8249588012695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4495754241943</t>
+    <t xml:space="preserve">21.5199565887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7311096191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8249568939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4495716094971</t>
   </si>
   <si>
     <t xml:space="preserve">20.9040946960449</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4026527404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.877742767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4701461791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1914958953857</t>
+    <t xml:space="preserve">21.4026546478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8777446746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4701442718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1914978027344</t>
   </si>
   <si>
     <t xml:space="preserve">21.1093845367432</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0565967559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7135162353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7047557830811</t>
+    <t xml:space="preserve">21.0565986633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7135124206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7047576904297</t>
   </si>
   <si>
     <t xml:space="preserve">23.9130191802979</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0449466705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3440780639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7546577453613</t>
+    <t xml:space="preserve">23.0449504852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3440799713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7546558380127</t>
   </si>
   <si>
     <t xml:space="preserve">23.7663860321045</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4496555328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5200386047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3469715118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0273532867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1563854217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8631210327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0508117675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9569683074951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7810039520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5229320526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4994697570801</t>
+    <t xml:space="preserve">23.4496536254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5200366973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3469696044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0273513793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1563892364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8631191253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0508155822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9569702148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7810096740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5229301452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4994678497314</t>
   </si>
   <si>
     <t xml:space="preserve">22.2765884399414</t>
@@ -1460,28 +1460,28 @@
     <t xml:space="preserve">22.4525451660156</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0771656036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2208251953125</t>
+    <t xml:space="preserve">22.0771675109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2208271026611</t>
   </si>
   <si>
     <t xml:space="preserve">20.7398681640625</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2677459716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6489124298096</t>
+    <t xml:space="preserve">21.267749786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6489143371582</t>
   </si>
   <si>
     <t xml:space="preserve">19.4260272979736</t>
   </si>
   <si>
-    <t xml:space="preserve">20.775053024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1621723175049</t>
+    <t xml:space="preserve">20.7750568389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1621685028076</t>
   </si>
   <si>
     <t xml:space="preserve">20.9158267974854</t>
@@ -1490,22 +1490,22 @@
     <t xml:space="preserve">21.3733234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3615913391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3264007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2794799804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3967876434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0448665618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7985172271729</t>
+    <t xml:space="preserve">21.36159324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3264026641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2794780731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.396785736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.044864654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7985191345215</t>
   </si>
   <si>
     <t xml:space="preserve">20.6812114715576</t>
@@ -1514,13 +1514,13 @@
     <t xml:space="preserve">20.0125637054443</t>
   </si>
   <si>
-    <t xml:space="preserve">19.332181930542</t>
+    <t xml:space="preserve">19.3321800231934</t>
   </si>
   <si>
     <t xml:space="preserve">19.015453338623</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3556442260742</t>
+    <t xml:space="preserve">19.3556461334229</t>
   </si>
   <si>
     <t xml:space="preserve">19.0975704193115</t>
@@ -1532,10 +1532,10 @@
     <t xml:space="preserve">20.071216583252</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9891033172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8394908905029</t>
+    <t xml:space="preserve">19.9891052246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8394947052002</t>
   </si>
   <si>
     <t xml:space="preserve">18.3468036651611</t>
@@ -1544,31 +1544,31 @@
     <t xml:space="preserve">18.5227661132812</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4377574920654</t>
+    <t xml:space="preserve">19.4377613067627</t>
   </si>
   <si>
     <t xml:space="preserve">19.2617988586426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9919948577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3233432769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3614292144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6987228393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9596939086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7221851348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1210308074951</t>
+    <t xml:space="preserve">18.9919967651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3233451843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3614273071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6987266540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9596920013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.722188949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1210269927979</t>
   </si>
   <si>
     <t xml:space="preserve">19.273530960083</t>
@@ -1580,22 +1580,22 @@
     <t xml:space="preserve">20.1533317565918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7310237884521</t>
+    <t xml:space="preserve">19.7310256958008</t>
   </si>
   <si>
     <t xml:space="preserve">19.5785293579102</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8131427764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6958351135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3461208343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3582210540771</t>
+    <t xml:space="preserve">19.813138961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.695837020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3461227416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3582191467285</t>
   </si>
   <si>
     <t xml:space="preserve">19.1404399871826</t>
@@ -1604,31 +1604,31 @@
     <t xml:space="preserve">19.0920448303223</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1646366119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7816829681396</t>
+    <t xml:space="preserve">19.1646385192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.781681060791</t>
   </si>
   <si>
     <t xml:space="preserve">19.9752655029297</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2656383514404</t>
+    <t xml:space="preserve">20.2656402587891</t>
   </si>
   <si>
     <t xml:space="preserve">20.435022354126</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6649017333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3745269775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.02366065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5397052764893</t>
+    <t xml:space="preserve">20.6648998260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3745250701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0236587524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5397033691406</t>
   </si>
   <si>
     <t xml:space="preserve">19.4429130554199</t>
@@ -1637,7 +1637,7 @@
     <t xml:space="preserve">19.6485939025879</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7211894989014</t>
+    <t xml:space="preserve">19.7211856842041</t>
   </si>
   <si>
     <t xml:space="preserve">18.9589595794678</t>
@@ -1646,19 +1646,19 @@
     <t xml:space="preserve">18.3298149108887</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4103012084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0836334228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2288150787354</t>
+    <t xml:space="preserve">17.4103031158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0836296081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.228816986084</t>
   </si>
   <si>
     <t xml:space="preserve">16.8779468536377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5149803161621</t>
+    <t xml:space="preserve">16.5149841308594</t>
   </si>
   <si>
     <t xml:space="preserve">15.6075668334961</t>
@@ -1667,40 +1667,40 @@
     <t xml:space="preserve">14.1677989959717</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8853168487549</t>
+    <t xml:space="preserve">12.8853158950806</t>
   </si>
   <si>
     <t xml:space="preserve">14.1194019317627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2282915115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.426082611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4865789413452</t>
+    <t xml:space="preserve">14.2282943725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4260835647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4865770339966</t>
   </si>
   <si>
     <t xml:space="preserve">15.0147190093994</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1478071212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8332366943359</t>
+    <t xml:space="preserve">15.1478099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8332376480103</t>
   </si>
   <si>
     <t xml:space="preserve">14.7001476287842</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2929973602295</t>
+    <t xml:space="preserve">15.2929944992065</t>
   </si>
   <si>
     <t xml:space="preserve">16.1520156860352</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5996742248535</t>
+    <t xml:space="preserve">16.5996723175049</t>
   </si>
   <si>
     <t xml:space="preserve">16.5754776000977</t>
@@ -1712,43 +1712,43 @@
     <t xml:space="preserve">16.7932567596436</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2409172058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7327613830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9021492004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6238708496094</t>
+    <t xml:space="preserve">17.2409152984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.732759475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9021472930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.623872756958</t>
   </si>
   <si>
     <t xml:space="preserve">15.970531463623</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4623785018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.571268081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5954666137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6438617706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6196632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7890491485596</t>
+    <t xml:space="preserve">15.462381362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5712690353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5954685211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6438627243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6196641921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7890510559082</t>
   </si>
   <si>
     <t xml:space="preserve">16.0431251525879</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4060916900635</t>
+    <t xml:space="preserve">16.4060935974121</t>
   </si>
   <si>
     <t xml:space="preserve">16.5875759124756</t>
@@ -1757,85 +1757,85 @@
     <t xml:space="preserve">16.2730045318604</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9100370407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9947299957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.825345993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.672269821167</t>
+    <t xml:space="preserve">15.9100379943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9947319030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8253450393677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6722660064697</t>
   </si>
   <si>
     <t xml:space="preserve">16.9384422302246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2851028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0552234649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2972030639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3577003479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2125110626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3655881881714</t>
+    <t xml:space="preserve">16.2851009368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0552253723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2972011566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3576965332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2125091552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3655862808228</t>
   </si>
   <si>
     <t xml:space="preserve">15.5470724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6396551132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3692722320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6838436126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6475458145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6354475021362</t>
+    <t xml:space="preserve">14.6396560668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.369270324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6838417053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6475448608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6354484558105</t>
   </si>
   <si>
     <t xml:space="preserve">13.2845792770386</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0426015853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5102500915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3771638870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4860525131226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4497566223145</t>
+    <t xml:space="preserve">13.0426025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5102510452271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3771619796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4860534667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4497556686401</t>
   </si>
   <si>
     <t xml:space="preserve">13.2603807449341</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7885246276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9700078964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9216136932373</t>
+    <t xml:space="preserve">12.7885255813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9700088500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9216146469116</t>
   </si>
   <si>
     <t xml:space="preserve">13.0909967422485</t>
@@ -1847,70 +1847,70 @@
     <t xml:space="preserve">12.2924699783325</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2561731338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7643280029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1998891830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6596441268921</t>
+    <t xml:space="preserve">12.2561740875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.764328956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1998872756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6596431732178</t>
   </si>
   <si>
     <t xml:space="preserve">13.526556968689</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3571729660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8895244598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5749530792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6717443466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3208751678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3450727462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5023612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.058910369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4218740463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3976774215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2645883560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4339723587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3934698104858</t>
+    <t xml:space="preserve">13.3571720123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8895215988159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5749540328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6717414855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3208742141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3450736999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5023593902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0589094161987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3976764678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2645902633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4339752197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3934679031372</t>
   </si>
   <si>
     <t xml:space="preserve">11.7359209060669</t>
   </si>
   <si>
-    <t xml:space="preserve">10.864800453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3003625869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6088848114014</t>
+    <t xml:space="preserve">10.8648014068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3003616333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6088838577271</t>
   </si>
   <si>
     <t xml:space="preserve">11.9778995513916</t>
@@ -1922,25 +1922,25 @@
     <t xml:space="preserve">10.3143014907837</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5865268707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2356595993042</t>
+    <t xml:space="preserve">10.5865278244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2356615066528</t>
   </si>
   <si>
     <t xml:space="preserve">9.86664390563965</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3263998031616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3022031784058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4957847595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92108821868896</t>
+    <t xml:space="preserve">10.3264007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3022041320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4957857131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92108917236328</t>
   </si>
   <si>
     <t xml:space="preserve">9.89689064025879</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">8.73539733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37847995758057</t>
+    <t xml:space="preserve">8.37848091125488</t>
   </si>
   <si>
     <t xml:space="preserve">8.22119426727295</t>
@@ -1964,16 +1964,16 @@
     <t xml:space="preserve">8.49946880340576</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9713249206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06206607818604</t>
+    <t xml:space="preserve">8.97132587432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06206798553467</t>
   </si>
   <si>
     <t xml:space="preserve">9.40083599090576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67911052703857</t>
+    <t xml:space="preserve">9.67910957336426</t>
   </si>
   <si>
     <t xml:space="preserve">10.217511177063</t>
@@ -1985,25 +1985,25 @@
     <t xml:space="preserve">9.12256145477295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21935272216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82008934020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12861251831055</t>
+    <t xml:space="preserve">9.21935367584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82008838653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12861156463623</t>
   </si>
   <si>
     <t xml:space="preserve">9.24960136413574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36453819274902</t>
+    <t xml:space="preserve">9.36453914642334</t>
   </si>
   <si>
     <t xml:space="preserve">9.58836841583252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48552989959717</t>
+    <t xml:space="preserve">9.48552799224854</t>
   </si>
   <si>
     <t xml:space="preserve">9.45528125762939</t>
@@ -2012,28 +2012,28 @@
     <t xml:space="preserve">9.70935726165771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61256790161133</t>
+    <t xml:space="preserve">9.61256694793701</t>
   </si>
   <si>
     <t xml:space="preserve">9.57021999359131</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8406028747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1370286941528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9071483612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5967836380005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3064126968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0099897384644</t>
+    <t xml:space="preserve">10.8406038284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1370267868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9071474075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5967855453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3064117431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.00998878479</t>
   </si>
   <si>
     <t xml:space="preserve">10.9676418304443</t>
@@ -2045,7 +2045,7 @@
     <t xml:space="preserve">10.8285045623779</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3385000228882</t>
+    <t xml:space="preserve">10.3385009765625</t>
   </si>
   <si>
     <t xml:space="preserve">10.7377634048462</t>
@@ -2060,37 +2060,37 @@
     <t xml:space="preserve">11.1007299423218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0039386749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8587522506714</t>
+    <t xml:space="preserve">11.0039396286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8587532043457</t>
   </si>
   <si>
     <t xml:space="preserve">10.3747959136963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81219863891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6912088394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37058925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17095565795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03786945343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34034252166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34638977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94528388977051</t>
+    <t xml:space="preserve">9.8121976852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69120979309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3705883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17095756530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03786849975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34034156799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34639167785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94528579711914</t>
   </si>
   <si>
     <t xml:space="preserve">10.4050436019897</t>
@@ -2099,7 +2099,7 @@
     <t xml:space="preserve">10.8043069839478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5562810897827</t>
+    <t xml:space="preserve">10.556282043457</t>
   </si>
   <si>
     <t xml:space="preserve">10.62282371521</t>
@@ -2108,16 +2108,16 @@
     <t xml:space="preserve">10.5804777145386</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5502309799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0239286422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62466526031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1025724411011</t>
+    <t xml:space="preserve">10.5502300262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0239295959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62466621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1025714874268</t>
   </si>
   <si>
     <t xml:space="preserve">10.2296094894409</t>
@@ -2126,31 +2126,31 @@
     <t xml:space="preserve">10.465537071228</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3687477111816</t>
+    <t xml:space="preserve">10.3687467575073</t>
   </si>
   <si>
     <t xml:space="preserve">9.98763275146484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96948528289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2780055999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4352922439575</t>
+    <t xml:space="preserve">9.969482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2780046463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4352912902832</t>
   </si>
   <si>
     <t xml:space="preserve">10.5320825576782</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1509666442871</t>
+    <t xml:space="preserve">10.1509675979614</t>
   </si>
   <si>
     <t xml:space="preserve">10.0299777984619</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1267681121826</t>
+    <t xml:space="preserve">10.1267690658569</t>
   </si>
   <si>
     <t xml:space="preserve">10.3445501327515</t>
@@ -2162,7 +2162,7 @@
     <t xml:space="preserve">9.64886283874512</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0946807861328</t>
+    <t xml:space="preserve">11.0946798324585</t>
   </si>
   <si>
     <t xml:space="preserve">12.6433382034302</t>
@@ -2171,16 +2171,16 @@
     <t xml:space="preserve">12.0323448181152</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3729553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.876898765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7014665603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6107263565063</t>
+    <t xml:space="preserve">11.3729543685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8769006729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7014675140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.610725402832</t>
   </si>
   <si>
     <t xml:space="preserve">10.5683784484863</t>
@@ -2189,19 +2189,19 @@
     <t xml:space="preserve">10.1086206436157</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3505992889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9373960494995</t>
+    <t xml:space="preserve">10.3505983352661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9373950958252</t>
   </si>
   <si>
     <t xml:space="preserve">11.0341863632202</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1128282546997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4818449020386</t>
+    <t xml:space="preserve">11.112829208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4818439483643</t>
   </si>
   <si>
     <t xml:space="preserve">10.9736909866333</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">9.54602241516113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35848999023438</t>
+    <t xml:space="preserve">9.35849094390869</t>
   </si>
   <si>
     <t xml:space="preserve">9.22540187835693</t>
@@ -2222,22 +2222,22 @@
     <t xml:space="preserve">9.08626556396484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1346607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92897987365723</t>
+    <t xml:space="preserve">9.13465976715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92898082733154</t>
   </si>
   <si>
     <t xml:space="preserve">8.97737407684326</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95317840576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84428691864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89873123168945</t>
+    <t xml:space="preserve">8.9531774520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84428596496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89873313903809</t>
   </si>
   <si>
     <t xml:space="preserve">9.0741662979126</t>
@@ -2246,43 +2246,43 @@
     <t xml:space="preserve">9.00157260894775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24355125427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49762630462646</t>
+    <t xml:space="preserve">9.24355030059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49762725830078</t>
   </si>
   <si>
     <t xml:space="preserve">9.47947978973389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46133136749268</t>
+    <t xml:space="preserve">9.46133041381836</t>
   </si>
   <si>
     <t xml:space="preserve">9.38873767852783</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6367654800415</t>
+    <t xml:space="preserve">9.63676452636719</t>
   </si>
   <si>
     <t xml:space="preserve">9.68516063690186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71540832519531</t>
+    <t xml:space="preserve">9.71540641784668</t>
   </si>
   <si>
     <t xml:space="preserve">9.83034706115723</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2636575698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94029140472412</t>
+    <t xml:space="preserve">10.2636585235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9402904510498</t>
   </si>
   <si>
     <t xml:space="preserve">9.65572929382324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7268705368042</t>
+    <t xml:space="preserve">9.72686958312988</t>
   </si>
   <si>
     <t xml:space="preserve">9.21595001220703</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">8.73736667633057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52394485473633</t>
+    <t xml:space="preserve">8.52394580841064</t>
   </si>
   <si>
     <t xml:space="preserve">8.2781867980957</t>
@@ -2306,67 +2306,67 @@
     <t xml:space="preserve">8.32345771789551</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37519645690918</t>
+    <t xml:space="preserve">8.37519836425781</t>
   </si>
   <si>
     <t xml:space="preserve">8.31699085235596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0712308883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87721252441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90954732894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82547330856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56678009033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72199487686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59264993667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54091024398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50210666656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3727593421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31455373764038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66378974914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32748889923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24341440200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2886848449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52150726318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26281499862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29515171051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25634813308716</t>
+    <t xml:space="preserve">8.07123184204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87721109390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90954828262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82547378540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56677961349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72199583053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59264945983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54090929031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50210618972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37275886535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31455326080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66379022598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32748794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24341344833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28868532180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52150869369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26281452178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2951512336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25634860992432</t>
   </si>
   <si>
     <t xml:space="preserve">7.41803169250488</t>
@@ -2384,67 +2384,67 @@
     <t xml:space="preserve">7.70259380340576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55384492874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76726818084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79960489273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67672443389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99362421035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18117618560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70503044128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65329170227051</t>
+    <t xml:space="preserve">7.55384540557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76726675033569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7996039390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67672491073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99362373352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18117713928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70502948760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65329265594482</t>
   </si>
   <si>
     <t xml:space="preserve">8.69856262207031</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79557418823242</t>
+    <t xml:space="preserve">8.79557228088379</t>
   </si>
   <si>
     <t xml:space="preserve">8.58215141296387</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57568550109863</t>
+    <t xml:space="preserve">8.57568359375</t>
   </si>
   <si>
     <t xml:space="preserve">8.49160861968994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55628108978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95725631713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94432163238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93785381317139</t>
+    <t xml:space="preserve">8.55628204345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95725727081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94432067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9378547668457</t>
   </si>
   <si>
     <t xml:space="preserve">8.7503023147583</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62742328643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82790946960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83437824249268</t>
+    <t xml:space="preserve">8.62742233276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82791042327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83437633514404</t>
   </si>
   <si>
     <t xml:space="preserve">8.71149730682373</t>
@@ -2453,19 +2453,19 @@
     <t xml:space="preserve">8.6080207824707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66622734069824</t>
+    <t xml:space="preserve">8.66622638702393</t>
   </si>
   <si>
     <t xml:space="preserve">8.38813209533691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29758739471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54334735870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02839756011963</t>
+    <t xml:space="preserve">8.29758930206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54334831237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02839660644531</t>
   </si>
   <si>
     <t xml:space="preserve">8.91845321655273</t>
@@ -2474,25 +2474,25 @@
     <t xml:space="preserve">8.88611602783203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12540721893311</t>
+    <t xml:space="preserve">9.12540817260742</t>
   </si>
   <si>
     <t xml:space="preserve">8.48514175415039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11003494262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87074518203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26525115966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33639240264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4334020614624</t>
+    <t xml:space="preserve">8.11003589630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8707447052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2652530670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33639335632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43340396881104</t>
   </si>
   <si>
     <t xml:space="preserve">8.36872863769531</t>
@@ -2501,31 +2501,31 @@
     <t xml:space="preserve">8.28465366363525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23938274383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5627498626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7697057723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02192974090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13187503814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2224178314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45524120330811</t>
+    <t xml:space="preserve">8.23938179016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56274890899658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76970481872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02192878723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13187408447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22241687774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45524024963379</t>
   </si>
   <si>
     <t xml:space="preserve">9.442307472229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50698089599609</t>
+    <t xml:space="preserve">9.50697994232178</t>
   </si>
   <si>
     <t xml:space="preserve">9.55871963500977</t>
@@ -2534,19 +2534,19 @@
     <t xml:space="preserve">9.58458805084229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69453239440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91442203521729</t>
+    <t xml:space="preserve">9.6945333480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9144229888916</t>
   </si>
   <si>
     <t xml:space="preserve">9.92088985443115</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73333644866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89502048492432</t>
+    <t xml:space="preserve">9.73333740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89502143859863</t>
   </si>
   <si>
     <t xml:space="preserve">9.90795516967773</t>
@@ -2558,37 +2558,37 @@
     <t xml:space="preserve">9.57812118530273</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66866302490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90148639678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7074670791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5199146270752</t>
+    <t xml:space="preserve">9.66866397857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90148830413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70746803283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51991558074951</t>
   </si>
   <si>
     <t xml:space="preserve">9.30649375915527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33236122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43583869934082</t>
+    <t xml:space="preserve">9.33236312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43583965301514</t>
   </si>
   <si>
     <t xml:space="preserve">9.09953689575195</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37116527557373</t>
+    <t xml:space="preserve">9.37116622924805</t>
   </si>
   <si>
     <t xml:space="preserve">9.52638149261475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79154396057129</t>
+    <t xml:space="preserve">9.79154300689697</t>
   </si>
   <si>
     <t xml:space="preserve">9.7398042678833</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">9.76567268371582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87561798095703</t>
+    <t xml:space="preserve">9.87561893463135</t>
   </si>
   <si>
     <t xml:space="preserve">9.95322608947754</t>
@@ -2609,46 +2609,46 @@
     <t xml:space="preserve">9.94675922393799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77213954925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88208675384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98556327819824</t>
+    <t xml:space="preserve">9.77214050292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88208484649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98556232452393</t>
   </si>
   <si>
     <t xml:space="preserve">10.224853515625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44877338409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83034610748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86914920806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1925172805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2377891540527</t>
+    <t xml:space="preserve">9.44877243041992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83034515380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86915016174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1925163269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2377872467041</t>
   </si>
   <si>
     <t xml:space="preserve">9.62339210510254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41643619537354</t>
+    <t xml:space="preserve">9.41643714904785</t>
   </si>
   <si>
     <t xml:space="preserve">9.34529685974121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24181842803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1900806427002</t>
+    <t xml:space="preserve">9.24181938171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19007968902588</t>
   </si>
   <si>
     <t xml:space="preserve">9.06073379516602</t>
@@ -2657,13 +2657,13 @@
     <t xml:space="preserve">9.08013534545898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97665786743164</t>
+    <t xml:space="preserve">8.97665882110596</t>
   </si>
   <si>
     <t xml:space="preserve">9.04133129119873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9249210357666</t>
+    <t xml:space="preserve">8.92491912841797</t>
   </si>
   <si>
     <t xml:space="preserve">8.76323699951172</t>
@@ -2672,40 +2672,40 @@
     <t xml:space="preserve">8.84731197357178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78263759613037</t>
+    <t xml:space="preserve">8.782639503479</t>
   </si>
   <si>
     <t xml:space="preserve">8.61448764801025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56921672821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67916202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86671447753906</t>
+    <t xml:space="preserve">8.56921577453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67916011810303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86671352386475</t>
   </si>
   <si>
     <t xml:space="preserve">8.8731803894043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81497573852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86024761199951</t>
+    <t xml:space="preserve">8.81497478485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8602466583252</t>
   </si>
   <si>
     <t xml:space="preserve">9.24828720092773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05426692962646</t>
+    <t xml:space="preserve">9.05426597595215</t>
   </si>
   <si>
     <t xml:space="preserve">9.14480972290039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2353515625</t>
+    <t xml:space="preserve">9.23535251617432</t>
   </si>
   <si>
     <t xml:space="preserve">9.15774345397949</t>
@@ -2714,112 +2714,112 @@
     <t xml:space="preserve">9.13834190368652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2676887512207</t>
+    <t xml:space="preserve">9.26768779754639</t>
   </si>
   <si>
     <t xml:space="preserve">9.0930700302124</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93138885498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20301532745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59105491638184</t>
+    <t xml:space="preserve">8.93138790130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20301628112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59105587005615</t>
   </si>
   <si>
     <t xml:space="preserve">9.57165336608887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51344585418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53284931182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32589435577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30002689361572</t>
+    <t xml:space="preserve">9.51344776153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5328483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32589530944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30002403259277</t>
   </si>
   <si>
     <t xml:space="preserve">9.74627208709717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47464370727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27415657043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62985897064209</t>
+    <t xml:space="preserve">9.47464275360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27415561676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62985992431641</t>
   </si>
   <si>
     <t xml:space="preserve">9.70100021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80447578430176</t>
+    <t xml:space="preserve">9.80447769165039</t>
   </si>
   <si>
     <t xml:space="preserve">10.1343116760254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1278448104858</t>
+    <t xml:space="preserve">10.1278438568115</t>
   </si>
   <si>
     <t xml:space="preserve">10.069637298584</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1407794952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0049638748169</t>
+    <t xml:space="preserve">10.1407785415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0049657821655</t>
   </si>
   <si>
     <t xml:space="preserve">10.1472454071045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35176372528076</t>
+    <t xml:space="preserve">9.35176563262939</t>
   </si>
   <si>
     <t xml:space="preserve">9.5522518157959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89258193969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4075345993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90308284759521</t>
+    <t xml:space="preserve">8.89258289337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40753364562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90308094024658</t>
   </si>
   <si>
     <t xml:space="preserve">6.88124322891235</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61608219146729</t>
+    <t xml:space="preserve">6.61608171463013</t>
   </si>
   <si>
     <t xml:space="preserve">6.5966796875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67185258865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93701171875</t>
+    <t xml:space="preserve">5.67185163497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93701267242432</t>
   </si>
   <si>
     <t xml:space="preserve">5.61364555358887</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44549465179443</t>
+    <t xml:space="preserve">5.44549369812012</t>
   </si>
   <si>
     <t xml:space="preserve">5.45842933654785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43902683258057</t>
+    <t xml:space="preserve">5.43902635574341</t>
   </si>
   <si>
     <t xml:space="preserve">5.75592613220215</t>
@@ -2828,10 +2828,10 @@
     <t xml:space="preserve">5.57160758972168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84000110626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86910533905029</t>
+    <t xml:space="preserve">5.84000158309937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86910486221313</t>
   </si>
   <si>
     <t xml:space="preserve">5.98228311538696</t>
@@ -2849,37 +2849,37 @@
     <t xml:space="preserve">5.75916051864624</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70095348358154</t>
+    <t xml:space="preserve">5.70095443725586</t>
   </si>
   <si>
     <t xml:space="preserve">5.78179550170898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83676862716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96934795379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94671297073364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9758152961731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83353471755981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71388864517212</t>
+    <t xml:space="preserve">5.83676815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96934747695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94671249389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97581577301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83353424072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71388912200928</t>
   </si>
   <si>
     <t xml:space="preserve">5.76886177062988</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77532911300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49723386764526</t>
+    <t xml:space="preserve">5.77532863616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49723339080811</t>
   </si>
   <si>
     <t xml:space="preserve">5.38405418395996</t>
@@ -2888,34 +2888,34 @@
     <t xml:space="preserve">5.51663541793823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81413221359253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93054485321045</t>
+    <t xml:space="preserve">5.81413269042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93054437637329</t>
   </si>
   <si>
     <t xml:space="preserve">5.77209520339966</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5619068145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6201114654541</t>
+    <t xml:space="preserve">5.56190633773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62011194229126</t>
   </si>
   <si>
     <t xml:space="preserve">5.58454275131226</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47136449813843</t>
+    <t xml:space="preserve">5.47136497497559</t>
   </si>
   <si>
     <t xml:space="preserve">5.55867290496826</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48106527328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40669059753418</t>
+    <t xml:space="preserve">5.48106575012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40669012069702</t>
   </si>
   <si>
     <t xml:space="preserve">5.32584857940674</t>
@@ -2924,19 +2924,19 @@
     <t xml:space="preserve">5.22560548782349</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19326877593994</t>
+    <t xml:space="preserve">5.19326829910278</t>
   </si>
   <si>
     <t xml:space="preserve">5.17386627197266</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94751024246216</t>
+    <t xml:space="preserve">4.94751071929932</t>
   </si>
   <si>
     <t xml:space="preserve">4.81169605255127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70821809768677</t>
+    <t xml:space="preserve">4.70821857452393</t>
   </si>
   <si>
     <t xml:space="preserve">4.7211537361145</t>
@@ -2948,34 +2948,34 @@
     <t xml:space="preserve">5.18033409118652</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33555030822754</t>
+    <t xml:space="preserve">5.33554983139038</t>
   </si>
   <si>
     <t xml:space="preserve">5.42932653427124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36465263366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40022373199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7268238067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94347953796387</t>
+    <t xml:space="preserve">5.36465311050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40022325515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72682285308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94347906112671</t>
   </si>
   <si>
     <t xml:space="preserve">6.2539119720459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7001576423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28624868392944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09222841262817</t>
+    <t xml:space="preserve">6.70015716552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28624773025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09222793579102</t>
   </si>
   <si>
     <t xml:space="preserve">5.67508459091187</t>
@@ -2996,52 +2996,52 @@
     <t xml:space="preserve">5.73329019546509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58777570724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53603792190552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3969898223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3161473274231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37435436248779</t>
+    <t xml:space="preserve">5.58777666091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53603839874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39699029922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31614780426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37435388565063</t>
   </si>
   <si>
     <t xml:space="preserve">5.49399900436401</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52957057952881</t>
+    <t xml:space="preserve">5.52957010269165</t>
   </si>
   <si>
     <t xml:space="preserve">5.51340103149414</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64598178863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75269317626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86587142944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80119800567627</t>
+    <t xml:space="preserve">5.64598226547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75269365310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8658709526062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80119848251343</t>
   </si>
   <si>
     <t xml:space="preserve">5.89497375488281</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87557172775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22804164886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3476881980896</t>
+    <t xml:space="preserve">5.87557220458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22804117202759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34768772125244</t>
   </si>
   <si>
     <t xml:space="preserve">6.39942693710327</t>
@@ -3050,22 +3050,22 @@
     <t xml:space="preserve">6.1957049369812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05989170074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91761064529419</t>
+    <t xml:space="preserve">6.05989122390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91761016845703</t>
   </si>
   <si>
     <t xml:space="preserve">5.77856254577637</t>
   </si>
   <si>
-    <t xml:space="preserve">5.607177734375</t>
+    <t xml:space="preserve">5.60717821121216</t>
   </si>
   <si>
     <t xml:space="preserve">5.60394430160522</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80766487121582</t>
+    <t xml:space="preserve">5.80766534805298</t>
   </si>
   <si>
     <t xml:space="preserve">5.81736660003662</t>
@@ -3077,16 +3077,16 @@
     <t xml:space="preserve">5.93377828598022</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91114330291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94024515151978</t>
+    <t xml:space="preserve">5.91114282608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94024562835693</t>
   </si>
   <si>
     <t xml:space="preserve">5.82383441925049</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7947301864624</t>
+    <t xml:space="preserve">5.79473066329956</t>
   </si>
   <si>
     <t xml:space="preserve">5.8982081413269</t>
@@ -3101,19 +3101,19 @@
     <t xml:space="preserve">5.79796457290649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6395149230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59101009368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58130931854248</t>
+    <t xml:space="preserve">5.63951444625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59101057052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58130884170532</t>
   </si>
   <si>
     <t xml:space="preserve">5.70418787002563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70742082595825</t>
+    <t xml:space="preserve">5.70742177963257</t>
   </si>
   <si>
     <t xml:space="preserve">5.66538429260254</t>
@@ -3122,13 +3122,13 @@
     <t xml:space="preserve">5.69448709487915</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88203954696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80443143844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7106556892395</t>
+    <t xml:space="preserve">5.88204002380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8044319152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71065521240234</t>
   </si>
   <si>
     <t xml:space="preserve">5.50693464279175</t>
@@ -3140,19 +3140,19 @@
     <t xml:space="preserve">5.33878374099731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43255996704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30321311950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31938171386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21267080307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21590423583984</t>
+    <t xml:space="preserve">5.43255949020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30321359634399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31938123703003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21266984939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21590375900269</t>
   </si>
   <si>
     <t xml:space="preserve">5.22883939743042</t>
@@ -3161,46 +3161,46 @@
     <t xml:space="preserve">5.34201765060425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26764297485352</t>
+    <t xml:space="preserve">5.26764249801636</t>
   </si>
   <si>
     <t xml:space="preserve">5.32261514663696</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29997873306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21913719177246</t>
+    <t xml:space="preserve">5.2999792098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21913766860962</t>
   </si>
   <si>
     <t xml:space="preserve">5.07362270355225</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12212753295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07685613632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07038974761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10919332504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20296955108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04128694534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99601459503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92164134979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81492948532104</t>
+    <t xml:space="preserve">5.12212800979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07685661315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07038927078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10919284820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20296907424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04128646850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9960150718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92164087295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8149299621582</t>
   </si>
   <si>
     <t xml:space="preserve">4.82463073730469</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">4.50773191452026</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36221647262573</t>
+    <t xml:space="preserve">4.36221599578857</t>
   </si>
   <si>
     <t xml:space="preserve">4.4527587890625</t>
@@ -3233,10 +3233,10 @@
     <t xml:space="preserve">5.13829660415649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14799785614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25794219970703</t>
+    <t xml:space="preserve">5.14799690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25794172286987</t>
   </si>
   <si>
     <t xml:space="preserve">5.23530673980713</t>
@@ -3254,16 +3254,16 @@
     <t xml:space="preserve">6.07605981826782</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00815296173096</t>
+    <t xml:space="preserve">6.00815200805664</t>
   </si>
   <si>
     <t xml:space="preserve">5.97904968261719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98875141143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90467548370361</t>
+    <t xml:space="preserve">5.98875045776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90467500686646</t>
   </si>
   <si>
     <t xml:space="preserve">6.17630338668823</t>
@@ -3275,67 +3275,67 @@
     <t xml:space="preserve">6.31858539581299</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34445476531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2183403968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19247150421143</t>
+    <t xml:space="preserve">6.34445428848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21834135055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19247102737427</t>
   </si>
   <si>
     <t xml:space="preserve">6.13103151321411</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05665731430054</t>
+    <t xml:space="preserve">6.0566577911377</t>
   </si>
   <si>
     <t xml:space="preserve">6.10516262054443</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10192823410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04049015045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03725528717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06635856628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88850688934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95318078994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99198436737061</t>
+    <t xml:space="preserve">6.10192918777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04048919677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03725576400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06635904312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8885064125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95318031311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99198484420776</t>
   </si>
   <si>
     <t xml:space="preserve">5.9855170249939</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02432060241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01138591766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97258234024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73005676269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73975801467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64921569824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55543947219849</t>
+    <t xml:space="preserve">6.02432012557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01138639450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97258281707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73005723953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73975849151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64921522140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55543899536133</t>
   </si>
   <si>
     <t xml:space="preserve">5.36788702011108</t>
@@ -3344,10 +3344,10 @@
     <t xml:space="preserve">5.46813011169434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41639137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72359085083008</t>
+    <t xml:space="preserve">5.41639232635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72359037399292</t>
   </si>
   <si>
     <t xml:space="preserve">6.07282638549805</t>
@@ -3356,7 +3356,7 @@
     <t xml:space="preserve">6.26037931442261</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39619302749634</t>
+    <t xml:space="preserve">6.39619255065918</t>
   </si>
   <si>
     <t xml:space="preserve">6.75836324691772</t>
@@ -3374,19 +3374,19 @@
     <t xml:space="preserve">6.66135358810425</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58374547958374</t>
+    <t xml:space="preserve">6.58374500274658</t>
   </si>
   <si>
     <t xml:space="preserve">6.64195156097412</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69369077682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90064477920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80363416671753</t>
+    <t xml:space="preserve">6.69368982315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90064525604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80363464355469</t>
   </si>
   <si>
     <t xml:space="preserve">6.97178554534912</t>
@@ -3404,13 +3404,13 @@
     <t xml:space="preserve">7.2110767364502</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19167470932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23694562911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42449903488159</t>
+    <t xml:space="preserve">7.19167423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23694515228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42449760437012</t>
   </si>
   <si>
     <t xml:space="preserve">7.48270416259766</t>
@@ -3419,64 +3419,64 @@
     <t xml:space="preserve">7.39216232299805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41156530380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16580438613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19814205169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24987983703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35335731506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36629199981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27574968338013</t>
+    <t xml:space="preserve">7.41156339645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16580486297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19814109802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24988126754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35335683822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36629295349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27574920654297</t>
   </si>
   <si>
     <t xml:space="preserve">7.32102108001709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34688997268677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15287160873413</t>
+    <t xml:space="preserve">7.34688949584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15287065505981</t>
   </si>
   <si>
     <t xml:space="preserve">7.49563980102539</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43743276596069</t>
+    <t xml:space="preserve">7.43743324279785</t>
   </si>
   <si>
     <t xml:space="preserve">7.39862966537476</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35982513427734</t>
+    <t xml:space="preserve">7.35982465744019</t>
   </si>
   <si>
     <t xml:space="preserve">7.08172941207886</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26928234100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46330308914185</t>
+    <t xml:space="preserve">7.26928281784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46330165863037</t>
   </si>
   <si>
     <t xml:space="preserve">7.51504182815552</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46976947784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44390106201172</t>
+    <t xml:space="preserve">7.4697699546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4439001083374</t>
   </si>
   <si>
     <t xml:space="preserve">7.47623777389526</t>
@@ -3488,25 +3488,25 @@
     <t xml:space="preserve">7.95482110977173</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69612741470337</t>
+    <t xml:space="preserve">7.69612646102905</t>
   </si>
   <si>
     <t xml:space="preserve">8.11650276184082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43986988067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46573829650879</t>
+    <t xml:space="preserve">8.43987083435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46574020385742</t>
   </si>
   <si>
     <t xml:space="preserve">8.40106582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25878429412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18764495849609</t>
+    <t xml:space="preserve">8.25878524780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18764591217041</t>
   </si>
   <si>
     <t xml:space="preserve">8.05182933807373</t>
@@ -3515,22 +3515,22 @@
     <t xml:space="preserve">8.22644901275635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31052303314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34932613372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4204683303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38166522979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50454235076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14883995056152</t>
+    <t xml:space="preserve">8.31052398681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34932708740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42046928405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38166332244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50454330444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14884090423584</t>
   </si>
   <si>
     <t xml:space="preserve">9.01546382904053</t>
@@ -3542,13 +3542,13 @@
     <t xml:space="preserve">8.64682388305664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59508609771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51101112365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29112243652344</t>
+    <t xml:space="preserve">8.59508514404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51101016998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29112148284912</t>
   </si>
   <si>
     <t xml:space="preserve">8.78910541534424</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">8.35579586029053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96372413635254</t>
+    <t xml:space="preserve">8.96372318267822</t>
   </si>
   <si>
     <t xml:space="preserve">8.98312568664551</t>
@@ -3569,70 +3569,70 @@
     <t xml:space="preserve">8.98959255218506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07366752624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00252819061279</t>
+    <t xml:space="preserve">9.07366847991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00252723693848</t>
   </si>
   <si>
     <t xml:space="preserve">8.99606132507324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06720161437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19654750823975</t>
+    <t xml:space="preserve">9.06720066070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19654846191406</t>
   </si>
   <si>
     <t xml:space="preserve">9.46817588806152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42290306091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3776330947876</t>
+    <t xml:space="preserve">9.4229040145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37763214111328</t>
   </si>
   <si>
     <t xml:space="preserve">9.39056873321533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46170806884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20948314666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3646993637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49404716491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48110961914062</t>
+    <t xml:space="preserve">9.46170997619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20948219299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36469745635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49404525756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48111057281494</t>
   </si>
   <si>
     <t xml:space="preserve">9.565185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81094360351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0437679290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0890407562256</t>
+    <t xml:space="preserve">9.81094551086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0437698364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0890398025513</t>
   </si>
   <si>
     <t xml:space="preserve">10.3283309936523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4059391021729</t>
+    <t xml:space="preserve">10.4059381484985</t>
   </si>
   <si>
     <t xml:space="preserve">10.4447422027588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.244255065918</t>
+    <t xml:space="preserve">10.2442560195923</t>
   </si>
   <si>
     <t xml:space="preserve">10.7616424560547</t>
@@ -3644,22 +3644,22 @@
     <t xml:space="preserve">11.1173458099365</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5611553192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9685974121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5934915542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8133811950684</t>
+    <t xml:space="preserve">10.5611543655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9685964584351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5934896469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.813380241394</t>
   </si>
   <si>
     <t xml:space="preserve">10.6775674819946</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6581659317017</t>
+    <t xml:space="preserve">10.658164024353</t>
   </si>
   <si>
     <t xml:space="preserve">10.8198490142822</t>
@@ -3668,40 +3668,40 @@
     <t xml:space="preserve">10.6840353012085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0074024200439</t>
+    <t xml:space="preserve">11.0074014663696</t>
   </si>
   <si>
     <t xml:space="preserve">11.0009336471558</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2567691802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2291116714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0908231735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9110450744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0078477859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1046504974365</t>
+    <t xml:space="preserve">11.2567701339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2291107177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0908222198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9110441207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0078468322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1046495437622</t>
   </si>
   <si>
     <t xml:space="preserve">11.0424203872681</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0562496185303</t>
+    <t xml:space="preserve">11.056248664856</t>
   </si>
   <si>
     <t xml:space="preserve">11.1945400238037</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3051710128784</t>
+    <t xml:space="preserve">11.3051700592041</t>
   </si>
   <si>
     <t xml:space="preserve">11.5056896209717</t>
@@ -3710,43 +3710,43 @@
     <t xml:space="preserve">11.5748348236084</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5955791473389</t>
+    <t xml:space="preserve">11.5955801010132</t>
   </si>
   <si>
     <t xml:space="preserve">11.6854667663574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6508941650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4780321121216</t>
+    <t xml:space="preserve">11.6508951187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4780330657959</t>
   </si>
   <si>
     <t xml:space="preserve">11.7131261825562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6923809051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6301507949829</t>
+    <t xml:space="preserve">11.6923818588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6301498413086</t>
   </si>
   <si>
     <t xml:space="preserve">11.5402641296387</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2636852264404</t>
+    <t xml:space="preserve">11.2636833190918</t>
   </si>
   <si>
     <t xml:space="preserve">11.1392230987549</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8280715942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9456176757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5514917373657</t>
+    <t xml:space="preserve">10.8280725479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9456167221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.55149269104</t>
   </si>
   <si>
     <t xml:space="preserve">10.5100049972534</t>
@@ -3755,22 +3755,22 @@
     <t xml:space="preserve">10.4961776733398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97067642211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.10205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2057685852051</t>
+    <t xml:space="preserve">9.97067737579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1020498275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2057695388794</t>
   </si>
   <si>
     <t xml:space="preserve">10.6828680038452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5445785522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4616041183472</t>
+    <t xml:space="preserve">10.5445775985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4616050720215</t>
   </si>
   <si>
     <t xml:space="preserve">10.8419008255005</t>
@@ -3779,10 +3779,10 @@
     <t xml:space="preserve">10.9940185546875</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8764715194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9663619995117</t>
+    <t xml:space="preserve">10.8764724731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9663610458374</t>
   </si>
   <si>
     <t xml:space="preserve">10.9179601669312</t>
@@ -3791,13 +3791,13 @@
     <t xml:space="preserve">10.8211574554443</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5653219223022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7381839752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.049334526062</t>
+    <t xml:space="preserve">10.5653209686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.738184928894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0493335723877</t>
   </si>
   <si>
     <t xml:space="preserve">11.0355062484741</t>
@@ -3809,43 +3809,43 @@
     <t xml:space="preserve">11.8030128479004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0934219360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.23171043396</t>
+    <t xml:space="preserve">12.0934209823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2317113876343</t>
   </si>
   <si>
     <t xml:space="preserve">12.1487369537354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9413032531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1210803985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0795927047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2593669891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.418399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4737176895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.605092048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7572116851807</t>
+    <t xml:space="preserve">11.9413042068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1210794448853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0795917510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2593679428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4184017181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4737157821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6050910949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7572107315063</t>
   </si>
   <si>
     <t xml:space="preserve">12.3285140991211</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2870254516602</t>
+    <t xml:space="preserve">12.2870264053345</t>
   </si>
   <si>
     <t xml:space="preserve">12.6880664825439</t>
@@ -3860,49 +3860,49 @@
     <t xml:space="preserve">12.2455377578735</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3561725616455</t>
+    <t xml:space="preserve">12.3561716079712</t>
   </si>
   <si>
     <t xml:space="preserve">12.376914024353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2662830352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2040510177612</t>
+    <t xml:space="preserve">12.2662839889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2040529251099</t>
   </si>
   <si>
     <t xml:space="preserve">12.6396646499634</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4806318283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3907423019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7364664077759</t>
+    <t xml:space="preserve">12.4806308746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3907432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7364683151245</t>
   </si>
   <si>
     <t xml:space="preserve">13.2757959365845</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1885089874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.312970161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9352703094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9905891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7554960250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7969818115234</t>
+    <t xml:space="preserve">14.1885080337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3129682540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9352722167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9905862808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7554969787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7969808578491</t>
   </si>
   <si>
     <t xml:space="preserve">13.9672451019287</t>
@@ -3911,25 +3911,25 @@
     <t xml:space="preserve">13.6215200424194</t>
   </si>
   <si>
-    <t xml:space="preserve">12.68115234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3380279541016</t>
+    <t xml:space="preserve">12.6811513900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3380289077759</t>
   </si>
   <si>
     <t xml:space="preserve">13.0960206985474</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3354263305664</t>
+    <t xml:space="preserve">12.335428237915</t>
   </si>
   <si>
     <t xml:space="preserve">12.5774354934692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3492565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2498559951782</t>
+    <t xml:space="preserve">12.3492574691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2498550415039</t>
   </si>
   <si>
     <t xml:space="preserve">10.7589263916016</t>
@@ -3941,28 +3941,28 @@
     <t xml:space="preserve">11.0285911560059</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3674011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8652429580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1694803237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8056135177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.715723991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7433834075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.061448097229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9992179870605</t>
+    <t xml:space="preserve">11.3674001693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8652439117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1694812774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8056116104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7157230377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7433824539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0614471435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9992160797119</t>
   </si>
   <si>
     <t xml:space="preserve">12.8885841369629</t>
@@ -3971,34 +3971,34 @@
     <t xml:space="preserve">13.0337905883789</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0683622360229</t>
+    <t xml:space="preserve">13.0683631896973</t>
   </si>
   <si>
     <t xml:space="preserve">12.9093294143677</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0199613571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2731962203979</t>
+    <t xml:space="preserve">13.0199604034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2731981277466</t>
   </si>
   <si>
     <t xml:space="preserve">12.6465797424316</t>
   </si>
   <si>
-    <t xml:space="preserve">12.494460105896</t>
+    <t xml:space="preserve">12.4944610595703</t>
   </si>
   <si>
     <t xml:space="preserve">12.5428619384766</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2524547576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5566921234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9551315307617</t>
+    <t xml:space="preserve">12.2524538040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5566911697388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.955132484436</t>
   </si>
   <si>
     <t xml:space="preserve">12.0865068435669</t>
@@ -4007,25 +4007,25 @@
     <t xml:space="preserve">11.9205589294434</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3466577529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5817489624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0242757797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3008575439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0381059646606</t>
+    <t xml:space="preserve">11.3466567993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.581750869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0242776870728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.300856590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0381050109863</t>
   </si>
   <si>
     <t xml:space="preserve">12.5793085098267</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5939340591431</t>
+    <t xml:space="preserve">12.5939350128174</t>
   </si>
   <si>
     <t xml:space="preserve">12.5208005905151</t>
@@ -4034,13 +4034,13 @@
     <t xml:space="preserve">12.7694597244263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6743841171265</t>
+    <t xml:space="preserve">12.6743850708008</t>
   </si>
   <si>
     <t xml:space="preserve">12.747519493103</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4184103012085</t>
+    <t xml:space="preserve">12.4184112548828</t>
   </si>
   <si>
     <t xml:space="preserve">12.3964700698853</t>
@@ -4055,73 +4055,73 @@
     <t xml:space="preserve">12.3525876998901</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1404943466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9795970916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7455625534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0434617996216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4803190231323</t>
+    <t xml:space="preserve">12.140495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9795951843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7455615997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0434627532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.480318069458</t>
   </si>
   <si>
     <t xml:space="preserve">10.5900220870972</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9630126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4583787918091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4437503814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6777839660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5095739364624</t>
+    <t xml:space="preserve">10.9630136489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4583778381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.443751335144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6777849197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5095729827881</t>
   </si>
   <si>
     <t xml:space="preserve">10.5022583007812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2389717102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.494945526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4291248321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3998689651489</t>
+    <t xml:space="preserve">10.2389707565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4949445724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.429123878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3998699188232</t>
   </si>
   <si>
     <t xml:space="preserve">10.209716796875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88060855865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75627708435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70508193969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31014919281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23701477050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43448066711426</t>
+    <t xml:space="preserve">9.88060665130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75627613067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70508289337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31015014648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23701572418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43448162078857</t>
   </si>
   <si>
     <t xml:space="preserve">9.69776916503906</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">8.82745552062988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97372722625732</t>
+    <t xml:space="preserve">8.97372627258301</t>
   </si>
   <si>
     <t xml:space="preserve">9.20776081085205</t>
@@ -4151,22 +4151,22 @@
     <t xml:space="preserve">9.24432849884033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18582057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25895500183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53687000274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21507358551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3686580657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39791393280029</t>
+    <t xml:space="preserve">9.18581962585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25895690917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53687191009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21507549285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36865901947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39791297912598</t>
   </si>
   <si>
     <t xml:space="preserve">9.5807523727417</t>
@@ -4175,43 +4175,43 @@
     <t xml:space="preserve">9.68314170837402</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55881118774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95374202728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0195636749268</t>
+    <t xml:space="preserve">9.55881214141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95374298095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0195646286011</t>
   </si>
   <si>
     <t xml:space="preserve">9.98299694061279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72702217102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47104835510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57343769073486</t>
+    <t xml:space="preserve">9.72702312469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47105026245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57343864440918</t>
   </si>
   <si>
     <t xml:space="preserve">9.80747127532959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97568321228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49298858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10537147521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22238731384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20044612884521</t>
+    <t xml:space="preserve">9.97568416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4929895401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10537052154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22238826751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20044708251953</t>
   </si>
   <si>
     <t xml:space="preserve">9.06880378723145</t>
@@ -4220,7 +4220,7 @@
     <t xml:space="preserve">8.82014274597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75432109832764</t>
+    <t xml:space="preserve">8.75432014465332</t>
   </si>
   <si>
     <t xml:space="preserve">8.81282997131348</t>
@@ -4229,22 +4229,22 @@
     <t xml:space="preserve">8.73969268798828</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51297283172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68849849700928</t>
+    <t xml:space="preserve">8.51297378540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68849945068359</t>
   </si>
   <si>
     <t xml:space="preserve">8.44715118408203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40327072143555</t>
+    <t xml:space="preserve">8.40326976776123</t>
   </si>
   <si>
     <t xml:space="preserve">8.27893924713135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35207653045654</t>
+    <t xml:space="preserve">8.35207557678223</t>
   </si>
   <si>
     <t xml:space="preserve">8.54222774505615</t>
@@ -4253,7 +4253,7 @@
     <t xml:space="preserve">9.01760864257812</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02492332458496</t>
+    <t xml:space="preserve">9.02492237091064</t>
   </si>
   <si>
     <t xml:space="preserve">9.14925289154053</t>
@@ -4262,19 +4262,19 @@
     <t xml:space="preserve">8.94447231292725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89327907562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59342193603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63730335235596</t>
+    <t xml:space="preserve">8.89327716827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59342288970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63730430603027</t>
   </si>
   <si>
     <t xml:space="preserve">8.34476184844971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35939025878906</t>
+    <t xml:space="preserve">8.35938835144043</t>
   </si>
   <si>
     <t xml:space="preserve">8.22043132781982</t>
@@ -4289,25 +4289,25 @@
     <t xml:space="preserve">8.32282066345215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41789817810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33013534545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24237251281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14729690551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07415866851807</t>
+    <t xml:space="preserve">8.41789722442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33013439178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2423734664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14729595184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07415962219238</t>
   </si>
   <si>
     <t xml:space="preserve">8.1619234085083</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04490661621094</t>
+    <t xml:space="preserve">8.04490566253662</t>
   </si>
   <si>
     <t xml:space="preserve">8.05221843719482</t>
@@ -4316,13 +4316,13 @@
     <t xml:space="preserve">8.28625297546387</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26431274414062</t>
+    <t xml:space="preserve">8.26431179046631</t>
   </si>
   <si>
     <t xml:space="preserve">8.30088043212891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38864326477051</t>
+    <t xml:space="preserve">8.38864421844482</t>
   </si>
   <si>
     <t xml:space="preserve">8.48371887207031</t>
@@ -4334,7 +4334,7 @@
     <t xml:space="preserve">8.71775245666504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88596439361572</t>
+    <t xml:space="preserve">8.88596343994141</t>
   </si>
   <si>
     <t xml:space="preserve">8.922532081604</t>
@@ -4346,7 +4346,7 @@
     <t xml:space="preserve">9.52955722808838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84403991699219</t>
+    <t xml:space="preserve">9.84403896331787</t>
   </si>
   <si>
     <t xml:space="preserve">10.0488185882568</t>
@@ -4355,10 +4355,10 @@
     <t xml:space="preserve">10.1804628372192</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1512088775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1146411895752</t>
+    <t xml:space="preserve">10.1512098312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1146402359009</t>
   </si>
   <si>
     <t xml:space="preserve">10.0049381256104</t>
@@ -4367,10 +4367,10 @@
     <t xml:space="preserve">10.3340473175049</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2789545059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3104372024536</t>
+    <t xml:space="preserve">10.2789535522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3104362487793</t>
   </si>
   <si>
     <t xml:space="preserve">10.3261766433716</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">10.3576583862305</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3497877120972</t>
+    <t xml:space="preserve">10.3497886657715</t>
   </si>
   <si>
     <t xml:space="preserve">10.389142036438</t>
@@ -4391,28 +4391,28 @@
     <t xml:space="preserve">10.2710828781128</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2002487182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.04283618927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86968517303467</t>
+    <t xml:space="preserve">10.2002477645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0428371429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86968421936035</t>
   </si>
   <si>
     <t xml:space="preserve">9.88542556762695</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0507068634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96413135528564</t>
+    <t xml:space="preserve">10.0507078170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96413230895996</t>
   </si>
   <si>
     <t xml:space="preserve">10.1608953475952</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1845073699951</t>
+    <t xml:space="preserve">10.1845064163208</t>
   </si>
   <si>
     <t xml:space="preserve">10.0034847259521</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">10.3419179916382</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4521064758301</t>
+    <t xml:space="preserve">10.4521055221558</t>
   </si>
   <si>
     <t xml:space="preserve">10.3812704086304</t>
@@ -4436,10 +4436,10 @@
     <t xml:space="preserve">10.4678478240967</t>
   </si>
   <si>
-    <t xml:space="preserve">10.47571849823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5780334472656</t>
+    <t xml:space="preserve">10.4757175445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5780344009399</t>
   </si>
   <si>
     <t xml:space="preserve">10.7433166503906</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">11.3650913238525</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3493509292603</t>
+    <t xml:space="preserve">11.3493499755859</t>
   </si>
   <si>
     <t xml:space="preserve">11.3414793014526</t>
@@ -4475,52 +4475,52 @@
     <t xml:space="preserve">11.3099975585938</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1919384002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.412314414978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3965740203857</t>
+    <t xml:space="preserve">11.1919393539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4123134613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3965730667114</t>
   </si>
   <si>
     <t xml:space="preserve">11.2155504226685</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4280567169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4752788543701</t>
+    <t xml:space="preserve">11.4280557632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4752779006958</t>
   </si>
   <si>
     <t xml:space="preserve">11.8294544219971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0813121795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1678886413574</t>
+    <t xml:space="preserve">12.0813131332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1678876876831</t>
   </si>
   <si>
     <t xml:space="preserve">12.3725233078003</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3095598220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4040060043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5220632553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5141925811768</t>
+    <t xml:space="preserve">12.3095588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4040050506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5220642089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5141935348511</t>
   </si>
   <si>
     <t xml:space="preserve">12.7266988754272</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8368854522705</t>
+    <t xml:space="preserve">12.8368864059448</t>
   </si>
   <si>
     <t xml:space="preserve">12.8132753372192</t>
@@ -4529,28 +4529,28 @@
     <t xml:space="preserve">12.537805557251</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3882646560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9077215194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7345695495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5063238143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2465934753418</t>
+    <t xml:space="preserve">12.3882637023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9077205657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7345685958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5063228607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2465944290161</t>
   </si>
   <si>
     <t xml:space="preserve">12.1049242019653</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2702054977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2308530807495</t>
+    <t xml:space="preserve">12.2702074050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2308521270752</t>
   </si>
   <si>
     <t xml:space="preserve">12.3016872406006</t>
@@ -4559,31 +4559,31 @@
     <t xml:space="preserve">12.3252992630005</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9160318374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4516677856445</t>
+    <t xml:space="preserve">11.9160299301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4516668319702</t>
   </si>
   <si>
     <t xml:space="preserve">11.6563024520874</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1132335662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1289739608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0974922180176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0266571044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8062801361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8456344604492</t>
+    <t xml:space="preserve">11.1132326126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1289749145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0974931716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0266561508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8062810897827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8456335067749</t>
   </si>
   <si>
     <t xml:space="preserve">10.7118349075317</t>
@@ -4592,19 +4592,19 @@
     <t xml:space="preserve">10.8613748550415</t>
   </si>
   <si>
-    <t xml:space="preserve">10.995174407959</t>
+    <t xml:space="preserve">10.9951753616333</t>
   </si>
   <si>
     <t xml:space="preserve">10.9873037338257</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9085988998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0581388473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.176197052002</t>
+    <t xml:space="preserve">10.908597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0581398010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1761980056763</t>
   </si>
   <si>
     <t xml:space="preserve">11.5854682922363</t>
@@ -4613,19 +4613,19 @@
     <t xml:space="preserve">11.5225019454956</t>
   </si>
   <si>
-    <t xml:space="preserve">11.774359703064</t>
+    <t xml:space="preserve">11.7743587493896</t>
   </si>
   <si>
     <t xml:space="preserve">11.8766775131226</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8137130737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9947347640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1285352706909</t>
+    <t xml:space="preserve">11.8137140274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9947357177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1285362243652</t>
   </si>
   <si>
     <t xml:space="preserve">11.9632530212402</t>
@@ -4652,13 +4652,13 @@
     <t xml:space="preserve">11.3257389068604</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3572206497192</t>
+    <t xml:space="preserve">11.3572216033936</t>
   </si>
   <si>
     <t xml:space="preserve">11.3336095809937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9122791290283</t>
+    <t xml:space="preserve">11.912278175354</t>
   </si>
   <si>
     <t xml:space="preserve">11.8475370407104</t>
@@ -4682,7 +4682,7 @@
     <t xml:space="preserve">11.3296117782593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5076484680176</t>
+    <t xml:space="preserve">11.5076494216919</t>
   </si>
   <si>
     <t xml:space="preserve">11.6371307373047</t>
@@ -4697,10 +4697,10 @@
     <t xml:space="preserve">11.5885744094849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5400199890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4429082870483</t>
+    <t xml:space="preserve">11.5400190353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4429092407227</t>
   </si>
   <si>
     <t xml:space="preserve">11.3862600326538</t>
@@ -4733,19 +4733,19 @@
     <t xml:space="preserve">11.6047601699829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6533164978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6209440231323</t>
+    <t xml:space="preserve">11.6533155441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6209449768066</t>
   </si>
   <si>
     <t xml:space="preserve">11.8637218475342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9770193099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.993203163147</t>
+    <t xml:space="preserve">11.9770183563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9932041168213</t>
   </si>
   <si>
     <t xml:space="preserve">11.8232593536377</t>
@@ -4754,7 +4754,7 @@
     <t xml:space="preserve">11.9446487426758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8151664733887</t>
+    <t xml:space="preserve">11.815167427063</t>
   </si>
   <si>
     <t xml:space="preserve">11.9365558624268</t>
@@ -4769,7 +4769,7 @@
     <t xml:space="preserve">12.2521677017212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4221105575562</t>
+    <t xml:space="preserve">12.4221115112305</t>
   </si>
   <si>
     <t xml:space="preserve">12.3816480636597</t>
@@ -4778,7 +4778,7 @@
     <t xml:space="preserve">12.3411846160889</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3249988555908</t>
+    <t xml:space="preserve">12.3249998092651</t>
   </si>
   <si>
     <t xml:space="preserve">12.3007211685181</t>
@@ -4790,7 +4790,7 @@
     <t xml:space="preserve">12.6082401275635</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8914813995361</t>
+    <t xml:space="preserve">12.8914804458618</t>
   </si>
   <si>
     <t xml:space="preserve">12.9966831207275</t>
@@ -4802,13 +4802,13 @@
     <t xml:space="preserve">12.5354070663452</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6163320541382</t>
+    <t xml:space="preserve">12.6163330078125</t>
   </si>
   <si>
     <t xml:space="preserve">13.1909055709839</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1261644363403</t>
+    <t xml:space="preserve">13.1261653900146</t>
   </si>
   <si>
     <t xml:space="preserve">12.8429250717163</t>
@@ -4820,7 +4820,7 @@
     <t xml:space="preserve">12.9804992675781</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0290546417236</t>
+    <t xml:space="preserve">13.0290536880493</t>
   </si>
   <si>
     <t xml:space="preserve">13.0937957763672</t>
@@ -4832,10 +4832,10 @@
     <t xml:space="preserve">12.9076662063599</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8510179519653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9885902404785</t>
+    <t xml:space="preserve">12.851016998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9885911941528</t>
   </si>
   <si>
     <t xml:space="preserve">12.9238510131836</t>
@@ -4847,7 +4847,7 @@
     <t xml:space="preserve">13.0776100158691</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1747217178345</t>
+    <t xml:space="preserve">13.1747207641602</t>
   </si>
   <si>
     <t xml:space="preserve">13.1666288375854</t>
@@ -4856,13 +4856,13 @@
     <t xml:space="preserve">12.9724073410034</t>
   </si>
   <si>
-    <t xml:space="preserve">12.931941986084</t>
+    <t xml:space="preserve">12.9319429397583</t>
   </si>
   <si>
     <t xml:space="preserve">12.6810731887817</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5677766799927</t>
+    <t xml:space="preserve">12.5677757263184</t>
   </si>
   <si>
     <t xml:space="preserve">12.4787578582764</t>
@@ -4871,22 +4871,22 @@
     <t xml:space="preserve">12.7539072036743</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7296276092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5839614868164</t>
+    <t xml:space="preserve">12.7296285629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5839624404907</t>
   </si>
   <si>
     <t xml:space="preserve">12.5758695602417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6729803085327</t>
+    <t xml:space="preserve">12.672981262207</t>
   </si>
   <si>
     <t xml:space="preserve">12.7943696975708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8752946853638</t>
+    <t xml:space="preserve">12.8752956390381</t>
   </si>
   <si>
     <t xml:space="preserve">13.0209617614746</t>
@@ -4913,13 +4913,13 @@
     <t xml:space="preserve">13.4903326034546</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2880172729492</t>
+    <t xml:space="preserve">13.2880163192749</t>
   </si>
   <si>
     <t xml:space="preserve">13.3203859329224</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3042011260986</t>
+    <t xml:space="preserve">13.3042020797729</t>
   </si>
   <si>
     <t xml:space="preserve">13.0128688812256</t>
@@ -4949,10 +4949,10 @@
     <t xml:space="preserve">13.4174976348877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4579601287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.595534324646</t>
+    <t xml:space="preserve">13.4579610824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5955333709717</t>
   </si>
   <si>
     <t xml:space="preserve">14.0163478851318</t>
@@ -4961,7 +4961,7 @@
     <t xml:space="preserve">13.8221273422241</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9435167312622</t>
+    <t xml:space="preserve">13.9435157775879</t>
   </si>
   <si>
     <t xml:space="preserve">13.8140335083008</t>
@@ -6048,6 +6048,9 @@
   </si>
   <si>
     <t xml:space="preserve">22.2399997711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2800006866455</t>
   </si>
 </sst>
 </file>
@@ -71178,7 +71181,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6493634259</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>95866</v>
@@ -71199,6 +71202,32 @@
         <v>2011</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6493402778</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>103456</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>22.5400009155273</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>22.2600002288818</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>22.2600002288818</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>22.2800006866455</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>2012</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IF.MI.xlsx
+++ b/data/IF.MI.xlsx
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.737078666687</t>
+    <t xml:space="preserve">15.7370767593384</t>
   </si>
   <si>
     <t xml:space="preserve">IF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3903484344482</t>
+    <t xml:space="preserve">15.3903512954712</t>
   </si>
   <si>
     <t xml:space="preserve">15.3232374191284</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5458908081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3613405227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3781213760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4284496307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1767930984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8646612167358</t>
+    <t xml:space="preserve">14.5458917617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3613414764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3781185150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4284515380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1767921447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8646602630615</t>
   </si>
   <si>
     <t xml:space="preserve">13.8524322509766</t>
@@ -74,61 +74,61 @@
     <t xml:space="preserve">14.4955596923828</t>
   </si>
   <si>
-    <t xml:space="preserve">14.640962600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.434042930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3735704421997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3959407806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.938404083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.943995475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5637121200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.10618019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0502529144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7706336975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1722421646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9597282409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5402984619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0583095550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0974531173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7405824661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7685432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8244676589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5347080230713</t>
+    <t xml:space="preserve">14.6409616470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4340438842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3735694885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3959398269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9384069442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9439973831177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5637130737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1061763763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0502548217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7706317901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1722450256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9597320556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5403003692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0583066940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0974559783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7405834197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7685441970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8244695663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5347061157227</t>
   </si>
   <si>
     <t xml:space="preserve">14.4396362304688</t>
@@ -137,73 +137,73 @@
     <t xml:space="preserve">14.3501577377319</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2718620300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3333797454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4350881576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.976508140564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7416276931763</t>
+    <t xml:space="preserve">14.2718658447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3333768844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4350872039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9765090942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7416286468506</t>
   </si>
   <si>
     <t xml:space="preserve">15.2057991027832</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0995416641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0436182022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4966020584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2840929031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9876928329468</t>
+    <t xml:space="preserve">15.0995407104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0436172485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4966039657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2840900421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9876956939697</t>
   </si>
   <si>
     <t xml:space="preserve">14.4452285766602</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5570764541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1656093597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4843769073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7192544937134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1834287643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3791637420654</t>
+    <t xml:space="preserve">14.5570774078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1656074523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.719256401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1834268569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3791608810425</t>
   </si>
   <si>
     <t xml:space="preserve">15.9999217987061</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2348041534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.09499168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9663667678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1173610687256</t>
+    <t xml:space="preserve">16.234806060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0949935913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9663648605347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1173629760742</t>
   </si>
   <si>
     <t xml:space="preserve">16.1403388977051</t>
@@ -215,193 +215,193 @@
     <t xml:space="preserve">16.7204704284668</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4160442352295</t>
+    <t xml:space="preserve">16.4160423278809</t>
   </si>
   <si>
     <t xml:space="preserve">15.8473987579346</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3815822601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6004133224487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6808252334595</t>
+    <t xml:space="preserve">16.3815784454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6004123687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6808280944824</t>
   </si>
   <si>
     <t xml:space="preserve">15.7842168807983</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8876066207886</t>
+    <t xml:space="preserve">15.8876075744629</t>
   </si>
   <si>
     <t xml:space="preserve">15.6348743438721</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2787551879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4280958175659</t>
+    <t xml:space="preserve">15.2787532806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.428092956543</t>
   </si>
   <si>
     <t xml:space="preserve">15.23854637146</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1409015655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3821487426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9570980072021</t>
+    <t xml:space="preserve">15.1409034729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3821449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9570970535278</t>
   </si>
   <si>
     <t xml:space="preserve">14.8479623794556</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5894899368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.623950958252</t>
+    <t xml:space="preserve">14.5894861221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6239519119263</t>
   </si>
   <si>
     <t xml:space="preserve">14.7043657302856</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5550260543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3482437133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1184854507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8427829742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1644401550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.670464515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6417465209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.325831413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1075620651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8376007080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9811983108521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7629280090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4814777374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6365642547607</t>
+    <t xml:space="preserve">14.5550241470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3482446670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1184883117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8427820205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1644382476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6704607009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6417436599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3258304595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1075639724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8376016616821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9811992645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7629289627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4814786911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6365652084351</t>
   </si>
   <si>
     <t xml:space="preserve">12.6882581710815</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3493690490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5791263580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9352445602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.514817237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9576578140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7853422164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5613317489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6647205352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3488054275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2683906555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.360297203064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1535120010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9639654159546</t>
+    <t xml:space="preserve">12.3493709564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5791254043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9352464675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5148162841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9576587677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7853412628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5613307952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.664722442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3488082885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2683925628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3602924346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1535148620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9639663696289</t>
   </si>
   <si>
     <t xml:space="preserve">12.7801609039307</t>
   </si>
   <si>
-    <t xml:space="preserve">12.550407409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2057723999023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.056432723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9185771942139</t>
+    <t xml:space="preserve">12.550404548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2057704925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0564298629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9185781478882</t>
   </si>
   <si>
     <t xml:space="preserve">11.6084070205688</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2287483215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6537942886353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5963573455811</t>
+    <t xml:space="preserve">12.2287473678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6537971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5963544845581</t>
   </si>
   <si>
     <t xml:space="preserve">12.9869413375854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1196126937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1781759262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2643375396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3217735290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4251651763916</t>
+    <t xml:space="preserve">12.1196136474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1781787872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2643365859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3217763900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4251642227173</t>
   </si>
   <si>
     <t xml:space="preserve">10.436653137207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4538860321045</t>
+    <t xml:space="preserve">10.4538869857788</t>
   </si>
   <si>
     <t xml:space="preserve">9.93693351745605</t>
@@ -410,43 +410,43 @@
     <t xml:space="preserve">9.58081340789795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5693244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73015594482422</t>
+    <t xml:space="preserve">9.56932353973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7301549911499</t>
   </si>
   <si>
     <t xml:space="preserve">9.76461791992188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8272371292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.281005859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4877853393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3269548416138</t>
+    <t xml:space="preserve">10.8272390365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2810039520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4877843856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3269538879395</t>
   </si>
   <si>
     <t xml:space="preserve">11.5165033340454</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2580318450928</t>
+    <t xml:space="preserve">11.2580308914185</t>
   </si>
   <si>
     <t xml:space="preserve">11.4992733001709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2293100357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0455045700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.861701965332</t>
+    <t xml:space="preserve">11.2293090820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.045503616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8617010116577</t>
   </si>
   <si>
     <t xml:space="preserve">10.6032247543335</t>
@@ -455,82 +455,82 @@
     <t xml:space="preserve">10.9995536804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7175397872925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4188575744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5796880722046</t>
+    <t xml:space="preserve">11.7175416946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4188594818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.579686164856</t>
   </si>
   <si>
     <t xml:space="preserve">11.1144323348999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1431522369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6026639938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7405185699463</t>
+    <t xml:space="preserve">11.1431531906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6026630401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7405166625977</t>
   </si>
   <si>
     <t xml:space="preserve">11.4016275405884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6543598175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5567121505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4533224105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3843955993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2867469787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9880657196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9765787124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0397615432739</t>
+    <t xml:space="preserve">11.6543607711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5567140579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4533214569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3843946456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2867488861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9880666732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.976580619812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0397605895996</t>
   </si>
   <si>
     <t xml:space="preserve">11.0282745361328</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0972013473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9708337783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9650897979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1201753616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2063322067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1891021728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.430347442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8324193954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.314905166626</t>
+    <t xml:space="preserve">11.0972003936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9708347320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9650907516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1201763153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2063360214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1891031265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4303455352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8324174880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3149061203003</t>
   </si>
   <si>
     <t xml:space="preserve">12.395320892334</t>
@@ -539,64 +539,64 @@
     <t xml:space="preserve">11.9587841033936</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6945667266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7749795913696</t>
+    <t xml:space="preserve">11.6945648193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7749786376953</t>
   </si>
   <si>
     <t xml:space="preserve">11.6715908050537</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6888208389282</t>
+    <t xml:space="preserve">11.6888236999512</t>
   </si>
   <si>
     <t xml:space="preserve">11.5739440917969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7692365646362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0621747970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0219659805298</t>
+    <t xml:space="preserve">11.7692356109619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0621738433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0219678878784</t>
   </si>
   <si>
     <t xml:space="preserve">11.6601009368896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5107612609863</t>
+    <t xml:space="preserve">11.5107622146606</t>
   </si>
   <si>
     <t xml:space="preserve">11.4935302734375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5279941558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7060537338257</t>
+    <t xml:space="preserve">11.5279932022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7060508728027</t>
   </si>
   <si>
     <t xml:space="preserve">11.7577486038208</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0277118682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4068098068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4349641799927</t>
+    <t xml:space="preserve">12.0277099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4068088531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4349660873413</t>
   </si>
   <si>
     <t xml:space="preserve">13.6991834640503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7279033660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8657569885254</t>
+    <t xml:space="preserve">13.7279043197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8657560348511</t>
   </si>
   <si>
     <t xml:space="preserve">13.9519157409668</t>
@@ -605,10 +605,10 @@
     <t xml:space="preserve">14.1759281158447</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3712186813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4631233215332</t>
+    <t xml:space="preserve">14.3712196350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4631214141846</t>
   </si>
   <si>
     <t xml:space="preserve">14.8824262619019</t>
@@ -617,34 +617,34 @@
     <t xml:space="preserve">14.9628400802612</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1064329147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2270593643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1351566314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9456081390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7158527374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7330856323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5090732574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.595232963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5435361862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3827085494995</t>
+    <t xml:space="preserve">15.1064367294312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2270584106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.135157585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9456100463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7158517837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7330846786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5090751647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5952301025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5435371398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3827066421509</t>
   </si>
   <si>
     <t xml:space="preserve">14.0725374221802</t>
@@ -653,19 +653,19 @@
     <t xml:space="preserve">14.0610494613647</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6474895477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6876945495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.590048789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5383529663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.050124168396</t>
+    <t xml:space="preserve">13.6474905014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6876964569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5900478363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5383548736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0501251220703</t>
   </si>
   <si>
     <t xml:space="preserve">13.1190500259399</t>
@@ -680,85 +680,85 @@
     <t xml:space="preserve">13.2109527587891</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4407091140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4234781265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2856216430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1414642333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2735757827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1931610107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.35973072052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9398670196533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6871337890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3884525299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.474609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7847757339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9341201782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2213182449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5831785202026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4970207214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4510717391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3361959457397</t>
+    <t xml:space="preserve">13.4407081604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4234790802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2856225967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1414632797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2735729217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1931581497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3597316741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9398651123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6871366500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3884496688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4746112823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7847805023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9341220855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2213163375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5831823348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4970216751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4510707855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3361940383911</t>
   </si>
   <si>
     <t xml:space="preserve">14.8364753723145</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9915628433228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2959852218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.163875579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0375108718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.089204788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0719728469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8307304382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6469268798828</t>
+    <t xml:space="preserve">14.9915609359741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2959861755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1638774871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0375099182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0892057418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0719747543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8307313919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6469240188599</t>
   </si>
   <si>
     <t xml:space="preserve">14.5320482254028</t>
@@ -767,37 +767,37 @@
     <t xml:space="preserve">14.2333660125732</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5263071060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4171733856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3941946029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0490016937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7618036270142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6584157943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8766832351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3936309814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8531455993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8416576385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0369491577148</t>
+    <t xml:space="preserve">14.5263061523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4171695709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3941965103149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0489978790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7618064880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6584167480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8766822814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3936347961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8531436920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8416557312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0369510650635</t>
   </si>
   <si>
     <t xml:space="preserve">16.5079479217529</t>
@@ -812,34 +812,34 @@
     <t xml:space="preserve">16.634313583374</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6113376617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0829010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8870429992676</t>
+    <t xml:space="preserve">16.6113357543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0828990936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8870449066162</t>
   </si>
   <si>
     <t xml:space="preserve">16.9444828033447</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3465557098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4844093322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5935401916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.059362411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1684951782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6911888122559</t>
+    <t xml:space="preserve">17.3465576171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.484411239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5935440063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0593605041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.168493270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6911907196045</t>
   </si>
   <si>
     <t xml:space="preserve">17.9152011871338</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">18.7365760803223</t>
   </si>
   <si>
-    <t xml:space="preserve">19.552209854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8164310455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9944915771484</t>
+    <t xml:space="preserve">19.5522117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8164291381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9944934844971</t>
   </si>
   <si>
     <t xml:space="preserve">20.942232131958</t>
@@ -863,58 +863,58 @@
     <t xml:space="preserve">20.5229263305664</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8503303527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7354507446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6780166625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6492958068848</t>
+    <t xml:space="preserve">20.8503284454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7354526519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6780128479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6492919921875</t>
   </si>
   <si>
     <t xml:space="preserve">20.321891784668</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5631370544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6378059387207</t>
+    <t xml:space="preserve">20.5631351470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6378078460693</t>
   </si>
   <si>
     <t xml:space="preserve">20.8388423919678</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8216075897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6090850830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1088047027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4132308959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2409172058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1777305603027</t>
+    <t xml:space="preserve">20.8216133117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6090869903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1088027954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4132328033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2409114837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1777324676514</t>
   </si>
   <si>
     <t xml:space="preserve">21.022647857666</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9594669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3098373413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5855503082275</t>
+    <t xml:space="preserve">20.9594631195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3098411560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5855484008789</t>
   </si>
   <si>
     <t xml:space="preserve">21.3155879974365</t>
@@ -923,10 +923,10 @@
     <t xml:space="preserve">22.2690734863281</t>
   </si>
   <si>
-    <t xml:space="preserve">22.136962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9818801879883</t>
+    <t xml:space="preserve">22.1369609832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9818744659424</t>
   </si>
   <si>
     <t xml:space="preserve">22.2288646697998</t>
@@ -935,10 +935,10 @@
     <t xml:space="preserve">22.7458152770996</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9335079193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5815868377686</t>
+    <t xml:space="preserve">22.9335041046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5815887451172</t>
   </si>
   <si>
     <t xml:space="preserve">22.3938941955566</t>
@@ -947,22 +947,22 @@
     <t xml:space="preserve">21.4671688079834</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4583263397217</t>
+    <t xml:space="preserve">20.4583282470703</t>
   </si>
   <si>
     <t xml:space="preserve">21.1035175323486</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8161163330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6342887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.692943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5873699188232</t>
+    <t xml:space="preserve">20.8161182403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6342945098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6929416656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5873680114746</t>
   </si>
   <si>
     <t xml:space="preserve">19.2969932556152</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">18.5872840881348</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5433349609375</t>
+    <t xml:space="preserve">19.5433330535889</t>
   </si>
   <si>
     <t xml:space="preserve">19.9656410217285</t>
@@ -980,10 +980,10 @@
     <t xml:space="preserve">20.4817905426025</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4700603485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.528715133667</t>
+    <t xml:space="preserve">20.4700622558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5287132263184</t>
   </si>
   <si>
     <t xml:space="preserve">20.4114074707031</t>
@@ -992,19 +992,19 @@
     <t xml:space="preserve">20.2706394195557</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3058280944824</t>
+    <t xml:space="preserve">20.3058300018311</t>
   </si>
   <si>
     <t xml:space="preserve">19.7955455780029</t>
   </si>
   <si>
-    <t xml:space="preserve">19.607852935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8835277557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2471752166748</t>
+    <t xml:space="preserve">19.6078548431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.88352394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2471771240234</t>
   </si>
   <si>
     <t xml:space="preserve">20.0594863891602</t>
@@ -1013,79 +1013,79 @@
     <t xml:space="preserve">20.176794052124</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7515964508057</t>
+    <t xml:space="preserve">20.7515983581543</t>
   </si>
   <si>
     <t xml:space="preserve">20.6988086700439</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3527545928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5521755218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5052547454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7046718597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4407348632812</t>
+    <t xml:space="preserve">20.3527507781982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5521774291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5052528381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7046775817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4407329559326</t>
   </si>
   <si>
     <t xml:space="preserve">20.1474666595459</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0477561950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0008296966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4876556396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6694850921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6460227966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.863037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9334201812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0096759796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9275608062744</t>
+    <t xml:space="preserve">20.0477542877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0008316040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4876575469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6694831848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6460208892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8630390167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.933422088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0096702575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9275569915771</t>
   </si>
   <si>
     <t xml:space="preserve">21.1152477264404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2560176849365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2912101745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5551509857178</t>
+    <t xml:space="preserve">21.2560157775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2912082672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5551490783691</t>
   </si>
   <si>
     <t xml:space="preserve">21.748706817627</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6314010620117</t>
+    <t xml:space="preserve">21.6314029693604</t>
   </si>
   <si>
     <t xml:space="preserve">21.6079349517822</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6431350708008</t>
+    <t xml:space="preserve">21.6431312561035</t>
   </si>
   <si>
     <t xml:space="preserve">21.8366851806641</t>
@@ -1094,46 +1094,46 @@
     <t xml:space="preserve">22.0830307006836</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7604331970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4642791748047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9041805267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6402378082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9686985015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7575454711914</t>
+    <t xml:space="preserve">21.7604351043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4642772674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9041786193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6402397155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9686965942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.75754737854</t>
   </si>
   <si>
     <t xml:space="preserve">23.2854270935059</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4907131195068</t>
+    <t xml:space="preserve">23.4907112121582</t>
   </si>
   <si>
     <t xml:space="preserve">23.7722492218018</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0068664550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.270809173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8719615936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1007080078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0479221343994</t>
+    <t xml:space="preserve">24.0068626403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2708072662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8719654083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1007099151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0479202270508</t>
   </si>
   <si>
     <t xml:space="preserve">23.5435028076172</t>
@@ -1142,31 +1142,31 @@
     <t xml:space="preserve">23.5669631958008</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1593627929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3529243469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3059978485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.854362487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0361919403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8367691040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8191757202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9716701507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7898464202881</t>
+    <t xml:space="preserve">24.159366607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3529205322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3059959411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8543643951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.036190032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8367710113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8191738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9716720581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7898483276367</t>
   </si>
   <si>
     <t xml:space="preserve">23.6373481750488</t>
@@ -1175,22 +1175,22 @@
     <t xml:space="preserve">23.1153335571289</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7077331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9012870788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1652297973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5347499847412</t>
+    <t xml:space="preserve">23.7077312469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9012889862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.165225982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5347480773926</t>
   </si>
   <si>
     <t xml:space="preserve">24.3411903381348</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0831127166748</t>
+    <t xml:space="preserve">24.0831165313721</t>
   </si>
   <si>
     <t xml:space="preserve">24.7400321960449</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">24.7107086181641</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4936847686768</t>
+    <t xml:space="preserve">24.4936828613281</t>
   </si>
   <si>
     <t xml:space="preserve">24.6989784240723</t>
@@ -1208,79 +1208,79 @@
     <t xml:space="preserve">25.0684909820557</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7078189849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7136821746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1594467163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4937686920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3823280334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5876197814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1301193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.59934425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.822229385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1330909729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7548198699951</t>
+    <t xml:space="preserve">25.7078151702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7136783599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1594429016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4937705993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3823299407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5876178741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1301212310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5993480682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8222312927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.133092880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7548179626465</t>
   </si>
   <si>
     <t xml:space="preserve">28.0656814575195</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2064571380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8984794616699</t>
+    <t xml:space="preserve">28.2064514160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8984851837158</t>
   </si>
   <si>
     <t xml:space="preserve">27.7489566802979</t>
   </si>
   <si>
-    <t xml:space="preserve">28.499719619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8281841278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8926982879639</t>
+    <t xml:space="preserve">28.4997215270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8281745910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8927001953125</t>
   </si>
   <si>
     <t xml:space="preserve">28.6580867767334</t>
   </si>
   <si>
-    <t xml:space="preserve">28.053955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9278049468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5289669036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2152137756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6404056549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5378036499023</t>
+    <t xml:space="preserve">28.0539569854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9278087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5289611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2152099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6404037475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5377979278564</t>
   </si>
   <si>
     <t xml:space="preserve">27.6316471099854</t>
@@ -1289,67 +1289,67 @@
     <t xml:space="preserve">27.6668376922607</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8428058624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3237609863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5671291351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6023216247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4556903839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5026092529297</t>
+    <t xml:space="preserve">27.8428020477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3237628936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5671329498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6023235321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4556922912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5026111602783</t>
   </si>
   <si>
     <t xml:space="preserve">27.0803031921387</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8163623809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.306079864502</t>
+    <t xml:space="preserve">26.8163642883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3060779571533</t>
   </si>
   <si>
     <t xml:space="preserve">25.9365653991699</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5992660522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8954238891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.951099395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8279285430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6021556854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7164916992188</t>
+    <t xml:space="preserve">24.5992622375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8954257965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9511051177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8279304504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6021595001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7164878845215</t>
   </si>
   <si>
     <t xml:space="preserve">22.7282199859619</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3176441192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9833183288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6754341125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4056224822998</t>
+    <t xml:space="preserve">22.3176403045654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9833202362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6754302978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4056243896484</t>
   </si>
   <si>
     <t xml:space="preserve">22.610912322998</t>
@@ -1358,19 +1358,19 @@
     <t xml:space="preserve">22.7927398681641</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2355270385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5492858886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5199584960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7311134338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8249588012695</t>
+    <t xml:space="preserve">22.2355289459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5492877960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5199546813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7311096191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8249530792236</t>
   </si>
   <si>
     <t xml:space="preserve">21.4495735168457</t>
@@ -1379,43 +1379,43 @@
     <t xml:space="preserve">20.9040966033936</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4026546478271</t>
+    <t xml:space="preserve">21.4026508331299</t>
   </si>
   <si>
     <t xml:space="preserve">21.8777446746826</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4701461791992</t>
+    <t xml:space="preserve">22.4701442718506</t>
   </si>
   <si>
     <t xml:space="preserve">21.1914978027344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1093864440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0565986633301</t>
+    <t xml:space="preserve">21.1093826293945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0565948486328</t>
   </si>
   <si>
     <t xml:space="preserve">21.7135124206543</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7047557830811</t>
+    <t xml:space="preserve">22.7047576904297</t>
   </si>
   <si>
     <t xml:space="preserve">23.9130172729492</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0449504852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3440818786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7546539306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7663822174072</t>
+    <t xml:space="preserve">23.0449466705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3440799713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7546558380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7663879394531</t>
   </si>
   <si>
     <t xml:space="preserve">23.4496555328369</t>
@@ -1424,31 +1424,31 @@
     <t xml:space="preserve">23.5200386047363</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3469734191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0273513793945</t>
+    <t xml:space="preserve">22.3469715118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0273532867432</t>
   </si>
   <si>
     <t xml:space="preserve">23.1563892364502</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8631191253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0508098602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9569664001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.781005859375</t>
+    <t xml:space="preserve">22.8631210327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0508117675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9569702148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7810077667236</t>
   </si>
   <si>
     <t xml:space="preserve">22.5229320526123</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4994716644287</t>
+    <t xml:space="preserve">22.4994697570801</t>
   </si>
   <si>
     <t xml:space="preserve">22.2765884399414</t>
@@ -1460,58 +1460,58 @@
     <t xml:space="preserve">22.4525489807129</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0771617889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2208271026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7398662567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2677478790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6489105224609</t>
+    <t xml:space="preserve">22.0771675109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2208251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7398681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2677459716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6489124298096</t>
   </si>
   <si>
     <t xml:space="preserve">19.4260292053223</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7750549316406</t>
+    <t xml:space="preserve">20.7750568389893</t>
   </si>
   <si>
     <t xml:space="preserve">21.1621723175049</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9158267974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3733234405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3615894317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3264026641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2794780731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3967838287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0448627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7985172271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6812152862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0125617980957</t>
+    <t xml:space="preserve">20.915828704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3733196258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.36159324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3264007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2794799804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.396785736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0448665618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7985153198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.681209564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0125637054443</t>
   </si>
   <si>
     <t xml:space="preserve">19.3321838378906</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">19.015453338623</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3556461334229</t>
+    <t xml:space="preserve">19.3556442260742</t>
   </si>
   <si>
     <t xml:space="preserve">19.0975704193115</t>
@@ -1529,49 +1529,49 @@
     <t xml:space="preserve">19.0858383178711</t>
   </si>
   <si>
-    <t xml:space="preserve">20.071216583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9891014099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8394927978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3468055725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5227680206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4377555847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2617988586426</t>
+    <t xml:space="preserve">20.0712184906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9891033172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8394947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3468036651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5227642059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4377574920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2618007659912</t>
   </si>
   <si>
     <t xml:space="preserve">18.9919948577881</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3233413696289</t>
+    <t xml:space="preserve">18.3233451843262</t>
   </si>
   <si>
     <t xml:space="preserve">17.3614273071289</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6987247467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9596900939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7221851348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1210289001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2735290527344</t>
+    <t xml:space="preserve">18.6987266540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9596920013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.722188949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1210308074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.273530960083</t>
   </si>
   <si>
     <t xml:space="preserve">19.4142971038818</t>
@@ -1583,46 +1583,46 @@
     <t xml:space="preserve">19.7310237884521</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5785255432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8131408691406</t>
+    <t xml:space="preserve">19.5785274505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8131370544434</t>
   </si>
   <si>
     <t xml:space="preserve">19.6958351135254</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3461208343506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3582229614258</t>
+    <t xml:space="preserve">19.3461227416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3582210540771</t>
   </si>
   <si>
     <t xml:space="preserve">19.1404399871826</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0920429229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1646404266357</t>
+    <t xml:space="preserve">19.0920448303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1646423339844</t>
   </si>
   <si>
     <t xml:space="preserve">19.7816829681396</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9752655029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2656383514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.435022354126</t>
+    <t xml:space="preserve">19.9752616882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2656364440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4350204467773</t>
   </si>
   <si>
     <t xml:space="preserve">20.6649017333984</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3745288848877</t>
+    <t xml:space="preserve">20.3745307922363</t>
   </si>
   <si>
     <t xml:space="preserve">20.0236587524414</t>
@@ -1631,13 +1631,13 @@
     <t xml:space="preserve">19.5397052764893</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4429130554199</t>
+    <t xml:space="preserve">19.4429111480713</t>
   </si>
   <si>
     <t xml:space="preserve">19.6485939025879</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7211894989014</t>
+    <t xml:space="preserve">19.7211875915527</t>
   </si>
   <si>
     <t xml:space="preserve">18.9589576721191</t>
@@ -1646,31 +1646,31 @@
     <t xml:space="preserve">18.3298149108887</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4102993011475</t>
+    <t xml:space="preserve">17.4103012084961</t>
   </si>
   <si>
     <t xml:space="preserve">17.0836296081543</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2288150787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.877950668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5149822235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6075649261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1677980422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8853158950806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1194038391113</t>
+    <t xml:space="preserve">17.228816986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8779468536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5149841308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6075658798218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.167799949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8853168487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.119402885437</t>
   </si>
   <si>
     <t xml:space="preserve">14.22829246521</t>
@@ -1679,64 +1679,64 @@
     <t xml:space="preserve">15.4260807037354</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4865751266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0147199630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1478099822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8332357406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7001466751099</t>
+    <t xml:space="preserve">15.4865760803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0147171020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1478080749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8332366943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7001495361328</t>
   </si>
   <si>
     <t xml:space="preserve">15.2929954528809</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1520195007324</t>
+    <t xml:space="preserve">16.1520156860352</t>
   </si>
   <si>
     <t xml:space="preserve">16.5996742248535</t>
   </si>
   <si>
-    <t xml:space="preserve">16.575475692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0794200897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7932548522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2409172058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7327613830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9021492004395</t>
+    <t xml:space="preserve">16.5754776000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0794239044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7932567596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2409152984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7327632904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9021472930908</t>
   </si>
   <si>
     <t xml:space="preserve">16.6238708496094</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9705333709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.462381362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5712699890137</t>
+    <t xml:space="preserve">15.970531463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4623775482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.571270942688</t>
   </si>
   <si>
     <t xml:space="preserve">15.5954685211182</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6438636779785</t>
+    <t xml:space="preserve">15.6438627243042</t>
   </si>
   <si>
     <t xml:space="preserve">15.619665145874</t>
@@ -1745,25 +1745,25 @@
     <t xml:space="preserve">15.7890491485596</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0431270599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4060897827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5875759124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2730045318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9100370407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9947319030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.825345993042</t>
+    <t xml:space="preserve">16.0431251525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4060935974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.587574005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2730026245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9100379943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9947309494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8253469467163</t>
   </si>
   <si>
     <t xml:space="preserve">16.6722679138184</t>
@@ -1772,28 +1772,28 @@
     <t xml:space="preserve">16.9384441375732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2851047515869</t>
+    <t xml:space="preserve">16.2851028442383</t>
   </si>
   <si>
     <t xml:space="preserve">16.0552253723145</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2972011566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3576965332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2125091552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3655872344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5470705032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6396570205688</t>
+    <t xml:space="preserve">16.2972030639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3576984405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2125110626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3655891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5470724105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6396551132202</t>
   </si>
   <si>
     <t xml:space="preserve">13.3692712783813</t>
@@ -1802,148 +1802,148 @@
     <t xml:space="preserve">13.6838426589966</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6475448608398</t>
+    <t xml:space="preserve">13.6475458145142</t>
   </si>
   <si>
     <t xml:space="preserve">13.6354465484619</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2845792770386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0426025390625</t>
+    <t xml:space="preserve">13.2845783233643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0426015853882</t>
   </si>
   <si>
     <t xml:space="preserve">12.5102491378784</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3771629333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4860515594482</t>
+    <t xml:space="preserve">12.3771619796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4860525131226</t>
   </si>
   <si>
     <t xml:space="preserve">12.4497556686401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2603807449341</t>
+    <t xml:space="preserve">13.2603826522827</t>
   </si>
   <si>
     <t xml:space="preserve">12.7885246276855</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9700078964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9216165542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0909957885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3408651351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2924690246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2561721801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7643280029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1998891830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6596450805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5265579223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3571710586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8895244598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5749540328979</t>
+    <t xml:space="preserve">12.9700088500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9216146469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0909967422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3408670425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2924709320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2561750411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7643270492554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1998863220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6596441268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.526556968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3571729660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8895235061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5749530792236</t>
   </si>
   <si>
     <t xml:space="preserve">13.6717462539673</t>
   </si>
   <si>
-    <t xml:space="preserve">13.320876121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3450727462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5023593902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0589075088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4218759536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3976764678955</t>
+    <t xml:space="preserve">13.3208770751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3450717926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5023612976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0589084625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3976736068726</t>
   </si>
   <si>
     <t xml:space="preserve">14.2645883560181</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4339733123779</t>
+    <t xml:space="preserve">14.4339752197266</t>
   </si>
   <si>
     <t xml:space="preserve">13.3934688568115</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7359209060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8647994995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3003635406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6088829040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9778985977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8024644851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3143005371094</t>
+    <t xml:space="preserve">11.7359228134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.864800453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3003616333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6088848114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9779005050659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8024673461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.314302444458</t>
   </si>
   <si>
     <t xml:space="preserve">10.5865268707275</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2356615066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86664390563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3264007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3022050857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4957847595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92108821868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89689064025879</t>
+    <t xml:space="preserve">10.2356595993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86664295196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3264017105103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3022031784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4957857131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92108726501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89689159393311</t>
   </si>
   <si>
     <t xml:space="preserve">9.5339241027832</t>
@@ -1952,7 +1952,7 @@
     <t xml:space="preserve">8.73539733886719</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37847995758057</t>
+    <t xml:space="preserve">8.37847900390625</t>
   </si>
   <si>
     <t xml:space="preserve">8.22119522094727</t>
@@ -1961,22 +1961,22 @@
     <t xml:space="preserve">8.46922206878662</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49946880340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9713249206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06206607818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40083599090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67911148071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.217511177063</t>
+    <t xml:space="preserve">8.49946975708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97132587432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06206703186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40083789825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67911052703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2175102233887</t>
   </si>
   <si>
     <t xml:space="preserve">9.88479232788086</t>
@@ -1994,16 +1994,16 @@
     <t xml:space="preserve">9.12861061096191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24959850311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36453914642334</t>
+    <t xml:space="preserve">9.24960041046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36454010009766</t>
   </si>
   <si>
     <t xml:space="preserve">9.58836936950684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48552894592285</t>
+    <t xml:space="preserve">9.48552799224854</t>
   </si>
   <si>
     <t xml:space="preserve">9.45528125762939</t>
@@ -2018,13 +2018,13 @@
     <t xml:space="preserve">9.57021999359131</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8406057357788</t>
+    <t xml:space="preserve">10.8406038284302</t>
   </si>
   <si>
     <t xml:space="preserve">11.1370267868042</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9071483612061</t>
+    <t xml:space="preserve">10.9071493148804</t>
   </si>
   <si>
     <t xml:space="preserve">11.5967845916748</t>
@@ -2033,10 +2033,10 @@
     <t xml:space="preserve">11.3064117431641</t>
   </si>
   <si>
-    <t xml:space="preserve">11.00998878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9676418304443</t>
+    <t xml:space="preserve">11.0099906921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.96764087677</t>
   </si>
   <si>
     <t xml:space="preserve">10.5139331817627</t>
@@ -2045,25 +2045,25 @@
     <t xml:space="preserve">10.8285045623779</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3385000228882</t>
+    <t xml:space="preserve">10.3385009765625</t>
   </si>
   <si>
     <t xml:space="preserve">10.7377634048462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2840566635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6409730911255</t>
+    <t xml:space="preserve">10.2840557098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6409740447998</t>
   </si>
   <si>
     <t xml:space="preserve">11.1007299423218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0039396286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8587522506714</t>
+    <t xml:space="preserve">11.0039386749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8587532043457</t>
   </si>
   <si>
     <t xml:space="preserve">10.3747978210449</t>
@@ -2075,40 +2075,40 @@
     <t xml:space="preserve">9.69121074676514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37059020996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1709566116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03786945343018</t>
+    <t xml:space="preserve">9.3705883026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17095851898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03786849975586</t>
   </si>
   <si>
     <t xml:space="preserve">9.34034156799316</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34639072418213</t>
+    <t xml:space="preserve">9.34639167785645</t>
   </si>
   <si>
     <t xml:space="preserve">9.94528579711914</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4050436019897</t>
+    <t xml:space="preserve">10.4050445556641</t>
   </si>
   <si>
     <t xml:space="preserve">10.8043069839478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5562810897827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6228246688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5804767608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5502309799194</t>
+    <t xml:space="preserve">10.556282043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6228227615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5804777145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5502300262451</t>
   </si>
   <si>
     <t xml:space="preserve">10.0239286422729</t>
@@ -2117,46 +2117,46 @@
     <t xml:space="preserve">9.62466526031494</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1025733947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2296085357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4655389785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3687467575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98763275146484</t>
+    <t xml:space="preserve">10.1025724411011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2296104431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.465537071228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3687477111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98763084411621</t>
   </si>
   <si>
     <t xml:space="preserve">9.96948432922363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2780055999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4352922439575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5320825576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1509675979614</t>
+    <t xml:space="preserve">10.2780046463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4352893829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5320816040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1509695053101</t>
   </si>
   <si>
     <t xml:space="preserve">10.0299777984619</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1267690658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3445510864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0662746429443</t>
+    <t xml:space="preserve">10.1267700195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3445501327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.06627368927</t>
   </si>
   <si>
     <t xml:space="preserve">9.64886283874512</t>
@@ -2168,10 +2168,10 @@
     <t xml:space="preserve">12.6433391571045</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0323419570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.372953414917</t>
+    <t xml:space="preserve">12.0323438644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3729553222656</t>
   </si>
   <si>
     <t xml:space="preserve">10.8769006729126</t>
@@ -2180,34 +2180,34 @@
     <t xml:space="preserve">10.7014665603638</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6107263565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5683784484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1086196899414</t>
+    <t xml:space="preserve">10.610725402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.568377494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.10862159729</t>
   </si>
   <si>
     <t xml:space="preserve">10.3506002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9373960494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0341873168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1128311157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4818458557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9736919403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54602146148682</t>
+    <t xml:space="preserve">10.9373950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0341854095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.112829208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4818429946899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9736938476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54602241516113</t>
   </si>
   <si>
     <t xml:space="preserve">9.35848999023438</t>
@@ -2216,13 +2216,13 @@
     <t xml:space="preserve">9.22540283203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1104621887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08626556396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13466167449951</t>
+    <t xml:space="preserve">9.11046314239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08626461029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1346607208252</t>
   </si>
   <si>
     <t xml:space="preserve">8.92897987365723</t>
@@ -2234,10 +2234,10 @@
     <t xml:space="preserve">8.95317840576172</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84428691864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89873218536377</t>
+    <t xml:space="preserve">8.84428596496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89873313903809</t>
   </si>
   <si>
     <t xml:space="preserve">9.0741662979126</t>
@@ -2258,49 +2258,49 @@
     <t xml:space="preserve">9.46133136749268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38873863220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63676452636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68516063690186</t>
+    <t xml:space="preserve">9.38873672485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6367654800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68515968322754</t>
   </si>
   <si>
     <t xml:space="preserve">9.715407371521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83034706115723</t>
+    <t xml:space="preserve">9.83034801483154</t>
   </si>
   <si>
     <t xml:space="preserve">10.2636585235596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9402904510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65572834014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72686958312988</t>
+    <t xml:space="preserve">9.94029140472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65573024749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7268705368042</t>
   </si>
   <si>
     <t xml:space="preserve">9.21595001220703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0477991104126</t>
+    <t xml:space="preserve">9.04780006408691</t>
   </si>
   <si>
     <t xml:space="preserve">8.73736763000488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52394485473633</t>
+    <t xml:space="preserve">8.52394676208496</t>
   </si>
   <si>
     <t xml:space="preserve">8.27818584442139</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86427545547485</t>
+    <t xml:space="preserve">7.86427736282349</t>
   </si>
   <si>
     <t xml:space="preserve">8.32345771789551</t>
@@ -2309,67 +2309,67 @@
     <t xml:space="preserve">8.37519645690918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31699085235596</t>
+    <t xml:space="preserve">8.31698989868164</t>
   </si>
   <si>
     <t xml:space="preserve">8.07123184204102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87721252441406</t>
+    <t xml:space="preserve">7.87721157073975</t>
   </si>
   <si>
     <t xml:space="preserve">7.90954828262329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82547426223755</t>
+    <t xml:space="preserve">7.82547330856323</t>
   </si>
   <si>
     <t xml:space="preserve">7.56677913665771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72199535369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59264898300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54090976715088</t>
+    <t xml:space="preserve">7.72199487686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59265041351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54091024398804</t>
   </si>
   <si>
     <t xml:space="preserve">7.50210666656494</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37276029586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31455373764038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66379022598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32748889923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24341201782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28868436813354</t>
+    <t xml:space="preserve">7.37276077270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31455421447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66379117965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32748937606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24341297149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2886848449707</t>
   </si>
   <si>
     <t xml:space="preserve">7.52150869369507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26281452178955</t>
+    <t xml:space="preserve">7.26281547546387</t>
   </si>
   <si>
     <t xml:space="preserve">7.29515171051025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25634908676147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41803169250488</t>
+    <t xml:space="preserve">7.25634813308716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41803216934204</t>
   </si>
   <si>
     <t xml:space="preserve">7.70906162261963</t>
@@ -2378,43 +2378,43 @@
     <t xml:space="preserve">8.03242778778076</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84487581253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70259428024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55384635925293</t>
+    <t xml:space="preserve">7.84487533569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70259523391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55384540557861</t>
   </si>
   <si>
     <t xml:space="preserve">7.76726722717285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7996039390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67672443389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99362421035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18117523193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7050313949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65329170227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69856357574463</t>
+    <t xml:space="preserve">7.79960441589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67672491073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99362373352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18117618560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70502948760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65329265594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69856262207031</t>
   </si>
   <si>
     <t xml:space="preserve">8.79557323455811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58215236663818</t>
+    <t xml:space="preserve">8.58215141296387</t>
   </si>
   <si>
     <t xml:space="preserve">8.57568454742432</t>
@@ -2423,52 +2423,52 @@
     <t xml:space="preserve">8.49160861968994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55628204345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95725631713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94432163238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9378547668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75030136108398</t>
+    <t xml:space="preserve">8.55628108978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95725536346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94432258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93785381317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7503023147583</t>
   </si>
   <si>
     <t xml:space="preserve">8.62742328643799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82790946960449</t>
+    <t xml:space="preserve">8.82791042327881</t>
   </si>
   <si>
     <t xml:space="preserve">8.83437728881836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71149730682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6080207824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66622638702393</t>
+    <t xml:space="preserve">8.71149826049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60802173614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66622734069824</t>
   </si>
   <si>
     <t xml:space="preserve">8.38813209533691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29758834838867</t>
+    <t xml:space="preserve">8.29758930206299</t>
   </si>
   <si>
     <t xml:space="preserve">8.5433464050293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02839660644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91845226287842</t>
+    <t xml:space="preserve">9.02839756011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91845321655273</t>
   </si>
   <si>
     <t xml:space="preserve">8.88611602783203</t>
@@ -2477,25 +2477,25 @@
     <t xml:space="preserve">9.12540721893311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48514270782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11003494262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87074565887451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2652530670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33639335632324</t>
+    <t xml:space="preserve">8.48513984680176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11003589630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87074518203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26525211334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33639240264893</t>
   </si>
   <si>
     <t xml:space="preserve">8.43340301513672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.368727684021</t>
+    <t xml:space="preserve">8.36872959136963</t>
   </si>
   <si>
     <t xml:space="preserve">8.28465461730957</t>
@@ -2504,40 +2504,40 @@
     <t xml:space="preserve">8.23938274383545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56274795532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76970291137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02192974090576</t>
+    <t xml:space="preserve">8.5627498626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76970481872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02192878723145</t>
   </si>
   <si>
     <t xml:space="preserve">9.13187408447266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22241687774658</t>
+    <t xml:space="preserve">9.22241592407227</t>
   </si>
   <si>
     <t xml:space="preserve">9.45524024963379</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44230556488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50697898864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55871868133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58458805084229</t>
+    <t xml:space="preserve">9.44230651855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50697994232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55871772766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5845890045166</t>
   </si>
   <si>
     <t xml:space="preserve">9.69453239440918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91442203521729</t>
+    <t xml:space="preserve">9.91442108154297</t>
   </si>
   <si>
     <t xml:space="preserve">9.92088985443115</t>
@@ -2549,13 +2549,13 @@
     <t xml:space="preserve">9.89502048492432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9079532623291</t>
+    <t xml:space="preserve">9.90795421600342</t>
   </si>
   <si>
     <t xml:space="preserve">9.67513084411621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57812118530273</t>
+    <t xml:space="preserve">9.57812023162842</t>
   </si>
   <si>
     <t xml:space="preserve">9.66866397857666</t>
@@ -2570,28 +2570,28 @@
     <t xml:space="preserve">9.5199146270752</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30649185180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33236312866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43583965301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09953784942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37116527557373</t>
+    <t xml:space="preserve">9.30649280548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33236122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43583869934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09953689575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37116622924805</t>
   </si>
   <si>
     <t xml:space="preserve">9.52638149261475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79154109954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73980236053467</t>
+    <t xml:space="preserve">9.79154300689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7398042678833</t>
   </si>
   <si>
     <t xml:space="preserve">9.76567363739014</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">9.94675922393799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77214050292969</t>
+    <t xml:space="preserve">9.77213954925537</t>
   </si>
   <si>
     <t xml:space="preserve">9.88208484649658</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">9.98556232452393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.224853515625</t>
+    <t xml:space="preserve">10.2248544692993</t>
   </si>
   <si>
     <t xml:space="preserve">9.44877433776855</t>
@@ -2627,13 +2627,13 @@
     <t xml:space="preserve">9.83034610748291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86915111541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1925182342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2377891540527</t>
+    <t xml:space="preserve">9.86915016174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1925172805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2377872467041</t>
   </si>
   <si>
     <t xml:space="preserve">9.62339305877686</t>
@@ -2645,64 +2645,64 @@
     <t xml:space="preserve">9.34529685974121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24181938171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19008159637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06073379516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08013725280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97665691375732</t>
+    <t xml:space="preserve">9.24181842803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1900806427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0607328414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08013534545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97665882110596</t>
   </si>
   <si>
     <t xml:space="preserve">9.04133129119873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92492008209229</t>
+    <t xml:space="preserve">8.92491912841797</t>
   </si>
   <si>
     <t xml:space="preserve">8.7632360458374</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84731292724609</t>
+    <t xml:space="preserve">8.84731197357178</t>
   </si>
   <si>
     <t xml:space="preserve">8.78263854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61448764801025</t>
+    <t xml:space="preserve">8.61448669433594</t>
   </si>
   <si>
     <t xml:space="preserve">8.56921577453613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67916011810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86671447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87318134307861</t>
+    <t xml:space="preserve">8.67916202545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86671257019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87318229675293</t>
   </si>
   <si>
     <t xml:space="preserve">8.81497573852539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86024570465088</t>
+    <t xml:space="preserve">8.8602466583252</t>
   </si>
   <si>
     <t xml:space="preserve">9.24828624725342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05426692962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14480972290039</t>
+    <t xml:space="preserve">9.05426597595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14481067657471</t>
   </si>
   <si>
     <t xml:space="preserve">9.2353515625</t>
@@ -2711,22 +2711,22 @@
     <t xml:space="preserve">9.15774345397949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13834285736084</t>
+    <t xml:space="preserve">9.13834190368652</t>
   </si>
   <si>
     <t xml:space="preserve">9.2676887512207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0930700302124</t>
+    <t xml:space="preserve">9.09307098388672</t>
   </si>
   <si>
     <t xml:space="preserve">8.93138790130615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2030143737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59105396270752</t>
+    <t xml:space="preserve">9.20301532745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59105491638184</t>
   </si>
   <si>
     <t xml:space="preserve">9.57165431976318</t>
@@ -2735,22 +2735,22 @@
     <t xml:space="preserve">9.51344776153564</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53285026550293</t>
+    <t xml:space="preserve">9.53284931182861</t>
   </si>
   <si>
     <t xml:space="preserve">9.32589435577393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30002593994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74627208709717</t>
+    <t xml:space="preserve">9.30002689361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74627113342285</t>
   </si>
   <si>
     <t xml:space="preserve">9.47464275360107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27415657043457</t>
+    <t xml:space="preserve">9.27415752410889</t>
   </si>
   <si>
     <t xml:space="preserve">9.62985992431641</t>
@@ -2759,16 +2759,16 @@
     <t xml:space="preserve">9.70100021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80447673797607</t>
+    <t xml:space="preserve">9.80447769165039</t>
   </si>
   <si>
     <t xml:space="preserve">10.1343107223511</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1278448104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0696382522583</t>
+    <t xml:space="preserve">10.1278438568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.069637298584</t>
   </si>
   <si>
     <t xml:space="preserve">10.1407785415649</t>
@@ -2777,10 +2777,10 @@
     <t xml:space="preserve">10.0049648284912</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1472463607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35176372528076</t>
+    <t xml:space="preserve">10.1472454071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35176277160645</t>
   </si>
   <si>
     <t xml:space="preserve">9.5522518157959</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">8.89258289337158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40753364562988</t>
+    <t xml:space="preserve">8.40753269195557</t>
   </si>
   <si>
     <t xml:space="preserve">7.9030818939209</t>
@@ -2798,46 +2798,46 @@
     <t xml:space="preserve">6.88124322891235</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61608219146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59667921066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67185211181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93701171875</t>
+    <t xml:space="preserve">6.61608123779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59668064117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67185115814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93701219558716</t>
   </si>
   <si>
     <t xml:space="preserve">5.61364507675171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44549465179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45842838287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43902635574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75592613220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57160758972168</t>
+    <t xml:space="preserve">5.44549512863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45842790603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43902683258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75592565536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57160711288452</t>
   </si>
   <si>
     <t xml:space="preserve">5.84000110626221</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86910533905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9822826385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90790843963623</t>
+    <t xml:space="preserve">5.86910438537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98228311538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90790987014771</t>
   </si>
   <si>
     <t xml:space="preserve">5.66215038299561</t>
@@ -2846,19 +2846,19 @@
     <t xml:space="preserve">5.78826284408569</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75915956497192</t>
+    <t xml:space="preserve">5.75916004180908</t>
   </si>
   <si>
     <t xml:space="preserve">5.70095348358154</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78179550170898</t>
+    <t xml:space="preserve">5.78179597854614</t>
   </si>
   <si>
     <t xml:space="preserve">5.83676815032959</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9693489074707</t>
+    <t xml:space="preserve">5.96934747695923</t>
   </si>
   <si>
     <t xml:space="preserve">5.94671249389648</t>
@@ -2870,22 +2870,22 @@
     <t xml:space="preserve">5.83353471755981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71388912200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76886177062988</t>
+    <t xml:space="preserve">5.71388864517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76886081695557</t>
   </si>
   <si>
     <t xml:space="preserve">5.77532863616943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49723434448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38405466079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51663494110107</t>
+    <t xml:space="preserve">5.49723386764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38405513763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51663446426392</t>
   </si>
   <si>
     <t xml:space="preserve">5.81413316726685</t>
@@ -2894,25 +2894,25 @@
     <t xml:space="preserve">5.93054437637329</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77209520339966</t>
+    <t xml:space="preserve">5.7720947265625</t>
   </si>
   <si>
     <t xml:space="preserve">5.5619068145752</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62011241912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58454179763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47136497497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55867290496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48106527328491</t>
+    <t xml:space="preserve">5.62011194229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5845422744751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47136402130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5586724281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4810643196106</t>
   </si>
   <si>
     <t xml:space="preserve">5.40669059753418</t>
@@ -2921,7 +2921,7 @@
     <t xml:space="preserve">5.32584857940674</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22560596466064</t>
+    <t xml:space="preserve">5.22560548782349</t>
   </si>
   <si>
     <t xml:space="preserve">5.19326877593994</t>
@@ -2939,49 +2939,49 @@
     <t xml:space="preserve">4.70821857452393</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72115278244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97984600067139</t>
+    <t xml:space="preserve">4.72115325927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9798469543457</t>
   </si>
   <si>
     <t xml:space="preserve">5.18033456802368</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33554983139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42932653427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36465263366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40022420883179</t>
+    <t xml:space="preserve">5.33555030822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42932605743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36465358734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40022325515747</t>
   </si>
   <si>
     <t xml:space="preserve">5.72682332992554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94347906112671</t>
+    <t xml:space="preserve">5.94347953796387</t>
   </si>
   <si>
     <t xml:space="preserve">6.25391101837158</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70015621185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28624868392944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09222841262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67508411407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63304710388184</t>
+    <t xml:space="preserve">6.70015716552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28624820709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09222745895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67508506774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63304805755615</t>
   </si>
   <si>
     <t xml:space="preserve">5.78502941131592</t>
@@ -2990,82 +2990,82 @@
     <t xml:space="preserve">5.87880563735962</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8206000328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73329019546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58777570724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5360369682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3969898223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31614780426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37435483932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49399948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52957057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51340055465698</t>
+    <t xml:space="preserve">5.82059955596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73329067230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58777618408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53603744506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39698934555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3161473274231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37435388565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49399852752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52957010269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5134015083313</t>
   </si>
   <si>
     <t xml:space="preserve">5.64598178863525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75269317626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86587142944336</t>
+    <t xml:space="preserve">5.75269269943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86587190628052</t>
   </si>
   <si>
     <t xml:space="preserve">5.80119848251343</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89497423171997</t>
+    <t xml:space="preserve">5.89497470855713</t>
   </si>
   <si>
     <t xml:space="preserve">5.87557220458984</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22804260253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3476881980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39942693710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19570589065552</t>
+    <t xml:space="preserve">6.2280421257019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34768772125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39942741394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1957049369812</t>
   </si>
   <si>
     <t xml:space="preserve">6.05989122390747</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91761016845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77856254577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60717868804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60394430160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8076639175415</t>
+    <t xml:space="preserve">5.91760969161987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77856302261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60717821121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60394477844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80766487121582</t>
   </si>
   <si>
     <t xml:space="preserve">5.81736612319946</t>
@@ -3074,7 +3074,7 @@
     <t xml:space="preserve">5.68478584289551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93377828598022</t>
+    <t xml:space="preserve">5.93377780914307</t>
   </si>
   <si>
     <t xml:space="preserve">5.91114282608032</t>
@@ -3089,22 +3089,22 @@
     <t xml:space="preserve">5.79473114013672</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89820861816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73652458190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74945974349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79796504974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6395149230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59101009368896</t>
+    <t xml:space="preserve">5.89820718765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73652362823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7494592666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79796409606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63951444625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59100961685181</t>
   </si>
   <si>
     <t xml:space="preserve">5.58130884170532</t>
@@ -3113,52 +3113,52 @@
     <t xml:space="preserve">5.70418834686279</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70742082595825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66538381576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69448757171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88203954696655</t>
+    <t xml:space="preserve">5.70742225646973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66538429260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69448661804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88203907012939</t>
   </si>
   <si>
     <t xml:space="preserve">5.80443143844604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71065473556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50693511962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39052295684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33878374099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43255949020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30321359634399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31938123703003</t>
+    <t xml:space="preserve">5.7106556892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50693416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39052248001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33878326416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43255996704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30321264266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31938171386719</t>
   </si>
   <si>
     <t xml:space="preserve">5.21267080307007</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21590423583984</t>
+    <t xml:space="preserve">5.21590375900269</t>
   </si>
   <si>
     <t xml:space="preserve">5.22883892059326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34201717376709</t>
+    <t xml:space="preserve">5.34201765060425</t>
   </si>
   <si>
     <t xml:space="preserve">5.26764297485352</t>
@@ -3167,19 +3167,19 @@
     <t xml:space="preserve">5.32261514663696</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29997968673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21913719177246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0736231803894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12212800979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07685613632202</t>
+    <t xml:space="preserve">5.29998016357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21913766860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07362270355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12212896347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07685708999634</t>
   </si>
   <si>
     <t xml:space="preserve">5.07038927078247</t>
@@ -3188,10 +3188,10 @@
     <t xml:space="preserve">5.10919332504272</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20296955108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0412859916687</t>
+    <t xml:space="preserve">5.20297002792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04128646850586</t>
   </si>
   <si>
     <t xml:space="preserve">4.9960150718689</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">4.8149299621582</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82463073730469</t>
+    <t xml:space="preserve">4.82463026046753</t>
   </si>
   <si>
     <t xml:space="preserve">4.50773143768311</t>
@@ -3218,130 +3218,130 @@
     <t xml:space="preserve">4.58857250213623</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78259229660034</t>
+    <t xml:space="preserve">4.78259325027466</t>
   </si>
   <si>
     <t xml:space="preserve">4.89900493621826</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82786417007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79229402542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13829660415649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14799737930298</t>
+    <t xml:space="preserve">4.82786512374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7922945022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13829612731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14799690246582</t>
   </si>
   <si>
     <t xml:space="preserve">5.25794219970703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23530673980713</t>
+    <t xml:space="preserve">5.23530626296997</t>
   </si>
   <si>
     <t xml:space="preserve">5.65891647338867</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8432354927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85940361022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07606029510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0081524848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97904872894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98875093460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90467500686646</t>
+    <t xml:space="preserve">5.84323596954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85940408706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07605934143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00815343856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97904920578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98875045776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90467548370361</t>
   </si>
   <si>
     <t xml:space="preserve">6.17630338668823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29918241500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31858491897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34445381164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2183403968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19247198104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13103151321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0566577911377</t>
+    <t xml:space="preserve">6.2991828918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31858539581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34445428848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21833992004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19247102737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13103246688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05665731430054</t>
   </si>
   <si>
     <t xml:space="preserve">6.10516262054443</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10192918777466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04049015045166</t>
+    <t xml:space="preserve">6.10193014144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0404896736145</t>
   </si>
   <si>
     <t xml:space="preserve">6.03725528717041</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06635856628418</t>
+    <t xml:space="preserve">6.06635904312134</t>
   </si>
   <si>
     <t xml:space="preserve">5.88850688934326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95318031311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99198436737061</t>
+    <t xml:space="preserve">5.95317983627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99198532104492</t>
   </si>
   <si>
     <t xml:space="preserve">5.9855170249939</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02432012557983</t>
+    <t xml:space="preserve">6.02432107925415</t>
   </si>
   <si>
     <t xml:space="preserve">6.01138591766357</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97258234024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73005676269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73975801467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64921522140503</t>
+    <t xml:space="preserve">5.97258281707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73005771636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73975849151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64921474456787</t>
   </si>
   <si>
     <t xml:space="preserve">5.55543947219849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36788654327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46812963485718</t>
+    <t xml:space="preserve">5.36788702011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46813106536865</t>
   </si>
   <si>
     <t xml:space="preserve">5.41639184951782</t>
@@ -3350,10 +3350,10 @@
     <t xml:space="preserve">5.72359085083008</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07282638549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26037883758545</t>
+    <t xml:space="preserve">6.07282590866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26037931442261</t>
   </si>
   <si>
     <t xml:space="preserve">6.39619255065918</t>
@@ -3362,43 +3362,43 @@
     <t xml:space="preserve">6.75836372375488</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67428779602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7518949508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6678204536438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66135358810425</t>
+    <t xml:space="preserve">6.67428731918335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75189447402954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66782093048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66135311126709</t>
   </si>
   <si>
     <t xml:space="preserve">6.58374547958374</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64195156097412</t>
+    <t xml:space="preserve">6.64195203781128</t>
   </si>
   <si>
     <t xml:space="preserve">6.69369029998779</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90064382553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80363464355469</t>
+    <t xml:space="preserve">6.90064525604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80363512039185</t>
   </si>
   <si>
     <t xml:space="preserve">6.97178554534912</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83597135543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85537385940552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7842321395874</t>
+    <t xml:space="preserve">6.83597087860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85537338256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78423309326172</t>
   </si>
   <si>
     <t xml:space="preserve">7.21107578277588</t>
@@ -3410,43 +3410,43 @@
     <t xml:space="preserve">7.23694610595703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42449903488159</t>
+    <t xml:space="preserve">7.42449855804443</t>
   </si>
   <si>
     <t xml:space="preserve">7.48270320892334</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39216184616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41156339645386</t>
+    <t xml:space="preserve">7.39216232299805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41156244277954</t>
   </si>
   <si>
     <t xml:space="preserve">7.16580533981323</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1981406211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24988079071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35335874557495</t>
+    <t xml:space="preserve">7.19814252853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24987936019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35335826873779</t>
   </si>
   <si>
     <t xml:space="preserve">7.36629247665405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27575016021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32102108001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34689140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15287160873413</t>
+    <t xml:space="preserve">7.27574968338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32102012634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34689044952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15287017822266</t>
   </si>
   <si>
     <t xml:space="preserve">7.49563932418823</t>
@@ -3461,43 +3461,43 @@
     <t xml:space="preserve">7.3598256111145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08172988891602</t>
+    <t xml:space="preserve">7.08173036575317</t>
   </si>
   <si>
     <t xml:space="preserve">7.26928234100342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46330213546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51504039764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46977043151855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44390058517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47623777389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52797698974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9548192024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69612646102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11650371551514</t>
+    <t xml:space="preserve">7.46330261230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51504135131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4697699546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44390106201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47623825073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52797555923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95482015609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69612503051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11650276184082</t>
   </si>
   <si>
     <t xml:space="preserve">8.43986988067627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46574020385742</t>
+    <t xml:space="preserve">8.46573925018311</t>
   </si>
   <si>
     <t xml:space="preserve">8.40106582641602</t>
@@ -3506,31 +3506,31 @@
     <t xml:space="preserve">8.25878429412842</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18764495849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05183029174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22644710540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31052303314209</t>
+    <t xml:space="preserve">8.18764305114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05182933807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22644805908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31052398681641</t>
   </si>
   <si>
     <t xml:space="preserve">8.34932708740234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42046737670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38166427612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50454235076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14883995056152</t>
+    <t xml:space="preserve">8.4204683303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38166332244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50454330444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14884090423584</t>
   </si>
   <si>
     <t xml:space="preserve">9.01546287536621</t>
@@ -3542,22 +3542,22 @@
     <t xml:space="preserve">8.64682483673096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59508514404297</t>
+    <t xml:space="preserve">8.59508609771729</t>
   </si>
   <si>
     <t xml:space="preserve">8.51101016998291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29112243652344</t>
+    <t xml:space="preserve">8.29112148284912</t>
   </si>
   <si>
     <t xml:space="preserve">8.78910636901855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2329158782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35579490661621</t>
+    <t xml:space="preserve">8.23291492462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35579586029053</t>
   </si>
   <si>
     <t xml:space="preserve">8.96372413635254</t>
@@ -3566,97 +3566,97 @@
     <t xml:space="preserve">8.98312664031982</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98959350585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07366752624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00252723693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99606132507324</t>
+    <t xml:space="preserve">8.98959255218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07366847991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00252819061279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99606037139893</t>
   </si>
   <si>
     <t xml:space="preserve">9.06720161437988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19654750823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46817588806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42290496826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37763404846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3905668258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46170902252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20948219299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3646993637085</t>
+    <t xml:space="preserve">9.19654846191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46817684173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4229040145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3776330947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39056777954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46170806884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20948314666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36469841003418</t>
   </si>
   <si>
     <t xml:space="preserve">9.49404525756836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48111152648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56518459320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81094455718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0437688827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0890398025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3283309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4059391021729</t>
+    <t xml:space="preserve">9.48110961914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56518650054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81094360351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0437679290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0890407562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.328330039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4059400558472</t>
   </si>
   <si>
     <t xml:space="preserve">10.4447431564331</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2442560195923</t>
+    <t xml:space="preserve">10.2442579269409</t>
   </si>
   <si>
     <t xml:space="preserve">10.7616415023804</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8263149261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1173458099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5611562728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9685955047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5934915542603</t>
+    <t xml:space="preserve">10.8263158798218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1173448562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5611543655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9685974121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5934906005859</t>
   </si>
   <si>
     <t xml:space="preserve">10.8133811950684</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6775674819946</t>
+    <t xml:space="preserve">10.6775665283203</t>
   </si>
   <si>
     <t xml:space="preserve">10.6581649780273</t>
@@ -3665,7 +3665,7 @@
     <t xml:space="preserve">10.8198480606079</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6840343475342</t>
+    <t xml:space="preserve">10.6840353012085</t>
   </si>
   <si>
     <t xml:space="preserve">11.0074014663696</t>
@@ -3680,10 +3680,10 @@
     <t xml:space="preserve">11.2291116714478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0908231735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9110441207886</t>
+    <t xml:space="preserve">11.0908212661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9110450744629</t>
   </si>
   <si>
     <t xml:space="preserve">11.0078477859497</t>
@@ -3692,106 +3692,106 @@
     <t xml:space="preserve">11.1046514511108</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0424194335938</t>
+    <t xml:space="preserve">11.0424203872681</t>
   </si>
   <si>
     <t xml:space="preserve">11.0562496185303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1945400238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3051700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.505690574646</t>
+    <t xml:space="preserve">11.1945390701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3051719665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5056896209717</t>
   </si>
   <si>
     <t xml:space="preserve">11.5748357772827</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5955781936646</t>
+    <t xml:space="preserve">11.5955791473389</t>
   </si>
   <si>
     <t xml:space="preserve">11.6854667663574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6508932113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4780321121216</t>
+    <t xml:space="preserve">11.6508951187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4780330657959</t>
   </si>
   <si>
     <t xml:space="preserve">11.7131261825562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6923799514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6301507949829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5402641296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2636852264404</t>
+    <t xml:space="preserve">11.6923828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6301498413086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.54026222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2636842727661</t>
   </si>
   <si>
     <t xml:space="preserve">11.1392240524292</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8280715942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9456186294556</t>
+    <t xml:space="preserve">10.828070640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9456167221069</t>
   </si>
   <si>
     <t xml:space="preserve">10.55149269104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5100059509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4961776733398</t>
+    <t xml:space="preserve">10.5100049972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4961767196655</t>
   </si>
   <si>
     <t xml:space="preserve">9.97067642211914</t>
   </si>
   <si>
-    <t xml:space="preserve">10.10205078125</t>
+    <t xml:space="preserve">10.1020517349243</t>
   </si>
   <si>
     <t xml:space="preserve">10.2057685852051</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6828680038452</t>
+    <t xml:space="preserve">10.6828670501709</t>
   </si>
   <si>
     <t xml:space="preserve">10.5445785522461</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4616050720215</t>
+    <t xml:space="preserve">10.4616041183472</t>
   </si>
   <si>
     <t xml:space="preserve">10.8419008255005</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9940195083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8764734268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9663591384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9179611206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8211584091187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5653200149536</t>
+    <t xml:space="preserve">10.9940185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8764724731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9663600921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9179592132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8211574554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5653209686279</t>
   </si>
   <si>
     <t xml:space="preserve">10.7381830215454</t>
@@ -3806,13 +3806,13 @@
     <t xml:space="preserve">11.7546119689941</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8030138015747</t>
+    <t xml:space="preserve">11.8030128479004</t>
   </si>
   <si>
     <t xml:space="preserve">12.0934209823608</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2317123413086</t>
+    <t xml:space="preserve">12.23171043396</t>
   </si>
   <si>
     <t xml:space="preserve">12.1487369537354</t>
@@ -3824,16 +3824,16 @@
     <t xml:space="preserve">12.1210803985596</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0795917510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2593679428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.418399810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4737186431885</t>
+    <t xml:space="preserve">12.0795907974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2593669891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4184007644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4737176895142</t>
   </si>
   <si>
     <t xml:space="preserve">12.605092048645</t>
@@ -3842,76 +3842,76 @@
     <t xml:space="preserve">12.7572116851807</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3285121917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2870273590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6880664825439</t>
+    <t xml:space="preserve">12.3285140991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2870283126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6880655288696</t>
   </si>
   <si>
     <t xml:space="preserve">12.5705194473267</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8514127731323</t>
+    <t xml:space="preserve">11.851414680481</t>
   </si>
   <si>
     <t xml:space="preserve">12.2455387115479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3561716079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3769130706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2662839889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2040510177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6396636962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4806308746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3907451629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7364664077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2757968902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1885089874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3129692077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9352722167969</t>
+    <t xml:space="preserve">12.3561725616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.376914024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2662811279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2040538787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6396646499634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4806318283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3907442092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7364673614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2757978439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1885080337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3129682540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9352703094482</t>
   </si>
   <si>
     <t xml:space="preserve">14.9905872344971</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7554950714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7969799041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9672431945801</t>
+    <t xml:space="preserve">14.7554960250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7969808578491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9672451019287</t>
   </si>
   <si>
     <t xml:space="preserve">13.6215209960938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6811504364014</t>
+    <t xml:space="preserve">12.68115234375</t>
   </si>
   <si>
     <t xml:space="preserve">13.3380279541016</t>
@@ -3920,13 +3920,13 @@
     <t xml:space="preserve">13.0960206985474</t>
   </si>
   <si>
-    <t xml:space="preserve">12.335428237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5774345397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3492565155029</t>
+    <t xml:space="preserve">12.3354272842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5774335861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3492574691772</t>
   </si>
   <si>
     <t xml:space="preserve">11.2498550415039</t>
@@ -3938,76 +3938,76 @@
     <t xml:space="preserve">11.7615261077881</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0285921096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3674011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8652439117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1694784164429</t>
+    <t xml:space="preserve">11.0285911560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3674001693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8652429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1694803237915</t>
   </si>
   <si>
     <t xml:space="preserve">12.8056116104126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.715723991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7433824539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.061448097229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9992160797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8885860443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0337905883789</t>
+    <t xml:space="preserve">12.7157230377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7433815002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0614461898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9992170333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8885879516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0337915420532</t>
   </si>
   <si>
     <t xml:space="preserve">13.0683612823486</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9093294143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.019962310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2731962203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6465797424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.494460105896</t>
+    <t xml:space="preserve">12.9093284606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0199604034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2731971740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6465787887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4944610595703</t>
   </si>
   <si>
     <t xml:space="preserve">12.5428628921509</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2524538040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5566911697388</t>
+    <t xml:space="preserve">12.2524547576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5566921234131</t>
   </si>
   <si>
     <t xml:space="preserve">11.955132484436</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0865068435669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9205598831177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3466577529907</t>
+    <t xml:space="preserve">12.0865077972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9205589294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3466567993164</t>
   </si>
   <si>
     <t xml:space="preserve">11.5817499160767</t>
@@ -4016,16 +4016,16 @@
     <t xml:space="preserve">12.0242767333984</t>
   </si>
   <si>
-    <t xml:space="preserve">12.300856590271</t>
+    <t xml:space="preserve">12.3008556365967</t>
   </si>
   <si>
     <t xml:space="preserve">12.0381050109863</t>
   </si>
   <si>
-    <t xml:space="preserve">12.579309463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5939340591431</t>
+    <t xml:space="preserve">12.5793085098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5939350128174</t>
   </si>
   <si>
     <t xml:space="preserve">12.5207996368408</t>
@@ -4034,13 +4034,13 @@
     <t xml:space="preserve">12.769458770752</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6743841171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.747519493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4184093475342</t>
+    <t xml:space="preserve">12.6743850708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7475204467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4184083938599</t>
   </si>
   <si>
     <t xml:space="preserve">12.3964691162109</t>
@@ -4049,40 +4049,40 @@
     <t xml:space="preserve">12.3745288848877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3452730178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3525876998901</t>
+    <t xml:space="preserve">12.3452739715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3525867462158</t>
   </si>
   <si>
     <t xml:space="preserve">12.140495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9795961380005</t>
+    <t xml:space="preserve">11.9795951843262</t>
   </si>
   <si>
     <t xml:space="preserve">11.7455625534058</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0434617996216</t>
+    <t xml:space="preserve">11.0434627532959</t>
   </si>
   <si>
     <t xml:space="preserve">10.4803190231323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5900211334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9630136489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4583778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4437503814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6777839660645</t>
+    <t xml:space="preserve">10.5900220870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9630126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4583787918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.443751335144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6777849197388</t>
   </si>
   <si>
     <t xml:space="preserve">10.5095720291138</t>
@@ -4103,31 +4103,31 @@
     <t xml:space="preserve">10.3998699188232</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2097187042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88060855865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75627708435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70508098602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31014919281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23701572418213</t>
+    <t xml:space="preserve">10.2097177505493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88060760498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7562780380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70508193969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31015014648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23701477050781</t>
   </si>
   <si>
     <t xml:space="preserve">9.43448066711426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69776916503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41254138946533</t>
+    <t xml:space="preserve">9.69776821136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41254043579102</t>
   </si>
   <si>
     <t xml:space="preserve">9.46373462677002</t>
@@ -4136,37 +4136,37 @@
     <t xml:space="preserve">9.06148910522461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62267780303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82745552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97372722625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20776081085205</t>
+    <t xml:space="preserve">8.62267684936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8274564743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97372817993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20776176452637</t>
   </si>
   <si>
     <t xml:space="preserve">9.24432849884033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18582153320312</t>
+    <t xml:space="preserve">9.18582057952881</t>
   </si>
   <si>
     <t xml:space="preserve">9.25895500183105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53687000274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21507453918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3686580657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39791297912598</t>
+    <t xml:space="preserve">9.5368709564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21507549285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36865901947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39791393280029</t>
   </si>
   <si>
     <t xml:space="preserve">9.5807523727417</t>
@@ -4184,16 +4184,16 @@
     <t xml:space="preserve">10.0195655822754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98299598693848</t>
+    <t xml:space="preserve">9.98299694061279</t>
   </si>
   <si>
     <t xml:space="preserve">9.72702217102051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47104835510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57343864440918</t>
+    <t xml:space="preserve">9.47104930877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57343769073486</t>
   </si>
   <si>
     <t xml:space="preserve">9.80747222900391</t>
@@ -4202,22 +4202,22 @@
     <t xml:space="preserve">9.97568416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49298858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10537052154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22238731384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20044612884521</t>
+    <t xml:space="preserve">9.4929895401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10537147521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22238826751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20044708251953</t>
   </si>
   <si>
     <t xml:space="preserve">9.06880283355713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.820143699646</t>
+    <t xml:space="preserve">8.82014274597168</t>
   </si>
   <si>
     <t xml:space="preserve">8.75432109832764</t>
@@ -4241,19 +4241,19 @@
     <t xml:space="preserve">8.40327072143555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27893829345703</t>
+    <t xml:space="preserve">8.27893924713135</t>
   </si>
   <si>
     <t xml:space="preserve">8.35207557678223</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54222774505615</t>
+    <t xml:space="preserve">8.54222869873047</t>
   </si>
   <si>
     <t xml:space="preserve">9.01760864257812</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02492332458496</t>
+    <t xml:space="preserve">9.02492237091064</t>
   </si>
   <si>
     <t xml:space="preserve">9.14925289154053</t>
@@ -4262,19 +4262,19 @@
     <t xml:space="preserve">8.94447231292725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89327812194824</t>
+    <t xml:space="preserve">8.89327716827393</t>
   </si>
   <si>
     <t xml:space="preserve">8.59342288970947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63730335235596</t>
+    <t xml:space="preserve">8.63730430603027</t>
   </si>
   <si>
     <t xml:space="preserve">8.34476184844971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35939025878906</t>
+    <t xml:space="preserve">8.35938835144043</t>
   </si>
   <si>
     <t xml:space="preserve">8.22043037414551</t>
@@ -4283,16 +4283,16 @@
     <t xml:space="preserve">8.13266849517822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86938142776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32282066345215</t>
+    <t xml:space="preserve">7.86938095092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32282161712646</t>
   </si>
   <si>
     <t xml:space="preserve">8.41789722442627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33013534545898</t>
+    <t xml:space="preserve">8.33013439178467</t>
   </si>
   <si>
     <t xml:space="preserve">8.24237251281738</t>
@@ -4301,16 +4301,16 @@
     <t xml:space="preserve">8.14729595184326</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07415962219238</t>
+    <t xml:space="preserve">8.07416152954102</t>
   </si>
   <si>
     <t xml:space="preserve">8.16192245483398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04490566253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05221843719482</t>
+    <t xml:space="preserve">8.04490661621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05221939086914</t>
   </si>
   <si>
     <t xml:space="preserve">8.28625392913818</t>
@@ -4325,7 +4325,7 @@
     <t xml:space="preserve">8.38864231109619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48371887207031</t>
+    <t xml:space="preserve">8.48371982574463</t>
   </si>
   <si>
     <t xml:space="preserve">8.56416893005371</t>
@@ -4334,7 +4334,7 @@
     <t xml:space="preserve">8.71775245666504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88596343994141</t>
+    <t xml:space="preserve">8.88596534729004</t>
   </si>
   <si>
     <t xml:space="preserve">8.922532081604</t>
@@ -4343,22 +4343,22 @@
     <t xml:space="preserve">9.56612491607666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52955627441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84403991699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0488195419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1804637908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1512088775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1146402359009</t>
+    <t xml:space="preserve">9.52955722808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84403896331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0488185882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1804628372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1512079238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1146421432495</t>
   </si>
   <si>
     <t xml:space="preserve">10.0049381256104</t>
@@ -4376,19 +4376,19 @@
     <t xml:space="preserve">10.3104362487793</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3261775970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3576593399048</t>
+    <t xml:space="preserve">10.3261766433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3576583862305</t>
   </si>
   <si>
     <t xml:space="preserve">10.3497886657715</t>
   </si>
   <si>
-    <t xml:space="preserve">10.389142036438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2553415298462</t>
+    <t xml:space="preserve">10.3891410827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2553424835205</t>
   </si>
   <si>
     <t xml:space="preserve">10.2710838317871</t>
@@ -4397,10 +4397,10 @@
     <t xml:space="preserve">10.2002477645874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.04283618927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86968421936035</t>
+    <t xml:space="preserve">10.0428380966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86968517303467</t>
   </si>
   <si>
     <t xml:space="preserve">9.88542556762695</t>
@@ -4409,34 +4409,34 @@
     <t xml:space="preserve">10.0507068634033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96413040161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1608953475952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1845073699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0034847259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0900602340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5229406356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3419170379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4521055221558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3812704086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4678478240967</t>
+    <t xml:space="preserve">9.96413135528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1608943939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1845064163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0034837722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0900611877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5229415893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3419179916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4521064758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3812713623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4678468704224</t>
   </si>
   <si>
     <t xml:space="preserve">10.47571849823</t>
@@ -4445,13 +4445,13 @@
     <t xml:space="preserve">10.5780344009399</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7433156967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0030450820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0345268249512</t>
+    <t xml:space="preserve">10.7433166503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.003044128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0345277786255</t>
   </si>
   <si>
     <t xml:space="preserve">11.0423974990845</t>
@@ -4460,7 +4460,7 @@
     <t xml:space="preserve">11.1998090744019</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2234210968018</t>
+    <t xml:space="preserve">11.2234201431274</t>
   </si>
   <si>
     <t xml:space="preserve">11.2863855361938</t>
@@ -4472,13 +4472,13 @@
     <t xml:space="preserve">11.3493499755859</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3414783477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3099975585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1919384002686</t>
+    <t xml:space="preserve">11.3414793014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3099966049194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1919393539429</t>
   </si>
   <si>
     <t xml:space="preserve">11.412314414978</t>
@@ -4487,46 +4487,46 @@
     <t xml:space="preserve">11.3965730667114</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2155504226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4280557632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4752798080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8294544219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0813131332397</t>
+    <t xml:space="preserve">11.2155513763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4280567169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4752788543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8294534683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0813121795654</t>
   </si>
   <si>
     <t xml:space="preserve">12.1678886413574</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3725233078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3095598220825</t>
+    <t xml:space="preserve">12.372522354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3095588684082</t>
   </si>
   <si>
     <t xml:space="preserve">12.4040050506592</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5220642089844</t>
+    <t xml:space="preserve">12.5220632553101</t>
   </si>
   <si>
     <t xml:space="preserve">12.5141925811768</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7266979217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8368864059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8132743835449</t>
+    <t xml:space="preserve">12.7266988754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8368854522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8132753372192</t>
   </si>
   <si>
     <t xml:space="preserve">12.537805557251</t>
@@ -4535,31 +4535,31 @@
     <t xml:space="preserve">12.3882637023926</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9077205657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7345685958862</t>
+    <t xml:space="preserve">12.9077215194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7345695495605</t>
   </si>
   <si>
     <t xml:space="preserve">12.5063228607178</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2465934753418</t>
+    <t xml:space="preserve">12.2465944290161</t>
   </si>
   <si>
     <t xml:space="preserve">12.1049242019653</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2702054977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2308540344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3016872406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3252992630005</t>
+    <t xml:space="preserve">12.270206451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2308530807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3016881942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3253002166748</t>
   </si>
   <si>
     <t xml:space="preserve">11.9160308837891</t>
@@ -4574,16 +4574,16 @@
     <t xml:space="preserve">11.1132326126099</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1289739608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0974922180176</t>
+    <t xml:space="preserve">11.1289749145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0974912643433</t>
   </si>
   <si>
     <t xml:space="preserve">11.0266571044922</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8062810897827</t>
+    <t xml:space="preserve">10.8062801361084</t>
   </si>
   <si>
     <t xml:space="preserve">10.8456344604492</t>
@@ -4598,22 +4598,22 @@
     <t xml:space="preserve">10.9951753616333</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9873056411743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9085988998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0581388473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.176197052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.585467338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5225019454956</t>
+    <t xml:space="preserve">10.9873037338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.908597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0581398010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1761980056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5854663848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5225028991699</t>
   </si>
   <si>
     <t xml:space="preserve">11.7743606567383</t>
@@ -4622,16 +4622,16 @@
     <t xml:space="preserve">11.8766775131226</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8137121200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9947366714478</t>
+    <t xml:space="preserve">11.8137130737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9947357177734</t>
   </si>
   <si>
     <t xml:space="preserve">12.1285352706909</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9632539749146</t>
+    <t xml:space="preserve">11.9632530212402</t>
   </si>
   <si>
     <t xml:space="preserve">11.9002885818481</t>
@@ -4640,13 +4640,13 @@
     <t xml:space="preserve">11.9789953231812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5697250366211</t>
+    <t xml:space="preserve">11.5697259902954</t>
   </si>
   <si>
     <t xml:space="preserve">11.6012077331543</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8058423995972</t>
+    <t xml:space="preserve">11.8058433532715</t>
   </si>
   <si>
     <t xml:space="preserve">11.9317722320557</t>
@@ -4655,22 +4655,22 @@
     <t xml:space="preserve">11.3257389068604</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3572216033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.333607673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.912278175354</t>
+    <t xml:space="preserve">11.3572206497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3336086273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9122791290283</t>
   </si>
   <si>
     <t xml:space="preserve">11.8475370407104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6614074707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6290378570557</t>
+    <t xml:space="preserve">11.6614084243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.62903881073</t>
   </si>
   <si>
     <t xml:space="preserve">11.807074546814</t>
@@ -4688,22 +4688,22 @@
     <t xml:space="preserve">11.5076484680176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6371307373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5319271087646</t>
+    <t xml:space="preserve">11.637131690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5319261550903</t>
   </si>
   <si>
     <t xml:space="preserve">11.5966672897339</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5885744094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5400190353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4429082870483</t>
+    <t xml:space="preserve">11.5885734558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5400199890137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4429092407227</t>
   </si>
   <si>
     <t xml:space="preserve">11.3862600326538</t>
@@ -4715,7 +4715,7 @@
     <t xml:space="preserve">11.4671869277954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4186305999756</t>
+    <t xml:space="preserve">11.4186296463013</t>
   </si>
   <si>
     <t xml:space="preserve">11.3781681060791</t>
@@ -4724,34 +4724,34 @@
     <t xml:space="preserve">11.3700752258301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723886489868</t>
+    <t xml:space="preserve">11.5723896026611</t>
   </si>
   <si>
     <t xml:space="preserve">11.3943529129028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4510011672974</t>
+    <t xml:space="preserve">11.451000213623</t>
   </si>
   <si>
     <t xml:space="preserve">11.6047601699829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6533145904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6209449768066</t>
+    <t xml:space="preserve">11.6533155441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6209440231323</t>
   </si>
   <si>
     <t xml:space="preserve">11.8637228012085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9770193099976</t>
+    <t xml:space="preserve">11.9770183563232</t>
   </si>
   <si>
     <t xml:space="preserve">11.993203163147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.823260307312</t>
+    <t xml:space="preserve">11.8232593536377</t>
   </si>
   <si>
     <t xml:space="preserve">11.9446496963501</t>
@@ -4763,13 +4763,13 @@
     <t xml:space="preserve">11.9365558624268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0903148651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1712408065796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2521667480469</t>
+    <t xml:space="preserve">12.090313911438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1712417602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2521677017212</t>
   </si>
   <si>
     <t xml:space="preserve">12.4221115112305</t>
@@ -4784,7 +4784,7 @@
     <t xml:space="preserve">12.3249988555908</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3007221221924</t>
+    <t xml:space="preserve">12.3007211685181</t>
   </si>
   <si>
     <t xml:space="preserve">12.4140186309814</t>
@@ -4805,7 +4805,7 @@
     <t xml:space="preserve">12.5354070663452</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6163320541382</t>
+    <t xml:space="preserve">12.6163330078125</t>
   </si>
   <si>
     <t xml:space="preserve">13.1909055709839</t>
@@ -4826,7 +4826,7 @@
     <t xml:space="preserve">13.0290546417236</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0937948226929</t>
+    <t xml:space="preserve">13.0937957763672</t>
   </si>
   <si>
     <t xml:space="preserve">13.1989984512329</t>
@@ -4835,22 +4835,22 @@
     <t xml:space="preserve">12.9076652526855</t>
   </si>
   <si>
-    <t xml:space="preserve">12.851016998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9885902404785</t>
+    <t xml:space="preserve">12.8510179519653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9885892868042</t>
   </si>
   <si>
     <t xml:space="preserve">12.9238510131836</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0452404022217</t>
+    <t xml:space="preserve">13.0452394485474</t>
   </si>
   <si>
     <t xml:space="preserve">13.0776090621948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1747207641602</t>
+    <t xml:space="preserve">13.1747217178345</t>
   </si>
   <si>
     <t xml:space="preserve">13.1666288375854</t>
@@ -4859,16 +4859,16 @@
     <t xml:space="preserve">12.9724073410034</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9319429397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6810722351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.567777633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.478759765625</t>
+    <t xml:space="preserve">12.931941986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6810731887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5677766799927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4787588119507</t>
   </si>
   <si>
     <t xml:space="preserve">12.75390625</t>
@@ -4880,7 +4880,7 @@
     <t xml:space="preserve">12.5839624404907</t>
   </si>
   <si>
-    <t xml:space="preserve">12.575870513916</t>
+    <t xml:space="preserve">12.5758695602417</t>
   </si>
   <si>
     <t xml:space="preserve">12.6729803085327</t>
@@ -4889,7 +4889,7 @@
     <t xml:space="preserve">12.7943696975708</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8752956390381</t>
+    <t xml:space="preserve">12.8752946853638</t>
   </si>
   <si>
     <t xml:space="preserve">13.0209617614746</t>
@@ -4898,7 +4898,7 @@
     <t xml:space="preserve">13.0371475219727</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2475547790527</t>
+    <t xml:space="preserve">13.2475538253784</t>
   </si>
   <si>
     <t xml:space="preserve">12.9400358200073</t>
@@ -4919,7 +4919,7 @@
     <t xml:space="preserve">13.2880172729492</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3203859329224</t>
+    <t xml:space="preserve">13.3203868865967</t>
   </si>
   <si>
     <t xml:space="preserve">13.3042011260986</t>
@@ -4937,7 +4937,7 @@
     <t xml:space="preserve">12.4544811248779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8995723724365</t>
+    <t xml:space="preserve">12.8995733261108</t>
   </si>
   <si>
     <t xml:space="preserve">13.0533313751221</t>
@@ -4946,7 +4946,7 @@
     <t xml:space="preserve">13.2151832580566</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5388851165771</t>
+    <t xml:space="preserve">13.5388870239258</t>
   </si>
   <si>
     <t xml:space="preserve">13.4174976348877</t>
@@ -4967,10 +4967,10 @@
     <t xml:space="preserve">13.9435157775879</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8140354156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7573881149292</t>
+    <t xml:space="preserve">13.8140335083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7573871612549</t>
   </si>
   <si>
     <t xml:space="preserve">13.9597015380859</t>
@@ -4988,13 +4988,13 @@
     <t xml:space="preserve">13.69007396698</t>
   </si>
   <si>
-    <t xml:space="preserve">13.750958442688</t>
+    <t xml:space="preserve">13.7509574890137</t>
   </si>
   <si>
     <t xml:space="preserve">13.4900283813477</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5248203277588</t>
+    <t xml:space="preserve">13.5248193740845</t>
   </si>
   <si>
     <t xml:space="preserve">13.6987714767456</t>
@@ -5012,7 +5012,7 @@
     <t xml:space="preserve">13.7857484817505</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7770509719849</t>
+    <t xml:space="preserve">13.7770500183105</t>
   </si>
   <si>
     <t xml:space="preserve">13.8205394744873</t>
@@ -5021,7 +5021,7 @@
     <t xml:space="preserve">14.1336545944214</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9683990478516</t>
+    <t xml:space="preserve">13.9683980941772</t>
   </si>
   <si>
     <t xml:space="preserve">13.8466329574585</t>
@@ -5036,28 +5036,28 @@
     <t xml:space="preserve">13.7335624694824</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7944450378418</t>
+    <t xml:space="preserve">13.7944459915161</t>
   </si>
   <si>
     <t xml:space="preserve">13.8118419647217</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9336080551147</t>
+    <t xml:space="preserve">13.9336090087891</t>
   </si>
   <si>
     <t xml:space="preserve">14.342396736145</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0379791259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.011887550354</t>
+    <t xml:space="preserve">14.0379781723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0118865966797</t>
   </si>
   <si>
     <t xml:space="preserve">13.5161218643188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6204929351807</t>
+    <t xml:space="preserve">13.620493888855</t>
   </si>
   <si>
     <t xml:space="preserve">13.6291913986206</t>
@@ -5078,10 +5078,10 @@
     <t xml:space="preserve">13.8031435012817</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0466766357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0640716552734</t>
+    <t xml:space="preserve">14.0466775894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0640726089478</t>
   </si>
   <si>
     <t xml:space="preserve">14.2641172409058</t>
@@ -5102,10 +5102,10 @@
     <t xml:space="preserve">14.2815132141113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3076076507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3858852386475</t>
+    <t xml:space="preserve">14.3076066970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3858861923218</t>
   </si>
   <si>
     <t xml:space="preserve">14.6033267974854</t>
@@ -5117,22 +5117,22 @@
     <t xml:space="preserve">14.7598829269409</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9686250686646</t>
+    <t xml:space="preserve">14.9686260223389</t>
   </si>
   <si>
     <t xml:space="preserve">14.8294630050659</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6989994049072</t>
+    <t xml:space="preserve">14.6990003585815</t>
   </si>
   <si>
     <t xml:space="preserve">14.6207208633423</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7337913513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7076969146729</t>
+    <t xml:space="preserve">14.7337923049927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7076978683472</t>
   </si>
   <si>
     <t xml:space="preserve">14.6903018951416</t>
@@ -5141,10 +5141,10 @@
     <t xml:space="preserve">14.8990440368652</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8381605148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7511854171753</t>
+    <t xml:space="preserve">14.8381624221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7511863708496</t>
   </si>
   <si>
     <t xml:space="preserve">14.7250938415527</t>
@@ -5156,10 +5156,10 @@
     <t xml:space="preserve">15.0121154785156</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0816965103149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1164865493774</t>
+    <t xml:space="preserve">15.0816955566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1164846420288</t>
   </si>
   <si>
     <t xml:space="preserve">15.4469966888428</t>
@@ -5183,7 +5183,7 @@
     <t xml:space="preserve">16.1341094970703</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9253664016724</t>
+    <t xml:space="preserve">15.9253644943237</t>
   </si>
   <si>
     <t xml:space="preserve">16.0471343994141</t>
@@ -5192,10 +5192,10 @@
     <t xml:space="preserve">16.6124801635742</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2995910644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.916898727417</t>
+    <t xml:space="preserve">17.2995929718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9168968200684</t>
   </si>
   <si>
     <t xml:space="preserve">16.9951763153076</t>
@@ -5207,10 +5207,10 @@
     <t xml:space="preserve">17.1952209472656</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4126605987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7083835601807</t>
+    <t xml:space="preserve">17.4126625061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.708381652832</t>
   </si>
   <si>
     <t xml:space="preserve">17.6561946868896</t>
@@ -5222,10 +5222,10 @@
     <t xml:space="preserve">18.038890838623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8127517700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3172149658203</t>
+    <t xml:space="preserve">17.8127536773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3172168731689</t>
   </si>
   <si>
     <t xml:space="preserve">18.2128448486328</t>
@@ -5234,10 +5234,10 @@
     <t xml:space="preserve">18.4041919708252</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3346099853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5433521270752</t>
+    <t xml:space="preserve">18.3346118927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5433540344238</t>
   </si>
   <si>
     <t xml:space="preserve">18.6651191711426</t>
@@ -5261,7 +5261,7 @@
     <t xml:space="preserve">17.9139595031738</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8503036499023</t>
+    <t xml:space="preserve">17.850305557251</t>
   </si>
   <si>
     <t xml:space="preserve">17.5775032043457</t>
@@ -5270,13 +5270,13 @@
     <t xml:space="preserve">17.5229434967041</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7320899963379</t>
+    <t xml:space="preserve">17.7320919036865</t>
   </si>
   <si>
     <t xml:space="preserve">17.7502784729004</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6866264343262</t>
+    <t xml:space="preserve">17.6866245269775</t>
   </si>
   <si>
     <t xml:space="preserve">17.3956356048584</t>
@@ -5288,7 +5288,7 @@
     <t xml:space="preserve">18.3504409790039</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2231330871582</t>
+    <t xml:space="preserve">18.2231349945068</t>
   </si>
   <si>
     <t xml:space="preserve">17.9958000183105</t>
@@ -5297,7 +5297,7 @@
     <t xml:space="preserve">18.2413196563721</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2049465179443</t>
+    <t xml:space="preserve">18.204948425293</t>
   </si>
   <si>
     <t xml:space="preserve">17.6411571502686</t>
@@ -5309,7 +5309,7 @@
     <t xml:space="preserve">17.5684108734131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2137699127197</t>
+    <t xml:space="preserve">17.2137680053711</t>
   </si>
   <si>
     <t xml:space="preserve">17.5956897735596</t>
@@ -5327,7 +5327,7 @@
     <t xml:space="preserve">17.6229705810547</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5323085784912</t>
+    <t xml:space="preserve">18.5323066711426</t>
   </si>
   <si>
     <t xml:space="preserve">18.068546295166</t>
@@ -5336,16 +5336,16 @@
     <t xml:space="preserve">17.9503307342529</t>
   </si>
   <si>
-    <t xml:space="preserve">17.668436050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6232414245605</t>
+    <t xml:space="preserve">17.6684379577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6232433319092</t>
   </si>
   <si>
     <t xml:space="preserve">18.4050006866455</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6778030395508</t>
+    <t xml:space="preserve">18.6778049468994</t>
   </si>
   <si>
     <t xml:space="preserve">18.8232975006104</t>
@@ -5366,22 +5366,22 @@
     <t xml:space="preserve">18.9687919616699</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0779113769531</t>
+    <t xml:space="preserve">19.0779094696045</t>
   </si>
   <si>
     <t xml:space="preserve">19.0415382385254</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1688442230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4234619140625</t>
+    <t xml:space="preserve">19.1688461303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4234600067139</t>
   </si>
   <si>
     <t xml:space="preserve">19.187032699585</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4052715301514</t>
+    <t xml:space="preserve">19.4052734375</t>
   </si>
   <si>
     <t xml:space="preserve">19.3507137298584</t>
@@ -5390,7 +5390,7 @@
     <t xml:space="preserve">19.2415924072266</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3870849609375</t>
+    <t xml:space="preserve">19.3870868682861</t>
   </si>
   <si>
     <t xml:space="preserve">19.5689544677734</t>
@@ -5399,7 +5399,7 @@
     <t xml:space="preserve">19.6780738830566</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9145030975342</t>
+    <t xml:space="preserve">19.9145011901855</t>
   </si>
   <si>
     <t xml:space="preserve">19.7326354980469</t>
@@ -5411,7 +5411,7 @@
     <t xml:space="preserve">17.9321441650391</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9048652648926</t>
+    <t xml:space="preserve">17.9048671722412</t>
   </si>
   <si>
     <t xml:space="preserve">18.3686275482178</t>
@@ -5426,28 +5426,28 @@
     <t xml:space="preserve">18.9869766235352</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7869243621826</t>
+    <t xml:space="preserve">18.786922454834</t>
   </si>
   <si>
     <t xml:space="preserve">19.0597229003906</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0051651000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1506576538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3325252532959</t>
+    <t xml:space="preserve">19.005163192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1506595611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3325271606445</t>
   </si>
   <si>
     <t xml:space="preserve">19.314338684082</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2052211761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9142284393311</t>
+    <t xml:space="preserve">19.2052192687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9142303466797</t>
   </si>
   <si>
     <t xml:space="preserve">18.8414821624756</t>
@@ -5468,16 +5468,16 @@
     <t xml:space="preserve">19.4416465759277</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5507678985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9690628051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1327438354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.496208190918</t>
+    <t xml:space="preserve">19.5507659912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9690608978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1327419281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4962062835693</t>
   </si>
   <si>
     <t xml:space="preserve">19.7871952056885</t>
@@ -5492,10 +5492,10 @@
     <t xml:space="preserve">20.169116973877</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2782363891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3873596191406</t>
+    <t xml:space="preserve">20.2782382965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.387357711792</t>
   </si>
   <si>
     <t xml:space="preserve">20.5874118804932</t>
@@ -5507,22 +5507,22 @@
     <t xml:space="preserve">20.696533203125</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6237869262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0057067871094</t>
+    <t xml:space="preserve">20.6237850189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.005708694458</t>
   </si>
   <si>
     <t xml:space="preserve">20.8056526184082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6601600646973</t>
+    <t xml:space="preserve">20.6601581573486</t>
   </si>
   <si>
     <t xml:space="preserve">20.4055461883545</t>
   </si>
   <si>
-    <t xml:space="preserve">20.296422958374</t>
+    <t xml:space="preserve">20.2964248657227</t>
   </si>
   <si>
     <t xml:space="preserve">20.2600517272949</t>
@@ -71320,7 +71320,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6911226852</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>137982</v>
@@ -71341,6 +71341,32 @@
         <v>1983</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6909722222</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>108204</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>22.3999996185303</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>22.1000003814697</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>22.3199996948242</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>22.3999996185303</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>1961</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IF.MI.xlsx
+++ b/data/IF.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7370805740356</t>
+    <t xml:space="preserve">15.737078666687</t>
   </si>
   <si>
     <t xml:space="preserve">IF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3903465270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3232364654541</t>
+    <t xml:space="preserve">15.3903474807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3232383728027</t>
   </si>
   <si>
     <t xml:space="preserve">14.5458917617798</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">14.3613424301147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3781175613403</t>
+    <t xml:space="preserve">14.3781185150146</t>
   </si>
   <si>
     <t xml:space="preserve">14.4284505844116</t>
@@ -65,19 +65,19 @@
     <t xml:space="preserve">14.1767921447754</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8646583557129</t>
+    <t xml:space="preserve">14.8646631240845</t>
   </si>
   <si>
     <t xml:space="preserve">13.8524322509766</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4955587387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.640962600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4340438842773</t>
+    <t xml:space="preserve">14.4955596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6409616470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.434042930603</t>
   </si>
   <si>
     <t xml:space="preserve">15.3735704421997</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">15.9384050369263</t>
   </si>
   <si>
-    <t xml:space="preserve">15.943998336792</t>
+    <t xml:space="preserve">15.9439973831177</t>
   </si>
   <si>
     <t xml:space="preserve">15.5637121200562</t>
@@ -98,37 +98,37 @@
     <t xml:space="preserve">16.1061744689941</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0502510070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7706298828125</t>
+    <t xml:space="preserve">16.0502548217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7706308364868</t>
   </si>
   <si>
     <t xml:space="preserve">15.1722431182861</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9597311019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5402994155884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0583076477051</t>
+    <t xml:space="preserve">14.9597330093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5403003692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0583066940308</t>
   </si>
   <si>
     <t xml:space="preserve">13.0974531173706</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7405824661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7685451507568</t>
+    <t xml:space="preserve">13.7405815124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7685441970825</t>
   </si>
   <si>
     <t xml:space="preserve">13.8244676589966</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5347080230713</t>
+    <t xml:space="preserve">14.534707069397</t>
   </si>
   <si>
     <t xml:space="preserve">14.4396362304688</t>
@@ -140,28 +140,28 @@
     <t xml:space="preserve">14.2718648910522</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3333778381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4350862503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9765110015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.741626739502</t>
+    <t xml:space="preserve">14.3333806991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4350872039795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9765090942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7416286468506</t>
   </si>
   <si>
     <t xml:space="preserve">15.2057981491089</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0995407104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0436172485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4966058731079</t>
+    <t xml:space="preserve">15.0995416641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0436182022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.496603012085</t>
   </si>
   <si>
     <t xml:space="preserve">15.2840900421143</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">14.5570774078369</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1656074523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7192573547363</t>
+    <t xml:space="preserve">14.1656064987183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4843769073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.719259262085</t>
   </si>
   <si>
     <t xml:space="preserve">15.1834268569946</t>
@@ -191,49 +191,49 @@
     <t xml:space="preserve">15.3791627883911</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9999217987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2348022460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.09499168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9663667678833</t>
+    <t xml:space="preserve">15.9999208450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2348041534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0949935913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9663686752319</t>
   </si>
   <si>
     <t xml:space="preserve">16.1173629760742</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1403388977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4849700927734</t>
+    <t xml:space="preserve">16.1403408050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4849739074707</t>
   </si>
   <si>
     <t xml:space="preserve">16.7204685211182</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4160461425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8474016189575</t>
+    <t xml:space="preserve">16.4160423278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8473997116089</t>
   </si>
   <si>
     <t xml:space="preserve">16.3815822601318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.600414276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6808280944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7842168807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8876066207886</t>
+    <t xml:space="preserve">15.6004123687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6808261871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7842149734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8876085281372</t>
   </si>
   <si>
     <t xml:space="preserve">15.6348762512207</t>
@@ -242,43 +242,43 @@
     <t xml:space="preserve">15.2787551879883</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4280958175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2385482788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1409015655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3821468353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9570941925049</t>
+    <t xml:space="preserve">15.4280948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2385473251343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1409025192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3821439743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9570970535278</t>
   </si>
   <si>
     <t xml:space="preserve">14.8479614257812</t>
   </si>
   <si>
-    <t xml:space="preserve">14.58948802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6239490509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.70436668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5550231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3482427597046</t>
+    <t xml:space="preserve">14.589485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6239500045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7043647766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5550260543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3482465744019</t>
   </si>
   <si>
     <t xml:space="preserve">14.1184873580933</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8427801132202</t>
+    <t xml:space="preserve">13.8427810668945</t>
   </si>
   <si>
     <t xml:space="preserve">14.164439201355</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">13.670464515686</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6417465209961</t>
+    <t xml:space="preserve">13.6417436599731</t>
   </si>
   <si>
     <t xml:space="preserve">13.325831413269</t>
@@ -296,85 +296,85 @@
     <t xml:space="preserve">13.1075639724731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8375997543335</t>
+    <t xml:space="preserve">12.8376007080078</t>
   </si>
   <si>
     <t xml:space="preserve">12.9811983108521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7629308700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4814767837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6365642547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6882591247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3493690490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5791244506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9352474212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.514817237854</t>
+    <t xml:space="preserve">12.7629299163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4814777374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6365652084351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6882600784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3493680953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5791254043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9352464675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5148191452026</t>
   </si>
   <si>
     <t xml:space="preserve">13.9576597213745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.785343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5613327026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6647233963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3488073348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2683925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3602924346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1535158157349</t>
+    <t xml:space="preserve">13.7853422164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5613307952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6647205352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3488063812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2683906555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3602962493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1535148620605</t>
   </si>
   <si>
     <t xml:space="preserve">12.9639654159546</t>
   </si>
   <si>
-    <t xml:space="preserve">12.780161857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5504064559937</t>
+    <t xml:space="preserve">12.7801628112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.550404548645</t>
   </si>
   <si>
     <t xml:space="preserve">12.205771446228</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0564308166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9185791015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6084079742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2287483215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6537961959839</t>
+    <t xml:space="preserve">12.0564298629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9185781478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6084060668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2287492752075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6537981033325</t>
   </si>
   <si>
     <t xml:space="preserve">12.5963582992554</t>
@@ -383,13 +383,13 @@
     <t xml:space="preserve">12.9869413375854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1196136474609</t>
+    <t xml:space="preserve">12.1196146011353</t>
   </si>
   <si>
     <t xml:space="preserve">10.1781778335571</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2643375396729</t>
+    <t xml:space="preserve">10.2643365859985</t>
   </si>
   <si>
     <t xml:space="preserve">10.3217744827271</t>
@@ -404,31 +404,31 @@
     <t xml:space="preserve">10.4538860321045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93693447113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58081340789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56932544708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73015403747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76461887359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8272371292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2810039520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4877853393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3269548416138</t>
+    <t xml:space="preserve">9.93693351745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58081245422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56932353973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73015308380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76461601257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8272380828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2810049057007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4877843856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3269557952881</t>
   </si>
   <si>
     <t xml:space="preserve">11.516505241394</t>
@@ -440,103 +440,103 @@
     <t xml:space="preserve">11.4992723464966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2293090820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0455055236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.861701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6032247543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9995536804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7175397872925</t>
+    <t xml:space="preserve">11.2293109893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0455045700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8616991043091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6032257080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9995527267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7175416946411</t>
   </si>
   <si>
     <t xml:space="preserve">11.4188575744629</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5796880722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1144313812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1431503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6026639938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.740517616272</t>
+    <t xml:space="preserve">11.5796871185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1144323348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1431512832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6026630401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7405166625977</t>
   </si>
   <si>
     <t xml:space="preserve">11.4016275405884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6543598175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5567140579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4533205032349</t>
+    <t xml:space="preserve">11.6543588638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5567121505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4533214569092</t>
   </si>
   <si>
     <t xml:space="preserve">11.3843955993652</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2867479324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9880647659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9765787124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0397615432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0282754898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0972013473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.970832824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9650897979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1201763153076</t>
+    <t xml:space="preserve">11.2867488861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9880657196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9765796661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0397605895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0282735824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0971994400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9708366394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9650907516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1201772689819</t>
   </si>
   <si>
     <t xml:space="preserve">11.2063360214233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1891031265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.430347442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8324174880981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3149061203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3953189849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9587841033936</t>
+    <t xml:space="preserve">11.1891021728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4303455352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8324203491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.314905166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.395320892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9587831497192</t>
   </si>
   <si>
     <t xml:space="preserve">11.6945657730103</t>
@@ -545,148 +545,148 @@
     <t xml:space="preserve">11.7749795913696</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6715898513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6888208389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5739431381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7692365646362</t>
+    <t xml:space="preserve">11.6715908050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6888227462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5739421844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7692356109619</t>
   </si>
   <si>
     <t xml:space="preserve">12.0621747970581</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0219678878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6601037979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5107612609863</t>
+    <t xml:space="preserve">12.0219669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6601028442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5107622146606</t>
   </si>
   <si>
     <t xml:space="preserve">11.4935293197632</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5279922485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7060537338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7577486038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0277090072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4068098068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.434965133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.699182510376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7279033660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.865758895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9519166946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.175929069519</t>
+    <t xml:space="preserve">11.5279932022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7060518264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7577495574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0277118682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4068088531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4349660873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6991844177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7278995513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8657560348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9519147872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1759271621704</t>
   </si>
   <si>
     <t xml:space="preserve">14.3712205886841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4631214141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8824253082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9628391265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1064367294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2270593643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.135157585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9456081390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7158517837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7330827713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.509072303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5952301025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5435371398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3827056884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0725374221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0610494613647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6474876403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6877002716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5900506973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5383548736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0501251220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1190528869629</t>
+    <t xml:space="preserve">14.4631252288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8824262619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9628410339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1064376831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2270584106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1351556777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9456071853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7158536911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7330837249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5090732574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5952339172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5435361862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3827095031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0725364685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0610504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6474895477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6876974105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5900497436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5383558273315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.050124168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1190509796143</t>
   </si>
   <si>
     <t xml:space="preserve">13.1822347640991</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7514419555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2109527587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4407110214233</t>
+    <t xml:space="preserve">12.7514410018921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2109537124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4407072067261</t>
   </si>
   <si>
     <t xml:space="preserve">13.4234790802002</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2856225967407</t>
+    <t xml:space="preserve">13.285623550415</t>
   </si>
   <si>
     <t xml:space="preserve">14.1414642333984</t>
@@ -698,76 +698,76 @@
     <t xml:space="preserve">14.1931581497192</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3597316741943</t>
+    <t xml:space="preserve">14.3597326278687</t>
   </si>
   <si>
     <t xml:space="preserve">14.9398651123047</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6871356964111</t>
+    <t xml:space="preserve">14.6871347427368</t>
   </si>
   <si>
     <t xml:space="preserve">14.3884506225586</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4746103286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7847805023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.934121131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2213163375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5831804275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4970226287842</t>
+    <t xml:space="preserve">14.474609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7847785949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9341230392456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2213153839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5831785202026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4970197677612</t>
   </si>
   <si>
     <t xml:space="preserve">15.4510707855225</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3361959457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8364763259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9915618896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2959842681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1638765335083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0375108718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0892066955566</t>
+    <t xml:space="preserve">15.3361930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8364734649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9915599822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2959871292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1638774871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0375099182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0892057418823</t>
   </si>
   <si>
     <t xml:space="preserve">15.0719747543335</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8307313919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6469259262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5320482254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2333641052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5263042449951</t>
+    <t xml:space="preserve">14.8307304382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6469268798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5320501327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2333660125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5263051986694</t>
   </si>
   <si>
     <t xml:space="preserve">14.4171714782715</t>
@@ -776,40 +776,40 @@
     <t xml:space="preserve">14.3941955566406</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0490007400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7618026733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6584157943726</t>
+    <t xml:space="preserve">15.0489978790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7618036270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6584138870239</t>
   </si>
   <si>
     <t xml:space="preserve">14.8766822814941</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3936309814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8531427383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8416538238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0369491577148</t>
+    <t xml:space="preserve">15.3936338424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8531446456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8416576385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0369510650635</t>
   </si>
   <si>
     <t xml:space="preserve">16.5079460144043</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9559745788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0880794525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6343116760254</t>
+    <t xml:space="preserve">16.9559726715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0880813598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.634313583374</t>
   </si>
   <si>
     <t xml:space="preserve">16.6113376617432</t>
@@ -818,16 +818,16 @@
     <t xml:space="preserve">16.0828990936279</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8870449066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9444828033447</t>
+    <t xml:space="preserve">16.8870468139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9444808959961</t>
   </si>
   <si>
     <t xml:space="preserve">17.3465576171875</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4844093322754</t>
+    <t xml:space="preserve">17.484411239624</t>
   </si>
   <si>
     <t xml:space="preserve">17.593542098999</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">17.1684951782227</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6911888122559</t>
+    <t xml:space="preserve">17.6911869049072</t>
   </si>
   <si>
     <t xml:space="preserve">17.9152011871338</t>
@@ -848,16 +848,16 @@
     <t xml:space="preserve">18.7365760803223</t>
   </si>
   <si>
-    <t xml:space="preserve">19.552209854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8164310455322</t>
+    <t xml:space="preserve">19.5522117614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8164291381836</t>
   </si>
   <si>
     <t xml:space="preserve">19.9944915771484</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9422283172607</t>
+    <t xml:space="preserve">20.942232131958</t>
   </si>
   <si>
     <t xml:space="preserve">20.5229263305664</t>
@@ -866,16 +866,16 @@
     <t xml:space="preserve">20.8503322601318</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7354526519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6780128479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6492938995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3218936920166</t>
+    <t xml:space="preserve">20.7354507446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6780109405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6492958068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.321891784668</t>
   </si>
   <si>
     <t xml:space="preserve">20.5631351470947</t>
@@ -884,19 +884,19 @@
     <t xml:space="preserve">20.6378078460693</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8388442993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8216094970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6090869903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1088047027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4132289886475</t>
+    <t xml:space="preserve">20.8388423919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8216114044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6090888977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1088066101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4132308959961</t>
   </si>
   <si>
     <t xml:space="preserve">21.2409133911133</t>
@@ -908,364 +908,364 @@
     <t xml:space="preserve">21.0226459503174</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9594669342041</t>
+    <t xml:space="preserve">20.9594650268555</t>
   </si>
   <si>
     <t xml:space="preserve">21.3098411560059</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5855503082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3155860900879</t>
+    <t xml:space="preserve">21.5855484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3155841827393</t>
   </si>
   <si>
     <t xml:space="preserve">22.2690715789795</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1369590759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9818801879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2288627624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7458114624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9335041046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5815868377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.393892288208</t>
+    <t xml:space="preserve">22.136962890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9818782806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2288646697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7458152770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9335079193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5815830230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3938941955566</t>
   </si>
   <si>
     <t xml:space="preserve">21.4671688079834</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4583301544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.103515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8161163330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6342887878418</t>
+    <t xml:space="preserve">20.4583282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1035175323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8161144256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6342906951904</t>
   </si>
   <si>
     <t xml:space="preserve">20.692943572998</t>
   </si>
   <si>
-    <t xml:space="preserve">20.587366104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2969951629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5872840881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5433368682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9656391143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4817905426025</t>
+    <t xml:space="preserve">20.5873641967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2969913482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5872859954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5433330535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9656410217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4817924499512</t>
   </si>
   <si>
     <t xml:space="preserve">20.4700622558594</t>
   </si>
   <si>
-    <t xml:space="preserve">20.528715133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4114055633545</t>
+    <t xml:space="preserve">20.5287132263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4114074707031</t>
   </si>
   <si>
     <t xml:space="preserve">20.2706394195557</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3058319091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7955474853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.607852935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8835277557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2471790313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0594844818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1767959594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7515983581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6988086700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3527507781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5521755218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5052509307861</t>
+    <t xml:space="preserve">20.3058300018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7955455780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6078567504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.88352394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2471771240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0594863891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1767921447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7515964508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6988105773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3527545928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5521774291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5052528381348</t>
   </si>
   <si>
     <t xml:space="preserve">20.7046718597412</t>
   </si>
   <si>
-    <t xml:space="preserve">20.440731048584</t>
+    <t xml:space="preserve">20.4407329559326</t>
   </si>
   <si>
     <t xml:space="preserve">20.1474647521973</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0477542877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0008277893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4876556396484</t>
+    <t xml:space="preserve">20.0477561950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0008296966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4876594543457</t>
   </si>
   <si>
     <t xml:space="preserve">20.6694812774658</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6460208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.863037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9334239959717</t>
+    <t xml:space="preserve">20.6460227966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8630352020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9334182739258</t>
   </si>
   <si>
     <t xml:space="preserve">21.009672164917</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9275608062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1152477264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2560176849365</t>
+    <t xml:space="preserve">20.9275588989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1152458190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2560138702393</t>
   </si>
   <si>
     <t xml:space="preserve">21.2912101745605</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5551490783691</t>
+    <t xml:space="preserve">21.5551509857178</t>
   </si>
   <si>
     <t xml:space="preserve">21.748706817627</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6314010620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6079349517822</t>
+    <t xml:space="preserve">21.6313972473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6079368591309</t>
   </si>
   <si>
     <t xml:space="preserve">21.6431312561035</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8366870880127</t>
+    <t xml:space="preserve">21.8366851806641</t>
   </si>
   <si>
     <t xml:space="preserve">22.0830326080322</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7604351043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4642772674561</t>
+    <t xml:space="preserve">21.7604370117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4642753601074</t>
   </si>
   <si>
     <t xml:space="preserve">22.9041786193848</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6402378082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9686985015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7575435638428</t>
+    <t xml:space="preserve">22.6402397155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9686965942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7575454711914</t>
   </si>
   <si>
     <t xml:space="preserve">23.2854290008545</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4907150268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7722492218018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0068626403809</t>
+    <t xml:space="preserve">23.4907093048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7722473144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0068664550781</t>
   </si>
   <si>
     <t xml:space="preserve">24.2708053588867</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8719596862793</t>
+    <t xml:space="preserve">23.8719635009766</t>
   </si>
   <si>
     <t xml:space="preserve">24.1007099151611</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0479202270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5435009002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.566967010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1593647003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3529243469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3059978485107</t>
+    <t xml:space="preserve">24.0479221343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5435028076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5669651031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1593608856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3529186248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3059959411621</t>
   </si>
   <si>
     <t xml:space="preserve">23.854362487793</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0361919403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8367691040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8191757202148</t>
+    <t xml:space="preserve">24.036190032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8367710113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8191738128662</t>
   </si>
   <si>
     <t xml:space="preserve">23.9716739654541</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7898483276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6373462677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1153316497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7077331542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9012870788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.165225982666</t>
+    <t xml:space="preserve">23.7898502349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6373443603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1153297424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7077293395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9012889862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1652317047119</t>
   </si>
   <si>
     <t xml:space="preserve">24.5347480773926</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3411922454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0831146240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7400321960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7107086181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4936866760254</t>
+    <t xml:space="preserve">24.3411903381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0831165313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7400360107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7107048034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4936847686768</t>
   </si>
   <si>
     <t xml:space="preserve">24.698974609375</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0684967041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7078170776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7136821746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1594486236572</t>
+    <t xml:space="preserve">25.0684909820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7078189849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7136783599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.15944480896</t>
   </si>
   <si>
     <t xml:space="preserve">26.4937705993652</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3823299407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5876178741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1301193237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5993480682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8222274780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.133092880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7548217773438</t>
+    <t xml:space="preserve">26.3823280334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5876197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1301212310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5993461608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8222312927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1330947875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7548198699951</t>
   </si>
   <si>
     <t xml:space="preserve">28.0656833648682</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2064533233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8984794616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7489566802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.499719619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.828182220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8926982879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6580867767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.053955078125</t>
+    <t xml:space="preserve">28.2064552307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8984813690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7489585876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4997272491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8281784057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8927001953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.6580829620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0539531707764</t>
   </si>
   <si>
     <t xml:space="preserve">26.9278049468994</t>
@@ -1277,148 +1277,148 @@
     <t xml:space="preserve">27.2152099609375</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6403999328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.537805557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6316509246826</t>
+    <t xml:space="preserve">26.6404056549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5378074645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.631649017334</t>
   </si>
   <si>
     <t xml:space="preserve">27.6668395996094</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8428020477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3237609863281</t>
+    <t xml:space="preserve">27.8428058624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3237590789795</t>
   </si>
   <si>
     <t xml:space="preserve">27.5671310424805</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6023235321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4556865692139</t>
+    <t xml:space="preserve">27.6023216247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4556922912598</t>
   </si>
   <si>
     <t xml:space="preserve">27.5026111602783</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0803031921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8163661956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3060817718506</t>
+    <t xml:space="preserve">27.0803050994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8163642883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.306079864502</t>
   </si>
   <si>
     <t xml:space="preserve">25.9365634918213</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5992641448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8954219818115</t>
+    <t xml:space="preserve">24.5992679595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8954200744629</t>
   </si>
   <si>
     <t xml:space="preserve">22.9511013031006</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8279285430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6021595001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7164897918701</t>
+    <t xml:space="preserve">22.8279247283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6021556854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7164878845215</t>
   </si>
   <si>
     <t xml:space="preserve">22.7282180786133</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3176422119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9833202362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6754283905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4056205749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6109104156494</t>
+    <t xml:space="preserve">22.3176441192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9833221435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6754322052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4056282043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6109142303467</t>
   </si>
   <si>
     <t xml:space="preserve">22.7927379608154</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2355289459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5492897033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5199546813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7311058044434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8249568939209</t>
+    <t xml:space="preserve">22.2355346679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5492858886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5199565887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7311096191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8249549865723</t>
   </si>
   <si>
     <t xml:space="preserve">21.4495754241943</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9040946960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4026527404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.877742767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4701442718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1914958953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1093845367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0565967559814</t>
+    <t xml:space="preserve">20.9040985107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4026508331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8777408599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.470142364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.191499710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1093807220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0565986633301</t>
   </si>
   <si>
     <t xml:space="preserve">21.7135143280029</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7047595977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9130210876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0449447631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3440818786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7546539306641</t>
+    <t xml:space="preserve">22.7047557830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9130191802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0449504852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3440780639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7546520233154</t>
   </si>
   <si>
     <t xml:space="preserve">23.7663860321045</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4496593475342</t>
+    <t xml:space="preserve">23.4496574401855</t>
   </si>
   <si>
     <t xml:space="preserve">23.5200424194336</t>
@@ -1427,16 +1427,16 @@
     <t xml:space="preserve">22.3469715118408</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0273513793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1563873291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8631210327148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0508098602295</t>
+    <t xml:space="preserve">23.0273494720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1563892364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8631229400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0508117675781</t>
   </si>
   <si>
     <t xml:space="preserve">22.9569664001465</t>
@@ -1445,10 +1445,10 @@
     <t xml:space="preserve">22.7810077667236</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5229358673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4994697570801</t>
+    <t xml:space="preserve">22.5229320526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4994735717773</t>
   </si>
   <si>
     <t xml:space="preserve">22.2765884399414</t>
@@ -1457,10 +1457,10 @@
     <t xml:space="preserve">22.9452342987061</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4525470733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0771675109863</t>
+    <t xml:space="preserve">22.452543258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0771656036377</t>
   </si>
   <si>
     <t xml:space="preserve">21.2208251953125</t>
@@ -1469,22 +1469,22 @@
     <t xml:space="preserve">20.7398662567139</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2677478790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6489124298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4260292053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7750587463379</t>
+    <t xml:space="preserve">21.267749786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6489105224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4260272979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7750568389893</t>
   </si>
   <si>
     <t xml:space="preserve">21.1621723175049</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9158248901367</t>
+    <t xml:space="preserve">20.9158306121826</t>
   </si>
   <si>
     <t xml:space="preserve">21.3733215332031</t>
@@ -1496,37 +1496,37 @@
     <t xml:space="preserve">21.3264007568359</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2794799804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.396785736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.044864654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7985210418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6812114715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0125617980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3321800231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0154514312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3556423187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0975704193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0858402252197</t>
+    <t xml:space="preserve">21.2794780731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3967819213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0448665618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7985191345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.681209564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.012565612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3321838378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.015453338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3556442260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0975723266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0858383178711</t>
   </si>
   <si>
     <t xml:space="preserve">20.071216583252</t>
@@ -1535,19 +1535,19 @@
     <t xml:space="preserve">19.9891033172607</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8394927978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3468055725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5227642059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4377632141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2617969512939</t>
+    <t xml:space="preserve">18.8394947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3468036651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5227661132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4377593994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2617988586426</t>
   </si>
   <si>
     <t xml:space="preserve">18.9919929504395</t>
@@ -1556,76 +1556,76 @@
     <t xml:space="preserve">18.3233432769775</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3614273071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6987266540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9596900939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7221870422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1210289001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.273530960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4142951965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1533336639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7310276031494</t>
+    <t xml:space="preserve">17.3614253997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6987247467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9596939086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.722188949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1210327148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2735290527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4142990112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1533317565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7310237884521</t>
   </si>
   <si>
     <t xml:space="preserve">19.5785293579102</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8131408691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6958351135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3461246490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3582210540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1404418945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0920467376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1646385192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.781681060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9752635955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2656383514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.435022354126</t>
+    <t xml:space="preserve">19.8131370544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.695837020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3461208343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3582248687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1404438018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0920448303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1646423339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7816829681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9752674102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2656364440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4350185394287</t>
   </si>
   <si>
     <t xml:space="preserve">20.6649017333984</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3745250701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0236587524414</t>
+    <t xml:space="preserve">20.3745288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.02366065979</t>
   </si>
   <si>
     <t xml:space="preserve">19.5397033691406</t>
@@ -1634,16 +1634,16 @@
     <t xml:space="preserve">19.4429130554199</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6485958099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7211856842041</t>
+    <t xml:space="preserve">19.6485939025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7211894989014</t>
   </si>
   <si>
     <t xml:space="preserve">18.9589576721191</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3298149108887</t>
+    <t xml:space="preserve">18.3298168182373</t>
   </si>
   <si>
     <t xml:space="preserve">17.4102993011475</t>
@@ -1652,67 +1652,67 @@
     <t xml:space="preserve">17.0836296081543</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2288150787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.877950668335</t>
+    <t xml:space="preserve">17.228816986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8779487609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.5149822235107</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6075649261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1677980422974</t>
+    <t xml:space="preserve">15.6075658798218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1677989959717</t>
   </si>
   <si>
     <t xml:space="preserve">12.8853149414062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1194019317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.22829246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4260816574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4865779876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0147199630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1478080749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8332366943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7001485824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2929944992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1520175933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5996761322021</t>
+    <t xml:space="preserve">14.1194009780884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2282943725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.426082611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4865760803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0147190093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1478099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8332376480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7001495361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2929935455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1520156860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5996723175049</t>
   </si>
   <si>
     <t xml:space="preserve">16.575475692749</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0794239044189</t>
+    <t xml:space="preserve">16.0794219970703</t>
   </si>
   <si>
     <t xml:space="preserve">16.7932567596436</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2409133911133</t>
+    <t xml:space="preserve">17.2409152984619</t>
   </si>
   <si>
     <t xml:space="preserve">16.7327632904053</t>
@@ -1721,46 +1721,46 @@
     <t xml:space="preserve">16.9021453857422</t>
   </si>
   <si>
-    <t xml:space="preserve">16.623872756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9705324172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4623794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5712699890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5954666137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6438627243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.619665145874</t>
+    <t xml:space="preserve">16.6238708496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9705333709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4623756408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.571268081665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5954685211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6438646316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6196641921997</t>
   </si>
   <si>
     <t xml:space="preserve">15.7890501022339</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0431270599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4060916900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.587574005127</t>
+    <t xml:space="preserve">16.0431251525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4060935974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5875778198242</t>
   </si>
   <si>
     <t xml:space="preserve">16.2730045318604</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9100370407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9947309494019</t>
+    <t xml:space="preserve">15.9100379943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9947319030762</t>
   </si>
   <si>
     <t xml:space="preserve">15.825345993042</t>
@@ -1778,19 +1778,19 @@
     <t xml:space="preserve">16.0552253723145</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2972030639648</t>
+    <t xml:space="preserve">16.2972011566162</t>
   </si>
   <si>
     <t xml:space="preserve">16.3576984405518</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2125091552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3655891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5470705032349</t>
+    <t xml:space="preserve">16.2125110626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3655862808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5470714569092</t>
   </si>
   <si>
     <t xml:space="preserve">14.6396551132202</t>
@@ -1802,46 +1802,46 @@
     <t xml:space="preserve">13.6838436126709</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6475439071655</t>
+    <t xml:space="preserve">13.6475467681885</t>
   </si>
   <si>
     <t xml:space="preserve">13.6354465484619</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2845773696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0426015853882</t>
+    <t xml:space="preserve">13.2845792770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0426006317139</t>
   </si>
   <si>
     <t xml:space="preserve">12.5102510452271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3771619796753</t>
+    <t xml:space="preserve">12.377161026001</t>
   </si>
   <si>
     <t xml:space="preserve">12.4860525131226</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4497575759888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2603826522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7885246276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.970009803772</t>
+    <t xml:space="preserve">12.4497547149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2603807449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7885255813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9700078964233</t>
   </si>
   <si>
     <t xml:space="preserve">12.921612739563</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0909957885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3408651351929</t>
+    <t xml:space="preserve">13.0909967422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3408670425415</t>
   </si>
   <si>
     <t xml:space="preserve">12.2924709320068</t>
@@ -1850,25 +1850,25 @@
     <t xml:space="preserve">12.2561740875244</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7643270492554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1998872756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6596450805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5265588760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3571729660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8895225524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5749540328979</t>
+    <t xml:space="preserve">12.764328956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1998882293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6596460342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5265579223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3571720123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8895254135132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5749521255493</t>
   </si>
   <si>
     <t xml:space="preserve">13.6717443466187</t>
@@ -1877,16 +1877,16 @@
     <t xml:space="preserve">13.3208770751953</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3450736999512</t>
+    <t xml:space="preserve">13.3450717926025</t>
   </si>
   <si>
     <t xml:space="preserve">13.5023593902588</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0589084625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4218740463257</t>
+    <t xml:space="preserve">14.0589075088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.421875</t>
   </si>
   <si>
     <t xml:space="preserve">14.3976764678955</t>
@@ -1895,25 +1895,25 @@
     <t xml:space="preserve">14.2645893096924</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4339742660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3934698104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7359209060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8648014068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3003616333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6088819503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9778985977173</t>
+    <t xml:space="preserve">14.4339733123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3934688568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7359218597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.864800453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3003625869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6088838577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9778995513916</t>
   </si>
   <si>
     <t xml:space="preserve">11.8024663925171</t>
@@ -1931,25 +1931,25 @@
     <t xml:space="preserve">9.86664199829102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3264007568359</t>
+    <t xml:space="preserve">10.3263988494873</t>
   </si>
   <si>
     <t xml:space="preserve">10.3022031784058</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4957847595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92108631134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89689159393311</t>
+    <t xml:space="preserve">10.4957857131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92108726501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89689064025879</t>
   </si>
   <si>
     <t xml:space="preserve">9.53392314910889</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73539638519287</t>
+    <t xml:space="preserve">8.7353982925415</t>
   </si>
   <si>
     <t xml:space="preserve">8.37848091125488</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">8.4692211151123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49946880340576</t>
+    <t xml:space="preserve">8.49946975708008</t>
   </si>
   <si>
     <t xml:space="preserve">8.9713249206543</t>
@@ -1973,34 +1973,34 @@
     <t xml:space="preserve">9.40083599090576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67911052703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.217511177063</t>
+    <t xml:space="preserve">9.67911243438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2175092697144</t>
   </si>
   <si>
     <t xml:space="preserve">9.88479232788086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12256145477295</t>
+    <t xml:space="preserve">9.12256050109863</t>
   </si>
   <si>
     <t xml:space="preserve">9.21935272216797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82008934020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1286096572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24960041046143</t>
+    <t xml:space="preserve">8.82009124755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12861251831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24960136413574</t>
   </si>
   <si>
     <t xml:space="preserve">9.36453914642334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58836841583252</t>
+    <t xml:space="preserve">9.58836936950684</t>
   </si>
   <si>
     <t xml:space="preserve">9.48552894592285</t>
@@ -2009,13 +2009,13 @@
     <t xml:space="preserve">9.45528125762939</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70935821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6125659942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57022094726562</t>
+    <t xml:space="preserve">9.70935726165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61256694793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57022190093994</t>
   </si>
   <si>
     <t xml:space="preserve">10.8406047821045</t>
@@ -2024,10 +2024,10 @@
     <t xml:space="preserve">11.1370267868042</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9071474075317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5967845916748</t>
+    <t xml:space="preserve">10.9071483612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5967855453491</t>
   </si>
   <si>
     <t xml:space="preserve">11.3064107894897</t>
@@ -2036,10 +2036,10 @@
     <t xml:space="preserve">11.0099897384644</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9676427841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5139350891113</t>
+    <t xml:space="preserve">10.967643737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5139331817627</t>
   </si>
   <si>
     <t xml:space="preserve">10.8285045623779</t>
@@ -2048,100 +2048,100 @@
     <t xml:space="preserve">10.3385000228882</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7377634048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2840566635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6409711837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1007299423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0039377212524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8587532043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3747959136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81219863891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6912088394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37058925628662</t>
+    <t xml:space="preserve">10.7377624511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2840538024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6409721374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1007289886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0039396286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.85875415802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3747978210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81219673156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69120979309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3705883026123</t>
   </si>
   <si>
     <t xml:space="preserve">9.17095756530762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03786849975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34034156799316</t>
+    <t xml:space="preserve">9.03786945343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34034061431885</t>
   </si>
   <si>
     <t xml:space="preserve">9.34639167785645</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94528579711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4050445556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8043069839478</t>
+    <t xml:space="preserve">9.94528675079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4050436019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8043079376221</t>
   </si>
   <si>
     <t xml:space="preserve">10.5562810897827</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6228227615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5804786682129</t>
+    <t xml:space="preserve">10.62282371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5804777145386</t>
   </si>
   <si>
     <t xml:space="preserve">10.5502300262451</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0239295959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62466526031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1025724411011</t>
+    <t xml:space="preserve">10.0239286422729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62466621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1025705337524</t>
   </si>
   <si>
     <t xml:space="preserve">10.2296104431152</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4655380249023</t>
+    <t xml:space="preserve">10.465537071228</t>
   </si>
   <si>
     <t xml:space="preserve">10.3687477111816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98763179779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.969482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2780055999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4352912902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5320825576782</t>
+    <t xml:space="preserve">9.98763370513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96948432922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2780065536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4352903366089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5320816040039</t>
   </si>
   <si>
     <t xml:space="preserve">10.1509675979614</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">10.0299787521362</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1267690658569</t>
+    <t xml:space="preserve">10.1267700195312</t>
   </si>
   <si>
     <t xml:space="preserve">10.3445491790771</t>
@@ -2165,22 +2165,22 @@
     <t xml:space="preserve">11.0946798324585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6433372497559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0323448181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3729543685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8768997192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7014675140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.610725402832</t>
+    <t xml:space="preserve">12.6433382034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0323429107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3729562759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.876898765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7014665603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6107263565063</t>
   </si>
   <si>
     <t xml:space="preserve">10.5683794021606</t>
@@ -2195,46 +2195,46 @@
     <t xml:space="preserve">10.9373950958252</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0341863632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1128311157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4818458557129</t>
+    <t xml:space="preserve">11.0341844558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1128301620483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4818439483643</t>
   </si>
   <si>
     <t xml:space="preserve">10.9736919403076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54602336883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35848999023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22540283203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11046409606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08626651763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13466167449951</t>
+    <t xml:space="preserve">9.54602241516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35849094390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22540378570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1104621887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08626556396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1346607208252</t>
   </si>
   <si>
     <t xml:space="preserve">8.92897987365723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97737598419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9531774520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84428787231445</t>
+    <t xml:space="preserve">8.97737503051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95317649841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84428691864014</t>
   </si>
   <si>
     <t xml:space="preserve">8.89873123168945</t>
@@ -2243,13 +2243,13 @@
     <t xml:space="preserve">9.0741662979126</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00157356262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24355125427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4976282119751</t>
+    <t xml:space="preserve">9.00157451629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24355030059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49762725830078</t>
   </si>
   <si>
     <t xml:space="preserve">9.47947883605957</t>
@@ -2261,13 +2261,13 @@
     <t xml:space="preserve">9.38873767852783</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63676357269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68515968322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71540641784668</t>
+    <t xml:space="preserve">9.63676452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68515872955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.715407371521</t>
   </si>
   <si>
     <t xml:space="preserve">9.83034706115723</t>
@@ -2276,118 +2276,118 @@
     <t xml:space="preserve">10.2636585235596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94029140472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65572929382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72686862945557</t>
+    <t xml:space="preserve">9.9402904510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65572834014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72686958312988</t>
   </si>
   <si>
     <t xml:space="preserve">9.21595001220703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0477991104126</t>
+    <t xml:space="preserve">9.04779815673828</t>
   </si>
   <si>
     <t xml:space="preserve">8.73736763000488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52394485473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27818584442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86427688598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32345867156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37519550323486</t>
+    <t xml:space="preserve">8.52394580841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2781867980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8642783164978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32345771789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37519645690918</t>
   </si>
   <si>
     <t xml:space="preserve">8.31699085235596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0712308883667</t>
+    <t xml:space="preserve">8.07123184204102</t>
   </si>
   <si>
     <t xml:space="preserve">7.87721252441406</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90954780578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82547378540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56678009033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72199487686157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59264802932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54091024398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50210618972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37275886535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31455373764038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66378974914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32749032974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24341249465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2886848449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52150774002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26281499862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29515075683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41803216934204</t>
+    <t xml:space="preserve">7.90954732894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82547330856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56677961349487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72199583053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59264945983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5409107208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50210762023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37275981903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3145546913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66379117965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32748746871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24341344833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28868532180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52150869369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26281547546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2951512336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25634860992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41803121566772</t>
   </si>
   <si>
     <t xml:space="preserve">7.70906114578247</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03242778778076</t>
+    <t xml:space="preserve">8.03242874145508</t>
   </si>
   <si>
     <t xml:space="preserve">7.84487533569336</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70259475708008</t>
+    <t xml:space="preserve">7.70259380340576</t>
   </si>
   <si>
     <t xml:space="preserve">7.55384540557861</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76726722717285</t>
+    <t xml:space="preserve">7.76726770401001</t>
   </si>
   <si>
     <t xml:space="preserve">7.79960346221924</t>
@@ -2396,13 +2396,13 @@
     <t xml:space="preserve">7.67672491073608</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99362277984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18117618560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70503044128418</t>
+    <t xml:space="preserve">7.99362325668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18117713928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7050313949585</t>
   </si>
   <si>
     <t xml:space="preserve">8.65329170227051</t>
@@ -2417,43 +2417,43 @@
     <t xml:space="preserve">8.58215141296387</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57568550109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49160861968994</t>
+    <t xml:space="preserve">8.57568359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49160957336426</t>
   </si>
   <si>
     <t xml:space="preserve">8.55628204345703</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95725727081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94432258605957</t>
+    <t xml:space="preserve">8.95725631713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94432163238525</t>
   </si>
   <si>
     <t xml:space="preserve">8.93785381317139</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75030136108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62742233276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82791042327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83437824249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71149730682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6080207824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66622638702393</t>
+    <t xml:space="preserve">8.7503023147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62742328643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82790946960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83437728881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71149826049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60801982879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66622734069824</t>
   </si>
   <si>
     <t xml:space="preserve">8.38813209533691</t>
@@ -2465,16 +2465,16 @@
     <t xml:space="preserve">8.54334735870361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02839660644531</t>
+    <t xml:space="preserve">9.02839756011963</t>
   </si>
   <si>
     <t xml:space="preserve">8.91845226287842</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88611602783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12540626525879</t>
+    <t xml:space="preserve">8.88611698150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12540721893311</t>
   </si>
   <si>
     <t xml:space="preserve">8.48514175415039</t>
@@ -2483,16 +2483,16 @@
     <t xml:space="preserve">8.11003589630127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87074518203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26525020599365</t>
+    <t xml:space="preserve">7.87074422836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26525115966797</t>
   </si>
   <si>
     <t xml:space="preserve">8.33639240264893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43340301513672</t>
+    <t xml:space="preserve">8.4334020614624</t>
   </si>
   <si>
     <t xml:space="preserve">8.36872863769531</t>
@@ -2501,25 +2501,25 @@
     <t xml:space="preserve">8.28465366363525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23938274383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56274890899658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76970291137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02193069458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13187503814697</t>
+    <t xml:space="preserve">8.23938179016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56274795532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76970481872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02192974090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13187408447266</t>
   </si>
   <si>
     <t xml:space="preserve">9.22241687774658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45524024963379</t>
+    <t xml:space="preserve">9.45524120330811</t>
   </si>
   <si>
     <t xml:space="preserve">9.442307472229</t>
@@ -2531,61 +2531,61 @@
     <t xml:space="preserve">9.55871868133545</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58458805084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6945333480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91442203521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92088890075684</t>
+    <t xml:space="preserve">9.5845890045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69453239440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91442108154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92089080810547</t>
   </si>
   <si>
     <t xml:space="preserve">9.73333644866943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89502048492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90795421600342</t>
+    <t xml:space="preserve">9.89501953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90795516967773</t>
   </si>
   <si>
     <t xml:space="preserve">9.67512989044189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57812023162842</t>
+    <t xml:space="preserve">9.57812118530273</t>
   </si>
   <si>
     <t xml:space="preserve">9.66866302490234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90148639678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70746803283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51991558074951</t>
+    <t xml:space="preserve">9.90148735046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7074670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51991367340088</t>
   </si>
   <si>
     <t xml:space="preserve">9.30649280548096</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33236122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43583965301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09953880310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37116622924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52638244628906</t>
+    <t xml:space="preserve">9.33236217498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43583869934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09953784942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37116527557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52638149261475</t>
   </si>
   <si>
     <t xml:space="preserve">9.79154300689697</t>
@@ -2594,16 +2594,16 @@
     <t xml:space="preserve">9.73980331420898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76567363739014</t>
+    <t xml:space="preserve">9.76567268371582</t>
   </si>
   <si>
     <t xml:space="preserve">9.87561893463135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95322704315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99849605560303</t>
+    <t xml:space="preserve">9.95322513580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99849700927734</t>
   </si>
   <si>
     <t xml:space="preserve">9.94675922393799</t>
@@ -2615,10 +2615,10 @@
     <t xml:space="preserve">9.8820858001709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98556137084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.224853515625</t>
+    <t xml:space="preserve">9.98556232452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2248554229736</t>
   </si>
   <si>
     <t xml:space="preserve">9.44877433776855</t>
@@ -2630,10 +2630,10 @@
     <t xml:space="preserve">9.86915111541748</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1925172805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2377891540527</t>
+    <t xml:space="preserve">10.19251537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2377882003784</t>
   </si>
   <si>
     <t xml:space="preserve">9.62339210510254</t>
@@ -2642,7 +2642,7 @@
     <t xml:space="preserve">9.41643714904785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34529685974121</t>
+    <t xml:space="preserve">9.34529781341553</t>
   </si>
   <si>
     <t xml:space="preserve">9.24181842803955</t>
@@ -2651,49 +2651,49 @@
     <t xml:space="preserve">9.1900806427002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06073379516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0801362991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97665786743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04133129119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92492008209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76323699951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84731197357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78263759613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61448860168457</t>
+    <t xml:space="preserve">9.06073474884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08013534545898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97665882110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04133033752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9249210357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7632360458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84731292724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78263854980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61448764801025</t>
   </si>
   <si>
     <t xml:space="preserve">8.56921577453613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67916202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86671257019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87318229675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81497573852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8602466583252</t>
+    <t xml:space="preserve">8.67916107177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86671447753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8731803894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81497478485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86024570465088</t>
   </si>
   <si>
     <t xml:space="preserve">9.24828720092773</t>
@@ -2705,25 +2705,25 @@
     <t xml:space="preserve">9.14480972290039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23535060882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15774345397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13833999633789</t>
+    <t xml:space="preserve">9.2353515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15774440765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13834190368652</t>
   </si>
   <si>
     <t xml:space="preserve">9.2676887512207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09307098388672</t>
+    <t xml:space="preserve">9.0930700302124</t>
   </si>
   <si>
     <t xml:space="preserve">8.93138790130615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2030143737793</t>
+    <t xml:space="preserve">9.20301532745361</t>
   </si>
   <si>
     <t xml:space="preserve">9.59105587005615</t>
@@ -2735,28 +2735,28 @@
     <t xml:space="preserve">9.51344680786133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53284931182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32589435577393</t>
+    <t xml:space="preserve">9.5328483581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32589530944824</t>
   </si>
   <si>
     <t xml:space="preserve">9.30002498626709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74627208709717</t>
+    <t xml:space="preserve">9.74627113342285</t>
   </si>
   <si>
     <t xml:space="preserve">9.47464275360107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27415561676025</t>
+    <t xml:space="preserve">9.27415466308594</t>
   </si>
   <si>
     <t xml:space="preserve">9.62985897064209</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70099925994873</t>
+    <t xml:space="preserve">9.70100021362305</t>
   </si>
   <si>
     <t xml:space="preserve">9.80447769165039</t>
@@ -2765,13 +2765,13 @@
     <t xml:space="preserve">10.1343116760254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1278438568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0696363449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1407804489136</t>
+    <t xml:space="preserve">10.1278448104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.069637298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1407794952393</t>
   </si>
   <si>
     <t xml:space="preserve">10.0049648284912</t>
@@ -2783,10 +2783,10 @@
     <t xml:space="preserve">9.35176372528076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55225086212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8925838470459</t>
+    <t xml:space="preserve">9.5522518157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89258289337158</t>
   </si>
   <si>
     <t xml:space="preserve">8.40753364562988</t>
@@ -2801,49 +2801,49 @@
     <t xml:space="preserve">6.61608123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5966796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67185163497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93701267242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61364459991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44549465179443</t>
+    <t xml:space="preserve">6.59668016433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67185115814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93701219558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61364555358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44549512863159</t>
   </si>
   <si>
     <t xml:space="preserve">5.45842885971069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43902683258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75592660903931</t>
+    <t xml:space="preserve">5.43902730941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75592708587646</t>
   </si>
   <si>
     <t xml:space="preserve">5.57160758972168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84000205993652</t>
+    <t xml:space="preserve">5.84000110626221</t>
   </si>
   <si>
     <t xml:space="preserve">5.86910533905029</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9822826385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90790891647339</t>
+    <t xml:space="preserve">5.98228406906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90790939331055</t>
   </si>
   <si>
     <t xml:space="preserve">5.66215038299561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78826332092285</t>
+    <t xml:space="preserve">5.78826284408569</t>
   </si>
   <si>
     <t xml:space="preserve">5.75916004180908</t>
@@ -2855,64 +2855,64 @@
     <t xml:space="preserve">5.78179550170898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83676815032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96934843063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9467134475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9758152961731</t>
+    <t xml:space="preserve">5.83676719665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96934795379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94671249389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97581624984741</t>
   </si>
   <si>
     <t xml:space="preserve">5.83353471755981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71388912200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76886177062988</t>
+    <t xml:space="preserve">5.71388864517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76886129379272</t>
   </si>
   <si>
     <t xml:space="preserve">5.77532911300659</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49723386764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38405466079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51663541793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81413221359253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93054485321045</t>
+    <t xml:space="preserve">5.49723291397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38405513763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51663494110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81413173675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93054437637329</t>
   </si>
   <si>
     <t xml:space="preserve">5.7720947265625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56190729141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62011241912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5845422744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47136402130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55867338180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48106575012207</t>
+    <t xml:space="preserve">5.56190633773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62011194229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58454322814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47136449813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55867290496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48106479644775</t>
   </si>
   <si>
     <t xml:space="preserve">5.40669059753418</t>
@@ -2924,13 +2924,13 @@
     <t xml:space="preserve">5.22560548782349</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19326877593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17386722564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94751024246216</t>
+    <t xml:space="preserve">5.19326829910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17386674880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.947509765625</t>
   </si>
   <si>
     <t xml:space="preserve">4.81169605255127</t>
@@ -2942,16 +2942,16 @@
     <t xml:space="preserve">4.7211537361145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97984647750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18033409118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33554935455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42932605743408</t>
+    <t xml:space="preserve">4.97984600067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18033456802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33554983139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42932653427124</t>
   </si>
   <si>
     <t xml:space="preserve">5.36465311050415</t>
@@ -2960,28 +2960,28 @@
     <t xml:space="preserve">5.40022325515747</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7268238067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94347906112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25391054153442</t>
+    <t xml:space="preserve">5.72682332992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94347953796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25391101837158</t>
   </si>
   <si>
     <t xml:space="preserve">6.70015668869019</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2862491607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09222793579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67508411407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63304758071899</t>
+    <t xml:space="preserve">6.28624820709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09222841262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67508459091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63304710388184</t>
   </si>
   <si>
     <t xml:space="preserve">5.78502941131592</t>
@@ -2993,13 +2993,13 @@
     <t xml:space="preserve">5.82059955596924</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7332911491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58777666091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53603744506836</t>
+    <t xml:space="preserve">5.73329067230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58777618408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53603839874268</t>
   </si>
   <si>
     <t xml:space="preserve">5.3969898223877</t>
@@ -3011,22 +3011,22 @@
     <t xml:space="preserve">5.37435436248779</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49399995803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52956962585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51340103149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64598178863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75269317626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86587142944336</t>
+    <t xml:space="preserve">5.49399948120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52957010269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5134015083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64598274230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75269365310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86587190628052</t>
   </si>
   <si>
     <t xml:space="preserve">5.80119895935059</t>
@@ -3044,10 +3044,10 @@
     <t xml:space="preserve">6.34768724441528</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39942646026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19570446014404</t>
+    <t xml:space="preserve">6.39942693710327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1957049369812</t>
   </si>
   <si>
     <t xml:space="preserve">6.05989170074463</t>
@@ -3059,7 +3059,7 @@
     <t xml:space="preserve">5.77856206893921</t>
   </si>
   <si>
-    <t xml:space="preserve">5.607177734375</t>
+    <t xml:space="preserve">5.60717821121216</t>
   </si>
   <si>
     <t xml:space="preserve">5.60394430160522</t>
@@ -3071,76 +3071,76 @@
     <t xml:space="preserve">5.81736612319946</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68478584289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93377828598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91114330291748</t>
+    <t xml:space="preserve">5.68478631973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93377780914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91114282608032</t>
   </si>
   <si>
     <t xml:space="preserve">5.94024658203125</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82383346557617</t>
+    <t xml:space="preserve">5.82383394241333</t>
   </si>
   <si>
     <t xml:space="preserve">5.79473066329956</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8982081413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73652458190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74945878982544</t>
+    <t xml:space="preserve">5.89820718765259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73652410507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7494592666626</t>
   </si>
   <si>
     <t xml:space="preserve">5.79796457290649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63951539993286</t>
+    <t xml:space="preserve">5.63951444625854</t>
   </si>
   <si>
     <t xml:space="preserve">5.59101009368896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58130931854248</t>
+    <t xml:space="preserve">5.58130884170532</t>
   </si>
   <si>
     <t xml:space="preserve">5.70418787002563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70742130279541</t>
+    <t xml:space="preserve">5.70742177963257</t>
   </si>
   <si>
     <t xml:space="preserve">5.66538429260254</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69448757171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88203954696655</t>
+    <t xml:space="preserve">5.69448709487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88204002380371</t>
   </si>
   <si>
     <t xml:space="preserve">5.80443239212036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7106556892395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50693464279175</t>
+    <t xml:space="preserve">5.71065521240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50693416595459</t>
   </si>
   <si>
     <t xml:space="preserve">5.39052200317383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33878374099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43255996704102</t>
+    <t xml:space="preserve">5.33878326416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43255949020386</t>
   </si>
   <si>
     <t xml:space="preserve">5.30321311950684</t>
@@ -3149,25 +3149,25 @@
     <t xml:space="preserve">5.31938219070435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21267032623291</t>
+    <t xml:space="preserve">5.21267080307007</t>
   </si>
   <si>
     <t xml:space="preserve">5.21590375900269</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2288384437561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34201669692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26764249801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32261562347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29997873306274</t>
+    <t xml:space="preserve">5.22883939743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34201765060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26764297485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3226146697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2999792098999</t>
   </si>
   <si>
     <t xml:space="preserve">5.21913766860962</t>
@@ -3176,25 +3176,25 @@
     <t xml:space="preserve">5.07362270355225</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12212753295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07685661315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07039022445679</t>
+    <t xml:space="preserve">5.12212800979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07685613632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07038974761963</t>
   </si>
   <si>
     <t xml:space="preserve">5.10919332504272</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20296907424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0412859916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99601554870605</t>
+    <t xml:space="preserve">5.20296955108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04128646850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9960150718689</t>
   </si>
   <si>
     <t xml:space="preserve">4.92164087295532</t>
@@ -3206,52 +3206,52 @@
     <t xml:space="preserve">4.82463121414185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50773096084595</t>
+    <t xml:space="preserve">4.50773143768311</t>
   </si>
   <si>
     <t xml:space="preserve">4.36221647262573</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45275926589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58857297897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7825927734375</t>
+    <t xml:space="preserve">4.4527587890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58857250213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78259325027466</t>
   </si>
   <si>
     <t xml:space="preserve">4.89900493621826</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82786464691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79229402542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13829612731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14799737930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25794219970703</t>
+    <t xml:space="preserve">4.82786417007446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7922945022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13829660415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14799690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25794124603271</t>
   </si>
   <si>
     <t xml:space="preserve">5.23530673980713</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65891647338867</t>
+    <t xml:space="preserve">5.65891599655151</t>
   </si>
   <si>
     <t xml:space="preserve">5.84323596954346</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85940408706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07606029510498</t>
+    <t xml:space="preserve">5.85940313339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07605934143066</t>
   </si>
   <si>
     <t xml:space="preserve">6.00815200805664</t>
@@ -3260,46 +3260,46 @@
     <t xml:space="preserve">5.97904920578003</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98875141143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90467500686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17630290985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2991828918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31858491897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34445381164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21834135055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19247198104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13103103637695</t>
+    <t xml:space="preserve">5.98875093460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90467548370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17630338668823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29918241500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31858539581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34445428848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21834087371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19247055053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13103151321411</t>
   </si>
   <si>
     <t xml:space="preserve">6.05665731430054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10516166687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10192918777466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04048919677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03725576400757</t>
+    <t xml:space="preserve">6.10516214370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10193014144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0404896736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03725528717041</t>
   </si>
   <si>
     <t xml:space="preserve">6.06635856628418</t>
@@ -3314,13 +3314,13 @@
     <t xml:space="preserve">5.99198484420776</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98551750183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02431964874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01138687133789</t>
+    <t xml:space="preserve">5.9855170249939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02432060241699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01138639450073</t>
   </si>
   <si>
     <t xml:space="preserve">5.97258234024048</t>
@@ -3329,10 +3329,10 @@
     <t xml:space="preserve">5.73005723953247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73975801467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64921522140503</t>
+    <t xml:space="preserve">5.7397575378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64921569824219</t>
   </si>
   <si>
     <t xml:space="preserve">5.55543947219849</t>
@@ -3341,22 +3341,22 @@
     <t xml:space="preserve">5.36788702011108</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46813106536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41639137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72358989715576</t>
+    <t xml:space="preserve">5.46813058853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41639184951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72359037399292</t>
   </si>
   <si>
     <t xml:space="preserve">6.07282590866089</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26037931442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39619255065918</t>
+    <t xml:space="preserve">6.26037883758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39619302749634</t>
   </si>
   <si>
     <t xml:space="preserve">6.75836324691772</t>
@@ -3365,34 +3365,34 @@
     <t xml:space="preserve">6.67428731918335</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75189542770386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66782093048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66135311126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58374547958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64195156097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69369029998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90064477920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80363464355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97178554534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83597135543823</t>
+    <t xml:space="preserve">6.75189590454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6678204536438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66135358810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5837459564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64195203781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69368934631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90064573287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.803635597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9717845916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83597183227539</t>
   </si>
   <si>
     <t xml:space="preserve">6.85537433624268</t>
@@ -3401,52 +3401,52 @@
     <t xml:space="preserve">6.78423357009888</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2110767364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19167470932007</t>
+    <t xml:space="preserve">7.21107578277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19167327880859</t>
   </si>
   <si>
     <t xml:space="preserve">7.23694610595703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42449808120728</t>
+    <t xml:space="preserve">7.42449903488159</t>
   </si>
   <si>
     <t xml:space="preserve">7.48270463943481</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39216136932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41156387329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16580438613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19814205169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24987983703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35335826873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36629247665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27575016021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32102108001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34689044952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15287113189697</t>
+    <t xml:space="preserve">7.39216089248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41156339645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16580486297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19814157485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24988031387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35335779190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36629152297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27575063705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32102060317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34688949584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15287065505981</t>
   </si>
   <si>
     <t xml:space="preserve">7.49563980102539</t>
@@ -3455,7 +3455,7 @@
     <t xml:space="preserve">7.43743276596069</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3986291885376</t>
+    <t xml:space="preserve">7.39862966537476</t>
   </si>
   <si>
     <t xml:space="preserve">7.3598256111145</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">7.08173036575317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26928234100342</t>
+    <t xml:space="preserve">7.26928281784058</t>
   </si>
   <si>
     <t xml:space="preserve">7.46330213546753</t>
@@ -3473,31 +3473,31 @@
     <t xml:space="preserve">7.51504135131836</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46976947784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44390058517456</t>
+    <t xml:space="preserve">7.4697699546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44390153884888</t>
   </si>
   <si>
     <t xml:space="preserve">7.47623777389526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52797603607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95482063293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69612693786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11650276184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43986892700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46574020385742</t>
+    <t xml:space="preserve">7.52797555923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95482015609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69612598419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11650371551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43987083435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46573829650879</t>
   </si>
   <si>
     <t xml:space="preserve">8.40106678009033</t>
@@ -3509,7 +3509,7 @@
     <t xml:space="preserve">8.18764400482178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05183029174805</t>
+    <t xml:space="preserve">8.05182933807373</t>
   </si>
   <si>
     <t xml:space="preserve">8.22644805908203</t>
@@ -3521,31 +3521,31 @@
     <t xml:space="preserve">8.34932708740234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42046928405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38166427612305</t>
+    <t xml:space="preserve">8.4204683303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38166332244873</t>
   </si>
   <si>
     <t xml:space="preserve">8.50454235076904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14884090423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01546192169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90551853179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64682579040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59508514404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51100921630859</t>
+    <t xml:space="preserve">8.14883995056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01546287536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.905517578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64682483673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59508609771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51101112365723</t>
   </si>
   <si>
     <t xml:space="preserve">8.29112148284912</t>
@@ -3554,67 +3554,67 @@
     <t xml:space="preserve">8.78910636901855</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23291492462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35579395294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96372318267822</t>
+    <t xml:space="preserve">8.23291397094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35579490661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96372413635254</t>
   </si>
   <si>
     <t xml:space="preserve">8.98312568664551</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98959255218506</t>
+    <t xml:space="preserve">8.98959350585938</t>
   </si>
   <si>
     <t xml:space="preserve">9.07366847991943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00252914428711</t>
+    <t xml:space="preserve">9.00252723693848</t>
   </si>
   <si>
     <t xml:space="preserve">8.99606037139893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06720066070557</t>
+    <t xml:space="preserve">9.0672025680542</t>
   </si>
   <si>
     <t xml:space="preserve">9.19654750823975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46817588806152</t>
+    <t xml:space="preserve">9.46817684173584</t>
   </si>
   <si>
     <t xml:space="preserve">9.42290496826172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37763500213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39056873321533</t>
+    <t xml:space="preserve">9.3776330947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39056777954102</t>
   </si>
   <si>
     <t xml:space="preserve">9.46170902252197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20948123931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36469745635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49404525756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48110866546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.565185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81094360351562</t>
+    <t xml:space="preserve">9.20948314666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36469841003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49404430389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48110961914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56518650054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81094551086426</t>
   </si>
   <si>
     <t xml:space="preserve">10.0437688827515</t>
@@ -3626,67 +3626,67 @@
     <t xml:space="preserve">10.3283309936523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4059381484985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4447431564331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.244255065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7616415023804</t>
+    <t xml:space="preserve">10.4059391021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4447441101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2442560195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7616405487061</t>
   </si>
   <si>
     <t xml:space="preserve">10.8263158798218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1173467636108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5611553192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9685964584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5934925079346</t>
+    <t xml:space="preserve">11.1173458099365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5611543655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9685974121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5934915542603</t>
   </si>
   <si>
     <t xml:space="preserve">10.8133811950684</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6775674819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6581649780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8198480606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6840333938599</t>
+    <t xml:space="preserve">10.6775665283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6581659317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8198471069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6840353012085</t>
   </si>
   <si>
     <t xml:space="preserve">11.0074014663696</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0009346008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2567691802979</t>
+    <t xml:space="preserve">11.0009317398071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2567701339722</t>
   </si>
   <si>
     <t xml:space="preserve">11.2291116714478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0908231735229</t>
+    <t xml:space="preserve">11.0908222198486</t>
   </si>
   <si>
     <t xml:space="preserve">10.9110450744629</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0078477859497</t>
+    <t xml:space="preserve">11.0078468322754</t>
   </si>
   <si>
     <t xml:space="preserve">11.1046504974365</t>
@@ -3704,16 +3704,16 @@
     <t xml:space="preserve">11.3051710128784</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5056896209717</t>
+    <t xml:space="preserve">11.5056886672974</t>
   </si>
   <si>
     <t xml:space="preserve">11.5748348236084</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5955791473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6854658126831</t>
+    <t xml:space="preserve">11.5955801010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6854677200317</t>
   </si>
   <si>
     <t xml:space="preserve">11.6508951187134</t>
@@ -3725,22 +3725,22 @@
     <t xml:space="preserve">11.7131242752075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6923828125</t>
+    <t xml:space="preserve">11.6923818588257</t>
   </si>
   <si>
     <t xml:space="preserve">11.6301507949829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5402641296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2636833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1392240524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.828070640564</t>
+    <t xml:space="preserve">11.5402631759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2636842727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1392230987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8280725479126</t>
   </si>
   <si>
     <t xml:space="preserve">10.9456176757812</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">10.4961776733398</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97067642211914</t>
+    <t xml:space="preserve">9.97067737579346</t>
   </si>
   <si>
     <t xml:space="preserve">10.1020517349243</t>
@@ -3764,7 +3764,7 @@
     <t xml:space="preserve">10.2057695388794</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6828689575195</t>
+    <t xml:space="preserve">10.6828680038452</t>
   </si>
   <si>
     <t xml:space="preserve">10.5445785522461</t>
@@ -3776,58 +3776,58 @@
     <t xml:space="preserve">10.8419017791748</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9940176010132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8764734268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9663600921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9179592132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8211574554443</t>
+    <t xml:space="preserve">10.9940185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8764724731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9663610458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9179601669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.82115650177</t>
   </si>
   <si>
     <t xml:space="preserve">10.5653219223022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7381830215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.049334526062</t>
+    <t xml:space="preserve">10.7381839752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0493335723877</t>
   </si>
   <si>
     <t xml:space="preserve">11.0355062484741</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7546129226685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8030128479004</t>
+    <t xml:space="preserve">11.7546110153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8030109405518</t>
   </si>
   <si>
     <t xml:space="preserve">12.0934209823608</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2317113876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1487369537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9413022994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1210784912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0795917510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2593688964844</t>
+    <t xml:space="preserve">12.23171043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1487379074097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9413042068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1210794448853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0795927047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2593679428101</t>
   </si>
   <si>
     <t xml:space="preserve">12.4184017181396</t>
@@ -3839,16 +3839,16 @@
     <t xml:space="preserve">12.6050910949707</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7572107315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3285121917725</t>
+    <t xml:space="preserve">12.7572116851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3285150527954</t>
   </si>
   <si>
     <t xml:space="preserve">12.2870264053345</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6880664825439</t>
+    <t xml:space="preserve">12.6880655288696</t>
   </si>
   <si>
     <t xml:space="preserve">12.5705194473267</t>
@@ -3857,64 +3857,64 @@
     <t xml:space="preserve">11.851414680481</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2455396652222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3561716079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3769149780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2662830352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2040519714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.639666557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4806318283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3907442092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7364673614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2757987976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1885089874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3129692077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9352712631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9905862808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7554950714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7969827651978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.967246055603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6215209960938</t>
+    <t xml:space="preserve">12.2455387115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3561706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.376914024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.266282081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2040529251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6396656036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4806299209595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3907432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7364664077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2757978439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1885080337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.312967300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9352703094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9905881881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7554969787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7969818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9672441482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6215200424194</t>
   </si>
   <si>
     <t xml:space="preserve">12.6811513900757</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3380289077759</t>
+    <t xml:space="preserve">13.3380279541016</t>
   </si>
   <si>
     <t xml:space="preserve">13.0960206985474</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">12.335428237915</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5774335861206</t>
+    <t xml:space="preserve">12.5774354934692</t>
   </si>
   <si>
     <t xml:space="preserve">12.3492574691772</t>
@@ -3935,52 +3935,52 @@
     <t xml:space="preserve">10.7589273452759</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7615261077881</t>
+    <t xml:space="preserve">11.7615242004395</t>
   </si>
   <si>
     <t xml:space="preserve">11.0285911560059</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3674011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8652420043945</t>
+    <t xml:space="preserve">11.3674001693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8652429580688</t>
   </si>
   <si>
     <t xml:space="preserve">12.1694812774658</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8056135177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7157249450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7433824539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0614490509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9992170333862</t>
+    <t xml:space="preserve">12.8056125640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7157230377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7433815002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0614471435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9992179870605</t>
   </si>
   <si>
     <t xml:space="preserve">12.8885850906372</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0337896347046</t>
+    <t xml:space="preserve">13.0337905883789</t>
   </si>
   <si>
     <t xml:space="preserve">13.0683622360229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9093294143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0199632644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2731971740723</t>
+    <t xml:space="preserve">12.9093284606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.019962310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2731962203979</t>
   </si>
   <si>
     <t xml:space="preserve">12.6465797424316</t>
@@ -3989,13 +3989,13 @@
     <t xml:space="preserve">12.4944610595703</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5428619384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2524547576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5566911697388</t>
+    <t xml:space="preserve">12.5428638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2524538040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5566921234131</t>
   </si>
   <si>
     <t xml:space="preserve">11.955132484436</t>
@@ -4004,46 +4004,46 @@
     <t xml:space="preserve">12.0865068435669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9205589294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3466567993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5817489624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0242757797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3008546829224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0381059646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.579309463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5939350128174</t>
+    <t xml:space="preserve">11.9205598831177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3466577529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5817499160767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0242767333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.300856590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.038104057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5793075561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5939359664917</t>
   </si>
   <si>
     <t xml:space="preserve">12.5208005905151</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7694597244263</t>
+    <t xml:space="preserve">12.7694616317749</t>
   </si>
   <si>
     <t xml:space="preserve">12.6743841171265</t>
   </si>
   <si>
-    <t xml:space="preserve">12.747519493103</t>
+    <t xml:space="preserve">12.7475185394287</t>
   </si>
   <si>
     <t xml:space="preserve">12.4184093475342</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3964710235596</t>
+    <t xml:space="preserve">12.3964691162109</t>
   </si>
   <si>
     <t xml:space="preserve">12.3745288848877</t>
@@ -4052,13 +4052,13 @@
     <t xml:space="preserve">12.3452730178833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3525876998901</t>
+    <t xml:space="preserve">12.3525867462158</t>
   </si>
   <si>
     <t xml:space="preserve">12.140495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9795970916748</t>
+    <t xml:space="preserve">11.9795961380005</t>
   </si>
   <si>
     <t xml:space="preserve">11.7455625534058</t>
@@ -4070,13 +4070,13 @@
     <t xml:space="preserve">10.4803190231323</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5900211334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9630136489868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4583787918091</t>
+    <t xml:space="preserve">10.5900230407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9630126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4583797454834</t>
   </si>
   <si>
     <t xml:space="preserve">10.4437503814697</t>
@@ -4088,13 +4088,13 @@
     <t xml:space="preserve">10.5095729827881</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5022583007812</t>
+    <t xml:space="preserve">10.5022592544556</t>
   </si>
   <si>
     <t xml:space="preserve">10.2389707565308</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4949464797974</t>
+    <t xml:space="preserve">10.494945526123</t>
   </si>
   <si>
     <t xml:space="preserve">10.429123878479</t>
@@ -4103,13 +4103,13 @@
     <t xml:space="preserve">10.3998689651489</t>
   </si>
   <si>
-    <t xml:space="preserve">10.209716796875</t>
+    <t xml:space="preserve">10.2097177505493</t>
   </si>
   <si>
     <t xml:space="preserve">9.88060760498047</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75627708435059</t>
+    <t xml:space="preserve">9.7562780380249</t>
   </si>
   <si>
     <t xml:space="preserve">9.70508193969727</t>
@@ -4124,10 +4124,10 @@
     <t xml:space="preserve">9.43448066711426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69777011871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41254043579102</t>
+    <t xml:space="preserve">9.69776916503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4125394821167</t>
   </si>
   <si>
     <t xml:space="preserve">9.46373462677002</t>
@@ -4136,7 +4136,7 @@
     <t xml:space="preserve">9.06149005889893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62267589569092</t>
+    <t xml:space="preserve">8.62267684936523</t>
   </si>
   <si>
     <t xml:space="preserve">8.82745552062988</t>
@@ -4145,10 +4145,10 @@
     <t xml:space="preserve">8.97372722625732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20775985717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24432945251465</t>
+    <t xml:space="preserve">9.20776176452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24432849884033</t>
   </si>
   <si>
     <t xml:space="preserve">9.18582057952881</t>
@@ -4157,28 +4157,28 @@
     <t xml:space="preserve">9.25895595550537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5368709564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21507549285889</t>
+    <t xml:space="preserve">9.53687000274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21507453918457</t>
   </si>
   <si>
     <t xml:space="preserve">9.36865901947021</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39791393280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5807523727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68314075469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55881118774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95374393463135</t>
+    <t xml:space="preserve">9.39791297912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58075141906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68314170837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55881023406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95374298095703</t>
   </si>
   <si>
     <t xml:space="preserve">10.0195646286011</t>
@@ -4190,43 +4190,43 @@
     <t xml:space="preserve">9.72702312469482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47104835510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57343864440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80747222900391</t>
+    <t xml:space="preserve">9.47104930877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57343769073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80747127532959</t>
   </si>
   <si>
     <t xml:space="preserve">9.97568416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49298858642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10537147521973</t>
+    <t xml:space="preserve">9.49298763275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10537052154541</t>
   </si>
   <si>
     <t xml:space="preserve">9.22238731384277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20044612884521</t>
+    <t xml:space="preserve">9.20044708251953</t>
   </si>
   <si>
     <t xml:space="preserve">9.06880283355713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82014179229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75432014465332</t>
+    <t xml:space="preserve">8.82014274597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75432109832764</t>
   </si>
   <si>
     <t xml:space="preserve">8.81282901763916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7396936416626</t>
+    <t xml:space="preserve">8.73969268798828</t>
   </si>
   <si>
     <t xml:space="preserve">8.51297378540039</t>
@@ -4244,55 +4244,55 @@
     <t xml:space="preserve">8.27893924713135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35207653045654</t>
+    <t xml:space="preserve">8.35207557678223</t>
   </si>
   <si>
     <t xml:space="preserve">8.54222774505615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01760959625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02492237091064</t>
+    <t xml:space="preserve">9.01760864257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02492141723633</t>
   </si>
   <si>
     <t xml:space="preserve">9.14925289154053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94447231292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89327716827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59342193603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63730335235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34476089477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35938835144043</t>
+    <t xml:space="preserve">8.94447135925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89327812194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59342288970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63730430603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34476184844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35938739776611</t>
   </si>
   <si>
     <t xml:space="preserve">8.22043132781982</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13266849517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86938142776489</t>
+    <t xml:space="preserve">8.13266754150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86938047409058</t>
   </si>
   <si>
     <t xml:space="preserve">8.32282161712646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41789722442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33013439178467</t>
+    <t xml:space="preserve">8.4178991317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33013343811035</t>
   </si>
   <si>
     <t xml:space="preserve">8.24237251281738</t>
@@ -4301,7 +4301,7 @@
     <t xml:space="preserve">8.14729690551758</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07416152954102</t>
+    <t xml:space="preserve">8.0741605758667</t>
   </si>
   <si>
     <t xml:space="preserve">8.1619234085083</t>
@@ -4310,13 +4310,13 @@
     <t xml:space="preserve">8.04490661621094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05221939086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2862548828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26431274414062</t>
+    <t xml:space="preserve">8.05222034454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28625202178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26431179046631</t>
   </si>
   <si>
     <t xml:space="preserve">8.30088138580322</t>
@@ -4325,49 +4325,49 @@
     <t xml:space="preserve">8.38864421844482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48371887207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56416797637939</t>
+    <t xml:space="preserve">8.48371982574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56416893005371</t>
   </si>
   <si>
     <t xml:space="preserve">8.71775245666504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88596343994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.922532081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56612491607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52955722808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84403991699219</t>
+    <t xml:space="preserve">8.88596534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92253303527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56612396240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52955627441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8440408706665</t>
   </si>
   <si>
     <t xml:space="preserve">10.0488195419312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1804637908936</t>
+    <t xml:space="preserve">10.1804628372192</t>
   </si>
   <si>
     <t xml:space="preserve">10.1512088775635</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1146421432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0049381256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3340463638306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2789545059204</t>
+    <t xml:space="preserve">10.1146411895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0049390792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3340482711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2789535522461</t>
   </si>
   <si>
     <t xml:space="preserve">10.3104362487793</t>
@@ -4376,28 +4376,28 @@
     <t xml:space="preserve">10.3261766433716</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3576574325562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3497886657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.389142036438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2553415298462</t>
+    <t xml:space="preserve">10.3576593399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3497877120972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3891410827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2553405761719</t>
   </si>
   <si>
     <t xml:space="preserve">10.2710828781128</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2002487182617</t>
+    <t xml:space="preserve">10.2002477645874</t>
   </si>
   <si>
     <t xml:space="preserve">10.0428371429443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86968326568604</t>
+    <t xml:space="preserve">9.86968517303467</t>
   </si>
   <si>
     <t xml:space="preserve">9.88542556762695</t>
@@ -4409,13 +4409,13 @@
     <t xml:space="preserve">9.96413135528564</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1608963012695</t>
+    <t xml:space="preserve">10.1608953475952</t>
   </si>
   <si>
     <t xml:space="preserve">10.1845073699951</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0034837722778</t>
+    <t xml:space="preserve">10.0034847259521</t>
   </si>
   <si>
     <t xml:space="preserve">10.0900592803955</t>
@@ -4436,25 +4436,25 @@
     <t xml:space="preserve">10.4678468704224</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4757175445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5780334472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7433166503906</t>
+    <t xml:space="preserve">10.47571849823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5780353546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7433156967163</t>
   </si>
   <si>
     <t xml:space="preserve">11.003044128418</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0345268249512</t>
+    <t xml:space="preserve">11.0345287322998</t>
   </si>
   <si>
     <t xml:space="preserve">11.0423974990845</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1998100280762</t>
+    <t xml:space="preserve">11.1998081207275</t>
   </si>
   <si>
     <t xml:space="preserve">11.2234210968018</t>
@@ -4469,19 +4469,19 @@
     <t xml:space="preserve">11.3493499755859</t>
   </si>
   <si>
-    <t xml:space="preserve">11.341480255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3099975585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1919393539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4123153686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3965721130371</t>
+    <t xml:space="preserve">11.3414793014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3099966049194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1919384002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4123134613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3965730667114</t>
   </si>
   <si>
     <t xml:space="preserve">11.2155504226685</t>
@@ -4490,25 +4490,25 @@
     <t xml:space="preserve">11.4280557632446</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4752788543701</t>
+    <t xml:space="preserve">11.4752798080444</t>
   </si>
   <si>
     <t xml:space="preserve">11.8294544219971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0813121795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1678886413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3725233078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3095588684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4040050506592</t>
+    <t xml:space="preserve">12.0813131332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1678876876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3725242614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3095579147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4040040969849</t>
   </si>
   <si>
     <t xml:space="preserve">12.5220632553101</t>
@@ -4520,16 +4520,16 @@
     <t xml:space="preserve">12.7266988754272</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8368854522705</t>
+    <t xml:space="preserve">12.8368864059448</t>
   </si>
   <si>
     <t xml:space="preserve">12.8132743835449</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5378046035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3882637023926</t>
+    <t xml:space="preserve">12.537805557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3882646560669</t>
   </si>
   <si>
     <t xml:space="preserve">12.9077205657959</t>
@@ -4541,7 +4541,7 @@
     <t xml:space="preserve">12.5063228607178</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2465934753418</t>
+    <t xml:space="preserve">12.2465944290161</t>
   </si>
   <si>
     <t xml:space="preserve">12.1049242019653</t>
@@ -4553,49 +4553,49 @@
     <t xml:space="preserve">12.2308530807495</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3016881942749</t>
+    <t xml:space="preserve">12.3016872406006</t>
   </si>
   <si>
     <t xml:space="preserve">12.3253002166748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9160308837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4516677856445</t>
+    <t xml:space="preserve">11.9160299301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4516668319702</t>
   </si>
   <si>
     <t xml:space="preserve">11.6563024520874</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1132335662842</t>
+    <t xml:space="preserve">11.1132326126099</t>
   </si>
   <si>
     <t xml:space="preserve">11.1289749145508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0974931716919</t>
+    <t xml:space="preserve">11.0974922180176</t>
   </si>
   <si>
     <t xml:space="preserve">11.0266571044922</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8062801361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8456344604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7118339538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8613758087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.995174407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9873046875</t>
+    <t xml:space="preserve">10.8062810897827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8456335067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7118349075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8613748550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9951753616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9873037338257</t>
   </si>
   <si>
     <t xml:space="preserve">10.908597946167</t>
@@ -4610,13 +4610,13 @@
     <t xml:space="preserve">11.585467338562</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5225028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7743606567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8766784667969</t>
+    <t xml:space="preserve">11.5225038528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.774359703064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8766775131226</t>
   </si>
   <si>
     <t xml:space="preserve">11.8137130737305</t>
@@ -4631,13 +4631,13 @@
     <t xml:space="preserve">11.9632530212402</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9002895355225</t>
+    <t xml:space="preserve">11.9002885818481</t>
   </si>
   <si>
     <t xml:space="preserve">11.9789953231812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5697250366211</t>
+    <t xml:space="preserve">11.5697259902954</t>
   </si>
   <si>
     <t xml:space="preserve">11.6012077331543</t>
@@ -4646,7 +4646,7 @@
     <t xml:space="preserve">11.8058433532715</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9317712783813</t>
+    <t xml:space="preserve">11.9317722320557</t>
   </si>
   <si>
     <t xml:space="preserve">11.3257389068604</t>
@@ -4661,7 +4661,7 @@
     <t xml:space="preserve">11.912278175354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8475370407104</t>
+    <t xml:space="preserve">11.8475379943848</t>
   </si>
   <si>
     <t xml:space="preserve">11.6614084243774</t>
@@ -4676,10 +4676,10 @@
     <t xml:space="preserve">11.7666120529175</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4995565414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3296117782593</t>
+    <t xml:space="preserve">11.4995574951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3296127319336</t>
   </si>
   <si>
     <t xml:space="preserve">11.5076494216919</t>
@@ -4694,10 +4694,10 @@
     <t xml:space="preserve">11.5966672897339</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5885744094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5400190353394</t>
+    <t xml:space="preserve">11.5885753631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5400199890137</t>
   </si>
   <si>
     <t xml:space="preserve">11.4429092407227</t>
@@ -4715,10 +4715,10 @@
     <t xml:space="preserve">11.4186305999756</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3781671524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3700752258301</t>
+    <t xml:space="preserve">11.3781681060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3700761795044</t>
   </si>
   <si>
     <t xml:space="preserve">11.5723896026611</t>
@@ -4763,22 +4763,22 @@
     <t xml:space="preserve">12.090313911438</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1712417602539</t>
+    <t xml:space="preserve">12.1712408065796</t>
   </si>
   <si>
     <t xml:space="preserve">12.2521677017212</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4221115112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3816480636597</t>
+    <t xml:space="preserve">12.4221105575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3816471099854</t>
   </si>
   <si>
     <t xml:space="preserve">12.3411846160889</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3249998092651</t>
+    <t xml:space="preserve">12.3249988555908</t>
   </si>
   <si>
     <t xml:space="preserve">12.3007211685181</t>
@@ -4796,7 +4796,7 @@
     <t xml:space="preserve">12.9966831207275</t>
   </si>
   <si>
-    <t xml:space="preserve">12.745813369751</t>
+    <t xml:space="preserve">12.7458143234253</t>
   </si>
   <si>
     <t xml:space="preserve">12.5354070663452</t>
@@ -4808,19 +4808,19 @@
     <t xml:space="preserve">13.1909055709839</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1261653900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8429250717163</t>
+    <t xml:space="preserve">13.1261644363403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.842924118042</t>
   </si>
   <si>
     <t xml:space="preserve">12.9562215805054</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9804992675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0290536880493</t>
+    <t xml:space="preserve">12.9805002212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0290546417236</t>
   </si>
   <si>
     <t xml:space="preserve">13.0937957763672</t>
@@ -4841,7 +4841,7 @@
     <t xml:space="preserve">12.9238510131836</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0452394485474</t>
+    <t xml:space="preserve">13.0452404022217</t>
   </si>
   <si>
     <t xml:space="preserve">13.0776100158691</t>
@@ -4862,10 +4862,10 @@
     <t xml:space="preserve">12.6810731887817</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5677757263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4787578582764</t>
+    <t xml:space="preserve">12.5677766799927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4787588119507</t>
   </si>
   <si>
     <t xml:space="preserve">12.7539072036743</t>
@@ -4877,13 +4877,13 @@
     <t xml:space="preserve">12.5839624404907</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5758695602417</t>
+    <t xml:space="preserve">12.575870513916</t>
   </si>
   <si>
     <t xml:space="preserve">12.672981262207</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7943696975708</t>
+    <t xml:space="preserve">12.7943706512451</t>
   </si>
   <si>
     <t xml:space="preserve">12.8752956390381</t>
@@ -4901,19 +4901,19 @@
     <t xml:space="preserve">12.9400358200073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1504430770874</t>
+    <t xml:space="preserve">13.1504421234131</t>
   </si>
   <si>
     <t xml:space="preserve">13.3365716934204</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5874423980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4903326034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2880163192749</t>
+    <t xml:space="preserve">13.587441444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4903316497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2880172729492</t>
   </si>
   <si>
     <t xml:space="preserve">13.3203859329224</t>
@@ -4931,7 +4931,7 @@
     <t xml:space="preserve">12.2036113739014</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4544820785522</t>
+    <t xml:space="preserve">12.4544811248779</t>
   </si>
   <si>
     <t xml:space="preserve">12.8995723724365</t>
@@ -4943,13 +4943,13 @@
     <t xml:space="preserve">13.2151832580566</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5388870239258</t>
+    <t xml:space="preserve">13.5388860702515</t>
   </si>
   <si>
     <t xml:space="preserve">13.4174976348877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4579610824585</t>
+    <t xml:space="preserve">13.4579601287842</t>
   </si>
   <si>
     <t xml:space="preserve">13.5955333709717</t>
@@ -4958,19 +4958,19 @@
     <t xml:space="preserve">14.0163478851318</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8221273422241</t>
+    <t xml:space="preserve">13.8221263885498</t>
   </si>
   <si>
     <t xml:space="preserve">13.9435157775879</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8140335083008</t>
+    <t xml:space="preserve">13.8140354156494</t>
   </si>
   <si>
     <t xml:space="preserve">13.7573871612549</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9597015380859</t>
+    <t xml:space="preserve">13.9597024917603</t>
   </si>
   <si>
     <t xml:space="preserve">13.8814220428467</t>
@@ -4979,22 +4979,22 @@
     <t xml:space="preserve">13.5770053863525</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7248649597168</t>
+    <t xml:space="preserve">13.7248659133911</t>
   </si>
   <si>
     <t xml:space="preserve">13.6900749206543</t>
   </si>
   <si>
-    <t xml:space="preserve">13.750958442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4900283813477</t>
+    <t xml:space="preserve">13.7509593963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.490029335022</t>
   </si>
   <si>
     <t xml:space="preserve">13.5248193740845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6987714767456</t>
+    <t xml:space="preserve">13.6987724304199</t>
   </si>
   <si>
     <t xml:space="preserve">13.6552839279175</t>
@@ -5003,7 +5003,7 @@
     <t xml:space="preserve">13.8553295135498</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6726789474487</t>
+    <t xml:space="preserve">13.672679901123</t>
   </si>
   <si>
     <t xml:space="preserve">13.7857484817505</t>
@@ -5015,7 +5015,7 @@
     <t xml:space="preserve">13.8205394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1336545944214</t>
+    <t xml:space="preserve">14.1336536407471</t>
   </si>
   <si>
     <t xml:space="preserve">13.9683980941772</t>
@@ -5042,7 +5042,7 @@
     <t xml:space="preserve">13.9336090087891</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3423976898193</t>
+    <t xml:space="preserve">14.342396736145</t>
   </si>
   <si>
     <t xml:space="preserve">14.0379791259766</t>
@@ -5051,7 +5051,7 @@
     <t xml:space="preserve">14.011887550354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5161218643188</t>
+    <t xml:space="preserve">13.5161228179932</t>
   </si>
   <si>
     <t xml:space="preserve">13.620493888855</t>
@@ -5072,13 +5072,13 @@
     <t xml:space="preserve">13.9249114990234</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8031444549561</t>
+    <t xml:space="preserve">13.8031435012817</t>
   </si>
   <si>
     <t xml:space="preserve">14.0466775894165</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0640735626221</t>
+    <t xml:space="preserve">14.0640726089478</t>
   </si>
   <si>
     <t xml:space="preserve">14.2641172409058</t>
@@ -5096,16 +5096,16 @@
     <t xml:space="preserve">14.4032802581787</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2815132141113</t>
+    <t xml:space="preserve">14.2815141677856</t>
   </si>
   <si>
     <t xml:space="preserve">14.3076066970825</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3858861923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6033267974854</t>
+    <t xml:space="preserve">14.3858852386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.603325843811</t>
   </si>
   <si>
     <t xml:space="preserve">14.5598363876343</t>
@@ -5114,16 +5114,16 @@
     <t xml:space="preserve">14.7598829269409</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9686269760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8294630050659</t>
+    <t xml:space="preserve">14.9686260223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8294639587402</t>
   </si>
   <si>
     <t xml:space="preserve">14.6990003585815</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6207208633423</t>
+    <t xml:space="preserve">14.620719909668</t>
   </si>
   <si>
     <t xml:space="preserve">14.7337913513184</t>
@@ -5135,7 +5135,7 @@
     <t xml:space="preserve">14.6903018951416</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8990440368652</t>
+    <t xml:space="preserve">14.8990459442139</t>
   </si>
   <si>
     <t xml:space="preserve">14.8381624221802</t>
@@ -5147,13 +5147,13 @@
     <t xml:space="preserve">14.7250928878784</t>
   </si>
   <si>
-    <t xml:space="preserve">14.672908782959</t>
+    <t xml:space="preserve">14.6729078292847</t>
   </si>
   <si>
     <t xml:space="preserve">15.0121145248413</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0816955566406</t>
+    <t xml:space="preserve">15.0816965103149</t>
   </si>
   <si>
     <t xml:space="preserve">15.1164855957031</t>
@@ -5162,10 +5162,10 @@
     <t xml:space="preserve">15.4469966888428</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6122531890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7079248428345</t>
+    <t xml:space="preserve">15.6122512817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7079267501831</t>
   </si>
   <si>
     <t xml:space="preserve">15.7862033843994</t>
@@ -5177,7 +5177,7 @@
     <t xml:space="preserve">15.9862489700317</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1341094970703</t>
+    <t xml:space="preserve">16.1341075897217</t>
   </si>
   <si>
     <t xml:space="preserve">15.9253644943237</t>
@@ -5186,7 +5186,7 @@
     <t xml:space="preserve">16.0471343994141</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6124782562256</t>
+    <t xml:space="preserve">16.6124801635742</t>
   </si>
   <si>
     <t xml:space="preserve">17.2995929718018</t>
@@ -5198,7 +5198,7 @@
     <t xml:space="preserve">16.9951763153076</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9777812957764</t>
+    <t xml:space="preserve">16.9777793884277</t>
   </si>
   <si>
     <t xml:space="preserve">17.1952209472656</t>
@@ -5219,7 +5219,7 @@
     <t xml:space="preserve">18.038890838623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8127536773682</t>
+    <t xml:space="preserve">17.8127517700195</t>
   </si>
   <si>
     <t xml:space="preserve">18.3172149658203</t>
@@ -5234,16 +5234,16 @@
     <t xml:space="preserve">18.3346118927002</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5433540344238</t>
+    <t xml:space="preserve">18.5433559417725</t>
   </si>
   <si>
     <t xml:space="preserve">18.6651210784912</t>
   </si>
   <si>
-    <t xml:space="preserve">18.717306137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9519157409668</t>
+    <t xml:space="preserve">18.7173080444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9519138336182</t>
   </si>
   <si>
     <t xml:space="preserve">18.0736827850342</t>
@@ -71398,7 +71398,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6911342593</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>106359</v>
@@ -71419,6 +71419,32 @@
         <v>2014</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.6911111111</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>170222</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>22.5200004577637</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>22.2199993133545</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>22.4200000762939</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>22.3999996185303</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>1960</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IF.MI.xlsx
+++ b/data/IF.MI.xlsx
@@ -47,88 +47,88 @@
     <t xml:space="preserve">15.3903484344482</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3232393264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5458927154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3613405227661</t>
+    <t xml:space="preserve">15.3232374191284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5458908081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3613414764404</t>
   </si>
   <si>
     <t xml:space="preserve">14.3781175613403</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4284505844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1767930984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8646602630615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8524293899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4955596923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6409635543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.434042930603</t>
+    <t xml:space="preserve">14.4284496307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1767911911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8646593093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8524332046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4955615997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6409664154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4340438842773</t>
   </si>
   <si>
     <t xml:space="preserve">15.3735704421997</t>
   </si>
   <si>
-    <t xml:space="preserve">15.395941734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9384059906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.943995475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5637111663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1061744689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0502529144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7706327438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1722440719604</t>
+    <t xml:space="preserve">15.3959398269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.938404083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9440002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5637130737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1061782836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0502548217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7706298828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1722431182861</t>
   </si>
   <si>
     <t xml:space="preserve">14.9597291946411</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5402994155884</t>
+    <t xml:space="preserve">14.5402984619141</t>
   </si>
   <si>
     <t xml:space="preserve">13.0583066940308</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0974559783936</t>
+    <t xml:space="preserve">13.0974540710449</t>
   </si>
   <si>
     <t xml:space="preserve">13.7405843734741</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7685432434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8244686126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.534704208374</t>
+    <t xml:space="preserve">13.7685461044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8244676589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5347089767456</t>
   </si>
   <si>
     <t xml:space="preserve">14.4396362304688</t>
@@ -137,79 +137,79 @@
     <t xml:space="preserve">14.3501577377319</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2718620300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.333381652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4350872039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9765100479126</t>
+    <t xml:space="preserve">14.2718629837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3333797454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4350862503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9765129089355</t>
   </si>
   <si>
     <t xml:space="preserve">14.741626739502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2057991027832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0995445251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0436182022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4966020584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2840900421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9876909255981</t>
+    <t xml:space="preserve">15.2057981491089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0995426177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0436162948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4966077804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2840890884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9876956939697</t>
   </si>
   <si>
     <t xml:space="preserve">14.4452276229858</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5570755004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1656064987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7192573547363</t>
+    <t xml:space="preserve">14.5570774078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1656055450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4843740463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.719256401062</t>
   </si>
   <si>
     <t xml:space="preserve">15.1834297180176</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3791646957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9999227523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2348041534424</t>
+    <t xml:space="preserve">15.3791637420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9999217987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.234806060791</t>
   </si>
   <si>
     <t xml:space="preserve">16.0949935913086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.966365814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1173629760742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1403388977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4849739074707</t>
+    <t xml:space="preserve">15.9663639068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1173648834229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1403369903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4849720001221</t>
   </si>
   <si>
     <t xml:space="preserve">16.7204704284668</t>
@@ -218,37 +218,37 @@
     <t xml:space="preserve">16.4160461425781</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8473978042603</t>
+    <t xml:space="preserve">15.8473997116089</t>
   </si>
   <si>
     <t xml:space="preserve">16.3815803527832</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6004152297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6808261871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.784218788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8876075744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.634877204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2787523269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4280958175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2385482788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1409034729004</t>
+    <t xml:space="preserve">15.6004123687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6808233261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.784215927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8876066207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6348743438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2787561416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4280977249146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2385454177856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1408996582031</t>
   </si>
   <si>
     <t xml:space="preserve">15.3821449279785</t>
@@ -257,25 +257,25 @@
     <t xml:space="preserve">14.9570980072021</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8479614257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.58948802948</t>
+    <t xml:space="preserve">14.8479623794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5894870758057</t>
   </si>
   <si>
     <t xml:space="preserve">14.6239500045776</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7043657302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.555025100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3482456207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1184892654419</t>
+    <t xml:space="preserve">14.7043647766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5550231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3482446670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1184854507446</t>
   </si>
   <si>
     <t xml:space="preserve">13.8427810668945</t>
@@ -284,10 +284,10 @@
     <t xml:space="preserve">14.1644401550293</t>
   </si>
   <si>
-    <t xml:space="preserve">13.670464515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6417474746704</t>
+    <t xml:space="preserve">13.6704626083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6417446136475</t>
   </si>
   <si>
     <t xml:space="preserve">13.325831413269</t>
@@ -299,52 +299,52 @@
     <t xml:space="preserve">12.8376007080078</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9811973571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7629270553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4814796447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6365642547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6882572174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3493690490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5791254043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9352464675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5148191452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9576568603516</t>
+    <t xml:space="preserve">12.9811964035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7629299163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4814786911011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6365633010864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6882591247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3493700027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5791234970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.935245513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.514817237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9576587677002</t>
   </si>
   <si>
     <t xml:space="preserve">13.7853412628174</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5613298416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.664719581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3488054275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2683935165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3602962493896</t>
+    <t xml:space="preserve">13.5613327026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6647205352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3488082885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2683925628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.360294342041</t>
   </si>
   <si>
     <t xml:space="preserve">13.1535139083862</t>
@@ -353,10 +353,10 @@
     <t xml:space="preserve">12.9639644622803</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7801599502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.550407409668</t>
+    <t xml:space="preserve">12.7801609039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5504064559937</t>
   </si>
   <si>
     <t xml:space="preserve">12.205771446228</t>
@@ -365,7 +365,7 @@
     <t xml:space="preserve">12.0564308166504</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9185781478882</t>
+    <t xml:space="preserve">11.9185771942139</t>
   </si>
   <si>
     <t xml:space="preserve">11.6084070205688</t>
@@ -374,313 +374,313 @@
     <t xml:space="preserve">12.2287483215332</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6537952423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5963573455811</t>
+    <t xml:space="preserve">12.6537961959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5963563919067</t>
   </si>
   <si>
     <t xml:space="preserve">12.9869403839111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1196146011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1781778335571</t>
+    <t xml:space="preserve">12.1196117401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1781768798828</t>
   </si>
   <si>
     <t xml:space="preserve">10.2643365859985</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3217735290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4251670837402</t>
+    <t xml:space="preserve">10.3217754364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4251642227173</t>
   </si>
   <si>
     <t xml:space="preserve">10.4366540908813</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4538860321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93693351745605</t>
+    <t xml:space="preserve">10.4538850784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93693542480469</t>
   </si>
   <si>
     <t xml:space="preserve">9.58081340789795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5693244934082</t>
+    <t xml:space="preserve">9.56932640075684</t>
   </si>
   <si>
     <t xml:space="preserve">9.7301549911499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76461791992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8272399902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2810039520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4877843856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3269557952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5165042877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2580308914185</t>
+    <t xml:space="preserve">9.76461696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8272380828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2810068130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4877853393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3269567489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5165033340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2580280303955</t>
   </si>
   <si>
     <t xml:space="preserve">11.4992733001709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2293109893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0455055236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8617010116577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6032266616821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9995527267456</t>
+    <t xml:space="preserve">11.2293081283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0455045700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.861701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6032247543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9995546340942</t>
   </si>
   <si>
     <t xml:space="preserve">11.7175407409668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4188556671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5796871185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1144323348999</t>
+    <t xml:space="preserve">11.4188585281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5796880722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1144332885742</t>
   </si>
   <si>
     <t xml:space="preserve">11.1431503295898</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6026630401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.740517616272</t>
+    <t xml:space="preserve">11.6026639938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7405157089233</t>
   </si>
   <si>
     <t xml:space="preserve">11.4016275405884</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6543588638306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5567111968994</t>
+    <t xml:space="preserve">11.6543607711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5567121505737</t>
   </si>
   <si>
     <t xml:space="preserve">11.4533224105835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3843946456909</t>
+    <t xml:space="preserve">11.3843965530396</t>
   </si>
   <si>
     <t xml:space="preserve">11.2867479324341</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9880685806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9765796661377</t>
+    <t xml:space="preserve">10.9880647659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.976580619812</t>
   </si>
   <si>
     <t xml:space="preserve">11.0397615432739</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0282726287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0971994400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9708337783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9650907516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1201753616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2063341140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1891031265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4303455352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8324213027954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3149080276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.395320892334</t>
+    <t xml:space="preserve">11.0282735824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0972013473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9708347320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9650897979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1201763153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.206335067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1891021728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4303464889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8324184417725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3149070739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3953189849854</t>
   </si>
   <si>
     <t xml:space="preserve">11.9587831497192</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6945667266846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7749805450439</t>
+    <t xml:space="preserve">11.6945676803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7749814987183</t>
   </si>
   <si>
     <t xml:space="preserve">11.6715898513794</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6888217926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5739440917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7692346572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0621747970581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0219688415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6601028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5107593536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4935283660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5279932022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7060527801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7577486038208</t>
+    <t xml:space="preserve">11.6888208389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5739431381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7692365646362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0621757507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0219678878784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6601009368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.510763168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4935293197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5279912948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7060518264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7577466964722</t>
   </si>
   <si>
     <t xml:space="preserve">12.0277118682861</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4068088531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4349641799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6991834640503</t>
+    <t xml:space="preserve">12.4068078994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.434965133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6991853713989</t>
   </si>
   <si>
     <t xml:space="preserve">13.7279043197632</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8657560348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9519157409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1759281158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3712196350098</t>
+    <t xml:space="preserve">13.865758895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9519176483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.175929069519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3712167739868</t>
   </si>
   <si>
     <t xml:space="preserve">14.4631223678589</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8824272155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9628410339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1064367294312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2270603179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1351566314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9456090927124</t>
+    <t xml:space="preserve">14.8824253082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9628400802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1064386367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2270584106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1351585388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9456081390381</t>
   </si>
   <si>
     <t xml:space="preserve">14.7158536911011</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7330827713013</t>
+    <t xml:space="preserve">14.7330856323242</t>
   </si>
   <si>
     <t xml:space="preserve">14.5090732574463</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5952320098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5435380935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3827085494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0725383758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0610513687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6474905014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6876964569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.590048789978</t>
+    <t xml:space="preserve">14.595232963562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5435371398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3827095031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0725355148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0610475540161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6474876403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6876955032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5900506973267</t>
   </si>
   <si>
     <t xml:space="preserve">13.5383539199829</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0501232147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1190519332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1822328567505</t>
+    <t xml:space="preserve">13.050124168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1190509796143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1822366714478</t>
   </si>
   <si>
     <t xml:space="preserve">12.7514429092407</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2109518051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4407081604004</t>
+    <t xml:space="preserve">13.2109508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4407091140747</t>
   </si>
   <si>
     <t xml:space="preserve">13.4234781265259</t>
@@ -689,172 +689,172 @@
     <t xml:space="preserve">13.285623550415</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1414632797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2735757827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1931600570679</t>
+    <t xml:space="preserve">14.1414642333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2735738754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1931591033936</t>
   </si>
   <si>
     <t xml:space="preserve">14.35973072052</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9398679733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6871347427368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3884515762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.474609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7847814559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9341201782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2213144302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5831813812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4970207214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4510717391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3361959457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8364753723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9915599822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2959861755371</t>
+    <t xml:space="preserve">14.939866065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6871309280396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3884496688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4746084213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7847776412964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.934118270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2213153839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.583179473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4970235824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4510698318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3361949920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8364744186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9915618896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2959852218628</t>
   </si>
   <si>
     <t xml:space="preserve">15.163875579834</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0375118255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0892086029053</t>
+    <t xml:space="preserve">15.0375127792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0892095565796</t>
   </si>
   <si>
     <t xml:space="preserve">15.0719747543335</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8307294845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6469259262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5320482254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2333641052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5263061523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4171724319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3941955566406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.048999786377</t>
+    <t xml:space="preserve">14.8307285308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6469230651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5320491790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2333650588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5263051986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4171705245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3941946029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0489988327026</t>
   </si>
   <si>
     <t xml:space="preserve">14.7618036270142</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6584138870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8766822814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3936319351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8531436920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8416547775269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0369491577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5079498291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9559726715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0880794525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6343097686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6113376617432</t>
+    <t xml:space="preserve">14.6584129333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8766841888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3936347961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8531446456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8416557312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0369472503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5079460144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9559707641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0880813598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6343116760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6113357543945</t>
   </si>
   <si>
     <t xml:space="preserve">16.0828990936279</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8870429992676</t>
+    <t xml:space="preserve">16.8870449066162</t>
   </si>
   <si>
     <t xml:space="preserve">16.9444808959961</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3465576171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.484411239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5935440063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0593605041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1684951782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6911888122559</t>
+    <t xml:space="preserve">17.3465557098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4844093322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.593542098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.059362411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.168493270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6911907196045</t>
   </si>
   <si>
     <t xml:space="preserve">17.9152011871338</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7365779876709</t>
+    <t xml:space="preserve">18.7365798950195</t>
   </si>
   <si>
     <t xml:space="preserve">19.5522117614746</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8164291381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9944915771484</t>
+    <t xml:space="preserve">19.816427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9944896697998</t>
   </si>
   <si>
     <t xml:space="preserve">20.942232131958</t>
@@ -863,85 +863,85 @@
     <t xml:space="preserve">20.522928237915</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8503341674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7354507446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6780166625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6492938995361</t>
+    <t xml:space="preserve">20.8503284454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7354488372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6780128479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6492919921875</t>
   </si>
   <si>
     <t xml:space="preserve">20.3218936920166</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5631370544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6378078460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8388423919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8216114044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6090908050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1088047027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4132328033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2409172058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1777324676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.022647857666</t>
+    <t xml:space="preserve">20.5631351470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6378040313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8388404846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8216094970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6090869903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1088066101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4132347106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2409152984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1777305603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0226440429688</t>
   </si>
   <si>
     <t xml:space="preserve">20.9594650268555</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3098411560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5855464935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3155822753906</t>
+    <t xml:space="preserve">21.3098392486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5855522155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3155860900879</t>
   </si>
   <si>
     <t xml:space="preserve">22.2690715789795</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1369590759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9818782806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2288646697998</t>
+    <t xml:space="preserve">22.1369647979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9818801879883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2288665771484</t>
   </si>
   <si>
     <t xml:space="preserve">22.7458114624023</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9335060119629</t>
+    <t xml:space="preserve">22.9335021972656</t>
   </si>
   <si>
     <t xml:space="preserve">22.5815849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3938941955566</t>
+    <t xml:space="preserve">22.3938961029053</t>
   </si>
   <si>
     <t xml:space="preserve">21.4671688079834</t>
@@ -950,28 +950,28 @@
     <t xml:space="preserve">20.4583282470703</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1035194396973</t>
+    <t xml:space="preserve">21.1035175323486</t>
   </si>
   <si>
     <t xml:space="preserve">20.8161163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6342906951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.692943572998</t>
+    <t xml:space="preserve">20.6342926025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6929416656494</t>
   </si>
   <si>
     <t xml:space="preserve">20.587366104126</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2969951629639</t>
+    <t xml:space="preserve">19.2969913482666</t>
   </si>
   <si>
     <t xml:space="preserve">18.5872840881348</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5433330535889</t>
+    <t xml:space="preserve">19.5433368682861</t>
   </si>
   <si>
     <t xml:space="preserve">19.9656410217285</t>
@@ -980,40 +980,40 @@
     <t xml:space="preserve">20.4817905426025</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4700603485107</t>
+    <t xml:space="preserve">20.4700622558594</t>
   </si>
   <si>
     <t xml:space="preserve">20.5287132263184</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4114074707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2706394195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3058280944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7955436706543</t>
+    <t xml:space="preserve">20.4114036560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2706413269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3058319091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7955455780029</t>
   </si>
   <si>
     <t xml:space="preserve">19.607852935791</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8835277557373</t>
+    <t xml:space="preserve">19.8835258483887</t>
   </si>
   <si>
     <t xml:space="preserve">20.2471771240234</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0594882965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1767921447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7515983581543</t>
+    <t xml:space="preserve">20.0594863891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.176794052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.751594543457</t>
   </si>
   <si>
     <t xml:space="preserve">20.6988105773926</t>
@@ -1022,124 +1022,124 @@
     <t xml:space="preserve">20.3527526855469</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5521755218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5052528381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7046756744385</t>
+    <t xml:space="preserve">20.5521774291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5052509307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7046699523926</t>
   </si>
   <si>
     <t xml:space="preserve">20.4407329559326</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1474666595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0477561950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0008316040039</t>
+    <t xml:space="preserve">20.1474628448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0477542877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0008296966553</t>
   </si>
   <si>
     <t xml:space="preserve">20.4876575469971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6694850921631</t>
+    <t xml:space="preserve">20.6694812774658</t>
   </si>
   <si>
     <t xml:space="preserve">20.6460208892822</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8630390167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.933422088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0096740722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9275569915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1152477264404</t>
+    <t xml:space="preserve">20.8630409240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9334201812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.009672164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9275588989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1152496337891</t>
   </si>
   <si>
     <t xml:space="preserve">21.2560176849365</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2912101745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5551509857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7487049102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6313972473145</t>
+    <t xml:space="preserve">21.2912063598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5551490783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7487087249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6313991546631</t>
   </si>
   <si>
     <t xml:space="preserve">21.6079387664795</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6431331634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8366851806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0830326080322</t>
+    <t xml:space="preserve">21.6431312561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8366870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.083028793335</t>
   </si>
   <si>
     <t xml:space="preserve">21.7604351043701</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4642772674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9041805267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6402378082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9686946868896</t>
+    <t xml:space="preserve">22.4642791748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9041786193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6402397155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9686965942383</t>
   </si>
   <si>
     <t xml:space="preserve">22.7575454711914</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2854270935059</t>
+    <t xml:space="preserve">23.2854290008545</t>
   </si>
   <si>
     <t xml:space="preserve">23.4907150268555</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7722492218018</t>
+    <t xml:space="preserve">23.7722511291504</t>
   </si>
   <si>
     <t xml:space="preserve">24.0068626403809</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2708053588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8719577789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1007137298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0479202270508</t>
+    <t xml:space="preserve">24.2708072662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8719615936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1007080078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0479221343994</t>
   </si>
   <si>
     <t xml:space="preserve">23.5435009002686</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5669631958008</t>
+    <t xml:space="preserve">23.566967010498</t>
   </si>
   <si>
     <t xml:space="preserve">24.1593627929688</t>
@@ -1151,190 +1151,190 @@
     <t xml:space="preserve">24.3059978485107</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8543643951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0361938476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8367671966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8191757202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9716739654541</t>
+    <t xml:space="preserve">23.854362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.036190032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8367691040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8191738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9716720581055</t>
   </si>
   <si>
     <t xml:space="preserve">23.7898483276367</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6373481750488</t>
+    <t xml:space="preserve">23.6373462677002</t>
   </si>
   <si>
     <t xml:space="preserve">23.1153316497803</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7077331542969</t>
+    <t xml:space="preserve">23.7077293395996</t>
   </si>
   <si>
     <t xml:space="preserve">23.9012889862061</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1652336120605</t>
+    <t xml:space="preserve">24.1652278900146</t>
   </si>
   <si>
     <t xml:space="preserve">24.5347461700439</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3411922454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0831146240234</t>
+    <t xml:space="preserve">24.3411884307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0831127166748</t>
   </si>
   <si>
     <t xml:space="preserve">24.7400341033936</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7107067108154</t>
+    <t xml:space="preserve">24.7107124328613</t>
   </si>
   <si>
     <t xml:space="preserve">24.4936866760254</t>
   </si>
   <si>
-    <t xml:space="preserve">24.698974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0684947967529</t>
+    <t xml:space="preserve">24.6989727020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0684928894043</t>
   </si>
   <si>
     <t xml:space="preserve">25.7078170776367</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7136821746826</t>
+    <t xml:space="preserve">25.7136783599854</t>
   </si>
   <si>
     <t xml:space="preserve">26.1594467163086</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4937725067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3823299407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5876159667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1301212310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5993461608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8222332000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.133092880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7548217773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0656814575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.2064533233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8984832763672</t>
+    <t xml:space="preserve">26.4937705993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3823318481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5876178741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1301174163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5993423461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8222351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1330947875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7548198699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0656833648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2064514160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8984813690186</t>
   </si>
   <si>
     <t xml:space="preserve">27.7489604949951</t>
   </si>
   <si>
-    <t xml:space="preserve">28.4997158050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8281841278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8927001953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.6580829620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0539512634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9278125762939</t>
+    <t xml:space="preserve">28.4997177124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8281803131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8926944732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.658088684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.053955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9278049468994</t>
   </si>
   <si>
     <t xml:space="preserve">26.5289630889893</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2152118682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6403999328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.537805557251</t>
+    <t xml:space="preserve">27.2152099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6404056549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5378036499023</t>
   </si>
   <si>
     <t xml:space="preserve">27.6316509246826</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6668395996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8428020477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3237609863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5671310424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6023273468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4556884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.502613067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0803050994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8163623809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3060817718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9365615844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5992641448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8954257965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9511051177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8279285430908</t>
+    <t xml:space="preserve">27.666841506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8428039550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3237552642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5671291351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6023235321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4556903839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5026111602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0803089141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8163681030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.306079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9365634918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5992584228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8954200744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9511013031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8279323577881</t>
   </si>
   <si>
     <t xml:space="preserve">23.6021556854248</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7164916992188</t>
+    <t xml:space="preserve">22.7164878845215</t>
   </si>
   <si>
     <t xml:space="preserve">22.7282199859619</t>
@@ -1343,55 +1343,55 @@
     <t xml:space="preserve">22.3176460266113</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9833183288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6754322052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4056301116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6109104156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7927360534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2355270385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5492858886719</t>
+    <t xml:space="preserve">21.9833202362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6754302978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4056262969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.610912322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7927398681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2355289459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5492820739746</t>
   </si>
   <si>
     <t xml:space="preserve">21.5199546813965</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7311115264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8249568939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4495716094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9040927886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4026527404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.877742767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4701480865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1915016174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1093845367432</t>
+    <t xml:space="preserve">21.731107711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8249530792236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4495697021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9040966033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4026508331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8777408599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4701442718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1914978027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1093826293945</t>
   </si>
   <si>
     <t xml:space="preserve">21.0565967559814</t>
@@ -1403,22 +1403,22 @@
     <t xml:space="preserve">22.7047557830811</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9130191802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0449485778809</t>
+    <t xml:space="preserve">23.9130172729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.044942855835</t>
   </si>
   <si>
     <t xml:space="preserve">23.3440799713135</t>
   </si>
   <si>
-    <t xml:space="preserve">23.75465965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7663879394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4496593475342</t>
+    <t xml:space="preserve">23.7546558380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7663898468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4496574401855</t>
   </si>
   <si>
     <t xml:space="preserve">23.520040512085</t>
@@ -1427,10 +1427,10 @@
     <t xml:space="preserve">22.3469696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0273475646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1563873291016</t>
+    <t xml:space="preserve">23.0273494720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1563892364502</t>
   </si>
   <si>
     <t xml:space="preserve">22.8631210327148</t>
@@ -1445,82 +1445,82 @@
     <t xml:space="preserve">22.781005859375</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5229320526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4994697570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2765884399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.945240020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4525470733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0771636962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2208251953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7398662567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2677459716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6489124298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4260311126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7750587463379</t>
+    <t xml:space="preserve">22.5229301452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4994716644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.27659034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9452362060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4525451660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0771656036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2208271026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7398643493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.267749786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6489105224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4260292053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7750568389893</t>
   </si>
   <si>
     <t xml:space="preserve">21.1621723175049</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9158229827881</t>
+    <t xml:space="preserve">20.9158267974854</t>
   </si>
   <si>
     <t xml:space="preserve">21.3733234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3615894317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3264026641846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2794799804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3967838287354</t>
+    <t xml:space="preserve">21.3615951538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3264007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2794780731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3967876434326</t>
   </si>
   <si>
     <t xml:space="preserve">21.0448627471924</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7985191345215</t>
+    <t xml:space="preserve">20.7985172271729</t>
   </si>
   <si>
     <t xml:space="preserve">20.6812114715576</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0125598907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3321838378906</t>
+    <t xml:space="preserve">20.0125637054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.332181930542</t>
   </si>
   <si>
     <t xml:space="preserve">19.015453338623</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3556423187256</t>
+    <t xml:space="preserve">19.3556442260742</t>
   </si>
   <si>
     <t xml:space="preserve">19.0975685119629</t>
@@ -1532,46 +1532,46 @@
     <t xml:space="preserve">20.0712184906006</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9891014099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8394947052002</t>
+    <t xml:space="preserve">19.9891052246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8394908905029</t>
   </si>
   <si>
     <t xml:space="preserve">18.3468055725098</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5227661132812</t>
+    <t xml:space="preserve">18.5227642059326</t>
   </si>
   <si>
     <t xml:space="preserve">19.4377593994141</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2617988586426</t>
+    <t xml:space="preserve">19.2618007659912</t>
   </si>
   <si>
     <t xml:space="preserve">18.9919929504395</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3233432769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3614292144775</t>
+    <t xml:space="preserve">18.3233451843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3614273071289</t>
   </si>
   <si>
     <t xml:space="preserve">18.6987266540527</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9596920013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7221908569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1210289001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2735290527344</t>
+    <t xml:space="preserve">17.9596900939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.722188949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1210308074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2735328674316</t>
   </si>
   <si>
     <t xml:space="preserve">19.4142971038818</t>
@@ -1586,13 +1586,13 @@
     <t xml:space="preserve">19.5785274505615</t>
   </si>
   <si>
-    <t xml:space="preserve">19.813138961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6958332061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3461227416992</t>
+    <t xml:space="preserve">19.8131408691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6958351135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3461208343506</t>
   </si>
   <si>
     <t xml:space="preserve">19.3582210540771</t>
@@ -1601,25 +1601,25 @@
     <t xml:space="preserve">19.1404418945312</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0920448303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1646404266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7816848754883</t>
+    <t xml:space="preserve">19.0920467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1646385192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7816829681396</t>
   </si>
   <si>
     <t xml:space="preserve">19.9752655029297</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2656364440918</t>
+    <t xml:space="preserve">20.2656383514404</t>
   </si>
   <si>
     <t xml:space="preserve">20.435022354126</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6649055480957</t>
+    <t xml:space="preserve">20.6648998260498</t>
   </si>
   <si>
     <t xml:space="preserve">20.3745288848877</t>
@@ -1628,10 +1628,10 @@
     <t xml:space="preserve">20.0236587524414</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5397033691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4429149627686</t>
+    <t xml:space="preserve">19.539701461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4429130554199</t>
   </si>
   <si>
     <t xml:space="preserve">19.6485939025879</t>
@@ -1640,67 +1640,67 @@
     <t xml:space="preserve">19.7211875915527</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9589576721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3298149108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4102993011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0836296081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2288150787354</t>
+    <t xml:space="preserve">18.9589595794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.32981300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4103012084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0836315155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.228816986084</t>
   </si>
   <si>
     <t xml:space="preserve">16.8779487609863</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5149803161621</t>
+    <t xml:space="preserve">16.5149822235107</t>
   </si>
   <si>
     <t xml:space="preserve">15.6075668334961</t>
   </si>
   <si>
-    <t xml:space="preserve">14.167799949646</t>
+    <t xml:space="preserve">14.1677980422974</t>
   </si>
   <si>
     <t xml:space="preserve">12.8853158950806</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1194038391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2282943725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4260835647583</t>
+    <t xml:space="preserve">14.119402885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.22829246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4260816574097</t>
   </si>
   <si>
     <t xml:space="preserve">15.4865760803223</t>
   </si>
   <si>
-    <t xml:space="preserve">15.014720916748</t>
+    <t xml:space="preserve">15.0147190093994</t>
   </si>
   <si>
     <t xml:space="preserve">15.1478099822998</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8332366943359</t>
+    <t xml:space="preserve">14.8332376480103</t>
   </si>
   <si>
     <t xml:space="preserve">14.7001495361328</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2929944992065</t>
+    <t xml:space="preserve">15.2929935455322</t>
   </si>
   <si>
     <t xml:space="preserve">16.1520156860352</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5996742248535</t>
+    <t xml:space="preserve">16.5996761322021</t>
   </si>
   <si>
     <t xml:space="preserve">16.575475692749</t>
@@ -1712,40 +1712,40 @@
     <t xml:space="preserve">16.7932567596436</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2409133911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.732759475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9021453857422</t>
+    <t xml:space="preserve">17.2409152984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7327613830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9021492004395</t>
   </si>
   <si>
     <t xml:space="preserve">16.623872756958</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9705324172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4623775482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.571268081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5954685211182</t>
+    <t xml:space="preserve">15.970531463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4623794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5712690353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5954666137695</t>
   </si>
   <si>
     <t xml:space="preserve">15.6438627243042</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6196632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7890501022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0431251525879</t>
+    <t xml:space="preserve">15.6196622848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7890491485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0431270599365</t>
   </si>
   <si>
     <t xml:space="preserve">16.4060916900635</t>
@@ -1754,40 +1754,40 @@
     <t xml:space="preserve">16.5875759124756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2730026245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9100370407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9947290420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8253440856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6722679138184</t>
+    <t xml:space="preserve">16.2730045318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9100399017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9947328567505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8253469467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6722660064697</t>
   </si>
   <si>
     <t xml:space="preserve">16.9384441375732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2851028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0552234649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2972049713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3576965332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2125110626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3655891418457</t>
+    <t xml:space="preserve">16.2851009368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0552253723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2972030639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3576984405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2125091552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3655862808228</t>
   </si>
   <si>
     <t xml:space="preserve">15.5470724105835</t>
@@ -1796,91 +1796,91 @@
     <t xml:space="preserve">14.6396570205688</t>
   </si>
   <si>
-    <t xml:space="preserve">13.369270324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6838426589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6475439071655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6354475021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2845783233643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0426006317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5102519989014</t>
+    <t xml:space="preserve">13.3692712783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6838417053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6475467681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6354484558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2845773696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0426025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5102510452271</t>
   </si>
   <si>
     <t xml:space="preserve">12.377161026001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4860515594482</t>
+    <t xml:space="preserve">12.4860534667969</t>
   </si>
   <si>
     <t xml:space="preserve">12.4497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2603826522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7885255813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9700088500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9216136932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0909976959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3408651351929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2924709320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2561721801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.764328956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1998872756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6596450805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.526556968689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3571720123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8895225524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5749540328979</t>
+    <t xml:space="preserve">13.2603797912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7885246276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.970009803772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9216117858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0909967422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3408660888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2924699783325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.256175994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7643260955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1998844146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6596431732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5265579223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3571710586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8895244598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5749530792236</t>
   </si>
   <si>
     <t xml:space="preserve">13.6717443466187</t>
   </si>
   <si>
-    <t xml:space="preserve">13.320876121521</t>
+    <t xml:space="preserve">13.3208770751953</t>
   </si>
   <si>
     <t xml:space="preserve">13.3450746536255</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5023574829102</t>
+    <t xml:space="preserve">13.5023584365845</t>
   </si>
   <si>
     <t xml:space="preserve">14.0589075088501</t>
@@ -1889,61 +1889,61 @@
     <t xml:space="preserve">14.4218759536743</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3976774215698</t>
+    <t xml:space="preserve">14.3976755142212</t>
   </si>
   <si>
     <t xml:space="preserve">14.2645893096924</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4339742660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3934707641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7359228134155</t>
+    <t xml:space="preserve">14.4339733123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3934698104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7359209060669</t>
   </si>
   <si>
     <t xml:space="preserve">10.864800453186</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3003625869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6088838577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.977897644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8024654388428</t>
+    <t xml:space="preserve">11.3003616333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6088848114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9778995513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8024663925171</t>
   </si>
   <si>
     <t xml:space="preserve">10.3143014907837</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5865268707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2356605529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86664390563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3264017105103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3022041320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4957866668701</t>
+    <t xml:space="preserve">10.5865278244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2356595993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86664295196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3264007568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3022031784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4957857131958</t>
   </si>
   <si>
     <t xml:space="preserve">9.92108821868896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89689254760742</t>
+    <t xml:space="preserve">9.89689159393311</t>
   </si>
   <si>
     <t xml:space="preserve">9.5339241027832</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">8.9713249206543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06206703186035</t>
+    <t xml:space="preserve">9.06206798553467</t>
   </si>
   <si>
     <t xml:space="preserve">9.40083599090576</t>
@@ -1979,10 +1979,10 @@
     <t xml:space="preserve">10.217511177063</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88479232788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12256145477295</t>
+    <t xml:space="preserve">9.88479328155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12256240844727</t>
   </si>
   <si>
     <t xml:space="preserve">9.21935272216797</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">8.82008934020996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12861061096191</t>
+    <t xml:space="preserve">9.12861156463623</t>
   </si>
   <si>
     <t xml:space="preserve">9.24960041046143</t>
@@ -2000,52 +2000,52 @@
     <t xml:space="preserve">9.36453914642334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58837032318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48552894592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45528030395508</t>
+    <t xml:space="preserve">9.58836841583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48552799224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45528125762939</t>
   </si>
   <si>
     <t xml:space="preserve">9.70935726165771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61256694793701</t>
+    <t xml:space="preserve">9.61256790161133</t>
   </si>
   <si>
     <t xml:space="preserve">9.57022094726562</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8406057357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1370277404785</t>
+    <t xml:space="preserve">10.8406047821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1370258331299</t>
   </si>
   <si>
     <t xml:space="preserve">10.9071483612061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5967836380005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3064136505127</t>
+    <t xml:space="preserve">11.5967855453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3064117431641</t>
   </si>
   <si>
     <t xml:space="preserve">11.00998878479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.96764087677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.513934135437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8285036087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3385000228882</t>
+    <t xml:space="preserve">10.9676427841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5139331817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8285045623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3385009765625</t>
   </si>
   <si>
     <t xml:space="preserve">10.7377634048462</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">10.2840557098389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6409711837769</t>
+    <t xml:space="preserve">10.6409721374512</t>
   </si>
   <si>
     <t xml:space="preserve">11.1007299423218</t>
@@ -2066,13 +2066,13 @@
     <t xml:space="preserve">10.8587532043457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3747978210449</t>
+    <t xml:space="preserve">10.3747968673706</t>
   </si>
   <si>
     <t xml:space="preserve">9.8121976852417</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69120979309082</t>
+    <t xml:space="preserve">9.69121074676514</t>
   </si>
   <si>
     <t xml:space="preserve">9.37058925628662</t>
@@ -2084,13 +2084,13 @@
     <t xml:space="preserve">9.03786849975586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34034156799316</t>
+    <t xml:space="preserve">9.34034061431885</t>
   </si>
   <si>
     <t xml:space="preserve">9.34639072418213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94528675079346</t>
+    <t xml:space="preserve">9.94528579711914</t>
   </si>
   <si>
     <t xml:space="preserve">10.4050445556641</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">10.5562801361084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.62282371521</t>
+    <t xml:space="preserve">10.6228227615356</t>
   </si>
   <si>
     <t xml:space="preserve">10.5804767608643</t>
@@ -2111,22 +2111,22 @@
     <t xml:space="preserve">10.5502300262451</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0239286422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62466526031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1025724411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2296094894409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4655380249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3687467575073</t>
+    <t xml:space="preserve">10.0239295959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62466621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1025705337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2296113967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4655389785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3687477111816</t>
   </si>
   <si>
     <t xml:space="preserve">9.98763275146484</t>
@@ -2135,16 +2135,16 @@
     <t xml:space="preserve">9.96948337554932</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2780046463013</t>
+    <t xml:space="preserve">10.2780055999756</t>
   </si>
   <si>
     <t xml:space="preserve">10.4352912902832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5320825576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1509685516357</t>
+    <t xml:space="preserve">10.5320835113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1509666442871</t>
   </si>
   <si>
     <t xml:space="preserve">10.0299777984619</t>
@@ -2153,85 +2153,85 @@
     <t xml:space="preserve">10.1267690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3445510864258</t>
+    <t xml:space="preserve">10.3445491790771</t>
   </si>
   <si>
     <t xml:space="preserve">10.0662755966187</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64886379241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0946798324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6433382034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0323438644409</t>
+    <t xml:space="preserve">9.64886283874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0946807861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6433372497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0323448181152</t>
   </si>
   <si>
     <t xml:space="preserve">11.3729543685913</t>
   </si>
   <si>
-    <t xml:space="preserve">10.876898765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7014684677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6107263565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5683794021606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.10862159729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3505992889404</t>
+    <t xml:space="preserve">10.8769016265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7014665603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6107244491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5683784484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1086206436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3505983352661</t>
   </si>
   <si>
     <t xml:space="preserve">10.9373950958252</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0341844558716</t>
+    <t xml:space="preserve">11.0341873168945</t>
   </si>
   <si>
     <t xml:space="preserve">11.112829208374</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4818449020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9736909866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54602241516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35848999023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22540187835693</t>
+    <t xml:space="preserve">11.4818439483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9736919403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54602336883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35849094390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22540283203125</t>
   </si>
   <si>
     <t xml:space="preserve">9.11046314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08626461029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13465976715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92898082733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97737503051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95317840576172</t>
+    <t xml:space="preserve">9.08626651763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1346607208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92897987365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97737598419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95317649841309</t>
   </si>
   <si>
     <t xml:space="preserve">8.84428691864014</t>
@@ -2240,46 +2240,46 @@
     <t xml:space="preserve">8.89873218536377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07416534423828</t>
+    <t xml:space="preserve">9.0741662979126</t>
   </si>
   <si>
     <t xml:space="preserve">9.00157260894775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24355030059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4976282119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47947883605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46133041381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38873767852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63676452636719</t>
+    <t xml:space="preserve">9.24354934692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49762725830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47947978973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46133136749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38873672485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6367654800415</t>
   </si>
   <si>
     <t xml:space="preserve">9.68515968322754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71540832519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83034801483154</t>
+    <t xml:space="preserve">9.71540546417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83034706115723</t>
   </si>
   <si>
     <t xml:space="preserve">10.2636585235596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9402904510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65572929382324</t>
+    <t xml:space="preserve">9.94029140472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65573024749756</t>
   </si>
   <si>
     <t xml:space="preserve">9.72686958312988</t>
@@ -2300,46 +2300,46 @@
     <t xml:space="preserve">8.27818584442139</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86427688598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32345867156982</t>
+    <t xml:space="preserve">7.86427736282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32345771789551</t>
   </si>
   <si>
     <t xml:space="preserve">8.37519645690918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31698989868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07123279571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87721252441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90954780578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82547378540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56677913665771</t>
+    <t xml:space="preserve">8.31699085235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0712308883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87721347808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90954923629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82547426223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56677865982056</t>
   </si>
   <si>
     <t xml:space="preserve">7.72199583053589</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59264898300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54091119766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5021071434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37276029586792</t>
+    <t xml:space="preserve">7.59264802932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54090976715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50210666656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37275981903076</t>
   </si>
   <si>
     <t xml:space="preserve">7.31455326080322</t>
@@ -2351,40 +2351,40 @@
     <t xml:space="preserve">7.32748985290527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24341344833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2886848449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52150917053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26281547546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2951512336731</t>
+    <t xml:space="preserve">7.24341297149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28868532180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52150821685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26281499862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29515218734741</t>
   </si>
   <si>
     <t xml:space="preserve">7.25634813308716</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41803169250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70906114578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03242778778076</t>
+    <t xml:space="preserve">7.41803073883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70906162261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03242874145508</t>
   </si>
   <si>
     <t xml:space="preserve">7.84487628936768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70259475708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55384492874146</t>
+    <t xml:space="preserve">7.7025933265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55384588241577</t>
   </si>
   <si>
     <t xml:space="preserve">7.76726722717285</t>
@@ -2396,10 +2396,10 @@
     <t xml:space="preserve">7.67672491073608</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99362468719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18117713928223</t>
+    <t xml:space="preserve">7.99362373352051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18117618560791</t>
   </si>
   <si>
     <t xml:space="preserve">8.70502948760986</t>
@@ -2417,25 +2417,25 @@
     <t xml:space="preserve">8.58215141296387</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57568359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49160766601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55628108978271</t>
+    <t xml:space="preserve">8.57568454742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49160957336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55628204345703</t>
   </si>
   <si>
     <t xml:space="preserve">8.95725727081299</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94432067871094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93785381317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75030040740967</t>
+    <t xml:space="preserve">8.94432163238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9378547668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75030136108398</t>
   </si>
   <si>
     <t xml:space="preserve">8.62742233276367</t>
@@ -2444,10 +2444,10 @@
     <t xml:space="preserve">8.82790946960449</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83437728881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71149921417236</t>
+    <t xml:space="preserve">8.83437633514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71149826049805</t>
   </si>
   <si>
     <t xml:space="preserve">8.60802173614502</t>
@@ -2459,10 +2459,10 @@
     <t xml:space="preserve">8.38813209533691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29758739471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54334831237793</t>
+    <t xml:space="preserve">8.29758930206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54334735870361</t>
   </si>
   <si>
     <t xml:space="preserve">9.02839756011963</t>
@@ -2477,34 +2477,34 @@
     <t xml:space="preserve">9.12540626525879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48514270782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11003494262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87074518203735</t>
+    <t xml:space="preserve">8.48514175415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11003589630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8707447052002</t>
   </si>
   <si>
     <t xml:space="preserve">8.26525211334229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33639335632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43340301513672</t>
+    <t xml:space="preserve">8.33639240264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43340396881104</t>
   </si>
   <si>
     <t xml:space="preserve">8.36872959136963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28465366363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23938179016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56275081634521</t>
+    <t xml:space="preserve">8.28465461730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23938274383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56274890899658</t>
   </si>
   <si>
     <t xml:space="preserve">8.76970386505127</t>
@@ -2513,10 +2513,10 @@
     <t xml:space="preserve">9.02192974090576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13187408447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2224178314209</t>
+    <t xml:space="preserve">9.13187503814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22241592407227</t>
   </si>
   <si>
     <t xml:space="preserve">9.45524120330811</t>
@@ -2528,34 +2528,34 @@
     <t xml:space="preserve">9.50697994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55871868133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58458805084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69453239440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9144229888916</t>
+    <t xml:space="preserve">9.55871772766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58458709716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69453144073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91442108154297</t>
   </si>
   <si>
     <t xml:space="preserve">9.92088890075684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73333740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89502048492432</t>
+    <t xml:space="preserve">9.73333644866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89501953125</t>
   </si>
   <si>
     <t xml:space="preserve">9.90795421600342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67513084411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57812023162842</t>
+    <t xml:space="preserve">9.67512989044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57812118530273</t>
   </si>
   <si>
     <t xml:space="preserve">9.66866397857666</t>
@@ -2564,13 +2564,13 @@
     <t xml:space="preserve">9.90148735046387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70746612548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5199146270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30649375915527</t>
+    <t xml:space="preserve">9.7074670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51991558074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30649280548096</t>
   </si>
   <si>
     <t xml:space="preserve">9.33236217498779</t>
@@ -2579,16 +2579,16 @@
     <t xml:space="preserve">9.43583965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09953689575195</t>
+    <t xml:space="preserve">9.09953784942627</t>
   </si>
   <si>
     <t xml:space="preserve">9.37116622924805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52638244628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79154205322266</t>
+    <t xml:space="preserve">9.52638149261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79154300689697</t>
   </si>
   <si>
     <t xml:space="preserve">9.7398042678833</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">9.87561798095703</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95322513580322</t>
+    <t xml:space="preserve">9.95322608947754</t>
   </si>
   <si>
     <t xml:space="preserve">9.99849700927734</t>
@@ -2609,31 +2609,31 @@
     <t xml:space="preserve">9.94675922393799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77213954925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8820858001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98556232452393</t>
+    <t xml:space="preserve">9.77214050292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88208389282227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98556137084961</t>
   </si>
   <si>
     <t xml:space="preserve">10.224853515625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44877243041992</t>
+    <t xml:space="preserve">9.44877338409424</t>
   </si>
   <si>
     <t xml:space="preserve">9.83034610748291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86915111541748</t>
+    <t xml:space="preserve">9.86915016174316</t>
   </si>
   <si>
     <t xml:space="preserve">10.1925172805786</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2377891540527</t>
+    <t xml:space="preserve">10.2377882003784</t>
   </si>
   <si>
     <t xml:space="preserve">9.62339210510254</t>
@@ -2645,13 +2645,13 @@
     <t xml:space="preserve">9.34529590606689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24182033538818</t>
+    <t xml:space="preserve">9.24181938171387</t>
   </si>
   <si>
     <t xml:space="preserve">9.19007968902588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06073474884033</t>
+    <t xml:space="preserve">9.06073379516602</t>
   </si>
   <si>
     <t xml:space="preserve">9.0801362991333</t>
@@ -2660,7 +2660,7 @@
     <t xml:space="preserve">8.97665882110596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04133129119873</t>
+    <t xml:space="preserve">9.04133319854736</t>
   </si>
   <si>
     <t xml:space="preserve">8.92492008209229</t>
@@ -2669,31 +2669,31 @@
     <t xml:space="preserve">8.7632360458374</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84731197357178</t>
+    <t xml:space="preserve">8.84731292724609</t>
   </si>
   <si>
     <t xml:space="preserve">8.78263854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61448764801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56921672821045</t>
+    <t xml:space="preserve">8.61448669433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56921577453613</t>
   </si>
   <si>
     <t xml:space="preserve">8.67916202545166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86671447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87318134307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81497478485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8602466583252</t>
+    <t xml:space="preserve">8.86671352386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87318229675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81497573852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86024570465088</t>
   </si>
   <si>
     <t xml:space="preserve">9.24828720092773</t>
@@ -2702,58 +2702,58 @@
     <t xml:space="preserve">9.05426692962646</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14480876922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15774440765381</t>
+    <t xml:space="preserve">9.14481067657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23535060882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15774345397949</t>
   </si>
   <si>
     <t xml:space="preserve">9.13834190368652</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26768779754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09307098388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93138790130615</t>
+    <t xml:space="preserve">9.2676887512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09307193756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93138694763184</t>
   </si>
   <si>
     <t xml:space="preserve">9.20301532745361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59105587005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57165431976318</t>
+    <t xml:space="preserve">9.59105396270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57165241241455</t>
   </si>
   <si>
     <t xml:space="preserve">9.51344680786133</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5328483581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32589530944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30002403259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74627208709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47464370727539</t>
+    <t xml:space="preserve">9.53284931182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32589340209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30002593994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74627017974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47464275360107</t>
   </si>
   <si>
     <t xml:space="preserve">9.27415561676025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62985897064209</t>
+    <t xml:space="preserve">9.62985992431641</t>
   </si>
   <si>
     <t xml:space="preserve">9.70100021362305</t>
@@ -2765,46 +2765,46 @@
     <t xml:space="preserve">10.1343116760254</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1278429031372</t>
+    <t xml:space="preserve">10.1278438568115</t>
   </si>
   <si>
     <t xml:space="preserve">10.0696382522583</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1407794952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0049638748169</t>
+    <t xml:space="preserve">10.1407785415649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0049657821655</t>
   </si>
   <si>
     <t xml:space="preserve">10.1472444534302</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35176467895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55225086212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8925838470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40753173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90308141708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88124227523804</t>
+    <t xml:space="preserve">9.35176277160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5522518157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89258289337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40753269195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9030818939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8812427520752</t>
   </si>
   <si>
     <t xml:space="preserve">6.61608123779297</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59667921066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67185163497925</t>
+    <t xml:space="preserve">6.59668016433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67185115814209</t>
   </si>
   <si>
     <t xml:space="preserve">5.93701219558716</t>
@@ -2813,28 +2813,28 @@
     <t xml:space="preserve">5.61364555358887</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44549465179443</t>
+    <t xml:space="preserve">5.44549512863159</t>
   </si>
   <si>
     <t xml:space="preserve">5.45842933654785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43902683258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75592613220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57160758972168</t>
+    <t xml:space="preserve">5.43902778625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75592660903931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57160806655884</t>
   </si>
   <si>
     <t xml:space="preserve">5.84000205993652</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86910486221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98228311538696</t>
+    <t xml:space="preserve">5.86910438537598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9822826385498</t>
   </si>
   <si>
     <t xml:space="preserve">5.90790891647339</t>
@@ -2843,22 +2843,22 @@
     <t xml:space="preserve">5.66215038299561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78826236724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75915956497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70095348358154</t>
+    <t xml:space="preserve">5.78826284408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75916004180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7009539604187</t>
   </si>
   <si>
     <t xml:space="preserve">5.78179550170898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83676719665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96934843063354</t>
+    <t xml:space="preserve">5.83676815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9693489074707</t>
   </si>
   <si>
     <t xml:space="preserve">5.94671297073364</t>
@@ -2867,10 +2867,10 @@
     <t xml:space="preserve">5.9758152961731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83353519439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71388864517212</t>
+    <t xml:space="preserve">5.83353471755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71388912200928</t>
   </si>
   <si>
     <t xml:space="preserve">5.76886177062988</t>
@@ -2882,16 +2882,16 @@
     <t xml:space="preserve">5.49723339080811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38405466079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51663446426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81413173675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93054437637329</t>
+    <t xml:space="preserve">5.38405418395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51663494110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81413316726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93054485321045</t>
   </si>
   <si>
     <t xml:space="preserve">5.77209520339966</t>
@@ -2900,37 +2900,37 @@
     <t xml:space="preserve">5.5619068145752</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62011289596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58454179763794</t>
+    <t xml:space="preserve">5.62011241912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58454275131226</t>
   </si>
   <si>
     <t xml:space="preserve">5.47136402130127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55867290496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48106527328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40669012069702</t>
+    <t xml:space="preserve">5.55867338180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48106479644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40669059753418</t>
   </si>
   <si>
     <t xml:space="preserve">5.32584857940674</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22560501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19326877593994</t>
+    <t xml:space="preserve">5.22560548782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19326782226562</t>
   </si>
   <si>
     <t xml:space="preserve">5.17386674880981</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94751024246216</t>
+    <t xml:space="preserve">4.947509765625</t>
   </si>
   <si>
     <t xml:space="preserve">4.81169605255127</t>
@@ -2942,43 +2942,43 @@
     <t xml:space="preserve">4.72115325927734</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97984600067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18033361434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33554983139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42932653427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36465263366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40022325515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7268238067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94347906112671</t>
+    <t xml:space="preserve">4.97984647750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18033456802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33555030822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42932605743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36465358734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40022277832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72682332992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94347953796387</t>
   </si>
   <si>
     <t xml:space="preserve">6.25391101837158</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70015716552734</t>
+    <t xml:space="preserve">6.70015811920166</t>
   </si>
   <si>
     <t xml:space="preserve">6.28624820709229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09222888946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67508459091187</t>
+    <t xml:space="preserve">6.09222841262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67508506774902</t>
   </si>
   <si>
     <t xml:space="preserve">5.63304758071899</t>
@@ -2987,19 +2987,19 @@
     <t xml:space="preserve">5.78502941131592</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87880611419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82059907913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73329019546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58777570724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53603744506836</t>
+    <t xml:space="preserve">5.87880563735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82059955596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73329067230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58777666091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53603792190552</t>
   </si>
   <si>
     <t xml:space="preserve">5.39698934555054</t>
@@ -3011,28 +3011,28 @@
     <t xml:space="preserve">5.37435388565063</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49399900436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52957057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5134015083313</t>
+    <t xml:space="preserve">5.49399948120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52956962585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51340103149414</t>
   </si>
   <si>
     <t xml:space="preserve">5.64598178863525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75269365310669</t>
+    <t xml:space="preserve">5.75269317626953</t>
   </si>
   <si>
     <t xml:space="preserve">5.86587142944336</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80119848251343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89497423171997</t>
+    <t xml:space="preserve">5.80119752883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89497375488281</t>
   </si>
   <si>
     <t xml:space="preserve">5.875572681427</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">6.39942693710327</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19570589065552</t>
+    <t xml:space="preserve">6.19570541381836</t>
   </si>
   <si>
     <t xml:space="preserve">6.05989122390747</t>
@@ -3056,31 +3056,31 @@
     <t xml:space="preserve">5.91760969161987</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77856206893921</t>
+    <t xml:space="preserve">5.77856254577637</t>
   </si>
   <si>
     <t xml:space="preserve">5.60717821121216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60394430160522</t>
+    <t xml:space="preserve">5.60394382476807</t>
   </si>
   <si>
     <t xml:space="preserve">5.80766487121582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81736707687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68478631973267</t>
+    <t xml:space="preserve">5.81736612319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68478584289551</t>
   </si>
   <si>
     <t xml:space="preserve">5.93377828598022</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91114187240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94024610519409</t>
+    <t xml:space="preserve">5.91114330291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94024562835693</t>
   </si>
   <si>
     <t xml:space="preserve">5.82383394241333</t>
@@ -3089,16 +3089,16 @@
     <t xml:space="preserve">5.79473114013672</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89820766448975</t>
+    <t xml:space="preserve">5.89820861816406</t>
   </si>
   <si>
     <t xml:space="preserve">5.73652458190918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74946022033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79796457290649</t>
+    <t xml:space="preserve">5.74945974349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79796409606934</t>
   </si>
   <si>
     <t xml:space="preserve">5.63951444625854</t>
@@ -3107,16 +3107,16 @@
     <t xml:space="preserve">5.59100961685181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58130836486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70418787002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70742225646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66538381576538</t>
+    <t xml:space="preserve">5.58130884170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70418739318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70742034912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66538429260254</t>
   </si>
   <si>
     <t xml:space="preserve">5.69448709487915</t>
@@ -3125,22 +3125,22 @@
     <t xml:space="preserve">5.88204002380371</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80443239212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71065521240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50693464279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39052200317383</t>
+    <t xml:space="preserve">5.8044319152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7106556892395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50693416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39052248001099</t>
   </si>
   <si>
     <t xml:space="preserve">5.33878374099731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4325590133667</t>
+    <t xml:space="preserve">5.43256044387817</t>
   </si>
   <si>
     <t xml:space="preserve">5.30321311950684</t>
@@ -3149,16 +3149,16 @@
     <t xml:space="preserve">5.31938171386719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21267080307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21590423583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2288384437561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34201717376709</t>
+    <t xml:space="preserve">5.21267127990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21590375900269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22883892059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34201765060425</t>
   </si>
   <si>
     <t xml:space="preserve">5.26764297485352</t>
@@ -3167,40 +3167,40 @@
     <t xml:space="preserve">5.32261514663696</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29997873306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21913814544678</t>
+    <t xml:space="preserve">5.29997968673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21913766860962</t>
   </si>
   <si>
     <t xml:space="preserve">5.07362222671509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1221284866333</t>
+    <t xml:space="preserve">5.12212800979614</t>
   </si>
   <si>
     <t xml:space="preserve">5.07685661315918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07038974761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10919380187988</t>
+    <t xml:space="preserve">5.07038927078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10919332504272</t>
   </si>
   <si>
     <t xml:space="preserve">5.20296955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0412859916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9960150718689</t>
+    <t xml:space="preserve">5.04128646850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99601459503174</t>
   </si>
   <si>
     <t xml:space="preserve">4.92164087295532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81492948532104</t>
+    <t xml:space="preserve">4.8149299621582</t>
   </si>
   <si>
     <t xml:space="preserve">4.82463121414185</t>
@@ -3209,13 +3209,13 @@
     <t xml:space="preserve">4.50773096084595</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36221647262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45275926589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58857297897339</t>
+    <t xml:space="preserve">4.36221599578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45275974273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58857250213623</t>
   </si>
   <si>
     <t xml:space="preserve">4.78259325027466</t>
@@ -3224,31 +3224,31 @@
     <t xml:space="preserve">4.8990044593811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82786464691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79229402542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13829565048218</t>
+    <t xml:space="preserve">4.82786512374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79229354858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13829708099365</t>
   </si>
   <si>
     <t xml:space="preserve">5.14799737930298</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25794172286987</t>
+    <t xml:space="preserve">5.25794219970703</t>
   </si>
   <si>
     <t xml:space="preserve">5.23530626296997</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65891599655151</t>
+    <t xml:space="preserve">5.65891695022583</t>
   </si>
   <si>
     <t xml:space="preserve">5.84323596954346</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85940408706665</t>
+    <t xml:space="preserve">5.85940456390381</t>
   </si>
   <si>
     <t xml:space="preserve">6.07606029510498</t>
@@ -3260,76 +3260,76 @@
     <t xml:space="preserve">5.97905015945435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98875045776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90467500686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17630338668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29918193817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31858491897583</t>
+    <t xml:space="preserve">5.98874998092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90467548370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17630386352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29918241500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31858539581299</t>
   </si>
   <si>
     <t xml:space="preserve">6.34445428848267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21834182739258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19247102737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13103103637695</t>
+    <t xml:space="preserve">6.2183403968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19247150421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13103246688843</t>
   </si>
   <si>
     <t xml:space="preserve">6.05665731430054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10516166687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1019287109375</t>
+    <t xml:space="preserve">6.10516262054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10192918777466</t>
   </si>
   <si>
     <t xml:space="preserve">6.04048919677734</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03725576400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06635856628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88850688934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95318078994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99198436737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9855170249939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02432012557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01138639450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97258281707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73005723953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73975801467896</t>
+    <t xml:space="preserve">6.03725528717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06635904312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88850736618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95317983627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99198484420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98551654815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02432107925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01138591766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97258186340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73005628585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73975849151611</t>
   </si>
   <si>
     <t xml:space="preserve">5.64921522140503</t>
@@ -3338,160 +3338,160 @@
     <t xml:space="preserve">5.55543947219849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36788702011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46813011169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41639137268066</t>
+    <t xml:space="preserve">5.36788606643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46813106536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41639184951782</t>
   </si>
   <si>
     <t xml:space="preserve">5.72358989715576</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07282543182373</t>
+    <t xml:space="preserve">6.07282686233521</t>
   </si>
   <si>
     <t xml:space="preserve">6.26037883758545</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39619207382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75836372375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67428779602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75189542770386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66782188415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66135358810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58374500274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64195156097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69368982315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90064334869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80363368988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97178506851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83597183227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85537481307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78423261642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2110767364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19167470932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23694562911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42449808120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48270511627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39216232299805</t>
+    <t xml:space="preserve">6.39619302749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75836277008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67428827285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75189590454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6678204536438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66135311126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58374643325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64195251464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69369029998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90064430236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80363512039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97178554534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83597135543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85537338256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78423309326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21107625961304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19167423248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23694658279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42449903488159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48270559310913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39216279983521</t>
   </si>
   <si>
     <t xml:space="preserve">7.41156339645386</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16580581665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19814205169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24988079071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35335874557495</t>
+    <t xml:space="preserve">7.16580533981323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19814157485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24988031387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35335779190063</t>
   </si>
   <si>
     <t xml:space="preserve">7.36629247665405</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27575016021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32102155685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34688997268677</t>
+    <t xml:space="preserve">7.27575063705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32102251052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34689044952393</t>
   </si>
   <si>
     <t xml:space="preserve">7.15287065505981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49564027786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43743324279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3986291885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3598256111145</t>
+    <t xml:space="preserve">7.49563932418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43743276596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39862966537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35982513427734</t>
   </si>
   <si>
     <t xml:space="preserve">7.08172988891602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26928234100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46330261230469</t>
+    <t xml:space="preserve">7.26928329467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46330165863037</t>
   </si>
   <si>
     <t xml:space="preserve">7.5150408744812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46976900100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4439001083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47623777389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52797698974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95482015609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69612693786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11650371551514</t>
+    <t xml:space="preserve">7.4697699546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44390106201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47623729705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52797651290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9548192024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69612598419189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1165018081665</t>
   </si>
   <si>
     <t xml:space="preserve">8.43986988067627</t>
@@ -3500,43 +3500,43 @@
     <t xml:space="preserve">8.46573925018311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40106582641602</t>
+    <t xml:space="preserve">8.40106678009033</t>
   </si>
   <si>
     <t xml:space="preserve">8.25878524780273</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18764400482178</t>
+    <t xml:space="preserve">8.18764209747314</t>
   </si>
   <si>
     <t xml:space="preserve">8.05182933807373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22644901275635</t>
+    <t xml:space="preserve">8.22644805908203</t>
   </si>
   <si>
     <t xml:space="preserve">8.31052398681641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34932708740234</t>
+    <t xml:space="preserve">8.34932613372803</t>
   </si>
   <si>
     <t xml:space="preserve">8.42046928405762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38166332244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50454235076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14884090423584</t>
+    <t xml:space="preserve">8.38166427612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50454425811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14883995056152</t>
   </si>
   <si>
     <t xml:space="preserve">9.01546192169189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90551853179932</t>
+    <t xml:space="preserve">8.90551948547363</t>
   </si>
   <si>
     <t xml:space="preserve">8.64682483673096</t>
@@ -3545,13 +3545,13 @@
     <t xml:space="preserve">8.59508609771729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51101112365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29112148284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78910636901855</t>
+    <t xml:space="preserve">8.51100921630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2911205291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78910541534424</t>
   </si>
   <si>
     <t xml:space="preserve">8.23291492462158</t>
@@ -3560,13 +3560,13 @@
     <t xml:space="preserve">8.35579490661621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96372413635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98312664031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98959350585938</t>
+    <t xml:space="preserve">8.96372222900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98312568664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98959445953369</t>
   </si>
   <si>
     <t xml:space="preserve">9.07366847991943</t>
@@ -3578,34 +3578,34 @@
     <t xml:space="preserve">8.99606037139893</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06720161437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19654846191406</t>
+    <t xml:space="preserve">9.0672025680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19654941558838</t>
   </si>
   <si>
     <t xml:space="preserve">9.46817588806152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4229040145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37763404846191</t>
+    <t xml:space="preserve">9.42290496826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3776330947876</t>
   </si>
   <si>
     <t xml:space="preserve">9.39056873321533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46170806884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20948123931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36469745635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49404525756836</t>
+    <t xml:space="preserve">9.46170997619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20948219299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36469841003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49404621124268</t>
   </si>
   <si>
     <t xml:space="preserve">9.48111057281494</t>
@@ -3617,10 +3617,10 @@
     <t xml:space="preserve">9.81094455718994</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0437688827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0890407562256</t>
+    <t xml:space="preserve">10.0437679290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0890398025513</t>
   </si>
   <si>
     <t xml:space="preserve">10.3283319473267</t>
@@ -3629,31 +3629,31 @@
     <t xml:space="preserve">10.4059391021729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4447422027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2442569732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7616424560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8263158798218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1173458099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5611562728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9685964584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5934915542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.813380241394</t>
+    <t xml:space="preserve">10.4447412490845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2442560195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.761643409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8263149261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1173467636108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5611553192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9685974121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5934906005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8133811950684</t>
   </si>
   <si>
     <t xml:space="preserve">10.6775674819946</t>
@@ -3662,31 +3662,31 @@
     <t xml:space="preserve">10.6581649780273</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8198490142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6840343475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0074014663696</t>
+    <t xml:space="preserve">10.8198480606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6840353012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0074005126953</t>
   </si>
   <si>
     <t xml:space="preserve">11.0009346008301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2567691802979</t>
+    <t xml:space="preserve">11.2567701339722</t>
   </si>
   <si>
     <t xml:space="preserve">11.2291116714478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0908231735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9110450744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.007848739624</t>
+    <t xml:space="preserve">11.0908212661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9110469818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0078477859497</t>
   </si>
   <si>
     <t xml:space="preserve">11.1046514511108</t>
@@ -3698,37 +3698,37 @@
     <t xml:space="preserve">11.056248664856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1945400238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3051710128784</t>
+    <t xml:space="preserve">11.1945390701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3051700592041</t>
   </si>
   <si>
     <t xml:space="preserve">11.505690574646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5748348236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5955781936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6854667663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6508941650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4780330657959</t>
+    <t xml:space="preserve">11.5748357772827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5955791473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6854658126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6508951187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4780321121216</t>
   </si>
   <si>
     <t xml:space="preserve">11.7131242752075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6923809051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6301507949829</t>
+    <t xml:space="preserve">11.6923818588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6301517486572</t>
   </si>
   <si>
     <t xml:space="preserve">11.5402631759644</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">11.2636842727661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1392240524292</t>
+    <t xml:space="preserve">11.1392230987549</t>
   </si>
   <si>
     <t xml:space="preserve">10.828070640564</t>
@@ -3746,31 +3746,31 @@
     <t xml:space="preserve">10.9456176757812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5514936447144</t>
+    <t xml:space="preserve">10.5514917373657</t>
   </si>
   <si>
     <t xml:space="preserve">10.5100049972534</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4961776733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97067737579346</t>
+    <t xml:space="preserve">10.4961767196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97067642211914</t>
   </si>
   <si>
     <t xml:space="preserve">10.10205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2057695388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6828680038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5445766448975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4616041183472</t>
+    <t xml:space="preserve">10.2057685852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6828670501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5445775985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4616050720215</t>
   </si>
   <si>
     <t xml:space="preserve">10.8419008255005</t>
@@ -3782,37 +3782,37 @@
     <t xml:space="preserve">10.8764724731445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9663610458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9179601669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8211574554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5653219223022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7381830215454</t>
+    <t xml:space="preserve">10.9663619995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9179592132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.82115650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5653209686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7381839752197</t>
   </si>
   <si>
     <t xml:space="preserve">11.049334526062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0355052947998</t>
+    <t xml:space="preserve">11.0355072021484</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546119689941</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8030128479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0934200286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2317123413086</t>
+    <t xml:space="preserve">11.8030118942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0934209823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.23171043396</t>
   </si>
   <si>
     <t xml:space="preserve">12.1487369537354</t>
@@ -3821,34 +3821,34 @@
     <t xml:space="preserve">11.9413022994995</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1210803985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0795917510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2593679428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4184007644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4737186431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6050930023193</t>
+    <t xml:space="preserve">12.1210794448853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0795907974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2593698501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4184017181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4737176895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.605092048645</t>
   </si>
   <si>
     <t xml:space="preserve">12.757212638855</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3285121917725</t>
+    <t xml:space="preserve">12.3285131454468</t>
   </si>
   <si>
     <t xml:space="preserve">12.2870273590088</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6880664825439</t>
+    <t xml:space="preserve">12.6880674362183</t>
   </si>
   <si>
     <t xml:space="preserve">12.570520401001</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">11.8514137268066</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2455396652222</t>
+    <t xml:space="preserve">12.2455387115479</t>
   </si>
   <si>
     <t xml:space="preserve">12.3561716079712</t>
@@ -3869,25 +3869,25 @@
     <t xml:space="preserve">12.266282081604</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2040538787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6396636962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4806299209595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3907442092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7364673614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2757968902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1885089874268</t>
+    <t xml:space="preserve">12.2040510177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.639666557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4806308746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3907432556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7364664077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2757959365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1885070800781</t>
   </si>
   <si>
     <t xml:space="preserve">14.3129682540894</t>
@@ -3896,52 +3896,52 @@
     <t xml:space="preserve">14.9352722167969</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9905881881714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7554931640625</t>
+    <t xml:space="preserve">14.9905872344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7554941177368</t>
   </si>
   <si>
     <t xml:space="preserve">14.7969818115234</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9672441482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6215219497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6811504364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3380289077759</t>
+    <t xml:space="preserve">13.9672431945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6215209960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6811532974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3380279541016</t>
   </si>
   <si>
     <t xml:space="preserve">13.0960216522217</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3354291915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5774345397949</t>
+    <t xml:space="preserve">12.335428237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5774354934692</t>
   </si>
   <si>
     <t xml:space="preserve">12.3492574691772</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2498540878296</t>
+    <t xml:space="preserve">11.2498550415039</t>
   </si>
   <si>
     <t xml:space="preserve">10.7589273452759</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7615261077881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0285921096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3674001693726</t>
+    <t xml:space="preserve">11.7615280151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0285911560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3674011230469</t>
   </si>
   <si>
     <t xml:space="preserve">11.8652429580688</t>
@@ -3953,61 +3953,61 @@
     <t xml:space="preserve">12.8056116104126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.715723991394</t>
+    <t xml:space="preserve">12.7157249450684</t>
   </si>
   <si>
     <t xml:space="preserve">12.7433824539185</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0614471435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9992170333862</t>
+    <t xml:space="preserve">13.0614490509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9992160797119</t>
   </si>
   <si>
     <t xml:space="preserve">12.8885860443115</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0337905883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0683622360229</t>
+    <t xml:space="preserve">13.0337896347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0683612823486</t>
   </si>
   <si>
     <t xml:space="preserve">12.9093294143677</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0199604034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2731962203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6465787887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4944610595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5428619384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2524547576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5566911697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9551305770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0865068435669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9205598831177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3466567993164</t>
+    <t xml:space="preserve">13.019962310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2731971740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.646580696106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4944620132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5428609848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2524538040161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5566921234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.955132484436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0865077972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9205589294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3466577529907</t>
   </si>
   <si>
     <t xml:space="preserve">11.5817489624023</t>
@@ -4016,10 +4016,10 @@
     <t xml:space="preserve">12.0242767333984</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3008556365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0381059646606</t>
+    <t xml:space="preserve">12.300856590271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.038106918335</t>
   </si>
   <si>
     <t xml:space="preserve">12.5793085098267</t>
@@ -4028,13 +4028,13 @@
     <t xml:space="preserve">12.5939340591431</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5208005905151</t>
+    <t xml:space="preserve">12.5207996368408</t>
   </si>
   <si>
     <t xml:space="preserve">12.7694597244263</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6743841171265</t>
+    <t xml:space="preserve">12.6743831634521</t>
   </si>
   <si>
     <t xml:space="preserve">12.747519493103</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">12.4184093475342</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3964700698853</t>
+    <t xml:space="preserve">12.3964691162109</t>
   </si>
   <si>
     <t xml:space="preserve">12.3745288848877</t>
@@ -4058,16 +4058,16 @@
     <t xml:space="preserve">12.140495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9795961380005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7455635070801</t>
+    <t xml:space="preserve">11.9795951843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7455625534058</t>
   </si>
   <si>
     <t xml:space="preserve">11.0434617996216</t>
   </si>
   <si>
-    <t xml:space="preserve">10.480318069458</t>
+    <t xml:space="preserve">10.4803190231323</t>
   </si>
   <si>
     <t xml:space="preserve">10.5900211334229</t>
@@ -4079,25 +4079,25 @@
     <t xml:space="preserve">10.4583787918091</t>
   </si>
   <si>
-    <t xml:space="preserve">10.443751335144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6777839660645</t>
+    <t xml:space="preserve">10.4437503814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6777849197388</t>
   </si>
   <si>
     <t xml:space="preserve">10.5095720291138</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5022573471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2389717102051</t>
+    <t xml:space="preserve">10.5022583007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2389707565308</t>
   </si>
   <si>
     <t xml:space="preserve">10.494945526123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.429123878479</t>
+    <t xml:space="preserve">10.4291248321533</t>
   </si>
   <si>
     <t xml:space="preserve">10.3998699188232</t>
@@ -4106,13 +4106,13 @@
     <t xml:space="preserve">10.2097177505493</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88060760498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75627613067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70508193969727</t>
+    <t xml:space="preserve">9.88060855865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7562780380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70508289337158</t>
   </si>
   <si>
     <t xml:space="preserve">9.31015014648438</t>
@@ -4121,7 +4121,7 @@
     <t xml:space="preserve">9.23701572418213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43448066711426</t>
+    <t xml:space="preserve">9.43448162078857</t>
   </si>
   <si>
     <t xml:space="preserve">9.69776916503906</t>
@@ -4130,7 +4130,7 @@
     <t xml:space="preserve">9.41254043579102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46373558044434</t>
+    <t xml:space="preserve">9.46373462677002</t>
   </si>
   <si>
     <t xml:space="preserve">9.06149005889893</t>
@@ -4139,13 +4139,13 @@
     <t xml:space="preserve">8.62267684936523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82745552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97372722625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20775985717773</t>
+    <t xml:space="preserve">8.8274564743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97372817993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20776176452637</t>
   </si>
   <si>
     <t xml:space="preserve">9.24432849884033</t>
@@ -4154,34 +4154,34 @@
     <t xml:space="preserve">9.18582057952881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25895595550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53687000274658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21507549285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3686580657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39791393280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58075141906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68314266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55881023406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95374202728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0195646286011</t>
+    <t xml:space="preserve">9.25895500183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5368709564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21507453918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36865901947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39791202545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5807523727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68314170837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55881118774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9537410736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0195655822754</t>
   </si>
   <si>
     <t xml:space="preserve">9.98299598693848</t>
@@ -4190,13 +4190,13 @@
     <t xml:space="preserve">9.72702312469482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47104835510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57343864440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80747222900391</t>
+    <t xml:space="preserve">9.47104930877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57343769073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80747032165527</t>
   </si>
   <si>
     <t xml:space="preserve">9.97568416595459</t>
@@ -4211,16 +4211,16 @@
     <t xml:space="preserve">9.22238731384277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20044708251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06880378723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82014274597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75432014465332</t>
+    <t xml:space="preserve">9.20044803619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06880283355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82014179229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75432109832764</t>
   </si>
   <si>
     <t xml:space="preserve">8.81282901763916</t>
@@ -4235,73 +4235,73 @@
     <t xml:space="preserve">8.68849945068359</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44715118408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40327072143555</t>
+    <t xml:space="preserve">8.44715213775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40326976776123</t>
   </si>
   <si>
     <t xml:space="preserve">8.27894020080566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35207462310791</t>
+    <t xml:space="preserve">8.35207557678223</t>
   </si>
   <si>
     <t xml:space="preserve">8.54222774505615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01760768890381</t>
+    <t xml:space="preserve">9.01760864257812</t>
   </si>
   <si>
     <t xml:space="preserve">9.02492237091064</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14925289154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94447231292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89327716827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59342193603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63730430603027</t>
+    <t xml:space="preserve">9.14925193786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94447326660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89327812194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59342288970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63730335235596</t>
   </si>
   <si>
     <t xml:space="preserve">8.34476089477539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35938835144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22043132781982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13266849517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86938095092773</t>
+    <t xml:space="preserve">8.35939025878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22043228149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13266944885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86938190460205</t>
   </si>
   <si>
     <t xml:space="preserve">8.32282161712646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41789722442627</t>
+    <t xml:space="preserve">8.41789817810059</t>
   </si>
   <si>
     <t xml:space="preserve">8.33013534545898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24237155914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14729595184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07415962219238</t>
+    <t xml:space="preserve">8.24237251281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14729499816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0741605758667</t>
   </si>
   <si>
     <t xml:space="preserve">8.16192245483398</t>
@@ -4325,7 +4325,7 @@
     <t xml:space="preserve">8.38864326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48371982574463</t>
+    <t xml:space="preserve">8.48371887207031</t>
   </si>
   <si>
     <t xml:space="preserve">8.56416893005371</t>
@@ -4340,73 +4340,73 @@
     <t xml:space="preserve">8.922532081604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56612396240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52955627441406</t>
+    <t xml:space="preserve">9.56612491607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5295581817627</t>
   </si>
   <si>
     <t xml:space="preserve">9.84403991699219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488195419312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1804628372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1512098312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1146402359009</t>
+    <t xml:space="preserve">10.0488185882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1804618835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1512088775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1146411895752</t>
   </si>
   <si>
     <t xml:space="preserve">10.0049381256104</t>
   </si>
   <si>
+    <t xml:space="preserve">10.3340473175049</t>
+  </si>
+  <si>
     <t xml:space="preserve">10.3340482711792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3340473175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2789535522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.310435295105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3261775970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3576602935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3497877120972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3891410827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2553405761719</t>
+    <t xml:space="preserve">10.2789545059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3104362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3261766433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3576583862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3497886657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3891401290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2553424835205</t>
   </si>
   <si>
     <t xml:space="preserve">10.2710828781128</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2002477645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.04283618927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86968326568604</t>
+    <t xml:space="preserve">10.2002468109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0428371429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86968421936035</t>
   </si>
   <si>
     <t xml:space="preserve">9.88542556762695</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0507078170776</t>
+    <t xml:space="preserve">10.0507068634033</t>
   </si>
   <si>
     <t xml:space="preserve">9.96413135528564</t>
@@ -4415,13 +4415,13 @@
     <t xml:space="preserve">10.1608943939209</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1845073699951</t>
+    <t xml:space="preserve">10.1845064163208</t>
   </si>
   <si>
     <t xml:space="preserve">10.0034837722778</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0900602340698</t>
+    <t xml:space="preserve">10.0900611877441</t>
   </si>
   <si>
     <t xml:space="preserve">10.5229406356812</t>
@@ -4433,40 +4433,40 @@
     <t xml:space="preserve">10.4521055221558</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3812704086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4678468704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.47571849823</t>
+    <t xml:space="preserve">10.3812713623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4678478240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4757175445557</t>
   </si>
   <si>
     <t xml:space="preserve">10.5780344009399</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7433156967163</t>
+    <t xml:space="preserve">10.743314743042</t>
   </si>
   <si>
     <t xml:space="preserve">11.0030450820923</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0345277786255</t>
+    <t xml:space="preserve">11.0345287322998</t>
   </si>
   <si>
     <t xml:space="preserve">11.0423984527588</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1998090744019</t>
+    <t xml:space="preserve">11.1998100280762</t>
   </si>
   <si>
     <t xml:space="preserve">11.2234210968018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2863855361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3650913238525</t>
+    <t xml:space="preserve">11.2863864898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3650903701782</t>
   </si>
   <si>
     <t xml:space="preserve">11.3493509292603</t>
@@ -4481,10 +4481,10 @@
     <t xml:space="preserve">11.1919393539429</t>
   </si>
   <si>
-    <t xml:space="preserve">11.412314414978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3965721130371</t>
+    <t xml:space="preserve">11.4123153686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3965730667114</t>
   </si>
   <si>
     <t xml:space="preserve">11.2155504226685</t>
@@ -4493,7 +4493,7 @@
     <t xml:space="preserve">11.4280567169189</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4752788543701</t>
+    <t xml:space="preserve">11.4752798080444</t>
   </si>
   <si>
     <t xml:space="preserve">11.8294544219971</t>
@@ -4505,31 +4505,31 @@
     <t xml:space="preserve">12.1678886413574</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3725242614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3095579147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4040050506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5220632553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5141925811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7266969680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8368864059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8132743835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5378046035767</t>
+    <t xml:space="preserve">12.372522354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3095588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4040040969849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5220642089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5141916275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7266988754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8368854522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8132762908936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.537805557251</t>
   </si>
   <si>
     <t xml:space="preserve">12.3882637023926</t>
@@ -4541,13 +4541,13 @@
     <t xml:space="preserve">12.7345695495605</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5063219070435</t>
+    <t xml:space="preserve">12.5063228607178</t>
   </si>
   <si>
     <t xml:space="preserve">12.2465944290161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1049242019653</t>
+    <t xml:space="preserve">12.1049251556396</t>
   </si>
   <si>
     <t xml:space="preserve">12.2702054977417</t>
@@ -4559,31 +4559,31 @@
     <t xml:space="preserve">12.3016872406006</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3252983093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9160299301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4516677856445</t>
+    <t xml:space="preserve">12.3253002166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9160308837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4516668319702</t>
   </si>
   <si>
     <t xml:space="preserve">11.6563024520874</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1132326126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1289739608765</t>
+    <t xml:space="preserve">11.1132335662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1289749145508</t>
   </si>
   <si>
     <t xml:space="preserve">11.0974922180176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0266580581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8062810897827</t>
+    <t xml:space="preserve">11.0266561508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8062801361084</t>
   </si>
   <si>
     <t xml:space="preserve">10.8456344604492</t>
@@ -4598,25 +4598,25 @@
     <t xml:space="preserve">10.995174407959</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9873046875</t>
+    <t xml:space="preserve">10.9873037338257</t>
   </si>
   <si>
     <t xml:space="preserve">10.908597946167</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0581398010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1761980056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5854663848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5225028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7743606567383</t>
+    <t xml:space="preserve">11.0581388473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.176197052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.585467338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5225019454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7743587493896</t>
   </si>
   <si>
     <t xml:space="preserve">11.8766775131226</t>
@@ -4628,7 +4628,7 @@
     <t xml:space="preserve">11.9947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1285362243652</t>
+    <t xml:space="preserve">12.1285352706909</t>
   </si>
   <si>
     <t xml:space="preserve">11.9632530212402</t>
@@ -4637,19 +4637,19 @@
     <t xml:space="preserve">11.9002885818481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9789953231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5697250366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6012077331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8058423995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9317722320557</t>
+    <t xml:space="preserve">11.9789962768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5697259902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6012086868286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8058414459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9317712783813</t>
   </si>
   <si>
     <t xml:space="preserve">11.3257389068604</t>
@@ -4658,19 +4658,19 @@
     <t xml:space="preserve">11.3572206497192</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3336086273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.912278175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8475379943848</t>
+    <t xml:space="preserve">11.333607673645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9122791290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8475370407104</t>
   </si>
   <si>
     <t xml:space="preserve">11.6614074707031</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6290369033813</t>
+    <t xml:space="preserve">11.6290378570557</t>
   </si>
   <si>
     <t xml:space="preserve">11.807074546814</t>
@@ -4682,7 +4682,7 @@
     <t xml:space="preserve">11.4995565414429</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3296117782593</t>
+    <t xml:space="preserve">11.3296127319336</t>
   </si>
   <si>
     <t xml:space="preserve">11.5076494216919</t>
@@ -4691,31 +4691,31 @@
     <t xml:space="preserve">11.6371307373047</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5319261550903</t>
+    <t xml:space="preserve">11.5319271087646</t>
   </si>
   <si>
     <t xml:space="preserve">11.5966672897339</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5885744094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5400199890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4429082870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3862590789795</t>
+    <t xml:space="preserve">11.5885753631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5400190353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4429092407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3862609863281</t>
   </si>
   <si>
     <t xml:space="preserve">11.5157413482666</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4671859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4186305999756</t>
+    <t xml:space="preserve">11.4671869277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4186296463013</t>
   </si>
   <si>
     <t xml:space="preserve">11.3781681060791</t>
@@ -4730,13 +4730,13 @@
     <t xml:space="preserve">11.3943529129028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4510011672974</t>
+    <t xml:space="preserve">11.451000213623</t>
   </si>
   <si>
     <t xml:space="preserve">11.6047601699829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6533155441284</t>
+    <t xml:space="preserve">11.6533145904541</t>
   </si>
   <si>
     <t xml:space="preserve">11.6209449768066</t>
@@ -4745,7 +4745,7 @@
     <t xml:space="preserve">11.8637228012085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9770193099976</t>
+    <t xml:space="preserve">11.9770183563232</t>
   </si>
   <si>
     <t xml:space="preserve">11.993203163147</t>
@@ -4757,10 +4757,10 @@
     <t xml:space="preserve">11.9446487426758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.815167427063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9365549087524</t>
+    <t xml:space="preserve">11.8151664733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9365558624268</t>
   </si>
   <si>
     <t xml:space="preserve">12.0903148651123</t>
@@ -4769,25 +4769,25 @@
     <t xml:space="preserve">12.1712408065796</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2521657943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4221105575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.381649017334</t>
+    <t xml:space="preserve">12.2521667480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4221115112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3816471099854</t>
   </si>
   <si>
     <t xml:space="preserve">12.3411846160889</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3249998092651</t>
+    <t xml:space="preserve">12.3249988555908</t>
   </si>
   <si>
     <t xml:space="preserve">12.3007221221924</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4140186309814</t>
+    <t xml:space="preserve">12.4140176773071</t>
   </si>
   <si>
     <t xml:space="preserve">12.6082401275635</t>
@@ -4796,28 +4796,28 @@
     <t xml:space="preserve">12.8914813995361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9966840744019</t>
+    <t xml:space="preserve">12.9966831207275</t>
   </si>
   <si>
     <t xml:space="preserve">12.745813369751</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5354061126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6163330078125</t>
+    <t xml:space="preserve">12.5354070663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6163320541382</t>
   </si>
   <si>
     <t xml:space="preserve">13.1909055709839</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1261653900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.842924118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9562206268311</t>
+    <t xml:space="preserve">13.1261644363403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8429250717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9562215805054</t>
   </si>
   <si>
     <t xml:space="preserve">12.9804992675781</t>
@@ -4826,16 +4826,16 @@
     <t xml:space="preserve">13.0290546417236</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0937957763672</t>
+    <t xml:space="preserve">13.0937948226929</t>
   </si>
   <si>
     <t xml:space="preserve">13.1989984512329</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9076662063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8510179519653</t>
+    <t xml:space="preserve">12.9076642990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.851016998291</t>
   </si>
   <si>
     <t xml:space="preserve">12.9885902404785</t>
@@ -4844,31 +4844,31 @@
     <t xml:space="preserve">12.9238510131836</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0452394485474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0776090621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1747207641602</t>
+    <t xml:space="preserve">13.045241355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0776100158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1747217178345</t>
   </si>
   <si>
     <t xml:space="preserve">13.1666288375854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9724063873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9319438934326</t>
+    <t xml:space="preserve">12.9724073410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9319429397583</t>
   </si>
   <si>
     <t xml:space="preserve">12.6810731887817</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5677766799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4787588119507</t>
+    <t xml:space="preserve">12.567777633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.478759765625</t>
   </si>
   <si>
     <t xml:space="preserve">12.75390625</t>
@@ -4877,7 +4877,7 @@
     <t xml:space="preserve">12.7296285629272</t>
   </si>
   <si>
-    <t xml:space="preserve">12.583963394165</t>
+    <t xml:space="preserve">12.5839624404907</t>
   </si>
   <si>
     <t xml:space="preserve">12.5758695602417</t>
@@ -4895,19 +4895,19 @@
     <t xml:space="preserve">13.0209617614746</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0371475219727</t>
+    <t xml:space="preserve">13.0371465682983</t>
   </si>
   <si>
     <t xml:space="preserve">13.2475547790527</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9400358200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1504440307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3365716934204</t>
+    <t xml:space="preserve">12.940034866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1504421234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3365726470947</t>
   </si>
   <si>
     <t xml:space="preserve">13.5874433517456</t>
@@ -4916,52 +4916,52 @@
     <t xml:space="preserve">13.4903316497803</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2880163192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3203859329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3042020797729</t>
+    <t xml:space="preserve">13.2880172729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3203868865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3042011260986</t>
   </si>
   <si>
     <t xml:space="preserve">13.0128688812256</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7862777709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2036113739014</t>
+    <t xml:space="preserve">12.7862768173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2036104202271</t>
   </si>
   <si>
     <t xml:space="preserve">12.4544811248779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8995723724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0533304214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.215184211731</t>
+    <t xml:space="preserve">12.8995733261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0533313751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2151832580566</t>
   </si>
   <si>
     <t xml:space="preserve">13.5388860702515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.417498588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4579610824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5955333709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0163488388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8221282958984</t>
+    <t xml:space="preserve">13.4174976348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4579601287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.595534324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0163478851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8221273422241</t>
   </si>
   <si>
     <t xml:space="preserve">13.9435157775879</t>
@@ -4973,7 +4973,7 @@
     <t xml:space="preserve">13.7573871612549</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9597015380859</t>
+    <t xml:space="preserve">13.9597005844116</t>
   </si>
   <si>
     <t xml:space="preserve">13.881422996521</t>
@@ -71508,25 +71508,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45967.6912615741</v>
+        <v>45968.6913078704</v>
       </c>
       <c r="B2505" t="n">
-        <v>92119</v>
+        <v>114970</v>
       </c>
       <c r="C2505" t="n">
-        <v>22.5599994659424</v>
+        <v>22.6200008392334</v>
       </c>
       <c r="D2505" t="n">
         <v>22.2399997711182</v>
       </c>
       <c r="E2505" t="n">
-        <v>22.4799995422363</v>
+        <v>22.3999996185303</v>
       </c>
       <c r="F2505" t="n">
-        <v>22.2399997711182</v>
+        <v>22.4400005340576</v>
       </c>
       <c r="G2505" t="s">
-        <v>2012</v>
+        <v>1932</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/IF.MI.xlsx
+++ b/data/IF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2020" uniqueCount="2020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2021" uniqueCount="2021">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,124 +38,124 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7370777130127</t>
+    <t xml:space="preserve">15.7370767593384</t>
   </si>
   <si>
     <t xml:space="preserve">IF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3903484344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3232393264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5458946228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3613414764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3781204223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4284515380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.176794052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8646621704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8524312973022</t>
+    <t xml:space="preserve">15.3903455734253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3232345581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5458908081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3613433837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3781185150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4284505844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1767921447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8646602630615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8524322509766</t>
   </si>
   <si>
     <t xml:space="preserve">14.4955606460571</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6409635543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.434042930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3735685348511</t>
+    <t xml:space="preserve">14.6409645080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4340448379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.373571395874</t>
   </si>
   <si>
     <t xml:space="preserve">15.3959398269653</t>
   </si>
   <si>
-    <t xml:space="preserve">15.938404083252</t>
+    <t xml:space="preserve">15.9384031295776</t>
   </si>
   <si>
     <t xml:space="preserve">15.9439973831177</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5637130737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1061763763428</t>
+    <t xml:space="preserve">15.5637121200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.10618019104</t>
   </si>
   <si>
     <t xml:space="preserve">16.0502529144287</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7706346511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1722421646118</t>
+    <t xml:space="preserve">15.7706298828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1722440719604</t>
   </si>
   <si>
     <t xml:space="preserve">14.9597311019897</t>
   </si>
   <si>
-    <t xml:space="preserve">14.540301322937</t>
+    <t xml:space="preserve">14.5402975082397</t>
   </si>
   <si>
     <t xml:space="preserve">13.0583076477051</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0974550247192</t>
+    <t xml:space="preserve">13.0974559783936</t>
   </si>
   <si>
     <t xml:space="preserve">13.7405824661255</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7685441970825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8244686126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5347061157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4396362304688</t>
+    <t xml:space="preserve">13.7685451507568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8244676589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.534707069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4396343231201</t>
   </si>
   <si>
     <t xml:space="preserve">14.3501567840576</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2718639373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3333797454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4350872039795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9765090942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7416276931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2057981491089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0995445251465</t>
+    <t xml:space="preserve">14.2718648910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3333768844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4350852966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9765110015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.741626739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2058010101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0995407104492</t>
   </si>
   <si>
     <t xml:space="preserve">15.0436182022095</t>
@@ -164,49 +164,49 @@
     <t xml:space="preserve">15.4966039657593</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2840957641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9876937866211</t>
+    <t xml:space="preserve">15.2840890884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9876909255981</t>
   </si>
   <si>
     <t xml:space="preserve">14.4452276229858</t>
   </si>
   <si>
-    <t xml:space="preserve">14.557074546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1656074523926</t>
+    <t xml:space="preserve">14.5570774078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1656093597412</t>
   </si>
   <si>
     <t xml:space="preserve">14.484375</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7192583084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1834278106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3791627883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9999227523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2348022460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0949935913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.966365814209</t>
+    <t xml:space="preserve">14.719256401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1834287643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3791637420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9999217987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2348041534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.09499168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9663667678833</t>
   </si>
   <si>
     <t xml:space="preserve">16.1173610687256</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1403369903564</t>
+    <t xml:space="preserve">16.1403408050537</t>
   </si>
   <si>
     <t xml:space="preserve">16.4849720001221</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">16.7204723358154</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4160442352295</t>
+    <t xml:space="preserve">16.4160461425781</t>
   </si>
   <si>
     <t xml:space="preserve">15.8473997116089</t>
@@ -230,22 +230,22 @@
     <t xml:space="preserve">15.6808280944824</t>
   </si>
   <si>
-    <t xml:space="preserve">15.784218788147</t>
+    <t xml:space="preserve">15.7842149734497</t>
   </si>
   <si>
     <t xml:space="preserve">15.8876075744629</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6348752975464</t>
+    <t xml:space="preserve">15.634877204895</t>
   </si>
   <si>
     <t xml:space="preserve">15.278754234314</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4280939102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2385473251343</t>
+    <t xml:space="preserve">15.4280958175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2385482788086</t>
   </si>
   <si>
     <t xml:space="preserve">15.1409015655518</t>
@@ -254,22 +254,22 @@
     <t xml:space="preserve">15.3821468353271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9570960998535</t>
+    <t xml:space="preserve">14.9570980072021</t>
   </si>
   <si>
     <t xml:space="preserve">14.8479633331299</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5894870758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6239500045776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.70436668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5550231933594</t>
+    <t xml:space="preserve">14.5894889831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6239519119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7043657302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5550241470337</t>
   </si>
   <si>
     <t xml:space="preserve">14.3482427597046</t>
@@ -278,178 +278,178 @@
     <t xml:space="preserve">14.1184883117676</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8427810668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.164439201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6704664230347</t>
+    <t xml:space="preserve">13.8427820205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1644401550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.670464515686</t>
   </si>
   <si>
     <t xml:space="preserve">13.6417465209961</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3258333206177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1075620651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8375997543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9811992645264</t>
+    <t xml:space="preserve">13.325831413269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1075649261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8376007080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9811983108521</t>
   </si>
   <si>
     <t xml:space="preserve">12.7629280090332</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4814786911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6365623474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6882581710815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3493709564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.579122543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9352464675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5148181915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9576578140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7853412628174</t>
+    <t xml:space="preserve">12.4814777374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6365661621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6882591247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3493690490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5791244506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9352474212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5148153305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9576587677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7853422164917</t>
   </si>
   <si>
     <t xml:space="preserve">13.5613298416138</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6647186279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3488063812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2683925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3602952957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1535129547119</t>
+    <t xml:space="preserve">13.6647214889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3488054275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2683935165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3602962493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1535148620605</t>
   </si>
   <si>
     <t xml:space="preserve">12.9639663696289</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7801609039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5504055023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2057723999023</t>
+    <t xml:space="preserve">12.780161857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.550404548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.205771446228</t>
   </si>
   <si>
     <t xml:space="preserve">12.0564317703247</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9185771942139</t>
+    <t xml:space="preserve">11.9185791015625</t>
   </si>
   <si>
     <t xml:space="preserve">11.6084060668945</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2287492752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6537961959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5963563919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9869422912598</t>
+    <t xml:space="preserve">12.2287483215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6537981033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5963573455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9869432449341</t>
   </si>
   <si>
     <t xml:space="preserve">12.1196146011353</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1781778335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2643375396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3217744827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4251670837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4366540908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4538841247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93693542480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58081340789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5693244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7301549911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76461887359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8272390365601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.281005859375</t>
+    <t xml:space="preserve">10.1781768798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2643365859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3217754364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4251651763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.436653137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4538850784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93693351745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58081245422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56932544708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73015308380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76461696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8272380828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2810049057007</t>
   </si>
   <si>
     <t xml:space="preserve">11.4877862930298</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3269567489624</t>
+    <t xml:space="preserve">11.3269557952881</t>
   </si>
   <si>
     <t xml:space="preserve">11.516505241394</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2580318450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4992733001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2293109893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0455045700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.861701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6032266616821</t>
+    <t xml:space="preserve">11.2580299377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4992742538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2293090820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0455055236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8617010116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6032247543335</t>
   </si>
   <si>
     <t xml:space="preserve">10.9995546340942</t>
@@ -458,43 +458,43 @@
     <t xml:space="preserve">11.7175397872925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4188575744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.579686164856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1144304275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1431503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6026639938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.740517616272</t>
+    <t xml:space="preserve">11.4188566207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5796871185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1144332885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1431522369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6026630401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7405166625977</t>
   </si>
   <si>
     <t xml:space="preserve">11.4016265869141</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6543607711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5567111968994</t>
+    <t xml:space="preserve">11.6543579101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5567121505737</t>
   </si>
   <si>
     <t xml:space="preserve">11.4533224105835</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3843965530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2867488861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9880666732788</t>
+    <t xml:space="preserve">11.3843975067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2867479324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9880657196045</t>
   </si>
   <si>
     <t xml:space="preserve">10.9765796661377</t>
@@ -503,28 +503,28 @@
     <t xml:space="preserve">11.0397605895996</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0282745361328</t>
+    <t xml:space="preserve">11.0282735824585</t>
   </si>
   <si>
     <t xml:space="preserve">11.0971994400024</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9708337783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9650897979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1201753616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2063341140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1891031265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4303464889526</t>
+    <t xml:space="preserve">10.97083568573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9650926589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1201772689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.206335067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1891021728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4303483963013</t>
   </si>
   <si>
     <t xml:space="preserve">11.8324184417725</t>
@@ -533,145 +533,145 @@
     <t xml:space="preserve">12.3149089813232</t>
   </si>
   <si>
-    <t xml:space="preserve">12.395320892334</t>
+    <t xml:space="preserve">12.3953199386597</t>
   </si>
   <si>
     <t xml:space="preserve">11.9587850570679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6945657730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7749805450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.671591758728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6888217926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5739450454712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7692356109619</t>
+    <t xml:space="preserve">11.6945648193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7749786376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6715888977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6888208389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5739431381226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7692375183105</t>
   </si>
   <si>
     <t xml:space="preserve">12.0621747970581</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0219688415527</t>
+    <t xml:space="preserve">12.0219669342041</t>
   </si>
   <si>
     <t xml:space="preserve">11.6601009368896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5107593536377</t>
+    <t xml:space="preserve">11.5107622146606</t>
   </si>
   <si>
     <t xml:space="preserve">11.4935302734375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5279932022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7060518264771</t>
+    <t xml:space="preserve">11.5279922485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7060527801514</t>
   </si>
   <si>
     <t xml:space="preserve">11.7577476501465</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0277128219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4068098068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.434965133667</t>
+    <t xml:space="preserve">12.0277099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4068078994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.434962272644</t>
   </si>
   <si>
     <t xml:space="preserve">13.6991844177246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7279043197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8657569885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9519166946411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1759271621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3712186813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4631223678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8824253082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9628391265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1064386367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2270584106445</t>
+    <t xml:space="preserve">13.7279033660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8657560348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9519157409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1759262084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3712205886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4631214141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8824272155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9628400802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1064376831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2270603179932</t>
   </si>
   <si>
     <t xml:space="preserve">15.1351566314697</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9456081390381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7158536911011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.733081817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5090732574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5952310562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5435361862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3827075958252</t>
+    <t xml:space="preserve">14.9456090927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7158546447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7330875396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5090742111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5952320098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5435371398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3827056884766</t>
   </si>
   <si>
     <t xml:space="preserve">14.0725374221802</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0610504150391</t>
+    <t xml:space="preserve">14.0610494613647</t>
   </si>
   <si>
     <t xml:space="preserve">13.6474895477295</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6876955032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5900506973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5383539199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0501251220703</t>
+    <t xml:space="preserve">13.6876964569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5900497436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5383558273315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0501222610474</t>
   </si>
   <si>
     <t xml:space="preserve">13.1190509796143</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1822319030762</t>
+    <t xml:space="preserve">13.1822347640991</t>
   </si>
   <si>
     <t xml:space="preserve">12.7514429092407</t>
@@ -680,13 +680,13 @@
     <t xml:space="preserve">13.2109518051147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4407081604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4234781265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.285623550415</t>
+    <t xml:space="preserve">13.4407072067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4234771728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2856216430664</t>
   </si>
   <si>
     <t xml:space="preserve">14.1414642333984</t>
@@ -695,19 +695,19 @@
     <t xml:space="preserve">14.2735748291016</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1931600570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3597297668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.939866065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6871337890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3884515762329</t>
+    <t xml:space="preserve">14.1931581497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3597316741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9398641586304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6871328353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3884496688843</t>
   </si>
   <si>
     <t xml:space="preserve">14.474609375</t>
@@ -716,43 +716,43 @@
     <t xml:space="preserve">14.7847805023193</t>
   </si>
   <si>
-    <t xml:space="preserve">14.934121131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2213144302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.583179473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4970207214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4510698318481</t>
+    <t xml:space="preserve">14.9341192245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2213163375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5831813812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4970226287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4510717391968</t>
   </si>
   <si>
     <t xml:space="preserve">15.3361959457397</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8364734649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9915637969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2959842681885</t>
+    <t xml:space="preserve">14.8364744186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9915618896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2959861755371</t>
   </si>
   <si>
     <t xml:space="preserve">15.1638774871826</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0375118255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0892066955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0719757080078</t>
+    <t xml:space="preserve">15.0375127792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0892057418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0719747543335</t>
   </si>
   <si>
     <t xml:space="preserve">14.8307294845581</t>
@@ -761,208 +761,208 @@
     <t xml:space="preserve">14.6469259262085</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5320463180542</t>
+    <t xml:space="preserve">14.5320482254028</t>
   </si>
   <si>
     <t xml:space="preserve">14.2333641052246</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5263051986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4171724319458</t>
+    <t xml:space="preserve">14.5263071060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4171686172485</t>
   </si>
   <si>
     <t xml:space="preserve">14.3941946029663</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0489988327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7618064880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6584129333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8766813278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3936338424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8531436920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8416566848755</t>
+    <t xml:space="preserve">15.0490007400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7618026733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6584157943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8766822814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.393630027771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.853141784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8416585922241</t>
   </si>
   <si>
     <t xml:space="preserve">16.0369491577148</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5079498291016</t>
+    <t xml:space="preserve">16.5079479217529</t>
   </si>
   <si>
     <t xml:space="preserve">16.9559726715088</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0880813598633</t>
+    <t xml:space="preserve">17.088077545166</t>
   </si>
   <si>
     <t xml:space="preserve">16.634313583374</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6113376617432</t>
+    <t xml:space="preserve">16.6113395690918</t>
   </si>
   <si>
     <t xml:space="preserve">16.0828990936279</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8870429992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9444847106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3465557098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4844074249268</t>
+    <t xml:space="preserve">16.8870449066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9444828033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3465576171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4844093322754</t>
   </si>
   <si>
     <t xml:space="preserve">17.593542098999</t>
   </si>
   <si>
-    <t xml:space="preserve">17.059362411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.168493270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6911869049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9152011871338</t>
+    <t xml:space="preserve">17.0593605041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1684951782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6911888122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9152050018311</t>
   </si>
   <si>
     <t xml:space="preserve">18.7365760803223</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5522117614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8164310455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9944915771484</t>
+    <t xml:space="preserve">19.552209854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8164291381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9944896697998</t>
   </si>
   <si>
     <t xml:space="preserve">20.942232131958</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5229301452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8503341674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7354526519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6780166625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6492938995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3218955993652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5631351470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6378059387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8388423919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8216094970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6090888977051</t>
+    <t xml:space="preserve">20.5229263305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8503303527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7354545593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6780128479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6492919921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.321891784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5631332397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.637809753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8388404846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8216133117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6090908050537</t>
   </si>
   <si>
     <t xml:space="preserve">21.1088066101074</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4132308959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2409152984619</t>
+    <t xml:space="preserve">21.4132289886475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2409172058105</t>
   </si>
   <si>
     <t xml:space="preserve">21.1777305603027</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0226497650146</t>
+    <t xml:space="preserve">21.022647857666</t>
   </si>
   <si>
     <t xml:space="preserve">20.9594631195068</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3098430633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5855484008789</t>
+    <t xml:space="preserve">21.3098392486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5855503082275</t>
   </si>
   <si>
     <t xml:space="preserve">21.3155841827393</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2690734863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1369590759277</t>
+    <t xml:space="preserve">22.2690715789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.136962890625</t>
   </si>
   <si>
     <t xml:space="preserve">21.9818801879883</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2288608551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7458114624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9335060119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5815868377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3938941955566</t>
+    <t xml:space="preserve">22.2288665771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7458152770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9335041046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5815830230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3938961029053</t>
   </si>
   <si>
     <t xml:space="preserve">21.4671688079834</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4583263397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1035175323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8161144256592</t>
+    <t xml:space="preserve">20.4583301544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1035194396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8161182403564</t>
   </si>
   <si>
     <t xml:space="preserve">20.6342906951904</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6929416656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5873641967773</t>
+    <t xml:space="preserve">20.692943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.587366104126</t>
   </si>
   <si>
     <t xml:space="preserve">19.2969932556152</t>
@@ -977,28 +977,28 @@
     <t xml:space="preserve">19.9656410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4817943572998</t>
+    <t xml:space="preserve">20.4817924499512</t>
   </si>
   <si>
     <t xml:space="preserve">20.4700603485107</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5287113189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4114055633545</t>
+    <t xml:space="preserve">20.5287170410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4114074707031</t>
   </si>
   <si>
     <t xml:space="preserve">20.2706394195557</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3058319091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7955436706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.607852935791</t>
+    <t xml:space="preserve">20.3058280944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7955474853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6078567504883</t>
   </si>
   <si>
     <t xml:space="preserve">19.8835277557373</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">20.176794052124</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7515983581543</t>
+    <t xml:space="preserve">20.7515964508057</t>
   </si>
   <si>
     <t xml:space="preserve">20.6988105773926</t>
@@ -1022,13 +1022,13 @@
     <t xml:space="preserve">20.3527545928955</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5521755218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5052547454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7046737670898</t>
+    <t xml:space="preserve">20.5521774291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5052509307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7046718597412</t>
   </si>
   <si>
     <t xml:space="preserve">20.4407329559326</t>
@@ -1043,22 +1043,22 @@
     <t xml:space="preserve">20.0008296966553</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4876556396484</t>
+    <t xml:space="preserve">20.4876575469971</t>
   </si>
   <si>
     <t xml:space="preserve">20.6694850921631</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6460189819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8630409240723</t>
+    <t xml:space="preserve">20.6460227966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.863037109375</t>
   </si>
   <si>
     <t xml:space="preserve">20.933422088623</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0096778869629</t>
+    <t xml:space="preserve">21.0096702575684</t>
   </si>
   <si>
     <t xml:space="preserve">20.9275588989258</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">21.1152477264404</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2560176849365</t>
+    <t xml:space="preserve">21.2560195922852</t>
   </si>
   <si>
     <t xml:space="preserve">21.2912082672119</t>
@@ -1082,103 +1082,103 @@
     <t xml:space="preserve">21.6313991546631</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6079387664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6431331634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.83669090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0830307006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7604351043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4642753601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9041805267334</t>
+    <t xml:space="preserve">21.6079406738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6431293487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8366870880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0830345153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7604331970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4642791748047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9041767120361</t>
   </si>
   <si>
     <t xml:space="preserve">22.6402378082275</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9686985015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.75754737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2854290008545</t>
+    <t xml:space="preserve">22.9687004089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7575454711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2854270935059</t>
   </si>
   <si>
     <t xml:space="preserve">23.4907131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7722473144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0068626403809</t>
+    <t xml:space="preserve">23.7722511291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0068645477295</t>
   </si>
   <si>
     <t xml:space="preserve">24.2708072662354</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8719577789307</t>
+    <t xml:space="preserve">23.8719596862793</t>
   </si>
   <si>
     <t xml:space="preserve">24.1007118225098</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0479183197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5435028076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5669612884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1593627929688</t>
+    <t xml:space="preserve">24.0479202270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5435009002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5669631958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1593647003174</t>
   </si>
   <si>
     <t xml:space="preserve">24.3529205322266</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3059959411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8543643951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.036190032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8367691040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8191757202148</t>
+    <t xml:space="preserve">24.3059940338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8543663024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0361938476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8367671966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8191776275635</t>
   </si>
   <si>
     <t xml:space="preserve">23.9716701507568</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7898483276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6373481750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1153297424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7077350616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9012870788574</t>
+    <t xml:space="preserve">23.7898445129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6373462677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1153335571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7077293395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9012908935547</t>
   </si>
   <si>
     <t xml:space="preserve">24.1652278900146</t>
@@ -1187,31 +1187,31 @@
     <t xml:space="preserve">24.5347499847412</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3411903381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0831165313721</t>
+    <t xml:space="preserve">24.3411922454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0831127166748</t>
   </si>
   <si>
     <t xml:space="preserve">24.7400302886963</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7107086181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4936866760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6989765167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0684947967529</t>
+    <t xml:space="preserve">24.7107067108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.493688583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6989727020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0684928894043</t>
   </si>
   <si>
     <t xml:space="preserve">25.7078132629395</t>
   </si>
   <si>
-    <t xml:space="preserve">25.713680267334</t>
+    <t xml:space="preserve">25.7136840820312</t>
   </si>
   <si>
     <t xml:space="preserve">26.15944480896</t>
@@ -1220,121 +1220,121 @@
     <t xml:space="preserve">26.4937705993652</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3823280334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5876235961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1301212310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5993480682373</t>
+    <t xml:space="preserve">26.3823299407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5876159667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1301174163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5993461608887</t>
   </si>
   <si>
     <t xml:space="preserve">26.822229385376</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1330966949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7548236846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0656833648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.206449508667</t>
+    <t xml:space="preserve">27.1330909729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7548217773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0656795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.2064533233643</t>
   </si>
   <si>
     <t xml:space="preserve">26.8984794616699</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7489566802979</t>
+    <t xml:space="preserve">27.7489585876465</t>
   </si>
   <si>
     <t xml:space="preserve">28.4997215270996</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8281803131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8926982879639</t>
+    <t xml:space="preserve">28.8281745910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.8926963806152</t>
   </si>
   <si>
     <t xml:space="preserve">28.658088684082</t>
   </si>
   <si>
-    <t xml:space="preserve">28.053955078125</t>
+    <t xml:space="preserve">28.0539493560791</t>
   </si>
   <si>
     <t xml:space="preserve">26.9278087615967</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5289649963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2152137756348</t>
+    <t xml:space="preserve">26.5289611816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2152099609375</t>
   </si>
   <si>
     <t xml:space="preserve">26.6403999328613</t>
   </si>
   <si>
-    <t xml:space="preserve">27.5377998352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6316471099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6668376922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8428020477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3237648010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5671272277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6023216247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4556903839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5026092529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0803050994873</t>
+    <t xml:space="preserve">27.5378036499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6316452026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6668434143066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8428039550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3237590789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5671291351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6023254394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4556884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5026111602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0803070068359</t>
   </si>
   <si>
     <t xml:space="preserve">26.8163661956787</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3060779571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9365653991699</t>
+    <t xml:space="preserve">26.3060817718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9365615844727</t>
   </si>
   <si>
     <t xml:space="preserve">24.5992641448975</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8954257965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9511013031006</t>
+    <t xml:space="preserve">23.8954219818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9511032104492</t>
   </si>
   <si>
     <t xml:space="preserve">22.8279285430908</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6021595001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7164897918701</t>
+    <t xml:space="preserve">23.6021575927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7164878845215</t>
   </si>
   <si>
     <t xml:space="preserve">22.7282199859619</t>
@@ -1343,25 +1343,25 @@
     <t xml:space="preserve">22.3176441192627</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9833202362061</t>
+    <t xml:space="preserve">21.9833221435547</t>
   </si>
   <si>
     <t xml:space="preserve">22.6754302978516</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4056243896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6109104156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7927341461182</t>
+    <t xml:space="preserve">22.4056262969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.610912322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7927360534668</t>
   </si>
   <si>
     <t xml:space="preserve">22.2355289459229</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5492877960205</t>
+    <t xml:space="preserve">21.5492839813232</t>
   </si>
   <si>
     <t xml:space="preserve">21.5199565887451</t>
@@ -1370,25 +1370,25 @@
     <t xml:space="preserve">21.7311115264893</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8249549865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4495735168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9040946960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4026546478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8777408599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4701442718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.191499710083</t>
+    <t xml:space="preserve">21.8249568939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4495754241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9040966033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4026508331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.877742767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.470142364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1914958953857</t>
   </si>
   <si>
     <t xml:space="preserve">21.1093826293945</t>
@@ -1397,40 +1397,40 @@
     <t xml:space="preserve">21.0565948486328</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7135124206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7047538757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9130210876465</t>
+    <t xml:space="preserve">21.7135143280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7047576904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9130153656006</t>
   </si>
   <si>
     <t xml:space="preserve">23.0449485778809</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3440818786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7546539306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7663841247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4496574401855</t>
+    <t xml:space="preserve">23.3440837860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7546577453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7663898468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4496536254883</t>
   </si>
   <si>
     <t xml:space="preserve">23.520040512085</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3469676971436</t>
+    <t xml:space="preserve">22.3469696044922</t>
   </si>
   <si>
     <t xml:space="preserve">23.0273494720459</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1563835144043</t>
+    <t xml:space="preserve">23.1563911437988</t>
   </si>
   <si>
     <t xml:space="preserve">22.8631210327148</t>
@@ -1439,10 +1439,10 @@
     <t xml:space="preserve">23.0508117675781</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9569664001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.781005859375</t>
+    <t xml:space="preserve">22.9569702148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7810039520264</t>
   </si>
   <si>
     <t xml:space="preserve">22.5229320526123</t>
@@ -1451,40 +1451,40 @@
     <t xml:space="preserve">22.4994697570801</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2765884399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9452381134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4525508880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0771656036377</t>
+    <t xml:space="preserve">22.2765865325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9452362060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4525470733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0771636962891</t>
   </si>
   <si>
     <t xml:space="preserve">21.2208251953125</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7398643493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2677440643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6489143371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4260292053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7750587463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1621723175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9158267974854</t>
+    <t xml:space="preserve">20.7398662567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2677459716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6489105224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4260272979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7750549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1621742248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.915828704834</t>
   </si>
   <si>
     <t xml:space="preserve">21.3733215332031</t>
@@ -1493,19 +1493,19 @@
     <t xml:space="preserve">21.3615913391113</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3264007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2794799804688</t>
+    <t xml:space="preserve">21.3264026641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2794742584229</t>
   </si>
   <si>
     <t xml:space="preserve">21.3967838287354</t>
   </si>
   <si>
-    <t xml:space="preserve">21.044864654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7985191345215</t>
+    <t xml:space="preserve">21.0448665618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7985172271729</t>
   </si>
   <si>
     <t xml:space="preserve">20.6812114715576</t>
@@ -1514,34 +1514,34 @@
     <t xml:space="preserve">20.0125617980957</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3321838378906</t>
+    <t xml:space="preserve">19.332181930542</t>
   </si>
   <si>
     <t xml:space="preserve">19.015453338623</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3556461334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0975685119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0858383178711</t>
+    <t xml:space="preserve">19.3556423187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0975723266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0858402252197</t>
   </si>
   <si>
     <t xml:space="preserve">20.071216583252</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9891014099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8394927978516</t>
+    <t xml:space="preserve">19.9890995025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8394908905029</t>
   </si>
   <si>
     <t xml:space="preserve">18.3468055725098</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5227642059326</t>
+    <t xml:space="preserve">18.5227661132812</t>
   </si>
   <si>
     <t xml:space="preserve">19.4377593994141</t>
@@ -1550,28 +1550,28 @@
     <t xml:space="preserve">19.2617988586426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9919929504395</t>
+    <t xml:space="preserve">18.9919910430908</t>
   </si>
   <si>
     <t xml:space="preserve">18.3233432769775</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3614292144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6987247467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9596920013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.722188949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1210327148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2735271453857</t>
+    <t xml:space="preserve">17.3614273071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6987266540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9596900939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7221870422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1210269927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.273530960083</t>
   </si>
   <si>
     <t xml:space="preserve">19.4142990112305</t>
@@ -1580,19 +1580,19 @@
     <t xml:space="preserve">20.1533317565918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7310276031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5785274505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.813138961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6958351135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3461208343506</t>
+    <t xml:space="preserve">19.7310256958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5785293579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8131408691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.695837020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3461227416992</t>
   </si>
   <si>
     <t xml:space="preserve">19.3582210540771</t>
@@ -1601,28 +1601,28 @@
     <t xml:space="preserve">19.1404399871826</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0920429229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1646385192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7816829681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9752635955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2656383514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4350204467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6649036407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3745288848877</t>
+    <t xml:space="preserve">19.0920467376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1646404266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7816848754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9752674102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2656364440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.435022354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6649017333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3745269775391</t>
   </si>
   <si>
     <t xml:space="preserve">20.02366065979</t>
@@ -1631,22 +1631,22 @@
     <t xml:space="preserve">19.5397033691406</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4429168701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6485919952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7211875915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9589576721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3298168182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4103031158447</t>
+    <t xml:space="preserve">19.4429130554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6485939025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7211837768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9589557647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3298149108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4102993011475</t>
   </si>
   <si>
     <t xml:space="preserve">17.0836315155029</t>
@@ -1655,13 +1655,13 @@
     <t xml:space="preserve">17.2288150787354</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8779487609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5149803161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6075668334961</t>
+    <t xml:space="preserve">16.877950668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5149822235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6075649261475</t>
   </si>
   <si>
     <t xml:space="preserve">14.167799949646</t>
@@ -1673,13 +1673,13 @@
     <t xml:space="preserve">14.119402885437</t>
   </si>
   <si>
-    <t xml:space="preserve">14.22829246521</t>
+    <t xml:space="preserve">14.2282915115356</t>
   </si>
   <si>
     <t xml:space="preserve">15.4260816574097</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4865760803223</t>
+    <t xml:space="preserve">15.4865779876709</t>
   </si>
   <si>
     <t xml:space="preserve">15.0147199630737</t>
@@ -1688,28 +1688,28 @@
     <t xml:space="preserve">15.1478080749512</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8332386016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7001476287842</t>
+    <t xml:space="preserve">14.8332376480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7001485824585</t>
   </si>
   <si>
     <t xml:space="preserve">15.2929964065552</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1520175933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5996723175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.575475692749</t>
+    <t xml:space="preserve">16.1520156860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5996742248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5754737854004</t>
   </si>
   <si>
     <t xml:space="preserve">16.0794239044189</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7932567596436</t>
+    <t xml:space="preserve">16.7932548522949</t>
   </si>
   <si>
     <t xml:space="preserve">17.2409133911133</t>
@@ -1718,16 +1718,16 @@
     <t xml:space="preserve">16.7327632904053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9021472930908</t>
+    <t xml:space="preserve">16.9021492004395</t>
   </si>
   <si>
     <t xml:space="preserve">16.623872756958</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9705324172974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4623794555664</t>
+    <t xml:space="preserve">15.970534324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4623775482178</t>
   </si>
   <si>
     <t xml:space="preserve">15.5712699890137</t>
@@ -1736,7 +1736,7 @@
     <t xml:space="preserve">15.5954685211182</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6438646316528</t>
+    <t xml:space="preserve">15.6438608169556</t>
   </si>
   <si>
     <t xml:space="preserve">15.619665145874</t>
@@ -1745,34 +1745,34 @@
     <t xml:space="preserve">15.7890510559082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0431270599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4060935974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5875759124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2730026245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9100370407104</t>
+    <t xml:space="preserve">16.0431251525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4060916900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5875778198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2730045318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9100379943848</t>
   </si>
   <si>
     <t xml:space="preserve">15.9947290420532</t>
   </si>
   <si>
-    <t xml:space="preserve">15.825345993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6722679138184</t>
+    <t xml:space="preserve">15.8253440856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6722660064697</t>
   </si>
   <si>
     <t xml:space="preserve">16.9384441375732</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2851028442383</t>
+    <t xml:space="preserve">16.2851047515869</t>
   </si>
   <si>
     <t xml:space="preserve">16.0552253723145</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">16.2972049713135</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3576984405518</t>
+    <t xml:space="preserve">16.3576965332031</t>
   </si>
   <si>
     <t xml:space="preserve">16.2125091552734</t>
@@ -1790,115 +1790,115 @@
     <t xml:space="preserve">15.3655891418457</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5470743179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6396560668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3692712783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6838407516479</t>
+    <t xml:space="preserve">15.5470705032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6396551132202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.36927318573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6838436126709</t>
   </si>
   <si>
     <t xml:space="preserve">13.6475448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6354484558105</t>
+    <t xml:space="preserve">13.6354475021362</t>
   </si>
   <si>
     <t xml:space="preserve">13.2845783233643</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0425996780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5102519989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.377161026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4860525131226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4497566223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2603816986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7885246276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9700078964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9216146469116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0909967422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3408641815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2924709320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2561740875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7643270492554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1998863220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6596450805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5265560150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3571729660034</t>
+    <t xml:space="preserve">13.0426015853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5102510452271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3771619796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4860515594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4497547149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2603826522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7885255813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9700117111206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9216156005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0909986495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3408660888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2924690246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2561750411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7643280029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1998853683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6596441268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5265579223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3571720123291</t>
   </si>
   <si>
     <t xml:space="preserve">13.8895235061646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5749521255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6717433929443</t>
+    <t xml:space="preserve">13.5749540328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6717443466187</t>
   </si>
   <si>
     <t xml:space="preserve">13.3208770751953</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3450736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5023574829102</t>
+    <t xml:space="preserve">13.3450727462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5023584365845</t>
   </si>
   <si>
     <t xml:space="preserve">14.0589065551758</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4218740463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3976755142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2645864486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4339733123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3934698104858</t>
+    <t xml:space="preserve">14.421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3976764678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2645893096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4339742660522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3934688568115</t>
   </si>
   <si>
     <t xml:space="preserve">11.7359218597412</t>
@@ -1910,49 +1910,49 @@
     <t xml:space="preserve">11.3003625869751</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6088838577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9778985977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8024663925171</t>
+    <t xml:space="preserve">11.6088829040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9778995513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8024673461914</t>
   </si>
   <si>
     <t xml:space="preserve">10.3143014907837</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5865259170532</t>
+    <t xml:space="preserve">10.5865278244019</t>
   </si>
   <si>
     <t xml:space="preserve">10.2356595993042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86664390563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3264007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3022031784058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4957857131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92108917236328</t>
+    <t xml:space="preserve">9.86664295196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3263998031616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3022041320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4957866668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92108821868896</t>
   </si>
   <si>
     <t xml:space="preserve">9.89689159393311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53392314910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73539733886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37848091125488</t>
+    <t xml:space="preserve">9.53392505645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73539638519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37847995758057</t>
   </si>
   <si>
     <t xml:space="preserve">8.22119426727295</t>
@@ -1961,13 +1961,13 @@
     <t xml:space="preserve">8.46922206878662</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49946880340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9713249206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06206703186035</t>
+    <t xml:space="preserve">8.49946975708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97132587432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06206607818604</t>
   </si>
   <si>
     <t xml:space="preserve">9.40083599090576</t>
@@ -1976,25 +1976,25 @@
     <t xml:space="preserve">9.67911052703857</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2175102233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88479328155518</t>
+    <t xml:space="preserve">10.217511177063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88479232788086</t>
   </si>
   <si>
     <t xml:space="preserve">9.12256050109863</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21935367584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82009029388428</t>
+    <t xml:space="preserve">9.21935176849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82008934020996</t>
   </si>
   <si>
     <t xml:space="preserve">9.12861061096191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24960041046143</t>
+    <t xml:space="preserve">9.24959945678711</t>
   </si>
   <si>
     <t xml:space="preserve">9.36454010009766</t>
@@ -2003,16 +2003,16 @@
     <t xml:space="preserve">9.58836936950684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48552894592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45528125762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70935726165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6125659942627</t>
+    <t xml:space="preserve">9.48552989959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45528030395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70935821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61256694793701</t>
   </si>
   <si>
     <t xml:space="preserve">9.57021999359131</t>
@@ -2024,34 +2024,34 @@
     <t xml:space="preserve">11.1370267868042</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9071474075317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5967826843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3064126968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.00998878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9676399230957</t>
+    <t xml:space="preserve">10.9071493148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5967836380005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3064107894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0099897384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9676418304443</t>
   </si>
   <si>
     <t xml:space="preserve">10.513934135437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8285036087036</t>
+    <t xml:space="preserve">10.8285045623779</t>
   </si>
   <si>
     <t xml:space="preserve">10.3385009765625</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7377624511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2840557098389</t>
+    <t xml:space="preserve">10.7377634048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2840547561646</t>
   </si>
   <si>
     <t xml:space="preserve">10.6409721374512</t>
@@ -2063,22 +2063,22 @@
     <t xml:space="preserve">11.0039396286011</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8587522506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3747968673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81219863891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6912088394165</t>
+    <t xml:space="preserve">10.8587512969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3747959136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8121976852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69121074676514</t>
   </si>
   <si>
     <t xml:space="preserve">9.3705883026123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17095756530762</t>
+    <t xml:space="preserve">9.1709566116333</t>
   </si>
   <si>
     <t xml:space="preserve">9.03786945343018</t>
@@ -2090,25 +2090,25 @@
     <t xml:space="preserve">9.34639072418213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94528675079346</t>
+    <t xml:space="preserve">9.94528579711914</t>
   </si>
   <si>
     <t xml:space="preserve">10.4050445556641</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8043079376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5562791824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.62282371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5804777145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5502290725708</t>
+    <t xml:space="preserve">10.8043069839478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5562801361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6228246688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5804767608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5502300262451</t>
   </si>
   <si>
     <t xml:space="preserve">10.0239286422729</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">10.1025714874268</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2296085357666</t>
+    <t xml:space="preserve">10.2296104431152</t>
   </si>
   <si>
     <t xml:space="preserve">10.4655380249023</t>
@@ -2129,7 +2129,7 @@
     <t xml:space="preserve">10.3687467575073</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98763179779053</t>
+    <t xml:space="preserve">9.98763370513916</t>
   </si>
   <si>
     <t xml:space="preserve">9.96948337554932</t>
@@ -2141,10 +2141,10 @@
     <t xml:space="preserve">10.4352912902832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5320816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1509675979614</t>
+    <t xml:space="preserve">10.5320825576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1509666442871</t>
   </si>
   <si>
     <t xml:space="preserve">10.0299777984619</t>
@@ -2159,61 +2159,61 @@
     <t xml:space="preserve">10.0662746429443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64886379241943</t>
+    <t xml:space="preserve">9.64886283874512</t>
   </si>
   <si>
     <t xml:space="preserve">11.0946807861328</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6433382034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0323429107666</t>
+    <t xml:space="preserve">12.6433391571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0323438644409</t>
   </si>
   <si>
     <t xml:space="preserve">11.3729543685913</t>
   </si>
   <si>
-    <t xml:space="preserve">10.876898765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7014675140381</t>
+    <t xml:space="preserve">10.8768997192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7014665603638</t>
   </si>
   <si>
     <t xml:space="preserve">10.6107263565063</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5683794021606</t>
+    <t xml:space="preserve">10.568377494812</t>
   </si>
   <si>
     <t xml:space="preserve">10.10862159729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3506002426147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9373950958252</t>
+    <t xml:space="preserve">10.3505992889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9373960494995</t>
   </si>
   <si>
     <t xml:space="preserve">11.0341854095459</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1128301620483</t>
+    <t xml:space="preserve">11.112829208374</t>
   </si>
   <si>
     <t xml:space="preserve">11.4818439483643</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9736909866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54602146148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35848999023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22540187835693</t>
+    <t xml:space="preserve">10.973690032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54602336883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35848903656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22540283203125</t>
   </si>
   <si>
     <t xml:space="preserve">9.11046409606934</t>
@@ -2225,16 +2225,16 @@
     <t xml:space="preserve">9.1346607208252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92897987365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97737407684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95317840576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84428596496582</t>
+    <t xml:space="preserve">8.92897891998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97737503051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9531774520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84428691864014</t>
   </si>
   <si>
     <t xml:space="preserve">8.89873313903809</t>
@@ -2243,34 +2243,34 @@
     <t xml:space="preserve">9.0741662979126</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00157260894775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24355030059814</t>
+    <t xml:space="preserve">9.00157356262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24355125427246</t>
   </si>
   <si>
     <t xml:space="preserve">9.4976282119751</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47947883605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46132946014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38873767852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63676357269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68515872955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.715407371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83034801483154</t>
+    <t xml:space="preserve">9.47947788238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46133041381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38873863220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63676452636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68515968322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71540641784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83034706115723</t>
   </si>
   <si>
     <t xml:space="preserve">10.2636575698853</t>
@@ -2282,13 +2282,13 @@
     <t xml:space="preserve">9.65572929382324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7268705368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21594905853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0477991104126</t>
+    <t xml:space="preserve">9.72686958312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21595001220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04779815673828</t>
   </si>
   <si>
     <t xml:space="preserve">8.73736763000488</t>
@@ -2297,7 +2297,7 @@
     <t xml:space="preserve">8.52394485473633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27818584442139</t>
+    <t xml:space="preserve">8.2781867980957</t>
   </si>
   <si>
     <t xml:space="preserve">7.86427688598633</t>
@@ -2306,58 +2306,58 @@
     <t xml:space="preserve">8.32345867156982</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37519550323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31698989868164</t>
+    <t xml:space="preserve">8.37519645690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31699085235596</t>
   </si>
   <si>
     <t xml:space="preserve">8.07123184204102</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87721252441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90954875946045</t>
+    <t xml:space="preserve">7.87721347808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90954780578613</t>
   </si>
   <si>
     <t xml:space="preserve">7.82547378540039</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56678009033203</t>
+    <t xml:space="preserve">7.56677913665771</t>
   </si>
   <si>
     <t xml:space="preserve">7.72199487686157</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59264898300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54090976715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50210762023926</t>
+    <t xml:space="preserve">7.59264993667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54091024398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50210666656494</t>
   </si>
   <si>
     <t xml:space="preserve">7.3727593421936</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31455278396606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66378974914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32748937606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24341297149658</t>
+    <t xml:space="preserve">7.31455373764038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66379070281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32748794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24341249465942</t>
   </si>
   <si>
     <t xml:space="preserve">7.2886848449707</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52150917053223</t>
+    <t xml:space="preserve">7.52150964736938</t>
   </si>
   <si>
     <t xml:space="preserve">7.26281547546387</t>
@@ -2369,7 +2369,7 @@
     <t xml:space="preserve">7.25634813308716</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41803216934204</t>
+    <t xml:space="preserve">7.41803169250488</t>
   </si>
   <si>
     <t xml:space="preserve">7.70906114578247</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">8.03242778778076</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84487628936768</t>
+    <t xml:space="preserve">7.84487438201904</t>
   </si>
   <si>
     <t xml:space="preserve">7.70259380340576</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">7.5538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76726627349854</t>
+    <t xml:space="preserve">7.76726722717285</t>
   </si>
   <si>
     <t xml:space="preserve">7.79960441589355</t>
@@ -2396,7 +2396,7 @@
     <t xml:space="preserve">7.6767258644104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99362373352051</t>
+    <t xml:space="preserve">7.99362468719482</t>
   </si>
   <si>
     <t xml:space="preserve">8.18117618560791</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">8.70503044128418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65329265594482</t>
+    <t xml:space="preserve">8.65329170227051</t>
   </si>
   <si>
     <t xml:space="preserve">8.69856262207031</t>
@@ -2414,13 +2414,13 @@
     <t xml:space="preserve">8.79557323455811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58215141296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57568454742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49160861968994</t>
+    <t xml:space="preserve">8.58215236663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57568359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49160957336426</t>
   </si>
   <si>
     <t xml:space="preserve">8.55628204345703</t>
@@ -2429,10 +2429,10 @@
     <t xml:space="preserve">8.95725727081299</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94432163238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9378547668457</t>
+    <t xml:space="preserve">8.94432258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93785572052002</t>
   </si>
   <si>
     <t xml:space="preserve">8.7503023147583</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">8.82790946960449</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83437728881836</t>
+    <t xml:space="preserve">8.83437633514404</t>
   </si>
   <si>
     <t xml:space="preserve">8.71149921417236</t>
@@ -2459,37 +2459,37 @@
     <t xml:space="preserve">8.3881311416626</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29758834838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5433464050293</t>
+    <t xml:space="preserve">8.29758739471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54334735870361</t>
   </si>
   <si>
     <t xml:space="preserve">9.02839756011963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91845321655273</t>
+    <t xml:space="preserve">8.91845226287842</t>
   </si>
   <si>
     <t xml:space="preserve">8.88611602783203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12540721893311</t>
+    <t xml:space="preserve">9.12540626525879</t>
   </si>
   <si>
     <t xml:space="preserve">8.48514175415039</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11003589630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87074518203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26525211334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33639335632324</t>
+    <t xml:space="preserve">8.11003684997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87074422836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26525115966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33639240264893</t>
   </si>
   <si>
     <t xml:space="preserve">8.4334020614624</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">8.36872959136963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28465366363525</t>
+    <t xml:space="preserve">8.28465461730957</t>
   </si>
   <si>
     <t xml:space="preserve">8.23938274383545</t>
@@ -2507,28 +2507,28 @@
     <t xml:space="preserve">8.56274890899658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76970386505127</t>
+    <t xml:space="preserve">8.76970481872559</t>
   </si>
   <si>
     <t xml:space="preserve">9.02192974090576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13187503814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2224178314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45524024963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44230651855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50697994232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55871868133545</t>
+    <t xml:space="preserve">9.13187408447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22241687774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45524120330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.442307472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50697898864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55871772766113</t>
   </si>
   <si>
     <t xml:space="preserve">9.58458805084229</t>
@@ -2537,28 +2537,28 @@
     <t xml:space="preserve">9.69453239440918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91442203521729</t>
+    <t xml:space="preserve">9.9144229888916</t>
   </si>
   <si>
     <t xml:space="preserve">9.92088890075684</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73333644866943</t>
+    <t xml:space="preserve">9.73333740234375</t>
   </si>
   <si>
     <t xml:space="preserve">9.89502048492432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90795421600342</t>
+    <t xml:space="preserve">9.9079532623291</t>
   </si>
   <si>
     <t xml:space="preserve">9.67512989044189</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57812023162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66866397857666</t>
+    <t xml:space="preserve">9.57812118530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66866302490234</t>
   </si>
   <si>
     <t xml:space="preserve">9.90148639678955</t>
@@ -2567,25 +2567,25 @@
     <t xml:space="preserve">9.7074670791626</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51991367340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30649375915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33236217498779</t>
+    <t xml:space="preserve">9.5199146270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30649185180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33236122131348</t>
   </si>
   <si>
     <t xml:space="preserve">9.43583965301514</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09953689575195</t>
+    <t xml:space="preserve">9.09953784942627</t>
   </si>
   <si>
     <t xml:space="preserve">9.37116527557373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52638149261475</t>
+    <t xml:space="preserve">9.52638244628906</t>
   </si>
   <si>
     <t xml:space="preserve">9.79154205322266</t>
@@ -2597,10 +2597,10 @@
     <t xml:space="preserve">9.76567363739014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87561893463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95322704315186</t>
+    <t xml:space="preserve">9.87561798095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95322608947754</t>
   </si>
   <si>
     <t xml:space="preserve">9.99849700927734</t>
@@ -2609,19 +2609,19 @@
     <t xml:space="preserve">9.94675922393799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77214050292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8820858001709</t>
+    <t xml:space="preserve">9.77213954925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88208484649658</t>
   </si>
   <si>
     <t xml:space="preserve">9.98556232452393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2248544692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44877338409424</t>
+    <t xml:space="preserve">10.224853515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44877433776855</t>
   </si>
   <si>
     <t xml:space="preserve">9.83034610748291</t>
@@ -2633,64 +2633,64 @@
     <t xml:space="preserve">10.1925172805786</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2377901077271</t>
+    <t xml:space="preserve">10.2377882003784</t>
   </si>
   <si>
     <t xml:space="preserve">9.62339210510254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41643810272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34529685974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24181938171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19008159637451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06073474884033</t>
+    <t xml:space="preserve">9.41643714904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34529590606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24181842803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19007873535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06073379516602</t>
   </si>
   <si>
     <t xml:space="preserve">9.08013534545898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97665882110596</t>
+    <t xml:space="preserve">8.97665786743164</t>
   </si>
   <si>
     <t xml:space="preserve">9.04133033752441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92491912841797</t>
+    <t xml:space="preserve">8.92492008209229</t>
   </si>
   <si>
     <t xml:space="preserve">8.7632360458374</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84731197357178</t>
+    <t xml:space="preserve">8.84731101989746</t>
   </si>
   <si>
     <t xml:space="preserve">8.78263854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61448764801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56921672821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67916107177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86671447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8731803894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81497573852539</t>
+    <t xml:space="preserve">8.61448669433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56921768188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67916202545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86671352386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87318134307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81497478485107</t>
   </si>
   <si>
     <t xml:space="preserve">8.8602466583252</t>
@@ -2699,25 +2699,25 @@
     <t xml:space="preserve">9.24828720092773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05426692962646</t>
+    <t xml:space="preserve">9.05426788330078</t>
   </si>
   <si>
     <t xml:space="preserve">9.14480972290039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2353515625</t>
+    <t xml:space="preserve">9.23535251617432</t>
   </si>
   <si>
     <t xml:space="preserve">9.15774345397949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13834095001221</t>
+    <t xml:space="preserve">9.13834190368652</t>
   </si>
   <si>
     <t xml:space="preserve">9.26768779754639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09307193756104</t>
+    <t xml:space="preserve">9.0930700302124</t>
   </si>
   <si>
     <t xml:space="preserve">8.93138694763184</t>
@@ -2726,31 +2726,31 @@
     <t xml:space="preserve">9.2030143737793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59105491638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5716552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51344776153564</t>
+    <t xml:space="preserve">9.59105587005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57165336608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51344871520996</t>
   </si>
   <si>
     <t xml:space="preserve">9.53284931182861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32589530944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30002403259277</t>
+    <t xml:space="preserve">9.32589435577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30002593994141</t>
   </si>
   <si>
     <t xml:space="preserve">9.74627208709717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47464466094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27415657043457</t>
+    <t xml:space="preserve">9.47464275360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27415561676025</t>
   </si>
   <si>
     <t xml:space="preserve">9.62985992431641</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">10.1278438568115</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0696382522583</t>
+    <t xml:space="preserve">10.069637298584</t>
   </si>
   <si>
     <t xml:space="preserve">10.1407794952393</t>
@@ -2780,31 +2780,31 @@
     <t xml:space="preserve">10.1472454071045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35176372528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5522518157959</t>
+    <t xml:space="preserve">9.35176467895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55225276947021</t>
   </si>
   <si>
     <t xml:space="preserve">8.8925838470459</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40753364562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90308237075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88124418258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61608076095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59667921066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67185211181641</t>
+    <t xml:space="preserve">8.40753269195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90308141708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88124370574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61608219146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59668016433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67185115814209</t>
   </si>
   <si>
     <t xml:space="preserve">5.93701171875</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">5.44549465179443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45842933654785</t>
+    <t xml:space="preserve">5.45842885971069</t>
   </si>
   <si>
     <t xml:space="preserve">5.43902683258057</t>
@@ -2825,25 +2825,25 @@
     <t xml:space="preserve">5.75592613220215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57160806655884</t>
+    <t xml:space="preserve">5.57160711288452</t>
   </si>
   <si>
     <t xml:space="preserve">5.84000205993652</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86910438537598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9822826385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90790891647339</t>
+    <t xml:space="preserve">5.86910486221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98228359222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90790987014771</t>
   </si>
   <si>
     <t xml:space="preserve">5.66215038299561</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78826236724854</t>
+    <t xml:space="preserve">5.78826284408569</t>
   </si>
   <si>
     <t xml:space="preserve">5.75916004180908</t>
@@ -2852,55 +2852,55 @@
     <t xml:space="preserve">5.7009539604187</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78179550170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83676767349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96934843063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94671249389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9758152961731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83353471755981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71388912200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76886224746704</t>
+    <t xml:space="preserve">5.78179502487183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83676815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96934795379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94671297073364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97581577301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83353567123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71388864517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76886177062988</t>
   </si>
   <si>
     <t xml:space="preserve">5.77532911300659</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49723339080811</t>
+    <t xml:space="preserve">5.49723243713379</t>
   </si>
   <si>
     <t xml:space="preserve">5.38405466079712</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51663446426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81413173675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93054485321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77209520339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5619068145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62011241912842</t>
+    <t xml:space="preserve">5.51663541793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81413221359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93054389953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7720947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56190729141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62011289596558</t>
   </si>
   <si>
     <t xml:space="preserve">5.58454179763794</t>
@@ -2915,19 +2915,19 @@
     <t xml:space="preserve">5.48106527328491</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40669012069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32584810256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22560548782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19326877593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17386627197266</t>
+    <t xml:space="preserve">5.40668964385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32584857940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22560501098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19326829910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17386674880981</t>
   </si>
   <si>
     <t xml:space="preserve">4.94751024246216</t>
@@ -2936,22 +2936,22 @@
     <t xml:space="preserve">4.81169605255127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70821905136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72115325927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97984600067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18033361434937</t>
+    <t xml:space="preserve">4.70821857452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7211537361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97984647750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18033409118652</t>
   </si>
   <si>
     <t xml:space="preserve">5.33554983139038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42932605743408</t>
+    <t xml:space="preserve">5.42932653427124</t>
   </si>
   <si>
     <t xml:space="preserve">5.36465263366699</t>
@@ -2960,43 +2960,43 @@
     <t xml:space="preserve">5.40022325515747</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7268238067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94347906112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25391101837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70015668869019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28624773025513</t>
+    <t xml:space="preserve">5.72682285308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94347858428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2539119720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70015621185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28624820709229</t>
   </si>
   <si>
     <t xml:space="preserve">6.09222841262817</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67508411407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63304662704468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78502893447876</t>
+    <t xml:space="preserve">5.67508459091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63304805755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78502941131592</t>
   </si>
   <si>
     <t xml:space="preserve">5.87880563735962</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82059955596924</t>
+    <t xml:space="preserve">5.8206000328064</t>
   </si>
   <si>
     <t xml:space="preserve">5.73329067230225</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58777618408203</t>
+    <t xml:space="preserve">5.58777666091919</t>
   </si>
   <si>
     <t xml:space="preserve">5.53603744506836</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">5.31614780426025</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37435388565063</t>
+    <t xml:space="preserve">5.37435436248779</t>
   </si>
   <si>
     <t xml:space="preserve">5.49399995803833</t>
@@ -3020,13 +3020,13 @@
     <t xml:space="preserve">5.51340103149414</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64598226547241</t>
+    <t xml:space="preserve">5.64598178863525</t>
   </si>
   <si>
     <t xml:space="preserve">5.75269365310669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86587142944336</t>
+    <t xml:space="preserve">5.8658709526062</t>
   </si>
   <si>
     <t xml:space="preserve">5.80119848251343</t>
@@ -3044,22 +3044,22 @@
     <t xml:space="preserve">6.34768676757812</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39942598342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19570541381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05989074707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91760969161987</t>
+    <t xml:space="preserve">6.39942646026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19570589065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05989170074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91761016845703</t>
   </si>
   <si>
     <t xml:space="preserve">5.77856206893921</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60717821121216</t>
+    <t xml:space="preserve">5.60717868804932</t>
   </si>
   <si>
     <t xml:space="preserve">5.60394430160522</t>
@@ -3068,16 +3068,16 @@
     <t xml:space="preserve">5.80766487121582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81736707687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68478631973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93377780914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91114234924316</t>
+    <t xml:space="preserve">5.81736660003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68478584289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93377828598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91114282608032</t>
   </si>
   <si>
     <t xml:space="preserve">5.94024610519409</t>
@@ -3092,16 +3092,16 @@
     <t xml:space="preserve">5.89820766448975</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73652410507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74946022033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79796457290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63951396942139</t>
+    <t xml:space="preserve">5.73652458190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74945974349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79796409606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63951444625854</t>
   </si>
   <si>
     <t xml:space="preserve">5.59100961685181</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">5.58130884170532</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70418787002563</t>
+    <t xml:space="preserve">5.70418834686279</t>
   </si>
   <si>
     <t xml:space="preserve">5.70742130279541</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">5.66538381576538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69448757171631</t>
+    <t xml:space="preserve">5.69448804855347</t>
   </si>
   <si>
     <t xml:space="preserve">5.88204002380371</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">5.39052200317383</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33878374099731</t>
+    <t xml:space="preserve">5.33878421783447</t>
   </si>
   <si>
     <t xml:space="preserve">5.43255949020386</t>
@@ -3146,31 +3146,31 @@
     <t xml:space="preserve">5.30321359634399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3193826675415</t>
+    <t xml:space="preserve">5.31938219070435</t>
   </si>
   <si>
     <t xml:space="preserve">5.21267080307007</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21590375900269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2288384437561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34201765060425</t>
+    <t xml:space="preserve">5.21590423583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22883892059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34201669692993</t>
   </si>
   <si>
     <t xml:space="preserve">5.26764345169067</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32261514663696</t>
+    <t xml:space="preserve">5.32261562347412</t>
   </si>
   <si>
     <t xml:space="preserve">5.2999792098999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21913719177246</t>
+    <t xml:space="preserve">5.21913766860962</t>
   </si>
   <si>
     <t xml:space="preserve">5.07362270355225</t>
@@ -3191,28 +3191,28 @@
     <t xml:space="preserve">5.20296955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04128646850586</t>
+    <t xml:space="preserve">5.0412859916687</t>
   </si>
   <si>
     <t xml:space="preserve">4.9960150718689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92164087295532</t>
+    <t xml:space="preserve">4.92164039611816</t>
   </si>
   <si>
     <t xml:space="preserve">4.8149299621582</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82463121414185</t>
+    <t xml:space="preserve">4.82463073730469</t>
   </si>
   <si>
     <t xml:space="preserve">4.50773143768311</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36221647262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45275926589966</t>
+    <t xml:space="preserve">4.36221599578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4527587890625</t>
   </si>
   <si>
     <t xml:space="preserve">4.58857297897339</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">4.78259325027466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89900493621826</t>
+    <t xml:space="preserve">4.89900541305542</t>
   </si>
   <si>
     <t xml:space="preserve">4.82786464691162</t>
@@ -3230,19 +3230,19 @@
     <t xml:space="preserve">4.79229402542114</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13829565048218</t>
+    <t xml:space="preserve">5.13829612731934</t>
   </si>
   <si>
     <t xml:space="preserve">5.14799785614014</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25794172286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23530673980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65891599655151</t>
+    <t xml:space="preserve">5.25794219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23530578613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65891647338867</t>
   </si>
   <si>
     <t xml:space="preserve">5.84323596954346</t>
@@ -3251,16 +3251,16 @@
     <t xml:space="preserve">5.85940408706665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07606077194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0081524848938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97904968261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98875093460083</t>
+    <t xml:space="preserve">6.07606029510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00815296173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97905015945435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98875045776367</t>
   </si>
   <si>
     <t xml:space="preserve">5.90467548370361</t>
@@ -3272,25 +3272,25 @@
     <t xml:space="preserve">6.29918193817139</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31858396530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34445524215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21834135055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19247150421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13103103637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05665731430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10516214370728</t>
+    <t xml:space="preserve">6.31858491897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34445333480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2183403968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19247198104858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13103151321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0566577911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10516309738159</t>
   </si>
   <si>
     <t xml:space="preserve">6.10192918777466</t>
@@ -3299,100 +3299,100 @@
     <t xml:space="preserve">6.04048919677734</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03725576400757</t>
+    <t xml:space="preserve">6.03725528717041</t>
   </si>
   <si>
     <t xml:space="preserve">6.06635856628418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8885064125061</t>
+    <t xml:space="preserve">5.88850688934326</t>
   </si>
   <si>
     <t xml:space="preserve">5.95318031311035</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99198532104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98551654815674</t>
+    <t xml:space="preserve">5.99198436737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9855170249939</t>
   </si>
   <si>
     <t xml:space="preserve">6.02432060241699</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01138639450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97258281707764</t>
+    <t xml:space="preserve">6.01138544082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97258234024048</t>
   </si>
   <si>
     <t xml:space="preserve">5.73005676269531</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7397575378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64921569824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55543899536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36788702011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46812963485718</t>
+    <t xml:space="preserve">5.73975801467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64921522140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55543947219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36788654327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46813058853149</t>
   </si>
   <si>
     <t xml:space="preserve">5.41639184951782</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72359037399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07282543182373</t>
+    <t xml:space="preserve">5.72358989715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07282590866089</t>
   </si>
   <si>
     <t xml:space="preserve">6.26037883758545</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39619255065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75836324691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67428779602051</t>
+    <t xml:space="preserve">6.39619302749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75836372375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67428684234619</t>
   </si>
   <si>
     <t xml:space="preserve">6.75189590454102</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66782093048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66135358810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58374547958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64195203781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69368982315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90064382553101</t>
+    <t xml:space="preserve">6.66782188415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66135311126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58374500274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64195156097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69369125366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90064477920532</t>
   </si>
   <si>
     <t xml:space="preserve">6.80363416671753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97178411483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83597087860107</t>
+    <t xml:space="preserve">6.97178554534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83597135543823</t>
   </si>
   <si>
     <t xml:space="preserve">6.85537385940552</t>
@@ -3404,67 +3404,67 @@
     <t xml:space="preserve">7.21107578277588</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19167470932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23694610595703</t>
+    <t xml:space="preserve">7.19167518615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23694562911987</t>
   </si>
   <si>
     <t xml:space="preserve">7.42449855804443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48270463943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39216184616089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41156387329102</t>
+    <t xml:space="preserve">7.48270416259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39216327667236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41156339645386</t>
   </si>
   <si>
     <t xml:space="preserve">7.16580581665039</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19814157485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24988079071045</t>
+    <t xml:space="preserve">7.19814205169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24988031387329</t>
   </si>
   <si>
     <t xml:space="preserve">7.35335779190063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36629343032837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27575016021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32102155685425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34689044952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15287065505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49563932418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43743324279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3986291885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35982656478882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08172988891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26928234100342</t>
+    <t xml:space="preserve">7.36629247665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27574920654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32102108001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34688949584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15287017822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49563980102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43743228912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39862871170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3598256111145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08172941207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2692813873291</t>
   </si>
   <si>
     <t xml:space="preserve">7.46330308914185</t>
@@ -3473,52 +3473,52 @@
     <t xml:space="preserve">7.5150408744812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46976900100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4439001083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47623682022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52797603607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95482063293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69612598419189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11650371551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43987083435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46573925018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40106678009033</t>
+    <t xml:space="preserve">7.4697699546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44390106201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47623777389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52797555923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95482015609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69612550735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11650276184082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43986988067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46574020385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40106582641602</t>
   </si>
   <si>
     <t xml:space="preserve">8.25878524780273</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18764495849609</t>
+    <t xml:space="preserve">8.18764305114746</t>
   </si>
   <si>
     <t xml:space="preserve">8.05182933807373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22644805908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31052398681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34932708740234</t>
+    <t xml:space="preserve">8.22644901275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31052207946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34932613372803</t>
   </si>
   <si>
     <t xml:space="preserve">8.4204683303833</t>
@@ -3530,13 +3530,13 @@
     <t xml:space="preserve">8.50454235076904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14883995056152</t>
+    <t xml:space="preserve">8.14883899688721</t>
   </si>
   <si>
     <t xml:space="preserve">9.01546287536621</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90551853179932</t>
+    <t xml:space="preserve">8.905517578125</t>
   </si>
   <si>
     <t xml:space="preserve">8.64682483673096</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">8.59508609771729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51101112365723</t>
+    <t xml:space="preserve">8.51101016998291</t>
   </si>
   <si>
     <t xml:space="preserve">8.29112148284912</t>
@@ -3557,49 +3557,49 @@
     <t xml:space="preserve">8.23291492462158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35579395294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96372318267822</t>
+    <t xml:space="preserve">8.35579586029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96372413635254</t>
   </si>
   <si>
     <t xml:space="preserve">8.98312664031982</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98959350585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07366847991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00252723693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99606037139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06720161437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19654750823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46817684173584</t>
+    <t xml:space="preserve">8.98959255218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07366752624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00252914428711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99606132507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0672025680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19654941558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46817588806152</t>
   </si>
   <si>
     <t xml:space="preserve">9.4229040145874</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3776330947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39056873321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46170806884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20948219299316</t>
+    <t xml:space="preserve">9.37763404846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39056777954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46170902252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20948314666748</t>
   </si>
   <si>
     <t xml:space="preserve">9.36469745635986</t>
@@ -3614,22 +3614,22 @@
     <t xml:space="preserve">9.56518650054932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81094551086426</t>
+    <t xml:space="preserve">9.81094455718994</t>
   </si>
   <si>
     <t xml:space="preserve">10.0437679290771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0890417098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3283319473267</t>
+    <t xml:space="preserve">10.0890407562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3283309936523</t>
   </si>
   <si>
     <t xml:space="preserve">10.4059391021729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4447422027588</t>
+    <t xml:space="preserve">10.4447431564331</t>
   </si>
   <si>
     <t xml:space="preserve">10.2442560195923</t>
@@ -3644,37 +3644,37 @@
     <t xml:space="preserve">11.1173467636108</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5611553192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9685964584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5934906005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.813380241394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6775674819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6581649780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8198480606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6840353012085</t>
+    <t xml:space="preserve">10.5611562728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9685955047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5934915542603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8133792877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6775684356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6581659317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8198490142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6840333938599</t>
   </si>
   <si>
     <t xml:space="preserve">11.0074014663696</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0009355545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2567691802979</t>
+    <t xml:space="preserve">11.0009346008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2567701339722</t>
   </si>
   <si>
     <t xml:space="preserve">11.2291107177734</t>
@@ -3683,37 +3683,37 @@
     <t xml:space="preserve">11.0908222198486</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9110441207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0078496932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1046504974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0424213409424</t>
+    <t xml:space="preserve">10.9110460281372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0078477859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1046495437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0424203872681</t>
   </si>
   <si>
     <t xml:space="preserve">11.056248664856</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1945400238037</t>
+    <t xml:space="preserve">11.1945390701294</t>
   </si>
   <si>
     <t xml:space="preserve">11.3051710128784</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5056896209717</t>
+    <t xml:space="preserve">11.505690574646</t>
   </si>
   <si>
     <t xml:space="preserve">11.5748348236084</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5955791473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6854677200317</t>
+    <t xml:space="preserve">11.5955801010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6854667663574</t>
   </si>
   <si>
     <t xml:space="preserve">11.6508951187134</t>
@@ -3725,37 +3725,37 @@
     <t xml:space="preserve">11.7131242752075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6923799514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6301507949829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5402631759644</t>
+    <t xml:space="preserve">11.6923818588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6301517486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5402641296387</t>
   </si>
   <si>
     <t xml:space="preserve">11.2636842727661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1392230987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.828070640564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9456186294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.55149269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5100049972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4961776733398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97067737579346</t>
+    <t xml:space="preserve">11.1392240524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8280715942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9456176757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5514936447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5100059509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4961757659912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97067642211914</t>
   </si>
   <si>
     <t xml:space="preserve">10.1020517349243</t>
@@ -3767,7 +3767,7 @@
     <t xml:space="preserve">10.6828680038452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5445775985718</t>
+    <t xml:space="preserve">10.5445785522461</t>
   </si>
   <si>
     <t xml:space="preserve">10.4616050720215</t>
@@ -3788,46 +3788,46 @@
     <t xml:space="preserve">10.9179592132568</t>
   </si>
   <si>
-    <t xml:space="preserve">10.82115650177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5653228759766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7381820678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0493354797363</t>
+    <t xml:space="preserve">10.8211574554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5653219223022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7381839752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.049334526062</t>
   </si>
   <si>
     <t xml:space="preserve">11.0355052947998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7546119689941</t>
+    <t xml:space="preserve">11.7546129226685</t>
   </si>
   <si>
     <t xml:space="preserve">11.8030128479004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0934200286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2317123413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1487369537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9413013458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1210794448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0795927047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2593669891357</t>
+    <t xml:space="preserve">12.0934209823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.23171043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1487379074097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9413022994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1210784912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0795907974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2593688964844</t>
   </si>
   <si>
     <t xml:space="preserve">12.4184007644653</t>
@@ -3845,40 +3845,40 @@
     <t xml:space="preserve">12.3285131454468</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2870264053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6880655288696</t>
+    <t xml:space="preserve">12.2870273590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6880664825439</t>
   </si>
   <si>
     <t xml:space="preserve">12.570520401001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8514137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2455396652222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3561716079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3769130706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.266282081604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2040529251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6396636962891</t>
+    <t xml:space="preserve">11.8514127731323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2455387115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3561706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.376914024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2662830352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2040519714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6396646499634</t>
   </si>
   <si>
     <t xml:space="preserve">12.4806308746338</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3907432556152</t>
+    <t xml:space="preserve">12.3907442092896</t>
   </si>
   <si>
     <t xml:space="preserve">12.7364683151245</t>
@@ -3887,85 +3887,85 @@
     <t xml:space="preserve">13.2757968902588</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1885099411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3129682540894</t>
+    <t xml:space="preserve">14.1885089874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.312967300415</t>
   </si>
   <si>
     <t xml:space="preserve">14.9352722167969</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9905881881714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7554931640625</t>
+    <t xml:space="preserve">14.9905862808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7554960250854</t>
   </si>
   <si>
     <t xml:space="preserve">14.7969808578491</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9672441482544</t>
+    <t xml:space="preserve">13.9672431945801</t>
   </si>
   <si>
     <t xml:space="preserve">13.6215219497681</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6811513900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3380279541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.096022605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3354291915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5774345397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3492574691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2498540878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7589263916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7615270614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0285921096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3674011230469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8652429580688</t>
+    <t xml:space="preserve">12.6811532974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3380270004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.096019744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.335428237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5774335861206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3492565155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2498559951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7589273452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7615261077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0285911560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3674001693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8652420043945</t>
   </si>
   <si>
     <t xml:space="preserve">12.1694803237915</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8056125640869</t>
+    <t xml:space="preserve">12.8056116104126</t>
   </si>
   <si>
     <t xml:space="preserve">12.715723991394</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7433815002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0614461898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9992170333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8885860443115</t>
+    <t xml:space="preserve">12.7433834075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0614471435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9992160797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8885850906372</t>
   </si>
   <si>
     <t xml:space="preserve">13.0337915420532</t>
@@ -3974,13 +3974,13 @@
     <t xml:space="preserve">13.0683622360229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9093294143677</t>
+    <t xml:space="preserve">12.909330368042</t>
   </si>
   <si>
     <t xml:space="preserve">13.0199613571167</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2731962203979</t>
+    <t xml:space="preserve">12.2731971740723</t>
   </si>
   <si>
     <t xml:space="preserve">12.6465797424316</t>
@@ -3989,19 +3989,19 @@
     <t xml:space="preserve">12.4944610595703</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5428619384766</t>
+    <t xml:space="preserve">12.5428609848022</t>
   </si>
   <si>
     <t xml:space="preserve">12.2524538040161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5566911697388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9551305770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0865077972412</t>
+    <t xml:space="preserve">12.5566921234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9551315307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0865068435669</t>
   </si>
   <si>
     <t xml:space="preserve">11.9205589294434</t>
@@ -4013,25 +4013,25 @@
     <t xml:space="preserve">11.5817499160767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0242767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3008556365967</t>
+    <t xml:space="preserve">12.0242757797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3008546829224</t>
   </si>
   <si>
     <t xml:space="preserve">12.0381059646606</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5793085098267</t>
+    <t xml:space="preserve">12.579309463501</t>
   </si>
   <si>
     <t xml:space="preserve">12.5939331054688</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5207996368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7694606781006</t>
+    <t xml:space="preserve">12.5207986831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7694597244263</t>
   </si>
   <si>
     <t xml:space="preserve">12.6743841171265</t>
@@ -4043,16 +4043,16 @@
     <t xml:space="preserve">12.4184093475342</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3964700698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3745279312134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3452739715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3525867462158</t>
+    <t xml:space="preserve">12.3964691162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3745288848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3452730178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3525876998901</t>
   </si>
   <si>
     <t xml:space="preserve">12.140495300293</t>
@@ -4061,22 +4061,22 @@
     <t xml:space="preserve">11.9795961380005</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7455625534058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0434617996216</t>
+    <t xml:space="preserve">11.7455615997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0434627532959</t>
   </si>
   <si>
     <t xml:space="preserve">10.480318069458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5900211334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9630126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4583778381348</t>
+    <t xml:space="preserve">10.5900220870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9630136489868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4583787918091</t>
   </si>
   <si>
     <t xml:space="preserve">10.4437503814697</t>
@@ -4085,10 +4085,10 @@
     <t xml:space="preserve">10.6777849197388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5095720291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5022602081299</t>
+    <t xml:space="preserve">10.5095729827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5022592544556</t>
   </si>
   <si>
     <t xml:space="preserve">10.2389717102051</t>
@@ -4097,19 +4097,19 @@
     <t xml:space="preserve">10.494945526123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4291248321533</t>
+    <t xml:space="preserve">10.429123878479</t>
   </si>
   <si>
     <t xml:space="preserve">10.3998689651489</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2097177505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88060855865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75627613067627</t>
+    <t xml:space="preserve">10.2097187042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88060665130615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75627708435059</t>
   </si>
   <si>
     <t xml:space="preserve">9.70508193969727</t>
@@ -4118,7 +4118,7 @@
     <t xml:space="preserve">9.31015014648438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23701572418213</t>
+    <t xml:space="preserve">9.23701477050781</t>
   </si>
   <si>
     <t xml:space="preserve">9.43448162078857</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">9.69776916503906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41254043579102</t>
+    <t xml:space="preserve">9.4125394821167</t>
   </si>
   <si>
     <t xml:space="preserve">9.46373462677002</t>
@@ -4136,7 +4136,7 @@
     <t xml:space="preserve">9.06149005889893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62267589569092</t>
+    <t xml:space="preserve">8.62267684936523</t>
   </si>
   <si>
     <t xml:space="preserve">8.8274564743042</t>
@@ -4145,25 +4145,25 @@
     <t xml:space="preserve">8.97372722625732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20776081085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24432849884033</t>
+    <t xml:space="preserve">9.20776176452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24432945251465</t>
   </si>
   <si>
     <t xml:space="preserve">9.18582057952881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25895595550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53687000274658</t>
+    <t xml:space="preserve">9.25895500183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5368709564209</t>
   </si>
   <si>
     <t xml:space="preserve">9.21507453918457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3686580657959</t>
+    <t xml:space="preserve">9.36865997314453</t>
   </si>
   <si>
     <t xml:space="preserve">9.39791393280029</t>
@@ -4172,43 +4172,43 @@
     <t xml:space="preserve">9.5807523727417</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68314075469971</t>
+    <t xml:space="preserve">9.68314170837402</t>
   </si>
   <si>
     <t xml:space="preserve">9.55881023406982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9537410736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0195636749268</t>
+    <t xml:space="preserve">9.95374298095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0195655822754</t>
   </si>
   <si>
     <t xml:space="preserve">9.98299598693848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72702217102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47104835510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57343864440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80747222900391</t>
+    <t xml:space="preserve">9.72702312469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47105026245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57343769073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80747127532959</t>
   </si>
   <si>
     <t xml:space="preserve">9.97568416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49299049377441</t>
+    <t xml:space="preserve">9.4929895401001</t>
   </si>
   <si>
     <t xml:space="preserve">9.10537052154541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22238826751709</t>
+    <t xml:space="preserve">9.22238731384277</t>
   </si>
   <si>
     <t xml:space="preserve">9.20044612884521</t>
@@ -4217,40 +4217,40 @@
     <t xml:space="preserve">9.06880378723145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82014274597168</t>
+    <t xml:space="preserve">8.820143699646</t>
   </si>
   <si>
     <t xml:space="preserve">8.75432109832764</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81282901763916</t>
+    <t xml:space="preserve">8.81282997131348</t>
   </si>
   <si>
     <t xml:space="preserve">8.7396936416626</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51297378540039</t>
+    <t xml:space="preserve">8.51297473907471</t>
   </si>
   <si>
     <t xml:space="preserve">8.68849849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44715118408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40327072143555</t>
+    <t xml:space="preserve">8.44715213775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40326976776123</t>
   </si>
   <si>
     <t xml:space="preserve">8.27893924713135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35207462310791</t>
+    <t xml:space="preserve">8.35207557678223</t>
   </si>
   <si>
     <t xml:space="preserve">8.54222774505615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01760768890381</t>
+    <t xml:space="preserve">9.01760864257812</t>
   </si>
   <si>
     <t xml:space="preserve">9.02492237091064</t>
@@ -4259,7 +4259,7 @@
     <t xml:space="preserve">9.14925289154053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94447231292725</t>
+    <t xml:space="preserve">8.94447326660156</t>
   </si>
   <si>
     <t xml:space="preserve">8.89327716827393</t>
@@ -4268,10 +4268,10 @@
     <t xml:space="preserve">8.59342193603516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63730335235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34476089477539</t>
+    <t xml:space="preserve">8.63730430603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34476184844971</t>
   </si>
   <si>
     <t xml:space="preserve">8.35938930511475</t>
@@ -4280,7 +4280,7 @@
     <t xml:space="preserve">8.22043132781982</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13266944885254</t>
+    <t xml:space="preserve">8.13266849517822</t>
   </si>
   <si>
     <t xml:space="preserve">7.86938142776489</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">8.32282161712646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41789627075195</t>
+    <t xml:space="preserve">8.41789817810059</t>
   </si>
   <si>
     <t xml:space="preserve">8.33013534545898</t>
@@ -4298,16 +4298,16 @@
     <t xml:space="preserve">8.24237251281738</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14729690551758</t>
+    <t xml:space="preserve">8.14729595184326</t>
   </si>
   <si>
     <t xml:space="preserve">8.07415962219238</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16192245483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04490566253662</t>
+    <t xml:space="preserve">8.1619234085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04490661621094</t>
   </si>
   <si>
     <t xml:space="preserve">8.05221939086914</t>
@@ -4316,7 +4316,7 @@
     <t xml:space="preserve">8.28625392913818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26431274414062</t>
+    <t xml:space="preserve">8.26431369781494</t>
   </si>
   <si>
     <t xml:space="preserve">8.30088043212891</t>
@@ -4325,19 +4325,19 @@
     <t xml:space="preserve">8.38864326477051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48371982574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56416893005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71775341033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88596439361572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92253112792969</t>
+    <t xml:space="preserve">8.48371887207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56416797637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71775245666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88596534729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.922532081604</t>
   </si>
   <si>
     <t xml:space="preserve">9.56612491607666</t>
@@ -4346,7 +4346,7 @@
     <t xml:space="preserve">9.52955722808838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84403896331787</t>
+    <t xml:space="preserve">9.84403991699219</t>
   </si>
   <si>
     <t xml:space="preserve">10.0488185882568</t>
@@ -4355,7 +4355,7 @@
     <t xml:space="preserve">10.1804628372192</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1512088775635</t>
+    <t xml:space="preserve">10.1512098312378</t>
   </si>
   <si>
     <t xml:space="preserve">10.1146411895752</t>
@@ -4367,16 +4367,16 @@
     <t xml:space="preserve">10.3340473175049</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2789535522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.310435295105</t>
+    <t xml:space="preserve">10.2789545059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3104362487793</t>
   </si>
   <si>
     <t xml:space="preserve">10.3261775970459</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3576602935791</t>
+    <t xml:space="preserve">10.3576583862305</t>
   </si>
   <si>
     <t xml:space="preserve">10.3497886657715</t>
@@ -4388,7 +4388,7 @@
     <t xml:space="preserve">10.2553415298462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2710838317871</t>
+    <t xml:space="preserve">10.2710828781128</t>
   </si>
   <si>
     <t xml:space="preserve">10.2002477645874</t>
@@ -4412,25 +4412,25 @@
     <t xml:space="preserve">10.1608953475952</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1845073699951</t>
+    <t xml:space="preserve">10.1845064163208</t>
   </si>
   <si>
     <t xml:space="preserve">10.0034837722778</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0900602340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5229406356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3419179916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4521055221558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3812694549561</t>
+    <t xml:space="preserve">10.0900592803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5229415893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3419189453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4521064758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3812704086304</t>
   </si>
   <si>
     <t xml:space="preserve">10.4678478240967</t>
@@ -4439,19 +4439,19 @@
     <t xml:space="preserve">10.47571849823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5780334472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7433166503906</t>
+    <t xml:space="preserve">10.5780344009399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7433156967163</t>
   </si>
   <si>
     <t xml:space="preserve">11.003044128418</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0345287322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0423974990845</t>
+    <t xml:space="preserve">11.0345277786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0423984527588</t>
   </si>
   <si>
     <t xml:space="preserve">11.1998090744019</t>
@@ -4460,40 +4460,40 @@
     <t xml:space="preserve">11.2234210968018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2863855361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3650903701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3493509292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3414783477783</t>
+    <t xml:space="preserve">11.2863845825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3650913238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3493499755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.341480255127</t>
   </si>
   <si>
     <t xml:space="preserve">11.3099966049194</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1919393539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4123134613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3965721130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2155494689941</t>
+    <t xml:space="preserve">11.1919384002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.412314414978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3965730667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2155513763428</t>
   </si>
   <si>
     <t xml:space="preserve">11.4280557632446</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4752798080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8294553756714</t>
+    <t xml:space="preserve">11.4752788543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8294544219971</t>
   </si>
   <si>
     <t xml:space="preserve">12.0813121795654</t>
@@ -4505,22 +4505,22 @@
     <t xml:space="preserve">12.3725233078003</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3095598220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4040050506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5220642089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5141925811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7266969680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8368864059448</t>
+    <t xml:space="preserve">12.3095588684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4040060043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5220632553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5141916275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7266979217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8368854522705</t>
   </si>
   <si>
     <t xml:space="preserve">12.8132743835449</t>
@@ -4538,7 +4538,7 @@
     <t xml:space="preserve">12.7345695495605</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5063238143921</t>
+    <t xml:space="preserve">12.5063228607178</t>
   </si>
   <si>
     <t xml:space="preserve">12.2465944290161</t>
@@ -4550,7 +4550,7 @@
     <t xml:space="preserve">12.270206451416</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2308530807495</t>
+    <t xml:space="preserve">12.2308521270752</t>
   </si>
   <si>
     <t xml:space="preserve">12.3016872406006</t>
@@ -4562,34 +4562,34 @@
     <t xml:space="preserve">11.9160299301147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4516677856445</t>
+    <t xml:space="preserve">11.4516668319702</t>
   </si>
   <si>
     <t xml:space="preserve">11.6563014984131</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1132326126099</t>
+    <t xml:space="preserve">11.1132335662842</t>
   </si>
   <si>
     <t xml:space="preserve">11.1289739608765</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0974912643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0266580581665</t>
+    <t xml:space="preserve">11.0974922180176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0266561508179</t>
   </si>
   <si>
     <t xml:space="preserve">10.8062801361084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8456335067749</t>
+    <t xml:space="preserve">10.8456344604492</t>
   </si>
   <si>
     <t xml:space="preserve">10.7118339538574</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8613739013672</t>
+    <t xml:space="preserve">10.8613748550415</t>
   </si>
   <si>
     <t xml:space="preserve">10.9951753616333</t>
@@ -4598,19 +4598,19 @@
     <t xml:space="preserve">10.9873046875</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9085988998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0581388473511</t>
+    <t xml:space="preserve">10.908597946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0581398010254</t>
   </si>
   <si>
     <t xml:space="preserve">11.1761980056763</t>
   </si>
   <si>
-    <t xml:space="preserve">11.585467338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5225028991699</t>
+    <t xml:space="preserve">11.5854663848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5225019454956</t>
   </si>
   <si>
     <t xml:space="preserve">11.7743606567383</t>
@@ -4625,19 +4625,19 @@
     <t xml:space="preserve">11.9947357177734</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1285362243652</t>
+    <t xml:space="preserve">12.1285352706909</t>
   </si>
   <si>
     <t xml:space="preserve">11.9632539749146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9002885818481</t>
+    <t xml:space="preserve">11.9002895355225</t>
   </si>
   <si>
     <t xml:space="preserve">11.9789953231812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5697250366211</t>
+    <t xml:space="preserve">11.5697259902954</t>
   </si>
   <si>
     <t xml:space="preserve">11.6012077331543</t>
@@ -4649,73 +4649,73 @@
     <t xml:space="preserve">11.9317712783813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3257389068604</t>
+    <t xml:space="preserve">11.325737953186</t>
   </si>
   <si>
     <t xml:space="preserve">11.3572206497192</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3336086273193</t>
+    <t xml:space="preserve">11.333607673645</t>
   </si>
   <si>
     <t xml:space="preserve">11.912278175354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8475379943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6614074707031</t>
+    <t xml:space="preserve">11.8475370407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6614084243774</t>
   </si>
   <si>
     <t xml:space="preserve">11.6290369033813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.807074546814</t>
+    <t xml:space="preserve">11.8070755004883</t>
   </si>
   <si>
     <t xml:space="preserve">11.7666120529175</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4995565414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3296117782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5076494216919</t>
+    <t xml:space="preserve">11.4995574951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3296127319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5076484680176</t>
   </si>
   <si>
     <t xml:space="preserve">11.6371307373047</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5319261550903</t>
+    <t xml:space="preserve">11.5319271087646</t>
   </si>
   <si>
     <t xml:space="preserve">11.5966672897339</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5885744094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5400199890137</t>
+    <t xml:space="preserve">11.5885753631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5400190353394</t>
   </si>
   <si>
     <t xml:space="preserve">11.4429082870483</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3862590789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5157413482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4671859741211</t>
+    <t xml:space="preserve">11.3862609863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5157423019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4671869277954</t>
   </si>
   <si>
     <t xml:space="preserve">11.4186305999756</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3781681060791</t>
+    <t xml:space="preserve">11.3781671524048</t>
   </si>
   <si>
     <t xml:space="preserve">11.3700752258301</t>
@@ -4751,40 +4751,40 @@
     <t xml:space="preserve">11.8232593536377</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9446487426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.815167427063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9365549087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0903148651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1712408065796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2521657943726</t>
+    <t xml:space="preserve">11.9446477890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8151664733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9365568161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.090313911438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1712417602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2521667480469</t>
   </si>
   <si>
     <t xml:space="preserve">12.4221105575562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.381649017334</t>
+    <t xml:space="preserve">12.3816480636597</t>
   </si>
   <si>
     <t xml:space="preserve">12.3411846160889</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3249998092651</t>
+    <t xml:space="preserve">12.3249988555908</t>
   </si>
   <si>
     <t xml:space="preserve">12.3007221221924</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4140186309814</t>
+    <t xml:space="preserve">12.4140176773071</t>
   </si>
   <si>
     <t xml:space="preserve">12.6082401275635</t>
@@ -4793,70 +4793,70 @@
     <t xml:space="preserve">12.8914813995361</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9966840744019</t>
+    <t xml:space="preserve">12.9966831207275</t>
   </si>
   <si>
     <t xml:space="preserve">12.745813369751</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5354061126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6163330078125</t>
+    <t xml:space="preserve">12.5354070663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6163320541382</t>
   </si>
   <si>
     <t xml:space="preserve">13.1909055709839</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1261653900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.842924118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9562206268311</t>
+    <t xml:space="preserve">13.1261644363403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8429250717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9562225341797</t>
   </si>
   <si>
     <t xml:space="preserve">12.9804992675781</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0290546417236</t>
+    <t xml:space="preserve">13.0290555953979</t>
   </si>
   <si>
     <t xml:space="preserve">13.0937957763672</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1989984512329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9076662063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8510179519653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9885902404785</t>
+    <t xml:space="preserve">13.1989974975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9076652526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.851016998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9885911941528</t>
   </si>
   <si>
     <t xml:space="preserve">12.9238510131836</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0452394485474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0776090621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1747207641602</t>
+    <t xml:space="preserve">13.0452404022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0776100158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1747217178345</t>
   </si>
   <si>
     <t xml:space="preserve">13.1666288375854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9724063873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9319438934326</t>
+    <t xml:space="preserve">12.9724073410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.931941986084</t>
   </si>
   <si>
     <t xml:space="preserve">12.6810731887817</t>
@@ -4868,13 +4868,13 @@
     <t xml:space="preserve">12.4787588119507</t>
   </si>
   <si>
-    <t xml:space="preserve">12.75390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7296285629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.583963394165</t>
+    <t xml:space="preserve">12.7539072036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7296276092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5839624404907</t>
   </si>
   <si>
     <t xml:space="preserve">12.5758695602417</t>
@@ -4883,49 +4883,49 @@
     <t xml:space="preserve">12.6729803085327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7943696975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8752956390381</t>
+    <t xml:space="preserve">12.7943687438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8752946853638</t>
   </si>
   <si>
     <t xml:space="preserve">13.0209617614746</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0371475219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2475547790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9400358200073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1504440307617</t>
+    <t xml:space="preserve">13.0371465682983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2475538253784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.940034866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1504430770874</t>
   </si>
   <si>
     <t xml:space="preserve">13.3365716934204</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5874433517456</t>
+    <t xml:space="preserve">13.5874423980713</t>
   </si>
   <si>
     <t xml:space="preserve">13.4903316497803</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2880163192749</t>
+    <t xml:space="preserve">13.2880172729492</t>
   </si>
   <si>
     <t xml:space="preserve">13.3203859329224</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3042020797729</t>
+    <t xml:space="preserve">13.3042011260986</t>
   </si>
   <si>
     <t xml:space="preserve">13.0128688812256</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7862777709961</t>
+    <t xml:space="preserve">12.7862768173218</t>
   </si>
   <si>
     <t xml:space="preserve">12.2036113739014</t>
@@ -4937,52 +4937,52 @@
     <t xml:space="preserve">12.8995723724365</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0533304214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.215184211731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5388860702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.417498588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4579610824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5955333709717</t>
+    <t xml:space="preserve">13.0533313751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2151832580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5388870239258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4174976348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4579601287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.595534324646</t>
   </si>
   <si>
     <t xml:space="preserve">14.0163488388062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8221282958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9435157775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8140344619751</t>
+    <t xml:space="preserve">13.8221263885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9435167312622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8140335083008</t>
   </si>
   <si>
     <t xml:space="preserve">13.7573871612549</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9597015380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.881422996521</t>
+    <t xml:space="preserve">13.9597005844116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8814220428467</t>
   </si>
   <si>
     <t xml:space="preserve">13.5770053863525</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7248640060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.69007396698</t>
+    <t xml:space="preserve">13.7248649597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6900749206543</t>
   </si>
   <si>
     <t xml:space="preserve">13.750958442688</t>
@@ -4991,7 +4991,7 @@
     <t xml:space="preserve">13.4900283813477</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5248203277588</t>
+    <t xml:space="preserve">13.5248193740845</t>
   </si>
   <si>
     <t xml:space="preserve">13.6987714767456</t>
@@ -5000,10 +5000,10 @@
     <t xml:space="preserve">13.6552839279175</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8553304672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.672679901123</t>
+    <t xml:space="preserve">13.8553295135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6726789474487</t>
   </si>
   <si>
     <t xml:space="preserve">13.7857484817505</t>
@@ -5018,10 +5018,10 @@
     <t xml:space="preserve">14.1336545944214</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9683990478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8466329574585</t>
+    <t xml:space="preserve">13.9683980941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8466320037842</t>
   </si>
   <si>
     <t xml:space="preserve">13.7074699401855</t>
@@ -5033,16 +5033,16 @@
     <t xml:space="preserve">13.7335624694824</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7944450378418</t>
+    <t xml:space="preserve">13.7944459915161</t>
   </si>
   <si>
     <t xml:space="preserve">13.8118419647217</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9336080551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.342396736145</t>
+    <t xml:space="preserve">13.9336090087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3423976898193</t>
   </si>
   <si>
     <t xml:space="preserve">14.0379791259766</t>
@@ -5054,7 +5054,7 @@
     <t xml:space="preserve">13.5161218643188</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6204929351807</t>
+    <t xml:space="preserve">13.620493888855</t>
   </si>
   <si>
     <t xml:space="preserve">13.6291913986206</t>
@@ -5069,16 +5069,16 @@
     <t xml:space="preserve">13.9857940673828</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9249105453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8031435012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0466766357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0640716552734</t>
+    <t xml:space="preserve">13.9249114990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8031444549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0466775894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0640735626221</t>
   </si>
   <si>
     <t xml:space="preserve">14.2641172409058</t>
@@ -5099,28 +5099,28 @@
     <t xml:space="preserve">14.2815132141113</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3076076507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3858852386475</t>
+    <t xml:space="preserve">14.3076066970825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3858861923218</t>
   </si>
   <si>
     <t xml:space="preserve">14.6033267974854</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5598373413086</t>
+    <t xml:space="preserve">14.5598363876343</t>
   </si>
   <si>
     <t xml:space="preserve">14.7598829269409</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9686250686646</t>
+    <t xml:space="preserve">14.9686269760132</t>
   </si>
   <si>
     <t xml:space="preserve">14.8294630050659</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6989994049072</t>
+    <t xml:space="preserve">14.6990003585815</t>
   </si>
   <si>
     <t xml:space="preserve">14.6207208633423</t>
@@ -5138,25 +5138,25 @@
     <t xml:space="preserve">14.8990440368652</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8381605148315</t>
+    <t xml:space="preserve">14.8381624221802</t>
   </si>
   <si>
     <t xml:space="preserve">14.7511854171753</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7250938415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6729078292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0121154785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0816965103149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1164865493774</t>
+    <t xml:space="preserve">14.7250928878784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.672908782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0121145248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0816955566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1164855957031</t>
   </si>
   <si>
     <t xml:space="preserve">15.4469966888428</t>
@@ -5174,25 +5174,25 @@
     <t xml:space="preserve">15.7340183258057</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9862499237061</t>
+    <t xml:space="preserve">15.9862489700317</t>
   </si>
   <si>
     <t xml:space="preserve">16.1341094970703</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9253664016724</t>
+    <t xml:space="preserve">15.9253644943237</t>
   </si>
   <si>
     <t xml:space="preserve">16.0471343994141</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6124801635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2995910644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.916898727417</t>
+    <t xml:space="preserve">16.6124782562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2995929718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9168968200684</t>
   </si>
   <si>
     <t xml:space="preserve">16.9951763153076</t>
@@ -5204,10 +5204,10 @@
     <t xml:space="preserve">17.1952209472656</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4126605987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7083835601807</t>
+    <t xml:space="preserve">17.4126625061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.708381652832</t>
   </si>
   <si>
     <t xml:space="preserve">17.6561946868896</t>
@@ -5219,34 +5219,34 @@
     <t xml:space="preserve">18.038890838623</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8127517700195</t>
+    <t xml:space="preserve">17.8127536773682</t>
   </si>
   <si>
     <t xml:space="preserve">18.3172149658203</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2128448486328</t>
+    <t xml:space="preserve">18.2128429412842</t>
   </si>
   <si>
     <t xml:space="preserve">18.4041919708252</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3346099853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5433521270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6651191711426</t>
+    <t xml:space="preserve">18.3346118927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5433540344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6651210784912</t>
   </si>
   <si>
     <t xml:space="preserve">18.717306137085</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9519138336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0736808776855</t>
+    <t xml:space="preserve">17.9519157409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0736827850342</t>
   </si>
   <si>
     <t xml:space="preserve">17.7605667114258</t>
@@ -5258,7 +5258,7 @@
     <t xml:space="preserve">17.9139595031738</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8503036499023</t>
+    <t xml:space="preserve">17.850305557251</t>
   </si>
   <si>
     <t xml:space="preserve">17.5775032043457</t>
@@ -5267,13 +5267,13 @@
     <t xml:space="preserve">17.5229434967041</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7320899963379</t>
+    <t xml:space="preserve">17.7320919036865</t>
   </si>
   <si>
     <t xml:space="preserve">17.7502784729004</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6866264343262</t>
+    <t xml:space="preserve">17.6866245269775</t>
   </si>
   <si>
     <t xml:space="preserve">17.3956356048584</t>
@@ -5285,7 +5285,7 @@
     <t xml:space="preserve">18.3504409790039</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2231330871582</t>
+    <t xml:space="preserve">18.2231349945068</t>
   </si>
   <si>
     <t xml:space="preserve">17.9958000183105</t>
@@ -5294,7 +5294,7 @@
     <t xml:space="preserve">18.2413196563721</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2049465179443</t>
+    <t xml:space="preserve">18.204948425293</t>
   </si>
   <si>
     <t xml:space="preserve">17.6411571502686</t>
@@ -5306,7 +5306,7 @@
     <t xml:space="preserve">17.5684108734131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2137699127197</t>
+    <t xml:space="preserve">17.2137680053711</t>
   </si>
   <si>
     <t xml:space="preserve">17.5956897735596</t>
@@ -5324,7 +5324,7 @@
     <t xml:space="preserve">17.6229705810547</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5323085784912</t>
+    <t xml:space="preserve">18.5323066711426</t>
   </si>
   <si>
     <t xml:space="preserve">18.068546295166</t>
@@ -5333,16 +5333,16 @@
     <t xml:space="preserve">17.9503307342529</t>
   </si>
   <si>
-    <t xml:space="preserve">17.668436050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6232414245605</t>
+    <t xml:space="preserve">17.6684379577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6232433319092</t>
   </si>
   <si>
     <t xml:space="preserve">18.4050006866455</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6778030395508</t>
+    <t xml:space="preserve">18.6778049468994</t>
   </si>
   <si>
     <t xml:space="preserve">18.8232975006104</t>
@@ -5363,22 +5363,22 @@
     <t xml:space="preserve">18.9687919616699</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0779113769531</t>
+    <t xml:space="preserve">19.0779094696045</t>
   </si>
   <si>
     <t xml:space="preserve">19.0415382385254</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1688442230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4234619140625</t>
+    <t xml:space="preserve">19.1688461303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4234600067139</t>
   </si>
   <si>
     <t xml:space="preserve">19.187032699585</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4052715301514</t>
+    <t xml:space="preserve">19.4052734375</t>
   </si>
   <si>
     <t xml:space="preserve">19.3507137298584</t>
@@ -5387,7 +5387,7 @@
     <t xml:space="preserve">19.2415924072266</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3870849609375</t>
+    <t xml:space="preserve">19.3870868682861</t>
   </si>
   <si>
     <t xml:space="preserve">19.5689544677734</t>
@@ -5396,7 +5396,7 @@
     <t xml:space="preserve">19.6780738830566</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9145030975342</t>
+    <t xml:space="preserve">19.9145011901855</t>
   </si>
   <si>
     <t xml:space="preserve">19.7326354980469</t>
@@ -5408,7 +5408,7 @@
     <t xml:space="preserve">17.9321441650391</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9048652648926</t>
+    <t xml:space="preserve">17.9048671722412</t>
   </si>
   <si>
     <t xml:space="preserve">18.3686275482178</t>
@@ -5423,28 +5423,28 @@
     <t xml:space="preserve">18.9869766235352</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7869243621826</t>
+    <t xml:space="preserve">18.786922454834</t>
   </si>
   <si>
     <t xml:space="preserve">19.0597229003906</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0051651000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1506576538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3325252532959</t>
+    <t xml:space="preserve">19.005163192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1506595611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3325271606445</t>
   </si>
   <si>
     <t xml:space="preserve">19.314338684082</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2052211761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9142284393311</t>
+    <t xml:space="preserve">19.2052192687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9142303466797</t>
   </si>
   <si>
     <t xml:space="preserve">18.8414821624756</t>
@@ -5465,16 +5465,16 @@
     <t xml:space="preserve">19.4416465759277</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5507678985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9690628051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1327438354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.496208190918</t>
+    <t xml:space="preserve">19.5507659912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9690608978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1327419281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4962062835693</t>
   </si>
   <si>
     <t xml:space="preserve">19.7871952056885</t>
@@ -5489,10 +5489,10 @@
     <t xml:space="preserve">20.169116973877</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2782363891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3873596191406</t>
+    <t xml:space="preserve">20.2782382965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.387357711792</t>
   </si>
   <si>
     <t xml:space="preserve">20.5874118804932</t>
@@ -5504,22 +5504,22 @@
     <t xml:space="preserve">20.696533203125</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6237869262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0057067871094</t>
+    <t xml:space="preserve">20.6237850189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.005708694458</t>
   </si>
   <si>
     <t xml:space="preserve">20.8056526184082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6601600646973</t>
+    <t xml:space="preserve">20.6601581573486</t>
   </si>
   <si>
     <t xml:space="preserve">20.4055461883545</t>
   </si>
   <si>
-    <t xml:space="preserve">20.296422958374</t>
+    <t xml:space="preserve">20.2964248657227</t>
   </si>
   <si>
     <t xml:space="preserve">20.2600517272949</t>
@@ -6072,6 +6072,9 @@
   </si>
   <si>
     <t xml:space="preserve">25.7199993133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6599998474121</t>
   </si>
 </sst>
 </file>
@@ -71670,7 +71673,7 @@
     </row>
     <row r="2511">
       <c r="A2511" s="1" t="n">
-        <v>45974.6912037037</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B2511" t="n">
         <v>452338</v>
@@ -71691,6 +71694,32 @@
         <v>2019</v>
       </c>
       <c r="H2511" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" s="1" t="n">
+        <v>45975.6919097222</v>
+      </c>
+      <c r="B2512" t="n">
+        <v>441547</v>
+      </c>
+      <c r="C2512" t="n">
+        <v>25.7000007629395</v>
+      </c>
+      <c r="D2512" t="n">
+        <v>25.1599998474121</v>
+      </c>
+      <c r="E2512" t="n">
+        <v>25.6000003814697</v>
+      </c>
+      <c r="F2512" t="n">
+        <v>25.6599998474121</v>
+      </c>
+      <c r="G2512" t="s">
+        <v>2020</v>
+      </c>
+      <c r="H2512" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IF.MI.xlsx
+++ b/data/IF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2023" uniqueCount="2023">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="2024">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7370796203613</t>
+    <t xml:space="preserve">15.7370767593384</t>
   </si>
   <si>
     <t xml:space="preserve">IF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3903493881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3232412338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5458936691284</t>
+    <t xml:space="preserve">15.3903465270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3232364654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5458917617798</t>
   </si>
   <si>
     <t xml:space="preserve">14.3613414764404</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3781185150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4284496307373</t>
+    <t xml:space="preserve">14.3781175613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4284505844116</t>
   </si>
   <si>
     <t xml:space="preserve">14.1767921447754</t>
@@ -68,16 +68,16 @@
     <t xml:space="preserve">14.8646602630615</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8524293899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4955577850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6409645080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4340419769287</t>
+    <t xml:space="preserve">13.8524312973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4955625534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.640962600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4340467453003</t>
   </si>
   <si>
     <t xml:space="preserve">15.3735685348511</t>
@@ -89,70 +89,70 @@
     <t xml:space="preserve">15.9384069442749</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9440002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5637121200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1061782836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0502548217773</t>
+    <t xml:space="preserve">15.9439945220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5637149810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1061763763428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0502529144287</t>
   </si>
   <si>
     <t xml:space="preserve">15.7706327438354</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1722450256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9597311019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5403003692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0583076477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0974559783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7405815124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7685451507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8244695663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5347061157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4396352767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3501605987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2718648910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3333797454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4350891113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9765100479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7416286468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2057981491089</t>
+    <t xml:space="preserve">15.1722412109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9597301483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5402994155884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0583066940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0974531173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7405834197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7685461044312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8244705200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5347080230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4396362304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3501577377319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2718620300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3333759307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4350862503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.976508140564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7416257858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2058000564575</t>
   </si>
   <si>
     <t xml:space="preserve">15.0995416641235</t>
@@ -161,58 +161,58 @@
     <t xml:space="preserve">15.0436162948608</t>
   </si>
   <si>
-    <t xml:space="preserve">15.496603012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2840929031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9876928329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4452285766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5570783615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1656064987183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.484375</t>
+    <t xml:space="preserve">15.4966058731079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2840919494629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9876937866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4452266693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5570793151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1656074523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4843740463257</t>
   </si>
   <si>
     <t xml:space="preserve">14.7192544937134</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1834306716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3791618347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9999217987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2348022460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0949897766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9663667678833</t>
+    <t xml:space="preserve">15.1834259033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3791627883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.999924659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.234806060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.09499168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.966365814209</t>
   </si>
   <si>
     <t xml:space="preserve">16.1173648834229</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1403408050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4849739074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7204723358154</t>
+    <t xml:space="preserve">16.1403369903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4849720001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7204704284668</t>
   </si>
   <si>
     <t xml:space="preserve">16.4160442352295</t>
@@ -224,70 +224,70 @@
     <t xml:space="preserve">16.3815822601318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6004114151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6808280944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7842168807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8876075744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.634877204895</t>
+    <t xml:space="preserve">15.6004133224487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6808252334595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.784215927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8876056671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6348752975464</t>
   </si>
   <si>
     <t xml:space="preserve">15.278754234314</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4280977249146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.23854637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1409015655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3821449279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9570980072021</t>
+    <t xml:space="preserve">15.4280967712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2385473251343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1409006118774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3821439743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9570960998535</t>
   </si>
   <si>
     <t xml:space="preserve">14.8479633331299</t>
   </si>
   <si>
-    <t xml:space="preserve">14.58948802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6239519119263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.704363822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5550222396851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3482418060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1184883117676</t>
+    <t xml:space="preserve">14.5894889831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.623950958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7043647766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5550241470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3482427597046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1184892654419</t>
   </si>
   <si>
     <t xml:space="preserve">13.8427810668945</t>
   </si>
   <si>
-    <t xml:space="preserve">14.164439201355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6704635620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6417446136475</t>
+    <t xml:space="preserve">14.1644382476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.670464515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6417455673218</t>
   </si>
   <si>
     <t xml:space="preserve">13.3258304595947</t>
@@ -302,118 +302,118 @@
     <t xml:space="preserve">12.9811983108521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7629289627075</t>
+    <t xml:space="preserve">12.7629270553589</t>
   </si>
   <si>
     <t xml:space="preserve">12.4814777374268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6365652084351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6882591247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3493680953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5791254043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9352445602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5148153305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9576597213745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.785343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5613298416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6647233963013</t>
+    <t xml:space="preserve">12.6365642547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6882600784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3493700027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5791244506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.935248374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5148162841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9576578140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7853422164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5613307952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.664722442627</t>
   </si>
   <si>
     <t xml:space="preserve">13.3488073348999</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2683925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3602952957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1535148620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9639663696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.780161857605</t>
+    <t xml:space="preserve">13.2683916091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.360294342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1535139083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9639654159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7801628112793</t>
   </si>
   <si>
     <t xml:space="preserve">12.5504064559937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2057704925537</t>
+    <t xml:space="preserve">12.2057733535767</t>
   </si>
   <si>
     <t xml:space="preserve">12.0564308166504</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9185762405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6084060668945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2287473678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6537952423096</t>
+    <t xml:space="preserve">11.9185781478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6084079742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2287454605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6537961959839</t>
   </si>
   <si>
     <t xml:space="preserve">12.5963563919067</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9869403839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1196146011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1781759262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2643375396729</t>
+    <t xml:space="preserve">12.9869413375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1196126937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1781778335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2643356323242</t>
   </si>
   <si>
     <t xml:space="preserve">10.3217744827271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4251642227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4366521835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4538850784302</t>
+    <t xml:space="preserve">10.4251651763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4366550445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4538860321045</t>
   </si>
   <si>
     <t xml:space="preserve">9.93693447113037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58081436157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5693244934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7301549911499</t>
+    <t xml:space="preserve">9.58081245422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56932544708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73015403747559</t>
   </si>
   <si>
     <t xml:space="preserve">9.76461791992188</t>
@@ -425,10 +425,10 @@
     <t xml:space="preserve">11.2810049057007</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4877862930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3269567489624</t>
+    <t xml:space="preserve">11.4877843856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3269557952881</t>
   </si>
   <si>
     <t xml:space="preserve">11.516505241394</t>
@@ -437,58 +437,58 @@
     <t xml:space="preserve">11.2580289840698</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4992733001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2293090820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.045506477356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8617000579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6032257080078</t>
+    <t xml:space="preserve">11.4992742538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2293100357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0455055236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8617010116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6032238006592</t>
   </si>
   <si>
     <t xml:space="preserve">10.9995536804199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7175407409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4188585281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5796880722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1144313812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1431522369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6026649475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.740517616272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4016275405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6543579101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5567111968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4533233642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3843955993652</t>
+    <t xml:space="preserve">11.7175416946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4188594818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5796890258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1144332885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1431531906128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6026639938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7405157089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4016284942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6543607711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.556713104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4533224105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3843946456909</t>
   </si>
   <si>
     <t xml:space="preserve">11.2867488861084</t>
@@ -497,19 +497,19 @@
     <t xml:space="preserve">10.9880666732788</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9765787124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0397605895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0282735824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0972003936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9708366394043</t>
+    <t xml:space="preserve">10.9765796661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0397615432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0282745361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0972013473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9708337783813</t>
   </si>
   <si>
     <t xml:space="preserve">10.9650917053223</t>
@@ -518,31 +518,31 @@
     <t xml:space="preserve">11.1201763153076</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2063360214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1891031265259</t>
+    <t xml:space="preserve">11.2063331604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1891021728516</t>
   </si>
   <si>
     <t xml:space="preserve">11.4303464889526</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8324203491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3149080276489</t>
+    <t xml:space="preserve">11.8324213027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3149061203003</t>
   </si>
   <si>
     <t xml:space="preserve">12.3953218460083</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9587850570679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6945676803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7749795913696</t>
+    <t xml:space="preserve">11.9587831497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6945638656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7749805450439</t>
   </si>
   <si>
     <t xml:space="preserve">11.6715898513794</t>
@@ -554,40 +554,40 @@
     <t xml:space="preserve">11.5739431381226</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7692337036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0621757507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0219688415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.660101890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.510760307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4935293197632</t>
+    <t xml:space="preserve">11.7692346572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0621747970581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0219678878784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6601009368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.510763168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4935302734375</t>
   </si>
   <si>
     <t xml:space="preserve">11.5279941558838</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7060518264771</t>
+    <t xml:space="preserve">11.7060527801514</t>
   </si>
   <si>
     <t xml:space="preserve">11.7577486038208</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0277109146118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4068078994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4349660873413</t>
+    <t xml:space="preserve">12.0277118682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4068088531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.434965133667</t>
   </si>
   <si>
     <t xml:space="preserve">13.6991844177246</t>
@@ -599,58 +599,58 @@
     <t xml:space="preserve">13.8657560348511</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9519157409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1759281158447</t>
+    <t xml:space="preserve">13.9519166946411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1759262084961</t>
   </si>
   <si>
     <t xml:space="preserve">14.3712186813354</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4631204605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8824253082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9628381729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1064376831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2270584106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1351594924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9456100463867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7158527374268</t>
+    <t xml:space="preserve">14.4631214141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8824243545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9628400802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1064386367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2270603179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1351537704468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9456090927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7158517837524</t>
   </si>
   <si>
     <t xml:space="preserve">14.7330837249756</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5090703964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.595232963562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5435380935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3827085494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0725364685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0610504150391</t>
+    <t xml:space="preserve">14.5090713500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5952301025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5435371398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3827104568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0725355148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0610485076904</t>
   </si>
   <si>
     <t xml:space="preserve">13.6474885940552</t>
@@ -659,151 +659,151 @@
     <t xml:space="preserve">13.6876974105835</t>
   </si>
   <si>
-    <t xml:space="preserve">13.590048789978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5383539199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0501260757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1190509796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1822357177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7514419555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2109518051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4407062530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4234781265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2856225967407</t>
+    <t xml:space="preserve">13.5900497436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5383548736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0501251220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1190500259399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1822366714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7514429092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2109546661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4407091140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4234771728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.285626411438</t>
   </si>
   <si>
     <t xml:space="preserve">14.1414642333984</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2735738754272</t>
+    <t xml:space="preserve">14.2735729217529</t>
   </si>
   <si>
     <t xml:space="preserve">14.1931591033936</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3597326278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9398651123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6871318817139</t>
+    <t xml:space="preserve">14.3597316741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.939866065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6871328353882</t>
   </si>
   <si>
     <t xml:space="preserve">14.3884515762329</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4746122360229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7847785949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9341192245483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2213153839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5831813812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4970207214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4510698318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3361930847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8364744186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9915599822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2959861755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.163875579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0375118255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0892057418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0719757080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8307313919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6469249725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5320482254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2333631515503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5263051986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4171695709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3941946029663</t>
+    <t xml:space="preserve">14.4746103286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7847805023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9341201782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2213163375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.583179473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4970235824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4510707855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3361911773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8364753723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9915590286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2959852218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1638784408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0375099182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.089204788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0719738006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8307294845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6469268798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5320463180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2333660125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5263071060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4171724319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.394193649292</t>
   </si>
   <si>
     <t xml:space="preserve">15.0490007400513</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7618055343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6584129333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8766841888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3936290740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.853141784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8416576385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0369491577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5079460144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9559726715088</t>
+    <t xml:space="preserve">14.7618026733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6584138870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8766822814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3936328887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8531427383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8416557312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0369472503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5079479217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9559669494629</t>
   </si>
   <si>
     <t xml:space="preserve">17.0880813598633</t>
@@ -812,10 +812,10 @@
     <t xml:space="preserve">16.634313583374</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6113357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0828990936279</t>
+    <t xml:space="preserve">16.6113376617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0828971862793</t>
   </si>
   <si>
     <t xml:space="preserve">16.8870449066162</t>
@@ -824,19 +824,19 @@
     <t xml:space="preserve">16.9444828033447</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3465538024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.484411239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5935440063477</t>
+    <t xml:space="preserve">17.3465557098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4844074249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5935401916504</t>
   </si>
   <si>
     <t xml:space="preserve">17.0593605041504</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1684951782227</t>
+    <t xml:space="preserve">17.1684970855713</t>
   </si>
   <si>
     <t xml:space="preserve">17.6911888122559</t>
@@ -845,94 +845,94 @@
     <t xml:space="preserve">17.9152011871338</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7365760803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.552209854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8164310455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9944953918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9422340393066</t>
+    <t xml:space="preserve">18.7365798950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5522136688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8164291381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9944896697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.942232131958</t>
   </si>
   <si>
     <t xml:space="preserve">20.522928237915</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8503284454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7354488372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6780166625977</t>
+    <t xml:space="preserve">20.8503303527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7354507446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.678014755249</t>
   </si>
   <si>
     <t xml:space="preserve">20.6492958068848</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3218955993652</t>
+    <t xml:space="preserve">20.321891784668</t>
   </si>
   <si>
     <t xml:space="preserve">20.5631332397461</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6378040313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8388404846191</t>
+    <t xml:space="preserve">20.6378078460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8388423919678</t>
   </si>
   <si>
     <t xml:space="preserve">20.8216114044189</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6090869903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1088047027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4132328033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2409152984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.177734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0226459503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9594631195068</t>
+    <t xml:space="preserve">20.6090908050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1088066101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4132308959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2409172058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1777324676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.022647857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9594669342041</t>
   </si>
   <si>
     <t xml:space="preserve">21.3098411560059</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5855503082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3155879974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2690734863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.136962890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.981876373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2288627624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7458152770996</t>
+    <t xml:space="preserve">21.5855522155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3155860900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2690715789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1369609832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9818820953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2288665771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7458114624023</t>
   </si>
   <si>
     <t xml:space="preserve">22.9335060119629</t>
@@ -941,31 +941,31 @@
     <t xml:space="preserve">22.5815849304199</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3938941955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4671669006348</t>
+    <t xml:space="preserve">22.393892288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4671649932861</t>
   </si>
   <si>
     <t xml:space="preserve">20.4583282470703</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1035175323486</t>
+    <t xml:space="preserve">21.103515625</t>
   </si>
   <si>
     <t xml:space="preserve">20.8161163330078</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6342887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6929416656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5873680114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2969951629639</t>
+    <t xml:space="preserve">20.6342906951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.692943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.587366104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.296989440918</t>
   </si>
   <si>
     <t xml:space="preserve">18.5872840881348</t>
@@ -974,16 +974,16 @@
     <t xml:space="preserve">19.5433368682861</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9656391143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4817886352539</t>
+    <t xml:space="preserve">19.9656410217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4817905426025</t>
   </si>
   <si>
     <t xml:space="preserve">20.4700603485107</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5287132263184</t>
+    <t xml:space="preserve">20.528715133667</t>
   </si>
   <si>
     <t xml:space="preserve">20.4114074707031</t>
@@ -995,13 +995,13 @@
     <t xml:space="preserve">20.3058300018311</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7955474853516</t>
+    <t xml:space="preserve">19.7955455780029</t>
   </si>
   <si>
     <t xml:space="preserve">19.6078567504883</t>
   </si>
   <si>
-    <t xml:space="preserve">19.88352394104</t>
+    <t xml:space="preserve">19.8835258483887</t>
   </si>
   <si>
     <t xml:space="preserve">20.2471771240234</t>
@@ -1016,13 +1016,13 @@
     <t xml:space="preserve">20.7515983581543</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6988124847412</t>
+    <t xml:space="preserve">20.6988067626953</t>
   </si>
   <si>
     <t xml:space="preserve">20.3527526855469</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5521755218506</t>
+    <t xml:space="preserve">20.5521793365479</t>
   </si>
   <si>
     <t xml:space="preserve">20.5052528381348</t>
@@ -1031,25 +1031,25 @@
     <t xml:space="preserve">20.7046756744385</t>
   </si>
   <si>
-    <t xml:space="preserve">20.440731048584</t>
+    <t xml:space="preserve">20.4407329559326</t>
   </si>
   <si>
     <t xml:space="preserve">20.1474666595459</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0477523803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0008335113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4876575469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6694850921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6460227966309</t>
+    <t xml:space="preserve">20.0477561950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0008316040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4876556396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6694831848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6460208892822</t>
   </si>
   <si>
     <t xml:space="preserve">20.863037109375</t>
@@ -1058,13 +1058,13 @@
     <t xml:space="preserve">20.933422088623</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0096702575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9275569915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1152515411377</t>
+    <t xml:space="preserve">21.0096740722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9275588989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1152496337891</t>
   </si>
   <si>
     <t xml:space="preserve">21.2560195922852</t>
@@ -1076,22 +1076,22 @@
     <t xml:space="preserve">21.5551490783691</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7487087249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6314010620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6079368591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6431312561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8366870880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0830326080322</t>
+    <t xml:space="preserve">21.748706817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6313991546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6079387664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6431293487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8366851806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0830307006836</t>
   </si>
   <si>
     <t xml:space="preserve">21.7604370117188</t>
@@ -1100,67 +1100,67 @@
     <t xml:space="preserve">22.4642772674561</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9041786193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6402397155762</t>
+    <t xml:space="preserve">22.9041805267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6402359008789</t>
   </si>
   <si>
     <t xml:space="preserve">22.9686985015869</t>
   </si>
   <si>
-    <t xml:space="preserve">22.75754737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2854270935059</t>
+    <t xml:space="preserve">22.7575454711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2854290008545</t>
   </si>
   <si>
     <t xml:space="preserve">23.4907131195068</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7722473144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0068664550781</t>
+    <t xml:space="preserve">23.7722492218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0068626403809</t>
   </si>
   <si>
     <t xml:space="preserve">24.2708072662354</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8719635009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1007099151611</t>
+    <t xml:space="preserve">23.8719654083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1007080078125</t>
   </si>
   <si>
     <t xml:space="preserve">24.0479202270508</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5435047149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5669631958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1593608856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3529205322266</t>
+    <t xml:space="preserve">23.5435009002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5669651031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1593647003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3529224395752</t>
   </si>
   <si>
     <t xml:space="preserve">24.3059978485107</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8543663024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0361881256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8367691040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8191757202148</t>
+    <t xml:space="preserve">23.8543643951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0361919403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8367710113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8191719055176</t>
   </si>
   <si>
     <t xml:space="preserve">23.9716701507568</t>
@@ -1169,145 +1169,145 @@
     <t xml:space="preserve">23.7898483276367</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6373462677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1153316497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7077293395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9012851715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1652317047119</t>
+    <t xml:space="preserve">23.6373443603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1153335571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7077312469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9012889862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1652336120605</t>
   </si>
   <si>
     <t xml:space="preserve">24.5347442626953</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3411865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0831146240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7400341033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7107067108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4936866760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.698974609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0684909820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7078170776367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7136783599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1594429016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4937686920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3823318481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5876178741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1301174163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5993461608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.822229385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1330909729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7548179626465</t>
+    <t xml:space="preserve">24.3411884307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0831165313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7400360107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7107105255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4936828613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6989765167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0684928894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7078151702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.713680267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.15944480896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4937725067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3823280334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5876159667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1301193237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5993480682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8222274780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1330966949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7548198699951</t>
   </si>
   <si>
     <t xml:space="preserve">28.0656852722168</t>
   </si>
   <si>
-    <t xml:space="preserve">28.2064514160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8984832763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7489547729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.4997158050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8281764984131</t>
+    <t xml:space="preserve">28.2064571380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8984794616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7489604949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.4997215270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.828182220459</t>
   </si>
   <si>
     <t xml:space="preserve">28.8926982879639</t>
   </si>
   <si>
-    <t xml:space="preserve">28.658088684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.0539512634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9278087615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5289611816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2152099609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6404037475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5378036499023</t>
+    <t xml:space="preserve">28.6580867767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0539569854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9278030395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5289669036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2152080535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.64040184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5378074645996</t>
   </si>
   <si>
     <t xml:space="preserve">27.631649017334</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6668395996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8428020477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.3237590789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5671310424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.6023216247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4556884765625</t>
+    <t xml:space="preserve">27.6668376922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8427982330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.3237609863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5671329498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.6023197174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4556865692139</t>
   </si>
   <si>
     <t xml:space="preserve">27.5026092529297</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0803070068359</t>
+    <t xml:space="preserve">27.0803050994873</t>
   </si>
   <si>
     <t xml:space="preserve">26.8163661956787</t>
@@ -1316,43 +1316,43 @@
     <t xml:space="preserve">26.306079864502</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9365653991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5992622375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8954200744629</t>
+    <t xml:space="preserve">25.936559677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5992660522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8954238891602</t>
   </si>
   <si>
     <t xml:space="preserve">22.9511032104492</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8279266357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6021556854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7164859771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7282161712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3176441192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9833164215088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6754302978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4056262969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.610912322998</t>
+    <t xml:space="preserve">22.8279304504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6021575927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7164878845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7282180786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3176460266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9833202362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6754283905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4056243896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6109104156494</t>
   </si>
   <si>
     <t xml:space="preserve">22.7927379608154</t>
@@ -1361,13 +1361,13 @@
     <t xml:space="preserve">22.2355270385742</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5492820739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5199584960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7311096191406</t>
+    <t xml:space="preserve">21.5492839813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5199565887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.731107711792</t>
   </si>
   <si>
     <t xml:space="preserve">21.8249549865723</t>
@@ -1376,43 +1376,43 @@
     <t xml:space="preserve">21.4495735168457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9040946960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4026489257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.877742767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4701442718506</t>
+    <t xml:space="preserve">20.9040985107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4026508331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8777446746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.470142364502</t>
   </si>
   <si>
     <t xml:space="preserve">21.1914978027344</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1093845367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0565967559814</t>
+    <t xml:space="preserve">21.1093864440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0565986633301</t>
   </si>
   <si>
     <t xml:space="preserve">21.7135143280029</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7047557830811</t>
+    <t xml:space="preserve">22.7047576904297</t>
   </si>
   <si>
     <t xml:space="preserve">23.9130191802979</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0449504852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3440799713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7546558380127</t>
+    <t xml:space="preserve">23.0449485778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3440818786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7546539306641</t>
   </si>
   <si>
     <t xml:space="preserve">23.7663841247559</t>
@@ -1421,28 +1421,28 @@
     <t xml:space="preserve">23.4496574401855</t>
   </si>
   <si>
-    <t xml:space="preserve">23.520040512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3469696044922</t>
+    <t xml:space="preserve">23.5200386047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3469715118408</t>
   </si>
   <si>
     <t xml:space="preserve">23.0273513793945</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1563911437988</t>
+    <t xml:space="preserve">23.1563835144043</t>
   </si>
   <si>
     <t xml:space="preserve">22.8631229400635</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0508136749268</t>
+    <t xml:space="preserve">23.0508117675781</t>
   </si>
   <si>
     <t xml:space="preserve">22.9569664001465</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7810096740723</t>
+    <t xml:space="preserve">22.781005859375</t>
   </si>
   <si>
     <t xml:space="preserve">22.5229320526123</t>
@@ -1454,55 +1454,55 @@
     <t xml:space="preserve">22.2765884399414</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9452342987061</t>
+    <t xml:space="preserve">22.9452362060547</t>
   </si>
   <si>
     <t xml:space="preserve">22.4525470733643</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0771656036377</t>
+    <t xml:space="preserve">22.0771675109863</t>
   </si>
   <si>
     <t xml:space="preserve">21.2208251953125</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7398662567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2677459716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6489105224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4260272979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7750549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1621704101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9158248901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3733234405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.36159324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3264007568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2794761657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.396785736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.044864654541</t>
+    <t xml:space="preserve">20.7398681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2677478790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6489143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4260292053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7750587463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1621723175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.915828704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3733215332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3615913391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3263988494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2794799804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3967838287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0448665618896</t>
   </si>
   <si>
     <t xml:space="preserve">20.7985210418701</t>
@@ -1514,82 +1514,82 @@
     <t xml:space="preserve">20.0125637054443</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3321838378906</t>
+    <t xml:space="preserve">19.332181930542</t>
   </si>
   <si>
     <t xml:space="preserve">19.015453338623</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3556461334229</t>
+    <t xml:space="preserve">19.3556442260742</t>
   </si>
   <si>
     <t xml:space="preserve">19.0975704193115</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0858383178711</t>
+    <t xml:space="preserve">19.0858364105225</t>
   </si>
   <si>
     <t xml:space="preserve">20.0712184906006</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9891033172607</t>
+    <t xml:space="preserve">19.9891014099121</t>
   </si>
   <si>
     <t xml:space="preserve">18.8394927978516</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3468036651611</t>
+    <t xml:space="preserve">18.3468055725098</t>
   </si>
   <si>
     <t xml:space="preserve">18.5227642059326</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4377593994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2618007659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9919948577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3233413696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3614292144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6987247467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9596920013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7221870422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1210289001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2735271453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4142971038818</t>
+    <t xml:space="preserve">19.4377613067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2617969512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9919929504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3233432769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3614273071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6987266540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9596939086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7221832275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1210308074951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.273530960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4142951965332</t>
   </si>
   <si>
     <t xml:space="preserve">20.1533317565918</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7310256958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5785274505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.813138961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6958351135254</t>
+    <t xml:space="preserve">19.7310237884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5785293579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8131408691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.695837020874</t>
   </si>
   <si>
     <t xml:space="preserve">19.3461227416992</t>
@@ -1598,124 +1598,124 @@
     <t xml:space="preserve">19.3582210540771</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1404399871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0920448303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1646404266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7816848754883</t>
+    <t xml:space="preserve">19.1404418945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0920429229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1646385192871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7816829681396</t>
   </si>
   <si>
     <t xml:space="preserve">19.9752655029297</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2656364440918</t>
+    <t xml:space="preserve">20.2656402587891</t>
   </si>
   <si>
     <t xml:space="preserve">20.435022354126</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6649036407471</t>
+    <t xml:space="preserve">20.6648998260498</t>
   </si>
   <si>
     <t xml:space="preserve">20.3745269775391</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0236568450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5397052764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4429111480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6485919952393</t>
+    <t xml:space="preserve">20.0236587524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5397033691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4429130554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6485958099365</t>
   </si>
   <si>
     <t xml:space="preserve">19.7211875915527</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9589595794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3298149108887</t>
+    <t xml:space="preserve">18.9589576721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3298168182373</t>
   </si>
   <si>
     <t xml:space="preserve">17.4102993011475</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0836315155029</t>
+    <t xml:space="preserve">17.0836296081543</t>
   </si>
   <si>
     <t xml:space="preserve">17.228816986084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.877950668335</t>
+    <t xml:space="preserve">16.8779487609863</t>
   </si>
   <si>
     <t xml:space="preserve">16.5149822235107</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6075639724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.167799949646</t>
+    <t xml:space="preserve">15.6075687408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1677980422974</t>
   </si>
   <si>
     <t xml:space="preserve">12.8853149414062</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1194019317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2282934188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4260835647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4865779876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0147199630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1478090286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8332357406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7001495361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2929944992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1520195007324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5996742248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5754776000977</t>
+    <t xml:space="preserve">14.119402885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2282943725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.426082611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4865741729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.014720916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1478080749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8332386016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7001476287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2929954528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1520156860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5996761322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.575475692749</t>
   </si>
   <si>
     <t xml:space="preserve">16.0794219970703</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7932548522949</t>
+    <t xml:space="preserve">16.7932567596436</t>
   </si>
   <si>
     <t xml:space="preserve">17.2409172058105</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7327632904053</t>
+    <t xml:space="preserve">16.7327613830566</t>
   </si>
   <si>
     <t xml:space="preserve">16.9021472930908</t>
@@ -1724,67 +1724,67 @@
     <t xml:space="preserve">16.6238708496094</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9705305099487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4623785018921</t>
+    <t xml:space="preserve">15.970531463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4623775482178</t>
   </si>
   <si>
     <t xml:space="preserve">15.5712699890137</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5954656600952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6438646316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6196641921997</t>
+    <t xml:space="preserve">15.5954685211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6438608169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6196622848511</t>
   </si>
   <si>
     <t xml:space="preserve">15.7890501022339</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0431251525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4060935974121</t>
+    <t xml:space="preserve">16.0431270599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4060955047607</t>
   </si>
   <si>
     <t xml:space="preserve">16.5875759124756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2730026245117</t>
+    <t xml:space="preserve">16.2730045318604</t>
   </si>
   <si>
     <t xml:space="preserve">15.9100399017334</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9947309494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8253450393677</t>
+    <t xml:space="preserve">15.9947299957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.825345993042</t>
   </si>
   <si>
     <t xml:space="preserve">16.6722679138184</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9384422302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2851047515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0552234649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2972049713135</t>
+    <t xml:space="preserve">16.9384441375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2851028442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0552253723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2972011566162</t>
   </si>
   <si>
     <t xml:space="preserve">16.3576984405518</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2125091552734</t>
+    <t xml:space="preserve">16.2125110626221</t>
   </si>
   <si>
     <t xml:space="preserve">15.3655881881714</t>
@@ -1793,13 +1793,13 @@
     <t xml:space="preserve">15.5470714569092</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6396551132202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3692712783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6838436126709</t>
+    <t xml:space="preserve">14.6396560668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3692722320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6838426589966</t>
   </si>
   <si>
     <t xml:space="preserve">13.6475467681885</t>
@@ -1808,28 +1808,28 @@
     <t xml:space="preserve">13.6354484558105</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2845802307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0426015853882</t>
+    <t xml:space="preserve">13.2845792770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0426025390625</t>
   </si>
   <si>
     <t xml:space="preserve">12.5102500915527</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3771619796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4860515594482</t>
+    <t xml:space="preserve">12.377161026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4860525131226</t>
   </si>
   <si>
     <t xml:space="preserve">12.4497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2603807449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7885236740112</t>
+    <t xml:space="preserve">13.2603816986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7885246276855</t>
   </si>
   <si>
     <t xml:space="preserve">12.9700078964233</t>
@@ -1838,7 +1838,7 @@
     <t xml:space="preserve">12.921612739563</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0909976959229</t>
+    <t xml:space="preserve">13.0909957885742</t>
   </si>
   <si>
     <t xml:space="preserve">12.3408651351929</t>
@@ -1850,67 +1850,67 @@
     <t xml:space="preserve">12.2561740875244</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7643260955811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1998863220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6596450805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5265598297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3571729660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8895244598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5749530792236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6717433929443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.320876121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3450736999512</t>
+    <t xml:space="preserve">12.7643270492554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1998882293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6596431732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.526556968689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3571720123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8895225524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5749540328979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6717443466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3208770751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3450746536255</t>
   </si>
   <si>
     <t xml:space="preserve">13.5023584365845</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0589094161987</t>
+    <t xml:space="preserve">14.0589065551758</t>
   </si>
   <si>
     <t xml:space="preserve">14.421875</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3976774215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2645874023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4339752197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3934707641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7359209060669</t>
+    <t xml:space="preserve">14.3976764678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2645902633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4339723587036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3934679031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7359218597412</t>
   </si>
   <si>
     <t xml:space="preserve">10.864800453186</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3003625869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6088819503784</t>
+    <t xml:space="preserve">11.3003616333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6088829040527</t>
   </si>
   <si>
     <t xml:space="preserve">11.9778985977173</t>
@@ -1922,10 +1922,10 @@
     <t xml:space="preserve">10.3143014907837</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5865268707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2356595993042</t>
+    <t xml:space="preserve">10.5865278244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2356605529785</t>
   </si>
   <si>
     <t xml:space="preserve">9.86664390563965</t>
@@ -1943,31 +1943,31 @@
     <t xml:space="preserve">9.92108726501465</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89689159393311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53392314910889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73539733886719</t>
+    <t xml:space="preserve">9.89689064025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5339241027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7353982925415</t>
   </si>
   <si>
     <t xml:space="preserve">8.37848091125488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22119426727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4692211151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49946975708008</t>
+    <t xml:space="preserve">8.22119522094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46922206878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49946880340576</t>
   </si>
   <si>
     <t xml:space="preserve">8.9713249206543</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06206607818604</t>
+    <t xml:space="preserve">9.06206798553467</t>
   </si>
   <si>
     <t xml:space="preserve">9.40083599090576</t>
@@ -1985,58 +1985,58 @@
     <t xml:space="preserve">9.12256145477295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21935367584229</t>
+    <t xml:space="preserve">9.21935272216797</t>
   </si>
   <si>
     <t xml:space="preserve">8.82008934020996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12861156463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24960041046143</t>
+    <t xml:space="preserve">9.12861061096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24959945678711</t>
   </si>
   <si>
     <t xml:space="preserve">9.36453914642334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58836841583252</t>
+    <t xml:space="preserve">9.58836936950684</t>
   </si>
   <si>
     <t xml:space="preserve">9.48552894592285</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45528030395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7093563079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61256694793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57021999359131</t>
+    <t xml:space="preserve">9.45528125762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70935726165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6125659942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57022094726562</t>
   </si>
   <si>
     <t xml:space="preserve">10.8406038284302</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1370248794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9071474075317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5967864990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3064117431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0099897384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.96764087677</t>
+    <t xml:space="preserve">11.1370267868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9071483612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5967855453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3064098358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.00998878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9676427841187</t>
   </si>
   <si>
     <t xml:space="preserve">10.5139331817627</t>
@@ -2048,28 +2048,28 @@
     <t xml:space="preserve">10.3385000228882</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7377624511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2840547561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6409730911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1007318496704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0039396286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8587512969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3747959136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81219863891602</t>
+    <t xml:space="preserve">10.7377614974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2840557098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6409721374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1007308959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0039377212524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.85875415802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3747968673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8121976852417</t>
   </si>
   <si>
     <t xml:space="preserve">9.69121074676514</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">9.37059020996094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1709566116333</t>
+    <t xml:space="preserve">9.17095756530762</t>
   </si>
   <si>
     <t xml:space="preserve">9.03786945343018</t>
@@ -2099,25 +2099,25 @@
     <t xml:space="preserve">10.8043079376221</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5562801361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.62282371521</t>
+    <t xml:space="preserve">10.5562810897827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6228227615356</t>
   </si>
   <si>
     <t xml:space="preserve">10.5804777145386</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5502300262451</t>
+    <t xml:space="preserve">10.5502309799194</t>
   </si>
   <si>
     <t xml:space="preserve">10.0239286422729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62466621398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1025714874268</t>
+    <t xml:space="preserve">9.62466526031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1025724411011</t>
   </si>
   <si>
     <t xml:space="preserve">10.2296104431152</t>
@@ -2132,16 +2132,16 @@
     <t xml:space="preserve">9.98763275146484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.969482421875</t>
+    <t xml:space="preserve">9.96948432922363</t>
   </si>
   <si>
     <t xml:space="preserve">10.2780055999756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4352903366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5320825576782</t>
+    <t xml:space="preserve">10.4352912902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5320835113525</t>
   </si>
   <si>
     <t xml:space="preserve">10.1509675979614</t>
@@ -2150,13 +2150,13 @@
     <t xml:space="preserve">10.0299777984619</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1267690658569</t>
+    <t xml:space="preserve">10.1267700195312</t>
   </si>
   <si>
     <t xml:space="preserve">10.3445491790771</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0662755966187</t>
+    <t xml:space="preserve">10.0662746429443</t>
   </si>
   <si>
     <t xml:space="preserve">9.64886283874512</t>
@@ -2165,34 +2165,34 @@
     <t xml:space="preserve">11.0946817398071</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6433382034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0323438644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3729543685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8769006729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7014665603638</t>
+    <t xml:space="preserve">12.6433372497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0323448181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3729553222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.876898765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7014675140381</t>
   </si>
   <si>
     <t xml:space="preserve">10.610725402832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.568377494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1086206436157</t>
+    <t xml:space="preserve">10.5683784484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.10862159729</t>
   </si>
   <si>
     <t xml:space="preserve">10.3506002426147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9373960494995</t>
+    <t xml:space="preserve">10.9373950958252</t>
   </si>
   <si>
     <t xml:space="preserve">11.0341863632202</t>
@@ -2201,19 +2201,19 @@
     <t xml:space="preserve">11.1128282546997</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4818449020386</t>
+    <t xml:space="preserve">11.4818439483643</t>
   </si>
   <si>
     <t xml:space="preserve">10.9736909866333</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54602241516113</t>
+    <t xml:space="preserve">9.54602146148682</t>
   </si>
   <si>
     <t xml:space="preserve">9.35848999023438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22540378570557</t>
+    <t xml:space="preserve">9.22540187835693</t>
   </si>
   <si>
     <t xml:space="preserve">9.11046314239502</t>
@@ -2222,13 +2222,13 @@
     <t xml:space="preserve">9.08626556396484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13466167449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92897987365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97737598419189</t>
+    <t xml:space="preserve">9.1346607208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92897891998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97737503051758</t>
   </si>
   <si>
     <t xml:space="preserve">8.9531774520874</t>
@@ -2240,10 +2240,10 @@
     <t xml:space="preserve">8.89873218536377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07416534423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00157260894775</t>
+    <t xml:space="preserve">9.0741662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00157356262207</t>
   </si>
   <si>
     <t xml:space="preserve">9.24355030059814</t>
@@ -2252,40 +2252,40 @@
     <t xml:space="preserve">9.49762725830078</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47947978973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46133041381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38873767852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63676261901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68516159057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71540641784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83034610748291</t>
+    <t xml:space="preserve">9.47947883605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46133136749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38873672485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6367654800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68515872955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.715407371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83034801483154</t>
   </si>
   <si>
     <t xml:space="preserve">10.2636585235596</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94029140472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65572834014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7268705368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21595001220703</t>
+    <t xml:space="preserve">9.94029331207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65573024749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72686958312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21595096588135</t>
   </si>
   <si>
     <t xml:space="preserve">9.0477991104126</t>
@@ -2297,22 +2297,22 @@
     <t xml:space="preserve">8.52394485473633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2781867980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86427688598633</t>
+    <t xml:space="preserve">8.27818584442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86427640914917</t>
   </si>
   <si>
     <t xml:space="preserve">8.32345771789551</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3751974105835</t>
+    <t xml:space="preserve">8.37519645690918</t>
   </si>
   <si>
     <t xml:space="preserve">8.31699085235596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07123184204102</t>
+    <t xml:space="preserve">8.0712308883667</t>
   </si>
   <si>
     <t xml:space="preserve">7.87721252441406</t>
@@ -2321,52 +2321,52 @@
     <t xml:space="preserve">7.90954923629761</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82547378540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56678104400635</t>
+    <t xml:space="preserve">7.82547426223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56677961349487</t>
   </si>
   <si>
     <t xml:space="preserve">7.72199583053589</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59264898300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54091024398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50210809707642</t>
+    <t xml:space="preserve">7.59264945983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5409107208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50210666656494</t>
   </si>
   <si>
     <t xml:space="preserve">7.37275981903076</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31455421447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66379022598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32748937606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24341344833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28868532180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52150917053223</t>
+    <t xml:space="preserve">7.31455373764038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66379117965698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32748746871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24341297149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2886848449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5215106010437</t>
   </si>
   <si>
     <t xml:space="preserve">7.26281499862671</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29515218734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25634813308716</t>
+    <t xml:space="preserve">7.29515171051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25634860992432</t>
   </si>
   <si>
     <t xml:space="preserve">7.41803121566772</t>
@@ -2375,31 +2375,31 @@
     <t xml:space="preserve">7.70906114578247</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03242683410645</t>
+    <t xml:space="preserve">8.03242778778076</t>
   </si>
   <si>
     <t xml:space="preserve">7.84487533569336</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7025933265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55384540557861</t>
+    <t xml:space="preserve">7.70259380340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55384635925293</t>
   </si>
   <si>
     <t xml:space="preserve">7.76726770401001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7996039390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67672443389893</t>
+    <t xml:space="preserve">7.79960346221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67672395706177</t>
   </si>
   <si>
     <t xml:space="preserve">7.99362325668335</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18117713928223</t>
+    <t xml:space="preserve">8.18117618560791</t>
   </si>
   <si>
     <t xml:space="preserve">8.70503044128418</t>
@@ -2408,19 +2408,19 @@
     <t xml:space="preserve">8.65329170227051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69856262207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79557418823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58215141296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57568454742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49160861968994</t>
+    <t xml:space="preserve">8.69856357574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79557323455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58215236663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57568359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49160766601562</t>
   </si>
   <si>
     <t xml:space="preserve">8.55628108978271</t>
@@ -2429,34 +2429,34 @@
     <t xml:space="preserve">8.95725727081299</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94432163238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93785381317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75030136108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62742233276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82791042327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83437728881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71149921417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60802173614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66622543334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3881311416626</t>
+    <t xml:space="preserve">8.94432067871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9378547668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7503023147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62742328643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82790946960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83437919616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71149730682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6080207824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66622638702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38813209533691</t>
   </si>
   <si>
     <t xml:space="preserve">8.29758930206299</t>
@@ -2465,28 +2465,28 @@
     <t xml:space="preserve">8.54334735870361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02839756011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91845226287842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88611507415771</t>
+    <t xml:space="preserve">9.02839660644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9184513092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88611602783203</t>
   </si>
   <si>
     <t xml:space="preserve">9.12540626525879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48514080047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11003589630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8707447052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26525115966797</t>
+    <t xml:space="preserve">8.48514175415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11003684997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87074422836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26525211334229</t>
   </si>
   <si>
     <t xml:space="preserve">8.33639240264893</t>
@@ -2495,10 +2495,10 @@
     <t xml:space="preserve">8.4334020614624</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36872959136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28465366363525</t>
+    <t xml:space="preserve">8.36872863769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28465270996094</t>
   </si>
   <si>
     <t xml:space="preserve">8.23938179016113</t>
@@ -2510,31 +2510,31 @@
     <t xml:space="preserve">8.76970386505127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02193069458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13187503814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22241687774658</t>
+    <t xml:space="preserve">9.02192974090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13187408447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2224178314209</t>
   </si>
   <si>
     <t xml:space="preserve">9.45524120330811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44230651855469</t>
+    <t xml:space="preserve">9.442307472229</t>
   </si>
   <si>
     <t xml:space="preserve">9.50697994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55871868133545</t>
+    <t xml:space="preserve">9.55871677398682</t>
   </si>
   <si>
     <t xml:space="preserve">9.58458805084229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6945333480835</t>
+    <t xml:space="preserve">9.69453239440918</t>
   </si>
   <si>
     <t xml:space="preserve">9.91442203521729</t>
@@ -2546,25 +2546,25 @@
     <t xml:space="preserve">9.73333740234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89502048492432</t>
+    <t xml:space="preserve">9.89501953125</t>
   </si>
   <si>
     <t xml:space="preserve">9.90795421600342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67513084411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5781192779541</t>
+    <t xml:space="preserve">9.67512989044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57812023162842</t>
   </si>
   <si>
     <t xml:space="preserve">9.66866302490234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90148735046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7074670791626</t>
+    <t xml:space="preserve">9.90148639678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70746803283691</t>
   </si>
   <si>
     <t xml:space="preserve">9.51991558074951</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">9.33236122131348</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43583965301514</t>
+    <t xml:space="preserve">9.43583869934082</t>
   </si>
   <si>
     <t xml:space="preserve">9.09953784942627</t>
@@ -2594,19 +2594,19 @@
     <t xml:space="preserve">9.7398042678833</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76567363739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87561798095703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95322704315186</t>
+    <t xml:space="preserve">9.76567268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87561893463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95322513580322</t>
   </si>
   <si>
     <t xml:space="preserve">9.99849700927734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94675922393799</t>
+    <t xml:space="preserve">9.94675827026367</t>
   </si>
   <si>
     <t xml:space="preserve">9.77214050292969</t>
@@ -2615,10 +2615,10 @@
     <t xml:space="preserve">9.88208484649658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98556327819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2248544692993</t>
+    <t xml:space="preserve">9.98556137084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2248554229736</t>
   </si>
   <si>
     <t xml:space="preserve">9.44877433776855</t>
@@ -2636,10 +2636,10 @@
     <t xml:space="preserve">10.2377872467041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62339115142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41643810272217</t>
+    <t xml:space="preserve">9.62339210510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41643714904785</t>
   </si>
   <si>
     <t xml:space="preserve">9.34529590606689</t>
@@ -2648,25 +2648,25 @@
     <t xml:space="preserve">9.24181938171387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19007873535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06073474884033</t>
+    <t xml:space="preserve">9.1900806427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06073379516602</t>
   </si>
   <si>
     <t xml:space="preserve">9.0801362991333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97665786743164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04133224487305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92492008209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7632360458374</t>
+    <t xml:space="preserve">8.97665882110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04133129119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92491912841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76323699951172</t>
   </si>
   <si>
     <t xml:space="preserve">8.84731197357178</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">8.61448764801025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56921768188477</t>
+    <t xml:space="preserve">8.56921577453613</t>
   </si>
   <si>
     <t xml:space="preserve">8.67916202545166</t>
@@ -2687,55 +2687,55 @@
     <t xml:space="preserve">8.86671447753906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87318134307861</t>
+    <t xml:space="preserve">8.87318229675293</t>
   </si>
   <si>
     <t xml:space="preserve">8.81497573852539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86024761199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24828624725342</t>
+    <t xml:space="preserve">8.86024570465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24828720092773</t>
   </si>
   <si>
     <t xml:space="preserve">9.05426597595215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14480972290039</t>
+    <t xml:space="preserve">9.14480876922607</t>
   </si>
   <si>
     <t xml:space="preserve">9.23535251617432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15774250030518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13834285736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26768970489502</t>
+    <t xml:space="preserve">9.15774440765381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13834190368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2676887512207</t>
   </si>
   <si>
     <t xml:space="preserve">9.09307098388672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93138694763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20301532745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59105491638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57165241241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51344776153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53284931182861</t>
+    <t xml:space="preserve">8.93138885498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2030143737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59105587005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57165336608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51344680786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5328483581543</t>
   </si>
   <si>
     <t xml:space="preserve">9.32589435577393</t>
@@ -2744,28 +2744,28 @@
     <t xml:space="preserve">9.30002593994141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74627113342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47464370727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27415752410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62986087799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70100021362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80447673797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1343116760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1278448104858</t>
+    <t xml:space="preserve">9.74627017974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47464275360107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27415561676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62985897064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70099925994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80447769165039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1343107223511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1278429031372</t>
   </si>
   <si>
     <t xml:space="preserve">10.069637298584</t>
@@ -2783,19 +2783,19 @@
     <t xml:space="preserve">9.35176372528076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5522518157959</t>
+    <t xml:space="preserve">9.55225276947021</t>
   </si>
   <si>
     <t xml:space="preserve">8.89258289337158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40753364562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90308094024658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88124322891235</t>
+    <t xml:space="preserve">8.40753269195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90308141708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8812427520752</t>
   </si>
   <si>
     <t xml:space="preserve">6.61608171463013</t>
@@ -2807,22 +2807,22 @@
     <t xml:space="preserve">5.67185115814209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93701076507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61364555358887</t>
+    <t xml:space="preserve">5.93701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61364603042603</t>
   </si>
   <si>
     <t xml:space="preserve">5.44549465179443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45842933654785</t>
+    <t xml:space="preserve">5.45842885971069</t>
   </si>
   <si>
     <t xml:space="preserve">5.43902730941772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75592613220215</t>
+    <t xml:space="preserve">5.75592660903931</t>
   </si>
   <si>
     <t xml:space="preserve">5.57160758972168</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">5.84000158309937</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86910486221313</t>
+    <t xml:space="preserve">5.86910533905029</t>
   </si>
   <si>
     <t xml:space="preserve">5.98228311538696</t>
@@ -2840,58 +2840,58 @@
     <t xml:space="preserve">5.90790891647339</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66215038299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78826332092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75916004180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70095491409302</t>
+    <t xml:space="preserve">5.66215085983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78826284408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75915956497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70095443725586</t>
   </si>
   <si>
     <t xml:space="preserve">5.78179597854614</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83676815032959</t>
+    <t xml:space="preserve">5.83676767349243</t>
   </si>
   <si>
     <t xml:space="preserve">5.96934795379639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94671297073364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97581624984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83353471755981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71388864517212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76886177062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77532958984375</t>
+    <t xml:space="preserve">5.9467134475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9758152961731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83353424072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71388912200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76886129379272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77532911300659</t>
   </si>
   <si>
     <t xml:space="preserve">5.49723339080811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38405513763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51663541793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81413269042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93054533004761</t>
+    <t xml:space="preserve">5.38405418395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51663494110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81413173675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93054485321045</t>
   </si>
   <si>
     <t xml:space="preserve">5.77209520339966</t>
@@ -2900,85 +2900,85 @@
     <t xml:space="preserve">5.5619068145752</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62011241912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58454275131226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47136402130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55867290496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4810643196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40669059753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.32584857940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22560501098633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19326877593994</t>
+    <t xml:space="preserve">5.62011194229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58454322814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47136449813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55867385864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48106479644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40669012069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3258490562439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22560548782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19326782226562</t>
   </si>
   <si>
     <t xml:space="preserve">5.17386674880981</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94751024246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81169557571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70821905136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72115325927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97984647750854</t>
+    <t xml:space="preserve">4.947509765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81169605255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70821857452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7211537361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9798469543457</t>
   </si>
   <si>
     <t xml:space="preserve">5.18033456802368</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33555030822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42932748794556</t>
+    <t xml:space="preserve">5.33554935455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4293270111084</t>
   </si>
   <si>
     <t xml:space="preserve">5.36465311050415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40022325515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72682332992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94347906112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25391054153442</t>
+    <t xml:space="preserve">5.40022373199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7268238067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94347953796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2539119720459</t>
   </si>
   <si>
     <t xml:space="preserve">6.70015716552734</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28624820709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09222793579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67508411407471</t>
+    <t xml:space="preserve">6.28624868392944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0922269821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67508506774902</t>
   </si>
   <si>
     <t xml:space="preserve">5.63304758071899</t>
@@ -2987,34 +2987,34 @@
     <t xml:space="preserve">5.78502941131592</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87880659103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82060050964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7332911491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58777618408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53603744506836</t>
+    <t xml:space="preserve">5.87880611419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8206000328064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73329162597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58777666091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53603792190552</t>
   </si>
   <si>
     <t xml:space="preserve">5.3969898223877</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31614875793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37435388565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49399995803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52957010269165</t>
+    <t xml:space="preserve">5.31614828109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37435436248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49399900436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52956962585449</t>
   </si>
   <si>
     <t xml:space="preserve">5.51340103149414</t>
@@ -3023,40 +3023,40 @@
     <t xml:space="preserve">5.64598178863525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75269317626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8658709526062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80119752883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89497423171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87557220458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22804260253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34768724441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39942693710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19570541381836</t>
+    <t xml:space="preserve">5.75269365310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86587142944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80119895935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89497470855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87557315826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22804307937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3476881980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39942646026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1957049369812</t>
   </si>
   <si>
     <t xml:space="preserve">6.05989122390747</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91760921478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77856302261353</t>
+    <t xml:space="preserve">5.91760969161987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77856254577637</t>
   </si>
   <si>
     <t xml:space="preserve">5.607177734375</t>
@@ -3065,13 +3065,13 @@
     <t xml:space="preserve">5.60394430160522</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80766487121582</t>
+    <t xml:space="preserve">5.80766534805298</t>
   </si>
   <si>
     <t xml:space="preserve">5.81736612319946</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68478584289551</t>
+    <t xml:space="preserve">5.68478631973267</t>
   </si>
   <si>
     <t xml:space="preserve">5.93377876281738</t>
@@ -3080,16 +3080,16 @@
     <t xml:space="preserve">5.91114234924316</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94024515151978</t>
+    <t xml:space="preserve">5.94024562835693</t>
   </si>
   <si>
     <t xml:space="preserve">5.82383346557617</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7947301864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8982081413269</t>
+    <t xml:space="preserve">5.79473066329956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89820766448975</t>
   </si>
   <si>
     <t xml:space="preserve">5.73652505874634</t>
@@ -3101,16 +3101,16 @@
     <t xml:space="preserve">5.79796409606934</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63951444625854</t>
+    <t xml:space="preserve">5.6395149230957</t>
   </si>
   <si>
     <t xml:space="preserve">5.59101009368896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58130836486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70418834686279</t>
+    <t xml:space="preserve">5.58130884170532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70418787002563</t>
   </si>
   <si>
     <t xml:space="preserve">5.70742130279541</t>
@@ -3119,16 +3119,16 @@
     <t xml:space="preserve">5.6653847694397</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69448709487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88204002380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80443143844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71065473556519</t>
+    <t xml:space="preserve">5.69448661804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88203954696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80443286895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71065521240234</t>
   </si>
   <si>
     <t xml:space="preserve">5.50693464279175</t>
@@ -3140,28 +3140,28 @@
     <t xml:space="preserve">5.33878374099731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43255949020386</t>
+    <t xml:space="preserve">5.43255996704102</t>
   </si>
   <si>
     <t xml:space="preserve">5.30321311950684</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31938219070435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21267127990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21590375900269</t>
+    <t xml:space="preserve">5.31938123703003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21267080307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21590423583984</t>
   </si>
   <si>
     <t xml:space="preserve">5.22883892059326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34201717376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26764345169067</t>
+    <t xml:space="preserve">5.34201765060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26764249801636</t>
   </si>
   <si>
     <t xml:space="preserve">5.32261514663696</t>
@@ -3185,7 +3185,7 @@
     <t xml:space="preserve">5.07038974761963</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10919332504272</t>
+    <t xml:space="preserve">5.10919380187988</t>
   </si>
   <si>
     <t xml:space="preserve">5.20297002792358</t>
@@ -3200,13 +3200,13 @@
     <t xml:space="preserve">4.92164039611816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81493043899536</t>
+    <t xml:space="preserve">4.81492948532104</t>
   </si>
   <si>
     <t xml:space="preserve">4.82463073730469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50773143768311</t>
+    <t xml:space="preserve">4.50773191452026</t>
   </si>
   <si>
     <t xml:space="preserve">4.36221647262573</t>
@@ -3215,16 +3215,16 @@
     <t xml:space="preserve">4.45275926589966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58857297897339</t>
+    <t xml:space="preserve">4.58857250213623</t>
   </si>
   <si>
     <t xml:space="preserve">4.7825927734375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8990044593811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82786417007446</t>
+    <t xml:space="preserve">4.89900541305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82786512374878</t>
   </si>
   <si>
     <t xml:space="preserve">4.79229402542114</t>
@@ -3233,7 +3233,7 @@
     <t xml:space="preserve">5.13829660415649</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14799690246582</t>
+    <t xml:space="preserve">5.14799737930298</t>
   </si>
   <si>
     <t xml:space="preserve">5.25794219970703</t>
@@ -3242,28 +3242,28 @@
     <t xml:space="preserve">5.23530626296997</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65891647338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8432354927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85940504074097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07605981826782</t>
+    <t xml:space="preserve">5.65891695022583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84323596954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85940408706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07606029510498</t>
   </si>
   <si>
     <t xml:space="preserve">6.0081524848938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97904920578003</t>
+    <t xml:space="preserve">5.97905015945435</t>
   </si>
   <si>
     <t xml:space="preserve">5.98875093460083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9046745300293</t>
+    <t xml:space="preserve">5.90467548370361</t>
   </si>
   <si>
     <t xml:space="preserve">6.17630290985107</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">6.29918241500854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31858444213867</t>
+    <t xml:space="preserve">6.31858396530151</t>
   </si>
   <si>
     <t xml:space="preserve">6.34445428848267</t>
@@ -3281,10 +3281,10 @@
     <t xml:space="preserve">6.21834087371826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19247150421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13103151321411</t>
+    <t xml:space="preserve">6.19247102737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13103199005127</t>
   </si>
   <si>
     <t xml:space="preserve">6.05665731430054</t>
@@ -3293,262 +3293,262 @@
     <t xml:space="preserve">6.10516262054443</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10192966461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0404896736145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03725576400757</t>
+    <t xml:space="preserve">6.10192918777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04048919677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03725624084473</t>
   </si>
   <si>
     <t xml:space="preserve">6.06635856628418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88850688934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95317983627319</t>
+    <t xml:space="preserve">5.8885064125061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95318031311035</t>
   </si>
   <si>
     <t xml:space="preserve">5.99198484420776</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98551654815674</t>
+    <t xml:space="preserve">5.9855170249939</t>
   </si>
   <si>
     <t xml:space="preserve">6.02432060241699</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01138591766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97258234024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73005676269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73975801467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64921522140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55543899536133</t>
+    <t xml:space="preserve">6.01138687133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97258186340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73005771636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7397575378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64921569824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55543947219849</t>
   </si>
   <si>
     <t xml:space="preserve">5.36788702011108</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46813011169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41639137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72358989715576</t>
+    <t xml:space="preserve">5.46813058853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41639232635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72359037399292</t>
   </si>
   <si>
     <t xml:space="preserve">6.07282638549805</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26037836074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39619207382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75836277008057</t>
+    <t xml:space="preserve">6.26037883758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3961935043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75836324691772</t>
   </si>
   <si>
     <t xml:space="preserve">6.67428779602051</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75189590454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66782093048096</t>
+    <t xml:space="preserve">6.75189542770386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66781997680664</t>
   </si>
   <si>
     <t xml:space="preserve">6.66135406494141</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58374643325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64195203781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69369029998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90064430236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80363512039185</t>
+    <t xml:space="preserve">6.58374500274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64195251464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69368982315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90064477920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.803635597229</t>
   </si>
   <si>
     <t xml:space="preserve">6.97178554534912</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83597040176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85537385940552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78423357009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21107625961304</t>
+    <t xml:space="preserve">6.83597135543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85537338256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78423309326172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21107530593872</t>
   </si>
   <si>
     <t xml:space="preserve">7.19167518615723</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23694562911987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42449903488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48270320892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39216232299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41156435012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16580533981323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19814205169678</t>
+    <t xml:space="preserve">7.23694610595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42449855804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48270463943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39216136932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41156387329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16580486297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19814157485962</t>
   </si>
   <si>
     <t xml:space="preserve">7.24988031387329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35335779190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36629295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27574920654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32102155685425</t>
+    <t xml:space="preserve">7.35335731506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36629152297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27575016021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32102060317993</t>
   </si>
   <si>
     <t xml:space="preserve">7.34689044952393</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15287113189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49563932418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43743324279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39862823486328</t>
+    <t xml:space="preserve">7.15287065505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49563980102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43743371963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39862871170044</t>
   </si>
   <si>
     <t xml:space="preserve">7.35982513427734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08172988891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26928234100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46330308914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51504135131836</t>
+    <t xml:space="preserve">7.08172941207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26928281784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46330261230469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5150408744812</t>
   </si>
   <si>
     <t xml:space="preserve">7.46976947784424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44390153884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47623682022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52797603607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95482110977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69612646102905</t>
+    <t xml:space="preserve">7.44389963150024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47623825073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52797555923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95482015609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69612693786621</t>
   </si>
   <si>
     <t xml:space="preserve">8.11650371551514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43986988067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46573829650879</t>
+    <t xml:space="preserve">8.43987083435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46574020385742</t>
   </si>
   <si>
     <t xml:space="preserve">8.40106582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25878429412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18764495849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05183029174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22644901275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31052303314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34932708740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4204683303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38166427612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50454425811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14884090423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01546287536621</t>
+    <t xml:space="preserve">8.25878620147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18764400482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05182933807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22644805908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31052398681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34932613372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42046737670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38166332244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50454330444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14883995056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01546382904053</t>
   </si>
   <si>
     <t xml:space="preserve">8.90551853179932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64682483673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59508514404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51101112365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29112243652344</t>
+    <t xml:space="preserve">8.64682579040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59508609771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51101016998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29112148284912</t>
   </si>
   <si>
     <t xml:space="preserve">8.78910636901855</t>
@@ -3557,40 +3557,40 @@
     <t xml:space="preserve">8.23291492462158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35579490661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96372318267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98312473297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98959350585938</t>
+    <t xml:space="preserve">8.35579395294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96372509002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98312664031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98959255218506</t>
   </si>
   <si>
     <t xml:space="preserve">9.07366847991943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00252819061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99606037139893</t>
+    <t xml:space="preserve">9.00252723693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99605941772461</t>
   </si>
   <si>
     <t xml:space="preserve">9.0672025680542</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19654846191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46817588806152</t>
+    <t xml:space="preserve">9.19654750823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46817684173584</t>
   </si>
   <si>
     <t xml:space="preserve">9.42290496826172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37763214111328</t>
+    <t xml:space="preserve">9.3776330947876</t>
   </si>
   <si>
     <t xml:space="preserve">9.39056777954102</t>
@@ -3599,16 +3599,16 @@
     <t xml:space="preserve">9.46170806884766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20948314666748</t>
+    <t xml:space="preserve">9.20948219299316</t>
   </si>
   <si>
     <t xml:space="preserve">9.36469841003418</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49404621124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48111057281494</t>
+    <t xml:space="preserve">9.49404525756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48110961914062</t>
   </si>
   <si>
     <t xml:space="preserve">9.565185546875</t>
@@ -3617,19 +3617,19 @@
     <t xml:space="preserve">9.81094455718994</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0437679290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0890407562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3283309936523</t>
+    <t xml:space="preserve">10.0437688827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0890398025513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3283319473267</t>
   </si>
   <si>
     <t xml:space="preserve">10.4059400558472</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4447431564331</t>
+    <t xml:space="preserve">10.4447441101074</t>
   </si>
   <si>
     <t xml:space="preserve">10.2442560195923</t>
@@ -3638,34 +3638,34 @@
     <t xml:space="preserve">10.7616424560547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8263149261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1173458099365</t>
+    <t xml:space="preserve">10.8263158798218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1173477172852</t>
   </si>
   <si>
     <t xml:space="preserve">10.5611543655396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9685945510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5934915542603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8133811950684</t>
+    <t xml:space="preserve">10.9685974121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5934925079346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.813380241394</t>
   </si>
   <si>
     <t xml:space="preserve">10.6775674819946</t>
   </si>
   <si>
-    <t xml:space="preserve">10.658164024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8198480606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6840343475342</t>
+    <t xml:space="preserve">10.6581649780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8198471069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6840353012085</t>
   </si>
   <si>
     <t xml:space="preserve">11.0074014663696</t>
@@ -3683,22 +3683,22 @@
     <t xml:space="preserve">11.0908222198486</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9110450744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0078477859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1046504974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0424194335938</t>
+    <t xml:space="preserve">10.9110441207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.007848739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1046495437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0424213409424</t>
   </si>
   <si>
     <t xml:space="preserve">11.0562496185303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1945400238037</t>
+    <t xml:space="preserve">11.1945390701294</t>
   </si>
   <si>
     <t xml:space="preserve">11.3051719665527</t>
@@ -3710,43 +3710,43 @@
     <t xml:space="preserve">11.5748348236084</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5955791473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6854658126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6508941650391</t>
+    <t xml:space="preserve">11.5955781936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6854667663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6508951187134</t>
   </si>
   <si>
     <t xml:space="preserve">11.4780330657959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7131261825562</t>
+    <t xml:space="preserve">11.7131242752075</t>
   </si>
   <si>
     <t xml:space="preserve">11.6923818588257</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6301498413086</t>
+    <t xml:space="preserve">11.6301507949829</t>
   </si>
   <si>
     <t xml:space="preserve">11.5402631759644</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2636842727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1392240524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8280725479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9456176757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5514917373657</t>
+    <t xml:space="preserve">11.2636833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1392230987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.828070640564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9456167221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.55149269104</t>
   </si>
   <si>
     <t xml:space="preserve">10.5100059509277</t>
@@ -3764,16 +3764,16 @@
     <t xml:space="preserve">10.2057685852051</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6828670501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5445785522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4616050720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8419008255005</t>
+    <t xml:space="preserve">10.6828680038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5445775985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4616041183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8419017791748</t>
   </si>
   <si>
     <t xml:space="preserve">10.9940185546875</t>
@@ -3782,16 +3782,16 @@
     <t xml:space="preserve">10.8764734268188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9663600921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9179601669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8211574554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5653219223022</t>
+    <t xml:space="preserve">10.9663610458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9179592132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.82115650177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5653209686279</t>
   </si>
   <si>
     <t xml:space="preserve">10.7381839752197</t>
@@ -3800,13 +3800,13 @@
     <t xml:space="preserve">11.049334526062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0355072021484</t>
+    <t xml:space="preserve">11.0355052947998</t>
   </si>
   <si>
     <t xml:space="preserve">11.7546119689941</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8030118942261</t>
+    <t xml:space="preserve">11.8030128479004</t>
   </si>
   <si>
     <t xml:space="preserve">12.0934209823608</t>
@@ -3818,16 +3818,16 @@
     <t xml:space="preserve">12.1487350463867</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9413022994995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1210794448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0795907974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2593679428101</t>
+    <t xml:space="preserve">11.9413042068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1210784912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0795927047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2593698501587</t>
   </si>
   <si>
     <t xml:space="preserve">12.4184017181396</t>
@@ -3845,22 +3845,22 @@
     <t xml:space="preserve">12.3285131454468</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2870254516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6880664825439</t>
+    <t xml:space="preserve">12.2870264053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6880674362183</t>
   </si>
   <si>
     <t xml:space="preserve">12.570520401001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8514137268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2455387115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3561735153198</t>
+    <t xml:space="preserve">11.8514156341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2455396652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3561716079712</t>
   </si>
   <si>
     <t xml:space="preserve">12.376914024353</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">12.2662839889526</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2040538787842</t>
+    <t xml:space="preserve">12.2040519714355</t>
   </si>
   <si>
     <t xml:space="preserve">12.6396646499634</t>
@@ -3881,28 +3881,28 @@
     <t xml:space="preserve">12.3907442092896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7364683151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2757949829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1885070800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3129692077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9352703094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9905862808228</t>
+    <t xml:space="preserve">12.7364664077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2757968902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1885080337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3129682540894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9352722167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9905872344971</t>
   </si>
   <si>
     <t xml:space="preserve">14.7554950714111</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7969808578491</t>
+    <t xml:space="preserve">14.7969837188721</t>
   </si>
   <si>
     <t xml:space="preserve">13.9672441482544</t>
@@ -3923,7 +3923,7 @@
     <t xml:space="preserve">12.335428237915</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5774354934692</t>
+    <t xml:space="preserve">12.5774345397949</t>
   </si>
   <si>
     <t xml:space="preserve">12.3492574691772</t>
@@ -3935,28 +3935,28 @@
     <t xml:space="preserve">10.7589273452759</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7615261077881</t>
+    <t xml:space="preserve">11.7615270614624</t>
   </si>
   <si>
     <t xml:space="preserve">11.0285911560059</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3674030303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8652439117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1694803237915</t>
+    <t xml:space="preserve">11.3674020767212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8652429580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1694812774658</t>
   </si>
   <si>
     <t xml:space="preserve">12.8056125640869</t>
   </si>
   <si>
-    <t xml:space="preserve">12.715723991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7433834075928</t>
+    <t xml:space="preserve">12.7157249450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7433815002441</t>
   </si>
   <si>
     <t xml:space="preserve">13.0614471435547</t>
@@ -3965,13 +3965,13 @@
     <t xml:space="preserve">12.9992170333862</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8885841369629</t>
+    <t xml:space="preserve">12.8885850906372</t>
   </si>
   <si>
     <t xml:space="preserve">13.0337896347046</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0683612823486</t>
+    <t xml:space="preserve">13.0683631896973</t>
   </si>
   <si>
     <t xml:space="preserve">12.909330368042</t>
@@ -3980,22 +3980,22 @@
     <t xml:space="preserve">13.019962310791</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2731981277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6465797424316</t>
+    <t xml:space="preserve">12.2731962203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.646580696106</t>
   </si>
   <si>
     <t xml:space="preserve">12.4944610595703</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5428609848022</t>
+    <t xml:space="preserve">12.5428619384766</t>
   </si>
   <si>
     <t xml:space="preserve">12.2524547576904</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5566902160645</t>
+    <t xml:space="preserve">12.5566911697388</t>
   </si>
   <si>
     <t xml:space="preserve">11.955132484436</t>
@@ -4010,19 +4010,19 @@
     <t xml:space="preserve">11.3466567993164</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5817489624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0242767333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3008556365967</t>
+    <t xml:space="preserve">11.581750869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0242748260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.300856590271</t>
   </si>
   <si>
     <t xml:space="preserve">12.0381050109863</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5793085098267</t>
+    <t xml:space="preserve">12.5793075561523</t>
   </si>
   <si>
     <t xml:space="preserve">12.5939340591431</t>
@@ -4034,10 +4034,10 @@
     <t xml:space="preserve">12.7694606781006</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6743831634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7475204467773</t>
+    <t xml:space="preserve">12.6743841171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.747519493103</t>
   </si>
   <si>
     <t xml:space="preserve">12.4184093475342</t>
@@ -4046,13 +4046,13 @@
     <t xml:space="preserve">12.3964691162109</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3745288848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3452739715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3525876998901</t>
+    <t xml:space="preserve">12.374529838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3452730178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3525886535645</t>
   </si>
   <si>
     <t xml:space="preserve">12.140495300293</t>
@@ -4061,16 +4061,16 @@
     <t xml:space="preserve">11.9795970916748</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7455615997314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0434617996216</t>
+    <t xml:space="preserve">11.7455625534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0434627532959</t>
   </si>
   <si>
     <t xml:space="preserve">10.480318069458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5900211334229</t>
+    <t xml:space="preserve">10.5900220870972</t>
   </si>
   <si>
     <t xml:space="preserve">10.9630126953125</t>
@@ -4079,25 +4079,25 @@
     <t xml:space="preserve">10.4583778381348</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4437503814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6777839660645</t>
+    <t xml:space="preserve">10.443751335144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6777849197388</t>
   </si>
   <si>
     <t xml:space="preserve">10.5095729827881</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5022592544556</t>
+    <t xml:space="preserve">10.5022583007812</t>
   </si>
   <si>
     <t xml:space="preserve">10.2389717102051</t>
   </si>
   <si>
-    <t xml:space="preserve">10.494945526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.429123878479</t>
+    <t xml:space="preserve">10.4949464797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4291248321533</t>
   </si>
   <si>
     <t xml:space="preserve">10.3998699188232</t>
@@ -4106,22 +4106,22 @@
     <t xml:space="preserve">10.209716796875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88060855865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75627613067627</t>
+    <t xml:space="preserve">9.88060760498047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75627708435059</t>
   </si>
   <si>
     <t xml:space="preserve">9.70508289337158</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31014919281006</t>
+    <t xml:space="preserve">9.31015014648438</t>
   </si>
   <si>
     <t xml:space="preserve">9.23701477050781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43448066711426</t>
+    <t xml:space="preserve">9.43448162078857</t>
   </si>
   <si>
     <t xml:space="preserve">9.69776916503906</t>
@@ -4133,37 +4133,37 @@
     <t xml:space="preserve">9.46373462677002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06149005889893</t>
+    <t xml:space="preserve">9.06149101257324</t>
   </si>
   <si>
     <t xml:space="preserve">8.62267780303955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82745552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97372722625732</t>
+    <t xml:space="preserve">8.8274564743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97372627258301</t>
   </si>
   <si>
     <t xml:space="preserve">9.20775985717773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24432945251465</t>
+    <t xml:space="preserve">9.24432849884033</t>
   </si>
   <si>
     <t xml:space="preserve">9.18582057952881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25895500183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53687000274658</t>
+    <t xml:space="preserve">9.25895595550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5368709564209</t>
   </si>
   <si>
     <t xml:space="preserve">9.21507453918457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36865901947021</t>
+    <t xml:space="preserve">9.3686580657959</t>
   </si>
   <si>
     <t xml:space="preserve">9.39791297912598</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">9.55881023406982</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95374298095703</t>
+    <t xml:space="preserve">9.95374202728271</t>
   </si>
   <si>
     <t xml:space="preserve">10.0195646286011</t>
@@ -4187,7 +4187,7 @@
     <t xml:space="preserve">9.98299694061279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72702407836914</t>
+    <t xml:space="preserve">9.72702312469482</t>
   </si>
   <si>
     <t xml:space="preserve">9.47104835510254</t>
@@ -4199,13 +4199,13 @@
     <t xml:space="preserve">9.80747222900391</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97568416595459</t>
+    <t xml:space="preserve">9.97568321228027</t>
   </si>
   <si>
     <t xml:space="preserve">9.49298858642578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10537242889404</t>
+    <t xml:space="preserve">9.10537147521973</t>
   </si>
   <si>
     <t xml:space="preserve">9.22238826751709</t>
@@ -4217,46 +4217,46 @@
     <t xml:space="preserve">9.06880283355713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.820143699646</t>
+    <t xml:space="preserve">8.82014274597168</t>
   </si>
   <si>
     <t xml:space="preserve">8.75432014465332</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81282997131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7396936416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51297473907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68849945068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44715213775635</t>
+    <t xml:space="preserve">8.81282806396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73969268798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51297378540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68849849700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44715023040771</t>
   </si>
   <si>
     <t xml:space="preserve">8.40326976776123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27894020080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35207653045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54222774505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01760864257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02492141723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14925193786621</t>
+    <t xml:space="preserve">8.27893924713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35207557678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54222869873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01760959625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02492237091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14925289154053</t>
   </si>
   <si>
     <t xml:space="preserve">8.94447326660156</t>
@@ -4271,34 +4271,34 @@
     <t xml:space="preserve">8.63730430603027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34476184844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35938930511475</t>
+    <t xml:space="preserve">8.34476280212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35938835144043</t>
   </si>
   <si>
     <t xml:space="preserve">8.22043132781982</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13266849517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86938142776489</t>
+    <t xml:space="preserve">8.13266944885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86938047409058</t>
   </si>
   <si>
     <t xml:space="preserve">8.32282066345215</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41789722442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33013534545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24237155914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14729595184326</t>
+    <t xml:space="preserve">8.41789627075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33013439178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24237251281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14729690551758</t>
   </si>
   <si>
     <t xml:space="preserve">8.07415962219238</t>
@@ -4307,16 +4307,16 @@
     <t xml:space="preserve">8.16192245483398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04490756988525</t>
+    <t xml:space="preserve">8.04490661621094</t>
   </si>
   <si>
     <t xml:space="preserve">8.05222034454346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28625297546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26431274414062</t>
+    <t xml:space="preserve">8.28625202178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26431369781494</t>
   </si>
   <si>
     <t xml:space="preserve">8.30088138580322</t>
@@ -4337,31 +4337,31 @@
     <t xml:space="preserve">8.88596343994141</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92253303527832</t>
+    <t xml:space="preserve">8.922532081604</t>
   </si>
   <si>
     <t xml:space="preserve">9.56612491607666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52955627441406</t>
+    <t xml:space="preserve">9.52955532073975</t>
   </si>
   <si>
     <t xml:space="preserve">9.84403991699219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0488204956055</t>
+    <t xml:space="preserve">10.0488185882568</t>
   </si>
   <si>
     <t xml:space="preserve">10.1804628372192</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1512079238892</t>
+    <t xml:space="preserve">10.1512088775635</t>
   </si>
   <si>
     <t xml:space="preserve">10.1146411895752</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0049390792847</t>
+    <t xml:space="preserve">10.0049381256104</t>
   </si>
   <si>
     <t xml:space="preserve">10.3340473175049</t>
@@ -4382,22 +4382,22 @@
     <t xml:space="preserve">10.3497886657715</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3891410827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2553424835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2710819244385</t>
+    <t xml:space="preserve">10.389142036438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2553415298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2710828781128</t>
   </si>
   <si>
     <t xml:space="preserve">10.2002477645874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.04283618927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86968421936035</t>
+    <t xml:space="preserve">10.0428371429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86968517303467</t>
   </si>
   <si>
     <t xml:space="preserve">9.88542556762695</t>
@@ -4412,19 +4412,19 @@
     <t xml:space="preserve">10.1608953475952</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1845064163208</t>
+    <t xml:space="preserve">10.1845073699951</t>
   </si>
   <si>
     <t xml:space="preserve">10.0034837722778</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0900592803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5229396820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3419179916382</t>
+    <t xml:space="preserve">10.0900602340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5229415893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3419189453125</t>
   </si>
   <si>
     <t xml:space="preserve">10.4521055221558</t>
@@ -4433,10 +4433,10 @@
     <t xml:space="preserve">10.3812704086304</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4678468704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4757165908813</t>
+    <t xml:space="preserve">10.467845916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.47571849823</t>
   </si>
   <si>
     <t xml:space="preserve">10.5780344009399</t>
@@ -4448,34 +4448,34 @@
     <t xml:space="preserve">11.003044128418</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0345277786255</t>
+    <t xml:space="preserve">11.0345287322998</t>
   </si>
   <si>
     <t xml:space="preserve">11.0423974990845</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1998090744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2234210968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2863855361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3650913238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3493499755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3414793014526</t>
+    <t xml:space="preserve">11.1998081207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2234201431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2863864898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3650903701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3493509292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3414783477783</t>
   </si>
   <si>
     <t xml:space="preserve">11.3099966049194</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1919393539429</t>
+    <t xml:space="preserve">11.1919384002686</t>
   </si>
   <si>
     <t xml:space="preserve">11.412314414978</t>
@@ -4484,46 +4484,46 @@
     <t xml:space="preserve">11.3965730667114</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2155513763428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4280567169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4752798080444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8294544219971</t>
+    <t xml:space="preserve">11.2155504226685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4280557632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4752788543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8294525146484</t>
   </si>
   <si>
     <t xml:space="preserve">12.0813131332397</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1678886413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3725233078003</t>
+    <t xml:space="preserve">12.1678876876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3725242614746</t>
   </si>
   <si>
     <t xml:space="preserve">12.3095588684082</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4040040969849</t>
+    <t xml:space="preserve">12.4040050506592</t>
   </si>
   <si>
     <t xml:space="preserve">12.5220632553101</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5141925811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7266979217529</t>
+    <t xml:space="preserve">12.5141935348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7266988754272</t>
   </si>
   <si>
     <t xml:space="preserve">12.8368854522705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8132743835449</t>
+    <t xml:space="preserve">12.8132753372192</t>
   </si>
   <si>
     <t xml:space="preserve">12.5378046035767</t>
@@ -4550,13 +4550,13 @@
     <t xml:space="preserve">12.2702054977417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2308540344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3016881942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3253002166748</t>
+    <t xml:space="preserve">12.2308521270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3016872406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3252992630005</t>
   </si>
   <si>
     <t xml:space="preserve">11.9160308837891</t>
@@ -4571,7 +4571,7 @@
     <t xml:space="preserve">11.1132335662842</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1289749145508</t>
+    <t xml:space="preserve">11.1289758682251</t>
   </si>
   <si>
     <t xml:space="preserve">11.0974922180176</t>
@@ -4580,7 +4580,7 @@
     <t xml:space="preserve">11.0266561508179</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8062801361084</t>
+    <t xml:space="preserve">10.8062810897827</t>
   </si>
   <si>
     <t xml:space="preserve">10.8456335067749</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">10.7118339538574</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8613767623901</t>
+    <t xml:space="preserve">10.8613758087158</t>
   </si>
   <si>
     <t xml:space="preserve">10.9951753616333</t>
@@ -4607,16 +4607,16 @@
     <t xml:space="preserve">11.176197052002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5854663848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5225038528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7743616104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8766784667969</t>
+    <t xml:space="preserve">11.585467338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5225028991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7743606567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8766775131226</t>
   </si>
   <si>
     <t xml:space="preserve">11.8137130737305</t>
@@ -4628,22 +4628,22 @@
     <t xml:space="preserve">12.1285362243652</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9632539749146</t>
+    <t xml:space="preserve">11.9632530212402</t>
   </si>
   <si>
     <t xml:space="preserve">11.9002895355225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9789953231812</t>
+    <t xml:space="preserve">11.9789943695068</t>
   </si>
   <si>
     <t xml:space="preserve">11.5697259902954</t>
   </si>
   <si>
-    <t xml:space="preserve">11.60120677948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8058423995972</t>
+    <t xml:space="preserve">11.6012077331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8058433532715</t>
   </si>
   <si>
     <t xml:space="preserve">11.9317722320557</t>
@@ -4652,16 +4652,16 @@
     <t xml:space="preserve">11.3257389068604</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3572206497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.333607673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.912278175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8475379943848</t>
+    <t xml:space="preserve">11.3572196960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3336086273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9122791290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8475370407104</t>
   </si>
   <si>
     <t xml:space="preserve">11.6614074707031</t>
@@ -4670,10 +4670,10 @@
     <t xml:space="preserve">11.6290378570557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8070735931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7666110992432</t>
+    <t xml:space="preserve">11.807074546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7666120529175</t>
   </si>
   <si>
     <t xml:space="preserve">11.4995565414429</t>
@@ -4682,7 +4682,7 @@
     <t xml:space="preserve">11.3296127319336</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5076484680176</t>
+    <t xml:space="preserve">11.5076494216919</t>
   </si>
   <si>
     <t xml:space="preserve">11.6371307373047</t>
@@ -4697,7 +4697,7 @@
     <t xml:space="preserve">11.5885753631592</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5400199890137</t>
+    <t xml:space="preserve">11.5400190353394</t>
   </si>
   <si>
     <t xml:space="preserve">11.4429092407227</t>
@@ -4721,7 +4721,7 @@
     <t xml:space="preserve">11.3700761795044</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5723886489868</t>
+    <t xml:space="preserve">11.5723905563354</t>
   </si>
   <si>
     <t xml:space="preserve">11.3943529129028</t>
@@ -4733,7 +4733,7 @@
     <t xml:space="preserve">11.6047601699829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6533155441284</t>
+    <t xml:space="preserve">11.6533145904541</t>
   </si>
   <si>
     <t xml:space="preserve">11.6209449768066</t>
@@ -4745,7 +4745,7 @@
     <t xml:space="preserve">11.9770183563232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9932050704956</t>
+    <t xml:space="preserve">11.9932041168213</t>
   </si>
   <si>
     <t xml:space="preserve">11.8232593536377</t>
@@ -4757,7 +4757,7 @@
     <t xml:space="preserve">11.815167427063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9365558624268</t>
+    <t xml:space="preserve">11.9365568161011</t>
   </si>
   <si>
     <t xml:space="preserve">12.090313911438</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">12.1712408065796</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2521667480469</t>
+    <t xml:space="preserve">12.2521657943726</t>
   </si>
   <si>
     <t xml:space="preserve">12.4221115112305</t>
@@ -4787,7 +4787,7 @@
     <t xml:space="preserve">12.4140186309814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6082391738892</t>
+    <t xml:space="preserve">12.6082401275635</t>
   </si>
   <si>
     <t xml:space="preserve">12.8914804458618</t>
@@ -4799,7 +4799,7 @@
     <t xml:space="preserve">12.745813369751</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5354061126709</t>
+    <t xml:space="preserve">12.5354070663452</t>
   </si>
   <si>
     <t xml:space="preserve">12.6163330078125</t>
@@ -4811,7 +4811,7 @@
     <t xml:space="preserve">13.1261644363403</t>
   </si>
   <si>
-    <t xml:space="preserve">12.842924118042</t>
+    <t xml:space="preserve">12.8429250717163</t>
   </si>
   <si>
     <t xml:space="preserve">12.9562215805054</t>
@@ -4820,13 +4820,13 @@
     <t xml:space="preserve">12.9804992675781</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0290546417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0937957763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1989974975586</t>
+    <t xml:space="preserve">13.0290555953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0937948226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1989984512329</t>
   </si>
   <si>
     <t xml:space="preserve">12.9076652526855</t>
@@ -4841,40 +4841,40 @@
     <t xml:space="preserve">12.9238500595093</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0452394485474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0776100158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1747207641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1666288375854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9724073410034</t>
+    <t xml:space="preserve">13.0452404022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0776090621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1747217178345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1666278839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9724063873291</t>
   </si>
   <si>
     <t xml:space="preserve">12.9319429397583</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6810722351074</t>
+    <t xml:space="preserve">12.6810731887817</t>
   </si>
   <si>
     <t xml:space="preserve">12.5677766799927</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4787588119507</t>
+    <t xml:space="preserve">12.478759765625</t>
   </si>
   <si>
     <t xml:space="preserve">12.75390625</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7296276092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5839614868164</t>
+    <t xml:space="preserve">12.7296285629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5839624404907</t>
   </si>
   <si>
     <t xml:space="preserve">12.5758695602417</t>
@@ -4883,7 +4883,7 @@
     <t xml:space="preserve">12.6729803085327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7943706512451</t>
+    <t xml:space="preserve">12.7943687438965</t>
   </si>
   <si>
     <t xml:space="preserve">12.8752946853638</t>
@@ -4892,7 +4892,7 @@
     <t xml:space="preserve">13.0209627151489</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0371475219727</t>
+    <t xml:space="preserve">13.0371465682983</t>
   </si>
   <si>
     <t xml:space="preserve">13.2475538253784</t>
@@ -4904,19 +4904,19 @@
     <t xml:space="preserve">13.1504430770874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3365726470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5874423980713</t>
+    <t xml:space="preserve">13.3365716934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5874433517456</t>
   </si>
   <si>
     <t xml:space="preserve">13.4903316497803</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2880172729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3203859329224</t>
+    <t xml:space="preserve">13.2880163192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3203868865967</t>
   </si>
   <si>
     <t xml:space="preserve">13.3042020797729</t>
@@ -4928,28 +4928,28 @@
     <t xml:space="preserve">12.7862777709961</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2036113739014</t>
+    <t xml:space="preserve">12.2036104202271</t>
   </si>
   <si>
     <t xml:space="preserve">12.4544811248779</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8995723724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0533313751221</t>
+    <t xml:space="preserve">12.8995733261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0533304214478</t>
   </si>
   <si>
     <t xml:space="preserve">13.2151832580566</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5388851165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.417498588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4579591751099</t>
+    <t xml:space="preserve">13.5388860702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4174976348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4579601287842</t>
   </si>
   <si>
     <t xml:space="preserve">13.595534324646</t>
@@ -4970,7 +4970,7 @@
     <t xml:space="preserve">13.7573862075806</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9597015380859</t>
+    <t xml:space="preserve">13.9597005844116</t>
   </si>
   <si>
     <t xml:space="preserve">13.881422996521</t>
@@ -6081,6 +6081,9 @@
   </si>
   <si>
     <t xml:space="preserve">24.8199996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1800003051758</t>
   </si>
 </sst>
 </file>
@@ -71757,7 +71760,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6909837963</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>405557</v>
@@ -71778,6 +71781,32 @@
         <v>2022</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6915046296</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>246450</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>25.1800003051758</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>24.6200008392334</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>24.7600002288818</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>25.1800003051758</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>2023</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IF.MI.xlsx
+++ b/data/IF.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2032" uniqueCount="2032">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2033" uniqueCount="2033">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,94 +38,94 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9798812866211</t>
+    <t xml:space="preserve">14.9798784255981</t>
   </si>
   <si>
     <t xml:space="preserve">IF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6498317718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5859498977661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8460083007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6703386306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6863069534302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7342176437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.494668006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1494398117065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1859130859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7980995178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9365072250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7395420074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.633864402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6551580429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1715211868286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1768455505371</t>
+    <t xml:space="preserve">14.6498327255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5859527587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8460092544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6703367233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6863098144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7342166900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4946670532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1494388580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1859159469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7981014251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.936505317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7395429611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6338624954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6551570892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1715202331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1768445968628</t>
   </si>
   <si>
     <t xml:space="preserve">14.8148574829102</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3312206268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2779874801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0118207931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4422225952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2399368286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8406867980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4299993515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4672651290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0794486999512</t>
+    <t xml:space="preserve">15.3312225341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2779865264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0118198394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4422235488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2399349212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8406858444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4300012588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.467264175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0794496536255</t>
   </si>
   <si>
     <t xml:space="preserve">13.1060647964478</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1592988967896</t>
+    <t xml:space="preserve">13.1592979431152</t>
   </si>
   <si>
     <t xml:space="preserve">13.8353633880615</t>
@@ -134,7 +134,7 @@
     <t xml:space="preserve">13.7448654174805</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6596927642822</t>
+    <t xml:space="preserve">13.6596937179565</t>
   </si>
   <si>
     <t xml:space="preserve">13.585165977478</t>
@@ -143,187 +143,187 @@
     <t xml:space="preserve">13.6437215805054</t>
   </si>
   <si>
-    <t xml:space="preserve">14.692421913147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2559080123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0323276519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4741640090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3730201721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.319785118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7509775161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5486888885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2665538787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7501878738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8566560745239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4840221405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7874536514282</t>
+    <t xml:space="preserve">14.692419052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2559051513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0323257446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4741630554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3730182647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3197870254517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7509746551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5486917495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2665519714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7501888275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8566551208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4840211868286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7874526977539</t>
   </si>
   <si>
     <t xml:space="preserve">14.0110311508179</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4528694152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6391849517822</t>
+    <t xml:space="preserve">14.4528703689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6391887664795</t>
   </si>
   <si>
     <t xml:space="preserve">15.2300777435303</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4536600112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.320574760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1981372833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3418684005737</t>
+    <t xml:space="preserve">15.4536571502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3205757141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1981363296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3418655395508</t>
   </si>
   <si>
     <t xml:space="preserve">15.3637399673462</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6917943954468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.915958404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6261787414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0848932266235</t>
+    <t xml:space="preserve">15.6917924880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9159555435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6261796951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0848960876465</t>
   </si>
   <si>
     <t xml:space="preserve">15.593373298645</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8497924804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9263362884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0247526168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1231679916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8825960159302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5436086654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6857643127441</t>
+    <t xml:space="preserve">14.8497905731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9263334274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0247507095337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1231698989868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8825969696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5436115264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6857662200928</t>
   </si>
   <si>
     <t xml:space="preserve">14.5053386688232</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4123878479004</t>
+    <t xml:space="preserve">14.412389755249</t>
   </si>
   <si>
     <t xml:space="preserve">14.6420249938965</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2374296188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.133544921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.887508392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9203119277954</t>
+    <t xml:space="preserve">14.2374267578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1335458755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8875074386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9203109741211</t>
   </si>
   <si>
     <t xml:space="preserve">13.9968557357788</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8547029495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6578722000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4391689300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1767301559448</t>
+    <t xml:space="preserve">13.8547039031982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6578674316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4391708374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1767272949219</t>
   </si>
   <si>
     <t xml:space="preserve">13.48291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0127048492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9853668212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6846523284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4768857955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2199125289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3566017150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1488351821899</t>
+    <t xml:space="preserve">13.0127029418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9853649139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6846532821655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4768867492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2199144363403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3566036224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1488332748413</t>
   </si>
   <si>
     <t xml:space="preserve">11.8809261322021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0285491943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0777568817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7551736831665</t>
+    <t xml:space="preserve">12.0285482406616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0777578353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7551717758179</t>
   </si>
   <si>
     <t xml:space="preserve">11.9738740921021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3128623962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8164300918579</t>
+    <t xml:space="preserve">12.3128604888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.816427230835</t>
   </si>
   <si>
     <t xml:space="preserve">13.2860774993896</t>
@@ -332,34 +332,34 @@
     <t xml:space="preserve">13.1220541000366</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9088230133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0072374343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.706521987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6299753189087</t>
+    <t xml:space="preserve">12.9088191986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0072345733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7065210342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6299772262573</t>
   </si>
   <si>
     <t xml:space="preserve">12.717456817627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5206251144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3401975631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1652374267578</t>
+    <t xml:space="preserve">12.5206260681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.34019947052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1652383804321</t>
   </si>
   <si>
     <t xml:space="preserve">11.9465370178223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6184854507446</t>
+    <t xml:space="preserve">11.6184844970703</t>
   </si>
   <si>
     <t xml:space="preserve">11.4763288497925</t>
@@ -371,262 +371,262 @@
     <t xml:space="preserve">11.0498638153076</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6403551101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0449504852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9902772903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3620700836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5364742279053</t>
+    <t xml:space="preserve">11.6403560638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0449523925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9902763366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3620681762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5364723205566</t>
   </si>
   <si>
     <t xml:space="preserve">9.68844890594482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77046298980713</t>
+    <t xml:space="preserve">9.77046394348145</t>
   </si>
   <si>
     <t xml:space="preserve">9.8251371383667</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92355251312256</t>
+    <t xml:space="preserve">9.92355346679688</t>
   </si>
   <si>
     <t xml:space="preserve">9.93448829650879</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95089244842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45881462097168</t>
+    <t xml:space="preserve">9.95089149475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45881271362305</t>
   </si>
   <si>
     <t xml:space="preserve">9.11982727050781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10889148712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26198387145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2947883605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3062801361084</t>
+    <t xml:space="preserve">9.10889339447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26198291778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29478645324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3062810897827</t>
   </si>
   <si>
     <t xml:space="preserve">10.7382144927979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9350452423096</t>
+    <t xml:space="preserve">10.9350442886353</t>
   </si>
   <si>
     <t xml:space="preserve">10.7819538116455</t>
   </si>
   <si>
-    <t xml:space="preserve">10.962381362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.716344833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9459819793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6890058517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5140438079834</t>
+    <t xml:space="preserve">10.9623823165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7163429260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9459791183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6890068054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5140466690063</t>
   </si>
   <si>
     <t xml:space="preserve">10.3390846252441</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0930452346802</t>
+    <t xml:space="preserve">10.0930461883545</t>
   </si>
   <si>
     <t xml:space="preserve">10.4703044891357</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1537466049194</t>
+    <t xml:space="preserve">11.1537446975708</t>
   </si>
   <si>
     <t xml:space="preserve">10.8694343566895</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0225238800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5796556472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6069927215576</t>
+    <t xml:space="preserve">11.0225248336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5796566009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6069936752319</t>
   </si>
   <si>
     <t xml:space="preserve">11.0443954467773</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1756162643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8530321121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.093602180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0006551742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9022407531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8366298675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7436809539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4593696594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4484357833862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5085763931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4976425170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5632543563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4429683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4375009536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5851249694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6671380996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6507339477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8803691864014</t>
+    <t xml:space="preserve">11.1756153106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8530340194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0936031341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0006542205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9022397994995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8366279602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7436819076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4593706130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4484367370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5085792541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4976444244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.56325340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.442967414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5851240158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6671361923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6507349014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8803701400757</t>
   </si>
   <si>
     <t xml:space="preserve">11.2630968093872</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7223682403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7989120483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3833818435669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1318731307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2084188461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1100034713745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1264085769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0170564651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.202953338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4817962646484</t>
+    <t xml:space="preserve">11.7223701477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7989130020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3833808898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1318759918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2084217071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1100082397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.126407623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0170574188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2029514312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4817981719971</t>
   </si>
   <si>
     <t xml:space="preserve">11.4435253143311</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0990705490112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.956916809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9405126571655</t>
+    <t xml:space="preserve">11.0990695953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9569139480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9405136108398</t>
   </si>
   <si>
     <t xml:space="preserve">10.9733171463013</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1428108215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1920194625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.448992729187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8098487854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7885360717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0400400161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0673761367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1985998153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.280611038208</t>
+    <t xml:space="preserve">11.1428098678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1920185089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4489908218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8098478317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.788535118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0400409698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0673770904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1986026763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.280613899231</t>
   </si>
   <si>
     <t xml:space="preserve">13.4938449859619</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6797409057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.76722240448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1663475036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2428960800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3795824050903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4944009780884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4069194793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2264947891235</t>
+    <t xml:space="preserve">13.6797389984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7672214508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1663484573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2428951263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3795833587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.494402885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4069232940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2264957427979</t>
   </si>
   <si>
     <t xml:space="preserve">14.0077924728394</t>
@@ -635,49 +635,49 @@
     <t xml:space="preserve">14.0241937637329</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8109617233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8929738998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.843768119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6906785964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3954296112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3844938278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9908323287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.029107093811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9361600875854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8869504928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4222116470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4878234863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5479621887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1379013061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5753030776978</t>
+    <t xml:space="preserve">13.8109636306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8929767608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8437671661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6906776428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3954315185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3844947814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9908332824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0291090011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9361581802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8869495391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.422212600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4878206253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5479650497437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1379022598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5753021240234</t>
   </si>
   <si>
     <t xml:space="preserve">12.794002532959</t>
@@ -686,133 +686,133 @@
     <t xml:space="preserve">12.7775993347168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6463785171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4610414505005</t>
+    <t xml:space="preserve">12.6463794708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4610404968262</t>
   </si>
   <si>
     <t xml:space="preserve">13.5867919921875</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5102481842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6688060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2210283279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9804563522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6961431503296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7781572341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0734024047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2155590057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4889335632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8333864212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7513723373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7076330184937</t>
+    <t xml:space="preserve">13.5102453231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6688070297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2210264205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9804544448853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6961421966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7781581878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0734004974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2155570983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4889354705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8333873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7513742446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7076358795166</t>
   </si>
   <si>
     <t xml:space="preserve">14.5982837677002</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1226081848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2702360153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5600118637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4342613220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3139734268188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3631820678711</t>
+    <t xml:space="preserve">14.1226110458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2702350616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5600109100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4342575073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3139715194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3631839752197</t>
   </si>
   <si>
     <t xml:space="preserve">14.3467779159546</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1171417236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9421815872192</t>
+    <t xml:space="preserve">14.1171455383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9421834945679</t>
   </si>
   <si>
     <t xml:space="preserve">13.8328323364258</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5485200881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8273658752441</t>
+    <t xml:space="preserve">13.5485210418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8273639678955</t>
   </si>
   <si>
     <t xml:space="preserve">13.7234830856323</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7016115188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3249092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0515308380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9531164169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1608800888062</t>
+    <t xml:space="preserve">13.7016124725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3249082565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0515336990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9531192779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1608819961548</t>
   </si>
   <si>
     <t xml:space="preserve">14.6529598236084</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0903644561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0794258117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.265323638916</t>
+    <t xml:space="preserve">15.0903606414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0794267654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2653226852417</t>
   </si>
   <si>
     <t xml:space="preserve">15.713659286499</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1401252746582</t>
+    <t xml:space="preserve">16.1401271820068</t>
   </si>
   <si>
     <t xml:space="preserve">16.2658805847168</t>
   </si>
   <si>
-    <t xml:space="preserve">15.833945274353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8120727539062</t>
+    <t xml:space="preserve">15.8339443206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8120737075806</t>
   </si>
   <si>
     <t xml:space="preserve">15.3090629577637</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">16.0745143890381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1291904449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5119190216064</t>
+    <t xml:space="preserve">16.1291923522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5119152069092</t>
   </si>
   <si>
     <t xml:space="preserve">16.643138885498</t>
@@ -833,13 +833,13 @@
     <t xml:space="preserve">16.7470226287842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2385444641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3424263000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8399677276611</t>
+    <t xml:space="preserve">16.2385406494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3424224853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8399658203125</t>
   </si>
   <si>
     <t xml:space="preserve">17.0532035827637</t>
@@ -851,97 +851,97 @@
     <t xml:space="preserve">18.6114463806152</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8629531860352</t>
+    <t xml:space="preserve">18.8629512786865</t>
   </si>
   <si>
     <t xml:space="preserve">19.0324459075928</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9345874786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5354537963867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8471050262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7377586364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6830825805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6557445526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3440990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5737323760986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6448097229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8361721038818</t>
+    <t xml:space="preserve">19.9345836639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.535457611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8471069335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.737756729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.683084487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6557426452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3440952301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.57373046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6448040008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8361701965332</t>
   </si>
   <si>
     <t xml:space="preserve">19.819766998291</t>
   </si>
   <si>
-    <t xml:space="preserve">19.617467880249</t>
+    <t xml:space="preserve">19.6174697875977</t>
   </si>
   <si>
     <t xml:space="preserve">20.0931453704834</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3829250335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2188949584961</t>
+    <t xml:space="preserve">20.3829212188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2188987731934</t>
   </si>
   <si>
     <t xml:space="preserve">20.1587543487549</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0111331939697</t>
+    <t xml:space="preserve">20.0111312866211</t>
   </si>
   <si>
     <t xml:space="preserve">19.9509906768799</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2845039367676</t>
+    <t xml:space="preserve">20.2845077514648</t>
   </si>
   <si>
     <t xml:space="preserve">20.5469512939453</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2899780273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1975860595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0718307495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9242095947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1593112945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6513862609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8300476074219</t>
+    <t xml:space="preserve">20.2899742126465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1975879669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.071834564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9242057800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1593132019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.651388168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8300495147705</t>
   </si>
   <si>
     <t xml:space="preserve">21.4950618743896</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3164024353027</t>
+    <t xml:space="preserve">21.3164005279541</t>
   </si>
   <si>
     <t xml:space="preserve">20.4342670440674</t>
@@ -953,31 +953,31 @@
     <t xml:space="preserve">20.0881118774414</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8145370483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6414585113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6972904205322</t>
+    <t xml:space="preserve">19.8145389556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6414623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6972942352295</t>
   </si>
   <si>
     <t xml:space="preserve">19.5967960357666</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3685092926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6929492950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6029968261719</t>
+    <t xml:space="preserve">18.3685073852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6929473876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6029987335205</t>
   </si>
   <si>
     <t xml:space="preserve">19.0049839019775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4962997436523</t>
+    <t xml:space="preserve">19.4962959289551</t>
   </si>
   <si>
     <t xml:space="preserve">19.4851341247559</t>
@@ -986,13 +986,13 @@
     <t xml:space="preserve">19.5409660339355</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4293022155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2953071594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3288040161133</t>
+    <t xml:space="preserve">19.4293041229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2953090667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3288059234619</t>
   </si>
   <si>
     <t xml:space="preserve">18.8430709838867</t>
@@ -1004,37 +1004,37 @@
     <t xml:space="preserve">18.9268226623535</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2729740142822</t>
+    <t xml:space="preserve">19.2729721069336</t>
   </si>
   <si>
     <t xml:space="preserve">19.0943145751953</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2059745788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7531280517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7028751373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3734703063965</t>
+    <t xml:space="preserve">19.2059803009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7531223297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7028789520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3734722137451</t>
   </si>
   <si>
     <t xml:space="preserve">19.5632991790771</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5186309814453</t>
+    <t xml:space="preserve">19.5186290740967</t>
   </si>
   <si>
     <t xml:space="preserve">19.708459854126</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4572162628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1780586242676</t>
+    <t xml:space="preserve">19.457218170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1780605316162</t>
   </si>
   <si>
     <t xml:space="preserve">19.0831489562988</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">19.0384826660156</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5018863677979</t>
+    <t xml:space="preserve">19.5018825531006</t>
   </si>
   <si>
     <t xml:space="preserve">19.6749610900879</t>
@@ -1055,19 +1055,19 @@
     <t xml:space="preserve">19.8592014312744</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9262027740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9987812042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.920618057251</t>
+    <t xml:space="preserve">19.9262008666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9987831115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9206161499023</t>
   </si>
   <si>
     <t xml:space="preserve">20.0992794036865</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2332763671875</t>
+    <t xml:space="preserve">20.2332744598389</t>
   </si>
   <si>
     <t xml:space="preserve">20.2667713165283</t>
@@ -1076,67 +1076,67 @@
     <t xml:space="preserve">20.5180130004883</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7022571563721</t>
+    <t xml:space="preserve">20.7022590637207</t>
   </si>
   <si>
     <t xml:space="preserve">20.5905933380127</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5682621002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6017608642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7860012054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0204963684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7134189605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3833961486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8021335601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5508918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8635482788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6625537872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1650371551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.360445022583</t>
+    <t xml:space="preserve">20.5682601928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6017627716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.786003112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0204944610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7134208679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3833980560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8021297454834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5508899688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.86354637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6625556945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1650409698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3604469299316</t>
   </si>
   <si>
     <t xml:space="preserve">22.6284351348877</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8517608642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.103006362915</t>
+    <t xml:space="preserve">22.8517627716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1030044555664</t>
   </si>
   <si>
     <t xml:space="preserve">22.7233505249023</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9410934448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8908405303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4106941223145</t>
+    <t xml:space="preserve">22.9410953521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8908443450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4106922149658</t>
   </si>
   <si>
     <t xml:space="preserve">22.4330291748047</t>
@@ -1145,10 +1145,10 @@
     <t xml:space="preserve">22.9969253540039</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1811656951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1364994049072</t>
+    <t xml:space="preserve">23.1811695098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1365032196045</t>
   </si>
   <si>
     <t xml:space="preserve">22.706600189209</t>
@@ -1157,136 +1157,136 @@
     <t xml:space="preserve">22.8796768188477</t>
   </si>
   <si>
-    <t xml:space="preserve">22.689847946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6731014251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8182621002197</t>
+    <t xml:space="preserve">22.6898555755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6731071472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8182640075684</t>
   </si>
   <si>
     <t xml:space="preserve">22.6451873779297</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5000228881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0031242370605</t>
+    <t xml:space="preserve">22.5000247955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0031261444092</t>
   </si>
   <si>
     <t xml:space="preserve">22.567024230957</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7512683868408</t>
+    <t xml:space="preserve">22.7512664794922</t>
   </si>
   <si>
     <t xml:space="preserve">23.0025081634521</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3542442321777</t>
+    <t xml:space="preserve">23.3542461395264</t>
   </si>
   <si>
     <t xml:space="preserve">23.1700019836426</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9243450164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.549654006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5217380523682</t>
+    <t xml:space="preserve">22.9243469238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5496501922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5217418670654</t>
   </si>
   <si>
     <t xml:space="preserve">23.3151607513428</t>
   </si>
   <si>
-    <t xml:space="preserve">23.510570526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8623142242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4708728790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4764537811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9007740020752</t>
+    <t xml:space="preserve">23.5105724334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8623123168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4708709716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4764518737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9007701873779</t>
   </si>
   <si>
     <t xml:space="preserve">25.2190093994141</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1129302978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3083400726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8728580474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3195095062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5316619873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8275699615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4193878173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7152862548828</t>
+    <t xml:space="preserve">25.1129341125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3083419799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8728542327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3195037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5316677093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8275680541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4193840026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7152881622314</t>
   </si>
   <si>
     <t xml:space="preserve">26.8492870330811</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6042461395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4138050079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1284427642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4410972595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5025100708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2791805267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7041244506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6321582794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2525081634521</t>
+    <t xml:space="preserve">25.6042518615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4137992858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1284408569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4410934448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5025119781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2791900634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7041263580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6321640014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2525062561035</t>
   </si>
   <si>
     <t xml:space="preserve">25.9057369232178</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3585872650146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2128086090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3021392822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3356399536133</t>
+    <t xml:space="preserve">25.3585891723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2128067016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3021411895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3356342315674</t>
   </si>
   <si>
     <t xml:space="preserve">26.5031356811523</t>
@@ -1298,52 +1298,52 @@
     <t xml:space="preserve">26.2407245635986</t>
   </si>
   <si>
-    <t xml:space="preserve">26.274227142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1346416473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1793117523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.777322769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5260810852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0403518676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6886100769043</t>
+    <t xml:space="preserve">26.2742214202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1346435546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1793079376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7773284912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5260848999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0403499603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6886138916016</t>
   </si>
   <si>
     <t xml:space="preserve">23.415657043457</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7456798553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8467979431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7295513153076</t>
+    <t xml:space="preserve">22.7456855773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8468017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.729549407959</t>
   </si>
   <si>
     <t xml:space="preserve">22.4665260314941</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6234741210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6346378326416</t>
+    <t xml:space="preserve">21.6234703063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.634635925293</t>
   </si>
   <si>
     <t xml:space="preserve">21.2438201904297</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9255847930908</t>
+    <t xml:space="preserve">20.9255809783936</t>
   </si>
   <si>
     <t xml:space="preserve">21.5843906402588</t>
@@ -1361,25 +1361,25 @@
     <t xml:space="preserve">21.165657043457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5124340057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4845123291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6855049133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7748355865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.417516708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.898286819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3728523254395</t>
+    <t xml:space="preserve">20.51243019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4845142364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6855068206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7748336791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4175148010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8982849121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3728542327881</t>
   </si>
   <si>
     <t xml:space="preserve">20.8250846862793</t>
@@ -1388,22 +1388,22 @@
     <t xml:space="preserve">21.3889808654785</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1718635559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0936946868896</t>
+    <t xml:space="preserve">20.1718616485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.093692779541</t>
   </si>
   <si>
     <t xml:space="preserve">20.0434474945068</t>
   </si>
   <si>
-    <t xml:space="preserve">20.668758392334</t>
+    <t xml:space="preserve">20.6687564849854</t>
   </si>
   <si>
     <t xml:space="preserve">21.6123085021973</t>
   </si>
   <si>
-    <t xml:space="preserve">22.76243019104</t>
+    <t xml:space="preserve">22.7624320983887</t>
   </si>
   <si>
     <t xml:space="preserve">21.9361305236816</t>
@@ -1412,16 +1412,16 @@
     <t xml:space="preserve">22.2208671569824</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6116886138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6228580474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3213672637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3883609771729</t>
+    <t xml:space="preserve">22.6116905212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6228504180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3213634490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3883628845215</t>
   </si>
   <si>
     <t xml:space="preserve">21.2717361450195</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">22.0422096252441</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7630519866943</t>
+    <t xml:space="preserve">21.763053894043</t>
   </si>
   <si>
     <t xml:space="preserve">21.9417114257812</t>
@@ -1442,10 +1442,10 @@
     <t xml:space="preserve">21.8523807525635</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6848850250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4392280578613</t>
+    <t xml:space="preserve">21.684886932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4392318725586</t>
   </si>
   <si>
     <t xml:space="preserve">21.4168968200684</t>
@@ -1454,46 +1454,46 @@
     <t xml:space="preserve">21.2047386169434</t>
   </si>
   <si>
-    <t xml:space="preserve">21.841215133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3722324371338</t>
+    <t xml:space="preserve">21.8412189483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3722286224365</t>
   </si>
   <si>
     <t xml:space="preserve">21.0149116516113</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1997756958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7419567108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2444381713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7034931182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4913368225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7754535675049</t>
+    <t xml:space="preserve">20.1997737884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7419586181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2444400787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7034969329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4913349151611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7754573822021</t>
   </si>
   <si>
     <t xml:space="preserve">20.1439437866211</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9094543457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.344934463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3337688446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3002700805664</t>
+    <t xml:space="preserve">19.9094524383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3449363708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3337707519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.300271987915</t>
   </si>
   <si>
     <t xml:space="preserve">20.2556056976318</t>
@@ -1502,16 +1502,16 @@
     <t xml:space="preserve">20.3672676086426</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0322780609131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7977886199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6861228942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0496482849121</t>
+    <t xml:space="preserve">20.0322799682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7977905273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6861248016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0496501922607</t>
   </si>
   <si>
     <t xml:space="preserve">18.4020042419434</t>
@@ -1520,43 +1520,43 @@
     <t xml:space="preserve">18.1005153656006</t>
   </si>
   <si>
-    <t xml:space="preserve">18.424337387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1786842346191</t>
+    <t xml:space="preserve">18.4243392944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1786804199219</t>
   </si>
   <si>
     <t xml:space="preserve">18.1675128936768</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1054801940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0273170471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9330234527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4640407562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6315364837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5025005340576</t>
+    <t xml:space="preserve">19.1054840087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0273189544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9330196380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4640426635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.631534576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5025043487549</t>
   </si>
   <si>
     <t xml:space="preserve">18.3350067138672</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0781879425049</t>
+    <t xml:space="preserve">18.0781841278076</t>
   </si>
   <si>
     <t xml:space="preserve">17.441707611084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5260734558105</t>
+    <t xml:space="preserve">16.5260715484619</t>
   </si>
   <si>
     <t xml:space="preserve">17.7990264892578</t>
@@ -1565,52 +1565,52 @@
     <t xml:space="preserve">17.095552444458</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8213596343994</t>
+    <t xml:space="preserve">17.821361541748</t>
   </si>
   <si>
     <t xml:space="preserve">18.2010116577148</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3461723327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4801712036133</t>
+    <t xml:space="preserve">18.3461742401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4801692962646</t>
   </si>
   <si>
     <t xml:space="preserve">19.1836452484131</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7816600799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6364994049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8598251342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.748161315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4152755737305</t>
+    <t xml:space="preserve">18.7816581726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6364974975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8598213195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7481594085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4152717590332</t>
   </si>
   <si>
     <t xml:space="preserve">18.4267883300781</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2194900512695</t>
+    <t xml:space="preserve">18.2194919586182</t>
   </si>
   <si>
     <t xml:space="preserve">18.1734237670898</t>
   </si>
   <si>
-    <t xml:space="preserve">18.242525100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8298778533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0141429901123</t>
+    <t xml:space="preserve">18.2425212860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8298759460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0141448974609</t>
   </si>
   <si>
     <t xml:space="preserve">19.2905464172363</t>
@@ -1619,10 +1619,10 @@
     <t xml:space="preserve">19.4517822265625</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6705989837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3941955566406</t>
+    <t xml:space="preserve">19.670597076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3941974639893</t>
   </si>
   <si>
     <t xml:space="preserve">19.0602111816406</t>
@@ -1634,28 +1634,28 @@
     <t xml:space="preserve">18.5074062347412</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7031917572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7722949981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0467395782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.447868347168</t>
+    <t xml:space="preserve">18.7031936645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7722911834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0467414855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4478664398193</t>
   </si>
   <si>
     <t xml:space="preserve">16.5725936889648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2616424560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3998413085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0658588409424</t>
+    <t xml:space="preserve">16.2616405487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3998432159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.065860748291</t>
   </si>
   <si>
     <t xml:space="preserve">15.7203559875488</t>
@@ -1664,103 +1664,103 @@
     <t xml:space="preserve">14.8565988540649</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4861078262329</t>
+    <t xml:space="preserve">13.4861068725586</t>
   </si>
   <si>
     <t xml:space="preserve">12.2653322219849</t>
   </si>
   <si>
-    <t xml:space="preserve">13.440037727356</t>
+    <t xml:space="preserve">13.4400415420532</t>
   </si>
   <si>
     <t xml:space="preserve">13.5436906814575</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6838474273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7414312362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2922801971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.418966293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1195297241211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9928426742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5571641921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3748559951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.800971031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7779417037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3057546615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9852418899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4113597869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9276561737061</t>
+    <t xml:space="preserve">14.6838483810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7414321899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2922792434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4189653396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1195287704468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.992844581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5571660995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3748550415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8009748458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7779378890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3057556152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9852409362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4113636016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9276580810547</t>
   </si>
   <si>
     <t xml:space="preserve">16.0888919830322</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8240060806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2021007537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7183980941772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8220481872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8450813293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8911533355713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8681163787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0293531417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.271203994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6167068481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7894554138184</t>
+    <t xml:space="preserve">15.8240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2021026611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7184009552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8220491409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8450841903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8911504745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8681144714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0293502807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2712049484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6167039871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.789454460144</t>
   </si>
   <si>
     <t xml:space="preserve">15.4900207519531</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1445169448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2251358032227</t>
+    <t xml:space="preserve">15.1445188522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2251377105713</t>
   </si>
   <si>
     <t xml:space="preserve">15.0639009475708</t>
@@ -1769,76 +1769,76 @@
     <t xml:space="preserve">15.8700723648071</t>
   </si>
   <si>
-    <t xml:space="preserve">16.123441696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5015392303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2827196121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5130567550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5706377029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4324359893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6262655258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7990169525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.935263633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7260026931763</t>
+    <t xml:space="preserve">16.1234436035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5015363693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2827205657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5130548477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5706386566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4324369430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6262626647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.799015045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9352617263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.726001739502</t>
   </si>
   <si>
     <t xml:space="preserve">13.0254392623901</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9908876419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9793701171875</t>
+    <t xml:space="preserve">12.9908866882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9793710708618</t>
   </si>
   <si>
     <t xml:space="preserve">12.6453847885132</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4150495529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9083137512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7816286087036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8852806091309</t>
+    <t xml:space="preserve">12.4150505065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9083127975464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7816295623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8852796554565</t>
   </si>
   <si>
     <t xml:space="preserve">11.8507289886475</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6223526000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1731977462769</t>
+    <t xml:space="preserve">12.622350692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1731986999512</t>
   </si>
   <si>
     <t xml:space="preserve">12.3459491729736</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2998838424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4611148834229</t>
+    <t xml:space="preserve">12.2998828887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4611167907715</t>
   </si>
   <si>
     <t xml:space="preserve">11.7470788955688</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">12.1501665115356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.564769744873</t>
+    <t xml:space="preserve">12.5647659301758</t>
   </si>
   <si>
     <t xml:space="preserve">13.0024042129517</t>
@@ -1862,103 +1862,103 @@
     <t xml:space="preserve">12.8757209777832</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7144861221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2212228775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9217882156372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0139207839966</t>
+    <t xml:space="preserve">12.7144870758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2212219238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9217872619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0139217376709</t>
   </si>
   <si>
     <t xml:space="preserve">12.6799373626709</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7029695510864</t>
+    <t xml:space="preserve">12.7029685974121</t>
   </si>
   <si>
     <t xml:space="preserve">12.8526878356934</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3824577331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7279586791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7049264907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5782413482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7394752502441</t>
+    <t xml:space="preserve">13.38245677948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7279596328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7049245834351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5782403945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7394762039185</t>
   </si>
   <si>
     <t xml:space="preserve">12.7490358352661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1712417602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3420352935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7566385269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0503168106079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4015760421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2345857620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81802272796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0771522521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74316692352295</t>
+    <t xml:space="preserve">11.1712436676025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3420362472534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7566394805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0503158569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4015769958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2345838546753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81802368164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0771512985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74316501617432</t>
   </si>
   <si>
     <t xml:space="preserve">9.39190483093262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82954120635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80650901794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9907751083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44373035430908</t>
+    <t xml:space="preserve">9.82953929901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80650806427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99077606201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4437313079834</t>
   </si>
   <si>
     <t xml:space="preserve">9.42069721221924</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0751953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31508922576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97534465789795</t>
+    <t xml:space="preserve">9.07519435882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31508827209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97534513473511</t>
   </si>
   <si>
     <t xml:space="preserve">7.82562828063965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0617208480835</t>
+    <t xml:space="preserve">8.06172180175781</t>
   </si>
   <si>
     <t xml:space="preserve">8.09051322937012</t>
@@ -1970,7 +1970,7 @@
     <t xml:space="preserve">8.6260404586792</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94851112365723</t>
+    <t xml:space="preserve">8.94850921630859</t>
   </si>
   <si>
     <t xml:space="preserve">9.21339416503906</t>
@@ -1979,28 +1979,28 @@
     <t xml:space="preserve">9.72589111328125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40918159484863</t>
+    <t xml:space="preserve">9.40917873382568</t>
   </si>
   <si>
     <t xml:space="preserve">8.68362426757812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77575874328613</t>
+    <t xml:space="preserve">8.77575969696045</t>
   </si>
   <si>
     <t xml:space="preserve">8.39570617675781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6893835067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80455017089844</t>
+    <t xml:space="preserve">8.68938446044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80455112457275</t>
   </si>
   <si>
     <t xml:space="preserve">8.91395950317383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12701988220215</t>
+    <t xml:space="preserve">9.12702083587646</t>
   </si>
   <si>
     <t xml:space="preserve">9.02912712097168</t>
@@ -2009,13 +2009,13 @@
     <t xml:space="preserve">9.00033569335938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15005207061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10974502563477</t>
+    <t xml:space="preserve">9.24218559265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15005397796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10974597930908</t>
   </si>
   <si>
     <t xml:space="preserve">10.3190031051636</t>
@@ -2024,25 +2024,25 @@
     <t xml:space="preserve">10.6011629104614</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3823461532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0387983322144</t>
+    <t xml:space="preserve">10.382345199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.038800239563</t>
   </si>
   <si>
     <t xml:space="preserve">10.7623977661133</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4802360534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4399280548096</t>
+    <t xml:space="preserve">10.4802379608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4399271011353</t>
   </si>
   <si>
     <t xml:space="preserve">10.0080509185791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.307487487793</t>
+    <t xml:space="preserve">10.3074865341187</t>
   </si>
   <si>
     <t xml:space="preserve">9.84105777740479</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">9.78923225402832</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1289758682251</t>
+    <t xml:space="preserve">10.1289768218994</t>
   </si>
   <si>
     <t xml:space="preserve">10.5666131973267</t>
@@ -2069,28 +2069,28 @@
     <t xml:space="preserve">9.87560749053955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34007930755615</t>
+    <t xml:space="preserve">9.34007835388184</t>
   </si>
   <si>
     <t xml:space="preserve">9.22491264343262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91971778869629</t>
+    <t xml:space="preserve">8.91971874237061</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969150543213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60300636291504</t>
+    <t xml:space="preserve">8.60300731658936</t>
   </si>
   <si>
     <t xml:space="preserve">8.89092636108398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89668560028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46676349639893</t>
+    <t xml:space="preserve">8.89668369293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46676540374756</t>
   </si>
   <si>
     <t xml:space="preserve">9.90439987182617</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">10.0483598709106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.111701965332</t>
+    <t xml:space="preserve">10.1117000579834</t>
   </si>
   <si>
     <t xml:space="preserve">10.0713930130005</t>
@@ -2111,40 +2111,40 @@
     <t xml:space="preserve">10.0426015853882</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54162311553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16156959533691</t>
+    <t xml:space="preserve">9.54162216186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16157054901123</t>
   </si>
   <si>
     <t xml:space="preserve">9.61648178100586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73740768432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96198463439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86985015869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50707149505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48979663848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78347396850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93319129943848</t>
+    <t xml:space="preserve">9.73740673065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9619836807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86984825134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50707244873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4897985458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78347301483154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93319225311279</t>
   </si>
   <si>
     <t xml:space="preserve">10.0253267288208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66254997253418</t>
+    <t xml:space="preserve">9.66254901885986</t>
   </si>
   <si>
     <t xml:space="preserve">9.5473804473877</t>
@@ -2156,34 +2156,34 @@
     <t xml:space="preserve">9.84681606292725</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58192920684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18460369110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5608549118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0349960327148</t>
+    <t xml:space="preserve">9.58193111419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18460464477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5608558654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0349979400635</t>
   </si>
   <si>
     <t xml:space="preserve">11.4534025192261</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8257398605347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3535528182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1865615844727</t>
+    <t xml:space="preserve">10.8257389068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.353551864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.186559677124</t>
   </si>
   <si>
     <t xml:space="preserve">10.1001853942871</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0598754882812</t>
+    <t xml:space="preserve">10.0598764419556</t>
   </si>
   <si>
     <t xml:space="preserve">9.62224006652832</t>
@@ -2192,19 +2192,19 @@
     <t xml:space="preserve">9.85257434844971</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4111356735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.503270149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5781307220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9293909072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.445686340332</t>
+    <t xml:space="preserve">10.4111366271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5032720565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5781297683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9293899536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4456844329834</t>
   </si>
   <si>
     <t xml:space="preserve">9.08671188354492</t>
@@ -2216,25 +2216,25 @@
     <t xml:space="preserve">8.78151893615723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6721076965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64907455444336</t>
+    <t xml:space="preserve">8.67210960388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64907646179199</t>
   </si>
   <si>
     <t xml:space="preserve">8.69514274597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49935722351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54542446136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52239036560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41874122619629</t>
+    <t xml:space="preserve">8.49935817718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54542541503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5223913192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41873931884766</t>
   </si>
   <si>
     <t xml:space="preserve">8.47056579589844</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">8.63755798339844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56845760345459</t>
+    <t xml:space="preserve">8.56845855712891</t>
   </si>
   <si>
     <t xml:space="preserve">8.79879188537598</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">9.04064464569092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02336978912354</t>
+    <t xml:space="preserve">9.02337074279785</t>
   </si>
   <si>
     <t xml:space="preserve">9.00609493255615</t>
@@ -2261,25 +2261,25 @@
     <t xml:space="preserve">8.93699359893799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17308616638184</t>
+    <t xml:space="preserve">9.17308712005615</t>
   </si>
   <si>
     <t xml:space="preserve">9.21915340423584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24794578552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35735416412354</t>
+    <t xml:space="preserve">9.24794483184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35735607147217</t>
   </si>
   <si>
     <t xml:space="preserve">9.76981639862061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46200942993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19114017486572</t>
+    <t xml:space="preserve">9.46201038360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19113922119141</t>
   </si>
   <si>
     <t xml:space="preserve">9.25885581970215</t>
@@ -2291,121 +2291,121 @@
     <t xml:space="preserve">8.61246013641357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31696510314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11381053924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87987804412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48588418960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92297077178955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9722204208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91681480407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68287992477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49819707870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.528977394104</t>
+    <t xml:space="preserve">8.3169641494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11381149291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87987661361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4858832359314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92297172546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97221946716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91681385040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68288135528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49819660186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52897644042969</t>
   </si>
   <si>
     <t xml:space="preserve">7.44894695281982</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20270013809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35044717788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22732591629028</t>
+    <t xml:space="preserve">7.2027006149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35044860839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22732543945312</t>
   </si>
   <si>
     <t xml:space="preserve">7.17807626724243</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14113903045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01801490783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96261119842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29504251480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9749231338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89489269256592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93798589706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15960788726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91336107254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94414234161377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90720558166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06110858917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33813667297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64594411849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46741485595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33198118209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19038820266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39354085922241</t>
+    <t xml:space="preserve">7.14114046096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01801586151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96261072158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29504299163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97492122650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8948917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93798685073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15960645675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9133620262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94414281845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90720510482788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06110906600952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33813619613647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6459436416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46741676330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33197927474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19038772583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39354228973389</t>
   </si>
   <si>
     <t xml:space="preserve">7.4243221282959</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30735540390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60900640487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78753423690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28618431091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23693466186523</t>
+    <t xml:space="preserve">7.3073558807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60900735855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78753471374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28618335723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23693561553955</t>
   </si>
   <si>
     <t xml:space="preserve">8.28002738952637</t>
@@ -2417,22 +2417,22 @@
     <t xml:space="preserve">8.16921615600586</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16306018829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08303070068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14459133148193</t>
+    <t xml:space="preserve">8.16306114196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08303165435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14459037780762</t>
   </si>
   <si>
     <t xml:space="preserve">8.52627468109131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51396179199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50780487060547</t>
+    <t xml:space="preserve">8.51396083831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5078067779541</t>
   </si>
   <si>
     <t xml:space="preserve">8.3292760848999</t>
@@ -2441,52 +2441,52 @@
     <t xml:space="preserve">8.21231079101562</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40314960479736</t>
+    <t xml:space="preserve">8.40315055847168</t>
   </si>
   <si>
     <t xml:space="preserve">8.40930652618408</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2923412322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19384288787842</t>
+    <t xml:space="preserve">8.29234027862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1938419342041</t>
   </si>
   <si>
     <t xml:space="preserve">8.24924659729004</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98453283309937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89834594726562</t>
+    <t xml:space="preserve">7.98453187942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8983473777771</t>
   </si>
   <si>
     <t xml:space="preserve">8.13228034973145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59399223327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48933792114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45855522155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68633270263672</t>
+    <t xml:space="preserve">8.59399127960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48933696746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45855617523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68633365631104</t>
   </si>
   <si>
     <t xml:space="preserve">8.07687473297119</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71981763839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49203872680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8675651550293</t>
+    <t xml:space="preserve">7.71981716156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4920392036438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86756610870361</t>
   </si>
   <si>
     <t xml:space="preserve">7.93528366088867</t>
@@ -2495,22 +2495,22 @@
     <t xml:space="preserve">8.02762508392334</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96606349945068</t>
+    <t xml:space="preserve">7.96606302261353</t>
   </si>
   <si>
     <t xml:space="preserve">7.88603401184082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84294128417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15074729919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34774398803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58783531188965</t>
+    <t xml:space="preserve">7.84294080734253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15074920654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34774494171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58783626556396</t>
   </si>
   <si>
     <t xml:space="preserve">8.69248962402344</t>
@@ -2519,37 +2519,37 @@
     <t xml:space="preserve">8.77867603302002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0002965927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9879846572876</t>
+    <t xml:space="preserve">9.00029754638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98798561096191</t>
   </si>
   <si>
     <t xml:space="preserve">9.04954719543457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09879589080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12342071533203</t>
+    <t xml:space="preserve">9.09879493713379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12341976165771</t>
   </si>
   <si>
     <t xml:space="preserve">9.22807598114014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43738460540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44354057312012</t>
+    <t xml:space="preserve">9.4373836517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44354152679443</t>
   </si>
   <si>
     <t xml:space="preserve">9.26501274108887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41891479492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.431227684021</t>
+    <t xml:space="preserve">9.41891574859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43122863769531</t>
   </si>
   <si>
     <t xml:space="preserve">9.20960712432861</t>
@@ -2558,55 +2558,55 @@
     <t xml:space="preserve">9.11726474761963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20345020294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42507266998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24038791656494</t>
+    <t xml:space="preserve">9.20345115661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42507171630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24038887023926</t>
   </si>
   <si>
     <t xml:space="preserve">9.06185913085938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85870742797852</t>
+    <t xml:space="preserve">8.85870552062988</t>
   </si>
   <si>
     <t xml:space="preserve">8.88333129882812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9818286895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66170787811279</t>
+    <t xml:space="preserve">8.98182964324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66170978546143</t>
   </si>
   <si>
     <t xml:space="preserve">8.92026805877686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06801509857178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3204174041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27116870880127</t>
+    <t xml:space="preserve">9.06801700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32041835784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27116966247559</t>
   </si>
   <si>
     <t xml:space="preserve">9.2957935333252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40044689178467</t>
+    <t xml:space="preserve">9.40044784545898</t>
   </si>
   <si>
     <t xml:space="preserve">9.47432231903076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51741409301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46816539764404</t>
+    <t xml:space="preserve">9.51741504669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46816444396973</t>
   </si>
   <si>
     <t xml:space="preserve">9.3019495010376</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">9.40660381317139</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50510215759277</t>
+    <t xml:space="preserve">9.50510311126709</t>
   </si>
   <si>
     <t xml:space="preserve">9.73288059234619</t>
@@ -2624,25 +2624,25 @@
     <t xml:space="preserve">8.99414157867432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39429187774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70209980010986</t>
+    <t xml:space="preserve">9.39429092407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70209884643555</t>
   </si>
   <si>
     <t xml:space="preserve">9.745192527771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16035747528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96335983276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89564323425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79714393615723</t>
+    <t xml:space="preserve">9.16035652160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96336078643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89564228057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79714488983154</t>
   </si>
   <si>
     <t xml:space="preserve">8.74789619445801</t>
@@ -2651,28 +2651,28 @@
     <t xml:space="preserve">8.62477207183838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64323997497559</t>
+    <t xml:space="preserve">8.6432409286499</t>
   </si>
   <si>
     <t xml:space="preserve">8.5447416305542</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60630321502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49549388885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34158897399902</t>
+    <t xml:space="preserve">8.60630226135254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49549293518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34158992767334</t>
   </si>
   <si>
     <t xml:space="preserve">8.4216194152832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36005687713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1999979019165</t>
+    <t xml:space="preserve">8.36005783081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19999694824219</t>
   </si>
   <si>
     <t xml:space="preserve">8.15690422058105</t>
@@ -2684,22 +2684,22 @@
     <t xml:space="preserve">8.44008731842041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44624328613281</t>
+    <t xml:space="preserve">8.44624423980713</t>
   </si>
   <si>
     <t xml:space="preserve">8.39083862304688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43393230438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80330181121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61861705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70480251312256</t>
+    <t xml:space="preserve">8.43393135070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80330085754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61861515045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70480155944824</t>
   </si>
   <si>
     <t xml:space="preserve">8.79098796844482</t>
@@ -2714,25 +2714,25 @@
     <t xml:space="preserve">8.82176876068115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65555381774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50164985656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76020812988281</t>
+    <t xml:space="preserve">8.65555286407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50164890289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7602071762085</t>
   </si>
   <si>
     <t xml:space="preserve">9.12957668304443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11110877990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05570220947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07417106628418</t>
+    <t xml:space="preserve">9.11110782623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05570316314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07417011260986</t>
   </si>
   <si>
     <t xml:space="preserve">8.87717533111572</t>
@@ -2741,25 +2741,25 @@
     <t xml:space="preserve">8.85255146026611</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27732467651367</t>
+    <t xml:space="preserve">9.27732563018799</t>
   </si>
   <si>
     <t xml:space="preserve">9.01876544952393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82792663574219</t>
+    <t xml:space="preserve">8.82792472839355</t>
   </si>
   <si>
     <t xml:space="preserve">9.16651439666748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23423194885254</t>
+    <t xml:space="preserve">9.23423099517822</t>
   </si>
   <si>
     <t xml:space="preserve">9.33273029327393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64669322967529</t>
+    <t xml:space="preserve">9.64669609069824</t>
   </si>
   <si>
     <t xml:space="preserve">9.64053726196289</t>
@@ -2768,16 +2768,16 @@
     <t xml:space="preserve">9.58513164520264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6528491973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52357196807861</t>
+    <t xml:space="preserve">9.65285015106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52357006072998</t>
   </si>
   <si>
     <t xml:space="preserve">9.65900611877441</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90179920196533</t>
+    <t xml:space="preserve">8.90180015563965</t>
   </si>
   <si>
     <t xml:space="preserve">9.09264087677002</t>
@@ -2786,7 +2786,7 @@
     <t xml:space="preserve">8.46471214294434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00300025939941</t>
+    <t xml:space="preserve">8.00300121307373</t>
   </si>
   <si>
     <t xml:space="preserve">7.52282094955444</t>
@@ -2795,19 +2795,19 @@
     <t xml:space="preserve">6.55014801025391</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29774522781372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27927827835083</t>
+    <t xml:space="preserve">6.2977466583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27927684783936</t>
   </si>
   <si>
     <t xml:space="preserve">5.39894771575928</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6513500213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34354209899902</t>
+    <t xml:space="preserve">5.65134906768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34354257583618</t>
   </si>
   <si>
     <t xml:space="preserve">5.18348217010498</t>
@@ -2819,22 +2819,22 @@
     <t xml:space="preserve">5.17732572555542</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47897815704346</t>
+    <t xml:space="preserve">5.47897672653198</t>
   </si>
   <si>
     <t xml:space="preserve">5.30352687835693</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55900764465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58670902252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6944432258606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62364768981934</t>
+    <t xml:space="preserve">5.55900716781616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58670997619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69444227218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62364673614502</t>
   </si>
   <si>
     <t xml:space="preserve">5.38971328735352</t>
@@ -2843,79 +2843,79 @@
     <t xml:space="preserve">5.50975799560547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48205518722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42665004730225</t>
+    <t xml:space="preserve">5.48205471038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42664957046509</t>
   </si>
   <si>
     <t xml:space="preserve">5.50360202789307</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5559287071228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68213081359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66058397293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68828678131104</t>
+    <t xml:space="preserve">5.55592918395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68213033676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66058349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68828725814819</t>
   </si>
   <si>
     <t xml:space="preserve">5.55285167694092</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43896245956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49129009246826</t>
+    <t xml:space="preserve">5.43896198272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4912896156311</t>
   </si>
   <si>
     <t xml:space="preserve">5.49744606018066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23273181915283</t>
+    <t xml:space="preserve">5.23273086547852</t>
   </si>
   <si>
     <t xml:space="preserve">5.12499809265137</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2512001991272</t>
+    <t xml:space="preserve">5.25119972229004</t>
   </si>
   <si>
     <t xml:space="preserve">5.53438234329224</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64519357681274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4943675994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29429292678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34969854354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3158392906189</t>
+    <t xml:space="preserve">5.64519453048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49436807632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29429244995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34969806671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31583976745605</t>
   </si>
   <si>
     <t xml:space="preserve">5.20810651779175</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29121494293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21734142303467</t>
+    <t xml:space="preserve">5.29121541976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21734046936035</t>
   </si>
   <si>
     <t xml:space="preserve">5.14654445648193</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06959342956543</t>
+    <t xml:space="preserve">5.06959247589111</t>
   </si>
   <si>
     <t xml:space="preserve">4.97417259216309</t>
@@ -2927,91 +2927,91 @@
     <t xml:space="preserve">4.92492341995239</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70945739746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58017873764038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48167991638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4939923286438</t>
+    <t xml:space="preserve">4.7094578742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58017826080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48168039321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49399280548096</t>
   </si>
   <si>
     <t xml:space="preserve">4.74023866653442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93107986450195</t>
+    <t xml:space="preserve">4.93107938766479</t>
   </si>
   <si>
     <t xml:space="preserve">5.07882785797119</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16809177398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10652923583984</t>
+    <t xml:space="preserve">5.16809225082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.106529712677</t>
   </si>
   <si>
     <t xml:space="preserve">5.14038896560669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45127391815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65750598907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95300102233887</t>
+    <t xml:space="preserve">5.45127439498901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65750551223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95300197601318</t>
   </si>
   <si>
     <t xml:space="preserve">6.37777614593506</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98378229141235</t>
+    <t xml:space="preserve">5.9837818145752</t>
   </si>
   <si>
     <t xml:space="preserve">5.79909706115723</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40202617645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36201095581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50668001174927</t>
+    <t xml:space="preserve">5.40202474594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36201000213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50667953491211</t>
   </si>
   <si>
     <t xml:space="preserve">5.59594440460205</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54053831100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45743131637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3189172744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26966857910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13731050491333</t>
+    <t xml:space="preserve">5.54053926467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45743083953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31891775131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2696681022644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13731145858765</t>
   </si>
   <si>
     <t xml:space="preserve">5.06035900115967</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11576414108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22965335845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.263512134552</t>
+    <t xml:space="preserve">5.11576509475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22965383529663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26351165771484</t>
   </si>
   <si>
     <t xml:space="preserve">5.24812173843384</t>
@@ -3020,100 +3020,100 @@
     <t xml:space="preserve">5.37432241439819</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47589921951294</t>
+    <t xml:space="preserve">5.47590017318726</t>
   </si>
   <si>
     <t xml:space="preserve">5.58363151550293</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52206993103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61133432388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59286546707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92837619781494</t>
+    <t xml:space="preserve">5.52207040786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61133527755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59286594390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9283766746521</t>
   </si>
   <si>
     <t xml:space="preserve">6.04226541519165</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09151554107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89759635925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7683162689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63288068771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50052404403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33738613128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3343071937561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52822589874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.53746128082275</t>
+    <t xml:space="preserve">6.09151458740234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89759540557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76831674575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63288164138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50052452087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33738565444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33430767059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52822637557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5374608039856</t>
   </si>
   <si>
     <t xml:space="preserve">5.41125965118408</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64827251434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62672567367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65442848205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.543616771698</t>
+    <t xml:space="preserve">5.64827156066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62672472000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65442800521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54361724853516</t>
   </si>
   <si>
     <t xml:space="preserve">5.51591444015503</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61441230773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46050977706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4728217124939</t>
+    <t xml:space="preserve">5.61441326141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46050882339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47282075881958</t>
   </si>
   <si>
     <t xml:space="preserve">5.51899290084839</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36816692352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3219952583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31276035308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42972755432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43280601501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39279174804688</t>
+    <t xml:space="preserve">5.36816644668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32199573516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3127613067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42972803115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43280696868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39279222488403</t>
   </si>
   <si>
     <t xml:space="preserve">5.42049407958984</t>
@@ -3122,31 +3122,31 @@
     <t xml:space="preserve">5.59902238845825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52514886856079</t>
+    <t xml:space="preserve">5.52514839172363</t>
   </si>
   <si>
     <t xml:space="preserve">5.43588399887085</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24196624755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13115453720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08190536499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17116975784302</t>
+    <t xml:space="preserve">5.24196577072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13115501403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08190488815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17116928100586</t>
   </si>
   <si>
     <t xml:space="preserve">5.04804611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06343793869019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96186065673828</t>
+    <t xml:space="preserve">5.06343698501587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96186017990112</t>
   </si>
   <si>
     <t xml:space="preserve">4.96493816375732</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">5.01418781280518</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06651496887207</t>
+    <t xml:space="preserve">5.06651449203491</t>
   </si>
   <si>
     <t xml:space="preserve">5.04496812820435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96801614761353</t>
+    <t xml:space="preserve">4.96801662445068</t>
   </si>
   <si>
     <t xml:space="preserve">4.82950305938721</t>
@@ -3179,127 +3179,127 @@
     <t xml:space="preserve">4.83258104324341</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82642459869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86336231231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95262670516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79872179031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75562906265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68483352661133</t>
+    <t xml:space="preserve">4.82642507553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86336183547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95262622833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79872274398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75562858581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68483304977417</t>
   </si>
   <si>
     <t xml:space="preserve">4.58325719833374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59249210357666</t>
+    <t xml:space="preserve">4.59249114990234</t>
   </si>
   <si>
     <t xml:space="preserve">4.29083919525146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1523265838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23851251602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36779117584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55247640609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66328716278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59557008743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56171035766602</t>
+    <t xml:space="preserve">4.15232610702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23851299285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36779165267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55247592926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6632866859436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5955696105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56170988082886</t>
   </si>
   <si>
     <t xml:space="preserve">4.89106464385986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90029954910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00495386123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98340702056885</t>
+    <t xml:space="preserve">4.90029859542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00495338439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98340749740601</t>
   </si>
   <si>
     <t xml:space="preserve">5.38663530349731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56208515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57747650146484</t>
+    <t xml:space="preserve">5.56208610534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57747602462769</t>
   </si>
   <si>
     <t xml:space="preserve">5.78370714187622</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71906709671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69136428833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.700599193573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62056827545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87912750244141</t>
+    <t xml:space="preserve">5.71906757354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69136333465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70059871673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62056875228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87912654876709</t>
   </si>
   <si>
     <t xml:space="preserve">5.99609375</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01456356048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03918790817261</t>
+    <t xml:space="preserve">6.01456260681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03918838500977</t>
   </si>
   <si>
     <t xml:space="preserve">5.91914176940918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89451789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83603429794312</t>
+    <t xml:space="preserve">5.89451837539673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83603382110596</t>
   </si>
   <si>
     <t xml:space="preserve">5.7652382850647</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81140947341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80833101272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74984788894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74677038192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77447271347046</t>
+    <t xml:space="preserve">5.81140899658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80833148956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74984884262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74677085876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77447319030762</t>
   </si>
   <si>
     <t xml:space="preserve">5.60517835617065</t>
@@ -3311,43 +3311,43 @@
     <t xml:space="preserve">5.7036771774292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6975212097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73445796966553</t>
+    <t xml:space="preserve">5.69752073287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73445653915405</t>
   </si>
   <si>
     <t xml:space="preserve">5.72214508056641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68520879745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45435285568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46358680725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37739992141724</t>
+    <t xml:space="preserve">5.68520832061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45435237884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46358728408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37740039825439</t>
   </si>
   <si>
     <t xml:space="preserve">5.28813695907593</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1096076965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20502805709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1557788848877</t>
+    <t xml:space="preserve">5.10960817337036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20502853393555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15577936172485</t>
   </si>
   <si>
     <t xml:space="preserve">5.44819688796997</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78062868118286</t>
+    <t xml:space="preserve">5.78062915802002</t>
   </si>
   <si>
     <t xml:space="preserve">5.95915746688843</t>
@@ -3356,25 +3356,25 @@
     <t xml:space="preserve">6.08843660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.433180809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35315084457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42702484130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34699535369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34083843231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26696586608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32237100601196</t>
+    <t xml:space="preserve">6.43318128585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35315132141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42702436447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34699487686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34083986282349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26696634292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3223705291748</t>
   </si>
   <si>
     <t xml:space="preserve">6.37162113189697</t>
@@ -3383,115 +3383,115 @@
     <t xml:space="preserve">6.56861686706543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47627449035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63633346557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50705432891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5255241394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45780515670776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86411237716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84564352035522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88873672485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06726455688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12267112731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03648471832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05495262145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8210186958313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85179948806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90104961395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99954748153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01186037063599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92567300796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96876621246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99339056015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80870580673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13498258590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0795783996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04264163970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00570344924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74098920822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91951704025269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10420179367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15345096588135</t>
+    <t xml:space="preserve">6.4762749671936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63633394241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50705480575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52552318572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45780563354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86411142349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84564304351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8887357711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06726503372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12267065048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0364842414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05495309829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82101821899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85179996490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90105009078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99954652786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01185989379883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92567348480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96876764297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99339199066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80870819091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13498306274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07957744598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04264068603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00570297241211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74098825454712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91951656341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10420227050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15345191955566</t>
   </si>
   <si>
     <t xml:space="preserve">7.11035823822021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08573436737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11651372909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16576337814331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57206916809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32582378387451</t>
+    <t xml:space="preserve">7.08573389053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11651420593262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16576433181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57207155227661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32582235336304</t>
   </si>
   <si>
     <t xml:space="preserve">7.72597360610962</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03378200531006</t>
+    <t xml:space="preserve">8.03378105163574</t>
   </si>
   <si>
     <t xml:space="preserve">8.05840587615967</t>
@@ -3500,28 +3500,28 @@
     <t xml:space="preserve">7.99684476852417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86140918731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79369115829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66441297531128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83062839508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91065788269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94759559631348</t>
+    <t xml:space="preserve">7.86140966415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79369211196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6644115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83062791824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91065835952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94759607315063</t>
   </si>
   <si>
     <t xml:space="preserve">8.01531314849854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9783763885498</t>
+    <t xml:space="preserve">7.97837591171265</t>
   </si>
   <si>
     <t xml:space="preserve">8.0953426361084</t>
@@ -3533,37 +3533,37 @@
     <t xml:space="preserve">8.58167839050293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47702503204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23077869415283</t>
+    <t xml:space="preserve">8.47702598571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23077774047852</t>
   </si>
   <si>
     <t xml:space="preserve">8.18152904510498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1014986038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89218997955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36621284484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83678340911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9537525177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53242969512939</t>
+    <t xml:space="preserve">8.10149955749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89218950271606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36621379852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83678436279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95375061035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53242874145508</t>
   </si>
   <si>
     <t xml:space="preserve">8.55089855194092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55705261230469</t>
+    <t xml:space="preserve">8.55705451965332</t>
   </si>
   <si>
     <t xml:space="preserve">8.63708400726318</t>
@@ -3572,88 +3572,88 @@
     <t xml:space="preserve">8.56936645507812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56321048736572</t>
+    <t xml:space="preserve">8.56321144104004</t>
   </si>
   <si>
     <t xml:space="preserve">8.6309289932251</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75405216217041</t>
+    <t xml:space="preserve">8.75405025482178</t>
   </si>
   <si>
     <t xml:space="preserve">9.01260948181152</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96951675415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92642402648926</t>
+    <t xml:space="preserve">8.96951580047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92642307281494</t>
   </si>
   <si>
     <t xml:space="preserve">8.93873596191406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00645446777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7663631439209</t>
+    <t xml:space="preserve">9.00645542144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76636409759521</t>
   </si>
   <si>
     <t xml:space="preserve">8.91411209106445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03723430633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02492141723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10495281219482</t>
+    <t xml:space="preserve">9.03723526000977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02492237091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10495185852051</t>
   </si>
   <si>
     <t xml:space="preserve">9.33888626098633</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56050682067871</t>
+    <t xml:space="preserve">9.56050777435303</t>
   </si>
   <si>
     <t xml:space="preserve">9.60360145568848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83137798309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90525341033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94218921661377</t>
+    <t xml:space="preserve">9.83137989044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90525245666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94219017028809</t>
   </si>
   <si>
     <t xml:space="preserve">9.7513484954834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2438411712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3054008483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5824298858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0530004501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4408378601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.083779335022</t>
+    <t xml:space="preserve">10.2438402175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3054027557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5824308395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.05299949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4408369064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0837812423706</t>
   </si>
   <si>
     <t xml:space="preserve">10.2930889129639</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1638107299805</t>
+    <t xml:space="preserve">10.1638097763062</t>
   </si>
   <si>
     <t xml:space="preserve">10.1453437805176</t>
@@ -3665,16 +3665,16 @@
     <t xml:space="preserve">10.1699676513672</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4777765274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4716186523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7151460647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.688817024231</t>
+    <t xml:space="preserve">10.4777746200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4716196060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.715145111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6888179779053</t>
   </si>
   <si>
     <t xml:space="preserve">10.5571813583374</t>
@@ -3683,31 +3683,31 @@
     <t xml:space="preserve">10.3860549926758</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4782018661499</t>
+    <t xml:space="preserve">10.4781999588013</t>
   </si>
   <si>
     <t xml:space="preserve">10.5703439712524</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5111093521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5242729187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6559085845947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7612180709839</t>
+    <t xml:space="preserve">10.5111103057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5242719650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.655909538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7612171173096</t>
   </si>
   <si>
     <t xml:space="preserve">10.9520883560181</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0179052352905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.037652015686</t>
+    <t xml:space="preserve">11.0179061889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0376510620117</t>
   </si>
   <si>
     <t xml:space="preserve">11.1232147216797</t>
@@ -3716,16 +3716,16 @@
     <t xml:space="preserve">11.0903062820435</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9257612228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1495418548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1297960281372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0705604553223</t>
+    <t xml:space="preserve">10.9257621765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.149543762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1297969818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0705595016479</t>
   </si>
   <si>
     <t xml:space="preserve">10.9849977493286</t>
@@ -3734,25 +3734,25 @@
     <t xml:space="preserve">10.7217264175415</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6032543182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3070726394653</t>
+    <t xml:space="preserve">10.6032552719116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3070735931396</t>
   </si>
   <si>
     <t xml:space="preserve">10.418963432312</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0438032150269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0043115615845</t>
+    <t xml:space="preserve">10.0438013076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0043125152588</t>
   </si>
   <si>
     <t xml:space="preserve">9.99114799499512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49093246459961</t>
+    <t xml:space="preserve">9.49093341827393</t>
   </si>
   <si>
     <t xml:space="preserve">9.61598682403564</t>
@@ -3761,7 +3761,7 @@
     <t xml:space="preserve">9.71471405029297</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1688556671143</t>
+    <t xml:space="preserve">10.1688547134399</t>
   </si>
   <si>
     <t xml:space="preserve">10.037220954895</t>
@@ -3770,16 +3770,16 @@
     <t xml:space="preserve">9.95823860168457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3202362060547</t>
+    <t xml:space="preserve">10.320237159729</t>
   </si>
   <si>
     <t xml:space="preserve">10.4650363922119</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3531465530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4387102127075</t>
+    <t xml:space="preserve">10.3531455993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4387092590332</t>
   </si>
   <si>
     <t xml:space="preserve">10.3926372528076</t>
@@ -3794,13 +3794,13 @@
     <t xml:space="preserve">10.2215099334717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5176906585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5045280456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1890335083008</t>
+    <t xml:space="preserve">10.517689704895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.50452709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1890325546265</t>
   </si>
   <si>
     <t xml:space="preserve">11.2351045608521</t>
@@ -3809,76 +3809,76 @@
     <t xml:space="preserve">11.5115404129028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6431741714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5641956329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3667411804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5378675460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4983749389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6695041656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8208827972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8735399246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9985914230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1433925628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7353200912476</t>
+    <t xml:space="preserve">11.6431770324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5641937255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3667421340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5378684997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4983758926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6695032119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8208837509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8735389709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9985933303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1433916091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7353219985962</t>
   </si>
   <si>
     <t xml:space="preserve">11.6958303451538</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0775747299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9656829833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2811756134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6563377380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7616481781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7813930511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6760854721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6168479919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0315017700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8801193237305</t>
+    <t xml:space="preserve">12.0775737762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9656839370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.281177520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6563386917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7616491317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7813920974731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6760845184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.616849899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0315008163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8801202774048</t>
   </si>
   <si>
     <t xml:space="preserve">11.7945575714111</t>
   </si>
   <si>
-    <t xml:space="preserve">12.123646736145</t>
+    <t xml:space="preserve">12.1236457824707</t>
   </si>
   <si>
     <t xml:space="preserve">12.6370248794556</t>
@@ -3893,10 +3893,10 @@
     <t xml:space="preserve">14.2166538238525</t>
   </si>
   <si>
-    <t xml:space="preserve">14.26930809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0455284118652</t>
+    <t xml:space="preserve">14.2693099975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0455265045166</t>
   </si>
   <si>
     <t xml:space="preserve">14.085018157959</t>
@@ -3908,52 +3908,52 @@
     <t xml:space="preserve">12.9661149978638</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0709915161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6962614059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4658994674683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7419033050537</t>
+    <t xml:space="preserve">12.0709934234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6962623596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4659013748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7419013977051</t>
   </si>
   <si>
     <t xml:space="preserve">11.9722652435303</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7550659179688</t>
+    <t xml:space="preserve">11.7550668716431</t>
   </si>
   <si>
     <t xml:space="preserve">10.7085618972778</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2412567138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1956148147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4979457855225</t>
+    <t xml:space="preserve">10.2412548065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1956157684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4979467391968</t>
   </si>
   <si>
     <t xml:space="preserve">10.8204526901245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.294340133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5839395523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1894645690918</t>
+    <t xml:space="preserve">11.2943420410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5839405059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1894636154175</t>
   </si>
   <si>
     <t xml:space="preserve">12.1039009094238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1302280426025</t>
+    <t xml:space="preserve">12.1302289962769</t>
   </si>
   <si>
     <t xml:space="preserve">12.4329891204834</t>
@@ -3965,124 +3965,124 @@
     <t xml:space="preserve">12.2684450149536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.406662940979</t>
+    <t xml:space="preserve">12.4066638946533</t>
   </si>
   <si>
     <t xml:space="preserve">12.4395723342896</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2881908416748</t>
+    <t xml:space="preserve">12.2881917953491</t>
   </si>
   <si>
     <t xml:space="preserve">12.3934993743896</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6826658248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0380840301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8932828903198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9393548965454</t>
+    <t xml:space="preserve">11.6826677322388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0380830764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8932847976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9393539428711</t>
   </si>
   <si>
     <t xml:space="preserve">11.6629209518433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9525203704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3799047470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.504958152771</t>
+    <t xml:space="preserve">11.9525194168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3799057006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5049591064453</t>
   </si>
   <si>
     <t xml:space="preserve">11.3469953536987</t>
   </si>
   <si>
-    <t xml:space="preserve">10.800708770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0244874954224</t>
+    <t xml:space="preserve">10.8007078170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0244884490967</t>
   </si>
   <si>
     <t xml:space="preserve">11.4457216262817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7089939117432</t>
+    <t xml:space="preserve">11.7089948654175</t>
   </si>
   <si>
     <t xml:space="preserve">11.4588861465454</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9740495681763</t>
+    <t xml:space="preserve">11.974048614502</t>
   </si>
   <si>
     <t xml:space="preserve">11.9879713058472</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9183559417725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1550512313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.064549446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.134165763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8208904266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8000087738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7791213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7512741088867</t>
+    <t xml:space="preserve">11.9183549880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1550493240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0645503997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1341667175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8208913803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8000078201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7791233062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.751275062561</t>
   </si>
   <si>
     <t xml:space="preserve">11.7582359313965</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5563478469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4031925201416</t>
+    <t xml:space="preserve">11.5563488006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.403190612793</t>
   </si>
   <si>
     <t xml:space="preserve">11.1804189682007</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5120992660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97605323791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0804786682129</t>
+    <t xml:space="preserve">10.5121002197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97605419158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0804777145386</t>
   </si>
   <si>
     <t xml:space="preserve">10.4355220794678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95516872406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94124412536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1640176773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0038995742798</t>
+    <t xml:space="preserve">9.95516777038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94124507904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1640186309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0039005279541</t>
   </si>
   <si>
     <t xml:space="preserve">9.99693775177002</t>
@@ -4091,7 +4091,7 @@
     <t xml:space="preserve">9.74631881713867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98997592926025</t>
+    <t xml:space="preserve">9.98997688293457</t>
   </si>
   <si>
     <t xml:space="preserve">9.927321434021</t>
@@ -4100,7 +4100,7 @@
     <t xml:space="preserve">9.89947509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71847248077393</t>
+    <t xml:space="preserve">9.71847152709961</t>
   </si>
   <si>
     <t xml:space="preserve">9.405198097229</t>
@@ -4109,67 +4109,67 @@
     <t xml:space="preserve">9.28684902191162</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23811721801758</t>
+    <t xml:space="preserve">9.23811817169189</t>
   </si>
   <si>
     <t xml:space="preserve">8.86218738555908</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79257106781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98053646087646</t>
+    <t xml:space="preserve">8.79257297515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98053741455078</t>
   </si>
   <si>
     <t xml:space="preserve">9.23115634918213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95965194702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00838184356689</t>
+    <t xml:space="preserve">8.95965099334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00838279724121</t>
   </si>
   <si>
     <t xml:space="preserve">8.62549209594727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20779132843018</t>
+    <t xml:space="preserve">8.20779228210449</t>
   </si>
   <si>
     <t xml:space="preserve">8.40271949768066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54195308685303</t>
+    <t xml:space="preserve">8.54195213317871</t>
   </si>
   <si>
     <t xml:space="preserve">8.76472473144531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79953289031982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74384117126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81345558166504</t>
+    <t xml:space="preserve">8.79953384399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74384021759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81345748901367</t>
   </si>
   <si>
     <t xml:space="preserve">9.07800006866455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77168655395508</t>
+    <t xml:space="preserve">8.77168846130371</t>
   </si>
   <si>
     <t xml:space="preserve">8.91788196563721</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94572830200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11977005004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21723365783691</t>
+    <t xml:space="preserve">8.94572925567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11976909637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2172327041626</t>
   </si>
   <si>
     <t xml:space="preserve">9.09888362884521</t>
@@ -4184,37 +4184,37 @@
     <t xml:space="preserve">9.50265979766846</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25900268554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01534461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11280822753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33557987213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49569988250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03622913360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66726207733154</t>
+    <t xml:space="preserve">9.25900363922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01534557342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11280727386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33558082580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49569892883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03623008728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66726303100586</t>
   </si>
   <si>
     <t xml:space="preserve">8.77864837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75776290893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63245296478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39575672149658</t>
+    <t xml:space="preserve">8.75776386260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63245391845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3957576751709</t>
   </si>
   <si>
     <t xml:space="preserve">8.33310317993164</t>
@@ -4226,22 +4226,22 @@
     <t xml:space="preserve">8.31917858123779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10336780548096</t>
+    <t xml:space="preserve">8.10336685180664</t>
   </si>
   <si>
     <t xml:space="preserve">8.27044773101807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04071235656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99894189834595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88059377670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95021152496338</t>
+    <t xml:space="preserve">8.0407133102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99894237518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8805947303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95021200180054</t>
   </si>
   <si>
     <t xml:space="preserve">8.1312141418457</t>
@@ -4250,28 +4250,28 @@
     <t xml:space="preserve">8.58372211456299</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59068298339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70903205871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51410579681396</t>
+    <t xml:space="preserve">8.59068393707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7090311050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51410484313965</t>
   </si>
   <si>
     <t xml:space="preserve">8.46537399291992</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17994499206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22171497344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9432487487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95717287063599</t>
+    <t xml:space="preserve">8.17994689941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22171592712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94324922561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9571738243103</t>
   </si>
   <si>
     <t xml:space="preserve">7.82490158081055</t>
@@ -4280,58 +4280,58 @@
     <t xml:space="preserve">7.74136114120483</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49074220657349</t>
+    <t xml:space="preserve">7.49074125289917</t>
   </si>
   <si>
     <t xml:space="preserve">7.92236471176147</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01286506652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92932605743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84578609466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75528621673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68566751480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76920890808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65782117843628</t>
+    <t xml:space="preserve">8.01286602020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92932558059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84578704833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75528573989868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68566846847534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76920795440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65782165527344</t>
   </si>
   <si>
     <t xml:space="preserve">7.66478300094604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88755702972412</t>
+    <t xml:space="preserve">7.88755559921265</t>
   </si>
   <si>
     <t xml:space="preserve">7.86667156219482</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90148019790649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98501968383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07552146911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15209865570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29829406738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45841026306152</t>
+    <t xml:space="preserve">7.90147924423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98502063751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07552051544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.152099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2982931137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45841121673584</t>
   </si>
   <si>
     <t xml:space="preserve">8.49322032928467</t>
@@ -4340,22 +4340,22 @@
     <t xml:space="preserve">9.10584545135498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07103633880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37038803100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56531524658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69062328338623</t>
+    <t xml:space="preserve">9.07103729248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37038898468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56531620025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69062519073486</t>
   </si>
   <si>
     <t xml:space="preserve">9.6627779006958</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62797069549561</t>
+    <t xml:space="preserve">9.62797164916992</t>
   </si>
   <si>
     <t xml:space="preserve">9.52354621887207</t>
@@ -4370,7 +4370,7 @@
     <t xml:space="preserve">9.81434440612793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82932758331299</t>
+    <t xml:space="preserve">9.82932662963867</t>
   </si>
   <si>
     <t xml:space="preserve">9.85929489135742</t>
@@ -4382,37 +4382,37 @@
     <t xml:space="preserve">9.88926315307617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76190185546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77688598632812</t>
+    <t xml:space="preserve">9.76190090179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77688503265381</t>
   </si>
   <si>
     <t xml:space="preserve">9.70945835113525</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55962181091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39479923248291</t>
+    <t xml:space="preserve">9.55962085723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39480018615723</t>
   </si>
   <si>
     <t xml:space="preserve">9.40978336334229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56711196899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48470115661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67199802398682</t>
+    <t xml:space="preserve">9.56711292266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48470306396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67199897766113</t>
   </si>
   <si>
     <t xml:space="preserve">9.69447422027588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52216053009033</t>
+    <t xml:space="preserve">9.52216148376465</t>
   </si>
   <si>
     <t xml:space="preserve">9.60457134246826</t>
@@ -4424,49 +4424,49 @@
     <t xml:space="preserve">9.84431171417236</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94919776916504</t>
+    <t xml:space="preserve">9.94919872283936</t>
   </si>
   <si>
     <t xml:space="preserve">9.88177108764648</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96418190002441</t>
+    <t xml:space="preserve">9.96418285369873</t>
   </si>
   <si>
     <t xml:space="preserve">9.9716739654541</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0690679550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2263975143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4736289978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5035963058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5110874176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.660924911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6834001541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.743335723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8182525634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8032703399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7957782745361</t>
+    <t xml:space="preserve">10.0690670013428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2263965606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4736280441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5035953521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5110883712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6609258651733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6834011077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7433347702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8182544708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8032712936401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7957801818848</t>
   </si>
   <si>
     <t xml:space="preserve">10.765811920166</t>
@@ -4478,19 +4478,19 @@
     <t xml:space="preserve">10.863205909729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8482208251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6759090423584</t>
+    <t xml:space="preserve">10.8482217788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6759080886841</t>
   </si>
   <si>
     <t xml:space="preserve">10.8781900405884</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9231405258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2602729797363</t>
+    <t xml:space="preserve">10.9231395721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2602739334106</t>
   </si>
   <si>
     <t xml:space="preserve">11.5000143051147</t>
@@ -4499,7 +4499,7 @@
     <t xml:space="preserve">11.5824241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7772130966187</t>
+    <t xml:space="preserve">11.777214050293</t>
   </si>
   <si>
     <t xml:space="preserve">11.7172784805298</t>
@@ -4520,10 +4520,10 @@
     <t xml:space="preserve">12.2192325592041</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1967582702637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9345417022705</t>
+    <t xml:space="preserve">12.1967573165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9345426559448</t>
   </si>
   <si>
     <t xml:space="preserve">11.792197227478</t>
@@ -4532,55 +4532,55 @@
     <t xml:space="preserve">12.2866592407227</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1218385696411</t>
+    <t xml:space="preserve">12.1218395233154</t>
   </si>
   <si>
     <t xml:space="preserve">11.9045753479004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6573438644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5224905014038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.67982006073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6423597335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7097864151001</t>
+    <t xml:space="preserve">11.6573429107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5224895477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6798191070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6423587799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7097854614258</t>
   </si>
   <si>
     <t xml:space="preserve">11.7322616577148</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3426837921143</t>
+    <t xml:space="preserve">11.3426847457886</t>
   </si>
   <si>
     <t xml:space="preserve">10.9006643295288</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0954532623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5785140991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5934982299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.563530921936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4961032867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2863321304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3237915039062</t>
+    <t xml:space="preserve">11.0954542160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5785150527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5934991836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5635318756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4961051940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2863311767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3237924575806</t>
   </si>
   <si>
     <t xml:space="preserve">10.1964292526245</t>
@@ -4589,16 +4589,16 @@
     <t xml:space="preserve">10.3387756347656</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4661359786987</t>
+    <t xml:space="preserve">10.466136932373</t>
   </si>
   <si>
     <t xml:space="preserve">10.4586448669434</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3837251663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5260715484619</t>
+    <t xml:space="preserve">10.3837261199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5260705947876</t>
   </si>
   <si>
     <t xml:space="preserve">10.6384496688843</t>
@@ -4610,46 +4610,46 @@
     <t xml:space="preserve">10.9680919647217</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2078304290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3052244186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2452907562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4176044464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5449647903442</t>
+    <t xml:space="preserve">11.2078323364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3052263259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2452917098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4176034927368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5449657440186</t>
   </si>
   <si>
     <t xml:space="preserve">11.3876361846924</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3277006149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4026203155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0130424499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0430088043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2377977371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3576679229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7807950973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8107624053955</t>
+    <t xml:space="preserve">11.3277015686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4026193618774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0130434036255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0430107116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2377996444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3576688766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7807960510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8107633590698</t>
   </si>
   <si>
     <t xml:space="preserve">10.7882862091064</t>
@@ -4661,7 +4661,7 @@
     <t xml:space="preserve">11.2774877548218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1003131866455</t>
+    <t xml:space="preserve">11.1003150939941</t>
   </si>
   <si>
     <t xml:space="preserve">11.0695018768311</t>
@@ -4670,22 +4670,22 @@
     <t xml:space="preserve">11.2389717102051</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2004547119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9462509155273</t>
+    <t xml:space="preserve">11.2004556655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.946249961853</t>
   </si>
   <si>
     <t xml:space="preserve">10.7844829559326</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9539527893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0772037506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9770631790161</t>
+    <t xml:space="preserve">10.953953742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.077205657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9770622253418</t>
   </si>
   <si>
     <t xml:space="preserve">11.038688659668</t>
@@ -4694,31 +4694,31 @@
     <t xml:space="preserve">11.03098487854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9847650527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8923273086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8384046554565</t>
+    <t xml:space="preserve">10.9847660064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8923282623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8384037017822</t>
   </si>
   <si>
     <t xml:space="preserve">10.9616565704346</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9154376983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8692178726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8307018280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8229999542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0155792236328</t>
+    <t xml:space="preserve">10.9154367446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8692169189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8307027816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.822998046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0155782699585</t>
   </si>
   <si>
     <t xml:space="preserve">10.8461084365845</t>
@@ -4736,25 +4736,25 @@
     <t xml:space="preserve">11.0617971420288</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2928943634033</t>
+    <t xml:space="preserve">11.292893409729</t>
   </si>
   <si>
     <t xml:space="preserve">11.4007387161255</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4161443710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2543773651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3699254989624</t>
+    <t xml:space="preserve">11.416145324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2543783187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3699264526367</t>
   </si>
   <si>
     <t xml:space="preserve">11.246675491333</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3622226715088</t>
+    <t xml:space="preserve">11.3622236251831</t>
   </si>
   <si>
     <t xml:space="preserve">11.5085830688477</t>
@@ -4772,7 +4772,7 @@
     <t xml:space="preserve">11.7858991622925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7473831176758</t>
+    <t xml:space="preserve">11.7473821640015</t>
   </si>
   <si>
     <t xml:space="preserve">11.7319755554199</t>
@@ -4781,13 +4781,13 @@
     <t xml:space="preserve">11.7088670730591</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8167114257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0015878677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2712001800537</t>
+    <t xml:space="preserve">11.8167123794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0015888214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.271201133728</t>
   </si>
   <si>
     <t xml:space="preserve">12.3713417053223</t>
@@ -4796,10 +4796,10 @@
     <t xml:space="preserve">12.1325426101685</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9322605133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0092926025391</t>
+    <t xml:space="preserve">11.9322595596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0092916488647</t>
   </si>
   <si>
     <t xml:space="preserve">12.5562181472778</t>
@@ -4811,46 +4811,46 @@
     <t xml:space="preserve">12.2249813079834</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3328266143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3559370040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4021558761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4637804031372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5639209747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2866058349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2326850891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3636379241943</t>
+    <t xml:space="preserve">12.3328247070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.355936050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4021549224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4637813568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5639219284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2866067886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.232684135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.36363697052</t>
   </si>
   <si>
     <t xml:space="preserve">12.3020133972168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4175624847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4483737945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5408134460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5331087112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3482332229614</t>
+    <t xml:space="preserve">12.4175615310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.44837474823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5408124923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.533109664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3482322692871</t>
   </si>
   <si>
     <t xml:space="preserve">12.3097162246704</t>
@@ -4865,37 +4865,37 @@
     <t xml:space="preserve">11.8783369064331</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1402454376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1171350479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.978479385376</t>
+    <t xml:space="preserve">12.1402463912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1171360015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9784784317017</t>
   </si>
   <si>
     <t xml:space="preserve">11.9707746505737</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0632133483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1787614822388</t>
+    <t xml:space="preserve">12.063214302063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1787624359131</t>
   </si>
   <si>
     <t xml:space="preserve">12.2557935714722</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3944520950317</t>
+    <t xml:space="preserve">12.3944511413574</t>
   </si>
   <si>
     <t xml:space="preserve">12.409857749939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6101408004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.317419052124</t>
+    <t xml:space="preserve">12.6101417541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3174200057983</t>
   </si>
   <si>
     <t xml:space="preserve">12.5177030563354</t>
@@ -4904,22 +4904,22 @@
     <t xml:space="preserve">12.6948766708374</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9336776733398</t>
+    <t xml:space="preserve">12.9336757659912</t>
   </si>
   <si>
     <t xml:space="preserve">12.8412380218506</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6486577987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6794700622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6640644073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3867473602295</t>
+    <t xml:space="preserve">12.6486568450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6794691085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6640634536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3867483139038</t>
   </si>
   <si>
     <t xml:space="preserve">12.1710586547852</t>
@@ -4928,28 +4928,28 @@
     <t xml:space="preserve">11.6164283752441</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8552284240723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.278904914856</t>
+    <t xml:space="preserve">11.8552274703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2789030075073</t>
   </si>
   <si>
     <t xml:space="preserve">12.4252634048462</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5793266296387</t>
+    <t xml:space="preserve">12.579327583313</t>
   </si>
   <si>
     <t xml:space="preserve">12.8874568939209</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7719078063965</t>
+    <t xml:space="preserve">12.7719087600708</t>
   </si>
   <si>
     <t xml:space="preserve">12.8104238510132</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9413785934448</t>
+    <t xml:space="preserve">12.9413776397705</t>
   </si>
   <si>
     <t xml:space="preserve">13.341944694519</t>
@@ -4967,31 +4967,31 @@
     <t xml:space="preserve">13.0954427719116</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2880220413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2135105133057</t>
+    <t xml:space="preserve">13.2880229949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.21351146698</t>
   </si>
   <si>
     <t xml:space="preserve">12.9237403869629</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0644865036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0313701629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0893249511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8409509658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8740663528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0396499633789</t>
+    <t xml:space="preserve">13.0644855499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0313692092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0893239974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8409490585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8740653991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0396490097046</t>
   </si>
   <si>
     <t xml:space="preserve">12.9982528686523</t>
@@ -5000,7 +5000,7 @@
     <t xml:space="preserve">13.1886739730835</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0148124694824</t>
+    <t xml:space="preserve">13.0148115158081</t>
   </si>
   <si>
     <t xml:space="preserve">13.1224403381348</t>
@@ -5009,28 +5009,28 @@
     <t xml:space="preserve">13.114161491394</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1555576324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4536056518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2963027954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1803951263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0479288101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9568576812744</t>
+    <t xml:space="preserve">13.155556678772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4536066055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2963008880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1803941726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0479278564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9568567276001</t>
   </si>
   <si>
     <t xml:space="preserve">13.0727653503418</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1307201385498</t>
+    <t xml:space="preserve">13.1307191848755</t>
   </si>
   <si>
     <t xml:space="preserve">13.1472778320312</t>
@@ -5039,28 +5039,28 @@
     <t xml:space="preserve">13.2631864547729</t>
   </si>
   <si>
-    <t xml:space="preserve">13.652304649353</t>
+    <t xml:space="preserve">13.6523056030273</t>
   </si>
   <si>
     <t xml:space="preserve">13.3625345230103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3376989364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8657875061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9651365280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9734163284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9154634475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2052326202393</t>
+    <t xml:space="preserve">13.3376979827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8657865524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9651355743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9734153747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9154615402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2052316665649</t>
   </si>
   <si>
     <t xml:space="preserve">13.3128604888916</t>
@@ -5069,22 +5069,22 @@
     <t xml:space="preserve">13.2549066543579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1389980316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3708152770996</t>
+    <t xml:space="preserve">13.1389989852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3708143234253</t>
   </si>
   <si>
     <t xml:space="preserve">13.3873729705811</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5777921676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4867238998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8096103668213</t>
+    <t xml:space="preserve">13.5777931213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.486722946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8096084594727</t>
   </si>
   <si>
     <t xml:space="preserve">13.701979637146</t>
@@ -5099,43 +5099,43 @@
     <t xml:space="preserve">13.6191892623901</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6937017440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9006795883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8592824935913</t>
+    <t xml:space="preserve">13.6937026977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9006805419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8592844009399</t>
   </si>
   <si>
     <t xml:space="preserve">14.0497035980225</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2484035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1159372329712</t>
+    <t xml:space="preserve">14.2484045028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1159362792969</t>
   </si>
   <si>
     <t xml:space="preserve">13.9917507171631</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9172372817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0248670578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0000286102295</t>
+    <t xml:space="preserve">13.9172382354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0248680114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0000295639038</t>
   </si>
   <si>
     <t xml:space="preserve">13.983470916748</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1821708679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1242170333862</t>
+    <t xml:space="preserve">14.1821699142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1242160797119</t>
   </si>
   <si>
     <t xml:space="preserve">14.0414247512817</t>
@@ -5144,7 +5144,7 @@
     <t xml:space="preserve">14.0165882110596</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9669132232666</t>
+    <t xml:space="preserve">13.9669141769409</t>
   </si>
   <si>
     <t xml:space="preserve">14.2897996902466</t>
@@ -5156,28 +5156,28 @@
     <t xml:space="preserve">14.3891477584839</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7037563323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8610601425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9521322250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0266427993774</t>
+    <t xml:space="preserve">14.7037572860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8610610961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9521293640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0266418457031</t>
   </si>
   <si>
     <t xml:space="preserve">14.9769678115845</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2170639038086</t>
+    <t xml:space="preserve">15.2170629501343</t>
   </si>
   <si>
     <t xml:space="preserve">15.3578081130981</t>
   </si>
   <si>
-    <t xml:space="preserve">15.159107208252</t>
+    <t xml:space="preserve">15.1591081619263</t>
   </si>
   <si>
     <t xml:space="preserve">15.2750177383423</t>
@@ -5186,22 +5186,22 @@
     <t xml:space="preserve">15.8131618499756</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4672145843506</t>
+    <t xml:space="preserve">16.467212677002</t>
   </si>
   <si>
     <t xml:space="preserve">16.1029319763184</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1774444580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1608867645264</t>
+    <t xml:space="preserve">16.1774463653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1608848571777</t>
   </si>
   <si>
     <t xml:space="preserve">16.3678646087646</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5748424530029</t>
+    <t xml:space="preserve">16.5748443603516</t>
   </si>
   <si>
     <t xml:space="preserve">16.8563346862793</t>
@@ -5216,13 +5216,13 @@
     <t xml:space="preserve">17.1709403991699</t>
   </si>
   <si>
-    <t xml:space="preserve">16.955680847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4358730316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3365230560303</t>
+    <t xml:space="preserve">16.9556846618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4358749389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3365249633789</t>
   </si>
   <si>
     <t xml:space="preserve">17.5186653137207</t>
@@ -5231,19 +5231,19 @@
     <t xml:space="preserve">17.4524326324463</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6511325836182</t>
+    <t xml:space="preserve">17.6511306762695</t>
   </si>
   <si>
     <t xml:space="preserve">17.7670383453369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8167152404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0881481170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2040576934814</t>
+    <t xml:space="preserve">17.8167133331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0881500244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2040596008301</t>
   </si>
   <si>
     <t xml:space="preserve">16.9060077667236</t>
@@ -6108,6 +6108,9 @@
   </si>
   <si>
     <t xml:space="preserve">24.3400001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9799995422363</t>
   </si>
 </sst>
 </file>
@@ -72070,7 +72073,7 @@
     </row>
     <row r="2525">
       <c r="A2525" s="1" t="n">
-        <v>45994.6911805556</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2525" t="n">
         <v>250522</v>
@@ -72091,6 +72094,32 @@
         <v>2031</v>
       </c>
       <c r="H2525" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2526">
+      <c r="A2526" s="1" t="n">
+        <v>45995.6912731481</v>
+      </c>
+      <c r="B2526" t="n">
+        <v>270505</v>
+      </c>
+      <c r="C2526" t="n">
+        <v>24.3600006103516</v>
+      </c>
+      <c r="D2526" t="n">
+        <v>23.8400001525879</v>
+      </c>
+      <c r="E2526" t="n">
+        <v>24.3400001525879</v>
+      </c>
+      <c r="F2526" t="n">
+        <v>23.9799995422363</v>
+      </c>
+      <c r="G2526" t="s">
+        <v>2032</v>
+      </c>
+      <c r="H2526" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IF.MI.xlsx
+++ b/data/IF.MI.xlsx
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9798793792725</t>
+    <t xml:space="preserve">14.9798803329468</t>
   </si>
   <si>
     <t xml:space="preserve">IF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6498346328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5859537124634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8460102081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6703395843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6863088607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7342214584351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.494668006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1494398117065</t>
+    <t xml:space="preserve">14.6498327255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5859546661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8460083007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6703386306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6863098144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7342224121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4946689605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1494388580322</t>
   </si>
   <si>
     <t xml:space="preserve">13.1859149932861</t>
@@ -74,73 +74,73 @@
     <t xml:space="preserve">13.7980985641479</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9365043640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7395420074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6338624954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6551551818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1715230941772</t>
+    <t xml:space="preserve">13.9365062713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7395448684692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.633864402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6551561355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1715221405029</t>
   </si>
   <si>
     <t xml:space="preserve">15.1768436431885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8148565292358</t>
+    <t xml:space="preserve">14.8148555755615</t>
   </si>
   <si>
     <t xml:space="preserve">15.3312196731567</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2779893875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0118217468262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4422225952148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2399349212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8406839370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4300022125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4672651290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0794467926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1060667037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1593017578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8353624343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7448654174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6596946716309</t>
+    <t xml:space="preserve">15.2779874801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0118236541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4422206878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2399368286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8406858444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4300003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.467264175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0794477462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1060657501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1592979431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8353633880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7448682785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6596899032593</t>
   </si>
   <si>
     <t xml:space="preserve">13.5851650238037</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6437215805054</t>
+    <t xml:space="preserve">13.6437206268311</t>
   </si>
   <si>
     <t xml:space="preserve">14.692419052124</t>
@@ -152,91 +152,91 @@
     <t xml:space="preserve">14.0323257446289</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4741659164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3730182647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.319787979126</t>
+    <t xml:space="preserve">14.4741630554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3730211257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.319785118103</t>
   </si>
   <si>
     <t xml:space="preserve">14.7509775161743</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5486888885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2665548324585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7501878738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8566589355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4840221405029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7874536514282</t>
+    <t xml:space="preserve">14.5486907958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2665529251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7501888275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8566579818726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4840211868286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7874526977539</t>
   </si>
   <si>
     <t xml:space="preserve">14.0110321044922</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4528713226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6391868591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2300786972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4536581039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3205757141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1981382369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3418684005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3637390136719</t>
+    <t xml:space="preserve">14.4528684616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6391878128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2300758361816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4536590576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3205728530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1981372833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.341869354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3637371063232</t>
   </si>
   <si>
     <t xml:space="preserve">15.6917905807495</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9159555435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6261796951294</t>
+    <t xml:space="preserve">15.9159574508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6261806488037</t>
   </si>
   <si>
     <t xml:space="preserve">15.0848951339722</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5933771133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8497934341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9263381958008</t>
+    <t xml:space="preserve">15.5933742523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8497915267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9263324737549</t>
   </si>
   <si>
     <t xml:space="preserve">15.0247535705566</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1231660842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8825960159302</t>
+    <t xml:space="preserve">15.1231670379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8825950622559</t>
   </si>
   <si>
     <t xml:space="preserve">14.5436096191406</t>
@@ -245,133 +245,133 @@
     <t xml:space="preserve">14.6857662200928</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5053367614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4123868942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6420249938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2374296188354</t>
+    <t xml:space="preserve">14.5053377151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4123907089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6420259475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2374267578125</t>
   </si>
   <si>
     <t xml:space="preserve">14.1335458755493</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8875064849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9203119277954</t>
+    <t xml:space="preserve">13.887508392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9203128814697</t>
   </si>
   <si>
     <t xml:space="preserve">13.9968566894531</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8547029495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6578702926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4391689300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1767292022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4829092025757</t>
+    <t xml:space="preserve">13.854700088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6578722000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4391717910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1767301559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.48291015625</t>
   </si>
   <si>
     <t xml:space="preserve">13.0127029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9853639602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6846542358398</t>
+    <t xml:space="preserve">12.9853649139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6846532821655</t>
   </si>
   <si>
     <t xml:space="preserve">12.4768867492676</t>
   </si>
   <si>
-    <t xml:space="preserve">12.219913482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3566007614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.148832321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8809251785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0285511016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0777568817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7551727294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9738750457764</t>
+    <t xml:space="preserve">12.2199106216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3565998077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1488332748413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8809261322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0285501480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0777549743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7551736831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9738740921021</t>
   </si>
   <si>
     <t xml:space="preserve">12.3128604888916</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8164281845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2860803604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1220541000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.908821105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0072374343872</t>
+    <t xml:space="preserve">13.8164300918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2860774993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1220550537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9088201522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0072345733643</t>
   </si>
   <si>
     <t xml:space="preserve">12.7065229415894</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6299772262573</t>
+    <t xml:space="preserve">12.6299781799316</t>
   </si>
   <si>
     <t xml:space="preserve">12.7174577713013</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5206260681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3401985168457</t>
+    <t xml:space="preserve">12.5206270217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.34019947052</t>
   </si>
   <si>
     <t xml:space="preserve">12.1652374267578</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9465370178223</t>
+    <t xml:space="preserve">11.9465360641479</t>
   </si>
   <si>
     <t xml:space="preserve">11.6184854507446</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4763288497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3451099395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.049861907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6403570175171</t>
+    <t xml:space="preserve">11.4763298034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3451070785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0498628616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6403560638428</t>
   </si>
   <si>
     <t xml:space="preserve">12.0449533462524</t>
@@ -380,22 +380,22 @@
     <t xml:space="preserve">11.9902772903442</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3620700836182</t>
+    <t xml:space="preserve">12.3620653152466</t>
   </si>
   <si>
     <t xml:space="preserve">11.5364713668823</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68844985961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77046394348145</t>
+    <t xml:space="preserve">9.68844890594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77046203613281</t>
   </si>
   <si>
     <t xml:space="preserve">9.82513809204102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92355346679688</t>
+    <t xml:space="preserve">9.92355251312256</t>
   </si>
   <si>
     <t xml:space="preserve">9.93448829650879</t>
@@ -407,16 +407,16 @@
     <t xml:space="preserve">9.45881271362305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11982822418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1088924407959</t>
+    <t xml:space="preserve">9.11982727050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10889339447021</t>
   </si>
   <si>
     <t xml:space="preserve">9.26198387145996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29478740692139</t>
+    <t xml:space="preserve">9.2947883605957</t>
   </si>
   <si>
     <t xml:space="preserve">10.3062801361084</t>
@@ -425,31 +425,31 @@
     <t xml:space="preserve">10.7382135391235</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9350471496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7819538116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.962381362915</t>
+    <t xml:space="preserve">10.9350442886353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7819547653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9623832702637</t>
   </si>
   <si>
     <t xml:space="preserve">10.7163457870483</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9459810256958</t>
+    <t xml:space="preserve">10.9459791183472</t>
   </si>
   <si>
     <t xml:space="preserve">10.6890058517456</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5140447616577</t>
+    <t xml:space="preserve">10.5140466690063</t>
   </si>
   <si>
     <t xml:space="preserve">10.3390855789185</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0930471420288</t>
+    <t xml:space="preserve">10.0930461883545</t>
   </si>
   <si>
     <t xml:space="preserve">10.4703054428101</t>
@@ -458,19 +458,19 @@
     <t xml:space="preserve">11.1537446975708</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8694343566895</t>
+    <t xml:space="preserve">10.8694334030151</t>
   </si>
   <si>
     <t xml:space="preserve">11.0225257873535</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5796566009521</t>
+    <t xml:space="preserve">10.5796556472778</t>
   </si>
   <si>
     <t xml:space="preserve">10.6069936752319</t>
   </si>
   <si>
-    <t xml:space="preserve">11.044397354126</t>
+    <t xml:space="preserve">11.044394493103</t>
   </si>
   <si>
     <t xml:space="preserve">11.1756162643433</t>
@@ -482,67 +482,67 @@
     <t xml:space="preserve">11.0936031341553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0006561279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9022397994995</t>
+    <t xml:space="preserve">11.000657081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9022407531738</t>
   </si>
   <si>
     <t xml:space="preserve">10.8366289138794</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7436828613281</t>
+    <t xml:space="preserve">10.7436809539795</t>
   </si>
   <si>
     <t xml:space="preserve">10.4593696594238</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4484348297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5085783004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4976415634155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5632514953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4429683685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5851221084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6671361923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6507349014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8803672790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2630968093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7223691940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7989120483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3833827972412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.131875038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2084226608276</t>
+    <t xml:space="preserve">10.4484367370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5085763931274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4976425170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5632543563843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4429693222046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4375009536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5851249694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6671380996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6507329940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8803701400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2630958557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7223672866821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7989139556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3833818435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1318778991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.208420753479</t>
   </si>
   <si>
     <t xml:space="preserve">11.1100053787231</t>
@@ -551,34 +551,34 @@
     <t xml:space="preserve">11.1264085769653</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0170555114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.202953338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4817953109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4435243606567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0990715026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9569139480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9405145645142</t>
+    <t xml:space="preserve">11.0170564651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2029542922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4817981719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4435234069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0990695953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9569149017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9405136108398</t>
   </si>
   <si>
     <t xml:space="preserve">10.9733171463013</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1428089141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1920175552368</t>
+    <t xml:space="preserve">11.1428098678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1920204162598</t>
   </si>
   <si>
     <t xml:space="preserve">11.4489917755127</t>
@@ -587,19 +587,19 @@
     <t xml:space="preserve">11.8098497390747</t>
   </si>
   <si>
-    <t xml:space="preserve">12.788535118103</t>
+    <t xml:space="preserve">12.7885332107544</t>
   </si>
   <si>
     <t xml:space="preserve">13.0400409698486</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0673789978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1985998153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.280613899231</t>
+    <t xml:space="preserve">13.0673799514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1985950469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2806129455566</t>
   </si>
   <si>
     <t xml:space="preserve">13.4938468933105</t>
@@ -608,55 +608,55 @@
     <t xml:space="preserve">13.6797409057617</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7672214508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1663503646851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2428970336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3795824050903</t>
+    <t xml:space="preserve">13.7672204971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.166353225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2428941726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3795833587646</t>
   </si>
   <si>
     <t xml:space="preserve">14.4944019317627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4069194793701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2264957427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0077924728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0241966247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8109636306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8929738998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8437652587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6906785964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.395432472229</t>
+    <t xml:space="preserve">14.4069185256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2264966964722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.007791519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0241947174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.810959815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8929758071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8437671661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6906757354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3954286575317</t>
   </si>
   <si>
     <t xml:space="preserve">13.3844938278198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9908351898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0291061401367</t>
+    <t xml:space="preserve">12.990834236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0291051864624</t>
   </si>
   <si>
     <t xml:space="preserve">12.9361581802368</t>
@@ -668,25 +668,25 @@
     <t xml:space="preserve">12.4222106933594</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4878206253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.547966003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1379013061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5753021240234</t>
+    <t xml:space="preserve">12.4878215789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5479640960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.137900352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5753011703491</t>
   </si>
   <si>
     <t xml:space="preserve">12.794002532959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7776031494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6463794708252</t>
+    <t xml:space="preserve">12.7775993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6463785171509</t>
   </si>
   <si>
     <t xml:space="preserve">13.4610414505005</t>
@@ -695,130 +695,130 @@
     <t xml:space="preserve">13.5867948532104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5102481842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6688041687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2210283279419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9804553985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6961450576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7781581878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0734004974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2155570983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4889335632324</t>
+    <t xml:space="preserve">13.5102472305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6688079833984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2210273742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9804534912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6961431503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7781591415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0734033584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2155561447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4889354705811</t>
   </si>
   <si>
     <t xml:space="preserve">14.8333883285522</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7513771057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7076368331909</t>
+    <t xml:space="preserve">14.7513751983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7076349258423</t>
   </si>
   <si>
     <t xml:space="preserve">14.5982847213745</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1226081848145</t>
+    <t xml:space="preserve">14.1226100921631</t>
   </si>
   <si>
     <t xml:space="preserve">14.2702322006226</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5600147247314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4342603683472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3139724731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3631811141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3467769622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1171426773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9421796798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8328313827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5485219955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8273649215698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7234792709351</t>
+    <t xml:space="preserve">14.5600137710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4342584609985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3139753341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3631820678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3467788696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1171407699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9421825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8328304290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5485210418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8273658752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7234802246094</t>
   </si>
   <si>
     <t xml:space="preserve">13.7016105651855</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3249092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.051531791687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9531164169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1608848571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.652961730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0903606414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0794277191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.265323638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.713662147522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1401252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2658824920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8339433670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8120737075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.309063911438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0745143890381</t>
+    <t xml:space="preserve">14.3249082565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.05153465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9531183242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1608839035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6529598236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0903625488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0794258117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2653255462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7136583328247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1401271820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2658805847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8339443206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8120765686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3090620040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0745162963867</t>
   </si>
   <si>
     <t xml:space="preserve">16.1291923522949</t>
@@ -827,148 +827,148 @@
     <t xml:space="preserve">16.5119171142578</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6431369781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7470207214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2385406494141</t>
+    <t xml:space="preserve">16.643138885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7470188140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2385444641113</t>
   </si>
   <si>
     <t xml:space="preserve">16.3424243927002</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8399677276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0532035827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8350582122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6114482879639</t>
+    <t xml:space="preserve">16.8399696350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0532054901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8350563049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6114463806152</t>
   </si>
   <si>
     <t xml:space="preserve">18.8629512786865</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0324440002441</t>
+    <t xml:space="preserve">19.0324478149414</t>
   </si>
   <si>
     <t xml:space="preserve">19.9345874786377</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5354557037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8471069335938</t>
+    <t xml:space="preserve">19.5354595184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8471050262451</t>
   </si>
   <si>
     <t xml:space="preserve">19.7377548217773</t>
   </si>
   <si>
-    <t xml:space="preserve">19.683084487915</t>
+    <t xml:space="preserve">19.6830806732178</t>
   </si>
   <si>
     <t xml:space="preserve">19.6557426452637</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3440971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.57373046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6448097229004</t>
+    <t xml:space="preserve">19.3440933227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5737266540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6448078155518</t>
   </si>
   <si>
     <t xml:space="preserve">19.8361682891846</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8197689056396</t>
+    <t xml:space="preserve">19.8197708129883</t>
   </si>
   <si>
     <t xml:space="preserve">19.6174716949463</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0931434631348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3829212188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2188949584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1587562561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0111293792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9509868621826</t>
+    <t xml:space="preserve">20.0931453704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3829231262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2188968658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1587524414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0111312866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9509887695312</t>
   </si>
   <si>
     <t xml:space="preserve">20.2845058441162</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5469512939453</t>
+    <t xml:space="preserve">20.546947479248</t>
   </si>
   <si>
     <t xml:space="preserve">20.2899761199951</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1975841522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0718288421631</t>
+    <t xml:space="preserve">21.1975860595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0718307495117</t>
   </si>
   <si>
     <t xml:space="preserve">20.9242095947266</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1593132019043</t>
+    <t xml:space="preserve">21.1593112945557</t>
   </si>
   <si>
     <t xml:space="preserve">21.651388168335</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8300476074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4950618743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3163986206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4342632293701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4739685058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.08811378479</t>
+    <t xml:space="preserve">21.8300495147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4950637817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3164024353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4342651367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4739646911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0881118774414</t>
   </si>
   <si>
     <t xml:space="preserve">19.8145389556885</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6414604187012</t>
+    <t xml:space="preserve">19.6414623260498</t>
   </si>
   <si>
     <t xml:space="preserve">19.6972942352295</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5967922210693</t>
+    <t xml:space="preserve">19.5967960357666</t>
   </si>
   <si>
     <t xml:space="preserve">18.3685073852539</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6929492950439</t>
+    <t xml:space="preserve">17.6929473876953</t>
   </si>
   <si>
     <t xml:space="preserve">18.6029968261719</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">19.0049858093262</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4962959289551</t>
+    <t xml:space="preserve">19.4962978363037</t>
   </si>
   <si>
     <t xml:space="preserve">19.4851322174072</t>
@@ -989,61 +989,61 @@
     <t xml:space="preserve">19.4293022155762</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2953090667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3288059234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8430709838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6644134521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9268188476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2729759216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0943164825439</t>
+    <t xml:space="preserve">19.2953071594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3288021087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8430728912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6644115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9268226623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2729721069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0943126678467</t>
   </si>
   <si>
     <t xml:space="preserve">19.2059764862061</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7531261444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7028789520264</t>
+    <t xml:space="preserve">19.7531223297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7028751373291</t>
   </si>
   <si>
     <t xml:space="preserve">19.3734722137451</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5633010864258</t>
+    <t xml:space="preserve">19.5632972717285</t>
   </si>
   <si>
     <t xml:space="preserve">19.5186328887939</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7084617614746</t>
+    <t xml:space="preserve">19.7084560394287</t>
   </si>
   <si>
     <t xml:space="preserve">19.4572162628174</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1780605316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0831470489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0384845733643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5018825531006</t>
+    <t xml:space="preserve">19.1780567169189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0831489562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.038480758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.501880645752</t>
   </si>
   <si>
     <t xml:space="preserve">19.6749610900879</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">19.6526298522949</t>
   </si>
   <si>
-    <t xml:space="preserve">19.859203338623</t>
+    <t xml:space="preserve">19.8592014312744</t>
   </si>
   <si>
     <t xml:space="preserve">19.9262008666992</t>
@@ -1061,61 +1061,61 @@
     <t xml:space="preserve">19.9987812042236</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9206161499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0992794036865</t>
+    <t xml:space="preserve">19.920618057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0992774963379</t>
   </si>
   <si>
     <t xml:space="preserve">20.2332763671875</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2667713165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5180110931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7022571563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.59059715271</t>
+    <t xml:space="preserve">20.2667694091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5180130004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7022590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5905952453613</t>
   </si>
   <si>
     <t xml:space="preserve">20.5682621002197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6017589569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7860012054443</t>
+    <t xml:space="preserve">20.6017608642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7860050201416</t>
   </si>
   <si>
     <t xml:space="preserve">21.0204963684082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7134208679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3833999633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8021335601807</t>
+    <t xml:space="preserve">20.7134189605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3833980560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.802131652832</t>
   </si>
   <si>
     <t xml:space="preserve">21.5508918762207</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8635501861572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6625537872314</t>
+    <t xml:space="preserve">21.8635482788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6625556945801</t>
   </si>
   <si>
     <t xml:space="preserve">22.1650352478027</t>
   </si>
   <si>
-    <t xml:space="preserve">22.360445022583</t>
+    <t xml:space="preserve">22.3604469299316</t>
   </si>
   <si>
     <t xml:space="preserve">22.628438949585</t>
@@ -1127,310 +1127,310 @@
     <t xml:space="preserve">23.1030044555664</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7233543395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9410934448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8908462524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4106979370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4330310821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9969272613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1811695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1365032196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.706600189209</t>
+    <t xml:space="preserve">22.7233505249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9410915374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8908443450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4106941223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4330253601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9969215393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1811637878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1365013122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7065982818604</t>
   </si>
   <si>
     <t xml:space="preserve">22.8796787261963</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6898517608643</t>
+    <t xml:space="preserve">22.6898498535156</t>
   </si>
   <si>
     <t xml:space="preserve">22.6731033325195</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8182601928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6451873779297</t>
+    <t xml:space="preserve">22.8182621002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6451854705811</t>
   </si>
   <si>
     <t xml:space="preserve">22.5000228881836</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0031261444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5670223236084</t>
+    <t xml:space="preserve">22.0031299591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5670261383057</t>
   </si>
   <si>
     <t xml:space="preserve">22.7512664794922</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0025100708008</t>
+    <t xml:space="preserve">23.0025062561035</t>
   </si>
   <si>
     <t xml:space="preserve">23.3542442321777</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1700019836426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9243431091309</t>
+    <t xml:space="preserve">23.1699981689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9243450164795</t>
   </si>
   <si>
     <t xml:space="preserve">23.549654006958</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5217399597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3151588439941</t>
+    <t xml:space="preserve">23.5217342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3151607513428</t>
   </si>
   <si>
     <t xml:space="preserve">23.5105724334717</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8623085021973</t>
+    <t xml:space="preserve">23.8623065948486</t>
   </si>
   <si>
     <t xml:space="preserve">24.4708709716797</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4764556884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9007682800293</t>
+    <t xml:space="preserve">24.4764518737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9007701873779</t>
   </si>
   <si>
     <t xml:space="preserve">25.2190093994141</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1129322052002</t>
+    <t xml:space="preserve">25.1129302978516</t>
   </si>
   <si>
     <t xml:space="preserve">25.3083400726318</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8728580474854</t>
+    <t xml:space="preserve">24.8728561401367</t>
   </si>
   <si>
     <t xml:space="preserve">25.319507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5316677093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8275737762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4193859100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7152900695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8492889404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6042461395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4138011932373</t>
+    <t xml:space="preserve">25.5316638946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8275699615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4193820953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7152881622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8492851257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.604248046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4138031005859</t>
   </si>
   <si>
     <t xml:space="preserve">27.1284446716309</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4411010742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5025119781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2791881561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7041244506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6321659088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2525081634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9057388305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3585910797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2128047943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3021373748779</t>
+    <t xml:space="preserve">27.4410972595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.502513885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2791862487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7041263580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6321601867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2525062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.905740737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.358585357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2128067016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3021450042725</t>
   </si>
   <si>
     <t xml:space="preserve">26.3356323242188</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5031318664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9609527587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.24072265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.274227142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1346473693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1793079376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7773265838623</t>
+    <t xml:space="preserve">26.5031299591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9609470367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2407264709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2742233276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1346492767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.179313659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7773246765137</t>
   </si>
   <si>
     <t xml:space="preserve">25.5260848999023</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0403461456299</t>
+    <t xml:space="preserve">25.0403499603271</t>
   </si>
   <si>
     <t xml:space="preserve">24.6886138916016</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4156551361084</t>
+    <t xml:space="preserve">23.415657043457</t>
   </si>
   <si>
     <t xml:space="preserve">22.7456817626953</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8467979431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7295513153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4665298461914</t>
+    <t xml:space="preserve">21.8467998504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.729549407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4665260314941</t>
   </si>
   <si>
     <t xml:space="preserve">21.6234741210938</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6346397399902</t>
+    <t xml:space="preserve">21.6346378326416</t>
   </si>
   <si>
     <t xml:space="preserve">21.2438201904297</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9255828857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5843925476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3275680541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5229740142822</t>
+    <t xml:space="preserve">20.9255809783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5843944549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3275699615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5229778289795</t>
   </si>
   <si>
     <t xml:space="preserve">21.6960544586182</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1656551361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5124320983887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4845142364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6855049133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7748336791992</t>
+    <t xml:space="preserve">21.1656532287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5124282836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4845123291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6855068206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7748374938965</t>
   </si>
   <si>
     <t xml:space="preserve">20.4175148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8982849121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3728504180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8250865936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3889865875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1718597412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0936946868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0434474945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6687564849854</t>
+    <t xml:space="preserve">19.898286819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3728523254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8250904083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3889808654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1718616485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0936965942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0434455871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.668758392334</t>
   </si>
   <si>
     <t xml:space="preserve">21.6123065948486</t>
   </si>
   <si>
-    <t xml:space="preserve">22.76243019104</t>
+    <t xml:space="preserve">22.7624340057373</t>
   </si>
   <si>
     <t xml:space="preserve">21.936128616333</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2208671569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6116905212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6228542327881</t>
+    <t xml:space="preserve">22.2208690643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.611686706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6228580474854</t>
   </si>
   <si>
     <t xml:space="preserve">22.3213653564453</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3883609771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2717380523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9193801879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0422096252441</t>
+    <t xml:space="preserve">22.3883666992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2717323303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.919376373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0422077178955</t>
   </si>
   <si>
     <t xml:space="preserve">21.763053894043</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">21.8523826599121</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6848907470703</t>
+    <t xml:space="preserve">21.6848831176758</t>
   </si>
   <si>
     <t xml:space="preserve">21.43922996521</t>
@@ -1451,76 +1451,76 @@
     <t xml:space="preserve">21.416898727417</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2047386169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8412132263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3722286224365</t>
+    <t xml:space="preserve">21.2047367095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.841215133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3722324371338</t>
   </si>
   <si>
     <t xml:space="preserve">21.01491355896</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1997756958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7419605255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2444362640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7034931182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4913349151611</t>
+    <t xml:space="preserve">20.1997737884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7419586181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2444381713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7034950256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4913368225098</t>
   </si>
   <si>
     <t xml:space="preserve">19.7754554748535</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1439437866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9094486236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3449363708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3337669372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3002700805664</t>
+    <t xml:space="preserve">20.1439476013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9094524383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.344934463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3337688446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3002681732178</t>
   </si>
   <si>
     <t xml:space="preserve">20.2556037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3672676086426</t>
+    <t xml:space="preserve">20.3672714233398</t>
   </si>
   <si>
     <t xml:space="preserve">20.0322818756104</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7977905273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6861267089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0496520996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4020042419434</t>
+    <t xml:space="preserve">19.7977886199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.686128616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0496482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.402006149292</t>
   </si>
   <si>
     <t xml:space="preserve">18.1005172729492</t>
   </si>
   <si>
-    <t xml:space="preserve">18.424337387085</t>
+    <t xml:space="preserve">18.4243392944336</t>
   </si>
   <si>
     <t xml:space="preserve">18.1786804199219</t>
@@ -1529,16 +1529,16 @@
     <t xml:space="preserve">18.1675148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1054782867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0273170471191</t>
+    <t xml:space="preserve">19.1054840087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0273189544678</t>
   </si>
   <si>
     <t xml:space="preserve">17.9330215454102</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4640407562256</t>
+    <t xml:space="preserve">17.4640369415283</t>
   </si>
   <si>
     <t xml:space="preserve">17.6315326690674</t>
@@ -1547,19 +1547,19 @@
     <t xml:space="preserve">18.5025005340576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3350105285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.078182220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.441707611084</t>
+    <t xml:space="preserve">18.3350086212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0781860351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4417057037354</t>
   </si>
   <si>
     <t xml:space="preserve">16.5260734558105</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7990245819092</t>
+    <t xml:space="preserve">17.7990283966064</t>
   </si>
   <si>
     <t xml:space="preserve">17.0955543518066</t>
@@ -1568,43 +1568,43 @@
     <t xml:space="preserve">17.8213596343994</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2010097503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3461761474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4801692962646</t>
+    <t xml:space="preserve">18.2010116577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3461742401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.480167388916</t>
   </si>
   <si>
     <t xml:space="preserve">19.1836433410645</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7816562652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6364974975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8598232269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7481632232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4152755737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.426794052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2194881439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1734237670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2425231933594</t>
+    <t xml:space="preserve">18.7816581726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.63649559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8598213195801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.748161315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4152736663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4267902374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2194900512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1734218597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2425212860107</t>
   </si>
   <si>
     <t xml:space="preserve">18.8298778533936</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">19.2905464172363</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4517822265625</t>
+    <t xml:space="preserve">19.4517803192139</t>
   </si>
   <si>
     <t xml:space="preserve">19.670597076416</t>
@@ -1625,22 +1625,22 @@
     <t xml:space="preserve">19.3941974639893</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0602111816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5995407104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5074081420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7031917572021</t>
+    <t xml:space="preserve">19.060209274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5995426177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5074100494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7031955718994</t>
   </si>
   <si>
     <t xml:space="preserve">18.7722911834717</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0467376708984</t>
+    <t xml:space="preserve">18.0467357635498</t>
   </si>
   <si>
     <t xml:space="preserve">17.4478664398193</t>
@@ -1649,25 +1649,25 @@
     <t xml:space="preserve">16.5725936889648</t>
   </si>
   <si>
-    <t xml:space="preserve">16.261646270752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3998470306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0658588409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7203578948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8566017150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4861087799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2653322219849</t>
+    <t xml:space="preserve">16.2616443634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3998432159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0658569335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7203540802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8566026687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4861078262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2653341293335</t>
   </si>
   <si>
     <t xml:space="preserve">13.4400405883789</t>
@@ -1676,136 +1676,136 @@
     <t xml:space="preserve">13.5436916351318</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6838474273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7414331436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2922811508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4189672470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1195278167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.992844581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5571660995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.374852180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8009757995605</t>
+    <t xml:space="preserve">14.6838502883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7414321899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2922782897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4189624786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1195287704468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9928417205811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5571641921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3748531341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8009729385376</t>
   </si>
   <si>
     <t xml:space="preserve">15.7779388427734</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3057518005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.985239982605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4113597869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9276561737061</t>
+    <t xml:space="preserve">15.3057565689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9852428436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4113616943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.927659034729</t>
   </si>
   <si>
     <t xml:space="preserve">16.0888919830322</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8240089416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2021045684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7184009552002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8220491409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8450841903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.891149520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8681163787842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.029351234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2712049484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6167049407959</t>
+    <t xml:space="preserve">15.8240079879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2021007537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7183980941772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8220500946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.84508228302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8911504745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8681125640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0293493270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2712030410767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6167039871216</t>
   </si>
   <si>
     <t xml:space="preserve">15.7894563674927</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4900207519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1445198059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2251358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0638990402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8700752258301</t>
+    <t xml:space="preserve">15.4900197982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1445178985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.225136756897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0639009475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8700742721558</t>
   </si>
   <si>
     <t xml:space="preserve">16.123441696167</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5015382766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2827205657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5130558013916</t>
+    <t xml:space="preserve">15.5015392303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2827224731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5130519866943</t>
   </si>
   <si>
     <t xml:space="preserve">15.5706396102905</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4324378967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6262645721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7990159988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9352607727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7260046005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0254373550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9908876419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9793729782104</t>
+    <t xml:space="preserve">15.4324369430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6262655258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.799017906189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9352617263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7260036468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0254392623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9908866882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9793710708618</t>
   </si>
   <si>
     <t xml:space="preserve">12.6453838348389</t>
@@ -1814,109 +1814,109 @@
     <t xml:space="preserve">12.4150505065918</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9083137512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7816276550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8852806091309</t>
+    <t xml:space="preserve">11.908314704895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7816295623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8852787017822</t>
   </si>
   <si>
     <t xml:space="preserve">11.8507299423218</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6223516464233</t>
+    <t xml:space="preserve">12.622350692749</t>
   </si>
   <si>
     <t xml:space="preserve">12.1731986999512</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3459501266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2998838424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4611167907715</t>
+    <t xml:space="preserve">12.3459482192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2998819351196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4611186981201</t>
   </si>
   <si>
     <t xml:space="preserve">11.7470788955688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7010126113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6664628982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1501655578613</t>
+    <t xml:space="preserve">11.7010116577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6664638519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1501636505127</t>
   </si>
   <si>
     <t xml:space="preserve">12.5647678375244</t>
   </si>
   <si>
-    <t xml:space="preserve">13.002405166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8757200241089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7144870758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2212238311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9217882156372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0139226913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6799383163452</t>
+    <t xml:space="preserve">13.0024042129517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8757219314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7144861221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2212200164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9217872619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0139217376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6799364089966</t>
   </si>
   <si>
     <t xml:space="preserve">12.7029685974121</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8526878356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.38245677948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7279586791992</t>
+    <t xml:space="preserve">12.852686882019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3824577331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7279596328735</t>
   </si>
   <si>
     <t xml:space="preserve">13.7049255371094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5782413482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7394752502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7490358352661</t>
+    <t xml:space="preserve">13.5782403945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7394762039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7490348815918</t>
   </si>
   <si>
     <t xml:space="preserve">11.1712427139282</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3420352935791</t>
+    <t xml:space="preserve">10.3420372009277</t>
   </si>
   <si>
     <t xml:space="preserve">10.7566394805908</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0503149032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4015760421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2345857620239</t>
+    <t xml:space="preserve">11.0503168106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4015769958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2345848083496</t>
   </si>
   <si>
     <t xml:space="preserve">9.81802368164062</t>
@@ -1931,28 +1931,28 @@
     <t xml:space="preserve">9.39190483093262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82953929901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8065071105957</t>
+    <t xml:space="preserve">9.82954120635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80650806427002</t>
   </si>
   <si>
     <t xml:space="preserve">9.99077606201172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44372940063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42069816589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07519435882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31508827209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97534465789795</t>
+    <t xml:space="preserve">9.44372844696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42069721221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0751953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31509017944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9753475189209</t>
   </si>
   <si>
     <t xml:space="preserve">7.82562780380249</t>
@@ -1961,28 +1961,28 @@
     <t xml:space="preserve">8.0617208480835</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09051322937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53966617584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6260404586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94851112365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21339702606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72589111328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68362617492676</t>
+    <t xml:space="preserve">8.0905122756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5396671295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62604141235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94851016998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21339511871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72589015960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40918064117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68362426757812</t>
   </si>
   <si>
     <t xml:space="preserve">8.77575874328613</t>
@@ -1991,112 +1991,112 @@
     <t xml:space="preserve">8.39570617675781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6893835067749</t>
+    <t xml:space="preserve">8.68938446044922</t>
   </si>
   <si>
     <t xml:space="preserve">8.80455112457275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91395950317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12702083587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02912712097168</t>
+    <t xml:space="preserve">8.91396045684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12701988220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.029128074646</t>
   </si>
   <si>
     <t xml:space="preserve">9.00033569335938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24218654632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15005397796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10974407196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3190021514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6011629104614</t>
+    <t xml:space="preserve">9.2421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15005302429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10974502563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3190031051636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6011638641357</t>
   </si>
   <si>
     <t xml:space="preserve">10.382345199585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0388011932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7623987197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4802370071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4399271011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0080509185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3074865341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84105777740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2211122512817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78923225402832</t>
+    <t xml:space="preserve">11.0387992858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.762396812439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4802379608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4399280548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0080499649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3074855804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8410587310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2211112976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78923320770264</t>
   </si>
   <si>
     <t xml:space="preserve">10.1289768218994</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5666122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4744787216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3362789154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87560939788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34007835388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22491359710693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91971874237061</t>
+    <t xml:space="preserve">10.5666131973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4744806289673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.336277961731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87560749053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34008026123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2249116897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91971778869629</t>
   </si>
   <si>
     <t xml:space="preserve">8.72969245910645</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60300731658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89092540740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89668464660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46676349639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90440082550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2844543457031</t>
+    <t xml:space="preserve">8.60300827026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89092636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89668369293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46676445007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90439987182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2844514846802</t>
   </si>
   <si>
     <t xml:space="preserve">10.0483589172363</t>
@@ -2105,13 +2105,13 @@
     <t xml:space="preserve">10.1117010116577</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0713930130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0426006317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54162120819092</t>
+    <t xml:space="preserve">10.0713911056519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0425996780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54162216186523</t>
   </si>
   <si>
     <t xml:space="preserve">9.16156959533691</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">9.61648178100586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73740673065186</t>
+    <t xml:space="preserve">9.73740768432617</t>
   </si>
   <si>
     <t xml:space="preserve">9.96198272705078</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">9.50707149505615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48979663848877</t>
+    <t xml:space="preserve">9.48979759216309</t>
   </si>
   <si>
     <t xml:space="preserve">9.78347492218018</t>
@@ -2141,49 +2141,49 @@
     <t xml:space="preserve">9.93319129943848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0253248214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66254806518555</t>
+    <t xml:space="preserve">10.0253257751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66254901885986</t>
   </si>
   <si>
     <t xml:space="preserve">9.54738140106201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6395149230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84681701660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58193206787109</t>
+    <t xml:space="preserve">9.63951396942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84681606292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58193016052246</t>
   </si>
   <si>
     <t xml:space="preserve">9.18460273742676</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5608558654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0349969863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4534025192261</t>
+    <t xml:space="preserve">10.5608539581299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0349979400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4534006118774</t>
   </si>
   <si>
     <t xml:space="preserve">10.8257398605347</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3535537719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1865606307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1001834869385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0598764419556</t>
+    <t xml:space="preserve">10.3535528182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.186559677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1001844406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0598745346069</t>
   </si>
   <si>
     <t xml:space="preserve">9.622239112854</t>
@@ -2195,25 +2195,25 @@
     <t xml:space="preserve">10.4111366271973</t>
   </si>
   <si>
-    <t xml:space="preserve">10.503270149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5781297683716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9293899536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4456853866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08671188354492</t>
+    <t xml:space="preserve">10.5032720565796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5781288146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.929388999939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.445686340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08671092987061</t>
   </si>
   <si>
     <t xml:space="preserve">8.90820217132568</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78151798248291</t>
+    <t xml:space="preserve">8.78151702880859</t>
   </si>
   <si>
     <t xml:space="preserve">8.67210865020752</t>
@@ -2225,22 +2225,22 @@
     <t xml:space="preserve">8.69514083862305</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49935626983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54542446136475</t>
+    <t xml:space="preserve">8.49935722351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54542350769043</t>
   </si>
   <si>
     <t xml:space="preserve">8.5223913192749</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41874122619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47056579589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63755893707275</t>
+    <t xml:space="preserve">8.41873931884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47056484222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63755798339844</t>
   </si>
   <si>
     <t xml:space="preserve">8.56845760345459</t>
@@ -2249,13 +2249,13 @@
     <t xml:space="preserve">8.79879283905029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0406436920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02336883544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00609493255615</t>
+    <t xml:space="preserve">9.04064464569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0233678817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00609302520752</t>
   </si>
   <si>
     <t xml:space="preserve">8.9369945526123</t>
@@ -2264,13 +2264,13 @@
     <t xml:space="preserve">9.17308712005615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21915435791016</t>
+    <t xml:space="preserve">9.21915340423584</t>
   </si>
   <si>
     <t xml:space="preserve">9.24794483184814</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35735607147217</t>
+    <t xml:space="preserve">9.35735416412354</t>
   </si>
   <si>
     <t xml:space="preserve">9.76981639862061</t>
@@ -2279,106 +2279,106 @@
     <t xml:space="preserve">9.46200942993164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19113731384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25885677337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7725191116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61246109008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3169641494751</t>
+    <t xml:space="preserve">9.19113922119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25885581970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77252006530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61245918273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31696510314941</t>
   </si>
   <si>
     <t xml:space="preserve">8.11381244659424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87987661361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48588371276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92296981811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97221946716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91681480407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68288040161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49819612503052</t>
+    <t xml:space="preserve">7.8798770904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48588418960571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92297172546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97222089767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91681432723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68288135528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49819660186768</t>
   </si>
   <si>
     <t xml:space="preserve">7.52897691726685</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44894742965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2027006149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3504490852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22732400894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17807579040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14113998413086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0180139541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96261072158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29504299163818</t>
+    <t xml:space="preserve">7.44894695281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20270013809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35044765472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22732496261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17807531356812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1411395072937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01801490783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96261119842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2950439453125</t>
   </si>
   <si>
     <t xml:space="preserve">6.97492265701294</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89489269256592</t>
+    <t xml:space="preserve">6.89489316940308</t>
   </si>
   <si>
     <t xml:space="preserve">6.93798685073853</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15960788726807</t>
+    <t xml:space="preserve">7.15960741043091</t>
   </si>
   <si>
     <t xml:space="preserve">6.91336107254028</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94414138793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90720462799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06110954284668</t>
+    <t xml:space="preserve">6.94414043426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90720510482788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06110906600952</t>
   </si>
   <si>
     <t xml:space="preserve">7.33813571929932</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64594316482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46741580963135</t>
+    <t xml:space="preserve">7.6459436416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46741533279419</t>
   </si>
   <si>
     <t xml:space="preserve">7.33197975158691</t>
@@ -2387,34 +2387,34 @@
     <t xml:space="preserve">7.19038867950439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39354181289673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42432260513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30735397338867</t>
+    <t xml:space="preserve">7.39354133605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42432165145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30735540390015</t>
   </si>
   <si>
     <t xml:space="preserve">7.60900640487671</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78753662109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28618335723877</t>
+    <t xml:space="preserve">7.78753519058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28618431091309</t>
   </si>
   <si>
     <t xml:space="preserve">8.23693466186523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28002738952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37237071990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16921615600586</t>
+    <t xml:space="preserve">8.28002834320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37236976623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16921710968018</t>
   </si>
   <si>
     <t xml:space="preserve">8.16306114196777</t>
@@ -2423,19 +2423,19 @@
     <t xml:space="preserve">8.08303165435791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14459133148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52627372741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51396179199219</t>
+    <t xml:space="preserve">8.14459037780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52627563476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51396083831787</t>
   </si>
   <si>
     <t xml:space="preserve">8.50780487060547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32927799224854</t>
+    <t xml:space="preserve">8.32927703857422</t>
   </si>
   <si>
     <t xml:space="preserve">8.21230888366699</t>
@@ -2444,64 +2444,64 @@
     <t xml:space="preserve">8.40315055847168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4093074798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2923412322998</t>
+    <t xml:space="preserve">8.40930652618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29233932495117</t>
   </si>
   <si>
     <t xml:space="preserve">8.19384288787842</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24924755096436</t>
+    <t xml:space="preserve">8.24924659729004</t>
   </si>
   <si>
     <t xml:space="preserve">7.98453235626221</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89834547042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13227939605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59399127960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48933601379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45855617523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68633460998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07687377929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71981716156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4920392036438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86756610870361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93528366088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02762508392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96606397628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88603496551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84294080734253</t>
+    <t xml:space="preserve">7.89834594726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13228034973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59399223327637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48933696746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45855712890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68633270263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07687473297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71981859207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49204063415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86756467819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93528318405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02762603759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96606349945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88603353500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84293985366821</t>
   </si>
   <si>
     <t xml:space="preserve">8.15074920654297</t>
@@ -2513,19 +2513,19 @@
     <t xml:space="preserve">8.58783531188965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69249057769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7786750793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00029850006104</t>
+    <t xml:space="preserve">8.69248962402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77867603302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00029754638672</t>
   </si>
   <si>
     <t xml:space="preserve">8.98798561096191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04954719543457</t>
+    <t xml:space="preserve">9.04954624176025</t>
   </si>
   <si>
     <t xml:space="preserve">9.09879589080811</t>
@@ -2537,37 +2537,37 @@
     <t xml:space="preserve">9.22807502746582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43738460540771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44354152679443</t>
+    <t xml:space="preserve">9.4373836517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44354057312012</t>
   </si>
   <si>
     <t xml:space="preserve">9.26501178741455</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41891670227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.431227684021</t>
+    <t xml:space="preserve">9.41891574859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43122863769531</t>
   </si>
   <si>
     <t xml:space="preserve">9.20960807800293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11726379394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20345211029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42507266998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24038791656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06185817718506</t>
+    <t xml:space="preserve">9.11726570129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20345020294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42507171630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24038696289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06185913085938</t>
   </si>
   <si>
     <t xml:space="preserve">8.8587064743042</t>
@@ -2579,124 +2579,124 @@
     <t xml:space="preserve">8.9818286895752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66170883178711</t>
+    <t xml:space="preserve">8.66170978546143</t>
   </si>
   <si>
     <t xml:space="preserve">8.92026805877686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06801605224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32041835784912</t>
+    <t xml:space="preserve">9.06801414489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3204174041748</t>
   </si>
   <si>
     <t xml:space="preserve">9.27116870880127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29579257965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40044784545898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47432136535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51741504669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46816539764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3019495010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40660285949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50510120391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73287963867188</t>
+    <t xml:space="preserve">9.29579448699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4004487991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47432231903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51741409301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46816635131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30194854736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40660381317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50510215759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73288154602051</t>
   </si>
   <si>
     <t xml:space="preserve">8.99414157867432</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39429187774658</t>
+    <t xml:space="preserve">9.39429092407227</t>
   </si>
   <si>
     <t xml:space="preserve">9.70209884643555</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74519348144531</t>
+    <t xml:space="preserve">9.745192527771</t>
   </si>
   <si>
     <t xml:space="preserve">9.16035747528076</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96335983276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89564323425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79714393615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74789524078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62477207183838</t>
+    <t xml:space="preserve">8.96336078643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8956413269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79714488983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74789428710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6247730255127</t>
   </si>
   <si>
     <t xml:space="preserve">8.64323997497559</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5447416305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60630226135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49549198150635</t>
+    <t xml:space="preserve">8.54474353790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60630321502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49549388885498</t>
   </si>
   <si>
     <t xml:space="preserve">8.34158802032471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4216194152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36005687713623</t>
+    <t xml:space="preserve">8.42162036895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36005783081055</t>
   </si>
   <si>
     <t xml:space="preserve">8.1999979019165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15690422058105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26155853271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44008731842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44624423980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39083862304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43393135070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80330085754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61861705780029</t>
+    <t xml:space="preserve">8.15690326690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26155948638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44008827209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44624328613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39083957672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43393230438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80329990386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61861610412598</t>
   </si>
   <si>
     <t xml:space="preserve">8.70480251312256</t>
@@ -2705,28 +2705,28 @@
     <t xml:space="preserve">8.79098796844482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71711540222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69864559173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82177066802979</t>
+    <t xml:space="preserve">8.71711444854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69864654541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82176780700684</t>
   </si>
   <si>
     <t xml:space="preserve">8.65555286407471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5016508102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76020622253418</t>
+    <t xml:space="preserve">8.50164890289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7602071762085</t>
   </si>
   <si>
     <t xml:space="preserve">9.12957763671875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11110782623291</t>
+    <t xml:space="preserve">9.11110877990723</t>
   </si>
   <si>
     <t xml:space="preserve">9.05570316314697</t>
@@ -2735,10 +2735,10 @@
     <t xml:space="preserve">9.07417106628418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87717533111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85254859924316</t>
+    <t xml:space="preserve">8.87717437744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8525505065918</t>
   </si>
   <si>
     <t xml:space="preserve">9.27732467651367</t>
@@ -2747,22 +2747,22 @@
     <t xml:space="preserve">9.01876544952393</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82792377471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16651439666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23423290252686</t>
+    <t xml:space="preserve">8.82792568206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16651344299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23423099517822</t>
   </si>
   <si>
     <t xml:space="preserve">9.33273029327393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64669418334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64053726196289</t>
+    <t xml:space="preserve">9.64669322967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64053916931152</t>
   </si>
   <si>
     <t xml:space="preserve">9.58513259887695</t>
@@ -2771,16 +2771,16 @@
     <t xml:space="preserve">9.65285015106201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52357006072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6590051651001</t>
+    <t xml:space="preserve">9.52357196807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65900611877441</t>
   </si>
   <si>
     <t xml:space="preserve">8.90179920196533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0926399230957</t>
+    <t xml:space="preserve">9.09263896942139</t>
   </si>
   <si>
     <t xml:space="preserve">8.46471214294434</t>
@@ -2789,55 +2789,55 @@
     <t xml:space="preserve">8.00300025939941</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5228214263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55014944076538</t>
+    <t xml:space="preserve">7.52281999588013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55014848709106</t>
   </si>
   <si>
     <t xml:space="preserve">6.29774570465088</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27927732467651</t>
+    <t xml:space="preserve">6.27927780151367</t>
   </si>
   <si>
     <t xml:space="preserve">5.39894723892212</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65134954452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34354209899902</t>
+    <t xml:space="preserve">5.6513500213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34354257583618</t>
   </si>
   <si>
     <t xml:space="preserve">5.18348217010498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19579410552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17732524871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47897720336914</t>
+    <t xml:space="preserve">5.19579362869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17732572555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4789776802063</t>
   </si>
   <si>
     <t xml:space="preserve">5.30352640151978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55900716781616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58671045303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69444227218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62364721298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38971328735352</t>
+    <t xml:space="preserve">5.55900764465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58670949935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6944432258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62364768981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38971281051636</t>
   </si>
   <si>
     <t xml:space="preserve">5.50975799560547</t>
@@ -2846,13 +2846,13 @@
     <t xml:space="preserve">5.48205518722534</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42665004730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50360202789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55592918395996</t>
+    <t xml:space="preserve">5.4266505241394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50360155105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55592966079712</t>
   </si>
   <si>
     <t xml:space="preserve">5.68213033676147</t>
@@ -2861,97 +2861,97 @@
     <t xml:space="preserve">5.66058349609375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68828725814819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55285167694092</t>
+    <t xml:space="preserve">5.68828678131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55285120010376</t>
   </si>
   <si>
     <t xml:space="preserve">5.43896198272705</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4912896156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49744606018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23273134231567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12499761581421</t>
+    <t xml:space="preserve">5.49129009246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49744558334351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23273086547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12499856948853</t>
   </si>
   <si>
     <t xml:space="preserve">5.25119972229004</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53438282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6451940536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49436855316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29429244995117</t>
+    <t xml:space="preserve">5.53438234329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64519309997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49436807632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29429292678833</t>
   </si>
   <si>
     <t xml:space="preserve">5.34969806671143</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31583976745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20810604095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29121446609497</t>
+    <t xml:space="preserve">5.3158392906189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20810699462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29121541976929</t>
   </si>
   <si>
     <t xml:space="preserve">5.21734046936035</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14654541015625</t>
+    <t xml:space="preserve">5.14654493331909</t>
   </si>
   <si>
     <t xml:space="preserve">5.06959342956543</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97417259216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9433913230896</t>
+    <t xml:space="preserve">4.97417306900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94339179992676</t>
   </si>
   <si>
     <t xml:space="preserve">4.92492341995239</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70945835113525</t>
+    <t xml:space="preserve">4.7094578742981</t>
   </si>
   <si>
     <t xml:space="preserve">4.58017873764038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48167991638184</t>
+    <t xml:space="preserve">4.48168039321899</t>
   </si>
   <si>
     <t xml:space="preserve">4.49399280548096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74023818969727</t>
+    <t xml:space="preserve">4.74023866653442</t>
   </si>
   <si>
     <t xml:space="preserve">4.93107986450195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07882738113403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16809225082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.106529712677</t>
+    <t xml:space="preserve">5.07882785797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16809177398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10653018951416</t>
   </si>
   <si>
     <t xml:space="preserve">5.14038896560669</t>
@@ -2960,40 +2960,40 @@
     <t xml:space="preserve">5.45127391815186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65750503540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95300102233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3777756690979</t>
+    <t xml:space="preserve">5.65750551223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95300149917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37777614593506</t>
   </si>
   <si>
     <t xml:space="preserve">5.9837818145752</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79909753799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.40202474594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36201047897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50668001174927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59594488143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54053926467896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45743131637573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31891822814941</t>
+    <t xml:space="preserve">5.79909706115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40202522277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36201095581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50667953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59594392776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54053831100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45743083953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31891775131226</t>
   </si>
   <si>
     <t xml:space="preserve">5.26966857910156</t>
@@ -3002,16 +3002,16 @@
     <t xml:space="preserve">5.13731098175049</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06035947799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11576366424561</t>
+    <t xml:space="preserve">5.06035852432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11576414108276</t>
   </si>
   <si>
     <t xml:space="preserve">5.22965335845947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26351261138916</t>
+    <t xml:space="preserve">5.263512134552</t>
   </si>
   <si>
     <t xml:space="preserve">5.24812126159668</t>
@@ -3023,19 +3023,19 @@
     <t xml:space="preserve">5.4758996963501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58363103866577</t>
+    <t xml:space="preserve">5.58363151550293</t>
   </si>
   <si>
     <t xml:space="preserve">5.52207136154175</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61133527755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59286546707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92837715148926</t>
+    <t xml:space="preserve">5.61133480072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59286594390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9283766746521</t>
   </si>
   <si>
     <t xml:space="preserve">6.04226493835449</t>
@@ -3047,85 +3047,85 @@
     <t xml:space="preserve">5.89759588241577</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76831674575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63288068771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50052404403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33738613128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3343071937561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52822589874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5374608039856</t>
+    <t xml:space="preserve">5.7683162689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63288116455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50052356719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33738565444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33430814743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52822637557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.53746128082275</t>
   </si>
   <si>
     <t xml:space="preserve">5.41125965118408</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6482720375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62672472000122</t>
+    <t xml:space="preserve">5.64827156066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62672519683838</t>
   </si>
   <si>
     <t xml:space="preserve">5.65442800521851</t>
   </si>
   <si>
-    <t xml:space="preserve">5.543616771698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51591348648071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61441230773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46050882339478</t>
+    <t xml:space="preserve">5.54361724853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51591444015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61441278457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46050930023193</t>
   </si>
   <si>
     <t xml:space="preserve">5.47282123565674</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51899290084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36816644668579</t>
+    <t xml:space="preserve">5.51899194717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36816596984863</t>
   </si>
   <si>
     <t xml:space="preserve">5.32199573516846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31276178359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42972850799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43280601501465</t>
+    <t xml:space="preserve">5.31276035308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42972803115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43280553817749</t>
   </si>
   <si>
     <t xml:space="preserve">5.39279174804688</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42049360275269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59902334213257</t>
+    <t xml:space="preserve">5.42049407958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59902286529541</t>
   </si>
   <si>
     <t xml:space="preserve">5.52514839172363</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43588352203369</t>
+    <t xml:space="preserve">5.43588399887085</t>
   </si>
   <si>
     <t xml:space="preserve">5.24196577072144</t>
@@ -3134,13 +3134,13 @@
     <t xml:space="preserve">5.13115453720093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08190536499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17116928100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04804563522339</t>
+    <t xml:space="preserve">5.08190488815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17116975784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04804611206055</t>
   </si>
   <si>
     <t xml:space="preserve">5.06343698501587</t>
@@ -3152,13 +3152,13 @@
     <t xml:space="preserve">4.96493816375732</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97725105285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08498382568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01418828964233</t>
+    <t xml:space="preserve">4.97725009918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08498430252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01418781280518</t>
   </si>
   <si>
     <t xml:space="preserve">5.06651449203491</t>
@@ -3167,13 +3167,13 @@
     <t xml:space="preserve">5.04496812820435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96801662445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82950258255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87567472457886</t>
+    <t xml:space="preserve">4.96801614761353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82950305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87567377090454</t>
   </si>
   <si>
     <t xml:space="preserve">4.83258104324341</t>
@@ -3182,10 +3182,10 @@
     <t xml:space="preserve">4.82642507553101</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86336231231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95262622833252</t>
+    <t xml:space="preserve">4.86336278915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95262670516968</t>
   </si>
   <si>
     <t xml:space="preserve">4.79872274398804</t>
@@ -3194,19 +3194,19 @@
     <t xml:space="preserve">4.75562906265259</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68483304977417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58325719833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5924916267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29084014892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1523265838623</t>
+    <t xml:space="preserve">4.68483400344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58325672149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59249114990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29083967208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15232610702515</t>
   </si>
   <si>
     <t xml:space="preserve">4.23851203918457</t>
@@ -3221,34 +3221,34 @@
     <t xml:space="preserve">4.6632866859436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59556865692139</t>
+    <t xml:space="preserve">4.5955696105957</t>
   </si>
   <si>
     <t xml:space="preserve">4.56171035766602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89106464385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90029907226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00495433807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98340654373169</t>
+    <t xml:space="preserve">4.89106416702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90029859542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00495338439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98340702056885</t>
   </si>
   <si>
     <t xml:space="preserve">5.38663530349731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56208515167236</t>
+    <t xml:space="preserve">5.56208562850952</t>
   </si>
   <si>
     <t xml:space="preserve">5.57747602462769</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78370761871338</t>
+    <t xml:space="preserve">5.78370666503906</t>
   </si>
   <si>
     <t xml:space="preserve">5.71906757354736</t>
@@ -3260,82 +3260,82 @@
     <t xml:space="preserve">5.700599193573</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62056922912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87912750244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99609518051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01456260681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03918790817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9191427230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89451789855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8360333442688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7652382850647</t>
+    <t xml:space="preserve">5.62056970596313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87912797927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99609422683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01456356048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03918743133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91914224624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89451742172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83603382110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76523876190186</t>
   </si>
   <si>
     <t xml:space="preserve">5.81140899658203</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80833148956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74984884262085</t>
+    <t xml:space="preserve">5.8083324432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74984836578369</t>
   </si>
   <si>
     <t xml:space="preserve">5.74676990509033</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77447319030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6051778793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66673994064331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7036771774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69752073287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73445701599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72214651107788</t>
+    <t xml:space="preserve">5.77447271347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60517835617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66674089431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70367670059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6975212097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73445796966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72214460372925</t>
   </si>
   <si>
     <t xml:space="preserve">5.68520879745483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45435285568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46358776092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37740135192871</t>
+    <t xml:space="preserve">5.45435237884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46358680725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37740039825439</t>
   </si>
   <si>
     <t xml:space="preserve">5.28813695907593</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10960865020752</t>
+    <t xml:space="preserve">5.10960817337036</t>
   </si>
   <si>
     <t xml:space="preserve">5.20502853393555</t>
@@ -3344,106 +3344,106 @@
     <t xml:space="preserve">5.15577936172485</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44819641113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78062915802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95915746688843</t>
+    <t xml:space="preserve">5.44819736480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78062963485718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95915842056274</t>
   </si>
   <si>
     <t xml:space="preserve">6.08843660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43318033218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35315036773682</t>
+    <t xml:space="preserve">6.43318128585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35315084457397</t>
   </si>
   <si>
     <t xml:space="preserve">6.42702484130859</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34699583053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34083938598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26696491241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3223705291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37162017822266</t>
+    <t xml:space="preserve">6.34699630737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34083843231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26696538925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32237005233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3716197013855</t>
   </si>
   <si>
     <t xml:space="preserve">6.56861734390259</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4762749671936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63633394241333</t>
+    <t xml:space="preserve">6.47627449035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63633489608765</t>
   </si>
   <si>
     <t xml:space="preserve">6.50705528259277</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52552366256714</t>
+    <t xml:space="preserve">6.52552461624146</t>
   </si>
   <si>
     <t xml:space="preserve">6.45780563354492</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86411142349243</t>
+    <t xml:space="preserve">6.86411190032959</t>
   </si>
   <si>
     <t xml:space="preserve">6.84564352035522</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88873624801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06726598739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12267017364502</t>
+    <t xml:space="preserve">6.8887357711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06726455688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12266969680786</t>
   </si>
   <si>
     <t xml:space="preserve">7.03648471832275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05495357513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82101821899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85179948806763</t>
+    <t xml:space="preserve">7.05495262145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82101964950562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85179901123047</t>
   </si>
   <si>
     <t xml:space="preserve">6.90104961395264</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99954700469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01186084747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92567300796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96876573562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99339151382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80870723724365</t>
+    <t xml:space="preserve">6.99954748153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01186037063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92567253112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96876764297485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99339199066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80870676040649</t>
   </si>
   <si>
     <t xml:space="preserve">7.13498306274414</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">7.07957744598389</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04263973236084</t>
+    <t xml:space="preserve">7.04264068603516</t>
   </si>
   <si>
     <t xml:space="preserve">7.00570344924927</t>
@@ -3461,85 +3461,85 @@
     <t xml:space="preserve">6.74098920822144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91951656341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10420179367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15345144271851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11035871505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08573389053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11651468276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16576528549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57206916809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3258228302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72597360610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03378105163574</t>
+    <t xml:space="preserve">6.91951704025269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10420227050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15345191955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11035919189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08573246002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1165132522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16576433181763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57207012176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32582330703735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72597408294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03378009796143</t>
   </si>
   <si>
     <t xml:space="preserve">8.05840587615967</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99684476852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86140966415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79369020462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66441059112549</t>
+    <t xml:space="preserve">7.99684381484985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86140918731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79369068145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6644115447998</t>
   </si>
   <si>
     <t xml:space="preserve">7.83062887191772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91065835952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.947594165802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01531314849854</t>
+    <t xml:space="preserve">7.9106593132019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94759368896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01531219482422</t>
   </si>
   <si>
     <t xml:space="preserve">7.97837591171265</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09534358978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75675487518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58168029785156</t>
+    <t xml:space="preserve">8.0953426361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75675582885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58167934417725</t>
   </si>
   <si>
     <t xml:space="preserve">8.47702407836914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23077869415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18152904510498</t>
+    <t xml:space="preserve">8.23077774047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18153095245361</t>
   </si>
   <si>
     <t xml:space="preserve">8.10149955749512</t>
@@ -3548,37 +3548,37 @@
     <t xml:space="preserve">7.89218950271606</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36621475219727</t>
+    <t xml:space="preserve">8.36621379852295</t>
   </si>
   <si>
     <t xml:space="preserve">7.83678436279297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95375061035156</t>
+    <t xml:space="preserve">7.95375108718872</t>
   </si>
   <si>
     <t xml:space="preserve">8.53242969512939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55089855194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55705547332764</t>
+    <t xml:space="preserve">8.55089664459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55705451965332</t>
   </si>
   <si>
     <t xml:space="preserve">8.6370849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56936550140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56321048736572</t>
+    <t xml:space="preserve">8.56936645507812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56321144104004</t>
   </si>
   <si>
     <t xml:space="preserve">8.6309289932251</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75405120849609</t>
+    <t xml:space="preserve">8.75405216217041</t>
   </si>
   <si>
     <t xml:space="preserve">9.01261043548584</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">8.96951770782471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92642307281494</t>
+    <t xml:space="preserve">8.92642402648926</t>
   </si>
   <si>
     <t xml:space="preserve">8.93873691558838</t>
@@ -3596,13 +3596,13 @@
     <t xml:space="preserve">9.00645351409912</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76636505126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91411113739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03723430633545</t>
+    <t xml:space="preserve">8.76636409759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91411018371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03723526000977</t>
   </si>
   <si>
     <t xml:space="preserve">9.02492237091064</t>
@@ -3611,61 +3611,61 @@
     <t xml:space="preserve">9.10495281219482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33888721466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56050682067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60360050201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83137798309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90525245666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94218826293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75134944915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2438402175903</t>
+    <t xml:space="preserve">9.33888626098633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56050777435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60360145568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83137893676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90525341033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94219017028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75134754180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2438411712646</t>
   </si>
   <si>
     <t xml:space="preserve">10.305401802063</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5824289321899</t>
+    <t xml:space="preserve">10.5824308395386</t>
   </si>
   <si>
     <t xml:space="preserve">10.0530004501343</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4408369064331</t>
+    <t xml:space="preserve">10.4408388137817</t>
   </si>
   <si>
     <t xml:space="preserve">10.0837812423706</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2930908203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1638107299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1453409194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2992448806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1699676513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4777746200562</t>
+    <t xml:space="preserve">10.2930898666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1638097763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1453418731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2992458343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1699686050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4777755737305</t>
   </si>
   <si>
     <t xml:space="preserve">10.4716196060181</t>
@@ -3674,7 +3674,7 @@
     <t xml:space="preserve">10.7151441574097</t>
   </si>
   <si>
-    <t xml:space="preserve">10.688817024231</t>
+    <t xml:space="preserve">10.6888160705566</t>
   </si>
   <si>
     <t xml:space="preserve">10.5571823120117</t>
@@ -3683,19 +3683,19 @@
     <t xml:space="preserve">10.3860549926758</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4782009124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5703439712524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5111093521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5242729187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6559085845947</t>
+    <t xml:space="preserve">10.4781999588013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5703458786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5111103057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5242719650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6559076309204</t>
   </si>
   <si>
     <t xml:space="preserve">10.7612171173096</t>
@@ -3704,121 +3704,121 @@
     <t xml:space="preserve">10.9520883560181</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0179061889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.037652015686</t>
+    <t xml:space="preserve">11.0179052352905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0376529693604</t>
   </si>
   <si>
     <t xml:space="preserve">11.1232147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0903072357178</t>
+    <t xml:space="preserve">11.0903062820435</t>
   </si>
   <si>
     <t xml:space="preserve">10.9257621765137</t>
   </si>
   <si>
-    <t xml:space="preserve">11.149543762207</t>
+    <t xml:space="preserve">11.1495418548584</t>
   </si>
   <si>
     <t xml:space="preserve">11.1297969818115</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0705595016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9849977493286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7217273712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6032552719116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3070735931396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4189653396606</t>
+    <t xml:space="preserve">11.0705604553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9849967956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7217264175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6032562255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.307074546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4189643859863</t>
   </si>
   <si>
     <t xml:space="preserve">10.0438032150269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0043134689331</t>
+    <t xml:space="preserve">10.0043125152588</t>
   </si>
   <si>
     <t xml:space="preserve">9.99114799499512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49093341827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61598682403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71471309661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1688566207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.037220954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95823955535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.320237159729</t>
+    <t xml:space="preserve">9.49093246459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61598587036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71471405029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1688556671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0372219085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95823860168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3202381134033</t>
   </si>
   <si>
     <t xml:space="preserve">10.4650363922119</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3531465530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4387092590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3926382064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3004913330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0569648742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2215099334717</t>
+    <t xml:space="preserve">10.3531455993652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4387083053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3926362991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3004922866821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0569658279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.221510887146</t>
   </si>
   <si>
     <t xml:space="preserve">10.517689704895</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5045280456543</t>
+    <t xml:space="preserve">10.50452709198</t>
   </si>
   <si>
     <t xml:space="preserve">11.1890335083008</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2351036071777</t>
+    <t xml:space="preserve">11.2351045608521</t>
   </si>
   <si>
     <t xml:space="preserve">11.5115394592285</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6431770324707</t>
+    <t xml:space="preserve">11.6431751251221</t>
   </si>
   <si>
     <t xml:space="preserve">11.5641946792603</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3667421340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5378694534302</t>
+    <t xml:space="preserve">11.3667430877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5378684997559</t>
   </si>
   <si>
     <t xml:space="preserve">11.4983777999878</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">11.8208827972412</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8735389709473</t>
+    <t xml:space="preserve">11.8735399246216</t>
   </si>
   <si>
     <t xml:space="preserve">11.9985933303833</t>
@@ -3839,22 +3839,22 @@
     <t xml:space="preserve">12.1433916091919</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7353200912476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6958303451538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0775747299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9656848907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.281177520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6563377380371</t>
+    <t xml:space="preserve">11.7353229522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6958312988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0775737762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9656839370728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2811765670776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6563386917114</t>
   </si>
   <si>
     <t xml:space="preserve">11.7616491317749</t>
@@ -3863,91 +3863,91 @@
     <t xml:space="preserve">11.7813940048218</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6760845184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6168489456177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0315008163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8801202774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7945556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1236457824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6370267868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5058221817017</t>
+    <t xml:space="preserve">11.676082611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6168479919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0315017700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8801183700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7945575714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.123646736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6370258331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.505820274353</t>
   </si>
   <si>
     <t xml:space="preserve">13.6242933273315</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2166538238525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2693071365356</t>
+    <t xml:space="preserve">14.2166528701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2693090438843</t>
   </si>
   <si>
     <t xml:space="preserve">14.0455284118652</t>
   </si>
   <si>
-    <t xml:space="preserve">14.085018157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.295205116272</t>
+    <t xml:space="preserve">14.0850172042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2952032089233</t>
   </si>
   <si>
     <t xml:space="preserve">12.9661159515381</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0709924697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6962614059448</t>
+    <t xml:space="preserve">12.0709915161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6962623596191</t>
   </si>
   <si>
     <t xml:space="preserve">12.4658994674683</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7419033050537</t>
+    <t xml:space="preserve">11.7419013977051</t>
   </si>
   <si>
     <t xml:space="preserve">11.9722661972046</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7550668716431</t>
+    <t xml:space="preserve">11.7550659179688</t>
   </si>
   <si>
     <t xml:space="preserve">10.7085628509521</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2412548065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1956157684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4979457855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8204536437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2943420410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5839414596558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1894655227661</t>
+    <t xml:space="preserve">10.2412567138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1956148147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4979448318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8204517364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2943410873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5839385986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1894645690918</t>
   </si>
   <si>
     <t xml:space="preserve">12.1038999557495</t>
@@ -3956,28 +3956,28 @@
     <t xml:space="preserve">12.1302280426025</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4329900741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3737545013428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2684450149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4066638946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4395732879639</t>
+    <t xml:space="preserve">12.4329891204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3737535476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2684440612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4066610336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4395713806152</t>
   </si>
   <si>
     <t xml:space="preserve">12.2881908416748</t>
   </si>
   <si>
-    <t xml:space="preserve">12.393500328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6826686859131</t>
+    <t xml:space="preserve">12.3935012817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6826667785645</t>
   </si>
   <si>
     <t xml:space="preserve">12.0380840301514</t>
@@ -3989,10 +3989,10 @@
     <t xml:space="preserve">11.9393548965454</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6629219055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9525194168091</t>
+    <t xml:space="preserve">11.6629209518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9525184631348</t>
   </si>
   <si>
     <t xml:space="preserve">11.3799057006836</t>
@@ -4001,31 +4001,31 @@
     <t xml:space="preserve">11.5049591064453</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3469944000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8007078170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0244884490967</t>
+    <t xml:space="preserve">11.3469953536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8007068634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0244874954224</t>
   </si>
   <si>
     <t xml:space="preserve">11.4457225799561</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7089948654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4588861465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.974048614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9879703521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9183568954468</t>
+    <t xml:space="preserve">11.7089939117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4588871002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9740476608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9879722595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9183549880981</t>
   </si>
   <si>
     <t xml:space="preserve">12.1550512313843</t>
@@ -4037,40 +4037,40 @@
     <t xml:space="preserve">12.1341667175293</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8208913803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8000078201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7791213989258</t>
+    <t xml:space="preserve">11.8208923339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8000068664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7791223526001</t>
   </si>
   <si>
     <t xml:space="preserve">11.751275062561</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7582368850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5563497543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4031925201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1804189682007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5121011734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97605228424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0804767608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4355220794678</t>
+    <t xml:space="preserve">11.7582359313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5563488006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4031915664673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.180419921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5121021270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97605323791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0804777145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4355211257935</t>
   </si>
   <si>
     <t xml:space="preserve">9.95516777038574</t>
@@ -4082,16 +4082,16 @@
     <t xml:space="preserve">10.1640176773071</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0038995742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9969367980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74631977081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98997783660889</t>
+    <t xml:space="preserve">10.0038986206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99693775177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74631786346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98997688293457</t>
   </si>
   <si>
     <t xml:space="preserve">9.927321434021</t>
@@ -4100,25 +4100,25 @@
     <t xml:space="preserve">9.89947509765625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71847152709961</t>
+    <t xml:space="preserve">9.71847248077393</t>
   </si>
   <si>
     <t xml:space="preserve">9.40519714355469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2868480682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23811817169189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86218738555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79257202148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98053550720215</t>
+    <t xml:space="preserve">9.28684902191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23811626434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86218643188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79257106781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98053646087646</t>
   </si>
   <si>
     <t xml:space="preserve">9.23115634918213</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">8.95965099334717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00838279724121</t>
+    <t xml:space="preserve">9.00838184356689</t>
   </si>
   <si>
     <t xml:space="preserve">8.62549209594727</t>
@@ -4136,19 +4136,19 @@
     <t xml:space="preserve">8.20779228210449</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40271854400635</t>
+    <t xml:space="preserve">8.40271759033203</t>
   </si>
   <si>
     <t xml:space="preserve">8.54195213317871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76472473144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79953193664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74384021759033</t>
+    <t xml:space="preserve">8.764723777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79953384399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74384117126465</t>
   </si>
   <si>
     <t xml:space="preserve">8.81345653533936</t>
@@ -4172,10 +4172,10 @@
     <t xml:space="preserve">9.2172327041626</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09888553619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47481346130371</t>
+    <t xml:space="preserve">9.09888362884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47481250762939</t>
   </si>
   <si>
     <t xml:space="preserve">9.53746795654297</t>
@@ -4184,49 +4184,49 @@
     <t xml:space="preserve">9.50266075134277</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25900268554688</t>
+    <t xml:space="preserve">9.25900173187256</t>
   </si>
   <si>
     <t xml:space="preserve">9.01534461975098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11280727386475</t>
+    <t xml:space="preserve">9.11280632019043</t>
   </si>
   <si>
     <t xml:space="preserve">9.33557987213135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49569892883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03623104095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66726016998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77864837646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75776386260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63245296478271</t>
+    <t xml:space="preserve">9.49569797515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03622817993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66726112365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77864933013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75776290893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63245391845703</t>
   </si>
   <si>
     <t xml:space="preserve">8.3957576751709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33310222625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38879489898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31917858123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10336685180664</t>
+    <t xml:space="preserve">8.33310127258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38879585266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31917953491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10336780548096</t>
   </si>
   <si>
     <t xml:space="preserve">8.27044773101807</t>
@@ -4235,22 +4235,22 @@
     <t xml:space="preserve">8.04071235656738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99894332885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8805947303772</t>
+    <t xml:space="preserve">7.99894285202026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88059425354004</t>
   </si>
   <si>
     <t xml:space="preserve">7.95021104812622</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1312141418457</t>
+    <t xml:space="preserve">8.13121509552002</t>
   </si>
   <si>
     <t xml:space="preserve">8.58372116088867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59068393707275</t>
+    <t xml:space="preserve">8.59068298339844</t>
   </si>
   <si>
     <t xml:space="preserve">8.70903205871582</t>
@@ -4259,13 +4259,13 @@
     <t xml:space="preserve">8.51410484313965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46537303924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17994594573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22171497344971</t>
+    <t xml:space="preserve">8.46537399291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17994689941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22171688079834</t>
   </si>
   <si>
     <t xml:space="preserve">7.94324922561646</t>
@@ -4274,16 +4274,16 @@
     <t xml:space="preserve">7.95717239379883</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82490015029907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74136161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49074172973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92236471176147</t>
+    <t xml:space="preserve">7.82490158081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74136066436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49074220657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92236423492432</t>
   </si>
   <si>
     <t xml:space="preserve">8.01286602020264</t>
@@ -4292,40 +4292,40 @@
     <t xml:space="preserve">7.9293270111084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84578561782837</t>
+    <t xml:space="preserve">7.84578657150269</t>
   </si>
   <si>
     <t xml:space="preserve">7.75528573989868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6856689453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76920795440674</t>
+    <t xml:space="preserve">7.68566799163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76920890808105</t>
   </si>
   <si>
     <t xml:space="preserve">7.6578221321106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66478300094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88755750656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86667156219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90147972106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98502016067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07552051544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15209865570068</t>
+    <t xml:space="preserve">7.66478395462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88755464553833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86667060852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90148019790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98501920700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07552242279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.152099609375</t>
   </si>
   <si>
     <t xml:space="preserve">8.2982931137085</t>
@@ -4334,13 +4334,13 @@
     <t xml:space="preserve">8.45841217041016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49322032928467</t>
+    <t xml:space="preserve">8.49322128295898</t>
   </si>
   <si>
     <t xml:space="preserve">9.10584545135498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07103824615479</t>
+    <t xml:space="preserve">9.07103729248047</t>
   </si>
   <si>
     <t xml:space="preserve">9.37038898468018</t>
@@ -4349,13 +4349,13 @@
     <t xml:space="preserve">9.56531524658203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69062519073486</t>
+    <t xml:space="preserve">9.69062614440918</t>
   </si>
   <si>
     <t xml:space="preserve">9.6627779006958</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62797069549561</t>
+    <t xml:space="preserve">9.62796974182129</t>
   </si>
   <si>
     <t xml:space="preserve">9.52354621887207</t>
@@ -4370,7 +4370,7 @@
     <t xml:space="preserve">9.81434440612793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8293285369873</t>
+    <t xml:space="preserve">9.82932758331299</t>
   </si>
   <si>
     <t xml:space="preserve">9.85929584503174</t>
@@ -4379,10 +4379,10 @@
     <t xml:space="preserve">9.85180282592773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88926124572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76190090179443</t>
+    <t xml:space="preserve">9.88926315307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76189994812012</t>
   </si>
   <si>
     <t xml:space="preserve">9.77688503265381</t>
@@ -4391,28 +4391,28 @@
     <t xml:space="preserve">9.70945739746094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55962085723877</t>
+    <t xml:space="preserve">9.55962181091309</t>
   </si>
   <si>
     <t xml:space="preserve">9.39480018615723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4097843170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56711387634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48470211029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67199802398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69447326660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52216053009033</t>
+    <t xml:space="preserve">9.40978336334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56711292266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48470306396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67199993133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69447422027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52216148376465</t>
   </si>
   <si>
     <t xml:space="preserve">9.60457229614258</t>
@@ -4421,31 +4421,31 @@
     <t xml:space="preserve">10.0166244506836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84431171417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94919776916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88177108764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96418190002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97167301177979</t>
+    <t xml:space="preserve">9.84431076049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94919681549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88177013397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9641809463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97167491912842</t>
   </si>
   <si>
     <t xml:space="preserve">10.0690670013428</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2263975143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4736280441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5035953521729</t>
+    <t xml:space="preserve">10.2263965606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4736270904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5035972595215</t>
   </si>
   <si>
     <t xml:space="preserve">10.5110874176025</t>
@@ -4454,13 +4454,13 @@
     <t xml:space="preserve">10.6609239578247</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6834001541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.743335723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8182535171509</t>
+    <t xml:space="preserve">10.6834011077881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7433347702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8182544708252</t>
   </si>
   <si>
     <t xml:space="preserve">10.8032712936401</t>
@@ -4475,34 +4475,34 @@
     <t xml:space="preserve">10.6534337997437</t>
   </si>
   <si>
-    <t xml:space="preserve">10.863205909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8482217788696</t>
+    <t xml:space="preserve">10.8632040023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8482208251953</t>
   </si>
   <si>
     <t xml:space="preserve">10.6759080886841</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8781890869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9231414794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2602739334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5000143051147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5824241638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7772121429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7172775268555</t>
+    <t xml:space="preserve">10.8781900405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9231405258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2602729797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5000152587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5824251174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7772130966187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7172784805298</t>
   </si>
   <si>
     <t xml:space="preserve">11.8071804046631</t>
@@ -4511,16 +4511,16 @@
     <t xml:space="preserve">11.9195594787598</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9120655059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1143474578857</t>
+    <t xml:space="preserve">11.9120664596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1143484115601</t>
   </si>
   <si>
     <t xml:space="preserve">12.2192325592041</t>
   </si>
   <si>
-    <t xml:space="preserve">12.196759223938</t>
+    <t xml:space="preserve">12.1967573165894</t>
   </si>
   <si>
     <t xml:space="preserve">11.9345426559448</t>
@@ -4529,7 +4529,7 @@
     <t xml:space="preserve">11.7921962738037</t>
   </si>
   <si>
-    <t xml:space="preserve">12.286660194397</t>
+    <t xml:space="preserve">12.2866592407227</t>
   </si>
   <si>
     <t xml:space="preserve">12.1218395233154</t>
@@ -4541,34 +4541,34 @@
     <t xml:space="preserve">11.6573438644409</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5224885940552</t>
+    <t xml:space="preserve">11.5224895477295</t>
   </si>
   <si>
     <t xml:space="preserve">11.6798191070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6423597335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7097864151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7322616577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3426856994629</t>
+    <t xml:space="preserve">11.6423587799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7097854614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7322626113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3426847457886</t>
   </si>
   <si>
     <t xml:space="preserve">10.9006643295288</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0954542160034</t>
+    <t xml:space="preserve">11.0954532623291</t>
   </si>
   <si>
     <t xml:space="preserve">10.5785150527954</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5934982299805</t>
+    <t xml:space="preserve">10.5934991836548</t>
   </si>
   <si>
     <t xml:space="preserve">10.563530921936</t>
@@ -4580,16 +4580,16 @@
     <t xml:space="preserve">10.2863311767578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3237895965576</t>
+    <t xml:space="preserve">10.3237905502319</t>
   </si>
   <si>
     <t xml:space="preserve">10.1964292526245</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3387746810913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4661359786987</t>
+    <t xml:space="preserve">10.338773727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4661378860474</t>
   </si>
   <si>
     <t xml:space="preserve">10.4586448669434</t>
@@ -4613,22 +4613,22 @@
     <t xml:space="preserve">11.2078313827515</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3052244186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2452898025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4176034927368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5449638366699</t>
+    <t xml:space="preserve">11.3052253723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2452907562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4176025390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5449657440186</t>
   </si>
   <si>
     <t xml:space="preserve">11.3876361846924</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3277006149292</t>
+    <t xml:space="preserve">11.3277015686035</t>
   </si>
   <si>
     <t xml:space="preserve">11.4026203155518</t>
@@ -4646,19 +4646,19 @@
     <t xml:space="preserve">11.3576679229736</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7807941436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8107614517212</t>
+    <t xml:space="preserve">10.7807960510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8107624053955</t>
   </si>
   <si>
     <t xml:space="preserve">10.7882862091064</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3391141891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2774877548218</t>
+    <t xml:space="preserve">11.3391122817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2774868011475</t>
   </si>
   <si>
     <t xml:space="preserve">11.1003131866455</t>
@@ -4667,16 +4667,16 @@
     <t xml:space="preserve">11.0695009231567</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2389717102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2004547119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9462509155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7844839096069</t>
+    <t xml:space="preserve">11.2389707565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2004556655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9462490081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7844829559326</t>
   </si>
   <si>
     <t xml:space="preserve">10.9539527893066</t>
@@ -4688,13 +4688,13 @@
     <t xml:space="preserve">10.9770622253418</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0386877059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.03098487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9847660064697</t>
+    <t xml:space="preserve">11.038688659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0309839248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9847650527954</t>
   </si>
   <si>
     <t xml:space="preserve">10.8923282623291</t>
@@ -4709,22 +4709,22 @@
     <t xml:space="preserve">10.9154367446899</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8692178726196</t>
+    <t xml:space="preserve">10.8692169189453</t>
   </si>
   <si>
     <t xml:space="preserve">10.8307018280029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.822998046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0155773162842</t>
+    <t xml:space="preserve">10.8229990005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0155782699585</t>
   </si>
   <si>
     <t xml:space="preserve">10.8461084365845</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9000301361084</t>
+    <t xml:space="preserve">10.9000310897827</t>
   </si>
   <si>
     <t xml:space="preserve">11.0463914871216</t>
@@ -4736,13 +4736,13 @@
     <t xml:space="preserve">11.0617971420288</t>
   </si>
   <si>
-    <t xml:space="preserve">11.292893409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4007377624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.416145324707</t>
+    <t xml:space="preserve">11.2928943634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4007396697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4161443710327</t>
   </si>
   <si>
     <t xml:space="preserve">11.2543783187866</t>
@@ -4751,7 +4751,7 @@
     <t xml:space="preserve">11.3699264526367</t>
   </si>
   <si>
-    <t xml:space="preserve">11.246675491333</t>
+    <t xml:space="preserve">11.2466745376587</t>
   </si>
   <si>
     <t xml:space="preserve">11.3622226715088</t>
@@ -4760,55 +4760,55 @@
     <t xml:space="preserve">11.5085830688477</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5856142044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6626482009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8244152069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7858982086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7473821640015</t>
+    <t xml:space="preserve">11.5856151580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6626472473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8244142532349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7858991622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7473812103271</t>
   </si>
   <si>
     <t xml:space="preserve">11.7319755554199</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7088670730591</t>
+    <t xml:space="preserve">11.7088661193848</t>
   </si>
   <si>
     <t xml:space="preserve">11.8167123794556</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0015888214111</t>
+    <t xml:space="preserve">12.0015878677368</t>
   </si>
   <si>
     <t xml:space="preserve">12.271201133728</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3713417053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1325426101685</t>
+    <t xml:space="preserve">12.3713426589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1325416564941</t>
   </si>
   <si>
     <t xml:space="preserve">11.9322595596313</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0092916488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5562181472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4945917129517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2249803543091</t>
+    <t xml:space="preserve">12.0092926025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5562191009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.494592666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2249822616577</t>
   </si>
   <si>
     <t xml:space="preserve">12.3328256607056</t>
@@ -4829,28 +4829,28 @@
     <t xml:space="preserve">12.2866067886353</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2326831817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3636388778687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3020133972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4175615310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.44837474823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5408134460449</t>
+    <t xml:space="preserve">12.232684135437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3636379241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3020143508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4175624847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4483737945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5408115386963</t>
   </si>
   <si>
     <t xml:space="preserve">12.533109664917</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3482332229614</t>
+    <t xml:space="preserve">12.3482322692871</t>
   </si>
   <si>
     <t xml:space="preserve">12.3097162246704</t>
@@ -4859,19 +4859,19 @@
     <t xml:space="preserve">12.0709171295166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9630708694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8783378601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1402454376221</t>
+    <t xml:space="preserve">11.9630718231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8783369064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1402463912964</t>
   </si>
   <si>
     <t xml:space="preserve">12.1171360015869</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9784784317017</t>
+    <t xml:space="preserve">11.978479385376</t>
   </si>
   <si>
     <t xml:space="preserve">11.970775604248</t>
@@ -4880,28 +4880,28 @@
     <t xml:space="preserve">12.0632133483887</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1787633895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2557945251465</t>
+    <t xml:space="preserve">12.1787624359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2557935714722</t>
   </si>
   <si>
     <t xml:space="preserve">12.3944511413574</t>
   </si>
   <si>
-    <t xml:space="preserve">12.409857749939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6101408004761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.317419052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5177021026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6948757171631</t>
+    <t xml:space="preserve">12.4098587036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6101417541504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3174200057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5177040100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6948766708374</t>
   </si>
   <si>
     <t xml:space="preserve">12.9336757659912</t>
@@ -4910,7 +4910,7 @@
     <t xml:space="preserve">12.8412380218506</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6486587524414</t>
+    <t xml:space="preserve">12.6486568450928</t>
   </si>
   <si>
     <t xml:space="preserve">12.6794691085815</t>
@@ -4922,52 +4922,52 @@
     <t xml:space="preserve">12.3867483139038</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1710596084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6164293289185</t>
+    <t xml:space="preserve">12.1710586547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6164283752441</t>
   </si>
   <si>
     <t xml:space="preserve">11.8552274703979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2789039611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4252634048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5793294906616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8874549865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7719078063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8104238510132</t>
+    <t xml:space="preserve">12.2789030075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4252624511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5793285369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8874568939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7719087600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8104248046875</t>
   </si>
   <si>
     <t xml:space="preserve">12.9413785934448</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3419437408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1570672988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2726154327393</t>
+    <t xml:space="preserve">13.3419456481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1570692062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2726173400879</t>
   </si>
   <si>
     <t xml:space="preserve">13.1493654251099</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0954427719116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2880239486694</t>
+    <t xml:space="preserve">13.0954437255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2880229949951</t>
   </si>
   <si>
     <t xml:space="preserve">13.2135105133057</t>
@@ -4976,13 +4976,13 @@
     <t xml:space="preserve">12.9237403869629</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0644865036011</t>
+    <t xml:space="preserve">13.0644855499268</t>
   </si>
   <si>
     <t xml:space="preserve">13.0313692092896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0893249511719</t>
+    <t xml:space="preserve">13.0893239974976</t>
   </si>
   <si>
     <t xml:space="preserve">12.8409490585327</t>
@@ -4991,10 +4991,10 @@
     <t xml:space="preserve">12.8740663528442</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0396490097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9982538223267</t>
+    <t xml:space="preserve">13.0396480560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9982528686523</t>
   </si>
   <si>
     <t xml:space="preserve">13.1886739730835</t>
@@ -5009,13 +5009,13 @@
     <t xml:space="preserve">13.114161491394</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1555576324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4536056518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2963018417358</t>
+    <t xml:space="preserve">13.155556678772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4536066055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2963027954102</t>
   </si>
   <si>
     <t xml:space="preserve">13.1803951263428</t>
@@ -5024,16 +5024,16 @@
     <t xml:space="preserve">13.0479278564453</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9568576812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0727663040161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1307201385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1472768783569</t>
+    <t xml:space="preserve">12.9568567276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0727653503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1307182312012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1472778320312</t>
   </si>
   <si>
     <t xml:space="preserve">13.2631855010986</t>
@@ -5045,13 +5045,13 @@
     <t xml:space="preserve">13.3625345230103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3376979827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8657875061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9651365280151</t>
+    <t xml:space="preserve">13.3376989364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8657865524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9651355743408</t>
   </si>
   <si>
     <t xml:space="preserve">12.9734153747559</t>
@@ -5069,100 +5069,100 @@
     <t xml:space="preserve">13.2549066543579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1389980316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3708152770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3873729705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5777931213379</t>
+    <t xml:space="preserve">13.1389989852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3708143234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3873720169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5777921676636</t>
   </si>
   <si>
     <t xml:space="preserve">13.4867238998413</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8096103668213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.701979637146</t>
+    <t xml:space="preserve">13.809609413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7019786834717</t>
   </si>
   <si>
     <t xml:space="preserve">13.710259437561</t>
   </si>
   <si>
-    <t xml:space="preserve">13.594352722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6191892623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6937026977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9006795883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8592824935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0497026443481</t>
+    <t xml:space="preserve">13.5943508148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6191902160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6937017440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9006805419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8592834472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0497035980225</t>
   </si>
   <si>
     <t xml:space="preserve">14.24840259552</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1159372329712</t>
+    <t xml:space="preserve">14.1159362792969</t>
   </si>
   <si>
     <t xml:space="preserve">13.9917507171631</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9172372817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0248680114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0000295639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9834718704224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1821708679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1242160797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0414257049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0165872573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9669132232666</t>
+    <t xml:space="preserve">13.9172382354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0248670578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0000286102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9834699630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1821699142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1242151260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0414247512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0165882110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9669141769409</t>
   </si>
   <si>
     <t xml:space="preserve">14.2897996902466</t>
   </si>
   <si>
-    <t xml:space="preserve">14.356032371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3891487121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7037582397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8610591888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9521312713623</t>
+    <t xml:space="preserve">14.3560333251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3891496658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7037572860718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8610610961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9521293640137</t>
   </si>
   <si>
     <t xml:space="preserve">15.0266418457031</t>
@@ -5174,37 +5174,37 @@
     <t xml:space="preserve">15.2170629501343</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3578071594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1591081619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2750177383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8131628036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4672145843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1029319763184</t>
+    <t xml:space="preserve">15.3578081130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1591091156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2750196456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8131618499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4672107696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.102933883667</t>
   </si>
   <si>
     <t xml:space="preserve">16.1774444580078</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1608848571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.367862701416</t>
+    <t xml:space="preserve">16.1608867645264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3678646087646</t>
   </si>
   <si>
     <t xml:space="preserve">16.5748424530029</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8563346862793</t>
+    <t xml:space="preserve">16.8563365936279</t>
   </si>
   <si>
     <t xml:space="preserve">16.8066577911377</t>
@@ -5219,7 +5219,7 @@
     <t xml:space="preserve">16.9556827545166</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4358711242676</t>
+    <t xml:space="preserve">17.4358730316162</t>
   </si>
   <si>
     <t xml:space="preserve">17.3365249633789</t>
@@ -5228,7 +5228,7 @@
     <t xml:space="preserve">17.5186653137207</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4524307250977</t>
+    <t xml:space="preserve">17.4524326324463</t>
   </si>
   <si>
     <t xml:space="preserve">17.6511306762695</t>
@@ -5240,19 +5240,19 @@
     <t xml:space="preserve">17.8167133331299</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0881481170654</t>
+    <t xml:space="preserve">17.0881500244141</t>
   </si>
   <si>
     <t xml:space="preserve">17.2040576934814</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9060096740723</t>
+    <t xml:space="preserve">16.9060077667236</t>
   </si>
   <si>
     <t xml:space="preserve">17.1212673187256</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0520191192627</t>
+    <t xml:space="preserve">17.0520210266113</t>
   </si>
   <si>
     <t xml:space="preserve">16.9914283752441</t>
@@ -5267,10 +5267,10 @@
     <t xml:space="preserve">16.8789024353027</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8962135314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8356246948242</t>
+    <t xml:space="preserve">16.8962154388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8356266021729</t>
   </si>
   <si>
     <t xml:space="preserve">16.5586357116699</t>
@@ -5279,7 +5279,7 @@
     <t xml:space="preserve">17.233793258667</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4675025939941</t>
+    <t xml:space="preserve">17.4675006866455</t>
   </si>
   <si>
     <t xml:space="preserve">17.3463172912598</t>
@@ -5294,13 +5294,13 @@
     <t xml:space="preserve">17.3290061950684</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7923431396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0952987670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7230949401855</t>
+    <t xml:space="preserve">16.7923450469971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0953006744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7230987548828</t>
   </si>
   <si>
     <t xml:space="preserve">16.3855209350586</t>
@@ -5309,10 +5309,10 @@
     <t xml:space="preserve">16.7490653991699</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7836894989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8010005950928</t>
+    <t xml:space="preserve">16.7836875915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8009986877441</t>
   </si>
   <si>
     <t xml:space="preserve">17.0000839233398</t>
@@ -5321,7 +5321,7 @@
     <t xml:space="preserve">16.775032043457</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6406154632568</t>
+    <t xml:space="preserve">17.6406173706055</t>
   </si>
   <si>
     <t xml:space="preserve">17.1991691589355</t>
@@ -5330,19 +5330,19 @@
     <t xml:space="preserve">17.0866413116455</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8183135986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7271766662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5194339752197</t>
+    <t xml:space="preserve">16.8183097839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7271747589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5194358825684</t>
   </si>
   <si>
     <t xml:space="preserve">17.7791118621826</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9176063537598</t>
+    <t xml:space="preserve">17.9176044464111</t>
   </si>
   <si>
     <t xml:space="preserve">18.0387859344482</t>
@@ -5372,28 +5372,28 @@
     <t xml:space="preserve">18.4888916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2638378143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4715785980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4196434020996</t>
+    <t xml:space="preserve">18.2638397216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4715766906738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4196453094482</t>
   </si>
   <si>
     <t xml:space="preserve">18.3157730102539</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4542675018311</t>
+    <t xml:space="preserve">18.4542655944824</t>
   </si>
   <si>
     <t xml:space="preserve">18.627384185791</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7312526702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9563045501709</t>
+    <t xml:space="preserve">18.7312545776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9563064575195</t>
   </si>
   <si>
     <t xml:space="preserve">18.7831897735596</t>
@@ -5414,13 +5414,13 @@
     <t xml:space="preserve">17.6059951782227</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9522266387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0734100341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8829803466797</t>
+    <t xml:space="preserve">17.9522285461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0734081268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8829822540283</t>
   </si>
   <si>
     <t xml:space="preserve">18.1426544189453</t>
@@ -5429,40 +5429,40 @@
     <t xml:space="preserve">18.0907230377197</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2292156219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4023323059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3850212097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2811508178711</t>
+    <t xml:space="preserve">18.2292137145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4023303985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3850193023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2811527252197</t>
   </si>
   <si>
     <t xml:space="preserve">18.0041618347168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9349174499512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8483581542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9695377349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2119045257568</t>
+    <t xml:space="preserve">17.9349155426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8483600616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.969539642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2119026184082</t>
   </si>
   <si>
     <t xml:space="preserve">18.436954498291</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5062007904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.610071182251</t>
+    <t xml:space="preserve">18.5062026977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6100730895996</t>
   </si>
   <si>
     <t xml:space="preserve">19.0082416534424</t>
@@ -5489,28 +5489,28 @@
     <t xml:space="preserve">19.3025398254395</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4064102172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5968399047852</t>
+    <t xml:space="preserve">19.4064121246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5968379974365</t>
   </si>
   <si>
     <t xml:space="preserve">19.7180213928223</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7007102966309</t>
+    <t xml:space="preserve">19.7007083892822</t>
   </si>
   <si>
     <t xml:space="preserve">19.6314640045166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9950084686279</t>
+    <t xml:space="preserve">19.9950065612793</t>
   </si>
   <si>
     <t xml:space="preserve">19.8045787811279</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6660842895508</t>
+    <t xml:space="preserve">19.6660861968994</t>
   </si>
   <si>
     <t xml:space="preserve">19.4237232208252</t>
@@ -5525,7 +5525,7 @@
     <t xml:space="preserve">19.3544750213623</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1121120452881</t>
+    <t xml:space="preserve">19.1121101379395</t>
   </si>
   <si>
     <t xml:space="preserve">19.0601768493652</t>
@@ -5534,19 +5534,19 @@
     <t xml:space="preserve">19.0774898529053</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9736194610596</t>
+    <t xml:space="preserve">18.9736175537109</t>
   </si>
   <si>
     <t xml:space="preserve">19.0255527496338</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5449028015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2332916259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3890972137451</t>
+    <t xml:space="preserve">19.5449047088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2332935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3890991210938</t>
   </si>
   <si>
     <t xml:space="preserve">19.3717861175537</t>
@@ -5561,7 +5561,7 @@
     <t xml:space="preserve">18.7999801635742</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1840267181396</t>
+    <t xml:space="preserve">19.184024810791</t>
   </si>
   <si>
     <t xml:space="preserve">19.0560111999512</t>
@@ -5570,16 +5570,16 @@
     <t xml:space="preserve">19.0377235412598</t>
   </si>
   <si>
-    <t xml:space="preserve">18.489086151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2422008514404</t>
+    <t xml:space="preserve">18.4890842437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2421989440918</t>
   </si>
   <si>
     <t xml:space="preserve">18.123327255249</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2879180908203</t>
+    <t xml:space="preserve">18.2879199981689</t>
   </si>
   <si>
     <t xml:space="preserve">18.2513427734375</t>
@@ -5588,10 +5588,10 @@
     <t xml:space="preserve">18.0776081085205</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3610687255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5256633758545</t>
+    <t xml:space="preserve">18.3610706329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5256614685059</t>
   </si>
   <si>
     <t xml:space="preserve">19.3486175537109</t>
@@ -5600,10 +5600,10 @@
     <t xml:space="preserve">19.1108741760254</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9279956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7816925048828</t>
+    <t xml:space="preserve">18.9279975891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7816944122314</t>
   </si>
   <si>
     <t xml:space="preserve">18.8731327056885</t>
@@ -5627,19 +5627,19 @@
     <t xml:space="preserve">19.092586517334</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0743007659912</t>
+    <t xml:space="preserve">19.0742988586426</t>
   </si>
   <si>
     <t xml:space="preserve">19.1657371520996</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3669052124023</t>
+    <t xml:space="preserve">19.366907119751</t>
   </si>
   <si>
     <t xml:space="preserve">19.3851947784424</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7875270843506</t>
+    <t xml:space="preserve">19.7875289916992</t>
   </si>
   <si>
     <t xml:space="preserve">19.5314979553223</t>
@@ -5648,13 +5648,13 @@
     <t xml:space="preserve">20.0069828033447</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7750759124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4824676513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5739097595215</t>
+    <t xml:space="preserve">20.775074005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4824695587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5739078521729</t>
   </si>
   <si>
     <t xml:space="preserve">20.8482265472412</t>
@@ -5666,22 +5666,22 @@
     <t xml:space="preserve">20.2995891571045</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3361644744873</t>
+    <t xml:space="preserve">20.3361663818359</t>
   </si>
   <si>
     <t xml:space="preserve">20.171573638916</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0435600280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7692413330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6046504974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2388916015625</t>
+    <t xml:space="preserve">20.0435581207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7692394256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6046485900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2388896942139</t>
   </si>
   <si>
     <t xml:space="preserve">19.1474514007568</t>
@@ -5693,7 +5693,7 @@
     <t xml:space="preserve">19.4034805297852</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2206039428711</t>
+    <t xml:space="preserve">19.2206020355225</t>
   </si>
   <si>
     <t xml:space="preserve">19.5680732727051</t>
@@ -5711,7 +5711,7 @@
     <t xml:space="preserve">19.4400577545166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5132083892822</t>
+    <t xml:space="preserve">19.5132102966309</t>
   </si>
   <si>
     <t xml:space="preserve">19.6412239074707</t>
@@ -5723,25 +5723,25 @@
     <t xml:space="preserve">19.9521198272705</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0618457794189</t>
+    <t xml:space="preserve">20.0618476867676</t>
   </si>
   <si>
     <t xml:space="preserve">20.3910293579102</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2447261810303</t>
+    <t xml:space="preserve">20.2447242736816</t>
   </si>
   <si>
     <t xml:space="preserve">20.4276065826416</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6287727355957</t>
+    <t xml:space="preserve">20.6287708282471</t>
   </si>
   <si>
     <t xml:space="preserve">20.4093170166016</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3178768157959</t>
+    <t xml:space="preserve">20.3178787231445</t>
   </si>
   <si>
     <t xml:space="preserve">19.6229362487793</t>
@@ -5753,7 +5753,7 @@
     <t xml:space="preserve">19.2571792602539</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0809154510498</t>
+    <t xml:space="preserve">17.0809173583984</t>
   </si>
   <si>
     <t xml:space="preserve">16.7425880432129</t>
@@ -5762,7 +5762,7 @@
     <t xml:space="preserve">17.5381145477295</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1083488464355</t>
+    <t xml:space="preserve">17.1083469390869</t>
   </si>
   <si>
     <t xml:space="preserve">17.8855838775635</t>
@@ -5774,7 +5774,7 @@
     <t xml:space="preserve">18.5439491271973</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5988140106201</t>
+    <t xml:space="preserve">18.5988121032715</t>
   </si>
   <si>
     <t xml:space="preserve">18.6353874206543</t>
@@ -5795,16 +5795,16 @@
     <t xml:space="preserve">21.3420009613037</t>
   </si>
   <si>
-    <t xml:space="preserve">21.159122467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3237133026123</t>
+    <t xml:space="preserve">21.1591205596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3237113952637</t>
   </si>
   <si>
     <t xml:space="preserve">21.2139854431152</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3602905273438</t>
+    <t xml:space="preserve">21.3602886199951</t>
   </si>
   <si>
     <t xml:space="preserve">22.559663772583</t>
@@ -6062,9 +6062,6 @@
     <t xml:space="preserve">21.1889495849609</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3602886199951</t>
-  </si>
-  <si>
     <t xml:space="preserve">23.7019233703613</t>
   </si>
   <si>
@@ -6123,6 +6120,9 @@
   </si>
   <si>
     <t xml:space="preserve">25.2000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6800003051758</t>
   </si>
 </sst>
 </file>
@@ -71635,7 +71635,7 @@
         <v>22.4400005340576</v>
       </c>
       <c r="G2507" t="s">
-        <v>2016</v>
+        <v>1930</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -71687,7 +71687,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G2509" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -71713,7 +71713,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G2510" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -71739,7 +71739,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G2511" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -71765,7 +71765,7 @@
         <v>25.6599998474121</v>
       </c>
       <c r="G2512" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -71791,7 +71791,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G2513" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -71817,7 +71817,7 @@
         <v>24.8199996948242</v>
       </c>
       <c r="G2514" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -71843,7 +71843,7 @@
         <v>25.1800003051758</v>
       </c>
       <c r="G2515" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -71869,7 +71869,7 @@
         <v>25.1800003051758</v>
       </c>
       <c r="G2516" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -71895,7 +71895,7 @@
         <v>24.9400005340576</v>
       </c>
       <c r="G2517" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -71921,7 +71921,7 @@
         <v>24</v>
       </c>
       <c r="G2518" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -71947,7 +71947,7 @@
         <v>24.7800006866455</v>
       </c>
       <c r="G2519" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -71973,7 +71973,7 @@
         <v>25</v>
       </c>
       <c r="G2520" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -71999,7 +71999,7 @@
         <v>24.7199993133545</v>
       </c>
       <c r="G2521" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -72025,7 +72025,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G2522" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -72051,7 +72051,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G2523" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -72077,7 +72077,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G2524" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -72103,7 +72103,7 @@
         <v>24.3400001525879</v>
       </c>
       <c r="G2525" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -72129,7 +72129,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G2526" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -72155,7 +72155,7 @@
         <v>24.1399993896484</v>
       </c>
       <c r="G2527" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -72181,7 +72181,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G2528" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -72189,7 +72189,7 @@
     </row>
     <row r="2529">
       <c r="A2529" s="1" t="n">
-        <v>46000.6915509259</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2529" t="n">
         <v>319910</v>
@@ -72207,9 +72207,35 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2529" t="s">
+        <v>2035</v>
+      </c>
+      <c r="H2529" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2530">
+      <c r="A2530" s="1" t="n">
+        <v>46001.6914583333</v>
+      </c>
+      <c r="B2530" t="n">
+        <v>183799</v>
+      </c>
+      <c r="C2530" t="n">
+        <v>25.1599998474121</v>
+      </c>
+      <c r="D2530" t="n">
+        <v>24.5599994659424</v>
+      </c>
+      <c r="E2530" t="n">
+        <v>25.1599998474121</v>
+      </c>
+      <c r="F2530" t="n">
+        <v>24.6800003051758</v>
+      </c>
+      <c r="G2530" t="s">
         <v>2036</v>
       </c>
-      <c r="H2529" t="s">
+      <c r="H2530" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IF.MI.xlsx
+++ b/data/IF.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">IF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6498336791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5859527587891</t>
+    <t xml:space="preserve">14.6498346328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5859546661377</t>
   </si>
   <si>
     <t xml:space="preserve">13.8460092544556</t>
@@ -59,157 +59,157 @@
     <t xml:space="preserve">13.6863098144531</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7342205047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4946660995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1494407653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1859140396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7980976104736</t>
+    <t xml:space="preserve">13.7342176437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4946699142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1494379043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1859159469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7980985641479</t>
   </si>
   <si>
     <t xml:space="preserve">13.9365062713623</t>
   </si>
   <si>
-    <t xml:space="preserve">13.739541053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6338634490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6551580429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.17151927948</t>
+    <t xml:space="preserve">13.7395439147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.633861541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6551570892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1715202331543</t>
   </si>
   <si>
     <t xml:space="preserve">15.1768426895142</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8148546218872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3312187194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2779884338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0118227005005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4422216415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2399349212646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8406858444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4300012588501</t>
+    <t xml:space="preserve">14.8148603439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3312215805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2779874801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0118236541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4422225952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2399368286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.84068775177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4299993515015</t>
   </si>
   <si>
     <t xml:space="preserve">12.467264175415</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0794477462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1060619354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1592998504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8353633880615</t>
+    <t xml:space="preserve">13.0794486999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1060647964478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1592969894409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8353614807129</t>
   </si>
   <si>
     <t xml:space="preserve">13.7448644638062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6596937179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5851669311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6437206268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.692419052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2559080123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0323247909546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4741640090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3730201721191</t>
+    <t xml:space="preserve">13.6596918106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5851640701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6437225341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6924209594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2559051513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0323266983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4741649627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3730182647705</t>
   </si>
   <si>
     <t xml:space="preserve">14.319787979126</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7509775161743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5486917495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2665529251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7501888275146</t>
+    <t xml:space="preserve">14.7509784698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5486927032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2665538787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7501850128174</t>
   </si>
   <si>
     <t xml:space="preserve">13.8566560745239</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4840221405029</t>
+    <t xml:space="preserve">13.4840230941772</t>
   </si>
   <si>
     <t xml:space="preserve">13.7874517440796</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0110330581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4528694152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6391859054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2300777435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4536590576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3205738067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1981363296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3418674468994</t>
+    <t xml:space="preserve">14.0110311508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4528703689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6391878128052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2300786972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4536571502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3205757141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1981372833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3418684005737</t>
   </si>
   <si>
     <t xml:space="preserve">15.3637380599976</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6917905807495</t>
+    <t xml:space="preserve">15.6917867660522</t>
   </si>
   <si>
     <t xml:space="preserve">15.9159574508667</t>
@@ -221,16 +221,16 @@
     <t xml:space="preserve">15.0848951339722</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5933742523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8497934341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9263353347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.024754524231</t>
+    <t xml:space="preserve">15.593376159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8497886657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9263343811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0247497558594</t>
   </si>
   <si>
     <t xml:space="preserve">15.1231660842896</t>
@@ -239,31 +239,31 @@
     <t xml:space="preserve">14.8825960159302</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5436115264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6857662200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5053377151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4123868942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6420269012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2374277114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1335439682007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.887505531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9203128814697</t>
+    <t xml:space="preserve">14.5436105728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6857643127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5053367614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4123907089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6420259475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2374296188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1335458755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8875064849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9203100204468</t>
   </si>
   <si>
     <t xml:space="preserve">13.9968576431274</t>
@@ -272,178 +272,178 @@
     <t xml:space="preserve">13.8547039031982</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6578702926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4391708374023</t>
+    <t xml:space="preserve">13.6578731536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.439169883728</t>
   </si>
   <si>
     <t xml:space="preserve">13.1767292022705</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4829082489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0127019882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9853677749634</t>
+    <t xml:space="preserve">13.48291015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0127038955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9853668212891</t>
   </si>
   <si>
     <t xml:space="preserve">12.6846513748169</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4768867492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2199125289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3566026687622</t>
+    <t xml:space="preserve">12.4768857955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2199144363403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3566036224365</t>
   </si>
   <si>
     <t xml:space="preserve">12.1488332748413</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8809261322021</t>
+    <t xml:space="preserve">11.8809251785278</t>
   </si>
   <si>
     <t xml:space="preserve">12.0285491943359</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0777568817139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7551736831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9738740921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3128604888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8164291381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2860765457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1220541000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9088201522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0072355270386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.706521987915</t>
+    <t xml:space="preserve">12.0777587890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7551746368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9738731384277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3128595352173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.816427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2860774993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1220550537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.908821105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0072383880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7065210342407</t>
   </si>
   <si>
     <t xml:space="preserve">12.6299772262573</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7174587249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5206251144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3401975631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1652393341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9465370178223</t>
+    <t xml:space="preserve">12.7174577713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5206270217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3401985168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1652383804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9465360641479</t>
   </si>
   <si>
     <t xml:space="preserve">11.6184844970703</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4763288497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3451080322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.049861907959</t>
+    <t xml:space="preserve">11.4763298034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3451099395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0498638153076</t>
   </si>
   <si>
     <t xml:space="preserve">11.6403570175171</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0449504852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9902782440186</t>
+    <t xml:space="preserve">12.0449533462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9902772903442</t>
   </si>
   <si>
     <t xml:space="preserve">12.3620700836182</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5364713668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68844890594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77046394348145</t>
+    <t xml:space="preserve">11.536473274231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68844985961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77046203613281</t>
   </si>
   <si>
     <t xml:space="preserve">9.82513809204102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92355251312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93448925018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95089054107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45881462097168</t>
+    <t xml:space="preserve">9.92355346679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93448829650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95089149475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45881366729736</t>
   </si>
   <si>
     <t xml:space="preserve">9.11982822418213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10889148712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26198387145996</t>
+    <t xml:space="preserve">9.1088924407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26198291778564</t>
   </si>
   <si>
     <t xml:space="preserve">9.2947883605957</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3062801361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7382135391235</t>
+    <t xml:space="preserve">10.306282043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7382154464722</t>
   </si>
   <si>
     <t xml:space="preserve">10.9350452423096</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7819528579712</t>
+    <t xml:space="preserve">10.7819538116455</t>
   </si>
   <si>
     <t xml:space="preserve">10.9623804092407</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7163438796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9459800720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6890058517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.514045715332</t>
+    <t xml:space="preserve">10.7163429260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9459791183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6890048980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5140447616577</t>
   </si>
   <si>
     <t xml:space="preserve">10.3390846252441</t>
@@ -458,49 +458,49 @@
     <t xml:space="preserve">11.1537456512451</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8694324493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0225257873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5796556472778</t>
+    <t xml:space="preserve">10.8694334030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0225276947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5796575546265</t>
   </si>
   <si>
     <t xml:space="preserve">10.6069936752319</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0443964004517</t>
+    <t xml:space="preserve">11.044397354126</t>
   </si>
   <si>
     <t xml:space="preserve">11.1756172180176</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8530321121216</t>
+    <t xml:space="preserve">10.8530311584473</t>
   </si>
   <si>
     <t xml:space="preserve">11.0936012268066</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0006551742554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9022417068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8366298675537</t>
+    <t xml:space="preserve">11.0006580352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9022407531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8366289138794</t>
   </si>
   <si>
     <t xml:space="preserve">10.7436800003052</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4593687057495</t>
+    <t xml:space="preserve">10.4593706130981</t>
   </si>
   <si>
     <t xml:space="preserve">10.4484348297119</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5085792541504</t>
+    <t xml:space="preserve">10.5085783004761</t>
   </si>
   <si>
     <t xml:space="preserve">10.4976434707642</t>
@@ -521,52 +521,52 @@
     <t xml:space="preserve">10.6671361923218</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6507339477539</t>
+    <t xml:space="preserve">10.6507320404053</t>
   </si>
   <si>
     <t xml:space="preserve">10.8803691864014</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2630977630615</t>
+    <t xml:space="preserve">11.2630968093872</t>
   </si>
   <si>
     <t xml:space="preserve">11.7223682403564</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7989130020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3833808898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1318759918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2084188461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1100063323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.126410484314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0170555114746</t>
+    <t xml:space="preserve">11.7989139556885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3833827972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1318769454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2084217071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1100053787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1264085769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0170583724976</t>
   </si>
   <si>
     <t xml:space="preserve">11.202953338623</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4817981719971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4435262680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0990705490112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9569149017334</t>
+    <t xml:space="preserve">11.4817972183228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4435243606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0990686416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9569158554077</t>
   </si>
   <si>
     <t xml:space="preserve">10.9405126571655</t>
@@ -575,133 +575,133 @@
     <t xml:space="preserve">10.9733171463013</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1428098678589</t>
+    <t xml:space="preserve">11.1428108215332</t>
   </si>
   <si>
     <t xml:space="preserve">11.1920185089111</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4489917755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8098468780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7885370254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0400428771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0673789978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1985988616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.280613899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4938488006592</t>
+    <t xml:space="preserve">11.4489946365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8098478317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7885341644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0400419235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0673761367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1985969543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.280611038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4938449859619</t>
   </si>
   <si>
     <t xml:space="preserve">13.679741859436</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7672243118286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1663522720337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2428979873657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3795852661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4944038391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4069232940674</t>
+    <t xml:space="preserve">13.76722240448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1663484573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2428941726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3795833587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4944019317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4069223403931</t>
   </si>
   <si>
     <t xml:space="preserve">14.2264928817749</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0077934265137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0241956710815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8109617233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8929748535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8437690734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6906785964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3954286575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3844947814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9908351898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0291080474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9361591339111</t>
+    <t xml:space="preserve">14.0077924728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0241966247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.810962677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8929758071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8437662124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6906776428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3954296112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3844957351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9908313751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0291032791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9361581802368</t>
   </si>
   <si>
     <t xml:space="preserve">12.8869504928589</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4222106933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4878196716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5479640960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1378993988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5753002166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7940044403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7775993347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6463785171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4610366821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5867938995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5102453231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6688089370728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2210273742676</t>
+    <t xml:space="preserve">12.4222097396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4878206253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5479650497437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1379013061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5753011703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.794002532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7776041030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6463794708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4610404968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5867929458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5102472305298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6688060760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2210254669189</t>
   </si>
   <si>
     <t xml:space="preserve">13.9804553985596</t>
@@ -713,28 +713,28 @@
     <t xml:space="preserve">13.7781581878662</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0734024047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.215558052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4889354705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8333864212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7513761520386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7076358795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5982866287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1226110458374</t>
+    <t xml:space="preserve">14.0734033584595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2155599594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4889345169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8333883285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7513742446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7076368331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5982828140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1226091384888</t>
   </si>
   <si>
     <t xml:space="preserve">14.2702341079712</t>
@@ -743,64 +743,64 @@
     <t xml:space="preserve">14.5600128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4342613220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3139743804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3631830215454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3467779159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1171417236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9421806335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8328323364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5485191345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8273658752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7234802246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7016096115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3249073028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0515336990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9531183242798</t>
+    <t xml:space="preserve">14.4342594146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3139753341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3631820678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3467807769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1171455383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9421844482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8328304290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5485219955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8273668289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.723482131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7016115188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3249101638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0515327453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9531173706055</t>
   </si>
   <si>
     <t xml:space="preserve">14.1608819961548</t>
   </si>
   <si>
-    <t xml:space="preserve">14.652961730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0903625488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0794248580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2653226852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7136611938477</t>
+    <t xml:space="preserve">14.6529607772827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0903615951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0794305801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2653198242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7136583328247</t>
   </si>
   <si>
     <t xml:space="preserve">16.1401271820068</t>
@@ -809,22 +809,22 @@
     <t xml:space="preserve">16.2658805847168</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8339433670044</t>
+    <t xml:space="preserve">15.8339462280273</t>
   </si>
   <si>
     <t xml:space="preserve">15.8120746612549</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3090648651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0745124816895</t>
+    <t xml:space="preserve">15.309063911438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0745162963867</t>
   </si>
   <si>
     <t xml:space="preserve">16.1291904449463</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5119152069092</t>
+    <t xml:space="preserve">16.5119190216064</t>
   </si>
   <si>
     <t xml:space="preserve">16.6431407928467</t>
@@ -842,10 +842,10 @@
     <t xml:space="preserve">16.8399696350098</t>
   </si>
   <si>
-    <t xml:space="preserve">17.053201675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8350582122803</t>
+    <t xml:space="preserve">17.0532035827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8350563049316</t>
   </si>
   <si>
     <t xml:space="preserve">18.6114463806152</t>
@@ -854,19 +854,19 @@
     <t xml:space="preserve">18.8629512786865</t>
   </si>
   <si>
-    <t xml:space="preserve">19.03244972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9345893859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.535457611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8471050262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.737756729126</t>
+    <t xml:space="preserve">19.0324459075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9345855712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5354537963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8471069335938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7377586364746</t>
   </si>
   <si>
     <t xml:space="preserve">19.6830825805664</t>
@@ -875,40 +875,40 @@
     <t xml:space="preserve">19.6557445526123</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3440971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5737266540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6448097229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8361701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.819766998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6174716949463</t>
+    <t xml:space="preserve">19.3440933227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5737285614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6448078155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8361682891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8197689056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6174697875977</t>
   </si>
   <si>
     <t xml:space="preserve">20.0931453704834</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3829212188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2188968658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1587543487549</t>
+    <t xml:space="preserve">20.3829231262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2188987731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1587524414062</t>
   </si>
   <si>
     <t xml:space="preserve">20.0111312866211</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9509868621826</t>
+    <t xml:space="preserve">19.9509887695312</t>
   </si>
   <si>
     <t xml:space="preserve">20.2845096588135</t>
@@ -917,28 +917,28 @@
     <t xml:space="preserve">20.5469493865967</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2899761199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1975860595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0718288421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9242076873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1593112945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6513862609863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8300476074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4950618743896</t>
+    <t xml:space="preserve">20.2899780273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1975841522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.071834564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9242095947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1593151092529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6513900756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8300514221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.495059967041</t>
   </si>
   <si>
     <t xml:space="preserve">21.3164005279541</t>
@@ -950,19 +950,19 @@
     <t xml:space="preserve">19.4739665985107</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0881099700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8145408630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6414604187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6972961425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.596794128418</t>
+    <t xml:space="preserve">20.0881118774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8145427703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6414623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6972923278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5967960357666</t>
   </si>
   <si>
     <t xml:space="preserve">18.3685092926025</t>
@@ -977,28 +977,28 @@
     <t xml:space="preserve">19.0049839019775</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4962997436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4851341247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5409641265869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4293041229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2953071594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3288040161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8430709838867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6644153594971</t>
+    <t xml:space="preserve">19.4962978363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4851322174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5409660339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4293022155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2953052520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3288021087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8430728912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6644134521484</t>
   </si>
   <si>
     <t xml:space="preserve">18.9268188476562</t>
@@ -1007,22 +1007,22 @@
     <t xml:space="preserve">19.2729759216309</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0943145751953</t>
+    <t xml:space="preserve">19.0943164825439</t>
   </si>
   <si>
     <t xml:space="preserve">19.2059764862061</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7531261444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7028770446777</t>
+    <t xml:space="preserve">19.7531223297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7028751373291</t>
   </si>
   <si>
     <t xml:space="preserve">19.3734703063965</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5632972717285</t>
+    <t xml:space="preserve">19.5632991790771</t>
   </si>
   <si>
     <t xml:space="preserve">19.5186309814453</t>
@@ -1037,46 +1037,46 @@
     <t xml:space="preserve">19.1780605316162</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0831451416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0384826660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5018825531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6749610900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6526298522949</t>
+    <t xml:space="preserve">19.0831489562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.038480758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.501880645752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6749629974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6526279449463</t>
   </si>
   <si>
     <t xml:space="preserve">19.8592014312744</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9261989593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9987812042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9206161499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0992794036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2332744598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2667713165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5180130004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7022590637207</t>
+    <t xml:space="preserve">19.9262008666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9987831115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9206199645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0992755889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2332725524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.266773223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5180149078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7022571563721</t>
   </si>
   <si>
     <t xml:space="preserve">20.59059715271</t>
@@ -1085,109 +1085,109 @@
     <t xml:space="preserve">20.5682621002197</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6017627716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7860050201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0204963684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7134246826172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3833999633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8021354675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5508937835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8635501861572</t>
+    <t xml:space="preserve">20.6017608642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.786003112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0204944610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7134208679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3833980560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8021335601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5508899688721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.86354637146</t>
   </si>
   <si>
     <t xml:space="preserve">21.6625556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1650371551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3604431152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6284370422363</t>
+    <t xml:space="preserve">22.1650352478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3604469299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.628438949585</t>
   </si>
   <si>
     <t xml:space="preserve">22.8517627716064</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1030025482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7233543395996</t>
+    <t xml:space="preserve">23.1030082702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.723352432251</t>
   </si>
   <si>
     <t xml:space="preserve">22.9410934448242</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8908405303955</t>
+    <t xml:space="preserve">22.8908424377441</t>
   </si>
   <si>
     <t xml:space="preserve">22.4106941223145</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4330291748047</t>
+    <t xml:space="preserve">22.4330234527588</t>
   </si>
   <si>
     <t xml:space="preserve">22.9969253540039</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1811656951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1365032196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7066020965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8796768188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6898536682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6731033325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8182621002197</t>
+    <t xml:space="preserve">23.1811676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1364994049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7066040039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8796787261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6898517608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6731014251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8182640075684</t>
   </si>
   <si>
     <t xml:space="preserve">22.6451873779297</t>
   </si>
   <si>
-    <t xml:space="preserve">22.500020980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0031223297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5670204162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7512664794922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0025100708008</t>
+    <t xml:space="preserve">22.5000228881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0031280517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5670223236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7512683868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0025043487549</t>
   </si>
   <si>
     <t xml:space="preserve">23.3542442321777</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1699981689453</t>
+    <t xml:space="preserve">23.1700019836426</t>
   </si>
   <si>
     <t xml:space="preserve">22.9243431091309</t>
@@ -1205,190 +1205,190 @@
     <t xml:space="preserve">23.5105762481689</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8623085021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4708728790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4764556884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9007701873779</t>
+    <t xml:space="preserve">23.8623142242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4708671569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4764537811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9007720947266</t>
   </si>
   <si>
     <t xml:space="preserve">25.2190113067627</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1129302978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3083400726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8728580474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.319507598877</t>
+    <t xml:space="preserve">25.1129322052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3083419799805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8728523254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3195037841797</t>
   </si>
   <si>
     <t xml:space="preserve">25.5316638946533</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8275699615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4193859100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7152919769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8492870330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6042461395264</t>
+    <t xml:space="preserve">25.8275718688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4193840026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7152900695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8492889404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6042499542236</t>
   </si>
   <si>
     <t xml:space="preserve">26.4138050079346</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1284446716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4410991668701</t>
+    <t xml:space="preserve">27.1284370422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4410972595215</t>
   </si>
   <si>
     <t xml:space="preserve">27.502513885498</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2791862487793</t>
+    <t xml:space="preserve">27.2791919708252</t>
   </si>
   <si>
     <t xml:space="preserve">26.7041244506836</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6321678161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2525081634521</t>
+    <t xml:space="preserve">25.6321620941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2525100708008</t>
   </si>
   <si>
     <t xml:space="preserve">25.9057350158691</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3585910797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2128086090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3021392822266</t>
+    <t xml:space="preserve">25.358585357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2128047943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3021354675293</t>
   </si>
   <si>
     <t xml:space="preserve">26.335636138916</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5031280517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9609508514404</t>
+    <t xml:space="preserve">26.5031318664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9609451293945</t>
   </si>
   <si>
     <t xml:space="preserve">26.2407283782959</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2742252349854</t>
+    <t xml:space="preserve">26.274227142334</t>
   </si>
   <si>
     <t xml:space="preserve">26.1346473693848</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1793117523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7773284912109</t>
+    <t xml:space="preserve">26.1793079376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.777322769165</t>
   </si>
   <si>
     <t xml:space="preserve">25.5260848999023</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0403499603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6886119842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4156589508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7456817626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8467979431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7295532226562</t>
+    <t xml:space="preserve">25.0403480529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6886157989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4156551361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7456855773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8467960357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.729549407959</t>
   </si>
   <si>
     <t xml:space="preserve">22.4665260314941</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6234741210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6346397399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2438201904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9255790710449</t>
+    <t xml:space="preserve">21.6234703063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6346378326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2438220977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9255847930908</t>
   </si>
   <si>
     <t xml:space="preserve">21.5843906402588</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3275661468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5229759216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6960525512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1656589508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5124320983887</t>
+    <t xml:space="preserve">21.3275699615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5229797363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6960544586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1656551361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.51243019104</t>
   </si>
   <si>
     <t xml:space="preserve">20.4845123291016</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6855068206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7748336791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4175148010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8982830047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3728485107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8250846862793</t>
+    <t xml:space="preserve">20.6855087280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7748355865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.417516708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.898286819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3728504180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8250865936279</t>
   </si>
   <si>
     <t xml:space="preserve">21.3889827728271</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1718597412109</t>
+    <t xml:space="preserve">20.1718616485596</t>
   </si>
   <si>
     <t xml:space="preserve">20.0936965942383</t>
@@ -1400,10 +1400,10 @@
     <t xml:space="preserve">20.668758392334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6123027801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7624320983887</t>
+    <t xml:space="preserve">21.6123046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.76243019104</t>
   </si>
   <si>
     <t xml:space="preserve">21.9361305236816</t>
@@ -1415,31 +1415,31 @@
     <t xml:space="preserve">22.611686706543</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6228561401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3213653564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3883590698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2717361450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9193801879883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0422115325928</t>
+    <t xml:space="preserve">22.6228523254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3213634490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3883609771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2717323303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.919376373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0422077178955</t>
   </si>
   <si>
     <t xml:space="preserve">21.7630500793457</t>
   </si>
   <si>
-    <t xml:space="preserve">21.941707611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8523769378662</t>
+    <t xml:space="preserve">21.9417114257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8523826599121</t>
   </si>
   <si>
     <t xml:space="preserve">21.684886932373</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">21.2047386169434</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8412132263184</t>
+    <t xml:space="preserve">21.8412170410156</t>
   </si>
   <si>
     <t xml:space="preserve">21.3722324371338</t>
@@ -1466,10 +1466,10 @@
     <t xml:space="preserve">20.1997756958008</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7419567108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2444381713867</t>
+    <t xml:space="preserve">19.7419586181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2444343566895</t>
   </si>
   <si>
     <t xml:space="preserve">18.7034950256348</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">20.1439437866211</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9094524383545</t>
+    <t xml:space="preserve">19.9094505310059</t>
   </si>
   <si>
     <t xml:space="preserve">20.3449363708496</t>
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">20.3337688446045</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3002758026123</t>
+    <t xml:space="preserve">20.300271987915</t>
   </si>
   <si>
     <t xml:space="preserve">20.2556037902832</t>
@@ -1502,55 +1502,55 @@
     <t xml:space="preserve">20.3672676086426</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0322818756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7977867126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6861248016357</t>
+    <t xml:space="preserve">20.0322780609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7977886199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6861267089844</t>
   </si>
   <si>
     <t xml:space="preserve">19.0496501922607</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4020042419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.100513458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4243392944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1786804199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1675128936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1054782867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0273170471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9330215454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4640407562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.631534576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5025024414062</t>
+    <t xml:space="preserve">18.402006149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1005153656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.424337387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1786823272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1675148010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1054821014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0273151397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9330196380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.464038848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6315326690674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5025005340576</t>
   </si>
   <si>
     <t xml:space="preserve">18.3350086212158</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0781860351562</t>
+    <t xml:space="preserve">18.078182220459</t>
   </si>
   <si>
     <t xml:space="preserve">17.441707611084</t>
@@ -1559,133 +1559,133 @@
     <t xml:space="preserve">16.5260734558105</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7990283966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.095552444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8213596343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2010116577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3461761474609</t>
+    <t xml:space="preserve">17.7990264892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0955486297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8213577270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2010097503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3461742401123</t>
   </si>
   <si>
     <t xml:space="preserve">18.480167388916</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1836414337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7816581726074</t>
+    <t xml:space="preserve">19.1836452484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7816600799561</t>
   </si>
   <si>
     <t xml:space="preserve">18.6364974975586</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8598232269287</t>
+    <t xml:space="preserve">18.8598213195801</t>
   </si>
   <si>
     <t xml:space="preserve">18.748161315918</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4152736663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4267921447754</t>
+    <t xml:space="preserve">18.4152717590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4267902374268</t>
   </si>
   <si>
     <t xml:space="preserve">18.2194900512695</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1734218597412</t>
+    <t xml:space="preserve">18.1734237670898</t>
   </si>
   <si>
     <t xml:space="preserve">18.2425231933594</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8298778533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0141448974609</t>
+    <t xml:space="preserve">18.8298797607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0141468048096</t>
   </si>
   <si>
     <t xml:space="preserve">19.2905464172363</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4517822265625</t>
+    <t xml:space="preserve">19.4517803192139</t>
   </si>
   <si>
     <t xml:space="preserve">19.6705989837646</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3941993713379</t>
+    <t xml:space="preserve">19.3941974639893</t>
   </si>
   <si>
     <t xml:space="preserve">19.0602111816406</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5995407104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5074100494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7031936645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7722930908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0467376708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.447868347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5725936889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.261646270752</t>
+    <t xml:space="preserve">18.5995426177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5074062347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7031955718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7722911834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0467395782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4478664398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5725955963135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2616424560547</t>
   </si>
   <si>
     <t xml:space="preserve">16.399845123291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0658588409424</t>
+    <t xml:space="preserve">16.065860748291</t>
   </si>
   <si>
     <t xml:space="preserve">15.7203559875488</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8566017150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4861097335815</t>
+    <t xml:space="preserve">14.8566007614136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4861068725586</t>
   </si>
   <si>
     <t xml:space="preserve">12.2653322219849</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4400396347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5436925888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6838483810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7414312362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2922782897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4189672470093</t>
+    <t xml:space="preserve">13.4400405883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5436897277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6838464736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.74143409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2922792434692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4189643859863</t>
   </si>
   <si>
     <t xml:space="preserve">14.1195287704468</t>
@@ -1694,154 +1694,154 @@
     <t xml:space="preserve">13.992844581604</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5571670532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3748540878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8009748458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7779417037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3057527542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9852409362793</t>
+    <t xml:space="preserve">14.5571660995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3748531341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8009738922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7779378890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3057546615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9852418899536</t>
   </si>
   <si>
     <t xml:space="preserve">16.4113597869873</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9276571273804</t>
+    <t xml:space="preserve">15.9276580810547</t>
   </si>
   <si>
     <t xml:space="preserve">16.0888919830322</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8240079879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2021026611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7184000015259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8220491409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8450841903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8911514282227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8681163787842</t>
+    <t xml:space="preserve">15.8240051269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2021036148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7183971405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8220500946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.845085144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8911533355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8681173324585</t>
   </si>
   <si>
     <t xml:space="preserve">15.0293502807617</t>
   </si>
   <si>
-    <t xml:space="preserve">15.271203994751</t>
+    <t xml:space="preserve">15.2712020874023</t>
   </si>
   <si>
     <t xml:space="preserve">15.6167068481445</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7894554138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4900245666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1445198059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2251358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0639028549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8700742721558</t>
+    <t xml:space="preserve">15.7894592285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4900207519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1445178985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.225136756897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0639019012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8700761795044</t>
   </si>
   <si>
     <t xml:space="preserve">16.123441696167</t>
   </si>
   <si>
-    <t xml:space="preserve">15.501540184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2827215194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5130577087402</t>
+    <t xml:space="preserve">15.5015392303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2827205657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5130548477173</t>
   </si>
   <si>
     <t xml:space="preserve">15.5706405639648</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4324388504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6262636184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7990169525146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9352617263794</t>
+    <t xml:space="preserve">15.4324369430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6262664794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7990140914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9352607727051</t>
   </si>
   <si>
     <t xml:space="preserve">12.7260026931763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0254383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9908876419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9793720245361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6453857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4150505065918</t>
+    <t xml:space="preserve">13.0254373550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9908885955811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9793729782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6453838348389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4150495529175</t>
   </si>
   <si>
     <t xml:space="preserve">11.9083137512207</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7816295623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8852787017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8507299423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6223526000977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1731977462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3459501266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2998838424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4611177444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7470788955688</t>
+    <t xml:space="preserve">11.7816276550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8852806091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8507308959961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6223516464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1731986999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3459491729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2998847961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4611158370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7470798492432</t>
   </si>
   <si>
     <t xml:space="preserve">11.7010126113892</t>
@@ -1850,46 +1850,46 @@
     <t xml:space="preserve">11.6664619445801</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1501636505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5647678375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0024042129517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8757200241089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7144842147827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2212228775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9217863082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0139217376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6799364089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7029695510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8526849746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3824577331543</t>
+    <t xml:space="preserve">12.1501665115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5647659301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0024032592773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8757209777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.714485168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2212219238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9217882156372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0139207839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6799345016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7029676437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8526859283447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3824586868286</t>
   </si>
   <si>
     <t xml:space="preserve">13.7279596328735</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7049245834351</t>
+    <t xml:space="preserve">13.7049236297607</t>
   </si>
   <si>
     <t xml:space="preserve">13.5782413482666</t>
@@ -1898,7 +1898,7 @@
     <t xml:space="preserve">13.7394762039185</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7490358352661</t>
+    <t xml:space="preserve">12.7490367889404</t>
   </si>
   <si>
     <t xml:space="preserve">11.1712427139282</t>
@@ -1907,55 +1907,55 @@
     <t xml:space="preserve">10.3420352935791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7566394805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0503158569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4015760421753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2345838546753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81802558898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0771522521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74316596984863</t>
+    <t xml:space="preserve">10.7566385269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0503168106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4015769958496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.234582901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81802272796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0771512985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74316692352295</t>
   </si>
   <si>
     <t xml:space="preserve">9.39190578460693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82953929901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80650806427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99077701568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44372940063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42069721221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07519435882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31508827209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97534513473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82562685012817</t>
+    <t xml:space="preserve">9.82954120635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80650997161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9907751083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44373035430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42069625854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07519626617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31509017944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97534608840942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82562875747681</t>
   </si>
   <si>
     <t xml:space="preserve">8.0617208480835</t>
@@ -1970,49 +1970,49 @@
     <t xml:space="preserve">8.62604141235352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94851016998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2133960723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72589111328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40918064117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68362617492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77575969696045</t>
+    <t xml:space="preserve">8.94850921630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21339511871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72589015960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40918159484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68362522125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77575778961182</t>
   </si>
   <si>
     <t xml:space="preserve">8.39570617675781</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6893835067749</t>
+    <t xml:space="preserve">8.68938446044922</t>
   </si>
   <si>
     <t xml:space="preserve">8.80455112457275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91395950317383</t>
+    <t xml:space="preserve">8.91395854949951</t>
   </si>
   <si>
     <t xml:space="preserve">9.12701988220215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02912712097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00033569335938</t>
+    <t xml:space="preserve">9.029128074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00033664703369</t>
   </si>
   <si>
     <t xml:space="preserve">9.2421875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15005397796631</t>
+    <t xml:space="preserve">9.15005207061768</t>
   </si>
   <si>
     <t xml:space="preserve">9.10974502563477</t>
@@ -2024,85 +2024,85 @@
     <t xml:space="preserve">10.6011638641357</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3823442459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0387992858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7623977661133</t>
+    <t xml:space="preserve">10.382345199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0388011932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.762396812439</t>
   </si>
   <si>
     <t xml:space="preserve">10.4802379608154</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4399280548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0080518722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3074855804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84105682373047</t>
+    <t xml:space="preserve">10.4399261474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0080490112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.30748462677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8410587310791</t>
   </si>
   <si>
     <t xml:space="preserve">10.2211112976074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78923225402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1289768218994</t>
+    <t xml:space="preserve">9.78923416137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1289777755737</t>
   </si>
   <si>
     <t xml:space="preserve">10.5666131973267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4744806289673</t>
+    <t xml:space="preserve">10.474479675293</t>
   </si>
   <si>
     <t xml:space="preserve">10.3362789154053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87560844421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34007930755615</t>
+    <t xml:space="preserve">9.87560749053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34007835388184</t>
   </si>
   <si>
     <t xml:space="preserve">9.22491264343262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91971778869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72969245910645</t>
+    <t xml:space="preserve">8.91971969604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72969341278076</t>
   </si>
   <si>
     <t xml:space="preserve">8.60300827026367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89092636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89668560028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46676349639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90439987182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2844543457031</t>
+    <t xml:space="preserve">8.89092540740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89668464660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46676540374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90440082550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2844533920288</t>
   </si>
   <si>
     <t xml:space="preserve">10.0483589172363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.111701965332</t>
+    <t xml:space="preserve">10.1117010116577</t>
   </si>
   <si>
     <t xml:space="preserve">10.0713930130005</t>
@@ -2114,58 +2114,58 @@
     <t xml:space="preserve">9.54162216186523</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16157054901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61648178100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73740768432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96198463439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86985111236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50707244873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48979663848877</t>
+    <t xml:space="preserve">9.16156959533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61648273468018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73740673065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9619836807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86984920501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50707340240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48979759216309</t>
   </si>
   <si>
     <t xml:space="preserve">9.78347396850586</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93319225311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0253267288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66254997253418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5473804473877</t>
+    <t xml:space="preserve">9.93319034576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0253257751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66254806518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54738140106201</t>
   </si>
   <si>
     <t xml:space="preserve">9.6395149230957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84681701660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58193016052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18460464477539</t>
+    <t xml:space="preserve">9.84681797027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58193111419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18460273742676</t>
   </si>
   <si>
     <t xml:space="preserve">10.5608549118042</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0349960327148</t>
+    <t xml:space="preserve">12.0349988937378</t>
   </si>
   <si>
     <t xml:space="preserve">11.4534015655518</t>
@@ -2174,64 +2174,64 @@
     <t xml:space="preserve">10.8257398605347</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3535528182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1865615844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1001844406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0598764419556</t>
+    <t xml:space="preserve">10.3535537719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1865606307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1001853942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0598754882812</t>
   </si>
   <si>
     <t xml:space="preserve">9.622239112854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85257434844971</t>
+    <t xml:space="preserve">9.85257625579834</t>
   </si>
   <si>
     <t xml:space="preserve">10.4111375808716</t>
   </si>
   <si>
-    <t xml:space="preserve">10.503270149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5781307220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9293909072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4456853866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08671092987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90820121765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78151798248291</t>
+    <t xml:space="preserve">10.5032711029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5781297683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9293899536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.445686340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08671188354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90820217132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78151702880859</t>
   </si>
   <si>
     <t xml:space="preserve">8.67210960388184</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64907646179199</t>
+    <t xml:space="preserve">8.64907550811768</t>
   </si>
   <si>
     <t xml:space="preserve">8.69514179229736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49935722351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54542541503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52239036560059</t>
+    <t xml:space="preserve">8.49935626983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54542446136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5223913192749</t>
   </si>
   <si>
     <t xml:space="preserve">8.41873931884766</t>
@@ -2240,40 +2240,40 @@
     <t xml:space="preserve">8.47056579589844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63755893707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56845664978027</t>
+    <t xml:space="preserve">8.63755798339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56845855712891</t>
   </si>
   <si>
     <t xml:space="preserve">8.79879283905029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04064464569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02336883544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00609493255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93699359893799</t>
+    <t xml:space="preserve">9.0406436920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02336978912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00609302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9369945526123</t>
   </si>
   <si>
     <t xml:space="preserve">9.17308712005615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21915531158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24794578552246</t>
+    <t xml:space="preserve">9.21915435791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24794483184814</t>
   </si>
   <si>
     <t xml:space="preserve">9.35735607147217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76981735229492</t>
+    <t xml:space="preserve">9.76981639862061</t>
   </si>
   <si>
     <t xml:space="preserve">9.46200942993164</t>
@@ -2282,247 +2282,247 @@
     <t xml:space="preserve">9.19113922119141</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25885581970215</t>
+    <t xml:space="preserve">9.25885677337646</t>
   </si>
   <si>
     <t xml:space="preserve">8.7725191116333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61246013641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3169641494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11381149291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87987661361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48588371276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92297029495239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9722204208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91681432723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68288087844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49819707870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.528977394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44894742965698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20270109176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3504490852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22732448577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17807626724243</t>
+    <t xml:space="preserve">8.61245918273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31696510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11381053924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87987804412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48588275909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92297077178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97221946716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91681480407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68287992477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49819612503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52897596359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44894695281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20269870758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35044860839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22732591629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17807579040527</t>
   </si>
   <si>
     <t xml:space="preserve">7.14113903045654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01801538467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96261072158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29504299163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9749231338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89489221572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93798637390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15960836410522</t>
+    <t xml:space="preserve">7.01801490783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96261024475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2950439453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97492265701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89489316940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93798685073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15960741043091</t>
   </si>
   <si>
     <t xml:space="preserve">6.91336154937744</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94414186477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90720510482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06111001968384</t>
+    <t xml:space="preserve">6.94414281845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90720558166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06110858917236</t>
   </si>
   <si>
     <t xml:space="preserve">7.33813619613647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64594459533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46741533279419</t>
+    <t xml:space="preserve">7.64594411849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46741485595703</t>
   </si>
   <si>
     <t xml:space="preserve">7.33197975158691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19038820266724</t>
+    <t xml:space="preserve">7.19038772583008</t>
   </si>
   <si>
     <t xml:space="preserve">7.39354085922241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42432355880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30735492706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60900783538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78753566741943</t>
+    <t xml:space="preserve">7.4243221282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30735540390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60900545120239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78753519058228</t>
   </si>
   <si>
     <t xml:space="preserve">8.28618431091309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23693561553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.280029296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37237071990967</t>
+    <t xml:space="preserve">8.23693466186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28002738952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37236976623535</t>
   </si>
   <si>
     <t xml:space="preserve">8.16921710968018</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16306114196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08303070068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14459228515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52627372741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51396083831787</t>
+    <t xml:space="preserve">8.16306018829346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08303165435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14459133148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52627468109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51396179199219</t>
   </si>
   <si>
     <t xml:space="preserve">8.50780582427979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32927703857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21230983734131</t>
+    <t xml:space="preserve">8.3292760848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21230888366699</t>
   </si>
   <si>
     <t xml:space="preserve">8.40315055847168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40930652618408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2923412322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19384384155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24924755096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98453283309937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89834642410278</t>
+    <t xml:space="preserve">8.4093074798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29234027862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1938419342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24924659729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98453235626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89834690093994</t>
   </si>
   <si>
     <t xml:space="preserve">8.13227939605713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59399223327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48933506011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45855712890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68633460998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07687377929688</t>
+    <t xml:space="preserve">8.59399127960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48933792114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45855522155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68633365631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07687568664551</t>
   </si>
   <si>
     <t xml:space="preserve">7.71981859207153</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49203968048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8675651550293</t>
+    <t xml:space="preserve">7.4920392036438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86756420135498</t>
   </si>
   <si>
     <t xml:space="preserve">7.93528366088867</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02762413024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96606397628784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88603401184082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84293985366821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15074920654297</t>
+    <t xml:space="preserve">8.02762508392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.966064453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88603496551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84294128417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15074729919434</t>
   </si>
   <si>
     <t xml:space="preserve">8.34774589538574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58783531188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69249153137207</t>
+    <t xml:space="preserve">8.58783626556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69248962402344</t>
   </si>
   <si>
     <t xml:space="preserve">8.77867698669434</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00029754638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98798656463623</t>
+    <t xml:space="preserve">9.0002965927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98798561096191</t>
   </si>
   <si>
     <t xml:space="preserve">9.04954719543457</t>
@@ -2531,28 +2531,28 @@
     <t xml:space="preserve">9.09879684448242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12342071533203</t>
+    <t xml:space="preserve">9.12341976165771</t>
   </si>
   <si>
     <t xml:space="preserve">9.22807598114014</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4373836517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44354152679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26501178741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41891670227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43122959136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20960807800293</t>
+    <t xml:space="preserve">9.43738460540771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4435396194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26501274108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41891574859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43122863769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20960712432861</t>
   </si>
   <si>
     <t xml:space="preserve">9.11726474761963</t>
@@ -2561,34 +2561,34 @@
     <t xml:space="preserve">9.20345115661621</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42507266998291</t>
+    <t xml:space="preserve">9.42507076263428</t>
   </si>
   <si>
     <t xml:space="preserve">9.24038791656494</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06185913085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85870552062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88333225250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98182964324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66170978546143</t>
+    <t xml:space="preserve">9.06185817718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8587064743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88333034515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9818286895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66170883178711</t>
   </si>
   <si>
     <t xml:space="preserve">8.92026805877686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06801605224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32041931152344</t>
+    <t xml:space="preserve">9.06801509857178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32041835784912</t>
   </si>
   <si>
     <t xml:space="preserve">9.27116966247559</t>
@@ -2597,28 +2597,28 @@
     <t xml:space="preserve">9.29579257965088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40044689178467</t>
+    <t xml:space="preserve">9.40044784545898</t>
   </si>
   <si>
     <t xml:space="preserve">9.47432231903076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51741600036621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46816635131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30194854736328</t>
+    <t xml:space="preserve">9.51741504669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46816444396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3019495010376</t>
   </si>
   <si>
     <t xml:space="preserve">9.40660381317139</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50510215759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73288059234619</t>
+    <t xml:space="preserve">9.50510120391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73287963867188</t>
   </si>
   <si>
     <t xml:space="preserve">8.99414157867432</t>
@@ -2627,19 +2627,19 @@
     <t xml:space="preserve">9.35735416412354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39429187774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70209884643555</t>
+    <t xml:space="preserve">9.3942928314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70210075378418</t>
   </si>
   <si>
     <t xml:space="preserve">9.745192527771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16035652160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96335983276367</t>
+    <t xml:space="preserve">9.16035842895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96335887908936</t>
   </si>
   <si>
     <t xml:space="preserve">8.89564228057861</t>
@@ -2648,25 +2648,25 @@
     <t xml:space="preserve">8.79714488983154</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74789524078369</t>
+    <t xml:space="preserve">8.74789619445801</t>
   </si>
   <si>
     <t xml:space="preserve">8.62477207183838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6432409286499</t>
+    <t xml:space="preserve">8.64323997497559</t>
   </si>
   <si>
     <t xml:space="preserve">8.54474258422852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60630416870117</t>
+    <t xml:space="preserve">8.60630321502686</t>
   </si>
   <si>
     <t xml:space="preserve">8.49549293518066</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34158992767334</t>
+    <t xml:space="preserve">8.34158897399902</t>
   </si>
   <si>
     <t xml:space="preserve">8.4216194152832</t>
@@ -2675,16 +2675,16 @@
     <t xml:space="preserve">8.36005783081055</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1999979019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15690517425537</t>
+    <t xml:space="preserve">8.19999694824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15690422058105</t>
   </si>
   <si>
     <t xml:space="preserve">8.26155948638916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44008731842041</t>
+    <t xml:space="preserve">8.44008922576904</t>
   </si>
   <si>
     <t xml:space="preserve">8.44624423980713</t>
@@ -2693,10 +2693,10 @@
     <t xml:space="preserve">8.39083862304688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43393230438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80330181121826</t>
+    <t xml:space="preserve">8.43393039703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80330085754395</t>
   </si>
   <si>
     <t xml:space="preserve">8.61861610412598</t>
@@ -2708,16 +2708,16 @@
     <t xml:space="preserve">8.79098892211914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71711444854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69864654541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82177066802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65555381774902</t>
+    <t xml:space="preserve">8.71711540222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69864559173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82176876068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65555286407471</t>
   </si>
   <si>
     <t xml:space="preserve">8.50164985656738</t>
@@ -2735,28 +2735,28 @@
     <t xml:space="preserve">9.05570316314697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07417106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87717533111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85254859924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27732563018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01876640319824</t>
+    <t xml:space="preserve">9.0741720199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87717437744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8525505065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27732467651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01876544952393</t>
   </si>
   <si>
     <t xml:space="preserve">8.82792663574219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16651439666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23423194885254</t>
+    <t xml:space="preserve">9.16651248931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23423099517822</t>
   </si>
   <si>
     <t xml:space="preserve">9.33273124694824</t>
@@ -2765,7 +2765,7 @@
     <t xml:space="preserve">9.64669418334961</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64053821563721</t>
+    <t xml:space="preserve">9.64053916931152</t>
   </si>
   <si>
     <t xml:space="preserve">9.58513259887695</t>
@@ -2774,40 +2774,40 @@
     <t xml:space="preserve">9.65285015106201</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52357006072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6590051651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90179824829102</t>
+    <t xml:space="preserve">9.5235710144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65900611877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90179920196533</t>
   </si>
   <si>
     <t xml:space="preserve">9.09264087677002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46471214294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00300025939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5228214263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55014848709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29774570465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27927732467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39894723892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65135049819946</t>
+    <t xml:space="preserve">8.46471309661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00300121307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52282047271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55014801025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29774475097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27927780151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39894771575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6513500213623</t>
   </si>
   <si>
     <t xml:space="preserve">5.34354209899902</t>
@@ -2816,10 +2816,10 @@
     <t xml:space="preserve">5.18348217010498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19579410552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17732572555542</t>
+    <t xml:space="preserve">5.19579362869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17732620239258</t>
   </si>
   <si>
     <t xml:space="preserve">5.47897720336914</t>
@@ -2831,22 +2831,22 @@
     <t xml:space="preserve">5.55900716781616</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58670997619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69444274902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62364721298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38971376419067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50975799560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48205518722534</t>
+    <t xml:space="preserve">5.58671045303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6944432258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62364768981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38971328735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50975751876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4820556640625</t>
   </si>
   <si>
     <t xml:space="preserve">5.42665004730225</t>
@@ -2855,31 +2855,31 @@
     <t xml:space="preserve">5.50360202789307</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55592918395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68212985992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66058349609375</t>
+    <t xml:space="preserve">5.55592966079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68213033676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66058397293091</t>
   </si>
   <si>
     <t xml:space="preserve">5.68828678131104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55285167694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43896198272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4912896156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49744653701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23273086547852</t>
+    <t xml:space="preserve">5.55285120010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43896245956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49129009246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49744606018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23273181915283</t>
   </si>
   <si>
     <t xml:space="preserve">5.12499856948853</t>
@@ -2888,28 +2888,28 @@
     <t xml:space="preserve">5.2512001991272</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53438282012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6451940536499</t>
+    <t xml:space="preserve">5.53438329696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64519357681274</t>
   </si>
   <si>
     <t xml:space="preserve">5.49436807632446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29429244995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34969854354858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31583976745605</t>
+    <t xml:space="preserve">5.29429292678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34969711303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3158392906189</t>
   </si>
   <si>
     <t xml:space="preserve">5.20810699462891</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29121446609497</t>
+    <t xml:space="preserve">5.29121494293213</t>
   </si>
   <si>
     <t xml:space="preserve">5.21734046936035</t>
@@ -2918,40 +2918,40 @@
     <t xml:space="preserve">5.14654493331909</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06959342956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97417259216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94339179992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92492389678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70945835113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58017826080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48167991638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49399328231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74023866653442</t>
+    <t xml:space="preserve">5.06959295272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97417211532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9433913230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92492341995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7094578742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58017921447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48167943954468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49399280548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74023914337158</t>
   </si>
   <si>
     <t xml:space="preserve">4.93107986450195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07882785797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16809225082397</t>
+    <t xml:space="preserve">5.07882738113403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16809177398682</t>
   </si>
   <si>
     <t xml:space="preserve">5.10653018951416</t>
@@ -2963,49 +2963,49 @@
     <t xml:space="preserve">5.45127439498901</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65750503540039</t>
+    <t xml:space="preserve">5.65750551223755</t>
   </si>
   <si>
     <t xml:space="preserve">5.95300149917603</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37777614593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98378229141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79909706115723</t>
+    <t xml:space="preserve">6.37777519226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98378133773804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79909801483154</t>
   </si>
   <si>
     <t xml:space="preserve">5.40202522277832</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36201047897339</t>
+    <t xml:space="preserve">5.36201095581055</t>
   </si>
   <si>
     <t xml:space="preserve">5.50668001174927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59594488143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54053974151611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45743083953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31891822814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26966857910156</t>
+    <t xml:space="preserve">5.59594440460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54053831100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45743036270142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31891679763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2696681022644</t>
   </si>
   <si>
     <t xml:space="preserve">5.13731098175049</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06035900115967</t>
+    <t xml:space="preserve">5.06035947799683</t>
   </si>
   <si>
     <t xml:space="preserve">5.11576461791992</t>
@@ -3014,13 +3014,13 @@
     <t xml:space="preserve">5.22965288162231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.263512134552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.248122215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37432241439819</t>
+    <t xml:space="preserve">5.26351261138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24812078475952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37432193756104</t>
   </si>
   <si>
     <t xml:space="preserve">5.4758996963501</t>
@@ -3029,40 +3029,40 @@
     <t xml:space="preserve">5.58363151550293</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52207136154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61133527755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59286642074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92837715148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04226589202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09151458740234</t>
+    <t xml:space="preserve">5.52206993103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6113338470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59286594390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92837619781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04226493835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09151601791382</t>
   </si>
   <si>
     <t xml:space="preserve">5.89759635925293</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76831674575806</t>
+    <t xml:space="preserve">5.76831722259521</t>
   </si>
   <si>
     <t xml:space="preserve">5.63288116455078</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50052499771118</t>
+    <t xml:space="preserve">5.50052356719971</t>
   </si>
   <si>
     <t xml:space="preserve">5.33738613128662</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33430767059326</t>
+    <t xml:space="preserve">5.33430814743042</t>
   </si>
   <si>
     <t xml:space="preserve">5.52822589874268</t>
@@ -3071,19 +3071,19 @@
     <t xml:space="preserve">5.5374608039856</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41126012802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6482720375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62672472000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65442848205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54361772537231</t>
+    <t xml:space="preserve">5.41125965118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64827156066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62672567367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65442800521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54361724853516</t>
   </si>
   <si>
     <t xml:space="preserve">5.51591396331787</t>
@@ -3095,31 +3095,31 @@
     <t xml:space="preserve">5.46050882339478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47282123565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51899337768555</t>
+    <t xml:space="preserve">5.47282218933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51899147033691</t>
   </si>
   <si>
     <t xml:space="preserve">5.36816644668579</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32199621200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31276178359985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42972898483276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.43280696868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39279222488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42049407958984</t>
+    <t xml:space="preserve">5.32199573516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3127613067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42972803115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43280649185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39279174804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.420494556427</t>
   </si>
   <si>
     <t xml:space="preserve">5.59902286529541</t>
@@ -3128,40 +3128,40 @@
     <t xml:space="preserve">5.52514886856079</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43588399887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24196577072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13115501403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08190536499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17116928100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04804611206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06343698501587</t>
+    <t xml:space="preserve">5.43588352203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24196672439575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13115453720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08190584182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17116975784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04804658889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06343746185303</t>
   </si>
   <si>
     <t xml:space="preserve">4.96186065673828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96493864059448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9772515296936</t>
+    <t xml:space="preserve">4.96493816375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97725057601929</t>
   </si>
   <si>
     <t xml:space="preserve">5.08498334884644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01418828964233</t>
+    <t xml:space="preserve">5.01418733596802</t>
   </si>
   <si>
     <t xml:space="preserve">5.06651449203491</t>
@@ -3170,16 +3170,16 @@
     <t xml:space="preserve">5.04496812820435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96801614761353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82950258255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87567472457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83258152008057</t>
+    <t xml:space="preserve">4.96801710128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82950305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8756742477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83258104324341</t>
   </si>
   <si>
     <t xml:space="preserve">4.82642507553101</t>
@@ -3188,58 +3188,58 @@
     <t xml:space="preserve">4.86336231231689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95262670516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79872226715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75562953948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68483400344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58325719833374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5924916267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29084014892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1523265838623</t>
+    <t xml:space="preserve">4.95262575149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79872274398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75562906265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68483352661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58325624465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59249114990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29083871841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15232610702515</t>
   </si>
   <si>
     <t xml:space="preserve">4.23851203918457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3677921295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55247640609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66328716278076</t>
+    <t xml:space="preserve">4.36779165267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5524754524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6632866859436</t>
   </si>
   <si>
     <t xml:space="preserve">4.5955696105957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56171035766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89106464385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90029859542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00495386123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98340749740601</t>
+    <t xml:space="preserve">4.56170988082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89106416702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90029907226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00495290756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98340654373169</t>
   </si>
   <si>
     <t xml:space="preserve">5.38663530349731</t>
@@ -3248,31 +3248,31 @@
     <t xml:space="preserve">5.56208515167236</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57747650146484</t>
+    <t xml:space="preserve">5.57747602462769</t>
   </si>
   <si>
     <t xml:space="preserve">5.78370714187622</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71906805038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69136428833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.700599193573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62056922912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87912750244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99609470367432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01456260681152</t>
+    <t xml:space="preserve">5.71906709671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69136476516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70059823989868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62056875228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87912797927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99609422683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01456308364868</t>
   </si>
   <si>
     <t xml:space="preserve">6.03918838500977</t>
@@ -3284,31 +3284,31 @@
     <t xml:space="preserve">5.89451789855957</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83603382110596</t>
+    <t xml:space="preserve">5.83603429794312</t>
   </si>
   <si>
     <t xml:space="preserve">5.76523876190186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81140995025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80833196640015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74984836578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74677038192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77447366714478</t>
+    <t xml:space="preserve">5.81140899658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8083324432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74984788894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74676990509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77447271347046</t>
   </si>
   <si>
     <t xml:space="preserve">5.60517835617065</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66673994064331</t>
+    <t xml:space="preserve">5.66674041748047</t>
   </si>
   <si>
     <t xml:space="preserve">5.7036771774292</t>
@@ -3317,88 +3317,88 @@
     <t xml:space="preserve">5.6975212097168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73445749282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72214603424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68520927429199</t>
+    <t xml:space="preserve">5.73445796966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72214508056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68520832061768</t>
   </si>
   <si>
     <t xml:space="preserve">5.45435285568237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46358776092529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37740087509155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28813648223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10960865020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20502853393555</t>
+    <t xml:space="preserve">5.46358728408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37740039825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28813695907593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1096076965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20502805709839</t>
   </si>
   <si>
     <t xml:space="preserve">5.15577936172485</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44819736480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78062963485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95915746688843</t>
+    <t xml:space="preserve">5.44819688796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78062868118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95915842056274</t>
   </si>
   <si>
     <t xml:space="preserve">6.0884370803833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.433180809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35315084457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42702531814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34699535369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34083986282349</t>
+    <t xml:space="preserve">6.43318176269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35315132141113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42702484130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34699487686157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34083843231201</t>
   </si>
   <si>
     <t xml:space="preserve">6.26696538925171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3223705291748</t>
+    <t xml:space="preserve">6.32237100601196</t>
   </si>
   <si>
     <t xml:space="preserve">6.37162065505981</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56861686706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4762749671936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63633441925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50705432891846</t>
+    <t xml:space="preserve">6.56861639022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47627401351929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63633394241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50705528259277</t>
   </si>
   <si>
     <t xml:space="preserve">6.5255241394043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45780515670776</t>
+    <t xml:space="preserve">6.45780563354492</t>
   </si>
   <si>
     <t xml:space="preserve">6.86411237716675</t>
@@ -3407,25 +3407,25 @@
     <t xml:space="preserve">6.84564399719238</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88873672485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06726551055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12267065048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03648471832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05495309829712</t>
+    <t xml:space="preserve">6.88873624801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06726503372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12267017364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03648519515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05495262145996</t>
   </si>
   <si>
     <t xml:space="preserve">6.82101821899414</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85179948806763</t>
+    <t xml:space="preserve">6.85179901123047</t>
   </si>
   <si>
     <t xml:space="preserve">6.90104913711548</t>
@@ -3434,22 +3434,22 @@
     <t xml:space="preserve">6.99954700469971</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01186084747314</t>
+    <t xml:space="preserve">7.01185894012451</t>
   </si>
   <si>
     <t xml:space="preserve">6.9256739616394</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96876668930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99339056015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80870676040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13498306274414</t>
+    <t xml:space="preserve">6.96876621246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9933910369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80870723724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13498210906982</t>
   </si>
   <si>
     <t xml:space="preserve">7.07957744598389</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">7.00570392608643</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74098920822144</t>
+    <t xml:space="preserve">6.74098873138428</t>
   </si>
   <si>
     <t xml:space="preserve">6.91951656341553</t>
@@ -3470,70 +3470,70 @@
     <t xml:space="preserve">7.10420227050781</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15345191955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11035919189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08573389053345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11651515960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16576433181763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57207107543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3258228302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72597312927246</t>
+    <t xml:space="preserve">7.15345239639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11035966873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08573436737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11651468276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16576337814331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57207012176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32582235336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72597360610962</t>
   </si>
   <si>
     <t xml:space="preserve">8.03378105163574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05840682983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99684524536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86141061782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79369258880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66441202163696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83062934875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91065883636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94759511947632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01531410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97837543487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09534358978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75675630569458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58168029785156</t>
+    <t xml:space="preserve">8.05840587615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9968433380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86140918731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79369020462036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66441297531128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83062839508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91065692901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94759559631348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01531314849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9783763885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0953426361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75675535202026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58167743682861</t>
   </si>
   <si>
     <t xml:space="preserve">8.47702407836914</t>
@@ -3542,19 +3542,19 @@
     <t xml:space="preserve">8.23077774047852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18152904510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10149955749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89218997955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36621379852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83678388595581</t>
+    <t xml:space="preserve">8.1815299987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1014986038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89218902587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36621475219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83678436279297</t>
   </si>
   <si>
     <t xml:space="preserve">7.95375061035156</t>
@@ -3566,10 +3566,10 @@
     <t xml:space="preserve">8.55089855194092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55705547332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6370849609375</t>
+    <t xml:space="preserve">8.55705451965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63708400726318</t>
   </si>
   <si>
     <t xml:space="preserve">8.56936645507812</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">8.75405120849609</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01260948181152</t>
+    <t xml:space="preserve">9.01261043548584</t>
   </si>
   <si>
     <t xml:space="preserve">8.96951770782471</t>
@@ -3596,22 +3596,22 @@
     <t xml:space="preserve">8.93873596191406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00645351409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76636505126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91411113739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03723335266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02492332458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10495281219482</t>
+    <t xml:space="preserve">9.0064525604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76636409759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91411209106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03723430633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02492141723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10495090484619</t>
   </si>
   <si>
     <t xml:space="preserve">9.33888626098633</t>
@@ -3620,19 +3620,19 @@
     <t xml:space="preserve">9.56050777435303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60360050201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83137893676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90525341033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94218826293945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75134944915771</t>
+    <t xml:space="preserve">9.60360145568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83137798309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90525150299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94218921661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7513484954834</t>
   </si>
   <si>
     <t xml:space="preserve">10.2438402175903</t>
@@ -3641,10 +3641,10 @@
     <t xml:space="preserve">10.305401802063</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5824289321899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0530004501343</t>
+    <t xml:space="preserve">10.5824298858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.05299949646</t>
   </si>
   <si>
     <t xml:space="preserve">10.4408378601074</t>
@@ -3656,13 +3656,13 @@
     <t xml:space="preserve">10.2930898666382</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1638107299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1453409194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2992467880249</t>
+    <t xml:space="preserve">10.1638116836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1453428268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2992458343506</t>
   </si>
   <si>
     <t xml:space="preserve">10.1699666976929</t>
@@ -3671,67 +3671,67 @@
     <t xml:space="preserve">10.4777746200562</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4716186523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7151441574097</t>
+    <t xml:space="preserve">10.4716196060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.715145111084</t>
   </si>
   <si>
     <t xml:space="preserve">10.688817024231</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5571823120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3860549926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4781999588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5703449249268</t>
+    <t xml:space="preserve">10.5571813583374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3860540390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4782018661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5703439712524</t>
   </si>
   <si>
     <t xml:space="preserve">10.5111093521118</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5242719650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.655909538269</t>
+    <t xml:space="preserve">10.5242729187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6559085845947</t>
   </si>
   <si>
     <t xml:space="preserve">10.7612171173096</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9520874023438</t>
+    <t xml:space="preserve">10.9520883560181</t>
   </si>
   <si>
     <t xml:space="preserve">11.0179061889648</t>
   </si>
   <si>
-    <t xml:space="preserve">11.037652015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.123215675354</t>
+    <t xml:space="preserve">11.0376529693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1232147216797</t>
   </si>
   <si>
     <t xml:space="preserve">11.0903072357178</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9257621765137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1495428085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1297969818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0705604553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9849977493286</t>
+    <t xml:space="preserve">10.9257612228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1495418548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1297979354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0705595016479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9849987030029</t>
   </si>
   <si>
     <t xml:space="preserve">10.7217273712158</t>
@@ -3740,10 +3740,10 @@
     <t xml:space="preserve">10.6032552719116</t>
   </si>
   <si>
-    <t xml:space="preserve">10.307074546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4189643859863</t>
+    <t xml:space="preserve">10.3070735931396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.418963432312</t>
   </si>
   <si>
     <t xml:space="preserve">10.0438022613525</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">10.0043115615845</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99114799499512</t>
+    <t xml:space="preserve">9.99114894866943</t>
   </si>
   <si>
     <t xml:space="preserve">9.49093341827393</t>
@@ -3761,37 +3761,37 @@
     <t xml:space="preserve">9.61598682403564</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71471309661865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1688566207886</t>
+    <t xml:space="preserve">9.71471405029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1688556671143</t>
   </si>
   <si>
     <t xml:space="preserve">10.037220954895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95823955535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.320237159729</t>
+    <t xml:space="preserve">9.95823860168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3202381134033</t>
   </si>
   <si>
     <t xml:space="preserve">10.4650363922119</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3531465530396</t>
+    <t xml:space="preserve">10.3531455993652</t>
   </si>
   <si>
     <t xml:space="preserve">10.4387092590332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3926382064819</t>
+    <t xml:space="preserve">10.392635345459</t>
   </si>
   <si>
     <t xml:space="preserve">10.3004922866821</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0569658279419</t>
+    <t xml:space="preserve">10.0569648742676</t>
   </si>
   <si>
     <t xml:space="preserve">10.221510887146</t>
@@ -3800,16 +3800,16 @@
     <t xml:space="preserve">10.5176906585693</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5045280456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1890325546265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2351036071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5115404129028</t>
+    <t xml:space="preserve">10.50452709198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1890344619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2351064682007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5115394592285</t>
   </si>
   <si>
     <t xml:space="preserve">11.6431770324707</t>
@@ -3818,10 +3818,10 @@
     <t xml:space="preserve">11.5641937255859</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3667421340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5378684997559</t>
+    <t xml:space="preserve">11.3667402267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5378675460815</t>
   </si>
   <si>
     <t xml:space="preserve">11.4983768463135</t>
@@ -3833,199 +3833,199 @@
     <t xml:space="preserve">11.8208827972412</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8735389709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9985933303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1433925628662</t>
+    <t xml:space="preserve">11.8735380172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9985914230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1433916091919</t>
   </si>
   <si>
     <t xml:space="preserve">11.7353210449219</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6958312988281</t>
+    <t xml:space="preserve">11.6958303451538</t>
   </si>
   <si>
     <t xml:space="preserve">12.0775747299194</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9656848907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2811784744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6563386917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7616500854492</t>
+    <t xml:space="preserve">11.9656820297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.281177520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6563396453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7616491317749</t>
   </si>
   <si>
     <t xml:space="preserve">11.7813930511475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6760845184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.616849899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0315008163452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8801193237305</t>
+    <t xml:space="preserve">11.6760854721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6168489456177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0315017700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8801183700562</t>
   </si>
   <si>
     <t xml:space="preserve">11.7945566177368</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1236457824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6370258331299</t>
+    <t xml:space="preserve">12.1236448287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6370277404785</t>
   </si>
   <si>
     <t xml:space="preserve">13.5058212280273</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6242942810059</t>
+    <t xml:space="preserve">13.6242933273315</t>
   </si>
   <si>
     <t xml:space="preserve">14.2166538238525</t>
   </si>
   <si>
-    <t xml:space="preserve">14.26930809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0455274581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.085018157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.295205116272</t>
+    <t xml:space="preserve">14.2693071365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0455284118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0850200653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2952032089233</t>
   </si>
   <si>
     <t xml:space="preserve">12.9661159515381</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0709924697876</t>
+    <t xml:space="preserve">12.0709915161133</t>
   </si>
   <si>
     <t xml:space="preserve">12.6962614059448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4659004211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7419023513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9722661972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7550678253174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7085628509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2412557601929</t>
+    <t xml:space="preserve">12.4658994674683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7419033050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.972264289856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7550668716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7085618972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2412567138672</t>
   </si>
   <si>
     <t xml:space="preserve">11.1956148147583</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4979467391968</t>
+    <t xml:space="preserve">10.4979448318481</t>
   </si>
   <si>
     <t xml:space="preserve">10.8204526901245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2943420410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5839405059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1894645690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1038999557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1302289962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4329900741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3737545013428</t>
+    <t xml:space="preserve">11.2943410873413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5839395523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1894655227661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1039018630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1302270889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4329891204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3737525939941</t>
   </si>
   <si>
     <t xml:space="preserve">12.2684450149536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4066619873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4395732879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2881908416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.393500328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6826677322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0380840301514</t>
+    <t xml:space="preserve">12.406662940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4395713806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2881898880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3934993743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6826658248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0380830764771</t>
   </si>
   <si>
     <t xml:space="preserve">11.8932828903198</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9393548965454</t>
+    <t xml:space="preserve">11.9393558502197</t>
   </si>
   <si>
     <t xml:space="preserve">11.6629219055176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9525194168091</t>
+    <t xml:space="preserve">11.9525203704834</t>
   </si>
   <si>
     <t xml:space="preserve">11.3799057006836</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5049591064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3469953536987</t>
+    <t xml:space="preserve">11.5049571990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.346996307373</t>
   </si>
   <si>
     <t xml:space="preserve">10.8007078170776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0244884490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4457225799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7089948654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4588871002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.974048614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9879703521729</t>
+    <t xml:space="preserve">11.0244874954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4457216262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7089939117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4588851928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9740495681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9879713058472</t>
   </si>
   <si>
     <t xml:space="preserve">11.9183559417725</t>
@@ -4034,52 +4034,52 @@
     <t xml:space="preserve">12.1550512313843</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0645503997803</t>
+    <t xml:space="preserve">12.064549446106</t>
   </si>
   <si>
     <t xml:space="preserve">12.1341667175293</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8208913803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8000087738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7791213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.751275062561</t>
+    <t xml:space="preserve">11.8208923339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8000068664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7791223526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7512741088867</t>
   </si>
   <si>
     <t xml:space="preserve">11.7582368850708</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5563497543335</t>
+    <t xml:space="preserve">11.5563488006592</t>
   </si>
   <si>
     <t xml:space="preserve">11.4031925201416</t>
   </si>
   <si>
-    <t xml:space="preserve">11.180419921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5121011734009</t>
+    <t xml:space="preserve">11.1804189682007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5121002197266</t>
   </si>
   <si>
     <t xml:space="preserve">9.97605228424072</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0804767608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4355230331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95516777038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94124412536621</t>
+    <t xml:space="preserve">10.0804777145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4355211257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95516872406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94124507904053</t>
   </si>
   <si>
     <t xml:space="preserve">10.1640186309814</t>
@@ -4088,19 +4088,19 @@
     <t xml:space="preserve">10.0038995742798</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9969367980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74631977081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98997688293457</t>
+    <t xml:space="preserve">9.99693775177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74631786346436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98997592926025</t>
   </si>
   <si>
     <t xml:space="preserve">9.927321434021</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89947605133057</t>
+    <t xml:space="preserve">9.89947509765625</t>
   </si>
   <si>
     <t xml:space="preserve">9.71847152709961</t>
@@ -4115,52 +4115,52 @@
     <t xml:space="preserve">9.23811817169189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8621883392334</t>
+    <t xml:space="preserve">8.86218738555908</t>
   </si>
   <si>
     <t xml:space="preserve">8.79257106781006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98053646087646</t>
+    <t xml:space="preserve">8.98053741455078</t>
   </si>
   <si>
     <t xml:space="preserve">9.23115634918213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95965003967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00838279724121</t>
+    <t xml:space="preserve">8.95965099334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00838184356689</t>
   </si>
   <si>
     <t xml:space="preserve">8.62549209594727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20779323577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40271854400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54195117950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76472473144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79953193664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74384021759033</t>
+    <t xml:space="preserve">8.20779228210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40271759033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54195213317871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.764723777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79953479766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74384117126465</t>
   </si>
   <si>
     <t xml:space="preserve">8.81345653533936</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07800006866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77168750762939</t>
+    <t xml:space="preserve">9.07799911499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77168655395508</t>
   </si>
   <si>
     <t xml:space="preserve">8.91788196563721</t>
@@ -4172,13 +4172,13 @@
     <t xml:space="preserve">9.11977005004883</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21723175048828</t>
+    <t xml:space="preserve">9.2172327041626</t>
   </si>
   <si>
     <t xml:space="preserve">9.09888458251953</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47481250762939</t>
+    <t xml:space="preserve">9.47481346130371</t>
   </si>
   <si>
     <t xml:space="preserve">9.53746795654297</t>
@@ -4193,25 +4193,25 @@
     <t xml:space="preserve">9.01534461975098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11280727386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33557987213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49569797515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03622913360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66726112365723</t>
+    <t xml:space="preserve">9.11280822753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33558082580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49569892883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03623008728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66726207733154</t>
   </si>
   <si>
     <t xml:space="preserve">8.77864837646484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75776290893555</t>
+    <t xml:space="preserve">8.75776195526123</t>
   </si>
   <si>
     <t xml:space="preserve">8.63245296478271</t>
@@ -4220,7 +4220,7 @@
     <t xml:space="preserve">8.3957576751709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33310222625732</t>
+    <t xml:space="preserve">8.33310317993164</t>
   </si>
   <si>
     <t xml:space="preserve">8.38879489898682</t>
@@ -4229,40 +4229,40 @@
     <t xml:space="preserve">8.31917858123779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10336780548096</t>
+    <t xml:space="preserve">8.10336685180664</t>
   </si>
   <si>
     <t xml:space="preserve">8.27044773101807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04071140289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99894332885742</t>
+    <t xml:space="preserve">8.0407133102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99894142150879</t>
   </si>
   <si>
     <t xml:space="preserve">7.88059377670288</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9502100944519</t>
+    <t xml:space="preserve">7.95021057128906</t>
   </si>
   <si>
     <t xml:space="preserve">8.1312141418457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58372211456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59068489074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7090311050415</t>
+    <t xml:space="preserve">8.5837230682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59068393707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70903205871582</t>
   </si>
   <si>
     <t xml:space="preserve">8.51410579681396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46537303924561</t>
+    <t xml:space="preserve">8.46537399291992</t>
   </si>
   <si>
     <t xml:space="preserve">8.17994594573975</t>
@@ -4271,70 +4271,70 @@
     <t xml:space="preserve">8.22171497344971</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94325017929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95717239379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82490110397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74136161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49074172973633</t>
+    <t xml:space="preserve">7.94324970245361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95717287063599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82490205764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74136114120483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49074125289917</t>
   </si>
   <si>
     <t xml:space="preserve">7.92236471176147</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01286602020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9293270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84578609466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75528573989868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6856689453125</t>
+    <t xml:space="preserve">8.01286506652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92932605743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84578514099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75528526306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68566846847534</t>
   </si>
   <si>
     <t xml:space="preserve">7.76920795440674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6578221321106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66478395462036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88755655288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86667156219482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90148067474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98501920700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07552051544189</t>
+    <t xml:space="preserve">7.65782165527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66478300094604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88755702972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86667060852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90148019790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98501968383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07552146911621</t>
   </si>
   <si>
     <t xml:space="preserve">8.15209865570068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2982931137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45841217041016</t>
+    <t xml:space="preserve">8.29829406738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45841026306152</t>
   </si>
   <si>
     <t xml:space="preserve">8.49322032928467</t>
@@ -4343,34 +4343,34 @@
     <t xml:space="preserve">9.10584545135498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07103729248047</t>
+    <t xml:space="preserve">9.07103633880615</t>
   </si>
   <si>
     <t xml:space="preserve">9.37038898468018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56531429290771</t>
+    <t xml:space="preserve">9.56531524658203</t>
   </si>
   <si>
     <t xml:space="preserve">9.69062423706055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6627779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62797069549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52354717254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83681964874268</t>
+    <t xml:space="preserve">9.66277885437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62796974182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52354621887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83682060241699</t>
   </si>
   <si>
     <t xml:space="preserve">9.7843770980835</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81434535980225</t>
+    <t xml:space="preserve">9.81434440612793</t>
   </si>
   <si>
     <t xml:space="preserve">9.8293285369873</t>
@@ -4382,31 +4382,31 @@
     <t xml:space="preserve">9.85180282592773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.88926124572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76189994812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77688503265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70945739746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55962085723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39479923248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4097843170166</t>
+    <t xml:space="preserve">9.88926219940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76190185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77688598632812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70945835113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55962181091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39480018615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40978336334229</t>
   </si>
   <si>
     <t xml:space="preserve">9.56711292266846</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48470211029053</t>
+    <t xml:space="preserve">9.48470115661621</t>
   </si>
   <si>
     <t xml:space="preserve">9.67199802398682</t>
@@ -4418,43 +4418,43 @@
     <t xml:space="preserve">9.52216053009033</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60457134246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.016622543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84431076049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94919776916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88177013397217</t>
+    <t xml:space="preserve">9.60457229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0166254043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84431171417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94919872283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8817720413208</t>
   </si>
   <si>
     <t xml:space="preserve">9.96418190002441</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97167301177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0690679550171</t>
+    <t xml:space="preserve">9.9716739654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0690689086914</t>
   </si>
   <si>
     <t xml:space="preserve">10.2263975143433</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4736270904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5035963058472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5110864639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.660924911499</t>
+    <t xml:space="preserve">10.4736280441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5035972595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5110874176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6609239578247</t>
   </si>
   <si>
     <t xml:space="preserve">10.6834001541138</t>
@@ -4463,10 +4463,10 @@
     <t xml:space="preserve">10.743335723877</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8182544708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8032712936401</t>
+    <t xml:space="preserve">10.8182525634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8032703399658</t>
   </si>
   <si>
     <t xml:space="preserve">10.7957792282104</t>
@@ -4475,16 +4475,16 @@
     <t xml:space="preserve">10.7658109664917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6534337997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.863205909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8482208251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6759080886841</t>
+    <t xml:space="preserve">10.6534328460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8632049560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8482217788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6759090423584</t>
   </si>
   <si>
     <t xml:space="preserve">10.8781890869141</t>
@@ -4502,28 +4502,28 @@
     <t xml:space="preserve">11.5824241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7772130966187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7172784805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8071804046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9195575714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9120655059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1143484115601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2192316055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1967582702637</t>
+    <t xml:space="preserve">11.777214050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7172775268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8071794509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9195585250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9120674133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1143474578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2192325592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1967573165894</t>
   </si>
   <si>
     <t xml:space="preserve">11.9345426559448</t>
@@ -4532,46 +4532,46 @@
     <t xml:space="preserve">11.792197227478</t>
   </si>
   <si>
-    <t xml:space="preserve">12.286660194397</t>
+    <t xml:space="preserve">12.2866592407227</t>
   </si>
   <si>
     <t xml:space="preserve">12.1218395233154</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9045743942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6573438644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5224885940552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6798181533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6423587799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7097864151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7322616577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3426847457886</t>
+    <t xml:space="preserve">11.9045753479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6573448181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5224905014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.67982006073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6423597335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7097873687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7322626113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3426837921143</t>
   </si>
   <si>
     <t xml:space="preserve">10.9006652832031</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0954532623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5785150527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5934982299805</t>
+    <t xml:space="preserve">11.0954523086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5785140991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5934991836548</t>
   </si>
   <si>
     <t xml:space="preserve">10.563530921936</t>
@@ -4580,58 +4580,58 @@
     <t xml:space="preserve">10.4961042404175</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2863311767578</t>
+    <t xml:space="preserve">10.2863321304321</t>
   </si>
   <si>
     <t xml:space="preserve">10.3237905502319</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1964282989502</t>
+    <t xml:space="preserve">10.1964292526245</t>
   </si>
   <si>
     <t xml:space="preserve">10.3387746810913</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4661359786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.458643913269</t>
+    <t xml:space="preserve">10.466136932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4586448669434</t>
   </si>
   <si>
     <t xml:space="preserve">10.3837251663208</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5260725021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.63844871521</t>
+    <t xml:space="preserve">10.5260715484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6384496688843</t>
   </si>
   <si>
     <t xml:space="preserve">11.0280256271362</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9680919647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2078313827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3052244186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2452898025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4176034927368</t>
+    <t xml:space="preserve">10.968092918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2078304290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3052253723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2452907562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4176025390625</t>
   </si>
   <si>
     <t xml:space="preserve">11.5449647903442</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3876361846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3277006149292</t>
+    <t xml:space="preserve">11.3876352310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3276996612549</t>
   </si>
   <si>
     <t xml:space="preserve">11.4026203155518</t>
@@ -4640,61 +4640,61 @@
     <t xml:space="preserve">11.0130424499512</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0430107116699</t>
+    <t xml:space="preserve">11.0430088043213</t>
   </si>
   <si>
     <t xml:space="preserve">11.2377986907959</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3576688766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7807950973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8107614517212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7882862091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3391132354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2774877548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1003141403198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0695009231567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2389707565308</t>
+    <t xml:space="preserve">11.3576679229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7807960510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8107633590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7882852554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3391122817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2774887084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1003131866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0695018768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2389717102051</t>
   </si>
   <si>
     <t xml:space="preserve">11.2004547119141</t>
   </si>
   <si>
-    <t xml:space="preserve">10.946249961853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7844839096069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9539527893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0772047042847</t>
+    <t xml:space="preserve">10.9462509155273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7844829559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9539518356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0772037506104</t>
   </si>
   <si>
     <t xml:space="preserve">10.9770622253418</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0386877059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.03098487854</t>
+    <t xml:space="preserve">11.038688659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0309839248657</t>
   </si>
   <si>
     <t xml:space="preserve">10.9847660064697</t>
@@ -4703,13 +4703,13 @@
     <t xml:space="preserve">10.8923273086548</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8384037017822</t>
+    <t xml:space="preserve">10.8384046554565</t>
   </si>
   <si>
     <t xml:space="preserve">10.9616565704346</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9154367446899</t>
+    <t xml:space="preserve">10.9154376983643</t>
   </si>
   <si>
     <t xml:space="preserve">10.8692178726196</t>
@@ -4724,13 +4724,13 @@
     <t xml:space="preserve">11.0155782699585</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8461074829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9000301361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0463914871216</t>
+    <t xml:space="preserve">10.8461084365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9000310897827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0463905334473</t>
   </si>
   <si>
     <t xml:space="preserve">11.0926103591919</t>
@@ -4742,13 +4742,13 @@
     <t xml:space="preserve">11.2928943634033</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4007377624512</t>
+    <t xml:space="preserve">11.4007387161255</t>
   </si>
   <si>
     <t xml:space="preserve">11.4161443710327</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2543783187866</t>
+    <t xml:space="preserve">11.2543773651123</t>
   </si>
   <si>
     <t xml:space="preserve">11.3699264526367</t>
@@ -4757,25 +4757,25 @@
     <t xml:space="preserve">11.246675491333</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3622226715088</t>
+    <t xml:space="preserve">11.3622217178345</t>
   </si>
   <si>
     <t xml:space="preserve">11.5085830688477</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5856142044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6626472473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8244152069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7858982086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7473821640015</t>
+    <t xml:space="preserve">11.5856151580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6626482009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8244142532349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7858991622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7473831176758</t>
   </si>
   <si>
     <t xml:space="preserve">11.7319755554199</t>
@@ -4784,28 +4784,28 @@
     <t xml:space="preserve">11.7088670730591</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8167123794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0015878677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.271201133728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3713426589966</t>
+    <t xml:space="preserve">11.8167114257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0015869140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2712001800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3713417053223</t>
   </si>
   <si>
     <t xml:space="preserve">12.1325426101685</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9322595596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0092906951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5562191009521</t>
+    <t xml:space="preserve">11.9322605133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0092926025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5562181472778</t>
   </si>
   <si>
     <t xml:space="preserve">12.494592666626</t>
@@ -4817,31 +4817,31 @@
     <t xml:space="preserve">12.3328266143799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.355936050415</t>
+    <t xml:space="preserve">12.3559370040894</t>
   </si>
   <si>
     <t xml:space="preserve">12.4021558761597</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4637813568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5639209747314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2866077423096</t>
+    <t xml:space="preserve">12.4637804031372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5639200210571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2866067886353</t>
   </si>
   <si>
     <t xml:space="preserve">12.2326850891113</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3636388778687</t>
+    <t xml:space="preserve">12.3636379241943</t>
   </si>
   <si>
     <t xml:space="preserve">12.3020133972168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4175615310669</t>
+    <t xml:space="preserve">12.4175624847412</t>
   </si>
   <si>
     <t xml:space="preserve">12.44837474823</t>
@@ -4850,19 +4850,19 @@
     <t xml:space="preserve">12.5408124923706</t>
   </si>
   <si>
-    <t xml:space="preserve">12.533109664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3482322692871</t>
+    <t xml:space="preserve">12.5331087112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3482332229614</t>
   </si>
   <si>
     <t xml:space="preserve">12.3097162246704</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0709171295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9630718231201</t>
+    <t xml:space="preserve">12.0709161758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9630727767944</t>
   </si>
   <si>
     <t xml:space="preserve">11.8783369064331</t>
@@ -4871,10 +4871,10 @@
     <t xml:space="preserve">12.1402454376221</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1171360015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9784784317017</t>
+    <t xml:space="preserve">12.1171350479126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.978479385376</t>
   </si>
   <si>
     <t xml:space="preserve">11.9707746505737</t>
@@ -4892,7 +4892,7 @@
     <t xml:space="preserve">12.3944520950317</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4098587036133</t>
+    <t xml:space="preserve">12.409857749939</t>
   </si>
   <si>
     <t xml:space="preserve">12.6101408004761</t>
@@ -4901,13 +4901,13 @@
     <t xml:space="preserve">12.317419052124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5177021026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6948757171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9336757659912</t>
+    <t xml:space="preserve">12.5177030563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6948776245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9336767196655</t>
   </si>
   <si>
     <t xml:space="preserve">12.8412380218506</t>
@@ -4922,34 +4922,34 @@
     <t xml:space="preserve">12.6640644073486</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3867483139038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1710596084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6164293289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8552274703979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2789030075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4252634048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5793285369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8874549865723</t>
+    <t xml:space="preserve">12.3867473602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1710586547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6164283752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8552284240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2789039611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4252643585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.579327583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8874559402466</t>
   </si>
   <si>
     <t xml:space="preserve">12.7719078063965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8104228973389</t>
+    <t xml:space="preserve">12.8104238510132</t>
   </si>
   <si>
     <t xml:space="preserve">12.9413776397705</t>
@@ -4958,10 +4958,10 @@
     <t xml:space="preserve">13.341944694519</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1570672988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2726154327393</t>
+    <t xml:space="preserve">13.1570682525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2726163864136</t>
   </si>
   <si>
     <t xml:space="preserve">13.1493654251099</t>
@@ -4970,10 +4970,10 @@
     <t xml:space="preserve">13.0954427719116</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2880229949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.21351146698</t>
+    <t xml:space="preserve">13.2880239486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2135105133057</t>
   </si>
   <si>
     <t xml:space="preserve">12.9237403869629</t>
@@ -4985,19 +4985,19 @@
     <t xml:space="preserve">13.0313701629639</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0893239974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.840950012207</t>
+    <t xml:space="preserve">13.0893249511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8409509658813</t>
   </si>
   <si>
     <t xml:space="preserve">12.8740663528442</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0396490097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.998251914978</t>
+    <t xml:space="preserve">13.0396499633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9982528686523</t>
   </si>
   <si>
     <t xml:space="preserve">13.1886739730835</t>
@@ -5006,7 +5006,7 @@
     <t xml:space="preserve">13.0148124694824</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1224412918091</t>
+    <t xml:space="preserve">13.1224403381348</t>
   </si>
   <si>
     <t xml:space="preserve">13.114161491394</t>
@@ -5021,28 +5021,28 @@
     <t xml:space="preserve">13.2963027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1803941726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0479278564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9568567276001</t>
+    <t xml:space="preserve">13.1803951263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0479288101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9568576812744</t>
   </si>
   <si>
     <t xml:space="preserve">13.0727653503418</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1307191848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1472787857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2631855010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6523056030273</t>
+    <t xml:space="preserve">13.1307201385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1472778320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2631864547729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.652304649353</t>
   </si>
   <si>
     <t xml:space="preserve">13.3625345230103</t>
@@ -5051,16 +5051,16 @@
     <t xml:space="preserve">13.3376989364624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8657865524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9651374816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9734153747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9154624938965</t>
+    <t xml:space="preserve">12.8657875061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9651365280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9734163284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9154634475708</t>
   </si>
   <si>
     <t xml:space="preserve">13.2052326202393</t>
@@ -5069,31 +5069,31 @@
     <t xml:space="preserve">13.3128604888916</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2549076080322</t>
+    <t xml:space="preserve">13.2549066543579</t>
   </si>
   <si>
     <t xml:space="preserve">13.1389980316162</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3708143234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3873739242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5777931213379</t>
+    <t xml:space="preserve">13.3708152770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3873729705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5777921676636</t>
   </si>
   <si>
     <t xml:space="preserve">13.4867238998413</t>
   </si>
   <si>
-    <t xml:space="preserve">13.809609413147</t>
+    <t xml:space="preserve">13.8096103668213</t>
   </si>
   <si>
     <t xml:space="preserve">13.701979637146</t>
   </si>
   <si>
-    <t xml:space="preserve">13.710259437561</t>
+    <t xml:space="preserve">13.7102584838867</t>
   </si>
   <si>
     <t xml:space="preserve">13.5943517684937</t>
@@ -5108,13 +5108,13 @@
     <t xml:space="preserve">13.9006795883179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8592834472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0497026443481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.24840259552</t>
+    <t xml:space="preserve">13.8592824935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0497035980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2484035491943</t>
   </si>
   <si>
     <t xml:space="preserve">14.1159372329712</t>
@@ -5123,10 +5123,10 @@
     <t xml:space="preserve">13.9917507171631</t>
   </si>
   <si>
-    <t xml:space="preserve">13.917236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0248680114746</t>
+    <t xml:space="preserve">13.9172372817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0248670578003</t>
   </si>
   <si>
     <t xml:space="preserve">14.0000286102295</t>
@@ -5135,13 +5135,13 @@
     <t xml:space="preserve">13.983470916748</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1821699142456</t>
+    <t xml:space="preserve">14.1821708679199</t>
   </si>
   <si>
     <t xml:space="preserve">14.1242170333862</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0414257049561</t>
+    <t xml:space="preserve">14.0414247512817</t>
   </si>
   <si>
     <t xml:space="preserve">14.0165882110596</t>
@@ -5156,10 +5156,10 @@
     <t xml:space="preserve">14.356032371521</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3891487121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7037572860718</t>
+    <t xml:space="preserve">14.3891477584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7037563323975</t>
   </si>
   <si>
     <t xml:space="preserve">14.8610601425171</t>
@@ -5177,28 +5177,28 @@
     <t xml:space="preserve">15.2170639038086</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3578090667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1591081619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2750186920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8131628036499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.467212677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.102933883667</t>
+    <t xml:space="preserve">15.3578081130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.159107208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2750177383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8131618499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4672145843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1029319763184</t>
   </si>
   <si>
     <t xml:space="preserve">16.1774444580078</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1608848571777</t>
+    <t xml:space="preserve">16.1608867645264</t>
   </si>
   <si>
     <t xml:space="preserve">16.3678646087646</t>
@@ -5213,40 +5213,40 @@
     <t xml:space="preserve">16.8066577911377</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2206172943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1709423065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9556827545166</t>
+    <t xml:space="preserve">17.2206153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1709403991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.955680847168</t>
   </si>
   <si>
     <t xml:space="preserve">17.4358730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3365249633789</t>
+    <t xml:space="preserve">17.3365230560303</t>
   </si>
   <si>
     <t xml:space="preserve">17.5186653137207</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4524307250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6511306762695</t>
+    <t xml:space="preserve">17.4524326324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6511325836182</t>
   </si>
   <si>
     <t xml:space="preserve">17.7670383453369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8167133331299</t>
+    <t xml:space="preserve">17.8167152404785</t>
   </si>
   <si>
     <t xml:space="preserve">17.0881481170654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2040596008301</t>
+    <t xml:space="preserve">17.2040576934814</t>
   </si>
   <si>
     <t xml:space="preserve">16.9060077667236</t>
@@ -5255,13 +5255,13 @@
     <t xml:space="preserve">17.1212673187256</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0520210266113</t>
+    <t xml:space="preserve">17.0520191192627</t>
   </si>
   <si>
     <t xml:space="preserve">16.9914283752441</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7317523956299</t>
+    <t xml:space="preserve">16.7317543029785</t>
   </si>
   <si>
     <t xml:space="preserve">16.6798191070557</t>
@@ -5270,10 +5270,10 @@
     <t xml:space="preserve">16.8789024353027</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8962154388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8356266021729</t>
+    <t xml:space="preserve">16.8962135314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8356246948242</t>
   </si>
   <si>
     <t xml:space="preserve">16.5586357116699</t>
@@ -5285,7 +5285,7 @@
     <t xml:space="preserve">17.4675006866455</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3463172912598</t>
+    <t xml:space="preserve">17.3463191986084</t>
   </si>
   <si>
     <t xml:space="preserve">17.1299228668213</t>
@@ -5294,19 +5294,19 @@
     <t xml:space="preserve">17.3636302947998</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3290061950684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7923450469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0953006744385</t>
+    <t xml:space="preserve">17.329008102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7923431396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0952987670898</t>
   </si>
   <si>
     <t xml:space="preserve">16.7230987548828</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3855209350586</t>
+    <t xml:space="preserve">16.38551902771</t>
   </si>
   <si>
     <t xml:space="preserve">16.7490653991699</t>
@@ -5315,7 +5315,7 @@
     <t xml:space="preserve">16.7836875915527</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8009986877441</t>
+    <t xml:space="preserve">16.8010005950928</t>
   </si>
   <si>
     <t xml:space="preserve">17.0000839233398</t>
@@ -5324,19 +5324,19 @@
     <t xml:space="preserve">16.775032043457</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6406173706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1991691589355</t>
+    <t xml:space="preserve">17.6406154632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1991710662842</t>
   </si>
   <si>
     <t xml:space="preserve">17.0866413116455</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8183097839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7271747589111</t>
+    <t xml:space="preserve">16.8183116912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7271766662598</t>
   </si>
   <si>
     <t xml:space="preserve">17.5194358825684</t>
@@ -5345,7 +5345,7 @@
     <t xml:space="preserve">17.7791118621826</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9176044464111</t>
+    <t xml:space="preserve">17.9176063537598</t>
   </si>
   <si>
     <t xml:space="preserve">18.0387859344482</t>
@@ -5357,13 +5357,13 @@
     <t xml:space="preserve">18.3677082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">18.350399017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0560989379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1599674224854</t>
+    <t xml:space="preserve">18.3503971099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0560970306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1599655151367</t>
   </si>
   <si>
     <t xml:space="preserve">18.1253452301025</t>
@@ -5375,13 +5375,13 @@
     <t xml:space="preserve">18.4888916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2638397216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4715766906738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4196453094482</t>
+    <t xml:space="preserve">18.2638378143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4715805053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4196434020996</t>
   </si>
   <si>
     <t xml:space="preserve">18.3157730102539</t>
@@ -5399,28 +5399,28 @@
     <t xml:space="preserve">18.9563064575195</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7831897735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4501895904541</t>
+    <t xml:space="preserve">18.7831916809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4501876831055</t>
   </si>
   <si>
     <t xml:space="preserve">17.0693302154541</t>
   </si>
   <si>
-    <t xml:space="preserve">17.043363571167</t>
+    <t xml:space="preserve">17.0433654785156</t>
   </si>
   <si>
     <t xml:space="preserve">17.4848117828369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6059951782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9522285461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0734081268311</t>
+    <t xml:space="preserve">17.605993270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9522266387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0734100341797</t>
   </si>
   <si>
     <t xml:space="preserve">17.8829822540283</t>
@@ -5429,16 +5429,16 @@
     <t xml:space="preserve">18.1426544189453</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0907230377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2292137145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4023303985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3850193023682</t>
+    <t xml:space="preserve">18.0907211303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2292156219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4023323059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3850212097168</t>
   </si>
   <si>
     <t xml:space="preserve">18.2811527252197</t>
@@ -5450,7 +5450,7 @@
     <t xml:space="preserve">17.9349155426025</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8483600616455</t>
+    <t xml:space="preserve">17.8483581542969</t>
   </si>
   <si>
     <t xml:space="preserve">17.969539642334</t>
@@ -5462,16 +5462,16 @@
     <t xml:space="preserve">18.436954498291</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5062026977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6100730895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0082416534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1640472412109</t>
+    <t xml:space="preserve">18.5062007904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.610071182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0082397460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1640453338623</t>
   </si>
   <si>
     <t xml:space="preserve">18.5581378936768</t>
@@ -5492,40 +5492,40 @@
     <t xml:space="preserve">19.3025398254395</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4064121246338</t>
+    <t xml:space="preserve">19.4064102172852</t>
   </si>
   <si>
     <t xml:space="preserve">19.5968379974365</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7180213928223</t>
+    <t xml:space="preserve">19.7180194854736</t>
   </si>
   <si>
     <t xml:space="preserve">19.7007083892822</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6314640045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9950065612793</t>
+    <t xml:space="preserve">19.631462097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9950084686279</t>
   </si>
   <si>
     <t xml:space="preserve">19.8045787811279</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6660861968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4237232208252</t>
+    <t xml:space="preserve">19.6660842895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4237213134766</t>
   </si>
   <si>
     <t xml:space="preserve">19.3198509216309</t>
   </si>
   <si>
-    <t xml:space="preserve">19.285228729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3544750213623</t>
+    <t xml:space="preserve">19.2852306365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3544769287109</t>
   </si>
   <si>
     <t xml:space="preserve">19.1121101379395</t>
@@ -72247,7 +72247,7 @@
     </row>
     <row r="2531">
       <c r="A2531" s="1" t="n">
-        <v>46002.6911342593</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B2531" t="n">
         <v>143617</v>
@@ -72268,6 +72268,32 @@
         <v>2038</v>
       </c>
       <c r="H2531" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" s="1" t="n">
+        <v>46003.6910648148</v>
+      </c>
+      <c r="B2532" t="n">
+        <v>114056</v>
+      </c>
+      <c r="C2532" t="n">
+        <v>25.0799999237061</v>
+      </c>
+      <c r="D2532" t="n">
+        <v>24.7600002288818</v>
+      </c>
+      <c r="E2532" t="n">
+        <v>24.7600002288818</v>
+      </c>
+      <c r="F2532" t="n">
+        <v>24.7800006866455</v>
+      </c>
+      <c r="G2532" t="s">
+        <v>2026</v>
+      </c>
+      <c r="H2532" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IF.MI.xlsx
+++ b/data/IF.MI.xlsx
@@ -38,130 +38,130 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9798784255981</t>
+    <t xml:space="preserve">14.9798803329468</t>
   </si>
   <si>
     <t xml:space="preserve">IF.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6498355865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5859546661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8460121154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6703395843506</t>
+    <t xml:space="preserve">14.6498336791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5859508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8460083007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.670337677002</t>
   </si>
   <si>
     <t xml:space="preserve">13.6863088607788</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7342205047607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4946670532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1494388580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1859149932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7980995178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9365043640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7395429611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6338634490967</t>
+    <t xml:space="preserve">13.7342176437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4946699142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1494379043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1859159469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7980976104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9365062713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.739541053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6338653564453</t>
   </si>
   <si>
     <t xml:space="preserve">14.6551561355591</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1715240478516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1768426895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8148584365845</t>
+    <t xml:space="preserve">15.17151927948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1768455505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8148565292358</t>
   </si>
   <si>
     <t xml:space="preserve">15.3312196731567</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2779884338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0118236541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4422235488892</t>
+    <t xml:space="preserve">15.2779893875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0118207931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4422216415405</t>
   </si>
   <si>
     <t xml:space="preserve">14.2399368286133</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8406867980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4300003051758</t>
+    <t xml:space="preserve">13.8406858444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4299993515015</t>
   </si>
   <si>
     <t xml:space="preserve">12.467264175415</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0794496536255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1060657501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1592988967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8353633880615</t>
+    <t xml:space="preserve">13.0794486999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1060676574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1592960357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8353624343872</t>
   </si>
   <si>
     <t xml:space="preserve">13.7448663711548</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6596918106079</t>
+    <t xml:space="preserve">13.6596908569336</t>
   </si>
   <si>
     <t xml:space="preserve">13.5851669311523</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6437215805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6924209594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2559080123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0323257446289</t>
+    <t xml:space="preserve">13.6437225341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.692421913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2559089660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0323247909546</t>
   </si>
   <si>
     <t xml:space="preserve">14.4741630554199</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3730230331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3197870254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7509765625</t>
+    <t xml:space="preserve">14.3730211257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3197841644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7509775161743</t>
   </si>
   <si>
     <t xml:space="preserve">14.5486917495728</t>
@@ -170,40 +170,40 @@
     <t xml:space="preserve">14.2665519714355</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7501888275146</t>
+    <t xml:space="preserve">13.7501878738403</t>
   </si>
   <si>
     <t xml:space="preserve">13.8566560745239</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4840230941772</t>
+    <t xml:space="preserve">13.4840211868286</t>
   </si>
   <si>
     <t xml:space="preserve">13.7874507904053</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0110311508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4528713226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6391887664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2300796508789</t>
+    <t xml:space="preserve">14.0110321044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4528684616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6391849517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2300777435303</t>
   </si>
   <si>
     <t xml:space="preserve">15.4536571502686</t>
   </si>
   <si>
-    <t xml:space="preserve">15.320574760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1981372833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3418664932251</t>
+    <t xml:space="preserve">15.3205728530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1981363296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3418674468994</t>
   </si>
   <si>
     <t xml:space="preserve">15.3637399673462</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">15.9159603118896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6261796951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0848932266235</t>
+    <t xml:space="preserve">15.6261787414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0848951339722</t>
   </si>
   <si>
     <t xml:space="preserve">15.593376159668</t>
@@ -227,58 +227,58 @@
     <t xml:space="preserve">14.8497905731201</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9263343811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.024751663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1231660842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8825931549072</t>
+    <t xml:space="preserve">14.9263372421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0247497558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1231679916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8825988769531</t>
   </si>
   <si>
     <t xml:space="preserve">14.5436096191406</t>
   </si>
   <si>
-    <t xml:space="preserve">14.68577003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5053367614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4123888015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6420269012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2374277114868</t>
+    <t xml:space="preserve">14.6857643127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.505334854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4123907089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6420240402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2374286651611</t>
   </si>
   <si>
     <t xml:space="preserve">14.1335458755493</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8875064849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9203109741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9968566894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8547019958496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6578693389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.439172744751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1767301559448</t>
+    <t xml:space="preserve">13.8875074386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9203119277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9968585968018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8547010421753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6578722000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4391717910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1767272949219</t>
   </si>
   <si>
     <t xml:space="preserve">13.48291015625</t>
@@ -287,19 +287,19 @@
     <t xml:space="preserve">13.0127029418945</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9853677749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6846542358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4768848419189</t>
+    <t xml:space="preserve">12.9853668212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6846523284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4768857955933</t>
   </si>
   <si>
     <t xml:space="preserve">12.219913482666</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3566017150879</t>
+    <t xml:space="preserve">12.3566007614136</t>
   </si>
   <si>
     <t xml:space="preserve">12.1488342285156</t>
@@ -308,49 +308,49 @@
     <t xml:space="preserve">11.8809270858765</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0285520553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0777578353882</t>
+    <t xml:space="preserve">12.0285511016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0777559280396</t>
   </si>
   <si>
     <t xml:space="preserve">11.7551727294922</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9738731384277</t>
+    <t xml:space="preserve">11.9738740921021</t>
   </si>
   <si>
     <t xml:space="preserve">12.3128604888916</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8164319992065</t>
+    <t xml:space="preserve">13.8164291381836</t>
   </si>
   <si>
     <t xml:space="preserve">13.2860803604126</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1220541000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9088191986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0072345733643</t>
+    <t xml:space="preserve">13.1220550537109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9088201522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0072374343872</t>
   </si>
   <si>
     <t xml:space="preserve">12.706521987915</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6299753189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.717456817627</t>
+    <t xml:space="preserve">12.6299772262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7174587249756</t>
   </si>
   <si>
     <t xml:space="preserve">12.5206260681152</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3401985168457</t>
+    <t xml:space="preserve">12.3401956558228</t>
   </si>
   <si>
     <t xml:space="preserve">12.1652374267578</t>
@@ -362,22 +362,22 @@
     <t xml:space="preserve">11.6184844970703</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4763307571411</t>
+    <t xml:space="preserve">11.4763278961182</t>
   </si>
   <si>
     <t xml:space="preserve">11.3451089859009</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0498609542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6403579711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0449504852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9902772903442</t>
+    <t xml:space="preserve">11.0498638153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6403570175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0449533462524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9902753829956</t>
   </si>
   <si>
     <t xml:space="preserve">12.3620681762695</t>
@@ -386,13 +386,13 @@
     <t xml:space="preserve">11.5364723205566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68844890594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77046298980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82513809204102</t>
+    <t xml:space="preserve">9.68844985961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77046203613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8251371383667</t>
   </si>
   <si>
     <t xml:space="preserve">9.92355251312256</t>
@@ -401,19 +401,19 @@
     <t xml:space="preserve">9.93448734283447</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95089054107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45881366729736</t>
+    <t xml:space="preserve">9.95089149475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45881271362305</t>
   </si>
   <si>
     <t xml:space="preserve">9.11982822418213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1088924407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26198482513428</t>
+    <t xml:space="preserve">9.10889148712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26198196411133</t>
   </si>
   <si>
     <t xml:space="preserve">9.2947883605957</t>
@@ -422,28 +422,28 @@
     <t xml:space="preserve">10.3062801361084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7382125854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9350442886353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7819538116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.962381362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7163438796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9459800720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6890048980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.514045715332</t>
+    <t xml:space="preserve">10.7382135391235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9350452423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7819547653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9623823165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.716344833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9459791183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6890077590942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5140438079834</t>
   </si>
   <si>
     <t xml:space="preserve">10.3390855789185</t>
@@ -452,58 +452,58 @@
     <t xml:space="preserve">10.0930461883545</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4703054428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1537446975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8694324493408</t>
+    <t xml:space="preserve">10.4703044891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1537456512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8694334030151</t>
   </si>
   <si>
     <t xml:space="preserve">11.0225248336792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5796546936035</t>
+    <t xml:space="preserve">10.5796556472778</t>
   </si>
   <si>
     <t xml:space="preserve">10.6069936752319</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0443954467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1756162643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8530321121216</t>
+    <t xml:space="preserve">11.0443964004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1756153106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8530330657959</t>
   </si>
   <si>
     <t xml:space="preserve">11.0936031341553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0006551742554</t>
+    <t xml:space="preserve">11.0006542205811</t>
   </si>
   <si>
     <t xml:space="preserve">10.9022397994995</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8366289138794</t>
+    <t xml:space="preserve">10.8366279602051</t>
   </si>
   <si>
     <t xml:space="preserve">10.7436819076538</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4593687057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4484348297119</t>
+    <t xml:space="preserve">10.4593696594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4484367370605</t>
   </si>
   <si>
     <t xml:space="preserve">10.5085783004761</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4976434707642</t>
+    <t xml:space="preserve">10.4976444244385</t>
   </si>
   <si>
     <t xml:space="preserve">10.56325340271</t>
@@ -512,34 +512,34 @@
     <t xml:space="preserve">10.4429683685303</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5851240158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6671352386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6507329940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8803701400757</t>
+    <t xml:space="preserve">10.4374990463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5851249694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6671361923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6507349014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8803682327271</t>
   </si>
   <si>
     <t xml:space="preserve">11.2630977630615</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7223682403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7989149093628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3833818435669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1318769454956</t>
+    <t xml:space="preserve">11.7223701477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7989158630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3833799362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1318759918213</t>
   </si>
   <si>
     <t xml:space="preserve">11.208420753479</t>
@@ -548,37 +548,37 @@
     <t xml:space="preserve">11.1100053787231</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1264066696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0170574188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.202953338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4817972183228</t>
+    <t xml:space="preserve">11.1264095306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0170564651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2029552459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4817991256714</t>
   </si>
   <si>
     <t xml:space="preserve">11.4435243606567</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0990705490112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9569139480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9405136108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9733190536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1428108215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1920156478882</t>
+    <t xml:space="preserve">11.0990686416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9569158554077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9405117034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.973316192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1428098678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1920175552368</t>
   </si>
   <si>
     <t xml:space="preserve">11.4489917755127</t>
@@ -587,103 +587,103 @@
     <t xml:space="preserve">11.8098487854004</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7885341644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0400409698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0673780441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1985988616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2806129455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4938449859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6797428131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7672214508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1663503646851</t>
+    <t xml:space="preserve">12.7885332107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0400419235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0673799514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1985998153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.280611038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4938430786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6797409057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.767219543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1663494110107</t>
   </si>
   <si>
     <t xml:space="preserve">14.2428951263428</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3795824050903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4944000244141</t>
+    <t xml:space="preserve">14.3795871734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4944019317627</t>
   </si>
   <si>
     <t xml:space="preserve">14.4069232940674</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2264976501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.007791519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0241937637329</t>
+    <t xml:space="preserve">14.2264928817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0077934265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0241947174072</t>
   </si>
   <si>
     <t xml:space="preserve">13.8109636306763</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8929748535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8437671661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6906785964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3954296112061</t>
+    <t xml:space="preserve">13.892972946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8437662124634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6906757354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3954305648804</t>
   </si>
   <si>
     <t xml:space="preserve">13.3844938278198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9908332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0291061401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9361591339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8869514465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4222116470337</t>
+    <t xml:space="preserve">12.9908323287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0291042327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9361572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8869495391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4222087860107</t>
   </si>
   <si>
     <t xml:space="preserve">12.4878225326538</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5479640960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1379013061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5753011703491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7940015792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7775983810425</t>
+    <t xml:space="preserve">12.547963142395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.137900352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5753021240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7940006256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7775993347168</t>
   </si>
   <si>
     <t xml:space="preserve">12.6463804244995</t>
@@ -692,70 +692,70 @@
     <t xml:space="preserve">13.4610414505005</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5867919921875</t>
+    <t xml:space="preserve">13.5867948532104</t>
   </si>
   <si>
     <t xml:space="preserve">13.5102472305298</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6688060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2210292816162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9804544448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6961441040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7781572341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0734043121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2155590057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4889326095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8333883285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7513751983643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7076358795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5982866287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1226100921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2702350616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5600128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4342603683472</t>
+    <t xml:space="preserve">13.6688051223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2210264205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9804534912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6961431503296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7781562805176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0734024047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.215558052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4889345169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8333911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7513771057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7076349258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5982828140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1226119995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2702331542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5600099563599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4342594146729</t>
   </si>
   <si>
     <t xml:space="preserve">14.3139724731445</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3631820678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3467807769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1171436309814</t>
+    <t xml:space="preserve">14.3631811141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3467769622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1171455383301</t>
   </si>
   <si>
     <t xml:space="preserve">13.9421834945679</t>
@@ -764,94 +764,94 @@
     <t xml:space="preserve">13.8328332901001</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5485191345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8273658752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7234811782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7016105651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3249092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.051531791687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9531192779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1608810424805</t>
+    <t xml:space="preserve">13.5485210418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8273649215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7234802246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7016096115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3249082565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0515336990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9531164169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1608839035034</t>
   </si>
   <si>
     <t xml:space="preserve">14.6529588699341</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0903625488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0794248580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2653226852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7136611938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1401271820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2658824920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8339462280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8120756149292</t>
+    <t xml:space="preserve">15.0903606414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0794277191162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2653217315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.713659286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1401252746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2658786773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.833945274353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8120765686035</t>
   </si>
   <si>
     <t xml:space="preserve">15.309063911438</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0745143890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1291885375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5119190216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6431369781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7470207214355</t>
+    <t xml:space="preserve">16.0745162963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1291923522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5119171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.643138885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7470188140869</t>
   </si>
   <si>
     <t xml:space="preserve">16.2385444641113</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3424243927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8399696350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0532035827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8350582122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6114444732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8629512786865</t>
+    <t xml:space="preserve">16.3424224853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8399715423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.053201675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8350563049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6114463806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8629493713379</t>
   </si>
   <si>
     <t xml:space="preserve">19.0324478149414</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">19.9345855712891</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5354557037354</t>
+    <t xml:space="preserve">19.5354595184326</t>
   </si>
   <si>
     <t xml:space="preserve">19.8471050262451</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7377548217773</t>
+    <t xml:space="preserve">19.737756729126</t>
   </si>
   <si>
     <t xml:space="preserve">19.6830806732178</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">19.6557426452637</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3440990447998</t>
+    <t xml:space="preserve">19.3440952301025</t>
   </si>
   <si>
     <t xml:space="preserve">19.5737266540527</t>
@@ -884,34 +884,34 @@
     <t xml:space="preserve">19.6448078155518</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8361721038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8197689056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.617467880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0931453704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3829212188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2188968658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1587505340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0111331939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9509925842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2845077514648</t>
+    <t xml:space="preserve">19.8361701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8197708129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6174697875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.093147277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3829231262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.218900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1587543487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0111351013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9509906768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2845058441162</t>
   </si>
   <si>
     <t xml:space="preserve">20.5469493865967</t>
@@ -920,49 +920,49 @@
     <t xml:space="preserve">20.2899761199951</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1975860595703</t>
+    <t xml:space="preserve">21.1975841522217</t>
   </si>
   <si>
     <t xml:space="preserve">21.0718307495117</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9242115020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.159309387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.651388168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8300476074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4950580596924</t>
+    <t xml:space="preserve">20.9242076873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1593112945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6513862609863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8300495147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4950618743896</t>
   </si>
   <si>
     <t xml:space="preserve">21.3163986206055</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4342651367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4739665985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0881118774414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8145389556885</t>
+    <t xml:space="preserve">20.434268951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4739685058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.08811378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8145408630371</t>
   </si>
   <si>
     <t xml:space="preserve">19.6414604187012</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6972904205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5967960357666</t>
+    <t xml:space="preserve">19.6972942352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.596794128418</t>
   </si>
   <si>
     <t xml:space="preserve">18.3685073852539</t>
@@ -971,13 +971,13 @@
     <t xml:space="preserve">17.6929492950439</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6029987335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0049839019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4962978363037</t>
+    <t xml:space="preserve">18.6029968261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0049858093262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4962959289551</t>
   </si>
   <si>
     <t xml:space="preserve">19.4851322174072</t>
@@ -989,13 +989,13 @@
     <t xml:space="preserve">19.4293003082275</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2953071594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3288059234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.843074798584</t>
+    <t xml:space="preserve">19.2953090667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3288040161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8430728912354</t>
   </si>
   <si>
     <t xml:space="preserve">18.6644134521484</t>
@@ -1004,22 +1004,22 @@
     <t xml:space="preserve">18.9268207550049</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2729721069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0943164825439</t>
+    <t xml:space="preserve">19.2729740142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.094310760498</t>
   </si>
   <si>
     <t xml:space="preserve">19.2059764862061</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7531261444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7028751373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3734683990479</t>
+    <t xml:space="preserve">19.7531242370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7028770446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3734741210938</t>
   </si>
   <si>
     <t xml:space="preserve">19.5632972717285</t>
@@ -1031,25 +1031,25 @@
     <t xml:space="preserve">19.7084579467773</t>
   </si>
   <si>
-    <t xml:space="preserve">19.457218170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1780624389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0831470489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0384788513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.501880645752</t>
+    <t xml:space="preserve">19.4572162628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1780586242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0831489562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.038480758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5018825531006</t>
   </si>
   <si>
     <t xml:space="preserve">19.6749610900879</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6526260375977</t>
+    <t xml:space="preserve">19.6526298522949</t>
   </si>
   <si>
     <t xml:space="preserve">19.859203338623</t>
@@ -1058,19 +1058,19 @@
     <t xml:space="preserve">19.9262008666992</t>
   </si>
   <si>
-    <t xml:space="preserve">19.998779296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.920618057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0992774963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2332725524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2667713165283</t>
+    <t xml:space="preserve">19.9987831115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9206218719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0992794036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2332744598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.266773223877</t>
   </si>
   <si>
     <t xml:space="preserve">20.5180149078369</t>
@@ -1079,25 +1079,25 @@
     <t xml:space="preserve">20.7022571563721</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5905914306641</t>
+    <t xml:space="preserve">20.5905933380127</t>
   </si>
   <si>
     <t xml:space="preserve">20.5682601928711</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6017608642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7860012054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0204925537109</t>
+    <t xml:space="preserve">20.6017627716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.786003112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0204963684082</t>
   </si>
   <si>
     <t xml:space="preserve">20.7134208679199</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3833980560303</t>
+    <t xml:space="preserve">21.3833961486816</t>
   </si>
   <si>
     <t xml:space="preserve">21.802131652832</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">21.6625556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1650371551514</t>
+    <t xml:space="preserve">22.1650390625</t>
   </si>
   <si>
     <t xml:space="preserve">22.3604431152344</t>
@@ -1121,22 +1121,22 @@
     <t xml:space="preserve">22.628438949585</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8517665863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1030044555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7233467102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9410915374756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8908443450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4106979370117</t>
+    <t xml:space="preserve">22.8517627716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1030082702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7233505249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9410953521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8908462524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4106941223145</t>
   </si>
   <si>
     <t xml:space="preserve">22.4330253601074</t>
@@ -1145,148 +1145,148 @@
     <t xml:space="preserve">22.9969253540039</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1811695098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1364994049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.706600189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.8796787261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6898517608643</t>
+    <t xml:space="preserve">23.1811656951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1365032196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7066020965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.8796825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6898498535156</t>
   </si>
   <si>
     <t xml:space="preserve">22.6731052398682</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8182640075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6451892852783</t>
+    <t xml:space="preserve">22.8182601928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6451873779297</t>
   </si>
   <si>
     <t xml:space="preserve">22.5000228881836</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0031261444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5670204162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7512683868408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0025081634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3542461395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1700000762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9243431091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5496520996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5217399597168</t>
+    <t xml:space="preserve">22.0031280517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5670223236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7512626647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0025100708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3542442321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1700019836426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9243412017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.549654006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5217342376709</t>
   </si>
   <si>
     <t xml:space="preserve">23.3151607513428</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5105743408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8623104095459</t>
+    <t xml:space="preserve">23.510570526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8623123168945</t>
   </si>
   <si>
     <t xml:space="preserve">24.4708709716797</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4764518737793</t>
+    <t xml:space="preserve">24.4764556884766</t>
   </si>
   <si>
     <t xml:space="preserve">24.9007701873779</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2190113067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1129322052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3083419799805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8728561401367</t>
+    <t xml:space="preserve">25.2190055847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1129283905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3083438873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8728580474854</t>
   </si>
   <si>
     <t xml:space="preserve">25.319507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">25.531665802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8275718688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4193878173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7152862548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8492851257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6042423248291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4137992858887</t>
+    <t xml:space="preserve">25.5316638946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8275737762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4193840026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7152900695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8492889404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6042461395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4138031005859</t>
   </si>
   <si>
     <t xml:space="preserve">27.1284408569336</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4410953521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5025157928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2791900634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7041206359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6321601867676</t>
+    <t xml:space="preserve">27.4410991668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5025119781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2791881561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7041244506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6321620941162</t>
   </si>
   <si>
     <t xml:space="preserve">25.2525081634521</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9057388305664</t>
+    <t xml:space="preserve">25.9057369232178</t>
   </si>
   <si>
     <t xml:space="preserve">25.3585872650146</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2128067016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3021373748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3356323242188</t>
+    <t xml:space="preserve">26.2128047943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3021354675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3356342315674</t>
   </si>
   <si>
     <t xml:space="preserve">26.5031356811523</t>
@@ -1295,10 +1295,10 @@
     <t xml:space="preserve">26.9609470367432</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2407283782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2742233276367</t>
+    <t xml:space="preserve">26.2407245635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2742252349854</t>
   </si>
   <si>
     <t xml:space="preserve">26.1346454620361</t>
@@ -1310,76 +1310,76 @@
     <t xml:space="preserve">25.777322769165</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5260829925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.040355682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6886157989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4156589508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7456855773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8467998504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.729549407959</t>
+    <t xml:space="preserve">25.526086807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0403499603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6886138916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.415657043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7456836700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8467979431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7295513153076</t>
   </si>
   <si>
     <t xml:space="preserve">22.4665260314941</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6234760284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6346416473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2438220977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9255790710449</t>
+    <t xml:space="preserve">21.6234741210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6346397399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2438201904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9255847930908</t>
   </si>
   <si>
     <t xml:space="preserve">21.5843925476074</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3275680541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5229740142822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6960506439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1656551361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.51243019104</t>
+    <t xml:space="preserve">21.3275699615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5229778289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6960544586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1656589508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5124340057373</t>
   </si>
   <si>
     <t xml:space="preserve">20.4845123291016</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6855049133301</t>
+    <t xml:space="preserve">20.6855068206787</t>
   </si>
   <si>
     <t xml:space="preserve">20.7748374938965</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4175128936768</t>
+    <t xml:space="preserve">20.417516708374</t>
   </si>
   <si>
     <t xml:space="preserve">19.8982830047607</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3728542327881</t>
+    <t xml:space="preserve">20.3728504180908</t>
   </si>
   <si>
     <t xml:space="preserve">20.8250846862793</t>
@@ -1391,46 +1391,46 @@
     <t xml:space="preserve">20.1718597412109</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0936946868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0434455871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6687564849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6123046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7624340057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.936128616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2208709716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6116886138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6228504180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3213634490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3883590698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2717342376709</t>
+    <t xml:space="preserve">20.0936965942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0434474945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.668758392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6123104095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7624320983887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9361305236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2208671569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6116847991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6228561401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3213653564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3883609771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2717361450195</t>
   </si>
   <si>
     <t xml:space="preserve">21.9193782806396</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0422077178955</t>
+    <t xml:space="preserve">22.0422058105469</t>
   </si>
   <si>
     <t xml:space="preserve">21.7630519866943</t>
@@ -1439,85 +1439,85 @@
     <t xml:space="preserve">21.9417114257812</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8523788452148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6848850250244</t>
+    <t xml:space="preserve">21.8523826599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6848888397217</t>
   </si>
   <si>
     <t xml:space="preserve">21.4392318725586</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4168949127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.204740524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8412132263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3722305297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0149116516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1997756958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7419567108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2444381713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7034969329834</t>
+    <t xml:space="preserve">21.4168968200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2047367095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.841215133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3722324371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.01491355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1997699737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7419586181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2444400787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7034931182861</t>
   </si>
   <si>
     <t xml:space="preserve">18.4913349151611</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7754535675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1439418792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9094486236572</t>
+    <t xml:space="preserve">19.7754573822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1439456939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9094524383545</t>
   </si>
   <si>
     <t xml:space="preserve">20.3449363708496</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3337669372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3002681732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2556056976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3672695159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0322818756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7977867126465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6861228942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0496482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.402006149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.100513458252</t>
+    <t xml:space="preserve">20.3337707519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3002700805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2556076049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3672676086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0322780609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7977848052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6861267089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0496463775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4020080566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1005153656006</t>
   </si>
   <si>
     <t xml:space="preserve">18.424337387085</t>
@@ -1526,55 +1526,55 @@
     <t xml:space="preserve">18.1786804199219</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1675186157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1054840087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0273170471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9330234527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4640407562256</t>
+    <t xml:space="preserve">18.1675148010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1054801940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0273151397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9330215454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.464038848877</t>
   </si>
   <si>
     <t xml:space="preserve">17.6315326690674</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5025024414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3350086212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0781879425049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4417057037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5260772705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7990264892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.095552444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.821361541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2010135650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3461761474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4801692962646</t>
+    <t xml:space="preserve">18.5025005340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3350067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0781841278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.441707611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5260753631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7990283966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0955505371094</t>
+  </si>
+  <si>
+    <t xml